--- a/data/UD.MI.xlsx
+++ b/data/UD.MI.xlsx
@@ -38322,6 +38322,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1651">
+      <c r="A1651" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B1651" t="n">
+        <v>80288</v>
+      </c>
+      <c r="C1651" t="n">
+        <v>3.46000003814697</v>
+      </c>
+      <c r="D1651" t="n">
+        <v>3.36999988555908</v>
+      </c>
+      <c r="E1651" t="n">
+        <v>3.39499998092651</v>
+      </c>
+      <c r="F1651" t="n">
+        <v>3.36999988555908</v>
+      </c>
+      <c r="G1651" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/UD.MI.xlsx
+++ b/data/UD.MI.xlsx
@@ -38345,6 +38345,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1652">
+      <c r="A1652" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B1652" t="n">
+        <v>80406</v>
+      </c>
+      <c r="C1652" t="n">
+        <v>3.4300000667572</v>
+      </c>
+      <c r="D1652" t="n">
+        <v>3.30999994277954</v>
+      </c>
+      <c r="E1652" t="n">
+        <v>3.38000011444092</v>
+      </c>
+      <c r="F1652" t="n">
+        <v>3.41499996185303</v>
+      </c>
+      <c r="G1652" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/UD.MI.xlsx
+++ b/data/UD.MI.xlsx
@@ -38368,6 +38368,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1653">
+      <c r="A1653" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B1653" t="n">
+        <v>87281</v>
+      </c>
+      <c r="C1653" t="n">
+        <v>3.48000001907349</v>
+      </c>
+      <c r="D1653" t="n">
+        <v>3.29999995231628</v>
+      </c>
+      <c r="E1653" t="n">
+        <v>3.29999995231628</v>
+      </c>
+      <c r="F1653" t="n">
+        <v>3.40499997138977</v>
+      </c>
+      <c r="G1653" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/UD.MI.xlsx
+++ b/data/UD.MI.xlsx
@@ -38391,6 +38391,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1654">
+      <c r="A1654" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B1654" t="n">
+        <v>52037</v>
+      </c>
+      <c r="C1654" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D1654" t="n">
+        <v>3.41499996185303</v>
+      </c>
+      <c r="E1654" t="n">
+        <v>3.49499988555908</v>
+      </c>
+      <c r="F1654" t="n">
+        <v>3.47000002861023</v>
+      </c>
+      <c r="G1654" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/UD.MI.xlsx
+++ b/data/UD.MI.xlsx
@@ -38232,22 +38232,22 @@
     </row>
     <row r="1647">
       <c r="A1647" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B1647" t="n">
-        <v>64520</v>
+        <v>68696</v>
       </c>
       <c r="C1647" t="n">
-        <v>3.3199999332428</v>
+        <v>3.28999996185303</v>
       </c>
       <c r="D1647" t="n">
-        <v>3.22000002861023</v>
+        <v>3.1949999332428</v>
       </c>
       <c r="E1647" t="n">
-        <v>3.26999998092651</v>
+        <v>3.20000004768372</v>
       </c>
       <c r="F1647" t="n">
-        <v>3.28500008583069</v>
+        <v>3.23000001907349</v>
       </c>
       <c r="G1647" t="s">
         <v>7</v>
@@ -38255,22 +38255,22 @@
     </row>
     <row r="1648">
       <c r="A1648" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B1648" t="n">
-        <v>110943</v>
+        <v>64520</v>
       </c>
       <c r="C1648" t="n">
-        <v>3.375</v>
+        <v>3.3199999332428</v>
       </c>
       <c r="D1648" t="n">
-        <v>3.28999996185303</v>
+        <v>3.22000002861023</v>
       </c>
       <c r="E1648" t="n">
-        <v>3.33999991416931</v>
+        <v>3.26999998092651</v>
       </c>
       <c r="F1648" t="n">
-        <v>3.3050000667572</v>
+        <v>3.28500008583069</v>
       </c>
       <c r="G1648" t="s">
         <v>7</v>
@@ -38278,22 +38278,22 @@
     </row>
     <row r="1649">
       <c r="A1649" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B1649" t="n">
-        <v>97669</v>
+        <v>110943</v>
       </c>
       <c r="C1649" t="n">
-        <v>3.43499994277954</v>
+        <v>3.375</v>
       </c>
       <c r="D1649" t="n">
-        <v>3.31500005722046</v>
+        <v>3.28999996185303</v>
       </c>
       <c r="E1649" t="n">
-        <v>3.32999992370605</v>
+        <v>3.33999991416931</v>
       </c>
       <c r="F1649" t="n">
-        <v>3.38000011444092</v>
+        <v>3.3050000667572</v>
       </c>
       <c r="G1649" t="s">
         <v>7</v>
@@ -38301,22 +38301,22 @@
     </row>
     <row r="1650">
       <c r="A1650" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B1650" t="n">
-        <v>101844</v>
+        <v>97669</v>
       </c>
       <c r="C1650" t="n">
-        <v>3.39499998092651</v>
+        <v>3.43499994277954</v>
       </c>
       <c r="D1650" t="n">
-        <v>3.25999999046326</v>
+        <v>3.31500005722046</v>
       </c>
       <c r="E1650" t="n">
-        <v>3.29500007629395</v>
+        <v>3.32999992370605</v>
       </c>
       <c r="F1650" t="n">
-        <v>3.39000010490417</v>
+        <v>3.38000011444092</v>
       </c>
       <c r="G1650" t="s">
         <v>7</v>
@@ -38324,22 +38324,22 @@
     </row>
     <row r="1651">
       <c r="A1651" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B1651" t="n">
-        <v>80288</v>
+        <v>101844</v>
       </c>
       <c r="C1651" t="n">
-        <v>3.46000003814697</v>
+        <v>3.39499998092651</v>
       </c>
       <c r="D1651" t="n">
-        <v>3.36999988555908</v>
+        <v>3.25999999046326</v>
       </c>
       <c r="E1651" t="n">
-        <v>3.39499998092651</v>
+        <v>3.29500007629395</v>
       </c>
       <c r="F1651" t="n">
-        <v>3.36999988555908</v>
+        <v>3.39000010490417</v>
       </c>
       <c r="G1651" t="s">
         <v>7</v>
@@ -38347,22 +38347,22 @@
     </row>
     <row r="1652">
       <c r="A1652" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B1652" t="n">
-        <v>80406</v>
+        <v>80288</v>
       </c>
       <c r="C1652" t="n">
-        <v>3.4300000667572</v>
+        <v>3.46000003814697</v>
       </c>
       <c r="D1652" t="n">
-        <v>3.30999994277954</v>
+        <v>3.36999988555908</v>
       </c>
       <c r="E1652" t="n">
-        <v>3.38000011444092</v>
+        <v>3.39499998092651</v>
       </c>
       <c r="F1652" t="n">
-        <v>3.41499996185303</v>
+        <v>3.36999988555908</v>
       </c>
       <c r="G1652" t="s">
         <v>7</v>
@@ -38370,22 +38370,22 @@
     </row>
     <row r="1653">
       <c r="A1653" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B1653" t="n">
-        <v>87281</v>
+        <v>80406</v>
       </c>
       <c r="C1653" t="n">
-        <v>3.48000001907349</v>
+        <v>3.4300000667572</v>
       </c>
       <c r="D1653" t="n">
-        <v>3.29999995231628</v>
+        <v>3.30999994277954</v>
       </c>
       <c r="E1653" t="n">
-        <v>3.29999995231628</v>
+        <v>3.38000011444092</v>
       </c>
       <c r="F1653" t="n">
-        <v>3.40499997138977</v>
+        <v>3.41499996185303</v>
       </c>
       <c r="G1653" t="s">
         <v>7</v>
@@ -38393,24 +38393,47 @@
     </row>
     <row r="1654">
       <c r="A1654" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B1654" t="n">
-        <v>52037</v>
+        <v>87281</v>
       </c>
       <c r="C1654" t="n">
-        <v>3.5</v>
+        <v>3.48000001907349</v>
       </c>
       <c r="D1654" t="n">
-        <v>3.41499996185303</v>
+        <v>3.29999995231628</v>
       </c>
       <c r="E1654" t="n">
-        <v>3.49499988555908</v>
+        <v>3.29999995231628</v>
       </c>
       <c r="F1654" t="n">
-        <v>3.47000002861023</v>
+        <v>3.40499997138977</v>
       </c>
       <c r="G1654" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1655">
+      <c r="A1655" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B1655" t="n">
+        <v>56733</v>
+      </c>
+      <c r="C1655" t="n">
+        <v>3.5699999332428</v>
+      </c>
+      <c r="D1655" t="n">
+        <v>3.41000008583069</v>
+      </c>
+      <c r="E1655" t="n">
+        <v>3.41000008583069</v>
+      </c>
+      <c r="F1655" t="n">
+        <v>3.4449999332428</v>
+      </c>
+      <c r="G1655" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/UD.MI.xlsx
+++ b/data/UD.MI.xlsx
@@ -421,7 +421,7 @@
         <v>1.5</v>
       </c>
       <c r="G2" t="n">
-        <v>1.47885513305664</v>
+        <v>1.47885501384735</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G5" t="n">
-        <v>1.50843226909637</v>
+        <v>1.50843238830566</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>1.56500005722046</v>
       </c>
       <c r="G6" t="n">
-        <v>1.5429390668869</v>
+        <v>1.54293882846832</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G9" t="n">
-        <v>1.55772745609283</v>
+        <v>1.55772757530212</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G11" t="n">
-        <v>1.56265711784363</v>
+        <v>1.56265699863434</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G13" t="n">
-        <v>1.55772745609283</v>
+        <v>1.55772757530212</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G17" t="n">
-        <v>1.66617691516876</v>
+        <v>1.66617703437805</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G18" t="n">
-        <v>1.67603588104248</v>
+        <v>1.67603600025177</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G19" t="n">
-        <v>1.67603588104248</v>
+        <v>1.67603600025177</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G25" t="n">
-        <v>1.58730459213257</v>
+        <v>1.58730471134186</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G31" t="n">
-        <v>1.63659965991974</v>
+        <v>1.63659977912903</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G33" t="n">
-        <v>1.61688148975372</v>
+        <v>1.61688160896301</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G37" t="n">
-        <v>1.70561301708221</v>
+        <v>1.70561289787292</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G38" t="n">
-        <v>1.70561301708221</v>
+        <v>1.70561289787292</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G39" t="n">
-        <v>1.67110645771027</v>
+        <v>1.67110633850098</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G40" t="n">
-        <v>1.69575381278992</v>
+        <v>1.69575393199921</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G41" t="n">
-        <v>1.6858948469162</v>
+        <v>1.68589496612549</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G45" t="n">
-        <v>1.66617691516876</v>
+        <v>1.66617703437805</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G46" t="n">
-        <v>1.67603588104248</v>
+        <v>1.67603600025177</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G50" t="n">
-        <v>1.74997866153717</v>
+        <v>1.74997878074646</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G52" t="n">
-        <v>1.74011969566345</v>
+        <v>1.74011981487274</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>1.74500000476837</v>
       </c>
       <c r="G53" t="n">
-        <v>1.72040164470673</v>
+        <v>1.72040152549744</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G56" t="n">
-        <v>1.69575381278992</v>
+        <v>1.69575393199921</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G57" t="n">
-        <v>1.67603588104248</v>
+        <v>1.67603600025177</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G66" t="n">
-        <v>1.67603588104248</v>
+        <v>1.67603600025177</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G67" t="n">
-        <v>1.66617691516876</v>
+        <v>1.66617703437805</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G68" t="n">
-        <v>1.6858948469162</v>
+        <v>1.68589496612549</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G76" t="n">
-        <v>1.67110645771027</v>
+        <v>1.67110633850098</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G77" t="n">
-        <v>1.6858948469162</v>
+        <v>1.68589496612549</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G79" t="n">
-        <v>1.67603588104248</v>
+        <v>1.67603600025177</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G80" t="n">
-        <v>1.67603588104248</v>
+        <v>1.67603600025177</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G81" t="n">
-        <v>1.67603588104248</v>
+        <v>1.67603600025177</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G84" t="n">
-        <v>1.63659965991974</v>
+        <v>1.63659977912903</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G95" t="n">
-        <v>1.58730459213257</v>
+        <v>1.58730471134186</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G97" t="n">
-        <v>1.58730459213257</v>
+        <v>1.58730471134186</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G98" t="n">
-        <v>1.58730459213257</v>
+        <v>1.58730471134186</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G103" t="n">
-        <v>1.63659965991974</v>
+        <v>1.63659977912903</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G104" t="n">
-        <v>1.63659965991974</v>
+        <v>1.63659977912903</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>1.63499999046326</v>
       </c>
       <c r="G105" t="n">
-        <v>1.61195206642151</v>
+        <v>1.6119521856308</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G109" t="n">
-        <v>1.66617691516876</v>
+        <v>1.66617703437805</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G110" t="n">
-        <v>1.67603588104248</v>
+        <v>1.67603600025177</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G111" t="n">
-        <v>1.67603588104248</v>
+        <v>1.67603600025177</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G112" t="n">
-        <v>1.67603588104248</v>
+        <v>1.67603600025177</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G113" t="n">
-        <v>1.67603588104248</v>
+        <v>1.67603600025177</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G114" t="n">
-        <v>1.67603588104248</v>
+        <v>1.67603600025177</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G115" t="n">
-        <v>1.67603588104248</v>
+        <v>1.67603600025177</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G117" t="n">
-        <v>1.6858948469162</v>
+        <v>1.68589496612549</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G118" t="n">
-        <v>1.6858948469162</v>
+        <v>1.68589496612549</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G124" t="n">
-        <v>1.85349833965302</v>
+        <v>1.8534984588623</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G126" t="n">
-        <v>1.83378040790558</v>
+        <v>1.83378028869629</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G127" t="n">
-        <v>1.82392144203186</v>
+        <v>1.82392132282257</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G128" t="n">
-        <v>1.82392144203186</v>
+        <v>1.82392132282257</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G129" t="n">
-        <v>1.82392144203186</v>
+        <v>1.82392132282257</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G131" t="n">
-        <v>1.83378040790558</v>
+        <v>1.83378028869629</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G133" t="n">
-        <v>1.85349833965302</v>
+        <v>1.8534984588623</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G134" t="n">
-        <v>1.85349833965302</v>
+        <v>1.8534984588623</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G135" t="n">
-        <v>1.85349833965302</v>
+        <v>1.8534984588623</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G141" t="n">
-        <v>1.82392144203186</v>
+        <v>1.82392132282257</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G142" t="n">
-        <v>1.82392144203186</v>
+        <v>1.82392132282257</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G143" t="n">
-        <v>1.79927396774292</v>
+        <v>1.79927384853363</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G151" t="n">
-        <v>1.74011969566345</v>
+        <v>1.74011981487274</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G155" t="n">
-        <v>1.82392144203186</v>
+        <v>1.82392132282257</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G156" t="n">
-        <v>1.82392144203186</v>
+        <v>1.82392132282257</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G158" t="n">
-        <v>1.83378040790558</v>
+        <v>1.83378028869629</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G168" t="n">
-        <v>1.74997866153717</v>
+        <v>1.74997878074646</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G172" t="n">
-        <v>1.81406259536743</v>
+        <v>1.81406247615814</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G184" t="n">
-        <v>2.01124310493469</v>
+        <v>2.01124286651611</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G188" t="n">
-        <v>2.01124310493469</v>
+        <v>2.01124286651611</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G189" t="n">
-        <v>2.01124310493469</v>
+        <v>2.01124286651611</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G190" t="n">
-        <v>1.91758215427399</v>
+        <v>1.91758227348328</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G194" t="n">
-        <v>1.92251181602478</v>
+        <v>1.92251169681549</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G199" t="n">
-        <v>1.91758215427399</v>
+        <v>1.91758227348328</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G200" t="n">
-        <v>1.92251181602478</v>
+        <v>1.92251169681549</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G204" t="n">
-        <v>1.92251181602478</v>
+        <v>1.92251169681549</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>1.9650000333786</v>
       </c>
       <c r="G209" t="n">
-        <v>1.93730020523071</v>
+        <v>1.93730032444</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G211" t="n">
-        <v>1.94715929031372</v>
+        <v>1.94715940952301</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G212" t="n">
-        <v>1.94222986698151</v>
+        <v>1.9422299861908</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G213" t="n">
-        <v>1.92251181602478</v>
+        <v>1.92251169681549</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G214" t="n">
-        <v>1.92251181602478</v>
+        <v>1.92251169681549</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G221" t="n">
-        <v>1.92251181602478</v>
+        <v>1.92251169681549</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G222" t="n">
-        <v>1.92251181602478</v>
+        <v>1.92251169681549</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G223" t="n">
-        <v>1.92251181602478</v>
+        <v>1.92251169681549</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G224" t="n">
-        <v>1.92251181602478</v>
+        <v>1.92251169681549</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G225" t="n">
-        <v>1.94222986698151</v>
+        <v>1.9422299861908</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G229" t="n">
-        <v>2.08025622367859</v>
+        <v>2.08025598526001</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G231" t="n">
-        <v>2.22814130783081</v>
+        <v>2.22814178466797</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>2.25</v>
       </c>
       <c r="G233" t="n">
-        <v>2.21828269958496</v>
+        <v>2.21828293800354</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G235" t="n">
-        <v>2.14926981925964</v>
+        <v>2.14926958084106</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>2.25</v>
       </c>
       <c r="G239" t="n">
-        <v>2.21828269958496</v>
+        <v>2.21828293800354</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G241" t="n">
-        <v>2.22814130783081</v>
+        <v>2.22814178466797</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G246" t="n">
-        <v>2.28729581832886</v>
+        <v>2.28729605674744</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G247" t="n">
-        <v>2.28729581832886</v>
+        <v>2.28729605674744</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G253" t="n">
-        <v>2.40560436248779</v>
+        <v>2.40560460090637</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G260" t="n">
-        <v>2.74081182479858</v>
+        <v>2.74081158638</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G262" t="n">
-        <v>2.78024768829346</v>
+        <v>2.78024744987488</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G263" t="n">
-        <v>2.9774284362793</v>
+        <v>2.97742819786072</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>3</v>
       </c>
       <c r="G265" t="n">
-        <v>2.95771026611328</v>
+        <v>2.9577100276947</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G272" t="n">
-        <v>2.99714660644531</v>
+        <v>2.99714636802673</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G277" t="n">
-        <v>3.17460918426514</v>
+        <v>3.17460942268372</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G278" t="n">
-        <v>3.18446850776672</v>
+        <v>3.18446826934814</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G281" t="n">
-        <v>3.18446850776672</v>
+        <v>3.18446826934814</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G285" t="n">
-        <v>3.35207176208496</v>
+        <v>3.35207200050354</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G286" t="n">
-        <v>3.49995732307434</v>
+        <v>3.49995756149292</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G292" t="n">
-        <v>3.64784288406372</v>
+        <v>3.64784264564514</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G293" t="n">
-        <v>3.64784288406372</v>
+        <v>3.64784264564514</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G297" t="n">
-        <v>3.55911111831665</v>
+        <v>3.55911135673523</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G299" t="n">
-        <v>3.49995732307434</v>
+        <v>3.49995756149292</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G300" t="n">
-        <v>3.4802393913269</v>
+        <v>3.48023962974548</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G302" t="n">
-        <v>3.49995732307434</v>
+        <v>3.49995756149292</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G307" t="n">
-        <v>3.97319078445435</v>
+        <v>3.9731912612915</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G308" t="n">
-        <v>4.26896142959595</v>
+        <v>4.26896190643311</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G311" t="n">
-        <v>4.14079427719116</v>
+        <v>4.14079475402832</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G312" t="n">
-        <v>3.99290943145752</v>
+        <v>3.99290895462036</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G314" t="n">
-        <v>4.05206346511841</v>
+        <v>4.05206394195557</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G317" t="n">
-        <v>4.14079427719116</v>
+        <v>4.14079475402832</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G318" t="n">
-        <v>4.17037105560303</v>
+        <v>4.17037153244019</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G323" t="n">
-        <v>4.18023061752319</v>
+        <v>4.18023014068604</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G324" t="n">
-        <v>4.18023061752319</v>
+        <v>4.18023014068604</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G327" t="n">
-        <v>4.16051244735718</v>
+        <v>4.16051197052002</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G328" t="n">
-        <v>4.16051244735718</v>
+        <v>4.16051197052002</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G329" t="n">
-        <v>4.02248620986938</v>
+        <v>4.02248573303223</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G333" t="n">
-        <v>4.16051244735718</v>
+        <v>4.16051197052002</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G334" t="n">
-        <v>4.16051244735718</v>
+        <v>4.16051197052002</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G335" t="n">
-        <v>4.17037105560303</v>
+        <v>4.17037153244019</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G338" t="n">
-        <v>4.16051244735718</v>
+        <v>4.16051197052002</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G339" t="n">
-        <v>4.16051244735718</v>
+        <v>4.16051197052002</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G340" t="n">
-        <v>4.14079427719116</v>
+        <v>4.14079475402832</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G341" t="n">
-        <v>4.14079427719116</v>
+        <v>4.14079475402832</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G343" t="n">
-        <v>4.14079427719116</v>
+        <v>4.14079475402832</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G344" t="n">
-        <v>4.1112174987793</v>
+        <v>4.11121797561646</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G347" t="n">
-        <v>4.02248620986938</v>
+        <v>4.02248573303223</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G348" t="n">
-        <v>4.02248620986938</v>
+        <v>4.02248573303223</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G349" t="n">
-        <v>4.21966743469238</v>
+        <v>4.21966648101807</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G356" t="n">
-        <v>4.14079427719116</v>
+        <v>4.14079475402832</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G357" t="n">
-        <v>4.05206346511841</v>
+        <v>4.05206394195557</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G359" t="n">
-        <v>4.21966743469238</v>
+        <v>4.21966648101807</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G366" t="n">
-        <v>4.14079427719116</v>
+        <v>4.14079475402832</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G367" t="n">
-        <v>4.14079427719116</v>
+        <v>4.14079475402832</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G368" t="n">
-        <v>4.14079427719116</v>
+        <v>4.14079475402832</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G371" t="n">
-        <v>4.01262712478638</v>
+        <v>4.01262760162354</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G373" t="n">
-        <v>4.14079427719116</v>
+        <v>4.14079475402832</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G374" t="n">
-        <v>4.14079427719116</v>
+        <v>4.14079475402832</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G375" t="n">
-        <v>4.14079427719116</v>
+        <v>4.14079475402832</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G377" t="n">
-        <v>4.22952508926392</v>
+        <v>4.22952556610107</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G378" t="n">
-        <v>4.27882146835327</v>
+        <v>4.27882099151611</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G379" t="n">
-        <v>4.21966743469238</v>
+        <v>4.21966648101807</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G380" t="n">
-        <v>4.21966743469238</v>
+        <v>4.21966648101807</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G381" t="n">
-        <v>4.25910329818726</v>
+        <v>4.2591028213501</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G382" t="n">
-        <v>4.29853963851929</v>
+        <v>4.29853916168213</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G389" t="n">
-        <v>4.26896142959595</v>
+        <v>4.26896190643311</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G396" t="n">
-        <v>4.22952508926392</v>
+        <v>4.22952556610107</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G401" t="n">
-        <v>4.18023061752319</v>
+        <v>4.18023014068604</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G403" t="n">
-        <v>4.29853963851929</v>
+        <v>4.29853916168213</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G405" t="n">
-        <v>4.38727045059204</v>
+        <v>4.38726997375488</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G407" t="n">
-        <v>4.38727045059204</v>
+        <v>4.38726997375488</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G408" t="n">
-        <v>4.38727045059204</v>
+        <v>4.38726997375488</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G409" t="n">
-        <v>4.49571943283081</v>
+        <v>4.49571990966797</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G411" t="n">
-        <v>5.0478253364563</v>
+        <v>5.04782485961914</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G412" t="n">
-        <v>5.30416059494019</v>
+        <v>5.30416011810303</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G413" t="n">
-        <v>5.24500703811646</v>
+        <v>5.2450065612793</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G418" t="n">
-        <v>4.98867177963257</v>
+        <v>4.98867130279541</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G420" t="n">
-        <v>5.00838947296143</v>
+        <v>5.00838994979858</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G428" t="n">
-        <v>5.00838947296143</v>
+        <v>5.00838994979858</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G431" t="n">
-        <v>4.98867177963257</v>
+        <v>4.98867130279541</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G437" t="n">
-        <v>4.90979957580566</v>
+        <v>4.90979909896851</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G442" t="n">
-        <v>4.90979957580566</v>
+        <v>4.90979909896851</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G443" t="n">
-        <v>5.0478253364563</v>
+        <v>5.04782485961914</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G450" t="n">
-        <v>4.8309268951416</v>
+        <v>4.83092641830444</v>
       </c>
       <c r="H450" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G451" t="n">
-        <v>4.8309268951416</v>
+        <v>4.83092641830444</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G457" t="n">
-        <v>5.0478253364563</v>
+        <v>5.04782485961914</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G461" t="n">
-        <v>5.30416059494019</v>
+        <v>5.30416011810303</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G464" t="n">
-        <v>5.0478253364563</v>
+        <v>5.04782485961914</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G465" t="n">
-        <v>5.16613435745239</v>
+        <v>5.16613388061523</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G468" t="n">
-        <v>5.16613435745239</v>
+        <v>5.16613388061523</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G474" t="n">
-        <v>4.98867177963257</v>
+        <v>4.98867130279541</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G477" t="n">
-        <v>5.00838947296143</v>
+        <v>5.00838994979858</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G486" t="n">
-        <v>5.0478253364563</v>
+        <v>5.04782485961914</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G487" t="n">
-        <v>5.16613435745239</v>
+        <v>5.16613388061523</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13083,7 +13083,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G489" t="n">
-        <v>4.98867177963257</v>
+        <v>4.98867130279541</v>
       </c>
       <c r="H489" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G491" t="n">
-        <v>4.98867177963257</v>
+        <v>4.98867130279541</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G493" t="n">
-        <v>5.16613435745239</v>
+        <v>5.16613388061523</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G497" t="n">
-        <v>4.87036323547363</v>
+        <v>4.87036275863647</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G500" t="n">
-        <v>5.0478253364563</v>
+        <v>5.04782485961914</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G504" t="n">
-        <v>4.8309268951416</v>
+        <v>4.83092641830444</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G505" t="n">
-        <v>4.98867177963257</v>
+        <v>4.98867130279541</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G510" t="n">
-        <v>4.98867177963257</v>
+        <v>4.98867130279541</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G513" t="n">
-        <v>5.00838947296143</v>
+        <v>5.00838994979858</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13785,7 +13785,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G516" t="n">
-        <v>5.00838947296143</v>
+        <v>5.00838994979858</v>
       </c>
       <c r="H516" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G518" t="n">
-        <v>5.00838947296143</v>
+        <v>5.00838994979858</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G522" t="n">
-        <v>5.0478253364563</v>
+        <v>5.04782485961914</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G526" t="n">
-        <v>5.00838947296143</v>
+        <v>5.00838994979858</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G529" t="n">
-        <v>4.77177238464355</v>
+        <v>4.77177286148071</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14201,7 +14201,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G532" t="n">
-        <v>4.77177238464355</v>
+        <v>4.77177286148071</v>
       </c>
       <c r="H532" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G536" t="n">
-        <v>4.71261835098267</v>
+        <v>4.71261882781982</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G540" t="n">
-        <v>4.8309268951416</v>
+        <v>4.83092641830444</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G545" t="n">
-        <v>4.8309268951416</v>
+        <v>4.83092641830444</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G546" t="n">
-        <v>4.75205421447754</v>
+        <v>4.7520546913147</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G547" t="n">
-        <v>4.62362098693848</v>
+        <v>4.62362051010132</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G550" t="n">
-        <v>4.6433801651001</v>
+        <v>4.64337968826294</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G551" t="n">
-        <v>4.7421760559082</v>
+        <v>4.74217557907104</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G552" t="n">
-        <v>4.78169393539429</v>
+        <v>4.78169345855713</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G553" t="n">
-        <v>4.78169393539429</v>
+        <v>4.78169345855713</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G554" t="n">
-        <v>4.78169393539429</v>
+        <v>4.78169345855713</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G556" t="n">
-        <v>4.7421760559082</v>
+        <v>4.74217557907104</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G557" t="n">
-        <v>4.7421760559082</v>
+        <v>4.74217557907104</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G563" t="n">
-        <v>4.84097099304199</v>
+        <v>4.84097051620483</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G564" t="n">
-        <v>4.84097099304199</v>
+        <v>4.84097051620483</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G565" t="n">
-        <v>4.84097099304199</v>
+        <v>4.84097051620483</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G566" t="n">
-        <v>4.84097099304199</v>
+        <v>4.84097051620483</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G571" t="n">
-        <v>4.84097099304199</v>
+        <v>4.84097051620483</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15423,7 +15423,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G579" t="n">
-        <v>4.27783727645874</v>
+        <v>4.2778377532959</v>
       </c>
       <c r="H579" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G581" t="n">
-        <v>4.40627193450928</v>
+        <v>4.40627145767212</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G583" t="n">
-        <v>4.6433801651001</v>
+        <v>4.64337968826294</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G584" t="n">
-        <v>4.78169393539429</v>
+        <v>4.78169345855713</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G586" t="n">
-        <v>4.7421760559082</v>
+        <v>4.74217557907104</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G588" t="n">
-        <v>4.4951868057251</v>
+        <v>4.49518728256226</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G590" t="n">
-        <v>4.3865122795105</v>
+        <v>4.38651180267334</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G594" t="n">
-        <v>4.48530769348145</v>
+        <v>4.48530721664429</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G595" t="n">
-        <v>4.35687398910522</v>
+        <v>4.35687351226807</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G597" t="n">
-        <v>4.40627193450928</v>
+        <v>4.40627145767212</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G598" t="n">
-        <v>4.4951868057251</v>
+        <v>4.49518728256226</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G600" t="n">
-        <v>4.48530769348145</v>
+        <v>4.48530721664429</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -15995,7 +15995,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G601" t="n">
-        <v>4.54458475112915</v>
+        <v>4.54458427429199</v>
       </c>
       <c r="H601" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G603" t="n">
-        <v>4.6433801651001</v>
+        <v>4.64337968826294</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G604" t="n">
-        <v>4.84097099304199</v>
+        <v>4.84097051620483</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G606" t="n">
-        <v>4.89036798477173</v>
+        <v>4.89036846160889</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G610" t="n">
-        <v>4.84097099304199</v>
+        <v>4.84097051620483</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -16307,7 +16307,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G613" t="n">
-        <v>4.78169393539429</v>
+        <v>4.78169345855713</v>
       </c>
       <c r="H613" t="s">
         <v>8</v>
@@ -16333,7 +16333,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G614" t="n">
-        <v>4.84097099304199</v>
+        <v>4.84097051620483</v>
       </c>
       <c r="H614" t="s">
         <v>8</v>
@@ -16359,7 +16359,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G615" t="n">
-        <v>4.88048887252808</v>
+        <v>4.88048839569092</v>
       </c>
       <c r="H615" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G620" t="n">
-        <v>4.99904346466064</v>
+        <v>4.99904298782349</v>
       </c>
       <c r="H620" t="s">
         <v>8</v>
@@ -16905,7 +16905,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G636" t="n">
-        <v>4.89036798477173</v>
+        <v>4.89036846160889</v>
       </c>
       <c r="H636" t="s">
         <v>8</v>
@@ -16931,7 +16931,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G637" t="n">
-        <v>4.88048887252808</v>
+        <v>4.88048839569092</v>
       </c>
       <c r="H637" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G638" t="n">
-        <v>4.88048887252808</v>
+        <v>4.88048839569092</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -17087,7 +17087,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G643" t="n">
-        <v>4.73229551315308</v>
+        <v>4.73229598999023</v>
       </c>
       <c r="H643" t="s">
         <v>8</v>
@@ -17113,7 +17113,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G644" t="n">
-        <v>4.54458475112915</v>
+        <v>4.54458427429199</v>
       </c>
       <c r="H644" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G645" t="n">
-        <v>4.4951868057251</v>
+        <v>4.49518728256226</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17269,7 +17269,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G650" t="n">
-        <v>4.52482604980469</v>
+        <v>4.52482557296753</v>
       </c>
       <c r="H650" t="s">
         <v>8</v>
@@ -17399,7 +17399,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G655" t="n">
-        <v>4.84097099304199</v>
+        <v>4.84097051620483</v>
       </c>
       <c r="H655" t="s">
         <v>8</v>
@@ -17503,7 +17503,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G659" t="n">
-        <v>4.7421760559082</v>
+        <v>4.74217557907104</v>
       </c>
       <c r="H659" t="s">
         <v>8</v>
@@ -17529,7 +17529,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G660" t="n">
-        <v>4.7421760559082</v>
+        <v>4.74217557907104</v>
       </c>
       <c r="H660" t="s">
         <v>8</v>
@@ -17555,7 +17555,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G661" t="n">
-        <v>4.88048887252808</v>
+        <v>4.88048839569092</v>
       </c>
       <c r="H661" t="s">
         <v>8</v>
@@ -17581,7 +17581,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G662" t="n">
-        <v>4.7421760559082</v>
+        <v>4.74217557907104</v>
       </c>
       <c r="H662" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G677" t="n">
-        <v>4.89036798477173</v>
+        <v>4.89036846160889</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G678" t="n">
-        <v>4.7421760559082</v>
+        <v>4.74217557907104</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18049,7 +18049,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G680" t="n">
-        <v>4.73229551315308</v>
+        <v>4.73229598999023</v>
       </c>
       <c r="H680" t="s">
         <v>8</v>
@@ -18153,7 +18153,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G684" t="n">
-        <v>4.52482604980469</v>
+        <v>4.52482557296753</v>
       </c>
       <c r="H684" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G695" t="n">
-        <v>4.99904346466064</v>
+        <v>4.99904298782349</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18673,7 +18673,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G704" t="n">
-        <v>4.7421760559082</v>
+        <v>4.74217557907104</v>
       </c>
       <c r="H704" t="s">
         <v>8</v>
@@ -18699,7 +18699,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G705" t="n">
-        <v>4.84097099304199</v>
+        <v>4.84097051620483</v>
       </c>
       <c r="H705" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G706" t="n">
-        <v>4.84097099304199</v>
+        <v>4.84097051620483</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G707" t="n">
-        <v>4.85085010528564</v>
+        <v>4.8508505821228</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -18855,7 +18855,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G711" t="n">
-        <v>4.88048887252808</v>
+        <v>4.88048839569092</v>
       </c>
       <c r="H711" t="s">
         <v>8</v>
@@ -19011,7 +19011,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G717" t="n">
-        <v>4.78169393539429</v>
+        <v>4.78169345855713</v>
       </c>
       <c r="H717" t="s">
         <v>8</v>
@@ -19115,7 +19115,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G721" t="n">
-        <v>5.09783840179443</v>
+        <v>5.09783792495728</v>
       </c>
       <c r="H721" t="s">
         <v>8</v>
@@ -19219,7 +19219,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G725" t="n">
-        <v>5.13735675811768</v>
+        <v>5.13735628128052</v>
       </c>
       <c r="H725" t="s">
         <v>8</v>
@@ -19323,7 +19323,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G729" t="n">
-        <v>4.84097099304199</v>
+        <v>4.84097051620483</v>
       </c>
       <c r="H729" t="s">
         <v>8</v>
@@ -19375,7 +19375,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G731" t="n">
-        <v>4.7421760559082</v>
+        <v>4.74217557907104</v>
       </c>
       <c r="H731" t="s">
         <v>8</v>
@@ -19427,7 +19427,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G733" t="n">
-        <v>4.88048887252808</v>
+        <v>4.88048839569092</v>
       </c>
       <c r="H733" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G734" t="n">
-        <v>4.78169393539429</v>
+        <v>4.78169345855713</v>
       </c>
       <c r="H734" t="s">
         <v>8</v>
@@ -19505,7 +19505,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G736" t="n">
-        <v>4.88048887252808</v>
+        <v>4.88048839569092</v>
       </c>
       <c r="H736" t="s">
         <v>8</v>
@@ -19531,7 +19531,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G737" t="n">
-        <v>4.89036798477173</v>
+        <v>4.89036846160889</v>
       </c>
       <c r="H737" t="s">
         <v>8</v>
@@ -19661,7 +19661,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G742" t="n">
-        <v>4.84097099304199</v>
+        <v>4.84097051620483</v>
       </c>
       <c r="H742" t="s">
         <v>8</v>
@@ -19687,7 +19687,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G743" t="n">
-        <v>4.85085010528564</v>
+        <v>4.8508505821228</v>
       </c>
       <c r="H743" t="s">
         <v>8</v>
@@ -19791,7 +19791,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G747" t="n">
-        <v>4.7421760559082</v>
+        <v>4.74217557907104</v>
       </c>
       <c r="H747" t="s">
         <v>8</v>
@@ -19843,7 +19843,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G749" t="n">
-        <v>4.78169393539429</v>
+        <v>4.78169345855713</v>
       </c>
       <c r="H749" t="s">
         <v>8</v>
@@ -19921,7 +19921,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G752" t="n">
-        <v>4.22843980789185</v>
+        <v>4.22843933105469</v>
       </c>
       <c r="H752" t="s">
         <v>8</v>
@@ -20129,7 +20129,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G760" t="n">
-        <v>4.16916275024414</v>
+        <v>4.16916227340698</v>
       </c>
       <c r="H760" t="s">
         <v>8</v>
@@ -20155,7 +20155,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G761" t="n">
-        <v>4.16916275024414</v>
+        <v>4.16916227340698</v>
       </c>
       <c r="H761" t="s">
         <v>8</v>
@@ -20207,7 +20207,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G763" t="n">
-        <v>4.05060815811157</v>
+        <v>4.05060768127441</v>
       </c>
       <c r="H763" t="s">
         <v>8</v>
@@ -20233,7 +20233,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G764" t="n">
-        <v>4.02096939086914</v>
+        <v>4.0209698677063</v>
       </c>
       <c r="H764" t="s">
         <v>8</v>
@@ -20805,7 +20805,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G786" t="n">
-        <v>3.96169257164001</v>
+        <v>3.96169233322144</v>
       </c>
       <c r="H786" t="s">
         <v>8</v>
@@ -20831,7 +20831,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G787" t="n">
-        <v>4.03084945678711</v>
+        <v>4.03084897994995</v>
       </c>
       <c r="H787" t="s">
         <v>8</v>
@@ -20883,7 +20883,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G789" t="n">
-        <v>3.92217397689819</v>
+        <v>3.92217421531677</v>
       </c>
       <c r="H789" t="s">
         <v>8</v>
@@ -43454,6 +43454,32 @@
         <v>3.44000005722046</v>
       </c>
       <c r="H1657" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1658">
+      <c r="A1658" s="1" t="n">
+        <v>46287.2916666667</v>
+      </c>
+      <c r="B1658" t="n">
+        <v>107837</v>
+      </c>
+      <c r="C1658" t="n">
+        <v>3.50999999046326</v>
+      </c>
+      <c r="D1658" t="n">
+        <v>3.36999988555908</v>
+      </c>
+      <c r="E1658" t="n">
+        <v>3.38000011444092</v>
+      </c>
+      <c r="F1658" t="n">
+        <v>3.4300000667572</v>
+      </c>
+      <c r="G1658" t="n">
+        <v>3.4300000667572</v>
+      </c>
+      <c r="H1658" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/UD.MI.xlsx
+++ b/data/UD.MI.xlsx
@@ -421,7 +421,7 @@
         <v>1.5</v>
       </c>
       <c r="G2" t="n">
-        <v>1.47885501384735</v>
+        <v>1.47885525226593</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>1.56500005722046</v>
       </c>
       <c r="G6" t="n">
-        <v>1.54293882846832</v>
+        <v>1.54293894767761</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G7" t="n">
-        <v>1.51829135417938</v>
+        <v>1.51829123497009</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G8" t="n">
-        <v>1.53800940513611</v>
+        <v>1.53800928592682</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G10" t="n">
-        <v>1.53800940513611</v>
+        <v>1.53800928592682</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G11" t="n">
-        <v>1.56265699863434</v>
+        <v>1.56265687942505</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G17" t="n">
-        <v>1.66617703437805</v>
+        <v>1.66617691516876</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G18" t="n">
-        <v>1.67603600025177</v>
+        <v>1.67603588104248</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G19" t="n">
-        <v>1.67603600025177</v>
+        <v>1.67603588104248</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G22" t="n">
-        <v>1.62181115150452</v>
+        <v>1.62181127071381</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G23" t="n">
-        <v>1.59716367721558</v>
+        <v>1.59716355800629</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G25" t="n">
-        <v>1.58730471134186</v>
+        <v>1.58730447292328</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G31" t="n">
-        <v>1.63659977912903</v>
+        <v>1.63659965991974</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G32" t="n">
-        <v>1.59716367721558</v>
+        <v>1.59716355800629</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G33" t="n">
-        <v>1.61688160896301</v>
+        <v>1.6168817281723</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G37" t="n">
-        <v>1.70561289787292</v>
+        <v>1.70561301708221</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G38" t="n">
-        <v>1.70561289787292</v>
+        <v>1.70561301708221</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G39" t="n">
-        <v>1.67110633850098</v>
+        <v>1.67110657691956</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G41" t="n">
-        <v>1.68589496612549</v>
+        <v>1.6858948469162</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G45" t="n">
-        <v>1.66617703437805</v>
+        <v>1.66617691516876</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G46" t="n">
-        <v>1.67603600025177</v>
+        <v>1.67603588104248</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G50" t="n">
-        <v>1.74997878074646</v>
+        <v>1.74997866153717</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G52" t="n">
-        <v>1.74011981487274</v>
+        <v>1.74011957645416</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G57" t="n">
-        <v>1.67603600025177</v>
+        <v>1.67603588104248</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>1.7150000333786</v>
       </c>
       <c r="G58" t="n">
-        <v>1.6908243894577</v>
+        <v>1.69082462787628</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>1.7150000333786</v>
       </c>
       <c r="G59" t="n">
-        <v>1.6908243894577</v>
+        <v>1.69082462787628</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G60" t="n">
-        <v>1.71547198295593</v>
+        <v>1.71547210216522</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G61" t="n">
-        <v>1.71547198295593</v>
+        <v>1.71547210216522</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>1.68499994277954</v>
       </c>
       <c r="G63" t="n">
-        <v>1.66124725341797</v>
+        <v>1.66124713420868</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G66" t="n">
-        <v>1.67603600025177</v>
+        <v>1.67603588104248</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G67" t="n">
-        <v>1.66617703437805</v>
+        <v>1.66617691516876</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G68" t="n">
-        <v>1.68589496612549</v>
+        <v>1.6858948469162</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G76" t="n">
-        <v>1.67110633850098</v>
+        <v>1.67110657691956</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G77" t="n">
-        <v>1.68589496612549</v>
+        <v>1.6858948469162</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G79" t="n">
-        <v>1.67603600025177</v>
+        <v>1.67603588104248</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G80" t="n">
-        <v>1.67603600025177</v>
+        <v>1.67603588104248</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G81" t="n">
-        <v>1.67603600025177</v>
+        <v>1.67603588104248</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G84" t="n">
-        <v>1.63659977912903</v>
+        <v>1.63659965991974</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G95" t="n">
-        <v>1.58730471134186</v>
+        <v>1.58730447292328</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G96" t="n">
-        <v>1.62181115150452</v>
+        <v>1.62181127071381</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G97" t="n">
-        <v>1.58730471134186</v>
+        <v>1.58730447292328</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G98" t="n">
-        <v>1.58730471134186</v>
+        <v>1.58730447292328</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G103" t="n">
-        <v>1.63659977912903</v>
+        <v>1.63659965991974</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G104" t="n">
-        <v>1.63659977912903</v>
+        <v>1.63659965991974</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>1.63499999046326</v>
       </c>
       <c r="G105" t="n">
-        <v>1.6119521856308</v>
+        <v>1.61195194721222</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>1.66499996185303</v>
       </c>
       <c r="G106" t="n">
-        <v>1.64152920246124</v>
+        <v>1.64152932167053</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G109" t="n">
-        <v>1.66617703437805</v>
+        <v>1.66617691516876</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G110" t="n">
-        <v>1.67603600025177</v>
+        <v>1.67603588104248</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G111" t="n">
-        <v>1.67603600025177</v>
+        <v>1.67603588104248</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G112" t="n">
-        <v>1.67603600025177</v>
+        <v>1.67603588104248</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G113" t="n">
-        <v>1.67603600025177</v>
+        <v>1.67603588104248</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G114" t="n">
-        <v>1.67603600025177</v>
+        <v>1.67603588104248</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G115" t="n">
-        <v>1.67603600025177</v>
+        <v>1.67603588104248</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G116" t="n">
-        <v>1.71547198295593</v>
+        <v>1.71547210216522</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G117" t="n">
-        <v>1.68589496612549</v>
+        <v>1.6858948469162</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G118" t="n">
-        <v>1.68589496612549</v>
+        <v>1.6858948469162</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G124" t="n">
-        <v>1.8534984588623</v>
+        <v>1.85349857807159</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G126" t="n">
-        <v>1.83378028869629</v>
+        <v>1.83378040790558</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G127" t="n">
-        <v>1.82392132282257</v>
+        <v>1.82392144203186</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G128" t="n">
-        <v>1.82392132282257</v>
+        <v>1.82392144203186</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G129" t="n">
-        <v>1.82392132282257</v>
+        <v>1.82392144203186</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G130" t="n">
-        <v>1.83870995044708</v>
+        <v>1.83871006965637</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G131" t="n">
-        <v>1.83378028869629</v>
+        <v>1.83378040790558</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G132" t="n">
-        <v>1.78448522090912</v>
+        <v>1.78448510169983</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G133" t="n">
-        <v>1.8534984588623</v>
+        <v>1.85349857807159</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G134" t="n">
-        <v>1.8534984588623</v>
+        <v>1.85349857807159</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G135" t="n">
-        <v>1.8534984588623</v>
+        <v>1.85349857807159</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G137" t="n">
-        <v>1.88307559490204</v>
+        <v>1.88307547569275</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G138" t="n">
-        <v>1.88307559490204</v>
+        <v>1.88307547569275</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G141" t="n">
-        <v>1.82392132282257</v>
+        <v>1.82392144203186</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G142" t="n">
-        <v>1.82392132282257</v>
+        <v>1.82392144203186</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G143" t="n">
-        <v>1.79927384853363</v>
+        <v>1.79927396774292</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G145" t="n">
-        <v>1.79434442520142</v>
+        <v>1.79434430599213</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G146" t="n">
-        <v>1.79434442520142</v>
+        <v>1.79434430599213</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G147" t="n">
-        <v>1.79434442520142</v>
+        <v>1.79434430599213</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G149" t="n">
-        <v>1.79434442520142</v>
+        <v>1.79434430599213</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G150" t="n">
-        <v>1.79434442520142</v>
+        <v>1.79434430599213</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G151" t="n">
-        <v>1.74011981487274</v>
+        <v>1.74011957645416</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G152" t="n">
-        <v>1.76969659328461</v>
+        <v>1.7696967124939</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G155" t="n">
-        <v>1.82392132282257</v>
+        <v>1.82392144203186</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G156" t="n">
-        <v>1.82392132282257</v>
+        <v>1.82392144203186</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G157" t="n">
-        <v>1.83870995044708</v>
+        <v>1.83871006965637</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G158" t="n">
-        <v>1.83378028869629</v>
+        <v>1.83378040790558</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G164" t="n">
-        <v>1.71547198295593</v>
+        <v>1.71547210216522</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G168" t="n">
-        <v>1.74997878074646</v>
+        <v>1.74997866153717</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G170" t="n">
-        <v>1.83870995044708</v>
+        <v>1.83871006965637</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G171" t="n">
-        <v>1.83870995044708</v>
+        <v>1.83871006965637</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G172" t="n">
-        <v>1.81406247615814</v>
+        <v>1.81406235694885</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G173" t="n">
-        <v>1.82885098457336</v>
+        <v>1.82885086536407</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G174" t="n">
-        <v>1.82885098457336</v>
+        <v>1.82885086536407</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G176" t="n">
-        <v>1.83870995044708</v>
+        <v>1.83871006965637</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G178" t="n">
-        <v>1.87814617156982</v>
+        <v>1.87814605236053</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G179" t="n">
-        <v>1.88307559490204</v>
+        <v>1.88307547569275</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G180" t="n">
-        <v>1.88800513744354</v>
+        <v>1.88800525665283</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G181" t="n">
-        <v>1.90279352664948</v>
+        <v>1.90279364585876</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G182" t="n">
-        <v>1.91265273094177</v>
+        <v>1.91265285015106</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G184" t="n">
-        <v>2.01124286651611</v>
+        <v>2.01124310493469</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G187" t="n">
-        <v>1.95208895206451</v>
+        <v>1.95208883285522</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G188" t="n">
-        <v>2.01124286651611</v>
+        <v>2.01124310493469</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G189" t="n">
-        <v>2.01124286651611</v>
+        <v>2.01124310493469</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G195" t="n">
-        <v>1.86335742473602</v>
+        <v>1.86335754394531</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G197" t="n">
-        <v>1.91265273094177</v>
+        <v>1.91265285015106</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G198" t="n">
-        <v>1.91265273094177</v>
+        <v>1.91265285015106</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G202" t="n">
-        <v>1.91265273094177</v>
+        <v>1.91265285015106</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G208" t="n">
-        <v>1.95208895206451</v>
+        <v>1.95208883285522</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G210" t="n">
-        <v>1.95701849460602</v>
+        <v>1.95701825618744</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G212" t="n">
-        <v>1.9422299861908</v>
+        <v>1.94222986698151</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G215" t="n">
-        <v>1.95701849460602</v>
+        <v>1.95701825618744</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G216" t="n">
-        <v>1.91265273094177</v>
+        <v>1.91265285015106</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G225" t="n">
-        <v>1.9422299861908</v>
+        <v>1.94222986698151</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G226" t="n">
-        <v>1.99152493476868</v>
+        <v>1.99152481555939</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G229" t="n">
-        <v>2.08025598526001</v>
+        <v>2.08025622367859</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G230" t="n">
-        <v>2.0211021900177</v>
+        <v>2.02110195159912</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G231" t="n">
-        <v>2.22814178466797</v>
+        <v>2.22814202308655</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G232" t="n">
-        <v>2.26757788658142</v>
+        <v>2.267578125</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>2.25</v>
       </c>
       <c r="G233" t="n">
-        <v>2.21828293800354</v>
+        <v>2.21828269958496</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G234" t="n">
-        <v>2.16898798942566</v>
+        <v>2.16898775100708</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>2.25</v>
       </c>
       <c r="G239" t="n">
-        <v>2.21828293800354</v>
+        <v>2.21828269958496</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G240" t="n">
-        <v>2.20842385292053</v>
+        <v>2.20842361450195</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G241" t="n">
-        <v>2.22814178466797</v>
+        <v>2.22814202308655</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G242" t="n">
-        <v>2.25771880149841</v>
+        <v>2.25771903991699</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G243" t="n">
-        <v>2.26757788658142</v>
+        <v>2.267578125</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G246" t="n">
-        <v>2.28729605674744</v>
+        <v>2.28729557991028</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G247" t="n">
-        <v>2.28729605674744</v>
+        <v>2.28729557991028</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G254" t="n">
-        <v>2.48447680473328</v>
+        <v>2.4844765663147</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>2.5</v>
       </c>
       <c r="G255" t="n">
-        <v>2.46475887298584</v>
+        <v>2.46475863456726</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G258" t="n">
-        <v>2.6126446723938</v>
+        <v>2.61264419555664</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G259" t="n">
-        <v>2.59292650222778</v>
+        <v>2.5929262638092</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G261" t="n">
-        <v>2.6619393825531</v>
+        <v>2.66193962097168</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>3</v>
       </c>
       <c r="G265" t="n">
-        <v>2.9577100276947</v>
+        <v>2.95771050453186</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G267" t="n">
-        <v>2.83940196037292</v>
+        <v>2.8394021987915</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G270" t="n">
-        <v>2.77038884162903</v>
+        <v>2.77038860321045</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G271" t="n">
-        <v>2.84926104545593</v>
+        <v>2.84926128387451</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G277" t="n">
-        <v>3.17460942268372</v>
+        <v>3.17460894584656</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G283" t="n">
-        <v>3.24362230300903</v>
+        <v>3.24362254142761</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G284" t="n">
-        <v>3.19432735443115</v>
+        <v>3.19432711601257</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G285" t="n">
-        <v>3.35207200050354</v>
+        <v>3.35207176208496</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G286" t="n">
-        <v>3.49995756149292</v>
+        <v>3.49995732307434</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G290" t="n">
-        <v>3.72671484947205</v>
+        <v>3.72671508789062</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G292" t="n">
-        <v>3.64784264564514</v>
+        <v>3.64784288406372</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G293" t="n">
-        <v>3.64784264564514</v>
+        <v>3.64784288406372</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G294" t="n">
-        <v>3.53939318656921</v>
+        <v>3.53939342498779</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G297" t="n">
-        <v>3.55911135673523</v>
+        <v>3.55911159515381</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G299" t="n">
-        <v>3.49995756149292</v>
+        <v>3.49995732307434</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G300" t="n">
-        <v>3.48023962974548</v>
+        <v>3.48023915290833</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G302" t="n">
-        <v>3.49995756149292</v>
+        <v>3.49995732307434</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G307" t="n">
-        <v>3.9731912612915</v>
+        <v>3.97319149971008</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G309" t="n">
-        <v>4.35769367218018</v>
+        <v>4.35769319534302</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G310" t="n">
-        <v>4.33797597885132</v>
+        <v>4.33797550201416</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G311" t="n">
-        <v>4.14079475402832</v>
+        <v>4.14079427719116</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G312" t="n">
-        <v>3.99290895462036</v>
+        <v>3.99290943145752</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G314" t="n">
-        <v>4.05206394195557</v>
+        <v>4.05206346511841</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G317" t="n">
-        <v>4.14079475402832</v>
+        <v>4.14079427719116</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G318" t="n">
-        <v>4.17037153244019</v>
+        <v>4.17037105560303</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G327" t="n">
-        <v>4.16051197052002</v>
+        <v>4.16051244735718</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G328" t="n">
-        <v>4.16051197052002</v>
+        <v>4.16051244735718</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G329" t="n">
-        <v>4.02248573303223</v>
+        <v>4.02248620986938</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G330" t="n">
-        <v>3.98304986953735</v>
+        <v>3.98304963111877</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G333" t="n">
-        <v>4.16051197052002</v>
+        <v>4.16051244735718</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G334" t="n">
-        <v>4.16051197052002</v>
+        <v>4.16051244735718</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G335" t="n">
-        <v>4.17037153244019</v>
+        <v>4.17037105560303</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G338" t="n">
-        <v>4.16051197052002</v>
+        <v>4.16051244735718</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G339" t="n">
-        <v>4.16051197052002</v>
+        <v>4.16051244735718</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G340" t="n">
-        <v>4.14079475402832</v>
+        <v>4.14079427719116</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G341" t="n">
-        <v>4.14079475402832</v>
+        <v>4.14079427719116</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G343" t="n">
-        <v>4.14079475402832</v>
+        <v>4.14079427719116</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G344" t="n">
-        <v>4.11121797561646</v>
+        <v>4.1112174987793</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G346" t="n">
-        <v>4.0422043800354</v>
+        <v>4.04220390319824</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G347" t="n">
-        <v>4.02248573303223</v>
+        <v>4.02248620986938</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G348" t="n">
-        <v>4.02248573303223</v>
+        <v>4.02248620986938</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G352" t="n">
-        <v>4.19994878768921</v>
+        <v>4.19994926452637</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>4.25</v>
       </c>
       <c r="G354" t="n">
-        <v>4.1900897026062</v>
+        <v>4.19009017944336</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G356" t="n">
-        <v>4.14079475402832</v>
+        <v>4.14079427719116</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G357" t="n">
-        <v>4.05206394195557</v>
+        <v>4.05206346511841</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G366" t="n">
-        <v>4.14079475402832</v>
+        <v>4.14079427719116</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G367" t="n">
-        <v>4.14079475402832</v>
+        <v>4.14079427719116</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G368" t="n">
-        <v>4.14079475402832</v>
+        <v>4.14079427719116</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G373" t="n">
-        <v>4.14079475402832</v>
+        <v>4.14079427719116</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G374" t="n">
-        <v>4.14079475402832</v>
+        <v>4.14079427719116</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G375" t="n">
-        <v>4.14079475402832</v>
+        <v>4.14079427719116</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G376" t="n">
-        <v>4.19994878768921</v>
+        <v>4.19994926452637</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G381" t="n">
-        <v>4.2591028213501</v>
+        <v>4.25910329818726</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G383" t="n">
-        <v>4.30839776992798</v>
+        <v>4.30839824676514</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G384" t="n">
-        <v>4.33797597885132</v>
+        <v>4.33797550201416</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G385" t="n">
-        <v>4.36755275726318</v>
+        <v>4.36755180358887</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G386" t="n">
-        <v>4.30839776992798</v>
+        <v>4.30839824676514</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G387" t="n">
-        <v>4.36755275726318</v>
+        <v>4.36755180358887</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G388" t="n">
-        <v>4.36755275726318</v>
+        <v>4.36755180358887</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G390" t="n">
-        <v>4.33797597885132</v>
+        <v>4.33797550201416</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G391" t="n">
-        <v>4.30839776992798</v>
+        <v>4.30839824676514</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>4.25</v>
       </c>
       <c r="G392" t="n">
-        <v>4.1900897026062</v>
+        <v>4.19009017944336</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G393" t="n">
-        <v>4.33797597885132</v>
+        <v>4.33797550201416</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G394" t="n">
-        <v>4.40698862075806</v>
+        <v>4.40698909759521</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>4.25</v>
       </c>
       <c r="G397" t="n">
-        <v>4.1900897026062</v>
+        <v>4.19009017944336</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G398" t="n">
-        <v>4.0422043800354</v>
+        <v>4.04220390319824</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G399" t="n">
-        <v>4.0422043800354</v>
+        <v>4.04220390319824</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G400" t="n">
-        <v>4.0422043800354</v>
+        <v>4.04220390319824</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G402" t="n">
-        <v>4.19994878768921</v>
+        <v>4.19994926452637</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G404" t="n">
-        <v>4.33797597885132</v>
+        <v>4.33797550201416</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G405" t="n">
-        <v>4.38726997375488</v>
+        <v>4.38727045059204</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G407" t="n">
-        <v>4.38726997375488</v>
+        <v>4.38727045059204</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G408" t="n">
-        <v>4.38726997375488</v>
+        <v>4.38727045059204</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G409" t="n">
-        <v>4.49571990966797</v>
+        <v>4.49571943283081</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G411" t="n">
-        <v>5.04782485961914</v>
+        <v>5.04782581329346</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G412" t="n">
-        <v>5.30416011810303</v>
+        <v>5.30416059494019</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G413" t="n">
-        <v>5.2450065612793</v>
+        <v>5.24500703811646</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>5</v>
       </c>
       <c r="G414" t="n">
-        <v>4.92951774597168</v>
+        <v>4.92951726913452</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>5</v>
       </c>
       <c r="G415" t="n">
-        <v>4.92951774597168</v>
+        <v>4.92951726913452</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G416" t="n">
-        <v>4.96895360946655</v>
+        <v>4.96895313262939</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>5</v>
       </c>
       <c r="G417" t="n">
-        <v>4.92951774597168</v>
+        <v>4.92951726913452</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G418" t="n">
-        <v>4.98867130279541</v>
+        <v>4.98867177963257</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G419" t="n">
-        <v>5.02810716629028</v>
+        <v>5.02810764312744</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G420" t="n">
-        <v>5.00838994979858</v>
+        <v>5.00838899612427</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>5</v>
       </c>
       <c r="G421" t="n">
-        <v>4.92951774597168</v>
+        <v>4.92951726913452</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>5</v>
       </c>
       <c r="G422" t="n">
-        <v>4.92951774597168</v>
+        <v>4.92951726913452</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>5</v>
       </c>
       <c r="G423" t="n">
-        <v>4.92951774597168</v>
+        <v>4.92951726913452</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G425" t="n">
-        <v>5.02810716629028</v>
+        <v>5.02810764312744</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G426" t="n">
-        <v>5.08726119995117</v>
+        <v>5.08726167678833</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G427" t="n">
-        <v>5.02810716629028</v>
+        <v>5.02810764312744</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G428" t="n">
-        <v>5.00838994979858</v>
+        <v>5.00838899612427</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G429" t="n">
-        <v>5.1266975402832</v>
+        <v>5.12669801712036</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>5</v>
       </c>
       <c r="G430" t="n">
-        <v>4.92951774597168</v>
+        <v>4.92951726913452</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G431" t="n">
-        <v>4.98867130279541</v>
+        <v>4.98867177963257</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>5</v>
       </c>
       <c r="G432" t="n">
-        <v>4.92951774597168</v>
+        <v>4.92951726913452</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G433" t="n">
-        <v>4.88022232055664</v>
+        <v>4.88022184371948</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>5</v>
       </c>
       <c r="G434" t="n">
-        <v>4.92951774597168</v>
+        <v>4.92951726913452</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G435" t="n">
-        <v>4.78163194656372</v>
+        <v>4.78163242340088</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G437" t="n">
-        <v>4.90979909896851</v>
+        <v>4.90979957580566</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>5</v>
       </c>
       <c r="G438" t="n">
-        <v>4.92951774597168</v>
+        <v>4.92951726913452</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>5</v>
       </c>
       <c r="G440" t="n">
-        <v>4.92951774597168</v>
+        <v>4.92951726913452</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G442" t="n">
-        <v>4.90979909896851</v>
+        <v>4.90979957580566</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G443" t="n">
-        <v>5.04782485961914</v>
+        <v>5.04782581329346</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G444" t="n">
-        <v>5.02810716629028</v>
+        <v>5.02810764312744</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G445" t="n">
-        <v>4.96895360946655</v>
+        <v>4.96895313262939</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G447" t="n">
-        <v>4.85064554214478</v>
+        <v>4.85064506530762</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>5</v>
       </c>
       <c r="G448" t="n">
-        <v>4.92951774597168</v>
+        <v>4.92951726913452</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>5</v>
       </c>
       <c r="G449" t="n">
-        <v>4.92951774597168</v>
+        <v>4.92951726913452</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G450" t="n">
-        <v>4.83092641830444</v>
+        <v>4.8309268951416</v>
       </c>
       <c r="H450" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G451" t="n">
-        <v>4.83092641830444</v>
+        <v>4.8309268951416</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>5</v>
       </c>
       <c r="G452" t="n">
-        <v>4.92951774597168</v>
+        <v>4.92951726913452</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12147,7 +12147,7 @@
         <v>5</v>
       </c>
       <c r="G453" t="n">
-        <v>4.92951774597168</v>
+        <v>4.92951726913452</v>
       </c>
       <c r="H453" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G455" t="n">
-        <v>4.85064554214478</v>
+        <v>4.85064506530762</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>5</v>
       </c>
       <c r="G456" t="n">
-        <v>4.92951774597168</v>
+        <v>4.92951726913452</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G457" t="n">
-        <v>5.04782485961914</v>
+        <v>5.04782581329346</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G459" t="n">
-        <v>5.26472473144531</v>
+        <v>5.26472425460815</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G460" t="n">
-        <v>5.34359645843506</v>
+        <v>5.34359693527222</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G461" t="n">
-        <v>5.30416011810303</v>
+        <v>5.30416059494019</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G462" t="n">
-        <v>5.2252893447876</v>
+        <v>5.22528839111328</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G463" t="n">
-        <v>5.2252893447876</v>
+        <v>5.22528839111328</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G464" t="n">
-        <v>5.04782485961914</v>
+        <v>5.04782581329346</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G466" t="n">
-        <v>5.1266975402832</v>
+        <v>5.12669801712036</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G467" t="n">
-        <v>5.1266975402832</v>
+        <v>5.12669801712036</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G469" t="n">
-        <v>5.2252893447876</v>
+        <v>5.22528839111328</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G470" t="n">
-        <v>5.08726119995117</v>
+        <v>5.08726167678833</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G471" t="n">
-        <v>5.2252893447876</v>
+        <v>5.22528839111328</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G472" t="n">
-        <v>5.2252893447876</v>
+        <v>5.22528839111328</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G473" t="n">
-        <v>5.20557069778442</v>
+        <v>5.20557022094727</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G474" t="n">
-        <v>4.98867130279541</v>
+        <v>4.98867177963257</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G476" t="n">
-        <v>5.02810716629028</v>
+        <v>5.02810764312744</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G477" t="n">
-        <v>5.00838994979858</v>
+        <v>5.00838899612427</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G478" t="n">
-        <v>4.96895360946655</v>
+        <v>4.96895313262939</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G479" t="n">
-        <v>5.02810716629028</v>
+        <v>5.02810764312744</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G483" t="n">
-        <v>5.1266975402832</v>
+        <v>5.12669801712036</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G484" t="n">
-        <v>5.1266975402832</v>
+        <v>5.12669801712036</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G485" t="n">
-        <v>5.1266975402832</v>
+        <v>5.12669801712036</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G486" t="n">
-        <v>5.04782485961914</v>
+        <v>5.04782581329346</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13083,7 +13083,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G489" t="n">
-        <v>4.98867130279541</v>
+        <v>4.98867177963257</v>
       </c>
       <c r="H489" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G490" t="n">
-        <v>5.1266975402832</v>
+        <v>5.12669801712036</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G491" t="n">
-        <v>4.98867130279541</v>
+        <v>4.98867177963257</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G492" t="n">
-        <v>4.96895360946655</v>
+        <v>4.96895313262939</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G495" t="n">
-        <v>5.08726119995117</v>
+        <v>5.08726167678833</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G498" t="n">
-        <v>5.02810716629028</v>
+        <v>5.02810764312744</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G499" t="n">
-        <v>5.02810716629028</v>
+        <v>5.02810764312744</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G500" t="n">
-        <v>5.04782485961914</v>
+        <v>5.04782581329346</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G502" t="n">
-        <v>5.08726119995117</v>
+        <v>5.08726167678833</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G503" t="n">
-        <v>5.02810716629028</v>
+        <v>5.02810764312744</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G504" t="n">
-        <v>4.83092641830444</v>
+        <v>4.8309268951416</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G505" t="n">
-        <v>4.98867130279541</v>
+        <v>4.98867177963257</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G506" t="n">
-        <v>5.1266975402832</v>
+        <v>5.12669801712036</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13577,7 +13577,7 @@
         <v>5</v>
       </c>
       <c r="G508" t="n">
-        <v>4.92951774597168</v>
+        <v>4.92951726913452</v>
       </c>
       <c r="H508" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G510" t="n">
-        <v>4.98867130279541</v>
+        <v>4.98867177963257</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G511" t="n">
-        <v>5.02810716629028</v>
+        <v>5.02810764312744</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G512" t="n">
-        <v>5.08726119995117</v>
+        <v>5.08726167678833</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G513" t="n">
-        <v>5.00838994979858</v>
+        <v>5.00838899612427</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G514" t="n">
-        <v>4.96895360946655</v>
+        <v>4.96895313262939</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13785,7 +13785,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G516" t="n">
-        <v>5.00838994979858</v>
+        <v>5.00838899612427</v>
       </c>
       <c r="H516" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G517" t="n">
-        <v>5.02810716629028</v>
+        <v>5.02810764312744</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G518" t="n">
-        <v>5.00838994979858</v>
+        <v>5.00838899612427</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>5</v>
       </c>
       <c r="G519" t="n">
-        <v>4.92951774597168</v>
+        <v>4.92951726913452</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13889,7 +13889,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G520" t="n">
-        <v>5.02810716629028</v>
+        <v>5.02810764312744</v>
       </c>
       <c r="H520" t="s">
         <v>8</v>
@@ -13915,7 +13915,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G521" t="n">
-        <v>5.20557069778442</v>
+        <v>5.20557022094727</v>
       </c>
       <c r="H521" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G522" t="n">
-        <v>5.04782485961914</v>
+        <v>5.04782581329346</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G523" t="n">
-        <v>5.02810716629028</v>
+        <v>5.02810764312744</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G525" t="n">
-        <v>4.88022232055664</v>
+        <v>4.88022184371948</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G526" t="n">
-        <v>5.00838994979858</v>
+        <v>5.00838899612427</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G527" t="n">
-        <v>4.85064554214478</v>
+        <v>4.85064506530762</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G528" t="n">
-        <v>4.80134963989258</v>
+        <v>4.80135011672974</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G529" t="n">
-        <v>4.77177286148071</v>
+        <v>4.77177238464355</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14149,7 +14149,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G530" t="n">
-        <v>4.73233652114868</v>
+        <v>4.732337474823</v>
       </c>
       <c r="H530" t="s">
         <v>8</v>
@@ -14175,7 +14175,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G531" t="n">
-        <v>4.80134963989258</v>
+        <v>4.80135011672974</v>
       </c>
       <c r="H531" t="s">
         <v>8</v>
@@ -14201,7 +14201,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G532" t="n">
-        <v>4.77177286148071</v>
+        <v>4.77177238464355</v>
       </c>
       <c r="H532" t="s">
         <v>8</v>
@@ -14227,7 +14227,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G533" t="n">
-        <v>4.79149055480957</v>
+        <v>4.79149103164673</v>
       </c>
       <c r="H533" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G534" t="n">
-        <v>4.73233652114868</v>
+        <v>4.732337474823</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G535" t="n">
-        <v>4.73233652114868</v>
+        <v>4.732337474823</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G537" t="n">
-        <v>4.73233652114868</v>
+        <v>4.732337474823</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G539" t="n">
-        <v>4.85064554214478</v>
+        <v>4.85064506530762</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G540" t="n">
-        <v>4.83092641830444</v>
+        <v>4.8309268951416</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G542" t="n">
-        <v>4.86050367355347</v>
+        <v>4.86050415039062</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G545" t="n">
-        <v>4.83092641830444</v>
+        <v>4.8309268951416</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G547" t="n">
-        <v>4.62362051010132</v>
+        <v>4.62362098693848</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G548" t="n">
-        <v>4.57422351837158</v>
+        <v>4.57422304153442</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G549" t="n">
-        <v>4.59398221969604</v>
+        <v>4.5939826965332</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>4.75</v>
       </c>
       <c r="G558" t="n">
-        <v>4.69277763366699</v>
+        <v>4.69277811050415</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>4.75</v>
       </c>
       <c r="G559" t="n">
-        <v>4.69277763366699</v>
+        <v>4.69277811050415</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G573" t="n">
-        <v>4.43590927124023</v>
+        <v>4.43590974807739</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15423,7 +15423,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G579" t="n">
-        <v>4.2778377532959</v>
+        <v>4.27783727645874</v>
       </c>
       <c r="H579" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G581" t="n">
-        <v>4.40627145767212</v>
+        <v>4.40627098083496</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G582" t="n">
-        <v>4.45566940307617</v>
+        <v>4.45566892623901</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G585" t="n">
-        <v>4.59398221969604</v>
+        <v>4.5939826965332</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G587" t="n">
-        <v>4.43590927124023</v>
+        <v>4.43590974807739</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G589" t="n">
-        <v>4.43590927124023</v>
+        <v>4.43590974807739</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G590" t="n">
-        <v>4.38651180267334</v>
+        <v>4.3865122795105</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G591" t="n">
-        <v>4.34699440002441</v>
+        <v>4.34699392318726</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G592" t="n">
-        <v>4.34699440002441</v>
+        <v>4.34699392318726</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15787,7 +15787,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G593" t="n">
-        <v>4.34699440002441</v>
+        <v>4.34699392318726</v>
       </c>
       <c r="H593" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G595" t="n">
-        <v>4.35687351226807</v>
+        <v>4.35687303543091</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G597" t="n">
-        <v>4.40627145767212</v>
+        <v>4.40627098083496</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G599" t="n">
-        <v>4.43590927124023</v>
+        <v>4.43590974807739</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -15995,7 +15995,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G601" t="n">
-        <v>4.54458427429199</v>
+        <v>4.54458475112915</v>
       </c>
       <c r="H601" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G602" t="n">
-        <v>4.59398221969604</v>
+        <v>4.5939826965332</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G606" t="n">
-        <v>4.89036846160889</v>
+        <v>4.89036798477173</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G607" t="n">
-        <v>4.7026572227478</v>
+        <v>4.70265769958496</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G608" t="n">
-        <v>4.7026572227478</v>
+        <v>4.70265769958496</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>4.75</v>
       </c>
       <c r="G612" t="n">
-        <v>4.69277763366699</v>
+        <v>4.69277811050415</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16359,7 +16359,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G615" t="n">
-        <v>4.88048839569092</v>
+        <v>4.88048887252808</v>
       </c>
       <c r="H615" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G616" t="n">
-        <v>4.97928428649902</v>
+        <v>4.97928380966187</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16411,7 +16411,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G617" t="n">
-        <v>4.97928428649902</v>
+        <v>4.97928380966187</v>
       </c>
       <c r="H617" t="s">
         <v>8</v>
@@ -16437,7 +16437,7 @@
         <v>5</v>
       </c>
       <c r="G618" t="n">
-        <v>4.93976593017578</v>
+        <v>4.93976545333862</v>
       </c>
       <c r="H618" t="s">
         <v>8</v>
@@ -16463,7 +16463,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G619" t="n">
-        <v>4.97928428649902</v>
+        <v>4.97928380966187</v>
       </c>
       <c r="H619" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G620" t="n">
-        <v>4.99904298782349</v>
+        <v>4.99904346466064</v>
       </c>
       <c r="H620" t="s">
         <v>8</v>
@@ -16515,7 +16515,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G621" t="n">
-        <v>5.01880264282227</v>
+        <v>5.01880168914795</v>
       </c>
       <c r="H621" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G622" t="n">
-        <v>5.01880264282227</v>
+        <v>5.01880168914795</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16567,7 +16567,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G623" t="n">
-        <v>5.01880264282227</v>
+        <v>5.01880168914795</v>
       </c>
       <c r="H623" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G624" t="n">
-        <v>5.03856086730957</v>
+        <v>5.03856134414673</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16619,7 +16619,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G625" t="n">
-        <v>5.03856086730957</v>
+        <v>5.03856134414673</v>
       </c>
       <c r="H625" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G628" t="n">
-        <v>4.87060880661011</v>
+        <v>4.87060928344727</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -16801,7 +16801,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G632" t="n">
-        <v>4.75205421447754</v>
+        <v>4.7520546913147</v>
       </c>
       <c r="H632" t="s">
         <v>8</v>
@@ -16879,7 +16879,7 @@
         <v>5</v>
       </c>
       <c r="G635" t="n">
-        <v>4.93976593017578</v>
+        <v>4.93976545333862</v>
       </c>
       <c r="H635" t="s">
         <v>8</v>
@@ -16905,7 +16905,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G636" t="n">
-        <v>4.89036846160889</v>
+        <v>4.89036798477173</v>
       </c>
       <c r="H636" t="s">
         <v>8</v>
@@ -16931,7 +16931,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G637" t="n">
-        <v>4.88048839569092</v>
+        <v>4.88048887252808</v>
       </c>
       <c r="H637" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G638" t="n">
-        <v>4.88048839569092</v>
+        <v>4.88048887252808</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G639" t="n">
-        <v>4.87060880661011</v>
+        <v>4.87060928344727</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17087,7 +17087,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G643" t="n">
-        <v>4.73229598999023</v>
+        <v>4.73229551315308</v>
       </c>
       <c r="H643" t="s">
         <v>8</v>
@@ -17113,7 +17113,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G644" t="n">
-        <v>4.54458427429199</v>
+        <v>4.54458475112915</v>
       </c>
       <c r="H644" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G647" t="n">
-        <v>4.34699440002441</v>
+        <v>4.34699392318726</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G648" t="n">
-        <v>4.34699440002441</v>
+        <v>4.34699392318726</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17269,7 +17269,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G650" t="n">
-        <v>4.52482557296753</v>
+        <v>4.52482509613037</v>
       </c>
       <c r="H650" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G651" t="n">
-        <v>4.61374139785767</v>
+        <v>4.61374187469482</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17555,7 +17555,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G661" t="n">
-        <v>4.88048839569092</v>
+        <v>4.88048887252808</v>
       </c>
       <c r="H661" t="s">
         <v>8</v>
@@ -17633,7 +17633,7 @@
         <v>5</v>
       </c>
       <c r="G664" t="n">
-        <v>4.93976593017578</v>
+        <v>4.93976545333862</v>
       </c>
       <c r="H664" t="s">
         <v>8</v>
@@ -17737,7 +17737,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G668" t="n">
-        <v>5.03856086730957</v>
+        <v>5.03856134414673</v>
       </c>
       <c r="H668" t="s">
         <v>8</v>
@@ -17763,7 +17763,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G669" t="n">
-        <v>5.11759757995605</v>
+        <v>5.1175971031189</v>
       </c>
       <c r="H669" t="s">
         <v>8</v>
@@ -17789,7 +17789,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G670" t="n">
-        <v>5.11759757995605</v>
+        <v>5.1175971031189</v>
       </c>
       <c r="H670" t="s">
         <v>8</v>
@@ -17815,7 +17815,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G671" t="n">
-        <v>5.03856086730957</v>
+        <v>5.03856134414673</v>
       </c>
       <c r="H671" t="s">
         <v>8</v>
@@ -17841,7 +17841,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G672" t="n">
-        <v>5.11759757995605</v>
+        <v>5.1175971031189</v>
       </c>
       <c r="H672" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G674" t="n">
-        <v>5.03856086730957</v>
+        <v>5.03856134414673</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G675" t="n">
-        <v>4.97928428649902</v>
+        <v>4.97928380966187</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -17945,7 +17945,7 @@
         <v>5</v>
       </c>
       <c r="G676" t="n">
-        <v>4.93976593017578</v>
+        <v>4.93976545333862</v>
       </c>
       <c r="H676" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G677" t="n">
-        <v>4.89036846160889</v>
+        <v>4.89036798477173</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -18023,7 +18023,7 @@
         <v>4.59000015258789</v>
       </c>
       <c r="G679" t="n">
-        <v>4.53470516204834</v>
+        <v>4.53470468521118</v>
       </c>
       <c r="H679" t="s">
         <v>8</v>
@@ -18049,7 +18049,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G680" t="n">
-        <v>4.73229598999023</v>
+        <v>4.73229551315308</v>
       </c>
       <c r="H680" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>4.71000003814697</v>
       </c>
       <c r="G681" t="n">
-        <v>4.65325927734375</v>
+        <v>4.65325975418091</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18101,7 +18101,7 @@
         <v>4.75</v>
       </c>
       <c r="G682" t="n">
-        <v>4.69277763366699</v>
+        <v>4.69277811050415</v>
       </c>
       <c r="H682" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>4.59000015258789</v>
       </c>
       <c r="G683" t="n">
-        <v>4.53470516204834</v>
+        <v>4.53470468521118</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18153,7 +18153,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G684" t="n">
-        <v>4.52482557296753</v>
+        <v>4.52482509613037</v>
       </c>
       <c r="H684" t="s">
         <v>8</v>
@@ -18179,7 +18179,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G685" t="n">
-        <v>4.34699440002441</v>
+        <v>4.34699392318726</v>
       </c>
       <c r="H685" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>4.75</v>
       </c>
       <c r="G689" t="n">
-        <v>4.69277763366699</v>
+        <v>4.69277811050415</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18309,7 +18309,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G690" t="n">
-        <v>4.71253681182861</v>
+        <v>4.7125358581543</v>
       </c>
       <c r="H690" t="s">
         <v>8</v>
@@ -18335,7 +18335,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G691" t="n">
-        <v>5.01880264282227</v>
+        <v>5.01880168914795</v>
       </c>
       <c r="H691" t="s">
         <v>8</v>
@@ -18361,7 +18361,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G692" t="n">
-        <v>5.03856086730957</v>
+        <v>5.03856134414673</v>
       </c>
       <c r="H692" t="s">
         <v>8</v>
@@ -18413,7 +18413,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G694" t="n">
-        <v>5.03856086730957</v>
+        <v>5.03856134414673</v>
       </c>
       <c r="H694" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G695" t="n">
-        <v>4.99904298782349</v>
+        <v>4.99904346466064</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18491,7 +18491,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G697" t="n">
-        <v>5.03856086730957</v>
+        <v>5.03856134414673</v>
       </c>
       <c r="H697" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G698" t="n">
-        <v>5.11759757995605</v>
+        <v>5.1175971031189</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18543,7 +18543,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G699" t="n">
-        <v>5.11759757995605</v>
+        <v>5.1175971031189</v>
       </c>
       <c r="H699" t="s">
         <v>8</v>
@@ -18569,7 +18569,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G700" t="n">
-        <v>5.03856086730957</v>
+        <v>5.03856134414673</v>
       </c>
       <c r="H700" t="s">
         <v>8</v>
@@ -18595,7 +18595,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G701" t="n">
-        <v>5.03856086730957</v>
+        <v>5.03856134414673</v>
       </c>
       <c r="H701" t="s">
         <v>8</v>
@@ -18621,7 +18621,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G702" t="n">
-        <v>5.03856086730957</v>
+        <v>5.03856134414673</v>
       </c>
       <c r="H702" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G703" t="n">
-        <v>4.87060880661011</v>
+        <v>4.87060928344727</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G707" t="n">
-        <v>4.8508505821228</v>
+        <v>4.85085010528564</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -18777,7 +18777,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G708" t="n">
-        <v>5.11759757995605</v>
+        <v>5.1175971031189</v>
       </c>
       <c r="H708" t="s">
         <v>8</v>
@@ -18855,7 +18855,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G711" t="n">
-        <v>4.88048839569092</v>
+        <v>4.88048887252808</v>
       </c>
       <c r="H711" t="s">
         <v>8</v>
@@ -18907,7 +18907,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G713" t="n">
-        <v>4.71253681182861</v>
+        <v>4.7125358581543</v>
       </c>
       <c r="H713" t="s">
         <v>8</v>
@@ -18933,7 +18933,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G714" t="n">
-        <v>4.60386180877686</v>
+        <v>4.6038613319397</v>
       </c>
       <c r="H714" t="s">
         <v>8</v>
@@ -18959,7 +18959,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G715" t="n">
-        <v>4.71253681182861</v>
+        <v>4.7125358581543</v>
       </c>
       <c r="H715" t="s">
         <v>8</v>
@@ -19089,7 +19089,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G720" t="n">
-        <v>5.01880264282227</v>
+        <v>5.01880168914795</v>
       </c>
       <c r="H720" t="s">
         <v>8</v>
@@ -19115,7 +19115,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G721" t="n">
-        <v>5.09783792495728</v>
+        <v>5.09783840179443</v>
       </c>
       <c r="H721" t="s">
         <v>8</v>
@@ -19167,7 +19167,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G723" t="n">
-        <v>5.11759757995605</v>
+        <v>5.1175971031189</v>
       </c>
       <c r="H723" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G724" t="n">
-        <v>5.11759757995605</v>
+        <v>5.1175971031189</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19245,7 +19245,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G726" t="n">
-        <v>5.03856086730957</v>
+        <v>5.03856134414673</v>
       </c>
       <c r="H726" t="s">
         <v>8</v>
@@ -19271,7 +19271,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G727" t="n">
-        <v>4.97928428649902</v>
+        <v>4.97928380966187</v>
       </c>
       <c r="H727" t="s">
         <v>8</v>
@@ -19297,7 +19297,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G728" t="n">
-        <v>4.76193475723267</v>
+        <v>4.76193428039551</v>
       </c>
       <c r="H728" t="s">
         <v>8</v>
@@ -19427,7 +19427,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G733" t="n">
-        <v>4.88048839569092</v>
+        <v>4.88048887252808</v>
       </c>
       <c r="H733" t="s">
         <v>8</v>
@@ -19505,7 +19505,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G736" t="n">
-        <v>4.88048839569092</v>
+        <v>4.88048887252808</v>
       </c>
       <c r="H736" t="s">
         <v>8</v>
@@ -19531,7 +19531,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G737" t="n">
-        <v>4.89036846160889</v>
+        <v>4.89036798477173</v>
       </c>
       <c r="H737" t="s">
         <v>8</v>
@@ -19687,7 +19687,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G743" t="n">
-        <v>4.8508505821228</v>
+        <v>4.85085010528564</v>
       </c>
       <c r="H743" t="s">
         <v>8</v>
@@ -19739,7 +19739,7 @@
         <v>5</v>
       </c>
       <c r="G745" t="n">
-        <v>4.93976593017578</v>
+        <v>4.93976545333862</v>
       </c>
       <c r="H745" t="s">
         <v>8</v>
@@ -19817,7 +19817,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G748" t="n">
-        <v>4.75205421447754</v>
+        <v>4.7520546913147</v>
       </c>
       <c r="H748" t="s">
         <v>8</v>
@@ -19869,7 +19869,7 @@
         <v>4.75</v>
       </c>
       <c r="G750" t="n">
-        <v>4.69277763366699</v>
+        <v>4.69277811050415</v>
       </c>
       <c r="H750" t="s">
         <v>8</v>
@@ -19895,7 +19895,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G751" t="n">
-        <v>4.17904186248779</v>
+        <v>4.17904138565063</v>
       </c>
       <c r="H751" t="s">
         <v>8</v>
@@ -19947,7 +19947,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G753" t="n">
-        <v>4.17904186248779</v>
+        <v>4.17904138565063</v>
       </c>
       <c r="H753" t="s">
         <v>8</v>
@@ -19973,7 +19973,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G754" t="n">
-        <v>4.17904186248779</v>
+        <v>4.17904138565063</v>
       </c>
       <c r="H754" t="s">
         <v>8</v>
@@ -19999,7 +19999,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G755" t="n">
-        <v>4.1889214515686</v>
+        <v>4.18892097473145</v>
       </c>
       <c r="H755" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G756" t="n">
-        <v>4.1889214515686</v>
+        <v>4.18892097473145</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20051,7 +20051,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G757" t="n">
-        <v>4.17904186248779</v>
+        <v>4.17904138565063</v>
       </c>
       <c r="H757" t="s">
         <v>8</v>
@@ -20077,7 +20077,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G758" t="n">
-        <v>4.14940357208252</v>
+        <v>4.14940309524536</v>
       </c>
       <c r="H758" t="s">
         <v>8</v>
@@ -20233,7 +20233,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G764" t="n">
-        <v>4.0209698677063</v>
+        <v>4.02096939086914</v>
       </c>
       <c r="H764" t="s">
         <v>8</v>
@@ -20311,7 +20311,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G767" t="n">
-        <v>3.86289691925049</v>
+        <v>3.86289715766907</v>
       </c>
       <c r="H767" t="s">
         <v>8</v>
@@ -20337,7 +20337,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G768" t="n">
-        <v>3.89253568649292</v>
+        <v>3.89253544807434</v>
       </c>
       <c r="H768" t="s">
         <v>8</v>
@@ -20415,7 +20415,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G771" t="n">
-        <v>3.76410174369812</v>
+        <v>3.76410150527954</v>
       </c>
       <c r="H771" t="s">
         <v>8</v>
@@ -20441,7 +20441,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G772" t="n">
-        <v>3.76410174369812</v>
+        <v>3.76410150527954</v>
       </c>
       <c r="H772" t="s">
         <v>8</v>
@@ -20493,7 +20493,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G774" t="n">
-        <v>3.75422191619873</v>
+        <v>3.75422167778015</v>
       </c>
       <c r="H774" t="s">
         <v>8</v>
@@ -20545,7 +20545,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G776" t="n">
-        <v>3.69494485855103</v>
+        <v>3.6949450969696</v>
       </c>
       <c r="H776" t="s">
         <v>8</v>
@@ -20571,7 +20571,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G777" t="n">
-        <v>3.75422191619873</v>
+        <v>3.75422167778015</v>
       </c>
       <c r="H777" t="s">
         <v>8</v>
@@ -20649,7 +20649,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G780" t="n">
-        <v>3.89253568649292</v>
+        <v>3.89253544807434</v>
       </c>
       <c r="H780" t="s">
         <v>8</v>
@@ -20727,7 +20727,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G783" t="n">
-        <v>3.98145174980164</v>
+        <v>3.98145151138306</v>
       </c>
       <c r="H783" t="s">
         <v>8</v>
@@ -20779,7 +20779,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G785" t="n">
-        <v>3.89253568649292</v>
+        <v>3.89253544807434</v>
       </c>
       <c r="H785" t="s">
         <v>8</v>
@@ -20987,7 +20987,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G793" t="n">
-        <v>3.93205380439758</v>
+        <v>3.932053565979</v>
       </c>
       <c r="H793" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G795" t="n">
-        <v>3.86289691925049</v>
+        <v>3.86289715766907</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21143,7 +21143,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G799" t="n">
-        <v>3.91229438781738</v>
+        <v>3.91229486465454</v>
       </c>
       <c r="H799" t="s">
         <v>8</v>
@@ -21195,7 +21195,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G801" t="n">
-        <v>3.85301756858826</v>
+        <v>3.85301733016968</v>
       </c>
       <c r="H801" t="s">
         <v>8</v>
@@ -21273,7 +21273,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G804" t="n">
-        <v>3.86292243003845</v>
+        <v>3.86292219161987</v>
       </c>
       <c r="H804" t="s">
         <v>8</v>
@@ -21299,7 +21299,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G805" t="n">
-        <v>3.80349254608154</v>
+        <v>3.80349278450012</v>
       </c>
       <c r="H805" t="s">
         <v>8</v>
@@ -21325,7 +21325,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G806" t="n">
-        <v>3.86292243003845</v>
+        <v>3.86292219161987</v>
       </c>
       <c r="H806" t="s">
         <v>8</v>
@@ -21351,7 +21351,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G807" t="n">
-        <v>4.01149654388428</v>
+        <v>4.01149606704712</v>
       </c>
       <c r="H807" t="s">
         <v>8</v>
@@ -21741,7 +21741,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G822" t="n">
-        <v>4.09073543548584</v>
+        <v>4.090735912323</v>
       </c>
       <c r="H822" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G823" t="n">
-        <v>4.06102085113525</v>
+        <v>4.0610203742981</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21871,7 +21871,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G827" t="n">
-        <v>4.03130626678467</v>
+        <v>4.03130578994751</v>
       </c>
       <c r="H827" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G828" t="n">
-        <v>4.06102085113525</v>
+        <v>4.0610203742981</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -21923,7 +21923,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G829" t="n">
-        <v>4.05111646652222</v>
+        <v>4.05111598968506</v>
       </c>
       <c r="H829" t="s">
         <v>8</v>
@@ -21949,7 +21949,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G830" t="n">
-        <v>4.06102085113525</v>
+        <v>4.0610203742981</v>
       </c>
       <c r="H830" t="s">
         <v>8</v>
@@ -22001,7 +22001,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G832" t="n">
-        <v>4.05111646652222</v>
+        <v>4.05111598968506</v>
       </c>
       <c r="H832" t="s">
         <v>8</v>
@@ -22027,7 +22027,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G833" t="n">
-        <v>4.05111646652222</v>
+        <v>4.05111598968506</v>
       </c>
       <c r="H833" t="s">
         <v>8</v>
@@ -22053,7 +22053,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G834" t="n">
-        <v>4.06102085113525</v>
+        <v>4.0610203742981</v>
       </c>
       <c r="H834" t="s">
         <v>8</v>
@@ -22079,7 +22079,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G835" t="n">
-        <v>4.02140140533447</v>
+        <v>4.02140092849731</v>
       </c>
       <c r="H835" t="s">
         <v>8</v>
@@ -22105,7 +22105,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G836" t="n">
-        <v>4.02140140533447</v>
+        <v>4.02140092849731</v>
       </c>
       <c r="H836" t="s">
         <v>8</v>
@@ -22131,7 +22131,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G837" t="n">
-        <v>3.98178148269653</v>
+        <v>3.98178124427795</v>
       </c>
       <c r="H837" t="s">
         <v>8</v>
@@ -22157,7 +22157,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G838" t="n">
-        <v>4.05111646652222</v>
+        <v>4.05111598968506</v>
       </c>
       <c r="H838" t="s">
         <v>8</v>
@@ -22261,7 +22261,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G842" t="n">
-        <v>4.07092571258545</v>
+        <v>4.07092618942261</v>
       </c>
       <c r="H842" t="s">
         <v>8</v>
@@ -22287,7 +22287,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G843" t="n">
-        <v>4.02140140533447</v>
+        <v>4.02140092849731</v>
       </c>
       <c r="H843" t="s">
         <v>8</v>
@@ -22313,7 +22313,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G844" t="n">
-        <v>3.98178148269653</v>
+        <v>3.98178124427795</v>
       </c>
       <c r="H844" t="s">
         <v>8</v>
@@ -22391,7 +22391,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G847" t="n">
-        <v>4.06102085113525</v>
+        <v>4.0610203742981</v>
       </c>
       <c r="H847" t="s">
         <v>8</v>
@@ -22417,7 +22417,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G848" t="n">
-        <v>4.0808310508728</v>
+        <v>4.08083057403564</v>
       </c>
       <c r="H848" t="s">
         <v>8</v>
@@ -22521,7 +22521,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G852" t="n">
-        <v>4.1996898651123</v>
+        <v>4.19968938827515</v>
       </c>
       <c r="H852" t="s">
         <v>8</v>
@@ -22573,7 +22573,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G854" t="n">
-        <v>4.16007041931152</v>
+        <v>4.16006994247437</v>
       </c>
       <c r="H854" t="s">
         <v>8</v>
@@ -22599,7 +22599,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G855" t="n">
-        <v>4.16007041931152</v>
+        <v>4.16006994247437</v>
       </c>
       <c r="H855" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G856" t="n">
-        <v>4.09073543548584</v>
+        <v>4.090735912323</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22651,7 +22651,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G857" t="n">
-        <v>4.07092571258545</v>
+        <v>4.07092618942261</v>
       </c>
       <c r="H857" t="s">
         <v>8</v>
@@ -22677,7 +22677,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G858" t="n">
-        <v>4.11054515838623</v>
+        <v>4.11054563522339</v>
       </c>
       <c r="H858" t="s">
         <v>8</v>
@@ -22729,7 +22729,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G860" t="n">
-        <v>4.07092571258545</v>
+        <v>4.07092618942261</v>
       </c>
       <c r="H860" t="s">
         <v>8</v>
@@ -22781,7 +22781,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G862" t="n">
-        <v>4.0808310508728</v>
+        <v>4.08083057403564</v>
       </c>
       <c r="H862" t="s">
         <v>8</v>
@@ -22807,7 +22807,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G863" t="n">
-        <v>4.11054515838623</v>
+        <v>4.11054563522339</v>
       </c>
       <c r="H863" t="s">
         <v>8</v>
@@ -22833,7 +22833,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G864" t="n">
-        <v>4.0808310508728</v>
+        <v>4.08083057403564</v>
       </c>
       <c r="H864" t="s">
         <v>8</v>
@@ -22859,7 +22859,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G865" t="n">
-        <v>4.0808310508728</v>
+        <v>4.08083057403564</v>
       </c>
       <c r="H865" t="s">
         <v>8</v>
@@ -22911,7 +22911,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G867" t="n">
-        <v>4.05111646652222</v>
+        <v>4.05111598968506</v>
       </c>
       <c r="H867" t="s">
         <v>8</v>
@@ -22963,7 +22963,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G869" t="n">
-        <v>4.01149654388428</v>
+        <v>4.01149606704712</v>
       </c>
       <c r="H869" t="s">
         <v>8</v>
@@ -22989,7 +22989,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G870" t="n">
-        <v>4.02140140533447</v>
+        <v>4.02140092849731</v>
       </c>
       <c r="H870" t="s">
         <v>8</v>
@@ -23041,7 +23041,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G872" t="n">
-        <v>4.02140140533447</v>
+        <v>4.02140092849731</v>
       </c>
       <c r="H872" t="s">
         <v>8</v>
@@ -23119,7 +23119,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G875" t="n">
-        <v>4.06102085113525</v>
+        <v>4.0610203742981</v>
       </c>
       <c r="H875" t="s">
         <v>8</v>
@@ -23145,7 +23145,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G876" t="n">
-        <v>4.0808310508728</v>
+        <v>4.08083057403564</v>
       </c>
       <c r="H876" t="s">
         <v>8</v>
@@ -23197,7 +23197,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G878" t="n">
-        <v>4.24921417236328</v>
+        <v>4.24921464920044</v>
       </c>
       <c r="H878" t="s">
         <v>8</v>
@@ -23223,7 +23223,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G879" t="n">
-        <v>4.29873991012573</v>
+        <v>4.29873943328857</v>
       </c>
       <c r="H879" t="s">
         <v>8</v>
@@ -23275,7 +23275,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G881" t="n">
-        <v>4.24921417236328</v>
+        <v>4.24921464920044</v>
       </c>
       <c r="H881" t="s">
         <v>8</v>
@@ -23353,7 +23353,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G884" t="n">
-        <v>4.36807346343994</v>
+        <v>4.36807298660278</v>
       </c>
       <c r="H884" t="s">
         <v>8</v>
@@ -23535,7 +23535,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G891" t="n">
-        <v>4.36807346343994</v>
+        <v>4.36807298660278</v>
       </c>
       <c r="H891" t="s">
         <v>8</v>
@@ -23561,7 +23561,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G892" t="n">
-        <v>4.36807346343994</v>
+        <v>4.36807298660278</v>
       </c>
       <c r="H892" t="s">
         <v>8</v>
@@ -23587,7 +23587,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G893" t="n">
-        <v>4.2393102645874</v>
+        <v>4.23930931091309</v>
       </c>
       <c r="H893" t="s">
         <v>8</v>
@@ -23769,7 +23769,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G900" t="n">
-        <v>4.25911998748779</v>
+        <v>4.25911951065063</v>
       </c>
       <c r="H900" t="s">
         <v>8</v>
@@ -23795,7 +23795,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G901" t="n">
-        <v>4.25911998748779</v>
+        <v>4.25911951065063</v>
       </c>
       <c r="H901" t="s">
         <v>8</v>
@@ -23821,7 +23821,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G902" t="n">
-        <v>4.1996898651123</v>
+        <v>4.19968938827515</v>
       </c>
       <c r="H902" t="s">
         <v>8</v>
@@ -23847,7 +23847,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G903" t="n">
-        <v>4.24921417236328</v>
+        <v>4.24921464920044</v>
       </c>
       <c r="H903" t="s">
         <v>8</v>
@@ -23873,7 +23873,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G904" t="n">
-        <v>4.07092571258545</v>
+        <v>4.07092618942261</v>
       </c>
       <c r="H904" t="s">
         <v>8</v>
@@ -23899,7 +23899,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G905" t="n">
-        <v>4.24921417236328</v>
+        <v>4.24921464920044</v>
       </c>
       <c r="H905" t="s">
         <v>8</v>
@@ -23925,7 +23925,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G906" t="n">
-        <v>4.24921417236328</v>
+        <v>4.24921464920044</v>
       </c>
       <c r="H906" t="s">
         <v>8</v>
@@ -23951,7 +23951,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G907" t="n">
-        <v>4.17988014221191</v>
+        <v>4.17987966537476</v>
       </c>
       <c r="H907" t="s">
         <v>8</v>
@@ -24003,7 +24003,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G909" t="n">
-        <v>4.11054515838623</v>
+        <v>4.11054563522339</v>
       </c>
       <c r="H909" t="s">
         <v>8</v>
@@ -24029,7 +24029,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G910" t="n">
-        <v>4.06102085113525</v>
+        <v>4.0610203742981</v>
       </c>
       <c r="H910" t="s">
         <v>8</v>
@@ -24263,7 +24263,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G919" t="n">
-        <v>3.85301756858826</v>
+        <v>3.85301733016968</v>
       </c>
       <c r="H919" t="s">
         <v>8</v>
@@ -24315,7 +24315,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G921" t="n">
-        <v>3.70444321632385</v>
+        <v>3.70444345474243</v>
       </c>
       <c r="H921" t="s">
         <v>8</v>
@@ -24471,7 +24471,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G927" t="n">
-        <v>3.56577444076538</v>
+        <v>3.5657742023468</v>
       </c>
       <c r="H927" t="s">
         <v>8</v>
@@ -24497,7 +24497,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G928" t="n">
-        <v>3.56577444076538</v>
+        <v>3.5657742023468</v>
       </c>
       <c r="H928" t="s">
         <v>8</v>
@@ -24523,7 +24523,7 @@
         <v>3.75</v>
       </c>
       <c r="G929" t="n">
-        <v>3.71434831619263</v>
+        <v>3.71434855461121</v>
       </c>
       <c r="H929" t="s">
         <v>8</v>
@@ -24575,7 +24575,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G931" t="n">
-        <v>3.56577444076538</v>
+        <v>3.5657742023468</v>
       </c>
       <c r="H931" t="s">
         <v>8</v>
@@ -24601,7 +24601,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G932" t="n">
-        <v>3.60539436340332</v>
+        <v>3.60539412498474</v>
       </c>
       <c r="H932" t="s">
         <v>8</v>
@@ -24627,7 +24627,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G933" t="n">
-        <v>3.56577444076538</v>
+        <v>3.5657742023468</v>
       </c>
       <c r="H933" t="s">
         <v>8</v>
@@ -24653,7 +24653,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G934" t="n">
-        <v>3.56577444076538</v>
+        <v>3.5657742023468</v>
       </c>
       <c r="H934" t="s">
         <v>8</v>
@@ -24705,7 +24705,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G936" t="n">
-        <v>3.67472863197327</v>
+        <v>3.67472839355469</v>
       </c>
       <c r="H936" t="s">
         <v>8</v>
@@ -24731,7 +24731,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G937" t="n">
-        <v>3.70444321632385</v>
+        <v>3.70444345474243</v>
       </c>
       <c r="H937" t="s">
         <v>8</v>
@@ -24757,7 +24757,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G938" t="n">
-        <v>3.70444321632385</v>
+        <v>3.70444345474243</v>
       </c>
       <c r="H938" t="s">
         <v>8</v>
@@ -24783,7 +24783,7 @@
         <v>3.75</v>
       </c>
       <c r="G939" t="n">
-        <v>3.71434831619263</v>
+        <v>3.71434855461121</v>
       </c>
       <c r="H939" t="s">
         <v>8</v>
@@ -24939,7 +24939,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G945" t="n">
-        <v>3.90254211425781</v>
+        <v>3.90254187583923</v>
       </c>
       <c r="H945" t="s">
         <v>8</v>
@@ -24991,7 +24991,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G947" t="n">
-        <v>4.06102085113525</v>
+        <v>4.0610203742981</v>
       </c>
       <c r="H947" t="s">
         <v>8</v>
@@ -25017,7 +25017,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G948" t="n">
-        <v>4.10064077377319</v>
+        <v>4.10064029693604</v>
       </c>
       <c r="H948" t="s">
         <v>8</v>
@@ -25043,7 +25043,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G949" t="n">
-        <v>4.17988014221191</v>
+        <v>4.17987966537476</v>
       </c>
       <c r="H949" t="s">
         <v>8</v>
@@ -25069,7 +25069,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G950" t="n">
-        <v>4.10064077377319</v>
+        <v>4.10064029693604</v>
       </c>
       <c r="H950" t="s">
         <v>8</v>
@@ -25095,7 +25095,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G951" t="n">
-        <v>3.98178148269653</v>
+        <v>3.98178124427795</v>
       </c>
       <c r="H951" t="s">
         <v>8</v>
@@ -25147,7 +25147,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G953" t="n">
-        <v>4.03130626678467</v>
+        <v>4.03130578994751</v>
       </c>
       <c r="H953" t="s">
         <v>8</v>
@@ -25173,7 +25173,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G954" t="n">
-        <v>4.06102085113525</v>
+        <v>4.0610203742981</v>
       </c>
       <c r="H954" t="s">
         <v>8</v>
@@ -25199,7 +25199,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G955" t="n">
-        <v>4.03130626678467</v>
+        <v>4.03130578994751</v>
       </c>
       <c r="H955" t="s">
         <v>8</v>
@@ -25329,7 +25329,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G960" t="n">
-        <v>4.02140140533447</v>
+        <v>4.02140092849731</v>
       </c>
       <c r="H960" t="s">
         <v>8</v>
@@ -25355,7 +25355,7 @@
         <v>40.5999984741211</v>
       </c>
       <c r="G961" t="n">
-        <v>40.2140083312988</v>
+        <v>40.2140121459961</v>
       </c>
       <c r="H961" t="s">
         <v>8</v>
@@ -25381,7 +25381,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G962" t="n">
-        <v>3.86292243003845</v>
+        <v>3.86292219161987</v>
       </c>
       <c r="H962" t="s">
         <v>8</v>
@@ -25407,7 +25407,7 @@
         <v>3.94400000572205</v>
       </c>
       <c r="G963" t="n">
-        <v>3.90650391578674</v>
+        <v>3.90650415420532</v>
       </c>
       <c r="H963" t="s">
         <v>8</v>
@@ -25459,7 +25459,7 @@
         <v>3.97849988937378</v>
       </c>
       <c r="G965" t="n">
-        <v>3.94067573547363</v>
+        <v>3.94067597389221</v>
       </c>
       <c r="H965" t="s">
         <v>8</v>
@@ -25537,7 +25537,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G968" t="n">
-        <v>3.90254211425781</v>
+        <v>3.90254187583923</v>
       </c>
       <c r="H968" t="s">
         <v>8</v>
@@ -25693,7 +25693,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G974" t="n">
-        <v>4.01149654388428</v>
+        <v>4.01149606704712</v>
       </c>
       <c r="H974" t="s">
         <v>8</v>
@@ -25797,7 +25797,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G978" t="n">
-        <v>4.02140140533447</v>
+        <v>4.02140092849731</v>
       </c>
       <c r="H978" t="s">
         <v>8</v>
@@ -26031,7 +26031,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G987" t="n">
-        <v>3.85301756858826</v>
+        <v>3.85301733016968</v>
       </c>
       <c r="H987" t="s">
         <v>8</v>
@@ -26057,7 +26057,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G988" t="n">
-        <v>3.85301756858826</v>
+        <v>3.85301733016968</v>
       </c>
       <c r="H988" t="s">
         <v>8</v>
@@ -26083,7 +26083,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G989" t="n">
-        <v>3.80349254608154</v>
+        <v>3.80349278450012</v>
       </c>
       <c r="H989" t="s">
         <v>8</v>
@@ -26109,7 +26109,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G990" t="n">
-        <v>3.80349254608154</v>
+        <v>3.80349278450012</v>
       </c>
       <c r="H990" t="s">
         <v>8</v>
@@ -26187,7 +26187,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G993" t="n">
-        <v>3.86292243003845</v>
+        <v>3.86292219161987</v>
       </c>
       <c r="H993" t="s">
         <v>8</v>
@@ -26213,7 +26213,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G994" t="n">
-        <v>3.85301756858826</v>
+        <v>3.85301733016968</v>
       </c>
       <c r="H994" t="s">
         <v>8</v>
@@ -26265,7 +26265,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G996" t="n">
-        <v>3.80349254608154</v>
+        <v>3.80349278450012</v>
       </c>
       <c r="H996" t="s">
         <v>8</v>
@@ -26291,7 +26291,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G997" t="n">
-        <v>3.80349254608154</v>
+        <v>3.80349278450012</v>
       </c>
       <c r="H997" t="s">
         <v>8</v>
@@ -26395,7 +26395,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1001" t="n">
-        <v>3.86292243003845</v>
+        <v>3.86292219161987</v>
       </c>
       <c r="H1001" t="s">
         <v>8</v>
@@ -26421,7 +26421,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G1002" t="n">
-        <v>3.90254211425781</v>
+        <v>3.90254187583923</v>
       </c>
       <c r="H1002" t="s">
         <v>8</v>
@@ -26499,7 +26499,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1005" t="n">
-        <v>3.76387286186218</v>
+        <v>3.7638726234436</v>
       </c>
       <c r="H1005" t="s">
         <v>8</v>
@@ -26551,7 +26551,7 @@
         <v>3.75</v>
       </c>
       <c r="G1007" t="n">
-        <v>3.71434831619263</v>
+        <v>3.71434855461121</v>
       </c>
       <c r="H1007" t="s">
         <v>8</v>
@@ -26629,7 +26629,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G1010" t="n">
-        <v>3.73415803909302</v>
+        <v>3.7341582775116</v>
       </c>
       <c r="H1010" t="s">
         <v>8</v>
@@ -26655,7 +26655,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G1011" t="n">
-        <v>3.73415803909302</v>
+        <v>3.7341582775116</v>
       </c>
       <c r="H1011" t="s">
         <v>8</v>
@@ -26681,7 +26681,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1012" t="n">
-        <v>3.76387286186218</v>
+        <v>3.7638726234436</v>
       </c>
       <c r="H1012" t="s">
         <v>8</v>
@@ -26707,7 +26707,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1013" t="n">
-        <v>3.67472863197327</v>
+        <v>3.67472839355469</v>
       </c>
       <c r="H1013" t="s">
         <v>8</v>
@@ -26837,7 +26837,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G1018" t="n">
-        <v>3.60539436340332</v>
+        <v>3.60539412498474</v>
       </c>
       <c r="H1018" t="s">
         <v>8</v>
@@ -26889,7 +26889,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G1020" t="n">
-        <v>3.60539436340332</v>
+        <v>3.60539412498474</v>
       </c>
       <c r="H1020" t="s">
         <v>8</v>
@@ -26941,7 +26941,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G1022" t="n">
-        <v>3.60539436340332</v>
+        <v>3.60539412498474</v>
       </c>
       <c r="H1022" t="s">
         <v>8</v>
@@ -27019,7 +27019,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G1025" t="n">
-        <v>3.58558416366577</v>
+        <v>3.58558392524719</v>
       </c>
       <c r="H1025" t="s">
         <v>8</v>
@@ -27175,7 +27175,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G1031" t="n">
-        <v>3.65491890907288</v>
+        <v>3.6549186706543</v>
       </c>
       <c r="H1031" t="s">
         <v>8</v>
@@ -27201,7 +27201,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G1032" t="n">
-        <v>3.65491890907288</v>
+        <v>3.6549186706543</v>
       </c>
       <c r="H1032" t="s">
         <v>8</v>
@@ -27227,7 +27227,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1033" t="n">
-        <v>3.67472863197327</v>
+        <v>3.67472839355469</v>
       </c>
       <c r="H1033" t="s">
         <v>8</v>
@@ -27279,7 +27279,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1035" t="n">
-        <v>3.56577444076538</v>
+        <v>3.5657742023468</v>
       </c>
       <c r="H1035" t="s">
         <v>8</v>
@@ -27331,7 +27331,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G1037" t="n">
-        <v>3.52615451812744</v>
+        <v>3.52615475654602</v>
       </c>
       <c r="H1037" t="s">
         <v>8</v>
@@ -27409,7 +27409,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1040" t="n">
-        <v>3.49643993377686</v>
+        <v>3.49643969535828</v>
       </c>
       <c r="H1040" t="s">
         <v>8</v>
@@ -27435,7 +27435,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1041" t="n">
-        <v>3.49643993377686</v>
+        <v>3.49643969535828</v>
       </c>
       <c r="H1041" t="s">
         <v>8</v>
@@ -27565,7 +27565,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G1046" t="n">
-        <v>3.52615451812744</v>
+        <v>3.52615475654602</v>
       </c>
       <c r="H1046" t="s">
         <v>8</v>
@@ -27591,7 +27591,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1047" t="n">
-        <v>3.44691514968872</v>
+        <v>3.4469153881073</v>
       </c>
       <c r="H1047" t="s">
         <v>8</v>
@@ -27617,7 +27617,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1048" t="n">
-        <v>3.41720056533813</v>
+        <v>3.41720032691956</v>
       </c>
       <c r="H1048" t="s">
         <v>8</v>
@@ -27643,7 +27643,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1049" t="n">
-        <v>3.43701028823853</v>
+        <v>3.4370105266571</v>
       </c>
       <c r="H1049" t="s">
         <v>8</v>
@@ -27669,7 +27669,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1050" t="n">
-        <v>3.43701028823853</v>
+        <v>3.4370105266571</v>
       </c>
       <c r="H1050" t="s">
         <v>8</v>
@@ -27695,7 +27695,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G1051" t="n">
-        <v>3.45682001113892</v>
+        <v>3.4568202495575</v>
       </c>
       <c r="H1051" t="s">
         <v>8</v>
@@ -27721,7 +27721,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1052" t="n">
-        <v>3.49643993377686</v>
+        <v>3.49643969535828</v>
       </c>
       <c r="H1052" t="s">
         <v>8</v>
@@ -27773,7 +27773,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1054" t="n">
-        <v>3.56577444076538</v>
+        <v>3.5657742023468</v>
       </c>
       <c r="H1054" t="s">
         <v>8</v>
@@ -27799,7 +27799,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1055" t="n">
-        <v>3.56577444076538</v>
+        <v>3.5657742023468</v>
       </c>
       <c r="H1055" t="s">
         <v>8</v>
@@ -27929,7 +27929,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1060" t="n">
-        <v>3.56577444076538</v>
+        <v>3.5657742023468</v>
       </c>
       <c r="H1060" t="s">
         <v>8</v>
@@ -27955,7 +27955,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G1061" t="n">
-        <v>3.90254211425781</v>
+        <v>3.90254187583923</v>
       </c>
       <c r="H1061" t="s">
         <v>8</v>
@@ -27981,7 +27981,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1062" t="n">
-        <v>3.76387286186218</v>
+        <v>3.7638726234436</v>
       </c>
       <c r="H1062" t="s">
         <v>8</v>
@@ -28007,7 +28007,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1063" t="n">
-        <v>3.80349254608154</v>
+        <v>3.80349278450012</v>
       </c>
       <c r="H1063" t="s">
         <v>8</v>
@@ -28059,7 +28059,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G1065" t="n">
-        <v>3.98178148269653</v>
+        <v>3.98178124427795</v>
       </c>
       <c r="H1065" t="s">
         <v>8</v>
@@ -28111,7 +28111,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G1067" t="n">
-        <v>4.01149654388428</v>
+        <v>4.01149606704712</v>
       </c>
       <c r="H1067" t="s">
         <v>8</v>
@@ -28137,7 +28137,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1068" t="n">
-        <v>3.80349254608154</v>
+        <v>3.80349278450012</v>
       </c>
       <c r="H1068" t="s">
         <v>8</v>
@@ -28163,7 +28163,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1069" t="n">
-        <v>3.86292243003845</v>
+        <v>3.86292219161987</v>
       </c>
       <c r="H1069" t="s">
         <v>8</v>
@@ -28189,7 +28189,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1070" t="n">
-        <v>3.80349254608154</v>
+        <v>3.80349278450012</v>
       </c>
       <c r="H1070" t="s">
         <v>8</v>
@@ -28215,7 +28215,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1071" t="n">
-        <v>3.80349254608154</v>
+        <v>3.80349278450012</v>
       </c>
       <c r="H1071" t="s">
         <v>8</v>
@@ -28267,7 +28267,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1073" t="n">
-        <v>3.76387286186218</v>
+        <v>3.7638726234436</v>
       </c>
       <c r="H1073" t="s">
         <v>8</v>
@@ -28397,7 +28397,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G1078" t="n">
-        <v>3.73415803909302</v>
+        <v>3.7341582775116</v>
       </c>
       <c r="H1078" t="s">
         <v>8</v>
@@ -28553,7 +28553,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1084" t="n">
-        <v>3.6347188949585</v>
+        <v>3.63471913337708</v>
       </c>
       <c r="H1084" t="s">
         <v>8</v>
@@ -28865,7 +28865,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1096" t="n">
-        <v>3.6347188949585</v>
+        <v>3.63471913337708</v>
       </c>
       <c r="H1096" t="s">
         <v>8</v>
@@ -28943,7 +28943,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1099" t="n">
-        <v>3.6347188949585</v>
+        <v>3.63471913337708</v>
       </c>
       <c r="H1099" t="s">
         <v>8</v>
@@ -29073,7 +29073,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G1104" t="n">
-        <v>3.55527138710022</v>
+        <v>3.55527114868164</v>
       </c>
       <c r="H1104" t="s">
         <v>8</v>
@@ -29099,7 +29099,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1105" t="n">
-        <v>3.67444252967834</v>
+        <v>3.67444276809692</v>
       </c>
       <c r="H1105" t="s">
         <v>8</v>
@@ -29281,7 +29281,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1112" t="n">
-        <v>3.50561690330505</v>
+        <v>3.50561666488647</v>
       </c>
       <c r="H1112" t="s">
         <v>8</v>
@@ -29307,7 +29307,7 @@
         <v>3.5</v>
       </c>
       <c r="G1113" t="n">
-        <v>3.47582411766052</v>
+        <v>3.47582387924194</v>
       </c>
       <c r="H1113" t="s">
         <v>8</v>
@@ -29333,7 +29333,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1114" t="n">
-        <v>3.43610048294067</v>
+        <v>3.43610024452209</v>
       </c>
       <c r="H1114" t="s">
         <v>8</v>
@@ -29359,7 +29359,7 @@
         <v>3.5</v>
       </c>
       <c r="G1115" t="n">
-        <v>3.47582411766052</v>
+        <v>3.47582387924194</v>
       </c>
       <c r="H1115" t="s">
         <v>8</v>
@@ -29385,7 +29385,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1116" t="n">
-        <v>3.43610048294067</v>
+        <v>3.43610024452209</v>
       </c>
       <c r="H1116" t="s">
         <v>8</v>
@@ -29437,7 +29437,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1118" t="n">
-        <v>3.51554775238037</v>
+        <v>3.51554751396179</v>
       </c>
       <c r="H1118" t="s">
         <v>8</v>
@@ -29515,7 +29515,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1121" t="n">
-        <v>3.50561690330505</v>
+        <v>3.50561666488647</v>
       </c>
       <c r="H1121" t="s">
         <v>8</v>
@@ -29541,7 +29541,7 @@
         <v>3.5</v>
       </c>
       <c r="G1122" t="n">
-        <v>3.47582411766052</v>
+        <v>3.47582387924194</v>
       </c>
       <c r="H1122" t="s">
         <v>8</v>
@@ -29567,7 +29567,7 @@
         <v>3.5</v>
       </c>
       <c r="G1123" t="n">
-        <v>3.47582411766052</v>
+        <v>3.47582387924194</v>
       </c>
       <c r="H1123" t="s">
         <v>8</v>
@@ -29619,7 +29619,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1125" t="n">
-        <v>3.41623854637146</v>
+        <v>3.41623830795288</v>
       </c>
       <c r="H1125" t="s">
         <v>8</v>
@@ -29645,7 +29645,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1126" t="n">
-        <v>3.41623854637146</v>
+        <v>3.41623830795288</v>
       </c>
       <c r="H1126" t="s">
         <v>8</v>
@@ -29671,7 +29671,7 @@
         <v>3.5</v>
       </c>
       <c r="G1127" t="n">
-        <v>3.47582411766052</v>
+        <v>3.47582387924194</v>
       </c>
       <c r="H1127" t="s">
         <v>8</v>
@@ -29697,7 +29697,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1128" t="n">
-        <v>3.51554775238037</v>
+        <v>3.51554751396179</v>
       </c>
       <c r="H1128" t="s">
         <v>8</v>
@@ -29801,7 +29801,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1132" t="n">
-        <v>3.41623854637146</v>
+        <v>3.41623830795288</v>
       </c>
       <c r="H1132" t="s">
         <v>8</v>
@@ -29931,7 +29931,7 @@
         <v>3.5</v>
       </c>
       <c r="G1137" t="n">
-        <v>3.47582411766052</v>
+        <v>3.47582387924194</v>
       </c>
       <c r="H1137" t="s">
         <v>8</v>
@@ -30009,7 +30009,7 @@
         <v>3.5</v>
       </c>
       <c r="G1140" t="n">
-        <v>3.47582411766052</v>
+        <v>3.47582387924194</v>
       </c>
       <c r="H1140" t="s">
         <v>8</v>
@@ -30087,7 +30087,7 @@
         <v>3.5</v>
       </c>
       <c r="G1143" t="n">
-        <v>3.47582411766052</v>
+        <v>3.47582387924194</v>
       </c>
       <c r="H1143" t="s">
         <v>8</v>
@@ -30139,7 +30139,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G1145" t="n">
-        <v>3.55527138710022</v>
+        <v>3.55527114868164</v>
       </c>
       <c r="H1145" t="s">
         <v>8</v>
@@ -30165,7 +30165,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1146" t="n">
-        <v>3.67444252967834</v>
+        <v>3.67444276809692</v>
       </c>
       <c r="H1146" t="s">
         <v>8</v>
@@ -30191,7 +30191,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1147" t="n">
-        <v>3.71416616439819</v>
+        <v>3.71416640281677</v>
       </c>
       <c r="H1147" t="s">
         <v>8</v>
@@ -30269,7 +30269,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1150" t="n">
-        <v>3.67444252967834</v>
+        <v>3.67444276809692</v>
       </c>
       <c r="H1150" t="s">
         <v>8</v>
@@ -30321,7 +30321,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1152" t="n">
-        <v>3.67444252967834</v>
+        <v>3.67444276809692</v>
       </c>
       <c r="H1152" t="s">
         <v>8</v>
@@ -30555,7 +30555,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G1161" t="n">
-        <v>3.55527138710022</v>
+        <v>3.55527114868164</v>
       </c>
       <c r="H1161" t="s">
         <v>8</v>
@@ -30763,7 +30763,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G1169" t="n">
-        <v>3.55527138710022</v>
+        <v>3.55527114868164</v>
       </c>
       <c r="H1169" t="s">
         <v>8</v>
@@ -30789,7 +30789,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1170" t="n">
-        <v>3.6347188949585</v>
+        <v>3.63471913337708</v>
       </c>
       <c r="H1170" t="s">
         <v>8</v>
@@ -30815,7 +30815,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1171" t="n">
-        <v>3.6347188949585</v>
+        <v>3.63471913337708</v>
       </c>
       <c r="H1171" t="s">
         <v>8</v>
@@ -31049,7 +31049,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G1180" t="n">
-        <v>3.55527138710022</v>
+        <v>3.55527114868164</v>
       </c>
       <c r="H1180" t="s">
         <v>8</v>
@@ -31101,7 +31101,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1182" t="n">
-        <v>3.50561690330505</v>
+        <v>3.50561666488647</v>
       </c>
       <c r="H1182" t="s">
         <v>8</v>
@@ -31127,7 +31127,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1183" t="n">
-        <v>3.50561690330505</v>
+        <v>3.50561666488647</v>
       </c>
       <c r="H1183" t="s">
         <v>8</v>
@@ -31179,7 +31179,7 @@
         <v>3.5</v>
       </c>
       <c r="G1185" t="n">
-        <v>3.47582411766052</v>
+        <v>3.47582387924194</v>
       </c>
       <c r="H1185" t="s">
         <v>8</v>
@@ -31257,7 +31257,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1188" t="n">
-        <v>3.41623854637146</v>
+        <v>3.41623830795288</v>
       </c>
       <c r="H1188" t="s">
         <v>8</v>
@@ -31413,7 +31413,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G1194" t="n">
-        <v>2.93955421447754</v>
+        <v>2.93955397605896</v>
       </c>
       <c r="H1194" t="s">
         <v>8</v>
@@ -31751,7 +31751,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G1207" t="n">
-        <v>2.76079750061035</v>
+        <v>2.76079726219177</v>
       </c>
       <c r="H1207" t="s">
         <v>8</v>
@@ -31777,7 +31777,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G1208" t="n">
-        <v>2.70121192932129</v>
+        <v>2.70121169090271</v>
       </c>
       <c r="H1208" t="s">
         <v>8</v>
@@ -32245,7 +32245,7 @@
         <v>3</v>
       </c>
       <c r="G1226" t="n">
-        <v>2.97927784919739</v>
+        <v>2.97927761077881</v>
       </c>
       <c r="H1226" t="s">
         <v>8</v>
@@ -32297,7 +32297,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G1228" t="n">
-        <v>2.93955421447754</v>
+        <v>2.93955397605896</v>
       </c>
       <c r="H1228" t="s">
         <v>8</v>
@@ -32349,7 +32349,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G1230" t="n">
-        <v>2.93955421447754</v>
+        <v>2.93955397605896</v>
       </c>
       <c r="H1230" t="s">
         <v>8</v>
@@ -32375,7 +32375,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G1231" t="n">
-        <v>2.93955421447754</v>
+        <v>2.93955397605896</v>
       </c>
       <c r="H1231" t="s">
         <v>8</v>
@@ -32401,7 +32401,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G1232" t="n">
-        <v>2.93955421447754</v>
+        <v>2.93955397605896</v>
       </c>
       <c r="H1232" t="s">
         <v>8</v>
@@ -32479,7 +32479,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1235" t="n">
-        <v>2.87996864318848</v>
+        <v>2.8799684047699</v>
       </c>
       <c r="H1235" t="s">
         <v>8</v>
@@ -32765,7 +32765,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G1246" t="n">
-        <v>2.58204078674316</v>
+        <v>2.58204054832458</v>
       </c>
       <c r="H1246" t="s">
         <v>8</v>
@@ -32999,7 +32999,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G1255" t="n">
-        <v>2.66148829460144</v>
+        <v>2.66148805618286</v>
       </c>
       <c r="H1255" t="s">
         <v>8</v>
@@ -33155,7 +33155,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1261" t="n">
-        <v>2.87996864318848</v>
+        <v>2.8799684047699</v>
       </c>
       <c r="H1261" t="s">
         <v>8</v>
@@ -33207,7 +33207,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G1263" t="n">
-        <v>2.84024477005005</v>
+        <v>2.84024453163147</v>
       </c>
       <c r="H1263" t="s">
         <v>8</v>
@@ -33233,7 +33233,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1264" t="n">
-        <v>2.87996864318848</v>
+        <v>2.8799684047699</v>
       </c>
       <c r="H1264" t="s">
         <v>8</v>
@@ -33389,7 +33389,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G1270" t="n">
-        <v>2.76079750061035</v>
+        <v>2.76079726219177</v>
       </c>
       <c r="H1270" t="s">
         <v>8</v>
@@ -33441,7 +33441,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G1272" t="n">
-        <v>2.76079750061035</v>
+        <v>2.76079726219177</v>
       </c>
       <c r="H1272" t="s">
         <v>8</v>
@@ -33493,7 +33493,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G1274" t="n">
-        <v>2.84024477005005</v>
+        <v>2.84024453163147</v>
       </c>
       <c r="H1274" t="s">
         <v>8</v>
@@ -33675,7 +33675,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G1281" t="n">
-        <v>2.84024477005005</v>
+        <v>2.84024453163147</v>
       </c>
       <c r="H1281" t="s">
         <v>8</v>
@@ -33831,7 +33831,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G1287" t="n">
-        <v>2.66148829460144</v>
+        <v>2.66148805618286</v>
       </c>
       <c r="H1287" t="s">
         <v>8</v>
@@ -33857,7 +33857,7 @@
         <v>2.5</v>
       </c>
       <c r="G1288" t="n">
-        <v>2.48273158073425</v>
+        <v>2.48273134231567</v>
       </c>
       <c r="H1288" t="s">
         <v>8</v>
@@ -34013,7 +34013,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G1294" t="n">
-        <v>2.62176465988159</v>
+        <v>2.62176442146301</v>
       </c>
       <c r="H1294" t="s">
         <v>8</v>
@@ -34247,7 +34247,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1303" t="n">
-        <v>2.87996864318848</v>
+        <v>2.8799684047699</v>
       </c>
       <c r="H1303" t="s">
         <v>8</v>
@@ -34377,7 +34377,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G1308" t="n">
-        <v>2.84024477005005</v>
+        <v>2.84024453163147</v>
       </c>
       <c r="H1308" t="s">
         <v>8</v>
@@ -34429,7 +34429,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G1310" t="n">
-        <v>2.8005211353302</v>
+        <v>2.80052089691162</v>
       </c>
       <c r="H1310" t="s">
         <v>8</v>
@@ -34533,7 +34533,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G1314" t="n">
-        <v>2.93955421447754</v>
+        <v>2.93955397605896</v>
       </c>
       <c r="H1314" t="s">
         <v>8</v>
@@ -43480,6 +43480,32 @@
         <v>3.4300000667572</v>
       </c>
       <c r="H1658" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1659">
+      <c r="A1659" s="1" t="n">
+        <v>46288.2916666667</v>
+      </c>
+      <c r="B1659" t="n">
+        <v>48802</v>
+      </c>
+      <c r="C1659" t="n">
+        <v>3.51999998092651</v>
+      </c>
+      <c r="D1659" t="n">
+        <v>3.3050000667572</v>
+      </c>
+      <c r="E1659" t="n">
+        <v>3.51999998092651</v>
+      </c>
+      <c r="F1659" t="n">
+        <v>3.41000008583069</v>
+      </c>
+      <c r="G1659" t="n">
+        <v>3.41000008583069</v>
+      </c>
+      <c r="H1659" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/UD.MI.xlsx
+++ b/data/UD.MI.xlsx
@@ -421,7 +421,7 @@
         <v>1.5</v>
       </c>
       <c r="G2" t="n">
-        <v>1.47885525226593</v>
+        <v>1.47885513305664</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G7" t="n">
-        <v>1.51829123497009</v>
+        <v>1.51829135417938</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G8" t="n">
-        <v>1.53800928592682</v>
+        <v>1.53800940513611</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G9" t="n">
-        <v>1.55772757530212</v>
+        <v>1.55772745609283</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G10" t="n">
-        <v>1.53800928592682</v>
+        <v>1.53800940513611</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G11" t="n">
-        <v>1.56265687942505</v>
+        <v>1.56265711784363</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G13" t="n">
-        <v>1.55772757530212</v>
+        <v>1.55772745609283</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G15" t="n">
-        <v>1.64645874500275</v>
+        <v>1.64645862579346</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G18" t="n">
-        <v>1.67603588104248</v>
+        <v>1.67603600025177</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G19" t="n">
-        <v>1.67603588104248</v>
+        <v>1.67603600025177</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G22" t="n">
-        <v>1.62181127071381</v>
+        <v>1.62181103229523</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G23" t="n">
-        <v>1.59716355800629</v>
+        <v>1.59716367721558</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G25" t="n">
-        <v>1.58730447292328</v>
+        <v>1.58730459213257</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G32" t="n">
-        <v>1.59716355800629</v>
+        <v>1.59716367721558</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G33" t="n">
-        <v>1.6168817281723</v>
+        <v>1.61688148975372</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G39" t="n">
-        <v>1.67110657691956</v>
+        <v>1.67110645771027</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G40" t="n">
-        <v>1.69575393199921</v>
+        <v>1.69575381278992</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G46" t="n">
-        <v>1.67603588104248</v>
+        <v>1.67603600025177</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G52" t="n">
-        <v>1.74011957645416</v>
+        <v>1.74011969566345</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>1.74500000476837</v>
       </c>
       <c r="G53" t="n">
-        <v>1.72040152549744</v>
+        <v>1.72040164470673</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G56" t="n">
-        <v>1.69575393199921</v>
+        <v>1.69575381278992</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G57" t="n">
-        <v>1.67603588104248</v>
+        <v>1.67603600025177</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>1.7150000333786</v>
       </c>
       <c r="G58" t="n">
-        <v>1.69082462787628</v>
+        <v>1.69082450866699</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>1.7150000333786</v>
       </c>
       <c r="G59" t="n">
-        <v>1.69082462787628</v>
+        <v>1.69082450866699</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G60" t="n">
-        <v>1.71547210216522</v>
+        <v>1.71547198295593</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G61" t="n">
-        <v>1.71547210216522</v>
+        <v>1.71547198295593</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>1.68499994277954</v>
       </c>
       <c r="G63" t="n">
-        <v>1.66124713420868</v>
+        <v>1.66124737262726</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G66" t="n">
-        <v>1.67603588104248</v>
+        <v>1.67603600025177</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G72" t="n">
-        <v>1.64645874500275</v>
+        <v>1.64645862579346</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>1.65499997138977</v>
       </c>
       <c r="G73" t="n">
-        <v>1.63167011737823</v>
+        <v>1.63166999816895</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G74" t="n">
-        <v>1.64645874500275</v>
+        <v>1.64645862579346</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G76" t="n">
-        <v>1.67110657691956</v>
+        <v>1.67110645771027</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G78" t="n">
-        <v>1.64645874500275</v>
+        <v>1.64645862579346</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G79" t="n">
-        <v>1.67603588104248</v>
+        <v>1.67603600025177</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G80" t="n">
-        <v>1.67603588104248</v>
+        <v>1.67603600025177</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G81" t="n">
-        <v>1.67603588104248</v>
+        <v>1.67603600025177</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G95" t="n">
-        <v>1.58730447292328</v>
+        <v>1.58730459213257</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G96" t="n">
-        <v>1.62181127071381</v>
+        <v>1.62181103229523</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G97" t="n">
-        <v>1.58730447292328</v>
+        <v>1.58730459213257</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G98" t="n">
-        <v>1.58730447292328</v>
+        <v>1.58730459213257</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>1.63499999046326</v>
       </c>
       <c r="G105" t="n">
-        <v>1.61195194721222</v>
+        <v>1.6119521856308</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>1.66499996185303</v>
       </c>
       <c r="G106" t="n">
-        <v>1.64152932167053</v>
+        <v>1.64152920246124</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G110" t="n">
-        <v>1.67603588104248</v>
+        <v>1.67603600025177</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G111" t="n">
-        <v>1.67603588104248</v>
+        <v>1.67603600025177</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G112" t="n">
-        <v>1.67603588104248</v>
+        <v>1.67603600025177</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G113" t="n">
-        <v>1.67603588104248</v>
+        <v>1.67603600025177</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G114" t="n">
-        <v>1.67603588104248</v>
+        <v>1.67603600025177</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G115" t="n">
-        <v>1.67603588104248</v>
+        <v>1.67603600025177</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G116" t="n">
-        <v>1.71547210216522</v>
+        <v>1.71547198295593</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G124" t="n">
-        <v>1.85349857807159</v>
+        <v>1.8534984588623</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G130" t="n">
-        <v>1.83871006965637</v>
+        <v>1.83870995044708</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G132" t="n">
-        <v>1.78448510169983</v>
+        <v>1.78448522090912</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G133" t="n">
-        <v>1.85349857807159</v>
+        <v>1.8534984588623</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G134" t="n">
-        <v>1.85349857807159</v>
+        <v>1.8534984588623</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G135" t="n">
-        <v>1.85349857807159</v>
+        <v>1.8534984588623</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G137" t="n">
-        <v>1.88307547569275</v>
+        <v>1.88307559490204</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G138" t="n">
-        <v>1.88307547569275</v>
+        <v>1.88307559490204</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G145" t="n">
-        <v>1.79434430599213</v>
+        <v>1.79434442520142</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G146" t="n">
-        <v>1.79434430599213</v>
+        <v>1.79434442520142</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G147" t="n">
-        <v>1.79434430599213</v>
+        <v>1.79434442520142</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G149" t="n">
-        <v>1.79434430599213</v>
+        <v>1.79434442520142</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G150" t="n">
-        <v>1.79434430599213</v>
+        <v>1.79434442520142</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G151" t="n">
-        <v>1.74011957645416</v>
+        <v>1.74011969566345</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G152" t="n">
-        <v>1.7696967124939</v>
+        <v>1.76969659328461</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G157" t="n">
-        <v>1.83871006965637</v>
+        <v>1.83870995044708</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G164" t="n">
-        <v>1.71547210216522</v>
+        <v>1.71547198295593</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G170" t="n">
-        <v>1.83871006965637</v>
+        <v>1.83870995044708</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G171" t="n">
-        <v>1.83871006965637</v>
+        <v>1.83870995044708</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G172" t="n">
-        <v>1.81406235694885</v>
+        <v>1.81406259536743</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G173" t="n">
-        <v>1.82885086536407</v>
+        <v>1.82885098457336</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G174" t="n">
-        <v>1.82885086536407</v>
+        <v>1.82885098457336</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G176" t="n">
-        <v>1.83871006965637</v>
+        <v>1.83870995044708</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G179" t="n">
-        <v>1.88307547569275</v>
+        <v>1.88307559490204</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G180" t="n">
-        <v>1.88800525665283</v>
+        <v>1.88800513744354</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G181" t="n">
-        <v>1.90279364585876</v>
+        <v>1.90279352664948</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G182" t="n">
-        <v>1.91265285015106</v>
+        <v>1.91265273094177</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G183" t="n">
-        <v>2.03096103668213</v>
+        <v>2.03096127510071</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G184" t="n">
-        <v>2.01124310493469</v>
+        <v>2.01124286651611</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G185" t="n">
-        <v>2.03096103668213</v>
+        <v>2.03096127510071</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G187" t="n">
-        <v>1.95208883285522</v>
+        <v>1.95208895206451</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G188" t="n">
-        <v>2.01124310493469</v>
+        <v>2.01124286651611</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G189" t="n">
-        <v>2.01124310493469</v>
+        <v>2.01124286651611</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G191" t="n">
-        <v>1.9323707818985</v>
+        <v>1.93237090110779</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G192" t="n">
-        <v>1.9323707818985</v>
+        <v>1.93237090110779</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G193" t="n">
-        <v>1.9323707818985</v>
+        <v>1.93237090110779</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G195" t="n">
-        <v>1.86335754394531</v>
+        <v>1.86335742473602</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G196" t="n">
-        <v>1.89293467998505</v>
+        <v>1.89293456077576</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G197" t="n">
-        <v>1.91265285015106</v>
+        <v>1.91265273094177</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G198" t="n">
-        <v>1.91265285015106</v>
+        <v>1.91265273094177</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G202" t="n">
-        <v>1.91265285015106</v>
+        <v>1.91265273094177</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G203" t="n">
-        <v>1.90772306919098</v>
+        <v>1.90772294998169</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G205" t="n">
-        <v>1.9323707818985</v>
+        <v>1.93237090110779</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G208" t="n">
-        <v>1.95208883285522</v>
+        <v>1.95208895206451</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G210" t="n">
-        <v>1.95701825618744</v>
+        <v>1.95701837539673</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G215" t="n">
-        <v>1.95701825618744</v>
+        <v>1.95701837539673</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G216" t="n">
-        <v>1.91265285015106</v>
+        <v>1.91265273094177</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G218" t="n">
-        <v>1.89293467998505</v>
+        <v>1.89293456077576</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G219" t="n">
-        <v>1.89293467998505</v>
+        <v>1.89293456077576</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G226" t="n">
-        <v>1.99152481555939</v>
+        <v>1.99152493476868</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G228" t="n">
-        <v>2.00138401985168</v>
+        <v>2.00138425827026</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G229" t="n">
-        <v>2.08025622367859</v>
+        <v>2.08025598526001</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G230" t="n">
-        <v>2.02110195159912</v>
+        <v>2.0211021900177</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G231" t="n">
-        <v>2.22814202308655</v>
+        <v>2.22814154624939</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G232" t="n">
-        <v>2.267578125</v>
+        <v>2.26757764816284</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>2.25</v>
       </c>
       <c r="G233" t="n">
-        <v>2.21828269958496</v>
+        <v>2.21828293800354</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G235" t="n">
-        <v>2.14926958084106</v>
+        <v>2.14926981925964</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G236" t="n">
-        <v>2.19856476783752</v>
+        <v>2.1985650062561</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G237" t="n">
-        <v>2.18870568275452</v>
+        <v>2.1887059211731</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>2.25</v>
       </c>
       <c r="G239" t="n">
-        <v>2.21828269958496</v>
+        <v>2.21828293800354</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G240" t="n">
-        <v>2.20842361450195</v>
+        <v>2.20842385292053</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G241" t="n">
-        <v>2.22814202308655</v>
+        <v>2.22814154624939</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G242" t="n">
-        <v>2.25771903991699</v>
+        <v>2.25771880149841</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G243" t="n">
-        <v>2.267578125</v>
+        <v>2.26757764816284</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G244" t="n">
-        <v>2.29715514183044</v>
+        <v>2.29715490341187</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G245" t="n">
-        <v>2.29715514183044</v>
+        <v>2.29715490341187</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G246" t="n">
-        <v>2.28729557991028</v>
+        <v>2.28729581832886</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G247" t="n">
-        <v>2.28729557991028</v>
+        <v>2.28729581832886</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G253" t="n">
-        <v>2.40560460090637</v>
+        <v>2.40560436248779</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G254" t="n">
-        <v>2.4844765663147</v>
+        <v>2.48447680473328</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>2.5</v>
       </c>
       <c r="G255" t="n">
-        <v>2.46475863456726</v>
+        <v>2.46475887298584</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G258" t="n">
-        <v>2.61264419555664</v>
+        <v>2.6126446723938</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G260" t="n">
-        <v>2.74081158638</v>
+        <v>2.74081182479858</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G261" t="n">
-        <v>2.66193962097168</v>
+        <v>2.6619393825531</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G263" t="n">
-        <v>2.97742819786072</v>
+        <v>2.9774284362793</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>3</v>
       </c>
       <c r="G265" t="n">
-        <v>2.95771050453186</v>
+        <v>2.95771026611328</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G267" t="n">
-        <v>2.8394021987915</v>
+        <v>2.83940196037292</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G270" t="n">
-        <v>2.77038860321045</v>
+        <v>2.77038884162903</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G271" t="n">
-        <v>2.84926128387451</v>
+        <v>2.84926104545593</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G272" t="n">
-        <v>2.99714636802673</v>
+        <v>2.99714660644531</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G274" t="n">
-        <v>3.26334023475647</v>
+        <v>3.26333999633789</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G275" t="n">
-        <v>3.26334023475647</v>
+        <v>3.26333999633789</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G276" t="n">
-        <v>3.29291749000549</v>
+        <v>3.29291725158691</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G277" t="n">
-        <v>3.17460894584656</v>
+        <v>3.17460918426514</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G278" t="n">
-        <v>3.18446826934814</v>
+        <v>3.18446850776672</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G281" t="n">
-        <v>3.18446826934814</v>
+        <v>3.18446850776672</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G283" t="n">
-        <v>3.24362254142761</v>
+        <v>3.24362206459045</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G284" t="n">
-        <v>3.19432711601257</v>
+        <v>3.19432735443115</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G285" t="n">
-        <v>3.35207176208496</v>
+        <v>3.35207200050354</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G290" t="n">
-        <v>3.72671508789062</v>
+        <v>3.72671484947205</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G294" t="n">
-        <v>3.53939342498779</v>
+        <v>3.53939318656921</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G297" t="n">
-        <v>3.55911159515381</v>
+        <v>3.55911135673523</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G300" t="n">
-        <v>3.48023915290833</v>
+        <v>3.4802393913269</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G307" t="n">
-        <v>3.97319149971008</v>
+        <v>3.97319102287292</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G309" t="n">
-        <v>4.35769319534302</v>
+        <v>4.35769367218018</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G311" t="n">
-        <v>4.14079427719116</v>
+        <v>4.14079475402832</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G312" t="n">
-        <v>3.99290943145752</v>
+        <v>3.99290895462036</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>4</v>
       </c>
       <c r="G313" t="n">
-        <v>3.9436137676239</v>
+        <v>3.94361352920532</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G314" t="n">
-        <v>4.05206346511841</v>
+        <v>4.05206298828125</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G316" t="n">
-        <v>4.08164024353027</v>
+        <v>4.08163976669312</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G317" t="n">
-        <v>4.14079427719116</v>
+        <v>4.14079475402832</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G323" t="n">
-        <v>4.18023014068604</v>
+        <v>4.18023061752319</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G324" t="n">
-        <v>4.18023014068604</v>
+        <v>4.18023061752319</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G325" t="n">
-        <v>4.06192207336426</v>
+        <v>4.06192255020142</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G326" t="n">
-        <v>4.00276803970337</v>
+        <v>4.00276851654053</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G327" t="n">
-        <v>4.16051244735718</v>
+        <v>4.16051197052002</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G328" t="n">
-        <v>4.16051244735718</v>
+        <v>4.16051197052002</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G329" t="n">
-        <v>4.02248620986938</v>
+        <v>4.02248573303223</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G330" t="n">
-        <v>3.98304963111877</v>
+        <v>3.98304986953735</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G333" t="n">
-        <v>4.16051244735718</v>
+        <v>4.16051197052002</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G334" t="n">
-        <v>4.16051244735718</v>
+        <v>4.16051197052002</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G336" t="n">
-        <v>4.00276803970337</v>
+        <v>4.00276851654053</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G337" t="n">
-        <v>4.00276803970337</v>
+        <v>4.00276851654053</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G338" t="n">
-        <v>4.16051244735718</v>
+        <v>4.16051197052002</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G339" t="n">
-        <v>4.16051244735718</v>
+        <v>4.16051197052002</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G340" t="n">
-        <v>4.14079427719116</v>
+        <v>4.14079475402832</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G341" t="n">
-        <v>4.14079427719116</v>
+        <v>4.14079475402832</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G342" t="n">
-        <v>4.06192207336426</v>
+        <v>4.06192255020142</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G343" t="n">
-        <v>4.14079427719116</v>
+        <v>4.14079475402832</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G345" t="n">
-        <v>4.08164024353027</v>
+        <v>4.08163976669312</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G346" t="n">
-        <v>4.04220390319824</v>
+        <v>4.0422043800354</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G347" t="n">
-        <v>4.02248620986938</v>
+        <v>4.02248573303223</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G348" t="n">
-        <v>4.02248620986938</v>
+        <v>4.02248573303223</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G349" t="n">
-        <v>4.21966648101807</v>
+        <v>4.21966695785522</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G352" t="n">
-        <v>4.19994926452637</v>
+        <v>4.19994878768921</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>4.25</v>
       </c>
       <c r="G354" t="n">
-        <v>4.19009017944336</v>
+        <v>4.1900897026062</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G355" t="n">
-        <v>4.08164024353027</v>
+        <v>4.08163976669312</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G356" t="n">
-        <v>4.14079427719116</v>
+        <v>4.14079475402832</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G357" t="n">
-        <v>4.05206346511841</v>
+        <v>4.05206298828125</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G359" t="n">
-        <v>4.21966648101807</v>
+        <v>4.21966695785522</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G361" t="n">
-        <v>4.08164024353027</v>
+        <v>4.08163976669312</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G363" t="n">
-        <v>4.12107610702515</v>
+        <v>4.1210765838623</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G364" t="n">
-        <v>4.12107610702515</v>
+        <v>4.1210765838623</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G365" t="n">
-        <v>4.12107610702515</v>
+        <v>4.1210765838623</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G366" t="n">
-        <v>4.14079427719116</v>
+        <v>4.14079475402832</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G367" t="n">
-        <v>4.14079427719116</v>
+        <v>4.14079475402832</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G368" t="n">
-        <v>4.14079427719116</v>
+        <v>4.14079475402832</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G369" t="n">
-        <v>4.08164024353027</v>
+        <v>4.08163976669312</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G371" t="n">
-        <v>4.01262760162354</v>
+        <v>4.01262712478638</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G372" t="n">
-        <v>4.08164024353027</v>
+        <v>4.08163976669312</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G373" t="n">
-        <v>4.14079427719116</v>
+        <v>4.14079475402832</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G374" t="n">
-        <v>4.14079427719116</v>
+        <v>4.14079475402832</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G375" t="n">
-        <v>4.14079427719116</v>
+        <v>4.14079475402832</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G376" t="n">
-        <v>4.19994926452637</v>
+        <v>4.19994878768921</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G377" t="n">
-        <v>4.22952556610107</v>
+        <v>4.22952508926392</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G379" t="n">
-        <v>4.21966648101807</v>
+        <v>4.21966695785522</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G380" t="n">
-        <v>4.21966648101807</v>
+        <v>4.21966695785522</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G382" t="n">
-        <v>4.29853916168213</v>
+        <v>4.29853963851929</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G383" t="n">
-        <v>4.30839824676514</v>
+        <v>4.30839776992798</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G385" t="n">
-        <v>4.36755180358887</v>
+        <v>4.36755228042603</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G386" t="n">
-        <v>4.30839824676514</v>
+        <v>4.30839776992798</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G387" t="n">
-        <v>4.36755180358887</v>
+        <v>4.36755228042603</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G388" t="n">
-        <v>4.36755180358887</v>
+        <v>4.36755228042603</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G391" t="n">
-        <v>4.30839824676514</v>
+        <v>4.30839776992798</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>4.25</v>
       </c>
       <c r="G392" t="n">
-        <v>4.19009017944336</v>
+        <v>4.1900897026062</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G394" t="n">
-        <v>4.40698909759521</v>
+        <v>4.40698862075806</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G396" t="n">
-        <v>4.22952556610107</v>
+        <v>4.22952508926392</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>4.25</v>
       </c>
       <c r="G397" t="n">
-        <v>4.19009017944336</v>
+        <v>4.1900897026062</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G398" t="n">
-        <v>4.04220390319824</v>
+        <v>4.0422043800354</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G399" t="n">
-        <v>4.04220390319824</v>
+        <v>4.0422043800354</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G400" t="n">
-        <v>4.04220390319824</v>
+        <v>4.0422043800354</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G401" t="n">
-        <v>4.18023014068604</v>
+        <v>4.18023061752319</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G402" t="n">
-        <v>4.19994926452637</v>
+        <v>4.19994878768921</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G403" t="n">
-        <v>4.29853916168213</v>
+        <v>4.29853963851929</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G406" t="n">
-        <v>4.39712953567505</v>
+        <v>4.39713001251221</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G411" t="n">
-        <v>5.04782581329346</v>
+        <v>5.0478253364563</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G412" t="n">
-        <v>5.30416059494019</v>
+        <v>5.30416011810303</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G413" t="n">
-        <v>5.24500703811646</v>
+        <v>5.2450065612793</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>5</v>
       </c>
       <c r="G414" t="n">
-        <v>4.92951726913452</v>
+        <v>4.92951774597168</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>5</v>
       </c>
       <c r="G415" t="n">
-        <v>4.92951726913452</v>
+        <v>4.92951774597168</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G416" t="n">
-        <v>4.96895313262939</v>
+        <v>4.96895360946655</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>5</v>
       </c>
       <c r="G417" t="n">
-        <v>4.92951726913452</v>
+        <v>4.92951774597168</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G420" t="n">
-        <v>5.00838899612427</v>
+        <v>5.00838947296143</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>5</v>
       </c>
       <c r="G421" t="n">
-        <v>4.92951726913452</v>
+        <v>4.92951774597168</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>5</v>
       </c>
       <c r="G422" t="n">
-        <v>4.92951726913452</v>
+        <v>4.92951774597168</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>5</v>
       </c>
       <c r="G423" t="n">
-        <v>4.92951726913452</v>
+        <v>4.92951774597168</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G428" t="n">
-        <v>5.00838899612427</v>
+        <v>5.00838947296143</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G429" t="n">
-        <v>5.12669801712036</v>
+        <v>5.1266975402832</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>5</v>
       </c>
       <c r="G430" t="n">
-        <v>4.92951726913452</v>
+        <v>4.92951774597168</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>5</v>
       </c>
       <c r="G432" t="n">
-        <v>4.92951726913452</v>
+        <v>4.92951774597168</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G433" t="n">
-        <v>4.88022184371948</v>
+        <v>4.88022232055664</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>5</v>
       </c>
       <c r="G434" t="n">
-        <v>4.92951726913452</v>
+        <v>4.92951774597168</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G435" t="n">
-        <v>4.78163242340088</v>
+        <v>4.78163194656372</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>5</v>
       </c>
       <c r="G438" t="n">
-        <v>4.92951726913452</v>
+        <v>4.92951774597168</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>5</v>
       </c>
       <c r="G440" t="n">
-        <v>4.92951726913452</v>
+        <v>4.92951774597168</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G443" t="n">
-        <v>5.04782581329346</v>
+        <v>5.0478253364563</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G445" t="n">
-        <v>4.96895313262939</v>
+        <v>4.96895360946655</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>5</v>
       </c>
       <c r="G448" t="n">
-        <v>4.92951726913452</v>
+        <v>4.92951774597168</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>5</v>
       </c>
       <c r="G449" t="n">
-        <v>4.92951726913452</v>
+        <v>4.92951774597168</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>5</v>
       </c>
       <c r="G452" t="n">
-        <v>4.92951726913452</v>
+        <v>4.92951774597168</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12147,7 +12147,7 @@
         <v>5</v>
       </c>
       <c r="G453" t="n">
-        <v>4.92951726913452</v>
+        <v>4.92951774597168</v>
       </c>
       <c r="H453" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>5</v>
       </c>
       <c r="G456" t="n">
-        <v>4.92951726913452</v>
+        <v>4.92951774597168</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G457" t="n">
-        <v>5.04782581329346</v>
+        <v>5.0478253364563</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G458" t="n">
-        <v>5.50134134292603</v>
+        <v>5.50134086608887</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G459" t="n">
-        <v>5.26472425460815</v>
+        <v>5.26472473144531</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G461" t="n">
-        <v>5.30416059494019</v>
+        <v>5.30416011810303</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G462" t="n">
-        <v>5.22528839111328</v>
+        <v>5.2252893447876</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G463" t="n">
-        <v>5.22528839111328</v>
+        <v>5.2252893447876</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G464" t="n">
-        <v>5.04782581329346</v>
+        <v>5.0478253364563</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G465" t="n">
-        <v>5.16613388061523</v>
+        <v>5.16613435745239</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G466" t="n">
-        <v>5.12669801712036</v>
+        <v>5.1266975402832</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G467" t="n">
-        <v>5.12669801712036</v>
+        <v>5.1266975402832</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G468" t="n">
-        <v>5.16613388061523</v>
+        <v>5.16613435745239</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G469" t="n">
-        <v>5.22528839111328</v>
+        <v>5.2252893447876</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G471" t="n">
-        <v>5.22528839111328</v>
+        <v>5.2252893447876</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G472" t="n">
-        <v>5.22528839111328</v>
+        <v>5.2252893447876</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G473" t="n">
-        <v>5.20557022094727</v>
+        <v>5.20557069778442</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G475" t="n">
-        <v>5.14641571044922</v>
+        <v>5.14641618728638</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G477" t="n">
-        <v>5.00838899612427</v>
+        <v>5.00838947296143</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G478" t="n">
-        <v>4.96895313262939</v>
+        <v>4.96895360946655</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G480" t="n">
-        <v>5.14641571044922</v>
+        <v>5.14641618728638</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G481" t="n">
-        <v>5.14641571044922</v>
+        <v>5.14641618728638</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G483" t="n">
-        <v>5.12669801712036</v>
+        <v>5.1266975402832</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G484" t="n">
-        <v>5.12669801712036</v>
+        <v>5.1266975402832</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G485" t="n">
-        <v>5.12669801712036</v>
+        <v>5.1266975402832</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G486" t="n">
-        <v>5.04782581329346</v>
+        <v>5.0478253364563</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G487" t="n">
-        <v>5.16613388061523</v>
+        <v>5.16613435745239</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G490" t="n">
-        <v>5.12669801712036</v>
+        <v>5.1266975402832</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G492" t="n">
-        <v>4.96895313262939</v>
+        <v>4.96895360946655</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G493" t="n">
-        <v>5.16613388061523</v>
+        <v>5.16613435745239</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G500" t="n">
-        <v>5.04782581329346</v>
+        <v>5.0478253364563</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G506" t="n">
-        <v>5.12669801712036</v>
+        <v>5.1266975402832</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13577,7 +13577,7 @@
         <v>5</v>
       </c>
       <c r="G508" t="n">
-        <v>4.92951726913452</v>
+        <v>4.92951774597168</v>
       </c>
       <c r="H508" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G513" t="n">
-        <v>5.00838899612427</v>
+        <v>5.00838947296143</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G514" t="n">
-        <v>4.96895313262939</v>
+        <v>4.96895360946655</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13785,7 +13785,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G516" t="n">
-        <v>5.00838899612427</v>
+        <v>5.00838947296143</v>
       </c>
       <c r="H516" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G518" t="n">
-        <v>5.00838899612427</v>
+        <v>5.00838947296143</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>5</v>
       </c>
       <c r="G519" t="n">
-        <v>4.92951726913452</v>
+        <v>4.92951774597168</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13915,7 +13915,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G521" t="n">
-        <v>5.20557022094727</v>
+        <v>5.20557069778442</v>
       </c>
       <c r="H521" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G522" t="n">
-        <v>5.04782581329346</v>
+        <v>5.0478253364563</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G525" t="n">
-        <v>4.88022184371948</v>
+        <v>4.88022232055664</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G526" t="n">
-        <v>5.00838899612427</v>
+        <v>5.00838947296143</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G528" t="n">
-        <v>4.80135011672974</v>
+        <v>4.80134963989258</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G529" t="n">
-        <v>4.77177238464355</v>
+        <v>4.77177286148071</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14149,7 +14149,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G530" t="n">
-        <v>4.732337474823</v>
+        <v>4.73233652114868</v>
       </c>
       <c r="H530" t="s">
         <v>8</v>
@@ -14175,7 +14175,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G531" t="n">
-        <v>4.80135011672974</v>
+        <v>4.80134963989258</v>
       </c>
       <c r="H531" t="s">
         <v>8</v>
@@ -14201,7 +14201,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G532" t="n">
-        <v>4.77177238464355</v>
+        <v>4.77177286148071</v>
       </c>
       <c r="H532" t="s">
         <v>8</v>
@@ -14227,7 +14227,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G533" t="n">
-        <v>4.79149103164673</v>
+        <v>4.79149055480957</v>
       </c>
       <c r="H533" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G534" t="n">
-        <v>4.732337474823</v>
+        <v>4.73233652114868</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G535" t="n">
-        <v>4.732337474823</v>
+        <v>4.73233652114868</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G537" t="n">
-        <v>4.732337474823</v>
+        <v>4.73233652114868</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G538" t="n">
-        <v>4.8999400138855</v>
+        <v>4.89994049072266</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G542" t="n">
-        <v>4.86050415039062</v>
+        <v>4.86050367355347</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G546" t="n">
-        <v>4.7520546913147</v>
+        <v>4.75205421447754</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G547" t="n">
-        <v>4.62362098693848</v>
+        <v>4.62362051010132</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G548" t="n">
-        <v>4.57422304153442</v>
+        <v>4.57422351837158</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G549" t="n">
-        <v>4.5939826965332</v>
+        <v>4.59398221969604</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>4.75</v>
       </c>
       <c r="G558" t="n">
-        <v>4.69277811050415</v>
+        <v>4.69277763366699</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>4.75</v>
       </c>
       <c r="G559" t="n">
-        <v>4.69277811050415</v>
+        <v>4.69277763366699</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G573" t="n">
-        <v>4.43590974807739</v>
+        <v>4.43590927124023</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15423,7 +15423,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G579" t="n">
-        <v>4.27783727645874</v>
+        <v>4.2778377532959</v>
       </c>
       <c r="H579" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G581" t="n">
-        <v>4.40627098083496</v>
+        <v>4.40627145767212</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G582" t="n">
-        <v>4.45566892623901</v>
+        <v>4.45566940307617</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G585" t="n">
-        <v>4.5939826965332</v>
+        <v>4.59398221969604</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G587" t="n">
-        <v>4.43590974807739</v>
+        <v>4.43590927124023</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G589" t="n">
-        <v>4.43590974807739</v>
+        <v>4.43590927124023</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G590" t="n">
-        <v>4.3865122795105</v>
+        <v>4.38651180267334</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G591" t="n">
-        <v>4.34699392318726</v>
+        <v>4.34699440002441</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G592" t="n">
-        <v>4.34699392318726</v>
+        <v>4.34699440002441</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15787,7 +15787,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G593" t="n">
-        <v>4.34699392318726</v>
+        <v>4.34699440002441</v>
       </c>
       <c r="H593" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G595" t="n">
-        <v>4.35687303543091</v>
+        <v>4.35687351226807</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G597" t="n">
-        <v>4.40627098083496</v>
+        <v>4.40627145767212</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G599" t="n">
-        <v>4.43590974807739</v>
+        <v>4.43590927124023</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -15995,7 +15995,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G601" t="n">
-        <v>4.54458475112915</v>
+        <v>4.54458427429199</v>
       </c>
       <c r="H601" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G602" t="n">
-        <v>4.5939826965332</v>
+        <v>4.59398221969604</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G606" t="n">
-        <v>4.89036798477173</v>
+        <v>4.89036846160889</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G607" t="n">
-        <v>4.70265769958496</v>
+        <v>4.7026572227478</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G608" t="n">
-        <v>4.70265769958496</v>
+        <v>4.7026572227478</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>4.75</v>
       </c>
       <c r="G612" t="n">
-        <v>4.69277811050415</v>
+        <v>4.69277763366699</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16359,7 +16359,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G615" t="n">
-        <v>4.88048887252808</v>
+        <v>4.88048839569092</v>
       </c>
       <c r="H615" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G616" t="n">
-        <v>4.97928380966187</v>
+        <v>4.97928428649902</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16411,7 +16411,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G617" t="n">
-        <v>4.97928380966187</v>
+        <v>4.97928428649902</v>
       </c>
       <c r="H617" t="s">
         <v>8</v>
@@ -16437,7 +16437,7 @@
         <v>5</v>
       </c>
       <c r="G618" t="n">
-        <v>4.93976545333862</v>
+        <v>4.93976593017578</v>
       </c>
       <c r="H618" t="s">
         <v>8</v>
@@ -16463,7 +16463,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G619" t="n">
-        <v>4.97928380966187</v>
+        <v>4.97928428649902</v>
       </c>
       <c r="H619" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G620" t="n">
-        <v>4.99904346466064</v>
+        <v>4.99904298782349</v>
       </c>
       <c r="H620" t="s">
         <v>8</v>
@@ -16515,7 +16515,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G621" t="n">
-        <v>5.01880168914795</v>
+        <v>5.01880264282227</v>
       </c>
       <c r="H621" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G622" t="n">
-        <v>5.01880168914795</v>
+        <v>5.01880264282227</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16567,7 +16567,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G623" t="n">
-        <v>5.01880168914795</v>
+        <v>5.01880264282227</v>
       </c>
       <c r="H623" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G624" t="n">
-        <v>5.03856134414673</v>
+        <v>5.03856086730957</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16619,7 +16619,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G625" t="n">
-        <v>5.03856134414673</v>
+        <v>5.03856086730957</v>
       </c>
       <c r="H625" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G628" t="n">
-        <v>4.87060928344727</v>
+        <v>4.87060880661011</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -16801,7 +16801,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G632" t="n">
-        <v>4.7520546913147</v>
+        <v>4.75205421447754</v>
       </c>
       <c r="H632" t="s">
         <v>8</v>
@@ -16879,7 +16879,7 @@
         <v>5</v>
       </c>
       <c r="G635" t="n">
-        <v>4.93976545333862</v>
+        <v>4.93976593017578</v>
       </c>
       <c r="H635" t="s">
         <v>8</v>
@@ -16905,7 +16905,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G636" t="n">
-        <v>4.89036798477173</v>
+        <v>4.89036846160889</v>
       </c>
       <c r="H636" t="s">
         <v>8</v>
@@ -16931,7 +16931,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G637" t="n">
-        <v>4.88048887252808</v>
+        <v>4.88048839569092</v>
       </c>
       <c r="H637" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G638" t="n">
-        <v>4.88048887252808</v>
+        <v>4.88048839569092</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G639" t="n">
-        <v>4.87060928344727</v>
+        <v>4.87060880661011</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17087,7 +17087,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G643" t="n">
-        <v>4.73229551315308</v>
+        <v>4.73229598999023</v>
       </c>
       <c r="H643" t="s">
         <v>8</v>
@@ -17113,7 +17113,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G644" t="n">
-        <v>4.54458475112915</v>
+        <v>4.54458427429199</v>
       </c>
       <c r="H644" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G647" t="n">
-        <v>4.34699392318726</v>
+        <v>4.34699440002441</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G648" t="n">
-        <v>4.34699392318726</v>
+        <v>4.34699440002441</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17269,7 +17269,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G650" t="n">
-        <v>4.52482509613037</v>
+        <v>4.52482557296753</v>
       </c>
       <c r="H650" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G651" t="n">
-        <v>4.61374187469482</v>
+        <v>4.61374139785767</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17555,7 +17555,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G661" t="n">
-        <v>4.88048887252808</v>
+        <v>4.88048839569092</v>
       </c>
       <c r="H661" t="s">
         <v>8</v>
@@ -17633,7 +17633,7 @@
         <v>5</v>
       </c>
       <c r="G664" t="n">
-        <v>4.93976545333862</v>
+        <v>4.93976593017578</v>
       </c>
       <c r="H664" t="s">
         <v>8</v>
@@ -17737,7 +17737,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G668" t="n">
-        <v>5.03856134414673</v>
+        <v>5.03856086730957</v>
       </c>
       <c r="H668" t="s">
         <v>8</v>
@@ -17763,7 +17763,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G669" t="n">
-        <v>5.1175971031189</v>
+        <v>5.11759757995605</v>
       </c>
       <c r="H669" t="s">
         <v>8</v>
@@ -17789,7 +17789,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G670" t="n">
-        <v>5.1175971031189</v>
+        <v>5.11759757995605</v>
       </c>
       <c r="H670" t="s">
         <v>8</v>
@@ -17815,7 +17815,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G671" t="n">
-        <v>5.03856134414673</v>
+        <v>5.03856086730957</v>
       </c>
       <c r="H671" t="s">
         <v>8</v>
@@ -17841,7 +17841,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G672" t="n">
-        <v>5.1175971031189</v>
+        <v>5.11759757995605</v>
       </c>
       <c r="H672" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G674" t="n">
-        <v>5.03856134414673</v>
+        <v>5.03856086730957</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G675" t="n">
-        <v>4.97928380966187</v>
+        <v>4.97928428649902</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -17945,7 +17945,7 @@
         <v>5</v>
       </c>
       <c r="G676" t="n">
-        <v>4.93976545333862</v>
+        <v>4.93976593017578</v>
       </c>
       <c r="H676" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G677" t="n">
-        <v>4.89036798477173</v>
+        <v>4.89036846160889</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -18023,7 +18023,7 @@
         <v>4.59000015258789</v>
       </c>
       <c r="G679" t="n">
-        <v>4.53470468521118</v>
+        <v>4.53470516204834</v>
       </c>
       <c r="H679" t="s">
         <v>8</v>
@@ -18049,7 +18049,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G680" t="n">
-        <v>4.73229551315308</v>
+        <v>4.73229598999023</v>
       </c>
       <c r="H680" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>4.71000003814697</v>
       </c>
       <c r="G681" t="n">
-        <v>4.65325975418091</v>
+        <v>4.65325927734375</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18101,7 +18101,7 @@
         <v>4.75</v>
       </c>
       <c r="G682" t="n">
-        <v>4.69277811050415</v>
+        <v>4.69277763366699</v>
       </c>
       <c r="H682" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>4.59000015258789</v>
       </c>
       <c r="G683" t="n">
-        <v>4.53470468521118</v>
+        <v>4.53470516204834</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18153,7 +18153,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G684" t="n">
-        <v>4.52482509613037</v>
+        <v>4.52482557296753</v>
       </c>
       <c r="H684" t="s">
         <v>8</v>
@@ -18179,7 +18179,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G685" t="n">
-        <v>4.34699392318726</v>
+        <v>4.34699440002441</v>
       </c>
       <c r="H685" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>4.75</v>
       </c>
       <c r="G689" t="n">
-        <v>4.69277811050415</v>
+        <v>4.69277763366699</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18309,7 +18309,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G690" t="n">
-        <v>4.7125358581543</v>
+        <v>4.71253681182861</v>
       </c>
       <c r="H690" t="s">
         <v>8</v>
@@ -18335,7 +18335,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G691" t="n">
-        <v>5.01880168914795</v>
+        <v>5.01880264282227</v>
       </c>
       <c r="H691" t="s">
         <v>8</v>
@@ -18361,7 +18361,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G692" t="n">
-        <v>5.03856134414673</v>
+        <v>5.03856086730957</v>
       </c>
       <c r="H692" t="s">
         <v>8</v>
@@ -18413,7 +18413,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G694" t="n">
-        <v>5.03856134414673</v>
+        <v>5.03856086730957</v>
       </c>
       <c r="H694" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G695" t="n">
-        <v>4.99904346466064</v>
+        <v>4.99904298782349</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18491,7 +18491,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G697" t="n">
-        <v>5.03856134414673</v>
+        <v>5.03856086730957</v>
       </c>
       <c r="H697" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G698" t="n">
-        <v>5.1175971031189</v>
+        <v>5.11759757995605</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18543,7 +18543,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G699" t="n">
-        <v>5.1175971031189</v>
+        <v>5.11759757995605</v>
       </c>
       <c r="H699" t="s">
         <v>8</v>
@@ -18569,7 +18569,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G700" t="n">
-        <v>5.03856134414673</v>
+        <v>5.03856086730957</v>
       </c>
       <c r="H700" t="s">
         <v>8</v>
@@ -18595,7 +18595,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G701" t="n">
-        <v>5.03856134414673</v>
+        <v>5.03856086730957</v>
       </c>
       <c r="H701" t="s">
         <v>8</v>
@@ -18621,7 +18621,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G702" t="n">
-        <v>5.03856134414673</v>
+        <v>5.03856086730957</v>
       </c>
       <c r="H702" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G703" t="n">
-        <v>4.87060928344727</v>
+        <v>4.87060880661011</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G707" t="n">
-        <v>4.85085010528564</v>
+        <v>4.8508505821228</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -18777,7 +18777,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G708" t="n">
-        <v>5.1175971031189</v>
+        <v>5.11759757995605</v>
       </c>
       <c r="H708" t="s">
         <v>8</v>
@@ -18855,7 +18855,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G711" t="n">
-        <v>4.88048887252808</v>
+        <v>4.88048839569092</v>
       </c>
       <c r="H711" t="s">
         <v>8</v>
@@ -18907,7 +18907,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G713" t="n">
-        <v>4.7125358581543</v>
+        <v>4.71253681182861</v>
       </c>
       <c r="H713" t="s">
         <v>8</v>
@@ -18933,7 +18933,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G714" t="n">
-        <v>4.6038613319397</v>
+        <v>4.60386180877686</v>
       </c>
       <c r="H714" t="s">
         <v>8</v>
@@ -18959,7 +18959,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G715" t="n">
-        <v>4.7125358581543</v>
+        <v>4.71253681182861</v>
       </c>
       <c r="H715" t="s">
         <v>8</v>
@@ -19089,7 +19089,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G720" t="n">
-        <v>5.01880168914795</v>
+        <v>5.01880264282227</v>
       </c>
       <c r="H720" t="s">
         <v>8</v>
@@ -19115,7 +19115,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G721" t="n">
-        <v>5.09783840179443</v>
+        <v>5.09783792495728</v>
       </c>
       <c r="H721" t="s">
         <v>8</v>
@@ -19167,7 +19167,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G723" t="n">
-        <v>5.1175971031189</v>
+        <v>5.11759757995605</v>
       </c>
       <c r="H723" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G724" t="n">
-        <v>5.1175971031189</v>
+        <v>5.11759757995605</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19245,7 +19245,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G726" t="n">
-        <v>5.03856134414673</v>
+        <v>5.03856086730957</v>
       </c>
       <c r="H726" t="s">
         <v>8</v>
@@ -19271,7 +19271,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G727" t="n">
-        <v>4.97928380966187</v>
+        <v>4.97928428649902</v>
       </c>
       <c r="H727" t="s">
         <v>8</v>
@@ -19297,7 +19297,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G728" t="n">
-        <v>4.76193428039551</v>
+        <v>4.76193475723267</v>
       </c>
       <c r="H728" t="s">
         <v>8</v>
@@ -19427,7 +19427,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G733" t="n">
-        <v>4.88048887252808</v>
+        <v>4.88048839569092</v>
       </c>
       <c r="H733" t="s">
         <v>8</v>
@@ -19505,7 +19505,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G736" t="n">
-        <v>4.88048887252808</v>
+        <v>4.88048839569092</v>
       </c>
       <c r="H736" t="s">
         <v>8</v>
@@ -19531,7 +19531,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G737" t="n">
-        <v>4.89036798477173</v>
+        <v>4.89036846160889</v>
       </c>
       <c r="H737" t="s">
         <v>8</v>
@@ -19687,7 +19687,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G743" t="n">
-        <v>4.85085010528564</v>
+        <v>4.8508505821228</v>
       </c>
       <c r="H743" t="s">
         <v>8</v>
@@ -19739,7 +19739,7 @@
         <v>5</v>
       </c>
       <c r="G745" t="n">
-        <v>4.93976545333862</v>
+        <v>4.93976593017578</v>
       </c>
       <c r="H745" t="s">
         <v>8</v>
@@ -19817,7 +19817,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G748" t="n">
-        <v>4.7520546913147</v>
+        <v>4.75205421447754</v>
       </c>
       <c r="H748" t="s">
         <v>8</v>
@@ -19869,7 +19869,7 @@
         <v>4.75</v>
       </c>
       <c r="G750" t="n">
-        <v>4.69277811050415</v>
+        <v>4.69277763366699</v>
       </c>
       <c r="H750" t="s">
         <v>8</v>
@@ -19895,7 +19895,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G751" t="n">
-        <v>4.17904138565063</v>
+        <v>4.17904186248779</v>
       </c>
       <c r="H751" t="s">
         <v>8</v>
@@ -19947,7 +19947,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G753" t="n">
-        <v>4.17904138565063</v>
+        <v>4.17904186248779</v>
       </c>
       <c r="H753" t="s">
         <v>8</v>
@@ -19973,7 +19973,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G754" t="n">
-        <v>4.17904138565063</v>
+        <v>4.17904186248779</v>
       </c>
       <c r="H754" t="s">
         <v>8</v>
@@ -19999,7 +19999,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G755" t="n">
-        <v>4.18892097473145</v>
+        <v>4.1889214515686</v>
       </c>
       <c r="H755" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G756" t="n">
-        <v>4.18892097473145</v>
+        <v>4.1889214515686</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20051,7 +20051,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G757" t="n">
-        <v>4.17904138565063</v>
+        <v>4.17904186248779</v>
       </c>
       <c r="H757" t="s">
         <v>8</v>
@@ -20077,7 +20077,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G758" t="n">
-        <v>4.14940309524536</v>
+        <v>4.14940357208252</v>
       </c>
       <c r="H758" t="s">
         <v>8</v>
@@ -20233,7 +20233,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G764" t="n">
-        <v>4.02096939086914</v>
+        <v>4.0209698677063</v>
       </c>
       <c r="H764" t="s">
         <v>8</v>
@@ -20311,7 +20311,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G767" t="n">
-        <v>3.86289715766907</v>
+        <v>3.86289691925049</v>
       </c>
       <c r="H767" t="s">
         <v>8</v>
@@ -20337,7 +20337,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G768" t="n">
-        <v>3.89253544807434</v>
+        <v>3.89253568649292</v>
       </c>
       <c r="H768" t="s">
         <v>8</v>
@@ -20415,7 +20415,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G771" t="n">
-        <v>3.76410150527954</v>
+        <v>3.76410174369812</v>
       </c>
       <c r="H771" t="s">
         <v>8</v>
@@ -20441,7 +20441,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G772" t="n">
-        <v>3.76410150527954</v>
+        <v>3.76410174369812</v>
       </c>
       <c r="H772" t="s">
         <v>8</v>
@@ -20493,7 +20493,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G774" t="n">
-        <v>3.75422167778015</v>
+        <v>3.75422191619873</v>
       </c>
       <c r="H774" t="s">
         <v>8</v>
@@ -20545,7 +20545,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G776" t="n">
-        <v>3.6949450969696</v>
+        <v>3.69494485855103</v>
       </c>
       <c r="H776" t="s">
         <v>8</v>
@@ -20571,7 +20571,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G777" t="n">
-        <v>3.75422167778015</v>
+        <v>3.75422191619873</v>
       </c>
       <c r="H777" t="s">
         <v>8</v>
@@ -20649,7 +20649,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G780" t="n">
-        <v>3.89253544807434</v>
+        <v>3.89253568649292</v>
       </c>
       <c r="H780" t="s">
         <v>8</v>
@@ -20727,7 +20727,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G783" t="n">
-        <v>3.98145151138306</v>
+        <v>3.98145174980164</v>
       </c>
       <c r="H783" t="s">
         <v>8</v>
@@ -20779,7 +20779,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G785" t="n">
-        <v>3.89253544807434</v>
+        <v>3.89253568649292</v>
       </c>
       <c r="H785" t="s">
         <v>8</v>
@@ -20987,7 +20987,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G793" t="n">
-        <v>3.932053565979</v>
+        <v>3.93205380439758</v>
       </c>
       <c r="H793" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G795" t="n">
-        <v>3.86289715766907</v>
+        <v>3.86289691925049</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21143,7 +21143,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G799" t="n">
-        <v>3.91229486465454</v>
+        <v>3.91229438781738</v>
       </c>
       <c r="H799" t="s">
         <v>8</v>
@@ -21195,7 +21195,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G801" t="n">
-        <v>3.85301733016968</v>
+        <v>3.85301756858826</v>
       </c>
       <c r="H801" t="s">
         <v>8</v>
@@ -21273,7 +21273,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G804" t="n">
-        <v>3.86292219161987</v>
+        <v>3.86292243003845</v>
       </c>
       <c r="H804" t="s">
         <v>8</v>
@@ -21299,7 +21299,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G805" t="n">
-        <v>3.80349278450012</v>
+        <v>3.80349254608154</v>
       </c>
       <c r="H805" t="s">
         <v>8</v>
@@ -21325,7 +21325,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G806" t="n">
-        <v>3.86292219161987</v>
+        <v>3.86292243003845</v>
       </c>
       <c r="H806" t="s">
         <v>8</v>
@@ -21351,7 +21351,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G807" t="n">
-        <v>4.01149606704712</v>
+        <v>4.01149654388428</v>
       </c>
       <c r="H807" t="s">
         <v>8</v>
@@ -21741,7 +21741,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G822" t="n">
-        <v>4.090735912323</v>
+        <v>4.09073543548584</v>
       </c>
       <c r="H822" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G823" t="n">
-        <v>4.0610203742981</v>
+        <v>4.06102085113525</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21871,7 +21871,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G827" t="n">
-        <v>4.03130578994751</v>
+        <v>4.03130626678467</v>
       </c>
       <c r="H827" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G828" t="n">
-        <v>4.0610203742981</v>
+        <v>4.06102085113525</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -21923,7 +21923,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G829" t="n">
-        <v>4.05111598968506</v>
+        <v>4.05111646652222</v>
       </c>
       <c r="H829" t="s">
         <v>8</v>
@@ -21949,7 +21949,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G830" t="n">
-        <v>4.0610203742981</v>
+        <v>4.06102085113525</v>
       </c>
       <c r="H830" t="s">
         <v>8</v>
@@ -22001,7 +22001,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G832" t="n">
-        <v>4.05111598968506</v>
+        <v>4.05111646652222</v>
       </c>
       <c r="H832" t="s">
         <v>8</v>
@@ -22027,7 +22027,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G833" t="n">
-        <v>4.05111598968506</v>
+        <v>4.05111646652222</v>
       </c>
       <c r="H833" t="s">
         <v>8</v>
@@ -22053,7 +22053,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G834" t="n">
-        <v>4.0610203742981</v>
+        <v>4.06102085113525</v>
       </c>
       <c r="H834" t="s">
         <v>8</v>
@@ -22079,7 +22079,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G835" t="n">
-        <v>4.02140092849731</v>
+        <v>4.02140140533447</v>
       </c>
       <c r="H835" t="s">
         <v>8</v>
@@ -22105,7 +22105,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G836" t="n">
-        <v>4.02140092849731</v>
+        <v>4.02140140533447</v>
       </c>
       <c r="H836" t="s">
         <v>8</v>
@@ -22131,7 +22131,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G837" t="n">
-        <v>3.98178124427795</v>
+        <v>3.98178148269653</v>
       </c>
       <c r="H837" t="s">
         <v>8</v>
@@ -22157,7 +22157,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G838" t="n">
-        <v>4.05111598968506</v>
+        <v>4.05111646652222</v>
       </c>
       <c r="H838" t="s">
         <v>8</v>
@@ -22261,7 +22261,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G842" t="n">
-        <v>4.07092618942261</v>
+        <v>4.07092571258545</v>
       </c>
       <c r="H842" t="s">
         <v>8</v>
@@ -22287,7 +22287,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G843" t="n">
-        <v>4.02140092849731</v>
+        <v>4.02140140533447</v>
       </c>
       <c r="H843" t="s">
         <v>8</v>
@@ -22313,7 +22313,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G844" t="n">
-        <v>3.98178124427795</v>
+        <v>3.98178148269653</v>
       </c>
       <c r="H844" t="s">
         <v>8</v>
@@ -22391,7 +22391,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G847" t="n">
-        <v>4.0610203742981</v>
+        <v>4.06102085113525</v>
       </c>
       <c r="H847" t="s">
         <v>8</v>
@@ -22417,7 +22417,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G848" t="n">
-        <v>4.08083057403564</v>
+        <v>4.0808310508728</v>
       </c>
       <c r="H848" t="s">
         <v>8</v>
@@ -22521,7 +22521,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G852" t="n">
-        <v>4.19968938827515</v>
+        <v>4.1996898651123</v>
       </c>
       <c r="H852" t="s">
         <v>8</v>
@@ -22573,7 +22573,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G854" t="n">
-        <v>4.16006994247437</v>
+        <v>4.16007041931152</v>
       </c>
       <c r="H854" t="s">
         <v>8</v>
@@ -22599,7 +22599,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G855" t="n">
-        <v>4.16006994247437</v>
+        <v>4.16007041931152</v>
       </c>
       <c r="H855" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G856" t="n">
-        <v>4.090735912323</v>
+        <v>4.09073543548584</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22651,7 +22651,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G857" t="n">
-        <v>4.07092618942261</v>
+        <v>4.07092571258545</v>
       </c>
       <c r="H857" t="s">
         <v>8</v>
@@ -22677,7 +22677,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G858" t="n">
-        <v>4.11054563522339</v>
+        <v>4.11054515838623</v>
       </c>
       <c r="H858" t="s">
         <v>8</v>
@@ -22729,7 +22729,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G860" t="n">
-        <v>4.07092618942261</v>
+        <v>4.07092571258545</v>
       </c>
       <c r="H860" t="s">
         <v>8</v>
@@ -22781,7 +22781,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G862" t="n">
-        <v>4.08083057403564</v>
+        <v>4.0808310508728</v>
       </c>
       <c r="H862" t="s">
         <v>8</v>
@@ -22807,7 +22807,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G863" t="n">
-        <v>4.11054563522339</v>
+        <v>4.11054515838623</v>
       </c>
       <c r="H863" t="s">
         <v>8</v>
@@ -22833,7 +22833,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G864" t="n">
-        <v>4.08083057403564</v>
+        <v>4.0808310508728</v>
       </c>
       <c r="H864" t="s">
         <v>8</v>
@@ -22859,7 +22859,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G865" t="n">
-        <v>4.08083057403564</v>
+        <v>4.0808310508728</v>
       </c>
       <c r="H865" t="s">
         <v>8</v>
@@ -22911,7 +22911,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G867" t="n">
-        <v>4.05111598968506</v>
+        <v>4.05111646652222</v>
       </c>
       <c r="H867" t="s">
         <v>8</v>
@@ -22963,7 +22963,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G869" t="n">
-        <v>4.01149606704712</v>
+        <v>4.01149654388428</v>
       </c>
       <c r="H869" t="s">
         <v>8</v>
@@ -22989,7 +22989,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G870" t="n">
-        <v>4.02140092849731</v>
+        <v>4.02140140533447</v>
       </c>
       <c r="H870" t="s">
         <v>8</v>
@@ -23041,7 +23041,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G872" t="n">
-        <v>4.02140092849731</v>
+        <v>4.02140140533447</v>
       </c>
       <c r="H872" t="s">
         <v>8</v>
@@ -23119,7 +23119,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G875" t="n">
-        <v>4.0610203742981</v>
+        <v>4.06102085113525</v>
       </c>
       <c r="H875" t="s">
         <v>8</v>
@@ -23145,7 +23145,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G876" t="n">
-        <v>4.08083057403564</v>
+        <v>4.0808310508728</v>
       </c>
       <c r="H876" t="s">
         <v>8</v>
@@ -23197,7 +23197,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G878" t="n">
-        <v>4.24921464920044</v>
+        <v>4.24921417236328</v>
       </c>
       <c r="H878" t="s">
         <v>8</v>
@@ -23223,7 +23223,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G879" t="n">
-        <v>4.29873943328857</v>
+        <v>4.29873991012573</v>
       </c>
       <c r="H879" t="s">
         <v>8</v>
@@ -23275,7 +23275,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G881" t="n">
-        <v>4.24921464920044</v>
+        <v>4.24921417236328</v>
       </c>
       <c r="H881" t="s">
         <v>8</v>
@@ -23353,7 +23353,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G884" t="n">
-        <v>4.36807298660278</v>
+        <v>4.36807346343994</v>
       </c>
       <c r="H884" t="s">
         <v>8</v>
@@ -23535,7 +23535,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G891" t="n">
-        <v>4.36807298660278</v>
+        <v>4.36807346343994</v>
       </c>
       <c r="H891" t="s">
         <v>8</v>
@@ -23561,7 +23561,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G892" t="n">
-        <v>4.36807298660278</v>
+        <v>4.36807346343994</v>
       </c>
       <c r="H892" t="s">
         <v>8</v>
@@ -23587,7 +23587,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G893" t="n">
-        <v>4.23930931091309</v>
+        <v>4.2393102645874</v>
       </c>
       <c r="H893" t="s">
         <v>8</v>
@@ -23769,7 +23769,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G900" t="n">
-        <v>4.25911951065063</v>
+        <v>4.25911998748779</v>
       </c>
       <c r="H900" t="s">
         <v>8</v>
@@ -23795,7 +23795,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G901" t="n">
-        <v>4.25911951065063</v>
+        <v>4.25911998748779</v>
       </c>
       <c r="H901" t="s">
         <v>8</v>
@@ -23821,7 +23821,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G902" t="n">
-        <v>4.19968938827515</v>
+        <v>4.1996898651123</v>
       </c>
       <c r="H902" t="s">
         <v>8</v>
@@ -23847,7 +23847,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G903" t="n">
-        <v>4.24921464920044</v>
+        <v>4.24921417236328</v>
       </c>
       <c r="H903" t="s">
         <v>8</v>
@@ -23873,7 +23873,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G904" t="n">
-        <v>4.07092618942261</v>
+        <v>4.07092571258545</v>
       </c>
       <c r="H904" t="s">
         <v>8</v>
@@ -23899,7 +23899,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G905" t="n">
-        <v>4.24921464920044</v>
+        <v>4.24921417236328</v>
       </c>
       <c r="H905" t="s">
         <v>8</v>
@@ -23925,7 +23925,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G906" t="n">
-        <v>4.24921464920044</v>
+        <v>4.24921417236328</v>
       </c>
       <c r="H906" t="s">
         <v>8</v>
@@ -23951,7 +23951,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G907" t="n">
-        <v>4.17987966537476</v>
+        <v>4.17988014221191</v>
       </c>
       <c r="H907" t="s">
         <v>8</v>
@@ -24003,7 +24003,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G909" t="n">
-        <v>4.11054563522339</v>
+        <v>4.11054515838623</v>
       </c>
       <c r="H909" t="s">
         <v>8</v>
@@ -24029,7 +24029,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G910" t="n">
-        <v>4.0610203742981</v>
+        <v>4.06102085113525</v>
       </c>
       <c r="H910" t="s">
         <v>8</v>
@@ -24263,7 +24263,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G919" t="n">
-        <v>3.85301733016968</v>
+        <v>3.85301756858826</v>
       </c>
       <c r="H919" t="s">
         <v>8</v>
@@ -24315,7 +24315,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G921" t="n">
-        <v>3.70444345474243</v>
+        <v>3.70444321632385</v>
       </c>
       <c r="H921" t="s">
         <v>8</v>
@@ -24471,7 +24471,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G927" t="n">
-        <v>3.5657742023468</v>
+        <v>3.56577444076538</v>
       </c>
       <c r="H927" t="s">
         <v>8</v>
@@ -24497,7 +24497,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G928" t="n">
-        <v>3.5657742023468</v>
+        <v>3.56577444076538</v>
       </c>
       <c r="H928" t="s">
         <v>8</v>
@@ -24523,7 +24523,7 @@
         <v>3.75</v>
       </c>
       <c r="G929" t="n">
-        <v>3.71434855461121</v>
+        <v>3.71434831619263</v>
       </c>
       <c r="H929" t="s">
         <v>8</v>
@@ -24575,7 +24575,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G931" t="n">
-        <v>3.5657742023468</v>
+        <v>3.56577444076538</v>
       </c>
       <c r="H931" t="s">
         <v>8</v>
@@ -24601,7 +24601,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G932" t="n">
-        <v>3.60539412498474</v>
+        <v>3.60539436340332</v>
       </c>
       <c r="H932" t="s">
         <v>8</v>
@@ -24627,7 +24627,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G933" t="n">
-        <v>3.5657742023468</v>
+        <v>3.56577444076538</v>
       </c>
       <c r="H933" t="s">
         <v>8</v>
@@ -24653,7 +24653,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G934" t="n">
-        <v>3.5657742023468</v>
+        <v>3.56577444076538</v>
       </c>
       <c r="H934" t="s">
         <v>8</v>
@@ -24705,7 +24705,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G936" t="n">
-        <v>3.67472839355469</v>
+        <v>3.67472863197327</v>
       </c>
       <c r="H936" t="s">
         <v>8</v>
@@ -24731,7 +24731,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G937" t="n">
-        <v>3.70444345474243</v>
+        <v>3.70444321632385</v>
       </c>
       <c r="H937" t="s">
         <v>8</v>
@@ -24757,7 +24757,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G938" t="n">
-        <v>3.70444345474243</v>
+        <v>3.70444321632385</v>
       </c>
       <c r="H938" t="s">
         <v>8</v>
@@ -24783,7 +24783,7 @@
         <v>3.75</v>
       </c>
       <c r="G939" t="n">
-        <v>3.71434855461121</v>
+        <v>3.71434831619263</v>
       </c>
       <c r="H939" t="s">
         <v>8</v>
@@ -24939,7 +24939,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G945" t="n">
-        <v>3.90254187583923</v>
+        <v>3.90254211425781</v>
       </c>
       <c r="H945" t="s">
         <v>8</v>
@@ -24991,7 +24991,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G947" t="n">
-        <v>4.0610203742981</v>
+        <v>4.06102085113525</v>
       </c>
       <c r="H947" t="s">
         <v>8</v>
@@ -25017,7 +25017,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G948" t="n">
-        <v>4.10064029693604</v>
+        <v>4.10064077377319</v>
       </c>
       <c r="H948" t="s">
         <v>8</v>
@@ -25043,7 +25043,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G949" t="n">
-        <v>4.17987966537476</v>
+        <v>4.17988014221191</v>
       </c>
       <c r="H949" t="s">
         <v>8</v>
@@ -25069,7 +25069,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G950" t="n">
-        <v>4.10064029693604</v>
+        <v>4.10064077377319</v>
       </c>
       <c r="H950" t="s">
         <v>8</v>
@@ -25095,7 +25095,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G951" t="n">
-        <v>3.98178124427795</v>
+        <v>3.98178148269653</v>
       </c>
       <c r="H951" t="s">
         <v>8</v>
@@ -25147,7 +25147,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G953" t="n">
-        <v>4.03130578994751</v>
+        <v>4.03130626678467</v>
       </c>
       <c r="H953" t="s">
         <v>8</v>
@@ -25173,7 +25173,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G954" t="n">
-        <v>4.0610203742981</v>
+        <v>4.06102085113525</v>
       </c>
       <c r="H954" t="s">
         <v>8</v>
@@ -25199,7 +25199,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G955" t="n">
-        <v>4.03130578994751</v>
+        <v>4.03130626678467</v>
       </c>
       <c r="H955" t="s">
         <v>8</v>
@@ -25329,7 +25329,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G960" t="n">
-        <v>4.02140092849731</v>
+        <v>4.02140140533447</v>
       </c>
       <c r="H960" t="s">
         <v>8</v>
@@ -25355,7 +25355,7 @@
         <v>40.5999984741211</v>
       </c>
       <c r="G961" t="n">
-        <v>40.2140121459961</v>
+        <v>40.2140083312988</v>
       </c>
       <c r="H961" t="s">
         <v>8</v>
@@ -25381,7 +25381,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G962" t="n">
-        <v>3.86292219161987</v>
+        <v>3.86292243003845</v>
       </c>
       <c r="H962" t="s">
         <v>8</v>
@@ -25407,7 +25407,7 @@
         <v>3.94400000572205</v>
       </c>
       <c r="G963" t="n">
-        <v>3.90650415420532</v>
+        <v>3.90650391578674</v>
       </c>
       <c r="H963" t="s">
         <v>8</v>
@@ -25459,7 +25459,7 @@
         <v>3.97849988937378</v>
       </c>
       <c r="G965" t="n">
-        <v>3.94067597389221</v>
+        <v>3.94067573547363</v>
       </c>
       <c r="H965" t="s">
         <v>8</v>
@@ -25537,7 +25537,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G968" t="n">
-        <v>3.90254187583923</v>
+        <v>3.90254211425781</v>
       </c>
       <c r="H968" t="s">
         <v>8</v>
@@ -25693,7 +25693,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G974" t="n">
-        <v>4.01149606704712</v>
+        <v>4.01149654388428</v>
       </c>
       <c r="H974" t="s">
         <v>8</v>
@@ -25797,7 +25797,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G978" t="n">
-        <v>4.02140092849731</v>
+        <v>4.02140140533447</v>
       </c>
       <c r="H978" t="s">
         <v>8</v>
@@ -26031,7 +26031,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G987" t="n">
-        <v>3.85301733016968</v>
+        <v>3.85301756858826</v>
       </c>
       <c r="H987" t="s">
         <v>8</v>
@@ -26057,7 +26057,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G988" t="n">
-        <v>3.85301733016968</v>
+        <v>3.85301756858826</v>
       </c>
       <c r="H988" t="s">
         <v>8</v>
@@ -26083,7 +26083,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G989" t="n">
-        <v>3.80349278450012</v>
+        <v>3.80349254608154</v>
       </c>
       <c r="H989" t="s">
         <v>8</v>
@@ -26109,7 +26109,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G990" t="n">
-        <v>3.80349278450012</v>
+        <v>3.80349254608154</v>
       </c>
       <c r="H990" t="s">
         <v>8</v>
@@ -26187,7 +26187,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G993" t="n">
-        <v>3.86292219161987</v>
+        <v>3.86292243003845</v>
       </c>
       <c r="H993" t="s">
         <v>8</v>
@@ -26213,7 +26213,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G994" t="n">
-        <v>3.85301733016968</v>
+        <v>3.85301756858826</v>
       </c>
       <c r="H994" t="s">
         <v>8</v>
@@ -26265,7 +26265,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G996" t="n">
-        <v>3.80349278450012</v>
+        <v>3.80349254608154</v>
       </c>
       <c r="H996" t="s">
         <v>8</v>
@@ -26291,7 +26291,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G997" t="n">
-        <v>3.80349278450012</v>
+        <v>3.80349254608154</v>
       </c>
       <c r="H997" t="s">
         <v>8</v>
@@ -26395,7 +26395,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1001" t="n">
-        <v>3.86292219161987</v>
+        <v>3.86292243003845</v>
       </c>
       <c r="H1001" t="s">
         <v>8</v>
@@ -26421,7 +26421,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G1002" t="n">
-        <v>3.90254187583923</v>
+        <v>3.90254211425781</v>
       </c>
       <c r="H1002" t="s">
         <v>8</v>
@@ -26499,7 +26499,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1005" t="n">
-        <v>3.7638726234436</v>
+        <v>3.76387286186218</v>
       </c>
       <c r="H1005" t="s">
         <v>8</v>
@@ -26551,7 +26551,7 @@
         <v>3.75</v>
       </c>
       <c r="G1007" t="n">
-        <v>3.71434855461121</v>
+        <v>3.71434831619263</v>
       </c>
       <c r="H1007" t="s">
         <v>8</v>
@@ -26629,7 +26629,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G1010" t="n">
-        <v>3.7341582775116</v>
+        <v>3.73415803909302</v>
       </c>
       <c r="H1010" t="s">
         <v>8</v>
@@ -26655,7 +26655,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G1011" t="n">
-        <v>3.7341582775116</v>
+        <v>3.73415803909302</v>
       </c>
       <c r="H1011" t="s">
         <v>8</v>
@@ -26681,7 +26681,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1012" t="n">
-        <v>3.7638726234436</v>
+        <v>3.76387286186218</v>
       </c>
       <c r="H1012" t="s">
         <v>8</v>
@@ -26707,7 +26707,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1013" t="n">
-        <v>3.67472839355469</v>
+        <v>3.67472863197327</v>
       </c>
       <c r="H1013" t="s">
         <v>8</v>
@@ -26837,7 +26837,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G1018" t="n">
-        <v>3.60539412498474</v>
+        <v>3.60539436340332</v>
       </c>
       <c r="H1018" t="s">
         <v>8</v>
@@ -26889,7 +26889,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G1020" t="n">
-        <v>3.60539412498474</v>
+        <v>3.60539436340332</v>
       </c>
       <c r="H1020" t="s">
         <v>8</v>
@@ -26941,7 +26941,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G1022" t="n">
-        <v>3.60539412498474</v>
+        <v>3.60539436340332</v>
       </c>
       <c r="H1022" t="s">
         <v>8</v>
@@ -27019,7 +27019,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G1025" t="n">
-        <v>3.58558392524719</v>
+        <v>3.58558416366577</v>
       </c>
       <c r="H1025" t="s">
         <v>8</v>
@@ -27175,7 +27175,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G1031" t="n">
-        <v>3.6549186706543</v>
+        <v>3.65491890907288</v>
       </c>
       <c r="H1031" t="s">
         <v>8</v>
@@ -27201,7 +27201,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G1032" t="n">
-        <v>3.6549186706543</v>
+        <v>3.65491890907288</v>
       </c>
       <c r="H1032" t="s">
         <v>8</v>
@@ -27227,7 +27227,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1033" t="n">
-        <v>3.67472839355469</v>
+        <v>3.67472863197327</v>
       </c>
       <c r="H1033" t="s">
         <v>8</v>
@@ -27279,7 +27279,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1035" t="n">
-        <v>3.5657742023468</v>
+        <v>3.56577444076538</v>
       </c>
       <c r="H1035" t="s">
         <v>8</v>
@@ -27331,7 +27331,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G1037" t="n">
-        <v>3.52615475654602</v>
+        <v>3.52615451812744</v>
       </c>
       <c r="H1037" t="s">
         <v>8</v>
@@ -27409,7 +27409,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1040" t="n">
-        <v>3.49643969535828</v>
+        <v>3.49643993377686</v>
       </c>
       <c r="H1040" t="s">
         <v>8</v>
@@ -27435,7 +27435,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1041" t="n">
-        <v>3.49643969535828</v>
+        <v>3.49643993377686</v>
       </c>
       <c r="H1041" t="s">
         <v>8</v>
@@ -27565,7 +27565,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G1046" t="n">
-        <v>3.52615475654602</v>
+        <v>3.52615451812744</v>
       </c>
       <c r="H1046" t="s">
         <v>8</v>
@@ -27591,7 +27591,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1047" t="n">
-        <v>3.4469153881073</v>
+        <v>3.44691514968872</v>
       </c>
       <c r="H1047" t="s">
         <v>8</v>
@@ -27617,7 +27617,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1048" t="n">
-        <v>3.41720032691956</v>
+        <v>3.41720056533813</v>
       </c>
       <c r="H1048" t="s">
         <v>8</v>
@@ -27643,7 +27643,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1049" t="n">
-        <v>3.4370105266571</v>
+        <v>3.43701028823853</v>
       </c>
       <c r="H1049" t="s">
         <v>8</v>
@@ -27669,7 +27669,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1050" t="n">
-        <v>3.4370105266571</v>
+        <v>3.43701028823853</v>
       </c>
       <c r="H1050" t="s">
         <v>8</v>
@@ -27695,7 +27695,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G1051" t="n">
-        <v>3.4568202495575</v>
+        <v>3.45682001113892</v>
       </c>
       <c r="H1051" t="s">
         <v>8</v>
@@ -27721,7 +27721,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1052" t="n">
-        <v>3.49643969535828</v>
+        <v>3.49643993377686</v>
       </c>
       <c r="H1052" t="s">
         <v>8</v>
@@ -27773,7 +27773,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1054" t="n">
-        <v>3.5657742023468</v>
+        <v>3.56577444076538</v>
       </c>
       <c r="H1054" t="s">
         <v>8</v>
@@ -27799,7 +27799,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1055" t="n">
-        <v>3.5657742023468</v>
+        <v>3.56577444076538</v>
       </c>
       <c r="H1055" t="s">
         <v>8</v>
@@ -27929,7 +27929,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1060" t="n">
-        <v>3.5657742023468</v>
+        <v>3.56577444076538</v>
       </c>
       <c r="H1060" t="s">
         <v>8</v>
@@ -27955,7 +27955,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G1061" t="n">
-        <v>3.90254187583923</v>
+        <v>3.90254211425781</v>
       </c>
       <c r="H1061" t="s">
         <v>8</v>
@@ -27981,7 +27981,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1062" t="n">
-        <v>3.7638726234436</v>
+        <v>3.76387286186218</v>
       </c>
       <c r="H1062" t="s">
         <v>8</v>
@@ -28007,7 +28007,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1063" t="n">
-        <v>3.80349278450012</v>
+        <v>3.80349254608154</v>
       </c>
       <c r="H1063" t="s">
         <v>8</v>
@@ -28059,7 +28059,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G1065" t="n">
-        <v>3.98178124427795</v>
+        <v>3.98178148269653</v>
       </c>
       <c r="H1065" t="s">
         <v>8</v>
@@ -28111,7 +28111,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G1067" t="n">
-        <v>4.01149606704712</v>
+        <v>4.01149654388428</v>
       </c>
       <c r="H1067" t="s">
         <v>8</v>
@@ -28137,7 +28137,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1068" t="n">
-        <v>3.80349278450012</v>
+        <v>3.80349254608154</v>
       </c>
       <c r="H1068" t="s">
         <v>8</v>
@@ -28163,7 +28163,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1069" t="n">
-        <v>3.86292219161987</v>
+        <v>3.86292243003845</v>
       </c>
       <c r="H1069" t="s">
         <v>8</v>
@@ -28189,7 +28189,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1070" t="n">
-        <v>3.80349278450012</v>
+        <v>3.80349254608154</v>
       </c>
       <c r="H1070" t="s">
         <v>8</v>
@@ -28215,7 +28215,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1071" t="n">
-        <v>3.80349278450012</v>
+        <v>3.80349254608154</v>
       </c>
       <c r="H1071" t="s">
         <v>8</v>
@@ -28267,7 +28267,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1073" t="n">
-        <v>3.7638726234436</v>
+        <v>3.76387286186218</v>
       </c>
       <c r="H1073" t="s">
         <v>8</v>
@@ -28397,7 +28397,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G1078" t="n">
-        <v>3.7341582775116</v>
+        <v>3.73415803909302</v>
       </c>
       <c r="H1078" t="s">
         <v>8</v>
@@ -28553,7 +28553,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1084" t="n">
-        <v>3.63471913337708</v>
+        <v>3.6347188949585</v>
       </c>
       <c r="H1084" t="s">
         <v>8</v>
@@ -28865,7 +28865,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1096" t="n">
-        <v>3.63471913337708</v>
+        <v>3.6347188949585</v>
       </c>
       <c r="H1096" t="s">
         <v>8</v>
@@ -28943,7 +28943,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1099" t="n">
-        <v>3.63471913337708</v>
+        <v>3.6347188949585</v>
       </c>
       <c r="H1099" t="s">
         <v>8</v>
@@ -29073,7 +29073,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G1104" t="n">
-        <v>3.55527114868164</v>
+        <v>3.55527138710022</v>
       </c>
       <c r="H1104" t="s">
         <v>8</v>
@@ -29099,7 +29099,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1105" t="n">
-        <v>3.67444276809692</v>
+        <v>3.67444252967834</v>
       </c>
       <c r="H1105" t="s">
         <v>8</v>
@@ -29281,7 +29281,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1112" t="n">
-        <v>3.50561666488647</v>
+        <v>3.50561690330505</v>
       </c>
       <c r="H1112" t="s">
         <v>8</v>
@@ -29307,7 +29307,7 @@
         <v>3.5</v>
       </c>
       <c r="G1113" t="n">
-        <v>3.47582387924194</v>
+        <v>3.47582411766052</v>
       </c>
       <c r="H1113" t="s">
         <v>8</v>
@@ -29333,7 +29333,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1114" t="n">
-        <v>3.43610024452209</v>
+        <v>3.43610048294067</v>
       </c>
       <c r="H1114" t="s">
         <v>8</v>
@@ -29359,7 +29359,7 @@
         <v>3.5</v>
       </c>
       <c r="G1115" t="n">
-        <v>3.47582387924194</v>
+        <v>3.47582411766052</v>
       </c>
       <c r="H1115" t="s">
         <v>8</v>
@@ -29385,7 +29385,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1116" t="n">
-        <v>3.43610024452209</v>
+        <v>3.43610048294067</v>
       </c>
       <c r="H1116" t="s">
         <v>8</v>
@@ -29437,7 +29437,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1118" t="n">
-        <v>3.51554751396179</v>
+        <v>3.51554775238037</v>
       </c>
       <c r="H1118" t="s">
         <v>8</v>
@@ -29515,7 +29515,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1121" t="n">
-        <v>3.50561666488647</v>
+        <v>3.50561690330505</v>
       </c>
       <c r="H1121" t="s">
         <v>8</v>
@@ -29541,7 +29541,7 @@
         <v>3.5</v>
       </c>
       <c r="G1122" t="n">
-        <v>3.47582387924194</v>
+        <v>3.47582411766052</v>
       </c>
       <c r="H1122" t="s">
         <v>8</v>
@@ -29567,7 +29567,7 @@
         <v>3.5</v>
       </c>
       <c r="G1123" t="n">
-        <v>3.47582387924194</v>
+        <v>3.47582411766052</v>
       </c>
       <c r="H1123" t="s">
         <v>8</v>
@@ -29619,7 +29619,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1125" t="n">
-        <v>3.41623830795288</v>
+        <v>3.41623854637146</v>
       </c>
       <c r="H1125" t="s">
         <v>8</v>
@@ -29645,7 +29645,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1126" t="n">
-        <v>3.41623830795288</v>
+        <v>3.41623854637146</v>
       </c>
       <c r="H1126" t="s">
         <v>8</v>
@@ -29671,7 +29671,7 @@
         <v>3.5</v>
       </c>
       <c r="G1127" t="n">
-        <v>3.47582387924194</v>
+        <v>3.47582411766052</v>
       </c>
       <c r="H1127" t="s">
         <v>8</v>
@@ -29697,7 +29697,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1128" t="n">
-        <v>3.51554751396179</v>
+        <v>3.51554775238037</v>
       </c>
       <c r="H1128" t="s">
         <v>8</v>
@@ -29801,7 +29801,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1132" t="n">
-        <v>3.41623830795288</v>
+        <v>3.41623854637146</v>
       </c>
       <c r="H1132" t="s">
         <v>8</v>
@@ -29931,7 +29931,7 @@
         <v>3.5</v>
       </c>
       <c r="G1137" t="n">
-        <v>3.47582387924194</v>
+        <v>3.47582411766052</v>
       </c>
       <c r="H1137" t="s">
         <v>8</v>
@@ -30009,7 +30009,7 @@
         <v>3.5</v>
       </c>
       <c r="G1140" t="n">
-        <v>3.47582387924194</v>
+        <v>3.47582411766052</v>
       </c>
       <c r="H1140" t="s">
         <v>8</v>
@@ -30087,7 +30087,7 @@
         <v>3.5</v>
       </c>
       <c r="G1143" t="n">
-        <v>3.47582387924194</v>
+        <v>3.47582411766052</v>
       </c>
       <c r="H1143" t="s">
         <v>8</v>
@@ -30139,7 +30139,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G1145" t="n">
-        <v>3.55527114868164</v>
+        <v>3.55527138710022</v>
       </c>
       <c r="H1145" t="s">
         <v>8</v>
@@ -30165,7 +30165,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1146" t="n">
-        <v>3.67444276809692</v>
+        <v>3.67444252967834</v>
       </c>
       <c r="H1146" t="s">
         <v>8</v>
@@ -30191,7 +30191,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1147" t="n">
-        <v>3.71416640281677</v>
+        <v>3.71416616439819</v>
       </c>
       <c r="H1147" t="s">
         <v>8</v>
@@ -30269,7 +30269,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1150" t="n">
-        <v>3.67444276809692</v>
+        <v>3.67444252967834</v>
       </c>
       <c r="H1150" t="s">
         <v>8</v>
@@ -30321,7 +30321,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1152" t="n">
-        <v>3.67444276809692</v>
+        <v>3.67444252967834</v>
       </c>
       <c r="H1152" t="s">
         <v>8</v>
@@ -30555,7 +30555,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G1161" t="n">
-        <v>3.55527114868164</v>
+        <v>3.55527138710022</v>
       </c>
       <c r="H1161" t="s">
         <v>8</v>
@@ -30763,7 +30763,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G1169" t="n">
-        <v>3.55527114868164</v>
+        <v>3.55527138710022</v>
       </c>
       <c r="H1169" t="s">
         <v>8</v>
@@ -30789,7 +30789,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1170" t="n">
-        <v>3.63471913337708</v>
+        <v>3.6347188949585</v>
       </c>
       <c r="H1170" t="s">
         <v>8</v>
@@ -30815,7 +30815,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1171" t="n">
-        <v>3.63471913337708</v>
+        <v>3.6347188949585</v>
       </c>
       <c r="H1171" t="s">
         <v>8</v>
@@ -31049,7 +31049,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G1180" t="n">
-        <v>3.55527114868164</v>
+        <v>3.55527138710022</v>
       </c>
       <c r="H1180" t="s">
         <v>8</v>
@@ -31101,7 +31101,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1182" t="n">
-        <v>3.50561666488647</v>
+        <v>3.50561690330505</v>
       </c>
       <c r="H1182" t="s">
         <v>8</v>
@@ -31127,7 +31127,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1183" t="n">
-        <v>3.50561666488647</v>
+        <v>3.50561690330505</v>
       </c>
       <c r="H1183" t="s">
         <v>8</v>
@@ -31179,7 +31179,7 @@
         <v>3.5</v>
       </c>
       <c r="G1185" t="n">
-        <v>3.47582387924194</v>
+        <v>3.47582411766052</v>
       </c>
       <c r="H1185" t="s">
         <v>8</v>
@@ -31257,7 +31257,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1188" t="n">
-        <v>3.41623830795288</v>
+        <v>3.41623854637146</v>
       </c>
       <c r="H1188" t="s">
         <v>8</v>
@@ -31413,7 +31413,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G1194" t="n">
-        <v>2.93955397605896</v>
+        <v>2.93955421447754</v>
       </c>
       <c r="H1194" t="s">
         <v>8</v>
@@ -31751,7 +31751,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G1207" t="n">
-        <v>2.76079726219177</v>
+        <v>2.76079750061035</v>
       </c>
       <c r="H1207" t="s">
         <v>8</v>
@@ -31777,7 +31777,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G1208" t="n">
-        <v>2.70121169090271</v>
+        <v>2.70121192932129</v>
       </c>
       <c r="H1208" t="s">
         <v>8</v>
@@ -32245,7 +32245,7 @@
         <v>3</v>
       </c>
       <c r="G1226" t="n">
-        <v>2.97927761077881</v>
+        <v>2.97927784919739</v>
       </c>
       <c r="H1226" t="s">
         <v>8</v>
@@ -32297,7 +32297,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G1228" t="n">
-        <v>2.93955397605896</v>
+        <v>2.93955421447754</v>
       </c>
       <c r="H1228" t="s">
         <v>8</v>
@@ -32349,7 +32349,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G1230" t="n">
-        <v>2.93955397605896</v>
+        <v>2.93955421447754</v>
       </c>
       <c r="H1230" t="s">
         <v>8</v>
@@ -32375,7 +32375,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G1231" t="n">
-        <v>2.93955397605896</v>
+        <v>2.93955421447754</v>
       </c>
       <c r="H1231" t="s">
         <v>8</v>
@@ -32401,7 +32401,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G1232" t="n">
-        <v>2.93955397605896</v>
+        <v>2.93955421447754</v>
       </c>
       <c r="H1232" t="s">
         <v>8</v>
@@ -32479,7 +32479,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1235" t="n">
-        <v>2.8799684047699</v>
+        <v>2.87996864318848</v>
       </c>
       <c r="H1235" t="s">
         <v>8</v>
@@ -32765,7 +32765,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G1246" t="n">
-        <v>2.58204054832458</v>
+        <v>2.58204078674316</v>
       </c>
       <c r="H1246" t="s">
         <v>8</v>
@@ -32999,7 +32999,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G1255" t="n">
-        <v>2.66148805618286</v>
+        <v>2.66148829460144</v>
       </c>
       <c r="H1255" t="s">
         <v>8</v>
@@ -33155,7 +33155,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1261" t="n">
-        <v>2.8799684047699</v>
+        <v>2.87996864318848</v>
       </c>
       <c r="H1261" t="s">
         <v>8</v>
@@ -33207,7 +33207,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G1263" t="n">
-        <v>2.84024453163147</v>
+        <v>2.84024477005005</v>
       </c>
       <c r="H1263" t="s">
         <v>8</v>
@@ -33233,7 +33233,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1264" t="n">
-        <v>2.8799684047699</v>
+        <v>2.87996864318848</v>
       </c>
       <c r="H1264" t="s">
         <v>8</v>
@@ -33389,7 +33389,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G1270" t="n">
-        <v>2.76079726219177</v>
+        <v>2.76079750061035</v>
       </c>
       <c r="H1270" t="s">
         <v>8</v>
@@ -33441,7 +33441,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G1272" t="n">
-        <v>2.76079726219177</v>
+        <v>2.76079750061035</v>
       </c>
       <c r="H1272" t="s">
         <v>8</v>
@@ -33493,7 +33493,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G1274" t="n">
-        <v>2.84024453163147</v>
+        <v>2.84024477005005</v>
       </c>
       <c r="H1274" t="s">
         <v>8</v>
@@ -33675,7 +33675,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G1281" t="n">
-        <v>2.84024453163147</v>
+        <v>2.84024477005005</v>
       </c>
       <c r="H1281" t="s">
         <v>8</v>
@@ -33831,7 +33831,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G1287" t="n">
-        <v>2.66148805618286</v>
+        <v>2.66148829460144</v>
       </c>
       <c r="H1287" t="s">
         <v>8</v>
@@ -33857,7 +33857,7 @@
         <v>2.5</v>
       </c>
       <c r="G1288" t="n">
-        <v>2.48273134231567</v>
+        <v>2.48273158073425</v>
       </c>
       <c r="H1288" t="s">
         <v>8</v>
@@ -34013,7 +34013,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G1294" t="n">
-        <v>2.62176442146301</v>
+        <v>2.62176465988159</v>
       </c>
       <c r="H1294" t="s">
         <v>8</v>
@@ -34247,7 +34247,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1303" t="n">
-        <v>2.8799684047699</v>
+        <v>2.87996864318848</v>
       </c>
       <c r="H1303" t="s">
         <v>8</v>
@@ -34377,7 +34377,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G1308" t="n">
-        <v>2.84024453163147</v>
+        <v>2.84024477005005</v>
       </c>
       <c r="H1308" t="s">
         <v>8</v>
@@ -34429,7 +34429,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G1310" t="n">
-        <v>2.80052089691162</v>
+        <v>2.8005211353302</v>
       </c>
       <c r="H1310" t="s">
         <v>8</v>
@@ -34533,7 +34533,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G1314" t="n">
-        <v>2.93955397605896</v>
+        <v>2.93955421447754</v>
       </c>
       <c r="H1314" t="s">
         <v>8</v>
@@ -43506,6 +43506,32 @@
         <v>3.41000008583069</v>
       </c>
       <c r="H1659" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1660">
+      <c r="A1660" s="1" t="n">
+        <v>46289.2916666667</v>
+      </c>
+      <c r="B1660" t="n">
+        <v>47952</v>
+      </c>
+      <c r="C1660" t="n">
+        <v>3.45499992370605</v>
+      </c>
+      <c r="D1660" t="n">
+        <v>3.36999988555908</v>
+      </c>
+      <c r="E1660" t="n">
+        <v>3.45499992370605</v>
+      </c>
+      <c r="F1660" t="n">
+        <v>3.4449999332428</v>
+      </c>
+      <c r="G1660" t="n">
+        <v>3.4449999332428</v>
+      </c>
+      <c r="H1660" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/UD.MI.xlsx
+++ b/data/UD.MI.xlsx
@@ -421,7 +421,7 @@
         <v>1.5</v>
       </c>
       <c r="G2" t="n">
-        <v>1.47885513305664</v>
+        <v>1.47885501384735</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G4" t="n">
-        <v>1.4591372013092</v>
+        <v>1.45913696289062</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G5" t="n">
-        <v>1.50843238830566</v>
+        <v>1.50843226909637</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G7" t="n">
-        <v>1.51829135417938</v>
+        <v>1.51829123497009</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G9" t="n">
-        <v>1.55772745609283</v>
+        <v>1.55772757530212</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G11" t="n">
-        <v>1.56265711784363</v>
+        <v>1.56265699863434</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G13" t="n">
-        <v>1.55772745609283</v>
+        <v>1.55772757530212</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G16" t="n">
-        <v>1.65631783008575</v>
+        <v>1.65631771087646</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G18" t="n">
-        <v>1.67603600025177</v>
+        <v>1.67603588104248</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G19" t="n">
-        <v>1.67603600025177</v>
+        <v>1.67603588104248</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G21" t="n">
-        <v>1.65631783008575</v>
+        <v>1.65631771087646</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G22" t="n">
-        <v>1.62181103229523</v>
+        <v>1.62181115150452</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G23" t="n">
-        <v>1.59716367721558</v>
+        <v>1.59716355800629</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G24" t="n">
-        <v>1.57744562625885</v>
+        <v>1.57744550704956</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G25" t="n">
-        <v>1.58730459213257</v>
+        <v>1.58730447292328</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G26" t="n">
-        <v>1.57744562625885</v>
+        <v>1.57744550704956</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G27" t="n">
-        <v>1.57744562625885</v>
+        <v>1.57744550704956</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G29" t="n">
-        <v>1.57744562625885</v>
+        <v>1.57744550704956</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G32" t="n">
-        <v>1.59716367721558</v>
+        <v>1.59716355800629</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G33" t="n">
-        <v>1.61688148975372</v>
+        <v>1.61688160896301</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G36" t="n">
-        <v>1.65631783008575</v>
+        <v>1.65631771087646</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G37" t="n">
-        <v>1.70561301708221</v>
+        <v>1.70561289787292</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G38" t="n">
-        <v>1.70561301708221</v>
+        <v>1.70561289787292</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G39" t="n">
-        <v>1.67110645771027</v>
+        <v>1.67110657691956</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G40" t="n">
-        <v>1.69575381278992</v>
+        <v>1.69575393199921</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G41" t="n">
-        <v>1.6858948469162</v>
+        <v>1.68589496612549</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G42" t="n">
-        <v>1.74504911899567</v>
+        <v>1.74504899978638</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>1.72500002384186</v>
       </c>
       <c r="G43" t="n">
-        <v>1.70068347454071</v>
+        <v>1.70068359375</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G44" t="n">
-        <v>1.65631783008575</v>
+        <v>1.65631771087646</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G46" t="n">
-        <v>1.67603600025177</v>
+        <v>1.67603588104248</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G47" t="n">
-        <v>1.65631783008575</v>
+        <v>1.65631771087646</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G48" t="n">
-        <v>1.65631783008575</v>
+        <v>1.65631771087646</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>1.72500002384186</v>
       </c>
       <c r="G49" t="n">
-        <v>1.70068347454071</v>
+        <v>1.70068359375</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G50" t="n">
-        <v>1.74997866153717</v>
+        <v>1.74997854232788</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>1.75</v>
       </c>
       <c r="G51" t="n">
-        <v>1.72533106803894</v>
+        <v>1.72533094882965</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G52" t="n">
-        <v>1.74011969566345</v>
+        <v>1.74011957645416</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>1.74500000476837</v>
       </c>
       <c r="G53" t="n">
-        <v>1.72040164470673</v>
+        <v>1.72040152549744</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>1.72500002384186</v>
       </c>
       <c r="G54" t="n">
-        <v>1.70068347454071</v>
+        <v>1.70068359375</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>1.72500002384186</v>
       </c>
       <c r="G55" t="n">
-        <v>1.70068347454071</v>
+        <v>1.70068359375</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G56" t="n">
-        <v>1.69575381278992</v>
+        <v>1.69575393199921</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G57" t="n">
-        <v>1.67603600025177</v>
+        <v>1.67603588104248</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>1.7150000333786</v>
       </c>
       <c r="G58" t="n">
-        <v>1.69082450866699</v>
+        <v>1.69082462787628</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>1.7150000333786</v>
       </c>
       <c r="G59" t="n">
-        <v>1.69082450866699</v>
+        <v>1.69082462787628</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G66" t="n">
-        <v>1.67603600025177</v>
+        <v>1.67603588104248</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G68" t="n">
-        <v>1.6858948469162</v>
+        <v>1.68589496612549</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G69" t="n">
-        <v>1.65631783008575</v>
+        <v>1.65631771087646</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>1.65499997138977</v>
       </c>
       <c r="G73" t="n">
-        <v>1.63166999816895</v>
+        <v>1.63167011737823</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G76" t="n">
-        <v>1.67110645771027</v>
+        <v>1.67110657691956</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G77" t="n">
-        <v>1.6858948469162</v>
+        <v>1.68589496612549</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G79" t="n">
-        <v>1.67603600025177</v>
+        <v>1.67603588104248</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G80" t="n">
-        <v>1.67603600025177</v>
+        <v>1.67603588104248</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G81" t="n">
-        <v>1.67603600025177</v>
+        <v>1.67603588104248</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G82" t="n">
-        <v>1.65631783008575</v>
+        <v>1.65631771087646</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G83" t="n">
-        <v>1.65631783008575</v>
+        <v>1.65631771087646</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G88" t="n">
-        <v>1.57744562625885</v>
+        <v>1.57744550704956</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G89" t="n">
-        <v>1.57744562625885</v>
+        <v>1.57744550704956</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>1.62999999523163</v>
       </c>
       <c r="G92" t="n">
-        <v>1.60702264308929</v>
+        <v>1.60702252388</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G95" t="n">
-        <v>1.58730459213257</v>
+        <v>1.58730447292328</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G96" t="n">
-        <v>1.62181103229523</v>
+        <v>1.62181115150452</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G97" t="n">
-        <v>1.58730459213257</v>
+        <v>1.58730447292328</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G98" t="n">
-        <v>1.58730459213257</v>
+        <v>1.58730447292328</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G101" t="n">
-        <v>1.65631783008575</v>
+        <v>1.65631771087646</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>1.63499999046326</v>
       </c>
       <c r="G105" t="n">
-        <v>1.6119521856308</v>
+        <v>1.61195206642151</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G110" t="n">
-        <v>1.67603600025177</v>
+        <v>1.67603588104248</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G111" t="n">
-        <v>1.67603600025177</v>
+        <v>1.67603588104248</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G112" t="n">
-        <v>1.67603600025177</v>
+        <v>1.67603588104248</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G113" t="n">
-        <v>1.67603600025177</v>
+        <v>1.67603588104248</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G114" t="n">
-        <v>1.67603600025177</v>
+        <v>1.67603588104248</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G115" t="n">
-        <v>1.67603600025177</v>
+        <v>1.67603588104248</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G117" t="n">
-        <v>1.6858948469162</v>
+        <v>1.68589496612549</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G118" t="n">
-        <v>1.6858948469162</v>
+        <v>1.68589496612549</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G119" t="n">
-        <v>1.77462613582611</v>
+        <v>1.7746262550354</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G124" t="n">
-        <v>1.8534984588623</v>
+        <v>1.85349857807159</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G125" t="n">
-        <v>1.77462613582611</v>
+        <v>1.7746262550354</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G126" t="n">
-        <v>1.83378040790558</v>
+        <v>1.83378052711487</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G127" t="n">
-        <v>1.82392144203186</v>
+        <v>1.82392156124115</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G128" t="n">
-        <v>1.82392144203186</v>
+        <v>1.82392156124115</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G129" t="n">
-        <v>1.82392144203186</v>
+        <v>1.82392156124115</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G131" t="n">
-        <v>1.83378040790558</v>
+        <v>1.83378052711487</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G133" t="n">
-        <v>1.8534984588623</v>
+        <v>1.85349857807159</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G134" t="n">
-        <v>1.8534984588623</v>
+        <v>1.85349857807159</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G135" t="n">
-        <v>1.8534984588623</v>
+        <v>1.85349857807159</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G141" t="n">
-        <v>1.82392144203186</v>
+        <v>1.82392156124115</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G142" t="n">
-        <v>1.82392144203186</v>
+        <v>1.82392156124115</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G143" t="n">
-        <v>1.79927396774292</v>
+        <v>1.79927384853363</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G144" t="n">
-        <v>1.77462613582611</v>
+        <v>1.7746262550354</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G148" t="n">
-        <v>1.7598375082016</v>
+        <v>1.75983762741089</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G151" t="n">
-        <v>1.74011969566345</v>
+        <v>1.74011957645416</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G153" t="n">
-        <v>1.74504911899567</v>
+        <v>1.74504899978638</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>1.81500005722046</v>
       </c>
       <c r="G154" t="n">
-        <v>1.78941488265991</v>
+        <v>1.78941476345062</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G155" t="n">
-        <v>1.82392144203186</v>
+        <v>1.82392156124115</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G156" t="n">
-        <v>1.82392144203186</v>
+        <v>1.82392156124115</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G158" t="n">
-        <v>1.83378040790558</v>
+        <v>1.83378052711487</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>1.81500005722046</v>
       </c>
       <c r="G159" t="n">
-        <v>1.78941488265991</v>
+        <v>1.78941476345062</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G160" t="n">
-        <v>1.77462613582611</v>
+        <v>1.7746262550354</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G161" t="n">
-        <v>1.77462613582611</v>
+        <v>1.7746262550354</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G162" t="n">
-        <v>1.74504911899567</v>
+        <v>1.74504899978638</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G163" t="n">
-        <v>1.74504911899567</v>
+        <v>1.74504899978638</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G165" t="n">
-        <v>1.77462613582611</v>
+        <v>1.7746262550354</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G166" t="n">
-        <v>1.77462613582611</v>
+        <v>1.7746262550354</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>1.81500005722046</v>
       </c>
       <c r="G167" t="n">
-        <v>1.78941488265991</v>
+        <v>1.78941476345062</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G168" t="n">
-        <v>1.74997866153717</v>
+        <v>1.74997854232788</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G169" t="n">
-        <v>1.77462613582611</v>
+        <v>1.7746262550354</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G172" t="n">
-        <v>1.81406259536743</v>
+        <v>1.81406247615814</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G181" t="n">
-        <v>1.90279352664948</v>
+        <v>1.90279364585876</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G182" t="n">
-        <v>1.91265273094177</v>
+        <v>1.91265285015106</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G183" t="n">
-        <v>2.03096127510071</v>
+        <v>2.03096103668213</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G184" t="n">
-        <v>2.01124286651611</v>
+        <v>2.01124310493469</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G185" t="n">
-        <v>2.03096127510071</v>
+        <v>2.03096103668213</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>1.99500000476837</v>
       </c>
       <c r="G186" t="n">
-        <v>1.96687746047974</v>
+        <v>1.96687734127045</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G188" t="n">
-        <v>2.01124286651611</v>
+        <v>2.01124310493469</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G189" t="n">
-        <v>2.01124286651611</v>
+        <v>2.01124310493469</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G194" t="n">
-        <v>1.92251169681549</v>
+        <v>1.92251181602478</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G195" t="n">
-        <v>1.86335742473602</v>
+        <v>1.86335754394531</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G196" t="n">
-        <v>1.89293456077576</v>
+        <v>1.89293467998505</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G197" t="n">
-        <v>1.91265273094177</v>
+        <v>1.91265285015106</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G198" t="n">
-        <v>1.91265273094177</v>
+        <v>1.91265285015106</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G200" t="n">
-        <v>1.92251169681549</v>
+        <v>1.92251181602478</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>1.95500004291534</v>
       </c>
       <c r="G201" t="n">
-        <v>1.92744123935699</v>
+        <v>1.92744135856628</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G202" t="n">
-        <v>1.91265273094177</v>
+        <v>1.91265285015106</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G203" t="n">
-        <v>1.90772294998169</v>
+        <v>1.90772318840027</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G204" t="n">
-        <v>1.92251169681549</v>
+        <v>1.92251181602478</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>1.95500004291534</v>
       </c>
       <c r="G206" t="n">
-        <v>1.92744123935699</v>
+        <v>1.92744135856628</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>1.95500004291534</v>
       </c>
       <c r="G207" t="n">
-        <v>1.92744123935699</v>
+        <v>1.92744135856628</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>1.9650000333786</v>
       </c>
       <c r="G209" t="n">
-        <v>1.93730032444</v>
+        <v>1.93730044364929</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G213" t="n">
-        <v>1.92251169681549</v>
+        <v>1.92251181602478</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G214" t="n">
-        <v>1.92251169681549</v>
+        <v>1.92251181602478</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G216" t="n">
-        <v>1.91265273094177</v>
+        <v>1.91265285015106</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G218" t="n">
-        <v>1.89293456077576</v>
+        <v>1.89293467998505</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G219" t="n">
-        <v>1.89293456077576</v>
+        <v>1.89293467998505</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G221" t="n">
-        <v>1.92251169681549</v>
+        <v>1.92251181602478</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G222" t="n">
-        <v>1.92251169681549</v>
+        <v>1.92251181602478</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G223" t="n">
-        <v>1.92251169681549</v>
+        <v>1.92251181602478</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G224" t="n">
-        <v>1.92251169681549</v>
+        <v>1.92251181602478</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G228" t="n">
-        <v>2.00138425827026</v>
+        <v>2.00138401985168</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G229" t="n">
-        <v>2.08025598526001</v>
+        <v>2.08025622367859</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G230" t="n">
-        <v>2.0211021900177</v>
+        <v>2.02110195159912</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G231" t="n">
-        <v>2.22814154624939</v>
+        <v>2.22814178466797</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G232" t="n">
-        <v>2.26757764816284</v>
+        <v>2.267578125</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>2.25</v>
       </c>
       <c r="G233" t="n">
-        <v>2.21828293800354</v>
+        <v>2.21828246116638</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G234" t="n">
-        <v>2.16898775100708</v>
+        <v>2.1689875125885</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G235" t="n">
-        <v>2.14926981925964</v>
+        <v>2.14926934242249</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G236" t="n">
-        <v>2.1985650062561</v>
+        <v>2.19856429100037</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G237" t="n">
-        <v>2.1887059211731</v>
+        <v>2.18870568275452</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G238" t="n">
-        <v>2.2380006313324</v>
+        <v>2.23800039291382</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>2.25</v>
       </c>
       <c r="G239" t="n">
-        <v>2.21828293800354</v>
+        <v>2.21828246116638</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G240" t="n">
-        <v>2.20842385292053</v>
+        <v>2.20842361450195</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G241" t="n">
-        <v>2.22814154624939</v>
+        <v>2.22814178466797</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G242" t="n">
-        <v>2.25771880149841</v>
+        <v>2.25771856307983</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G243" t="n">
-        <v>2.26757764816284</v>
+        <v>2.267578125</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G246" t="n">
-        <v>2.28729581832886</v>
+        <v>2.28729605674744</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G247" t="n">
-        <v>2.28729581832886</v>
+        <v>2.28729605674744</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G254" t="n">
-        <v>2.48447680473328</v>
+        <v>2.4844765663147</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>2.5</v>
       </c>
       <c r="G255" t="n">
-        <v>2.46475887298584</v>
+        <v>2.46475839614868</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G258" t="n">
-        <v>2.6126446723938</v>
+        <v>2.61264443397522</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G260" t="n">
-        <v>2.74081182479858</v>
+        <v>2.74081158638</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G262" t="n">
-        <v>2.78024744987488</v>
+        <v>2.78024768829346</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G264" t="n">
-        <v>3.1548912525177</v>
+        <v>3.15489101409912</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>3</v>
       </c>
       <c r="G265" t="n">
-        <v>2.95771026611328</v>
+        <v>2.9577100276947</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G267" t="n">
-        <v>2.83940196037292</v>
+        <v>2.8394021987915</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G270" t="n">
-        <v>2.77038884162903</v>
+        <v>2.77038860321045</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G271" t="n">
-        <v>2.84926104545593</v>
+        <v>2.84926128387451</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G272" t="n">
-        <v>2.99714660644531</v>
+        <v>2.99714636802673</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G273" t="n">
-        <v>2.96756935119629</v>
+        <v>2.96756958961487</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G274" t="n">
-        <v>3.26333999633789</v>
+        <v>3.26334023475647</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G275" t="n">
-        <v>3.26333999633789</v>
+        <v>3.26334023475647</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G277" t="n">
-        <v>3.17460918426514</v>
+        <v>3.17460894584656</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G278" t="n">
-        <v>3.18446850776672</v>
+        <v>3.18446803092957</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G281" t="n">
-        <v>3.18446850776672</v>
+        <v>3.18446803092957</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G282" t="n">
-        <v>3.21404528617859</v>
+        <v>3.21404504776001</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G283" t="n">
-        <v>3.24362206459045</v>
+        <v>3.24362230300903</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G284" t="n">
-        <v>3.19432735443115</v>
+        <v>3.19432711601257</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G285" t="n">
-        <v>3.35207200050354</v>
+        <v>3.35207176208496</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G286" t="n">
-        <v>3.49995732307434</v>
+        <v>3.49995708465576</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G288" t="n">
-        <v>3.52953433990479</v>
+        <v>3.52953410148621</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G290" t="n">
-        <v>3.72671484947205</v>
+        <v>3.72671508789062</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G292" t="n">
-        <v>3.64784288406372</v>
+        <v>3.6478431224823</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G293" t="n">
-        <v>3.64784288406372</v>
+        <v>3.6478431224823</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G295" t="n">
-        <v>3.5196750164032</v>
+        <v>3.51967525482178</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G296" t="n">
-        <v>3.54925227165222</v>
+        <v>3.5492525100708</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G298" t="n">
-        <v>3.49009823799133</v>
+        <v>3.49009799957275</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G299" t="n">
-        <v>3.49995732307434</v>
+        <v>3.49995708465576</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G300" t="n">
-        <v>3.4802393913269</v>
+        <v>3.48023915290833</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G301" t="n">
-        <v>3.49009823799133</v>
+        <v>3.49009799957275</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G302" t="n">
-        <v>3.49995732307434</v>
+        <v>3.49995708465576</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G303" t="n">
-        <v>3.49009823799133</v>
+        <v>3.49009799957275</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G304" t="n">
-        <v>3.52953433990479</v>
+        <v>3.52953410148621</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G305" t="n">
-        <v>3.52953433990479</v>
+        <v>3.52953410148621</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G309" t="n">
-        <v>4.35769367218018</v>
+        <v>4.35769319534302</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G310" t="n">
-        <v>4.33797550201416</v>
+        <v>4.337975025177</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G311" t="n">
-        <v>4.14079475402832</v>
+        <v>4.14079427719116</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G312" t="n">
-        <v>3.99290895462036</v>
+        <v>3.99290919303894</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>4</v>
       </c>
       <c r="G313" t="n">
-        <v>3.94361352920532</v>
+        <v>3.9436137676239</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G314" t="n">
-        <v>4.05206298828125</v>
+        <v>4.05206346511841</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G316" t="n">
-        <v>4.08163976669312</v>
+        <v>4.08164024353027</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G317" t="n">
-        <v>4.14079475402832</v>
+        <v>4.14079427719116</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G325" t="n">
-        <v>4.06192255020142</v>
+        <v>4.06192207336426</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G326" t="n">
-        <v>4.00276851654053</v>
+        <v>4.00276803970337</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G327" t="n">
-        <v>4.16051197052002</v>
+        <v>4.16051244735718</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G328" t="n">
-        <v>4.16051197052002</v>
+        <v>4.16051244735718</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G329" t="n">
-        <v>4.02248573303223</v>
+        <v>4.02248620986938</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G333" t="n">
-        <v>4.16051197052002</v>
+        <v>4.16051244735718</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G334" t="n">
-        <v>4.16051197052002</v>
+        <v>4.16051244735718</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G336" t="n">
-        <v>4.00276851654053</v>
+        <v>4.00276803970337</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G337" t="n">
-        <v>4.00276851654053</v>
+        <v>4.00276803970337</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G338" t="n">
-        <v>4.16051197052002</v>
+        <v>4.16051244735718</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G339" t="n">
-        <v>4.16051197052002</v>
+        <v>4.16051244735718</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G340" t="n">
-        <v>4.14079475402832</v>
+        <v>4.14079427719116</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G341" t="n">
-        <v>4.14079475402832</v>
+        <v>4.14079427719116</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G342" t="n">
-        <v>4.06192255020142</v>
+        <v>4.06192207336426</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G343" t="n">
-        <v>4.14079475402832</v>
+        <v>4.14079427719116</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G345" t="n">
-        <v>4.08163976669312</v>
+        <v>4.08164024353027</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G346" t="n">
-        <v>4.0422043800354</v>
+        <v>4.04220390319824</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G347" t="n">
-        <v>4.02248573303223</v>
+        <v>4.02248620986938</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G348" t="n">
-        <v>4.02248573303223</v>
+        <v>4.02248620986938</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G352" t="n">
-        <v>4.19994878768921</v>
+        <v>4.19994926452637</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G355" t="n">
-        <v>4.08163976669312</v>
+        <v>4.08164024353027</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G356" t="n">
-        <v>4.14079475402832</v>
+        <v>4.14079427719116</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G357" t="n">
-        <v>4.05206298828125</v>
+        <v>4.05206346511841</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G361" t="n">
-        <v>4.08163976669312</v>
+        <v>4.08164024353027</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G363" t="n">
-        <v>4.1210765838623</v>
+        <v>4.12107610702515</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G364" t="n">
-        <v>4.1210765838623</v>
+        <v>4.12107610702515</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G365" t="n">
-        <v>4.1210765838623</v>
+        <v>4.12107610702515</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G366" t="n">
-        <v>4.14079475402832</v>
+        <v>4.14079427719116</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G367" t="n">
-        <v>4.14079475402832</v>
+        <v>4.14079427719116</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G368" t="n">
-        <v>4.14079475402832</v>
+        <v>4.14079427719116</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G369" t="n">
-        <v>4.08163976669312</v>
+        <v>4.08164024353027</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G371" t="n">
-        <v>4.01262712478638</v>
+        <v>4.01262760162354</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G372" t="n">
-        <v>4.08163976669312</v>
+        <v>4.08164024353027</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G373" t="n">
-        <v>4.14079475402832</v>
+        <v>4.14079427719116</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G374" t="n">
-        <v>4.14079475402832</v>
+        <v>4.14079427719116</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G375" t="n">
-        <v>4.14079475402832</v>
+        <v>4.14079427719116</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G376" t="n">
-        <v>4.19994878768921</v>
+        <v>4.19994926452637</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G377" t="n">
-        <v>4.22952508926392</v>
+        <v>4.22952604293823</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G378" t="n">
-        <v>4.27882099151611</v>
+        <v>4.27882146835327</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G382" t="n">
-        <v>4.29853963851929</v>
+        <v>4.29853868484497</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G383" t="n">
-        <v>4.30839776992798</v>
+        <v>4.30839824676514</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G384" t="n">
-        <v>4.33797550201416</v>
+        <v>4.337975025177</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G385" t="n">
-        <v>4.36755228042603</v>
+        <v>4.36755180358887</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G386" t="n">
-        <v>4.30839776992798</v>
+        <v>4.30839824676514</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G387" t="n">
-        <v>4.36755228042603</v>
+        <v>4.36755180358887</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G388" t="n">
-        <v>4.36755228042603</v>
+        <v>4.36755180358887</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G390" t="n">
-        <v>4.33797550201416</v>
+        <v>4.337975025177</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G391" t="n">
-        <v>4.30839776992798</v>
+        <v>4.30839824676514</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G393" t="n">
-        <v>4.33797550201416</v>
+        <v>4.337975025177</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G394" t="n">
-        <v>4.40698862075806</v>
+        <v>4.4069881439209</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G396" t="n">
-        <v>4.22952508926392</v>
+        <v>4.22952604293823</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G398" t="n">
-        <v>4.0422043800354</v>
+        <v>4.04220390319824</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G399" t="n">
-        <v>4.0422043800354</v>
+        <v>4.04220390319824</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G400" t="n">
-        <v>4.0422043800354</v>
+        <v>4.04220390319824</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G402" t="n">
-        <v>4.19994878768921</v>
+        <v>4.19994926452637</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G403" t="n">
-        <v>4.29853963851929</v>
+        <v>4.29853868484497</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G404" t="n">
-        <v>4.33797550201416</v>
+        <v>4.337975025177</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G406" t="n">
-        <v>4.39713001251221</v>
+        <v>4.39712858200073</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G412" t="n">
-        <v>5.30416011810303</v>
+        <v>5.30416059494019</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G413" t="n">
-        <v>5.2450065612793</v>
+        <v>5.24500703811646</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>5</v>
       </c>
       <c r="G414" t="n">
-        <v>4.92951774597168</v>
+        <v>4.92951679229736</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>5</v>
       </c>
       <c r="G415" t="n">
-        <v>4.92951774597168</v>
+        <v>4.92951679229736</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G416" t="n">
-        <v>4.96895360946655</v>
+        <v>4.96895313262939</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>5</v>
       </c>
       <c r="G417" t="n">
-        <v>4.92951774597168</v>
+        <v>4.92951679229736</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G420" t="n">
-        <v>5.00838947296143</v>
+        <v>5.00838899612427</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>5</v>
       </c>
       <c r="G421" t="n">
-        <v>4.92951774597168</v>
+        <v>4.92951679229736</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>5</v>
       </c>
       <c r="G422" t="n">
-        <v>4.92951774597168</v>
+        <v>4.92951679229736</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>5</v>
       </c>
       <c r="G423" t="n">
-        <v>4.92951774597168</v>
+        <v>4.92951679229736</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G424" t="n">
-        <v>4.89008140563965</v>
+        <v>4.89008092880249</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G428" t="n">
-        <v>5.00838947296143</v>
+        <v>5.00838899612427</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>5</v>
       </c>
       <c r="G430" t="n">
-        <v>4.92951774597168</v>
+        <v>4.92951679229736</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>5</v>
       </c>
       <c r="G432" t="n">
-        <v>4.92951774597168</v>
+        <v>4.92951679229736</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G433" t="n">
-        <v>4.88022232055664</v>
+        <v>4.88022184371948</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>5</v>
       </c>
       <c r="G434" t="n">
-        <v>4.92951774597168</v>
+        <v>4.92951679229736</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>5</v>
       </c>
       <c r="G438" t="n">
-        <v>4.92951774597168</v>
+        <v>4.92951679229736</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G439" t="n">
-        <v>4.89008140563965</v>
+        <v>4.89008092880249</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>5</v>
       </c>
       <c r="G440" t="n">
-        <v>4.92951774597168</v>
+        <v>4.92951679229736</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G441" t="n">
-        <v>4.89008140563965</v>
+        <v>4.89008092880249</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G445" t="n">
-        <v>4.96895360946655</v>
+        <v>4.96895313262939</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G447" t="n">
-        <v>4.85064506530762</v>
+        <v>4.85064458847046</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>5</v>
       </c>
       <c r="G448" t="n">
-        <v>4.92951774597168</v>
+        <v>4.92951679229736</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>5</v>
       </c>
       <c r="G449" t="n">
-        <v>4.92951774597168</v>
+        <v>4.92951679229736</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>5</v>
       </c>
       <c r="G452" t="n">
-        <v>4.92951774597168</v>
+        <v>4.92951679229736</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12147,7 +12147,7 @@
         <v>5</v>
       </c>
       <c r="G453" t="n">
-        <v>4.92951774597168</v>
+        <v>4.92951679229736</v>
       </c>
       <c r="H453" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G455" t="n">
-        <v>4.85064506530762</v>
+        <v>4.85064458847046</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>5</v>
       </c>
       <c r="G456" t="n">
-        <v>4.92951774597168</v>
+        <v>4.92951679229736</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G458" t="n">
-        <v>5.50134086608887</v>
+        <v>5.50134134292603</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G459" t="n">
-        <v>5.26472473144531</v>
+        <v>5.26472520828247</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G461" t="n">
-        <v>5.30416011810303</v>
+        <v>5.30416059494019</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G462" t="n">
-        <v>5.2252893447876</v>
+        <v>5.22528886795044</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G463" t="n">
-        <v>5.2252893447876</v>
+        <v>5.22528886795044</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G465" t="n">
-        <v>5.16613435745239</v>
+        <v>5.16613388061523</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G468" t="n">
-        <v>5.16613435745239</v>
+        <v>5.16613388061523</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G469" t="n">
-        <v>5.2252893447876</v>
+        <v>5.22528886795044</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G471" t="n">
-        <v>5.2252893447876</v>
+        <v>5.22528886795044</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G472" t="n">
-        <v>5.2252893447876</v>
+        <v>5.22528886795044</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G473" t="n">
-        <v>5.20557069778442</v>
+        <v>5.20557022094727</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G477" t="n">
-        <v>5.00838947296143</v>
+        <v>5.00838899612427</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G478" t="n">
-        <v>4.96895360946655</v>
+        <v>4.96895313262939</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G487" t="n">
-        <v>5.16613435745239</v>
+        <v>5.16613388061523</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G488" t="n">
-        <v>5.06754350662231</v>
+        <v>5.06754398345947</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G492" t="n">
-        <v>4.96895360946655</v>
+        <v>4.96895313262939</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G493" t="n">
-        <v>5.16613435745239</v>
+        <v>5.16613388061523</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G497" t="n">
-        <v>4.87036275863647</v>
+        <v>4.87036323547363</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G501" t="n">
-        <v>5.06754350662231</v>
+        <v>5.06754398345947</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13577,7 +13577,7 @@
         <v>5</v>
       </c>
       <c r="G508" t="n">
-        <v>4.92951774597168</v>
+        <v>4.92951679229736</v>
       </c>
       <c r="H508" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G509" t="n">
-        <v>5.06754350662231</v>
+        <v>5.06754398345947</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G513" t="n">
-        <v>5.00838947296143</v>
+        <v>5.00838899612427</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G514" t="n">
-        <v>4.96895360946655</v>
+        <v>4.96895313262939</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13785,7 +13785,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G516" t="n">
-        <v>5.00838947296143</v>
+        <v>5.00838899612427</v>
       </c>
       <c r="H516" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G518" t="n">
-        <v>5.00838947296143</v>
+        <v>5.00838899612427</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>5</v>
       </c>
       <c r="G519" t="n">
-        <v>4.92951774597168</v>
+        <v>4.92951679229736</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13915,7 +13915,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G521" t="n">
-        <v>5.20557069778442</v>
+        <v>5.20557022094727</v>
       </c>
       <c r="H521" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G525" t="n">
-        <v>4.88022232055664</v>
+        <v>4.88022184371948</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G526" t="n">
-        <v>5.00838947296143</v>
+        <v>5.00838899612427</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G527" t="n">
-        <v>4.85064506530762</v>
+        <v>4.85064458847046</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G529" t="n">
-        <v>4.77177286148071</v>
+        <v>4.77177333831787</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14149,7 +14149,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G530" t="n">
-        <v>4.73233652114868</v>
+        <v>4.732337474823</v>
       </c>
       <c r="H530" t="s">
         <v>8</v>
@@ -14201,7 +14201,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G532" t="n">
-        <v>4.77177286148071</v>
+        <v>4.77177333831787</v>
       </c>
       <c r="H532" t="s">
         <v>8</v>
@@ -14227,7 +14227,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G533" t="n">
-        <v>4.79149055480957</v>
+        <v>4.79149150848389</v>
       </c>
       <c r="H533" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G534" t="n">
-        <v>4.73233652114868</v>
+        <v>4.732337474823</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G535" t="n">
-        <v>4.73233652114868</v>
+        <v>4.732337474823</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G537" t="n">
-        <v>4.73233652114868</v>
+        <v>4.732337474823</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G538" t="n">
-        <v>4.89994049072266</v>
+        <v>4.8999400138855</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G539" t="n">
-        <v>4.85064506530762</v>
+        <v>4.85064458847046</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G542" t="n">
-        <v>4.86050367355347</v>
+        <v>4.86050415039062</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G546" t="n">
-        <v>4.75205421447754</v>
+        <v>4.75205516815186</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G547" t="n">
-        <v>4.62362051010132</v>
+        <v>4.62362098693848</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G548" t="n">
-        <v>4.57422351837158</v>
+        <v>4.57422304153442</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G549" t="n">
-        <v>4.59398221969604</v>
+        <v>4.5939826965332</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G551" t="n">
-        <v>4.74217557907104</v>
+        <v>4.7421760559082</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G552" t="n">
-        <v>4.78169345855713</v>
+        <v>4.78169393539429</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G553" t="n">
-        <v>4.78169345855713</v>
+        <v>4.78169393539429</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G554" t="n">
-        <v>4.78169345855713</v>
+        <v>4.78169393539429</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G555" t="n">
-        <v>4.86072969436646</v>
+        <v>4.8607292175293</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G556" t="n">
-        <v>4.74217557907104</v>
+        <v>4.7421760559082</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G557" t="n">
-        <v>4.74217557907104</v>
+        <v>4.7421760559082</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G560" t="n">
-        <v>4.80145263671875</v>
+        <v>4.80145311355591</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G567" t="n">
-        <v>4.82121181488037</v>
+        <v>4.82121133804321</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G568" t="n">
-        <v>4.82121181488037</v>
+        <v>4.82121133804321</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G569" t="n">
-        <v>4.82121181488037</v>
+        <v>4.82121133804321</v>
       </c>
       <c r="H569" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G570" t="n">
-        <v>4.82121181488037</v>
+        <v>4.82121133804321</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G573" t="n">
-        <v>4.43590927124023</v>
+        <v>4.43591022491455</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15319,7 +15319,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G575" t="n">
-        <v>4.32723522186279</v>
+        <v>4.32723474502563</v>
       </c>
       <c r="H575" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>4.5</v>
       </c>
       <c r="G576" t="n">
-        <v>4.4457893371582</v>
+        <v>4.44578886032104</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15371,7 +15371,7 @@
         <v>4.5</v>
       </c>
       <c r="G577" t="n">
-        <v>4.4457893371582</v>
+        <v>4.44578886032104</v>
       </c>
       <c r="H577" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>4.5</v>
       </c>
       <c r="G578" t="n">
-        <v>4.4457893371582</v>
+        <v>4.44578886032104</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15423,7 +15423,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G579" t="n">
-        <v>4.2778377532959</v>
+        <v>4.27783727645874</v>
       </c>
       <c r="H579" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G581" t="n">
-        <v>4.40627145767212</v>
+        <v>4.4062705039978</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G582" t="n">
-        <v>4.45566940307617</v>
+        <v>4.45566892623901</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G584" t="n">
-        <v>4.78169345855713</v>
+        <v>4.78169393539429</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G585" t="n">
-        <v>4.59398221969604</v>
+        <v>4.5939826965332</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G586" t="n">
-        <v>4.74217557907104</v>
+        <v>4.7421760559082</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G587" t="n">
-        <v>4.43590927124023</v>
+        <v>4.43591022491455</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G589" t="n">
-        <v>4.43590927124023</v>
+        <v>4.43591022491455</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G590" t="n">
-        <v>4.38651180267334</v>
+        <v>4.3865122795105</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G591" t="n">
-        <v>4.34699440002441</v>
+        <v>4.34699392318726</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G592" t="n">
-        <v>4.34699440002441</v>
+        <v>4.34699392318726</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15787,7 +15787,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G593" t="n">
-        <v>4.34699440002441</v>
+        <v>4.34699392318726</v>
       </c>
       <c r="H593" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G594" t="n">
-        <v>4.48530721664429</v>
+        <v>4.48530673980713</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>4.5</v>
       </c>
       <c r="G596" t="n">
-        <v>4.4457893371582</v>
+        <v>4.44578886032104</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G597" t="n">
-        <v>4.40627145767212</v>
+        <v>4.4062705039978</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G599" t="n">
-        <v>4.43590927124023</v>
+        <v>4.43591022491455</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G600" t="n">
-        <v>4.48530721664429</v>
+        <v>4.48530673980713</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -15995,7 +15995,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G601" t="n">
-        <v>4.54458427429199</v>
+        <v>4.54458475112915</v>
       </c>
       <c r="H601" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G602" t="n">
-        <v>4.59398221969604</v>
+        <v>4.5939826965332</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G606" t="n">
-        <v>4.89036846160889</v>
+        <v>4.89036798477173</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G607" t="n">
-        <v>4.7026572227478</v>
+        <v>4.70265769958496</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G608" t="n">
-        <v>4.7026572227478</v>
+        <v>4.70265769958496</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16307,7 +16307,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G613" t="n">
-        <v>4.78169345855713</v>
+        <v>4.78169393539429</v>
       </c>
       <c r="H613" t="s">
         <v>8</v>
@@ -16359,7 +16359,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G615" t="n">
-        <v>4.88048839569092</v>
+        <v>4.88048887252808</v>
       </c>
       <c r="H615" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G616" t="n">
-        <v>4.97928428649902</v>
+        <v>4.97928380966187</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16411,7 +16411,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G617" t="n">
-        <v>4.97928428649902</v>
+        <v>4.97928380966187</v>
       </c>
       <c r="H617" t="s">
         <v>8</v>
@@ -16437,7 +16437,7 @@
         <v>5</v>
       </c>
       <c r="G618" t="n">
-        <v>4.93976593017578</v>
+        <v>4.93976545333862</v>
       </c>
       <c r="H618" t="s">
         <v>8</v>
@@ -16463,7 +16463,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G619" t="n">
-        <v>4.97928428649902</v>
+        <v>4.97928380966187</v>
       </c>
       <c r="H619" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G620" t="n">
-        <v>4.99904298782349</v>
+        <v>4.99904346466064</v>
       </c>
       <c r="H620" t="s">
         <v>8</v>
@@ -16515,7 +16515,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G621" t="n">
-        <v>5.01880264282227</v>
+        <v>5.01880168914795</v>
       </c>
       <c r="H621" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G622" t="n">
-        <v>5.01880264282227</v>
+        <v>5.01880168914795</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16567,7 +16567,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G623" t="n">
-        <v>5.01880264282227</v>
+        <v>5.01880168914795</v>
       </c>
       <c r="H623" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G624" t="n">
-        <v>5.03856086730957</v>
+        <v>5.03856134414673</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16619,7 +16619,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G625" t="n">
-        <v>5.03856086730957</v>
+        <v>5.03856134414673</v>
       </c>
       <c r="H625" t="s">
         <v>8</v>
@@ -16671,7 +16671,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G627" t="n">
-        <v>4.86072969436646</v>
+        <v>4.8607292175293</v>
       </c>
       <c r="H627" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G628" t="n">
-        <v>4.87060880661011</v>
+        <v>4.87060928344727</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -16723,7 +16723,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G629" t="n">
-        <v>4.86072969436646</v>
+        <v>4.8607292175293</v>
       </c>
       <c r="H629" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G630" t="n">
-        <v>4.86072969436646</v>
+        <v>4.8607292175293</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G631" t="n">
-        <v>4.86072969436646</v>
+        <v>4.8607292175293</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -16801,7 +16801,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G632" t="n">
-        <v>4.75205421447754</v>
+        <v>4.7520546913147</v>
       </c>
       <c r="H632" t="s">
         <v>8</v>
@@ -16879,7 +16879,7 @@
         <v>5</v>
       </c>
       <c r="G635" t="n">
-        <v>4.93976593017578</v>
+        <v>4.93976545333862</v>
       </c>
       <c r="H635" t="s">
         <v>8</v>
@@ -16905,7 +16905,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G636" t="n">
-        <v>4.89036846160889</v>
+        <v>4.89036798477173</v>
       </c>
       <c r="H636" t="s">
         <v>8</v>
@@ -16931,7 +16931,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G637" t="n">
-        <v>4.88048839569092</v>
+        <v>4.88048887252808</v>
       </c>
       <c r="H637" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G638" t="n">
-        <v>4.88048839569092</v>
+        <v>4.88048887252808</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G639" t="n">
-        <v>4.87060880661011</v>
+        <v>4.87060928344727</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17087,7 +17087,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G643" t="n">
-        <v>4.73229598999023</v>
+        <v>4.73229551315308</v>
       </c>
       <c r="H643" t="s">
         <v>8</v>
@@ -17113,7 +17113,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G644" t="n">
-        <v>4.54458427429199</v>
+        <v>4.54458475112915</v>
       </c>
       <c r="H644" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>4.5</v>
       </c>
       <c r="G646" t="n">
-        <v>4.4457893371582</v>
+        <v>4.44578886032104</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G647" t="n">
-        <v>4.34699440002441</v>
+        <v>4.34699392318726</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G648" t="n">
-        <v>4.34699440002441</v>
+        <v>4.34699392318726</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G649" t="n">
-        <v>4.39639139175415</v>
+        <v>4.39639186859131</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17269,7 +17269,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G650" t="n">
-        <v>4.52482557296753</v>
+        <v>4.52482509613037</v>
       </c>
       <c r="H650" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G652" t="n">
-        <v>4.68289804458618</v>
+        <v>4.68289756774902</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17373,7 +17373,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G654" t="n">
-        <v>4.86072969436646</v>
+        <v>4.8607292175293</v>
       </c>
       <c r="H654" t="s">
         <v>8</v>
@@ -17477,7 +17477,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G658" t="n">
-        <v>4.80145263671875</v>
+        <v>4.80145311355591</v>
       </c>
       <c r="H658" t="s">
         <v>8</v>
@@ -17503,7 +17503,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G659" t="n">
-        <v>4.74217557907104</v>
+        <v>4.7421760559082</v>
       </c>
       <c r="H659" t="s">
         <v>8</v>
@@ -17529,7 +17529,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G660" t="n">
-        <v>4.74217557907104</v>
+        <v>4.7421760559082</v>
       </c>
       <c r="H660" t="s">
         <v>8</v>
@@ -17555,7 +17555,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G661" t="n">
-        <v>4.88048839569092</v>
+        <v>4.88048887252808</v>
       </c>
       <c r="H661" t="s">
         <v>8</v>
@@ -17581,7 +17581,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G662" t="n">
-        <v>4.74217557907104</v>
+        <v>4.7421760559082</v>
       </c>
       <c r="H662" t="s">
         <v>8</v>
@@ -17633,7 +17633,7 @@
         <v>5</v>
       </c>
       <c r="G664" t="n">
-        <v>4.93976593017578</v>
+        <v>4.93976545333862</v>
       </c>
       <c r="H664" t="s">
         <v>8</v>
@@ -17659,7 +17659,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G665" t="n">
-        <v>4.86072969436646</v>
+        <v>4.8607292175293</v>
       </c>
       <c r="H665" t="s">
         <v>8</v>
@@ -17711,7 +17711,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G667" t="n">
-        <v>4.82121181488037</v>
+        <v>4.82121133804321</v>
       </c>
       <c r="H667" t="s">
         <v>8</v>
@@ -17737,7 +17737,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G668" t="n">
-        <v>5.03856086730957</v>
+        <v>5.03856134414673</v>
       </c>
       <c r="H668" t="s">
         <v>8</v>
@@ -17815,7 +17815,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G671" t="n">
-        <v>5.03856086730957</v>
+        <v>5.03856134414673</v>
       </c>
       <c r="H671" t="s">
         <v>8</v>
@@ -17867,7 +17867,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G673" t="n">
-        <v>5.07807922363281</v>
+        <v>5.07807970046997</v>
       </c>
       <c r="H673" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G674" t="n">
-        <v>5.03856086730957</v>
+        <v>5.03856134414673</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G675" t="n">
-        <v>4.97928428649902</v>
+        <v>4.97928380966187</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -17945,7 +17945,7 @@
         <v>5</v>
       </c>
       <c r="G676" t="n">
-        <v>4.93976593017578</v>
+        <v>4.93976545333862</v>
       </c>
       <c r="H676" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G677" t="n">
-        <v>4.89036846160889</v>
+        <v>4.89036798477173</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G678" t="n">
-        <v>4.74217557907104</v>
+        <v>4.7421760559082</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18049,7 +18049,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G680" t="n">
-        <v>4.73229598999023</v>
+        <v>4.73229551315308</v>
       </c>
       <c r="H680" t="s">
         <v>8</v>
@@ -18153,7 +18153,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G684" t="n">
-        <v>4.52482557296753</v>
+        <v>4.52482509613037</v>
       </c>
       <c r="H684" t="s">
         <v>8</v>
@@ -18179,7 +18179,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G685" t="n">
-        <v>4.34699440002441</v>
+        <v>4.34699392318726</v>
       </c>
       <c r="H685" t="s">
         <v>8</v>
@@ -18205,7 +18205,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G686" t="n">
-        <v>4.39639139175415</v>
+        <v>4.39639186859131</v>
       </c>
       <c r="H686" t="s">
         <v>8</v>
@@ -18231,7 +18231,7 @@
         <v>4.5</v>
       </c>
       <c r="G687" t="n">
-        <v>4.4457893371582</v>
+        <v>4.44578886032104</v>
       </c>
       <c r="H687" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>4.5</v>
       </c>
       <c r="G688" t="n">
-        <v>4.4457893371582</v>
+        <v>4.44578886032104</v>
       </c>
       <c r="H688" t="s">
         <v>8</v>
@@ -18309,7 +18309,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G690" t="n">
-        <v>4.71253681182861</v>
+        <v>4.71253633499146</v>
       </c>
       <c r="H690" t="s">
         <v>8</v>
@@ -18335,7 +18335,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G691" t="n">
-        <v>5.01880264282227</v>
+        <v>5.01880168914795</v>
       </c>
       <c r="H691" t="s">
         <v>8</v>
@@ -18361,7 +18361,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G692" t="n">
-        <v>5.03856086730957</v>
+        <v>5.03856134414673</v>
       </c>
       <c r="H692" t="s">
         <v>8</v>
@@ -18387,7 +18387,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G693" t="n">
-        <v>5.15711545944214</v>
+        <v>5.1571159362793</v>
       </c>
       <c r="H693" t="s">
         <v>8</v>
@@ -18413,7 +18413,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G694" t="n">
-        <v>5.03856086730957</v>
+        <v>5.03856134414673</v>
       </c>
       <c r="H694" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G695" t="n">
-        <v>4.99904298782349</v>
+        <v>4.99904346466064</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18491,7 +18491,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G697" t="n">
-        <v>5.03856086730957</v>
+        <v>5.03856134414673</v>
       </c>
       <c r="H697" t="s">
         <v>8</v>
@@ -18569,7 +18569,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G700" t="n">
-        <v>5.03856086730957</v>
+        <v>5.03856134414673</v>
       </c>
       <c r="H700" t="s">
         <v>8</v>
@@ -18595,7 +18595,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G701" t="n">
-        <v>5.03856086730957</v>
+        <v>5.03856134414673</v>
       </c>
       <c r="H701" t="s">
         <v>8</v>
@@ -18621,7 +18621,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G702" t="n">
-        <v>5.03856086730957</v>
+        <v>5.03856134414673</v>
       </c>
       <c r="H702" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G703" t="n">
-        <v>4.87060880661011</v>
+        <v>4.87060928344727</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -18673,7 +18673,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G704" t="n">
-        <v>4.74217557907104</v>
+        <v>4.7421760559082</v>
       </c>
       <c r="H704" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G707" t="n">
-        <v>4.8508505821228</v>
+        <v>4.85085010528564</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -18855,7 +18855,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G711" t="n">
-        <v>4.88048839569092</v>
+        <v>4.88048887252808</v>
       </c>
       <c r="H711" t="s">
         <v>8</v>
@@ -18907,7 +18907,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G713" t="n">
-        <v>4.71253681182861</v>
+        <v>4.71253633499146</v>
       </c>
       <c r="H713" t="s">
         <v>8</v>
@@ -18933,7 +18933,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G714" t="n">
-        <v>4.60386180877686</v>
+        <v>4.6038613319397</v>
       </c>
       <c r="H714" t="s">
         <v>8</v>
@@ -18959,7 +18959,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G715" t="n">
-        <v>4.71253681182861</v>
+        <v>4.71253633499146</v>
       </c>
       <c r="H715" t="s">
         <v>8</v>
@@ -19011,7 +19011,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G717" t="n">
-        <v>4.78169345855713</v>
+        <v>4.78169393539429</v>
       </c>
       <c r="H717" t="s">
         <v>8</v>
@@ -19037,7 +19037,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G718" t="n">
-        <v>4.82121181488037</v>
+        <v>4.82121133804321</v>
       </c>
       <c r="H718" t="s">
         <v>8</v>
@@ -19089,7 +19089,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G720" t="n">
-        <v>5.01880264282227</v>
+        <v>5.01880168914795</v>
       </c>
       <c r="H720" t="s">
         <v>8</v>
@@ -19115,7 +19115,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G721" t="n">
-        <v>5.09783792495728</v>
+        <v>5.09783840179443</v>
       </c>
       <c r="H721" t="s">
         <v>8</v>
@@ -19141,7 +19141,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G722" t="n">
-        <v>5.07807922363281</v>
+        <v>5.07807970046997</v>
       </c>
       <c r="H722" t="s">
         <v>8</v>
@@ -19245,7 +19245,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G726" t="n">
-        <v>5.03856086730957</v>
+        <v>5.03856134414673</v>
       </c>
       <c r="H726" t="s">
         <v>8</v>
@@ -19271,7 +19271,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G727" t="n">
-        <v>4.97928428649902</v>
+        <v>4.97928380966187</v>
       </c>
       <c r="H727" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G730" t="n">
-        <v>4.82121181488037</v>
+        <v>4.82121133804321</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19375,7 +19375,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G731" t="n">
-        <v>4.74217557907104</v>
+        <v>4.7421760559082</v>
       </c>
       <c r="H731" t="s">
         <v>8</v>
@@ -19401,7 +19401,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G732" t="n">
-        <v>4.86072969436646</v>
+        <v>4.8607292175293</v>
       </c>
       <c r="H732" t="s">
         <v>8</v>
@@ -19427,7 +19427,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G733" t="n">
-        <v>4.88048839569092</v>
+        <v>4.88048887252808</v>
       </c>
       <c r="H733" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G734" t="n">
-        <v>4.78169345855713</v>
+        <v>4.78169393539429</v>
       </c>
       <c r="H734" t="s">
         <v>8</v>
@@ -19505,7 +19505,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G736" t="n">
-        <v>4.88048839569092</v>
+        <v>4.88048887252808</v>
       </c>
       <c r="H736" t="s">
         <v>8</v>
@@ -19531,7 +19531,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G737" t="n">
-        <v>4.89036846160889</v>
+        <v>4.89036798477173</v>
       </c>
       <c r="H737" t="s">
         <v>8</v>
@@ -19557,7 +19557,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G738" t="n">
-        <v>4.82121181488037</v>
+        <v>4.82121133804321</v>
       </c>
       <c r="H738" t="s">
         <v>8</v>
@@ -19583,7 +19583,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G739" t="n">
-        <v>4.82121181488037</v>
+        <v>4.82121133804321</v>
       </c>
       <c r="H739" t="s">
         <v>8</v>
@@ -19635,7 +19635,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G741" t="n">
-        <v>4.82121181488037</v>
+        <v>4.82121133804321</v>
       </c>
       <c r="H741" t="s">
         <v>8</v>
@@ -19687,7 +19687,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G743" t="n">
-        <v>4.8508505821228</v>
+        <v>4.85085010528564</v>
       </c>
       <c r="H743" t="s">
         <v>8</v>
@@ -19713,7 +19713,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G744" t="n">
-        <v>4.86072969436646</v>
+        <v>4.8607292175293</v>
       </c>
       <c r="H744" t="s">
         <v>8</v>
@@ -19739,7 +19739,7 @@
         <v>5</v>
       </c>
       <c r="G745" t="n">
-        <v>4.93976593017578</v>
+        <v>4.93976545333862</v>
       </c>
       <c r="H745" t="s">
         <v>8</v>
@@ -19765,7 +19765,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G746" t="n">
-        <v>4.92000675201416</v>
+        <v>4.92000722885132</v>
       </c>
       <c r="H746" t="s">
         <v>8</v>
@@ -19791,7 +19791,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G747" t="n">
-        <v>4.74217557907104</v>
+        <v>4.7421760559082</v>
       </c>
       <c r="H747" t="s">
         <v>8</v>
@@ -19817,7 +19817,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G748" t="n">
-        <v>4.75205421447754</v>
+        <v>4.7520546913147</v>
       </c>
       <c r="H748" t="s">
         <v>8</v>
@@ -19843,7 +19843,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G749" t="n">
-        <v>4.78169345855713</v>
+        <v>4.78169393539429</v>
       </c>
       <c r="H749" t="s">
         <v>8</v>
@@ -19895,7 +19895,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G751" t="n">
-        <v>4.17904186248779</v>
+        <v>4.17904138565063</v>
       </c>
       <c r="H751" t="s">
         <v>8</v>
@@ -19921,7 +19921,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G752" t="n">
-        <v>4.22843933105469</v>
+        <v>4.22843980789185</v>
       </c>
       <c r="H752" t="s">
         <v>8</v>
@@ -19947,7 +19947,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G753" t="n">
-        <v>4.17904186248779</v>
+        <v>4.17904138565063</v>
       </c>
       <c r="H753" t="s">
         <v>8</v>
@@ -19973,7 +19973,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G754" t="n">
-        <v>4.17904186248779</v>
+        <v>4.17904138565063</v>
       </c>
       <c r="H754" t="s">
         <v>8</v>
@@ -20051,7 +20051,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G757" t="n">
-        <v>4.17904186248779</v>
+        <v>4.17904138565063</v>
       </c>
       <c r="H757" t="s">
         <v>8</v>
@@ -20077,7 +20077,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G758" t="n">
-        <v>4.14940357208252</v>
+        <v>4.14940309524536</v>
       </c>
       <c r="H758" t="s">
         <v>8</v>
@@ -20103,7 +20103,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G759" t="n">
-        <v>4.15928268432617</v>
+        <v>4.15928316116333</v>
       </c>
       <c r="H759" t="s">
         <v>8</v>
@@ -20181,7 +20181,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G762" t="n">
-        <v>4.15928268432617</v>
+        <v>4.15928316116333</v>
       </c>
       <c r="H762" t="s">
         <v>8</v>
@@ -20259,7 +20259,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G765" t="n">
-        <v>3.8727765083313</v>
+        <v>3.87277674674988</v>
       </c>
       <c r="H765" t="s">
         <v>8</v>
@@ -20285,7 +20285,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G766" t="n">
-        <v>3.8727765083313</v>
+        <v>3.87277674674988</v>
       </c>
       <c r="H766" t="s">
         <v>8</v>
@@ -20311,7 +20311,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G767" t="n">
-        <v>3.86289691925049</v>
+        <v>3.86289715766907</v>
       </c>
       <c r="H767" t="s">
         <v>8</v>
@@ -20363,7 +20363,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G769" t="n">
-        <v>3.83325839042664</v>
+        <v>3.83325862884521</v>
       </c>
       <c r="H769" t="s">
         <v>8</v>
@@ -20415,7 +20415,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G771" t="n">
-        <v>3.76410174369812</v>
+        <v>3.76410150527954</v>
       </c>
       <c r="H771" t="s">
         <v>8</v>
@@ -20441,7 +20441,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G772" t="n">
-        <v>3.76410174369812</v>
+        <v>3.76410150527954</v>
       </c>
       <c r="H772" t="s">
         <v>8</v>
@@ -20545,7 +20545,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G776" t="n">
-        <v>3.69494485855103</v>
+        <v>3.6949450969696</v>
       </c>
       <c r="H776" t="s">
         <v>8</v>
@@ -20701,7 +20701,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G782" t="n">
-        <v>4.04072856903076</v>
+        <v>4.04072904586792</v>
       </c>
       <c r="H782" t="s">
         <v>8</v>
@@ -20727,7 +20727,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G783" t="n">
-        <v>3.98145174980164</v>
+        <v>3.98145151138306</v>
       </c>
       <c r="H783" t="s">
         <v>8</v>
@@ -20987,7 +20987,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G793" t="n">
-        <v>3.93205380439758</v>
+        <v>3.932053565979</v>
       </c>
       <c r="H793" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G795" t="n">
-        <v>3.86289691925049</v>
+        <v>3.86289715766907</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21065,7 +21065,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G796" t="n">
-        <v>3.8727765083313</v>
+        <v>3.87277674674988</v>
       </c>
       <c r="H796" t="s">
         <v>8</v>
@@ -21117,7 +21117,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G798" t="n">
-        <v>3.83325839042664</v>
+        <v>3.83325862884521</v>
       </c>
       <c r="H798" t="s">
         <v>8</v>
@@ -21143,7 +21143,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G799" t="n">
-        <v>3.91229438781738</v>
+        <v>3.91229486465454</v>
       </c>
       <c r="H799" t="s">
         <v>8</v>
@@ -21299,7 +21299,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G805" t="n">
-        <v>3.80349254608154</v>
+        <v>3.80349278450012</v>
       </c>
       <c r="H805" t="s">
         <v>8</v>
@@ -21715,7 +21715,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G821" t="n">
-        <v>4.14026021957397</v>
+        <v>4.14025974273682</v>
       </c>
       <c r="H821" t="s">
         <v>8</v>
@@ -21741,7 +21741,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G822" t="n">
-        <v>4.09073543548584</v>
+        <v>4.090735912323</v>
       </c>
       <c r="H822" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G823" t="n">
-        <v>4.06102085113525</v>
+        <v>4.0610203742981</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G828" t="n">
-        <v>4.06102085113525</v>
+        <v>4.0610203742981</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -21949,7 +21949,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G830" t="n">
-        <v>4.06102085113525</v>
+        <v>4.0610203742981</v>
       </c>
       <c r="H830" t="s">
         <v>8</v>
@@ -22053,7 +22053,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G834" t="n">
-        <v>4.06102085113525</v>
+        <v>4.0610203742981</v>
       </c>
       <c r="H834" t="s">
         <v>8</v>
@@ -22079,7 +22079,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G835" t="n">
-        <v>4.02140140533447</v>
+        <v>4.02140092849731</v>
       </c>
       <c r="H835" t="s">
         <v>8</v>
@@ -22105,7 +22105,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G836" t="n">
-        <v>4.02140140533447</v>
+        <v>4.02140092849731</v>
       </c>
       <c r="H836" t="s">
         <v>8</v>
@@ -22131,7 +22131,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G837" t="n">
-        <v>3.98178148269653</v>
+        <v>3.98178124427795</v>
       </c>
       <c r="H837" t="s">
         <v>8</v>
@@ -22287,7 +22287,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G843" t="n">
-        <v>4.02140140533447</v>
+        <v>4.02140092849731</v>
       </c>
       <c r="H843" t="s">
         <v>8</v>
@@ -22313,7 +22313,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G844" t="n">
-        <v>3.98178148269653</v>
+        <v>3.98178124427795</v>
       </c>
       <c r="H844" t="s">
         <v>8</v>
@@ -22391,7 +22391,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G847" t="n">
-        <v>4.06102085113525</v>
+        <v>4.0610203742981</v>
       </c>
       <c r="H847" t="s">
         <v>8</v>
@@ -22417,7 +22417,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G848" t="n">
-        <v>4.0808310508728</v>
+        <v>4.08083057403564</v>
       </c>
       <c r="H848" t="s">
         <v>8</v>
@@ -22469,7 +22469,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G850" t="n">
-        <v>4.14026021957397</v>
+        <v>4.14025974273682</v>
       </c>
       <c r="H850" t="s">
         <v>8</v>
@@ -22495,7 +22495,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G851" t="n">
-        <v>4.16997480392456</v>
+        <v>4.16997528076172</v>
       </c>
       <c r="H851" t="s">
         <v>8</v>
@@ -22573,7 +22573,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G854" t="n">
-        <v>4.16007041931152</v>
+        <v>4.16006994247437</v>
       </c>
       <c r="H854" t="s">
         <v>8</v>
@@ -22599,7 +22599,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G855" t="n">
-        <v>4.16007041931152</v>
+        <v>4.16006994247437</v>
       </c>
       <c r="H855" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G856" t="n">
-        <v>4.09073543548584</v>
+        <v>4.090735912323</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22781,7 +22781,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G862" t="n">
-        <v>4.0808310508728</v>
+        <v>4.08083057403564</v>
       </c>
       <c r="H862" t="s">
         <v>8</v>
@@ -22833,7 +22833,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G864" t="n">
-        <v>4.0808310508728</v>
+        <v>4.08083057403564</v>
       </c>
       <c r="H864" t="s">
         <v>8</v>
@@ -22859,7 +22859,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G865" t="n">
-        <v>4.0808310508728</v>
+        <v>4.08083057403564</v>
       </c>
       <c r="H865" t="s">
         <v>8</v>
@@ -22989,7 +22989,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G870" t="n">
-        <v>4.02140140533447</v>
+        <v>4.02140092849731</v>
       </c>
       <c r="H870" t="s">
         <v>8</v>
@@ -23041,7 +23041,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G872" t="n">
-        <v>4.02140140533447</v>
+        <v>4.02140092849731</v>
       </c>
       <c r="H872" t="s">
         <v>8</v>
@@ -23119,7 +23119,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G875" t="n">
-        <v>4.06102085113525</v>
+        <v>4.0610203742981</v>
       </c>
       <c r="H875" t="s">
         <v>8</v>
@@ -23145,7 +23145,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G876" t="n">
-        <v>4.0808310508728</v>
+        <v>4.08083057403564</v>
       </c>
       <c r="H876" t="s">
         <v>8</v>
@@ -23171,7 +23171,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G877" t="n">
-        <v>4.16997480392456</v>
+        <v>4.16997528076172</v>
       </c>
       <c r="H877" t="s">
         <v>8</v>
@@ -23197,7 +23197,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G878" t="n">
-        <v>4.24921417236328</v>
+        <v>4.24921464920044</v>
       </c>
       <c r="H878" t="s">
         <v>8</v>
@@ -23223,7 +23223,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G879" t="n">
-        <v>4.29873991012573</v>
+        <v>4.29873943328857</v>
       </c>
       <c r="H879" t="s">
         <v>8</v>
@@ -23275,7 +23275,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G881" t="n">
-        <v>4.24921417236328</v>
+        <v>4.24921464920044</v>
       </c>
       <c r="H881" t="s">
         <v>8</v>
@@ -23327,7 +23327,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G883" t="n">
-        <v>4.33835887908936</v>
+        <v>4.3383584022522</v>
       </c>
       <c r="H883" t="s">
         <v>8</v>
@@ -23379,7 +23379,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G885" t="n">
-        <v>4.33835887908936</v>
+        <v>4.3383584022522</v>
       </c>
       <c r="H885" t="s">
         <v>8</v>
@@ -23587,7 +23587,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G893" t="n">
-        <v>4.2393102645874</v>
+        <v>4.23930978775024</v>
       </c>
       <c r="H893" t="s">
         <v>8</v>
@@ -23769,7 +23769,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G900" t="n">
-        <v>4.25911998748779</v>
+        <v>4.25911951065063</v>
       </c>
       <c r="H900" t="s">
         <v>8</v>
@@ -23795,7 +23795,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G901" t="n">
-        <v>4.25911998748779</v>
+        <v>4.25911951065063</v>
       </c>
       <c r="H901" t="s">
         <v>8</v>
@@ -23847,7 +23847,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G903" t="n">
-        <v>4.24921417236328</v>
+        <v>4.24921464920044</v>
       </c>
       <c r="H903" t="s">
         <v>8</v>
@@ -23899,7 +23899,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G905" t="n">
-        <v>4.24921417236328</v>
+        <v>4.24921464920044</v>
       </c>
       <c r="H905" t="s">
         <v>8</v>
@@ -23925,7 +23925,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G906" t="n">
-        <v>4.24921417236328</v>
+        <v>4.24921464920044</v>
       </c>
       <c r="H906" t="s">
         <v>8</v>
@@ -23951,7 +23951,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G907" t="n">
-        <v>4.17988014221191</v>
+        <v>4.17987966537476</v>
       </c>
       <c r="H907" t="s">
         <v>8</v>
@@ -24029,7 +24029,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G910" t="n">
-        <v>4.06102085113525</v>
+        <v>4.0610203742981</v>
       </c>
       <c r="H910" t="s">
         <v>8</v>
@@ -24107,7 +24107,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G913" t="n">
-        <v>3.84311246871948</v>
+        <v>3.84311270713806</v>
       </c>
       <c r="H913" t="s">
         <v>8</v>
@@ -24263,7 +24263,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G919" t="n">
-        <v>3.85301756858826</v>
+        <v>3.85301733016968</v>
       </c>
       <c r="H919" t="s">
         <v>8</v>
@@ -24315,7 +24315,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G921" t="n">
-        <v>3.70444321632385</v>
+        <v>3.70444345474243</v>
       </c>
       <c r="H921" t="s">
         <v>8</v>
@@ -24445,7 +24445,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G926" t="n">
-        <v>3.62520408630371</v>
+        <v>3.62520432472229</v>
       </c>
       <c r="H926" t="s">
         <v>8</v>
@@ -24549,7 +24549,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G930" t="n">
-        <v>3.66482377052307</v>
+        <v>3.66482400894165</v>
       </c>
       <c r="H930" t="s">
         <v>8</v>
@@ -24731,7 +24731,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G937" t="n">
-        <v>3.70444321632385</v>
+        <v>3.70444345474243</v>
       </c>
       <c r="H937" t="s">
         <v>8</v>
@@ -24757,7 +24757,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G938" t="n">
-        <v>3.70444321632385</v>
+        <v>3.70444345474243</v>
       </c>
       <c r="H938" t="s">
         <v>8</v>
@@ -24835,7 +24835,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G941" t="n">
-        <v>3.88273215293884</v>
+        <v>3.88273239135742</v>
       </c>
       <c r="H941" t="s">
         <v>8</v>
@@ -24991,7 +24991,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G947" t="n">
-        <v>4.06102085113525</v>
+        <v>4.0610203742981</v>
       </c>
       <c r="H947" t="s">
         <v>8</v>
@@ -25017,7 +25017,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G948" t="n">
-        <v>4.10064077377319</v>
+        <v>4.10064029693604</v>
       </c>
       <c r="H948" t="s">
         <v>8</v>
@@ -25043,7 +25043,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G949" t="n">
-        <v>4.17988014221191</v>
+        <v>4.17987966537476</v>
       </c>
       <c r="H949" t="s">
         <v>8</v>
@@ -25069,7 +25069,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G950" t="n">
-        <v>4.10064077377319</v>
+        <v>4.10064029693604</v>
       </c>
       <c r="H950" t="s">
         <v>8</v>
@@ -25095,7 +25095,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G951" t="n">
-        <v>3.98178148269653</v>
+        <v>3.98178124427795</v>
       </c>
       <c r="H951" t="s">
         <v>8</v>
@@ -25173,7 +25173,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G954" t="n">
-        <v>4.06102085113525</v>
+        <v>4.0610203742981</v>
       </c>
       <c r="H954" t="s">
         <v>8</v>
@@ -25329,7 +25329,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G960" t="n">
-        <v>4.02140140533447</v>
+        <v>4.02140092849731</v>
       </c>
       <c r="H960" t="s">
         <v>8</v>
@@ -25459,7 +25459,7 @@
         <v>3.97849988937378</v>
       </c>
       <c r="G965" t="n">
-        <v>3.94067573547363</v>
+        <v>3.94067597389221</v>
       </c>
       <c r="H965" t="s">
         <v>8</v>
@@ -25563,7 +25563,7 @@
         <v>3.99699997901917</v>
       </c>
       <c r="G969" t="n">
-        <v>3.95900011062622</v>
+        <v>3.95899987220764</v>
       </c>
       <c r="H969" t="s">
         <v>8</v>
@@ -25615,7 +25615,7 @@
         <v>3.99799990653992</v>
       </c>
       <c r="G971" t="n">
-        <v>3.95999050140381</v>
+        <v>3.95999026298523</v>
       </c>
       <c r="H971" t="s">
         <v>8</v>
@@ -25797,7 +25797,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G978" t="n">
-        <v>4.02140140533447</v>
+        <v>4.02140092849731</v>
       </c>
       <c r="H978" t="s">
         <v>8</v>
@@ -26005,7 +26005,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G986" t="n">
-        <v>3.88273215293884</v>
+        <v>3.88273239135742</v>
       </c>
       <c r="H986" t="s">
         <v>8</v>
@@ -26031,7 +26031,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G987" t="n">
-        <v>3.85301756858826</v>
+        <v>3.85301733016968</v>
       </c>
       <c r="H987" t="s">
         <v>8</v>
@@ -26057,7 +26057,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G988" t="n">
-        <v>3.85301756858826</v>
+        <v>3.85301733016968</v>
       </c>
       <c r="H988" t="s">
         <v>8</v>
@@ -26083,7 +26083,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G989" t="n">
-        <v>3.80349254608154</v>
+        <v>3.80349278450012</v>
       </c>
       <c r="H989" t="s">
         <v>8</v>
@@ -26109,7 +26109,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G990" t="n">
-        <v>3.80349254608154</v>
+        <v>3.80349278450012</v>
       </c>
       <c r="H990" t="s">
         <v>8</v>
@@ -26213,7 +26213,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G994" t="n">
-        <v>3.85301756858826</v>
+        <v>3.85301733016968</v>
       </c>
       <c r="H994" t="s">
         <v>8</v>
@@ -26265,7 +26265,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G996" t="n">
-        <v>3.80349254608154</v>
+        <v>3.80349278450012</v>
       </c>
       <c r="H996" t="s">
         <v>8</v>
@@ -26291,7 +26291,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G997" t="n">
-        <v>3.80349254608154</v>
+        <v>3.80349278450012</v>
       </c>
       <c r="H997" t="s">
         <v>8</v>
@@ -26733,7 +26733,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1014" t="n">
-        <v>3.66482377052307</v>
+        <v>3.66482400894165</v>
       </c>
       <c r="H1014" t="s">
         <v>8</v>
@@ -26759,7 +26759,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1015" t="n">
-        <v>3.66482377052307</v>
+        <v>3.66482400894165</v>
       </c>
       <c r="H1015" t="s">
         <v>8</v>
@@ -26967,7 +26967,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1023" t="n">
-        <v>3.66482377052307</v>
+        <v>3.66482400894165</v>
       </c>
       <c r="H1023" t="s">
         <v>8</v>
@@ -27409,7 +27409,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1040" t="n">
-        <v>3.49643993377686</v>
+        <v>3.49643969535828</v>
       </c>
       <c r="H1040" t="s">
         <v>8</v>
@@ -27435,7 +27435,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1041" t="n">
-        <v>3.49643993377686</v>
+        <v>3.49643969535828</v>
       </c>
       <c r="H1041" t="s">
         <v>8</v>
@@ -27539,7 +27539,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1045" t="n">
-        <v>3.50634479522705</v>
+        <v>3.50634455680847</v>
       </c>
       <c r="H1045" t="s">
         <v>8</v>
@@ -27721,7 +27721,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1052" t="n">
-        <v>3.49643993377686</v>
+        <v>3.49643969535828</v>
       </c>
       <c r="H1052" t="s">
         <v>8</v>
@@ -28007,7 +28007,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1063" t="n">
-        <v>3.80349254608154</v>
+        <v>3.80349278450012</v>
       </c>
       <c r="H1063" t="s">
         <v>8</v>
@@ -28059,7 +28059,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G1065" t="n">
-        <v>3.98178148269653</v>
+        <v>3.98178124427795</v>
       </c>
       <c r="H1065" t="s">
         <v>8</v>
@@ -28137,7 +28137,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1068" t="n">
-        <v>3.80349254608154</v>
+        <v>3.80349278450012</v>
       </c>
       <c r="H1068" t="s">
         <v>8</v>
@@ -28189,7 +28189,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1070" t="n">
-        <v>3.80349254608154</v>
+        <v>3.80349278450012</v>
       </c>
       <c r="H1070" t="s">
         <v>8</v>
@@ -28215,7 +28215,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1071" t="n">
-        <v>3.80349254608154</v>
+        <v>3.80349278450012</v>
       </c>
       <c r="H1071" t="s">
         <v>8</v>
@@ -28553,7 +28553,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1084" t="n">
-        <v>3.6347188949585</v>
+        <v>3.63471913337708</v>
       </c>
       <c r="H1084" t="s">
         <v>8</v>
@@ -28865,7 +28865,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1096" t="n">
-        <v>3.6347188949585</v>
+        <v>3.63471913337708</v>
       </c>
       <c r="H1096" t="s">
         <v>8</v>
@@ -28943,7 +28943,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1099" t="n">
-        <v>3.6347188949585</v>
+        <v>3.63471913337708</v>
       </c>
       <c r="H1099" t="s">
         <v>8</v>
@@ -29073,7 +29073,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G1104" t="n">
-        <v>3.55527138710022</v>
+        <v>3.55527114868164</v>
       </c>
       <c r="H1104" t="s">
         <v>8</v>
@@ -29099,7 +29099,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1105" t="n">
-        <v>3.67444252967834</v>
+        <v>3.67444276809692</v>
       </c>
       <c r="H1105" t="s">
         <v>8</v>
@@ -29281,7 +29281,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1112" t="n">
-        <v>3.50561690330505</v>
+        <v>3.50561666488647</v>
       </c>
       <c r="H1112" t="s">
         <v>8</v>
@@ -29307,7 +29307,7 @@
         <v>3.5</v>
       </c>
       <c r="G1113" t="n">
-        <v>3.47582411766052</v>
+        <v>3.47582387924194</v>
       </c>
       <c r="H1113" t="s">
         <v>8</v>
@@ -29333,7 +29333,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1114" t="n">
-        <v>3.43610048294067</v>
+        <v>3.43610024452209</v>
       </c>
       <c r="H1114" t="s">
         <v>8</v>
@@ -29359,7 +29359,7 @@
         <v>3.5</v>
       </c>
       <c r="G1115" t="n">
-        <v>3.47582411766052</v>
+        <v>3.47582387924194</v>
       </c>
       <c r="H1115" t="s">
         <v>8</v>
@@ -29385,7 +29385,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1116" t="n">
-        <v>3.43610048294067</v>
+        <v>3.43610024452209</v>
       </c>
       <c r="H1116" t="s">
         <v>8</v>
@@ -29437,7 +29437,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1118" t="n">
-        <v>3.51554775238037</v>
+        <v>3.51554751396179</v>
       </c>
       <c r="H1118" t="s">
         <v>8</v>
@@ -29515,7 +29515,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1121" t="n">
-        <v>3.50561690330505</v>
+        <v>3.50561666488647</v>
       </c>
       <c r="H1121" t="s">
         <v>8</v>
@@ -29541,7 +29541,7 @@
         <v>3.5</v>
       </c>
       <c r="G1122" t="n">
-        <v>3.47582411766052</v>
+        <v>3.47582387924194</v>
       </c>
       <c r="H1122" t="s">
         <v>8</v>
@@ -29567,7 +29567,7 @@
         <v>3.5</v>
       </c>
       <c r="G1123" t="n">
-        <v>3.47582411766052</v>
+        <v>3.47582387924194</v>
       </c>
       <c r="H1123" t="s">
         <v>8</v>
@@ -29619,7 +29619,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1125" t="n">
-        <v>3.41623854637146</v>
+        <v>3.41623830795288</v>
       </c>
       <c r="H1125" t="s">
         <v>8</v>
@@ -29645,7 +29645,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1126" t="n">
-        <v>3.41623854637146</v>
+        <v>3.41623830795288</v>
       </c>
       <c r="H1126" t="s">
         <v>8</v>
@@ -29671,7 +29671,7 @@
         <v>3.5</v>
       </c>
       <c r="G1127" t="n">
-        <v>3.47582411766052</v>
+        <v>3.47582387924194</v>
       </c>
       <c r="H1127" t="s">
         <v>8</v>
@@ -29697,7 +29697,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1128" t="n">
-        <v>3.51554775238037</v>
+        <v>3.51554751396179</v>
       </c>
       <c r="H1128" t="s">
         <v>8</v>
@@ -29801,7 +29801,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1132" t="n">
-        <v>3.41623854637146</v>
+        <v>3.41623830795288</v>
       </c>
       <c r="H1132" t="s">
         <v>8</v>
@@ -29931,7 +29931,7 @@
         <v>3.5</v>
       </c>
       <c r="G1137" t="n">
-        <v>3.47582411766052</v>
+        <v>3.47582387924194</v>
       </c>
       <c r="H1137" t="s">
         <v>8</v>
@@ -30009,7 +30009,7 @@
         <v>3.5</v>
       </c>
       <c r="G1140" t="n">
-        <v>3.47582411766052</v>
+        <v>3.47582387924194</v>
       </c>
       <c r="H1140" t="s">
         <v>8</v>
@@ -30087,7 +30087,7 @@
         <v>3.5</v>
       </c>
       <c r="G1143" t="n">
-        <v>3.47582411766052</v>
+        <v>3.47582387924194</v>
       </c>
       <c r="H1143" t="s">
         <v>8</v>
@@ -30139,7 +30139,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G1145" t="n">
-        <v>3.55527138710022</v>
+        <v>3.55527114868164</v>
       </c>
       <c r="H1145" t="s">
         <v>8</v>
@@ -30165,7 +30165,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1146" t="n">
-        <v>3.67444252967834</v>
+        <v>3.67444276809692</v>
       </c>
       <c r="H1146" t="s">
         <v>8</v>
@@ -30191,7 +30191,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1147" t="n">
-        <v>3.71416616439819</v>
+        <v>3.71416640281677</v>
       </c>
       <c r="H1147" t="s">
         <v>8</v>
@@ -30269,7 +30269,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1150" t="n">
-        <v>3.67444252967834</v>
+        <v>3.67444276809692</v>
       </c>
       <c r="H1150" t="s">
         <v>8</v>
@@ -30321,7 +30321,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1152" t="n">
-        <v>3.67444252967834</v>
+        <v>3.67444276809692</v>
       </c>
       <c r="H1152" t="s">
         <v>8</v>
@@ -30555,7 +30555,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G1161" t="n">
-        <v>3.55527138710022</v>
+        <v>3.55527114868164</v>
       </c>
       <c r="H1161" t="s">
         <v>8</v>
@@ -30763,7 +30763,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G1169" t="n">
-        <v>3.55527138710022</v>
+        <v>3.55527114868164</v>
       </c>
       <c r="H1169" t="s">
         <v>8</v>
@@ -30789,7 +30789,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1170" t="n">
-        <v>3.6347188949585</v>
+        <v>3.63471913337708</v>
       </c>
       <c r="H1170" t="s">
         <v>8</v>
@@ -30815,7 +30815,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1171" t="n">
-        <v>3.6347188949585</v>
+        <v>3.63471913337708</v>
       </c>
       <c r="H1171" t="s">
         <v>8</v>
@@ -31049,7 +31049,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G1180" t="n">
-        <v>3.55527138710022</v>
+        <v>3.55527114868164</v>
       </c>
       <c r="H1180" t="s">
         <v>8</v>
@@ -31101,7 +31101,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1182" t="n">
-        <v>3.50561690330505</v>
+        <v>3.50561666488647</v>
       </c>
       <c r="H1182" t="s">
         <v>8</v>
@@ -31127,7 +31127,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1183" t="n">
-        <v>3.50561690330505</v>
+        <v>3.50561666488647</v>
       </c>
       <c r="H1183" t="s">
         <v>8</v>
@@ -31179,7 +31179,7 @@
         <v>3.5</v>
       </c>
       <c r="G1185" t="n">
-        <v>3.47582411766052</v>
+        <v>3.47582387924194</v>
       </c>
       <c r="H1185" t="s">
         <v>8</v>
@@ -31257,7 +31257,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1188" t="n">
-        <v>3.41623854637146</v>
+        <v>3.41623830795288</v>
       </c>
       <c r="H1188" t="s">
         <v>8</v>
@@ -31413,7 +31413,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G1194" t="n">
-        <v>2.93955421447754</v>
+        <v>2.93955397605896</v>
       </c>
       <c r="H1194" t="s">
         <v>8</v>
@@ -31751,7 +31751,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G1207" t="n">
-        <v>2.76079750061035</v>
+        <v>2.76079726219177</v>
       </c>
       <c r="H1207" t="s">
         <v>8</v>
@@ -31777,7 +31777,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G1208" t="n">
-        <v>2.70121192932129</v>
+        <v>2.70121169090271</v>
       </c>
       <c r="H1208" t="s">
         <v>8</v>
@@ -32245,7 +32245,7 @@
         <v>3</v>
       </c>
       <c r="G1226" t="n">
-        <v>2.97927784919739</v>
+        <v>2.97927761077881</v>
       </c>
       <c r="H1226" t="s">
         <v>8</v>
@@ -32297,7 +32297,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G1228" t="n">
-        <v>2.93955421447754</v>
+        <v>2.93955397605896</v>
       </c>
       <c r="H1228" t="s">
         <v>8</v>
@@ -32349,7 +32349,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G1230" t="n">
-        <v>2.93955421447754</v>
+        <v>2.93955397605896</v>
       </c>
       <c r="H1230" t="s">
         <v>8</v>
@@ -32375,7 +32375,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G1231" t="n">
-        <v>2.93955421447754</v>
+        <v>2.93955397605896</v>
       </c>
       <c r="H1231" t="s">
         <v>8</v>
@@ -32401,7 +32401,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G1232" t="n">
-        <v>2.93955421447754</v>
+        <v>2.93955397605896</v>
       </c>
       <c r="H1232" t="s">
         <v>8</v>
@@ -32479,7 +32479,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1235" t="n">
-        <v>2.87996864318848</v>
+        <v>2.8799684047699</v>
       </c>
       <c r="H1235" t="s">
         <v>8</v>
@@ -32765,7 +32765,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G1246" t="n">
-        <v>2.58204078674316</v>
+        <v>2.58204054832458</v>
       </c>
       <c r="H1246" t="s">
         <v>8</v>
@@ -32999,7 +32999,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G1255" t="n">
-        <v>2.66148829460144</v>
+        <v>2.66148805618286</v>
       </c>
       <c r="H1255" t="s">
         <v>8</v>
@@ -33155,7 +33155,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1261" t="n">
-        <v>2.87996864318848</v>
+        <v>2.8799684047699</v>
       </c>
       <c r="H1261" t="s">
         <v>8</v>
@@ -33207,7 +33207,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G1263" t="n">
-        <v>2.84024477005005</v>
+        <v>2.84024453163147</v>
       </c>
       <c r="H1263" t="s">
         <v>8</v>
@@ -33233,7 +33233,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1264" t="n">
-        <v>2.87996864318848</v>
+        <v>2.8799684047699</v>
       </c>
       <c r="H1264" t="s">
         <v>8</v>
@@ -33389,7 +33389,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G1270" t="n">
-        <v>2.76079750061035</v>
+        <v>2.76079726219177</v>
       </c>
       <c r="H1270" t="s">
         <v>8</v>
@@ -33441,7 +33441,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G1272" t="n">
-        <v>2.76079750061035</v>
+        <v>2.76079726219177</v>
       </c>
       <c r="H1272" t="s">
         <v>8</v>
@@ -33493,7 +33493,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G1274" t="n">
-        <v>2.84024477005005</v>
+        <v>2.84024453163147</v>
       </c>
       <c r="H1274" t="s">
         <v>8</v>
@@ -33675,7 +33675,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G1281" t="n">
-        <v>2.84024477005005</v>
+        <v>2.84024453163147</v>
       </c>
       <c r="H1281" t="s">
         <v>8</v>
@@ -33831,7 +33831,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G1287" t="n">
-        <v>2.66148829460144</v>
+        <v>2.66148805618286</v>
       </c>
       <c r="H1287" t="s">
         <v>8</v>
@@ -33857,7 +33857,7 @@
         <v>2.5</v>
       </c>
       <c r="G1288" t="n">
-        <v>2.48273158073425</v>
+        <v>2.48273134231567</v>
       </c>
       <c r="H1288" t="s">
         <v>8</v>
@@ -34013,7 +34013,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G1294" t="n">
-        <v>2.62176465988159</v>
+        <v>2.62176442146301</v>
       </c>
       <c r="H1294" t="s">
         <v>8</v>
@@ -34247,7 +34247,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1303" t="n">
-        <v>2.87996864318848</v>
+        <v>2.8799684047699</v>
       </c>
       <c r="H1303" t="s">
         <v>8</v>
@@ -34377,7 +34377,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G1308" t="n">
-        <v>2.84024477005005</v>
+        <v>2.84024453163147</v>
       </c>
       <c r="H1308" t="s">
         <v>8</v>
@@ -34429,7 +34429,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G1310" t="n">
-        <v>2.8005211353302</v>
+        <v>2.80052089691162</v>
       </c>
       <c r="H1310" t="s">
         <v>8</v>
@@ -34533,7 +34533,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G1314" t="n">
-        <v>2.93955421447754</v>
+        <v>2.93955397605896</v>
       </c>
       <c r="H1314" t="s">
         <v>8</v>
@@ -43532,6 +43532,32 @@
         <v>3.4449999332428</v>
       </c>
       <c r="H1660" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1661">
+      <c r="A1661" s="1" t="n">
+        <v>46290.2916666667</v>
+      </c>
+      <c r="B1661" t="n">
+        <v>17828</v>
+      </c>
+      <c r="C1661" t="n">
+        <v>3.4449999332428</v>
+      </c>
+      <c r="D1661" t="n">
+        <v>3.36999988555908</v>
+      </c>
+      <c r="E1661" t="n">
+        <v>3.4449999332428</v>
+      </c>
+      <c r="F1661" t="n">
+        <v>3.40499997138977</v>
+      </c>
+      <c r="G1661" t="n">
+        <v>3.40499997138977</v>
+      </c>
+      <c r="H1661" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/UD.MI.xlsx
+++ b/data/UD.MI.xlsx
@@ -421,7 +421,7 @@
         <v>1.5</v>
       </c>
       <c r="G2" t="n">
-        <v>1.47885513305664</v>
+        <v>1.47885525226593</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -447,7 +447,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G3" t="n">
-        <v>1.43941903114319</v>
+        <v>1.43941915035248</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G7" t="n">
-        <v>1.51829135417938</v>
+        <v>1.51829123497009</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G8" t="n">
-        <v>1.53800940513611</v>
+        <v>1.53800928592682</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G9" t="n">
-        <v>1.55772745609283</v>
+        <v>1.55772757530212</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G10" t="n">
-        <v>1.53800940513611</v>
+        <v>1.53800928592682</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G11" t="n">
-        <v>1.56265711784363</v>
+        <v>1.56265687942505</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G13" t="n">
-        <v>1.55772745609283</v>
+        <v>1.55772757530212</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G18" t="n">
-        <v>1.67603588104248</v>
+        <v>1.67603576183319</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G19" t="n">
-        <v>1.67603588104248</v>
+        <v>1.67603576183319</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>1.67499995231628</v>
       </c>
       <c r="G20" t="n">
-        <v>1.65138816833496</v>
+        <v>1.65138828754425</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G22" t="n">
-        <v>1.62181115150452</v>
+        <v>1.62181127071381</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>1.59500002861023</v>
       </c>
       <c r="G28" t="n">
-        <v>1.57251608371735</v>
+        <v>1.57251620292664</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G33" t="n">
-        <v>1.61688148975372</v>
+        <v>1.61688160896301</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G39" t="n">
-        <v>1.67110645771027</v>
+        <v>1.67110657691956</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G40" t="n">
-        <v>1.69575381278992</v>
+        <v>1.6957540512085</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G46" t="n">
-        <v>1.67603588104248</v>
+        <v>1.67603576183319</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G56" t="n">
-        <v>1.69575381278992</v>
+        <v>1.6957540512085</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G57" t="n">
-        <v>1.67603588104248</v>
+        <v>1.67603576183319</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>1.7150000333786</v>
       </c>
       <c r="G58" t="n">
-        <v>1.6908243894577</v>
+        <v>1.69082450866699</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>1.7150000333786</v>
       </c>
       <c r="G59" t="n">
-        <v>1.6908243894577</v>
+        <v>1.69082450866699</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>1.67499995231628</v>
       </c>
       <c r="G62" t="n">
-        <v>1.65138816833496</v>
+        <v>1.65138828754425</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>1.68499994277954</v>
       </c>
       <c r="G63" t="n">
-        <v>1.66124725341797</v>
+        <v>1.66124713420868</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>1.67499995231628</v>
       </c>
       <c r="G64" t="n">
-        <v>1.65138816833496</v>
+        <v>1.65138828754425</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>1.67499995231628</v>
       </c>
       <c r="G65" t="n">
-        <v>1.65138816833496</v>
+        <v>1.65138828754425</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G66" t="n">
-        <v>1.67603588104248</v>
+        <v>1.67603576183319</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>1.67499995231628</v>
       </c>
       <c r="G75" t="n">
-        <v>1.65138816833496</v>
+        <v>1.65138828754425</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G76" t="n">
-        <v>1.67110645771027</v>
+        <v>1.67110657691956</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G79" t="n">
-        <v>1.67603588104248</v>
+        <v>1.67603576183319</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G80" t="n">
-        <v>1.67603588104248</v>
+        <v>1.67603576183319</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G81" t="n">
-        <v>1.67603588104248</v>
+        <v>1.67603576183319</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>1.59500002861023</v>
       </c>
       <c r="G90" t="n">
-        <v>1.57251608371735</v>
+        <v>1.57251620292664</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>1.59500002861023</v>
       </c>
       <c r="G91" t="n">
-        <v>1.57251608371735</v>
+        <v>1.57251620292664</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>1.59500002861023</v>
       </c>
       <c r="G93" t="n">
-        <v>1.57251608371735</v>
+        <v>1.57251620292664</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>1.59500002861023</v>
       </c>
       <c r="G94" t="n">
-        <v>1.57251608371735</v>
+        <v>1.57251620292664</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G96" t="n">
-        <v>1.62181115150452</v>
+        <v>1.62181127071381</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>1.66499996185303</v>
       </c>
       <c r="G106" t="n">
-        <v>1.64152920246124</v>
+        <v>1.64152932167053</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G110" t="n">
-        <v>1.67603588104248</v>
+        <v>1.67603576183319</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G111" t="n">
-        <v>1.67603588104248</v>
+        <v>1.67603576183319</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G112" t="n">
-        <v>1.67603588104248</v>
+        <v>1.67603576183319</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G113" t="n">
-        <v>1.67603588104248</v>
+        <v>1.67603576183319</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G114" t="n">
-        <v>1.67603588104248</v>
+        <v>1.67603576183319</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G115" t="n">
-        <v>1.67603588104248</v>
+        <v>1.67603576183319</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G124" t="n">
-        <v>1.85349833965302</v>
+        <v>1.85349857807159</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G130" t="n">
-        <v>1.83870995044708</v>
+        <v>1.83871006965637</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G132" t="n">
-        <v>1.78448522090912</v>
+        <v>1.78448510169983</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G133" t="n">
-        <v>1.85349833965302</v>
+        <v>1.85349857807159</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G134" t="n">
-        <v>1.85349833965302</v>
+        <v>1.85349857807159</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G135" t="n">
-        <v>1.85349833965302</v>
+        <v>1.85349857807159</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G137" t="n">
-        <v>1.88307559490204</v>
+        <v>1.88307547569275</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G138" t="n">
-        <v>1.88307559490204</v>
+        <v>1.88307547569275</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G143" t="n">
-        <v>1.79927396774292</v>
+        <v>1.79927384853363</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G152" t="n">
-        <v>1.76969659328461</v>
+        <v>1.7696967124939</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G157" t="n">
-        <v>1.83870995044708</v>
+        <v>1.83871006965637</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G170" t="n">
-        <v>1.83870995044708</v>
+        <v>1.83871006965637</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G171" t="n">
-        <v>1.83870995044708</v>
+        <v>1.83871006965637</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G172" t="n">
-        <v>1.81406259536743</v>
+        <v>1.81406235694885</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G176" t="n">
-        <v>1.83870995044708</v>
+        <v>1.83871006965637</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G179" t="n">
-        <v>1.88307559490204</v>
+        <v>1.88307547569275</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G181" t="n">
-        <v>1.90279352664948</v>
+        <v>1.90279376506805</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G184" t="n">
-        <v>2.01124310493469</v>
+        <v>2.01124286651611</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G187" t="n">
-        <v>1.95208895206451</v>
+        <v>1.95208883285522</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G188" t="n">
-        <v>2.01124310493469</v>
+        <v>2.01124286651611</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G189" t="n">
-        <v>2.01124310493469</v>
+        <v>2.01124286651611</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G190" t="n">
-        <v>1.91758215427399</v>
+        <v>1.91758239269257</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G195" t="n">
-        <v>1.86335742473602</v>
+        <v>1.86335754394531</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G199" t="n">
-        <v>1.91758215427399</v>
+        <v>1.91758239269257</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G208" t="n">
-        <v>1.95208895206451</v>
+        <v>1.95208883285522</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G210" t="n">
-        <v>1.95701849460602</v>
+        <v>1.95701837539673</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G211" t="n">
-        <v>1.94715929031372</v>
+        <v>1.94715940952301</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G215" t="n">
-        <v>1.95701849460602</v>
+        <v>1.95701837539673</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G227" t="n">
-        <v>1.98166584968567</v>
+        <v>1.98166608810425</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G230" t="n">
-        <v>2.0211021900177</v>
+        <v>2.02110195159912</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G231" t="n">
-        <v>2.22814130783081</v>
+        <v>2.22814178466797</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G232" t="n">
-        <v>2.26757788658142</v>
+        <v>2.267578125</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>2.25</v>
       </c>
       <c r="G233" t="n">
-        <v>2.21828269958496</v>
+        <v>2.21828293800354</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G234" t="n">
-        <v>2.16898798942566</v>
+        <v>2.16898775100708</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G235" t="n">
-        <v>2.14926981925964</v>
+        <v>2.14926958084106</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G238" t="n">
-        <v>2.2380006313324</v>
+        <v>2.23800086975098</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>2.25</v>
       </c>
       <c r="G239" t="n">
-        <v>2.21828269958496</v>
+        <v>2.21828293800354</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G240" t="n">
-        <v>2.20842385292053</v>
+        <v>2.20842361450195</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G241" t="n">
-        <v>2.22814130783081</v>
+        <v>2.22814178466797</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G243" t="n">
-        <v>2.26757788658142</v>
+        <v>2.267578125</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G244" t="n">
-        <v>2.29715514183044</v>
+        <v>2.29715490341187</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G245" t="n">
-        <v>2.29715514183044</v>
+        <v>2.29715490341187</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G254" t="n">
-        <v>2.48447680473328</v>
+        <v>2.4844765663147</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G258" t="n">
-        <v>2.6126446723938</v>
+        <v>2.61264443397522</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G259" t="n">
-        <v>2.59292650222778</v>
+        <v>2.59292602539062</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G260" t="n">
-        <v>2.74081182479858</v>
+        <v>2.74081134796143</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G261" t="n">
-        <v>2.6619393825531</v>
+        <v>2.66193962097168</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G262" t="n">
-        <v>2.78024768829346</v>
+        <v>2.78024792671204</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G263" t="n">
-        <v>2.9774284362793</v>
+        <v>2.97742867469788</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>3</v>
       </c>
       <c r="G265" t="n">
-        <v>2.95771026611328</v>
+        <v>2.95771050453186</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G266" t="n">
-        <v>2.87883806228638</v>
+        <v>2.87883830070496</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G270" t="n">
-        <v>2.77038884162903</v>
+        <v>2.77038860321045</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G272" t="n">
-        <v>2.99714660644531</v>
+        <v>2.99714636802673</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G278" t="n">
-        <v>3.18446850776672</v>
+        <v>3.18446826934814</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G279" t="n">
-        <v>3.30277633666992</v>
+        <v>3.3027765750885</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G281" t="n">
-        <v>3.18446850776672</v>
+        <v>3.18446826934814</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G283" t="n">
-        <v>3.24362230300903</v>
+        <v>3.24362254142761</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G285" t="n">
-        <v>3.35207176208496</v>
+        <v>3.35207152366638</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G287" t="n">
-        <v>3.60840702056885</v>
+        <v>3.60840678215027</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G290" t="n">
-        <v>3.72671484947205</v>
+        <v>3.72671508789062</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G294" t="n">
-        <v>3.53939318656921</v>
+        <v>3.53939342498779</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G297" t="n">
-        <v>3.55911111831665</v>
+        <v>3.55911135673523</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G307" t="n">
-        <v>3.97319078445435</v>
+        <v>3.9731912612915</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G308" t="n">
-        <v>4.26896142959595</v>
+        <v>4.26896190643311</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G309" t="n">
-        <v>4.35769367218018</v>
+        <v>4.35769319534302</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G310" t="n">
-        <v>4.33797597885132</v>
+        <v>4.33797550201416</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G311" t="n">
-        <v>4.14079427719116</v>
+        <v>4.14079475402832</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G317" t="n">
-        <v>4.14079427719116</v>
+        <v>4.14079475402832</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G318" t="n">
-        <v>4.17037105560303</v>
+        <v>4.17037153244019</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G323" t="n">
-        <v>4.18023061752319</v>
+        <v>4.18023014068604</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G324" t="n">
-        <v>4.18023061752319</v>
+        <v>4.18023014068604</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G329" t="n">
-        <v>4.02248620986938</v>
+        <v>4.02248573303223</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G335" t="n">
-        <v>4.17037105560303</v>
+        <v>4.17037153244019</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G340" t="n">
-        <v>4.14079427719116</v>
+        <v>4.14079475402832</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G341" t="n">
-        <v>4.14079427719116</v>
+        <v>4.14079475402832</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G343" t="n">
-        <v>4.14079427719116</v>
+        <v>4.14079475402832</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G346" t="n">
-        <v>4.0422043800354</v>
+        <v>4.04220390319824</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G347" t="n">
-        <v>4.02248620986938</v>
+        <v>4.02248573303223</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G348" t="n">
-        <v>4.02248620986938</v>
+        <v>4.02248573303223</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G349" t="n">
-        <v>4.21966743469238</v>
+        <v>4.21966695785522</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G352" t="n">
-        <v>4.19994878768921</v>
+        <v>4.19994926452637</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G356" t="n">
-        <v>4.14079427719116</v>
+        <v>4.14079475402832</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G359" t="n">
-        <v>4.21966743469238</v>
+        <v>4.21966695785522</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G366" t="n">
-        <v>4.14079427719116</v>
+        <v>4.14079475402832</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G367" t="n">
-        <v>4.14079427719116</v>
+        <v>4.14079475402832</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G368" t="n">
-        <v>4.14079427719116</v>
+        <v>4.14079475402832</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G373" t="n">
-        <v>4.14079427719116</v>
+        <v>4.14079475402832</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G374" t="n">
-        <v>4.14079427719116</v>
+        <v>4.14079475402832</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G375" t="n">
-        <v>4.14079427719116</v>
+        <v>4.14079475402832</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G376" t="n">
-        <v>4.19994878768921</v>
+        <v>4.19994926452637</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G377" t="n">
-        <v>4.22952508926392</v>
+        <v>4.22952556610107</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G379" t="n">
-        <v>4.21966743469238</v>
+        <v>4.21966695785522</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G380" t="n">
-        <v>4.21966743469238</v>
+        <v>4.21966695785522</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G382" t="n">
-        <v>4.29853963851929</v>
+        <v>4.29853916168213</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G384" t="n">
-        <v>4.33797597885132</v>
+        <v>4.33797550201416</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G385" t="n">
-        <v>4.36755275726318</v>
+        <v>4.36755180358887</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G387" t="n">
-        <v>4.36755275726318</v>
+        <v>4.36755180358887</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G388" t="n">
-        <v>4.36755275726318</v>
+        <v>4.36755180358887</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G389" t="n">
-        <v>4.26896142959595</v>
+        <v>4.26896190643311</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G390" t="n">
-        <v>4.33797597885132</v>
+        <v>4.33797550201416</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G393" t="n">
-        <v>4.33797597885132</v>
+        <v>4.33797550201416</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G394" t="n">
-        <v>4.40698862075806</v>
+        <v>4.4069881439209</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G396" t="n">
-        <v>4.22952508926392</v>
+        <v>4.22952556610107</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G398" t="n">
-        <v>4.0422043800354</v>
+        <v>4.04220390319824</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G399" t="n">
-        <v>4.0422043800354</v>
+        <v>4.04220390319824</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G400" t="n">
-        <v>4.0422043800354</v>
+        <v>4.04220390319824</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G401" t="n">
-        <v>4.18023061752319</v>
+        <v>4.18023014068604</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G402" t="n">
-        <v>4.19994878768921</v>
+        <v>4.19994926452637</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G403" t="n">
-        <v>4.29853963851929</v>
+        <v>4.29853916168213</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G404" t="n">
-        <v>4.33797597885132</v>
+        <v>4.33797550201416</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G409" t="n">
-        <v>4.49571943283081</v>
+        <v>4.49571990966797</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G411" t="n">
-        <v>5.0478253364563</v>
+        <v>5.04782581329346</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G413" t="n">
-        <v>5.24500703811646</v>
+        <v>5.2450065612793</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G416" t="n">
-        <v>4.96895360946655</v>
+        <v>4.96895313262939</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G418" t="n">
-        <v>4.98867177963257</v>
+        <v>4.98867130279541</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G419" t="n">
-        <v>5.02810716629028</v>
+        <v>5.02810764312744</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G420" t="n">
-        <v>5.00838947296143</v>
+        <v>5.00838899612427</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G424" t="n">
-        <v>4.89008140563965</v>
+        <v>4.89008092880249</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G425" t="n">
-        <v>5.02810716629028</v>
+        <v>5.02810764312744</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G427" t="n">
-        <v>5.02810716629028</v>
+        <v>5.02810764312744</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G428" t="n">
-        <v>5.00838947296143</v>
+        <v>5.00838899612427</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G429" t="n">
-        <v>5.1266975402832</v>
+        <v>5.12669801712036</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G431" t="n">
-        <v>4.98867177963257</v>
+        <v>4.98867130279541</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G433" t="n">
-        <v>4.88022232055664</v>
+        <v>4.88022184371948</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G437" t="n">
-        <v>4.90979957580566</v>
+        <v>4.90979909896851</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G439" t="n">
-        <v>4.89008140563965</v>
+        <v>4.89008092880249</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G441" t="n">
-        <v>4.89008140563965</v>
+        <v>4.89008092880249</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G442" t="n">
-        <v>4.90979957580566</v>
+        <v>4.90979909896851</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G443" t="n">
-        <v>5.0478253364563</v>
+        <v>5.04782581329346</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G444" t="n">
-        <v>5.02810716629028</v>
+        <v>5.02810764312744</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G445" t="n">
-        <v>4.96895360946655</v>
+        <v>4.96895313262939</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G446" t="n">
-        <v>4.94923543930054</v>
+        <v>4.9492359161377</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G450" t="n">
-        <v>4.8309268951416</v>
+        <v>4.83092737197876</v>
       </c>
       <c r="H450" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G451" t="n">
-        <v>4.8309268951416</v>
+        <v>4.83092737197876</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G457" t="n">
-        <v>5.0478253364563</v>
+        <v>5.04782581329346</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G462" t="n">
-        <v>5.2252893447876</v>
+        <v>5.22528886795044</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G463" t="n">
-        <v>5.2252893447876</v>
+        <v>5.22528886795044</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G464" t="n">
-        <v>5.0478253364563</v>
+        <v>5.04782581329346</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G466" t="n">
-        <v>5.1266975402832</v>
+        <v>5.12669801712036</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G467" t="n">
-        <v>5.1266975402832</v>
+        <v>5.12669801712036</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G469" t="n">
-        <v>5.2252893447876</v>
+        <v>5.22528886795044</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G471" t="n">
-        <v>5.2252893447876</v>
+        <v>5.22528886795044</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G472" t="n">
-        <v>5.2252893447876</v>
+        <v>5.22528886795044</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G473" t="n">
-        <v>5.20557069778442</v>
+        <v>5.20557022094727</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G474" t="n">
-        <v>4.98867177963257</v>
+        <v>4.98867130279541</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G476" t="n">
-        <v>5.02810716629028</v>
+        <v>5.02810764312744</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G477" t="n">
-        <v>5.00838947296143</v>
+        <v>5.00838899612427</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G478" t="n">
-        <v>4.96895360946655</v>
+        <v>4.96895313262939</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G479" t="n">
-        <v>5.02810716629028</v>
+        <v>5.02810764312744</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G483" t="n">
-        <v>5.1266975402832</v>
+        <v>5.12669801712036</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G484" t="n">
-        <v>5.1266975402832</v>
+        <v>5.12669801712036</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G485" t="n">
-        <v>5.1266975402832</v>
+        <v>5.12669801712036</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G486" t="n">
-        <v>5.0478253364563</v>
+        <v>5.04782581329346</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13083,7 +13083,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G489" t="n">
-        <v>4.98867177963257</v>
+        <v>4.98867130279541</v>
       </c>
       <c r="H489" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G490" t="n">
-        <v>5.1266975402832</v>
+        <v>5.12669801712036</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G491" t="n">
-        <v>4.98867177963257</v>
+        <v>4.98867130279541</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G492" t="n">
-        <v>4.96895360946655</v>
+        <v>4.96895313262939</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G496" t="n">
-        <v>4.94923543930054</v>
+        <v>4.9492359161377</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G498" t="n">
-        <v>5.02810716629028</v>
+        <v>5.02810764312744</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G499" t="n">
-        <v>5.02810716629028</v>
+        <v>5.02810764312744</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G500" t="n">
-        <v>5.0478253364563</v>
+        <v>5.04782581329346</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G503" t="n">
-        <v>5.02810716629028</v>
+        <v>5.02810764312744</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G504" t="n">
-        <v>4.8309268951416</v>
+        <v>4.83092737197876</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G505" t="n">
-        <v>4.98867177963257</v>
+        <v>4.98867130279541</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G506" t="n">
-        <v>5.1266975402832</v>
+        <v>5.12669801712036</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G510" t="n">
-        <v>4.98867177963257</v>
+        <v>4.98867130279541</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G511" t="n">
-        <v>5.02810716629028</v>
+        <v>5.02810764312744</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G513" t="n">
-        <v>5.00838947296143</v>
+        <v>5.00838899612427</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G514" t="n">
-        <v>4.96895360946655</v>
+        <v>4.96895313262939</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G515" t="n">
-        <v>4.94923543930054</v>
+        <v>4.9492359161377</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13785,7 +13785,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G516" t="n">
-        <v>5.00838947296143</v>
+        <v>5.00838899612427</v>
       </c>
       <c r="H516" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G517" t="n">
-        <v>5.02810716629028</v>
+        <v>5.02810764312744</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G518" t="n">
-        <v>5.00838947296143</v>
+        <v>5.00838899612427</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13889,7 +13889,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G520" t="n">
-        <v>5.02810716629028</v>
+        <v>5.02810764312744</v>
       </c>
       <c r="H520" t="s">
         <v>8</v>
@@ -13915,7 +13915,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G521" t="n">
-        <v>5.20557069778442</v>
+        <v>5.20557022094727</v>
       </c>
       <c r="H521" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G522" t="n">
-        <v>5.0478253364563</v>
+        <v>5.04782581329346</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G523" t="n">
-        <v>5.02810716629028</v>
+        <v>5.02810764312744</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G524" t="n">
-        <v>4.94923543930054</v>
+        <v>4.9492359161377</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G525" t="n">
-        <v>4.88022232055664</v>
+        <v>4.88022184371948</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G526" t="n">
-        <v>5.00838947296143</v>
+        <v>5.00838899612427</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G529" t="n">
-        <v>4.77177238464355</v>
+        <v>4.77177286148071</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14149,7 +14149,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G530" t="n">
-        <v>4.73233652114868</v>
+        <v>4.73233699798584</v>
       </c>
       <c r="H530" t="s">
         <v>8</v>
@@ -14201,7 +14201,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G532" t="n">
-        <v>4.77177238464355</v>
+        <v>4.77177286148071</v>
       </c>
       <c r="H532" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G534" t="n">
-        <v>4.73233652114868</v>
+        <v>4.73233699798584</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G535" t="n">
-        <v>4.73233652114868</v>
+        <v>4.73233699798584</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G536" t="n">
-        <v>4.71261835098267</v>
+        <v>4.71261882781982</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G537" t="n">
-        <v>4.73233652114868</v>
+        <v>4.73233699798584</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G538" t="n">
-        <v>4.8999400138855</v>
+        <v>4.89993953704834</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G540" t="n">
-        <v>4.8309268951416</v>
+        <v>4.83092737197876</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G541" t="n">
-        <v>4.94923543930054</v>
+        <v>4.9492359161377</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G542" t="n">
-        <v>4.86050367355347</v>
+        <v>4.86050415039062</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G545" t="n">
-        <v>4.8309268951416</v>
+        <v>4.83092737197876</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G546" t="n">
-        <v>4.75205421447754</v>
+        <v>4.75205516815186</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G548" t="n">
-        <v>4.57422351837158</v>
+        <v>4.57422304153442</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G549" t="n">
-        <v>4.59398221969604</v>
+        <v>4.5939826965332</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G550" t="n">
-        <v>4.6433801651001</v>
+        <v>4.64337968826294</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G551" t="n">
-        <v>4.7421760559082</v>
+        <v>4.74217557907104</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G556" t="n">
-        <v>4.7421760559082</v>
+        <v>4.74217557907104</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G557" t="n">
-        <v>4.7421760559082</v>
+        <v>4.74217557907104</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G560" t="n">
-        <v>4.80145263671875</v>
+        <v>4.80145215988159</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G567" t="n">
-        <v>4.82121181488037</v>
+        <v>4.82121133804321</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G568" t="n">
-        <v>4.82121181488037</v>
+        <v>4.82121133804321</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G569" t="n">
-        <v>4.82121181488037</v>
+        <v>4.82121133804321</v>
       </c>
       <c r="H569" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G570" t="n">
-        <v>4.82121181488037</v>
+        <v>4.82121133804321</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G572" t="n">
-        <v>4.55446434020996</v>
+        <v>4.55446481704712</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G573" t="n">
-        <v>4.43590927124023</v>
+        <v>4.43590974807739</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G581" t="n">
-        <v>4.40627193450928</v>
+        <v>4.40627098083496</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G583" t="n">
-        <v>4.6433801651001</v>
+        <v>4.64337968826294</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G585" t="n">
-        <v>4.59398221969604</v>
+        <v>4.5939826965332</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G586" t="n">
-        <v>4.7421760559082</v>
+        <v>4.74217557907104</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G587" t="n">
-        <v>4.43590927124023</v>
+        <v>4.43590974807739</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G588" t="n">
-        <v>4.4951868057251</v>
+        <v>4.49518728256226</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G589" t="n">
-        <v>4.43590927124023</v>
+        <v>4.43590974807739</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G591" t="n">
-        <v>4.34699440002441</v>
+        <v>4.34699392318726</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G592" t="n">
-        <v>4.34699440002441</v>
+        <v>4.34699392318726</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15787,7 +15787,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G593" t="n">
-        <v>4.34699440002441</v>
+        <v>4.34699392318726</v>
       </c>
       <c r="H593" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G594" t="n">
-        <v>4.48530769348145</v>
+        <v>4.48530721664429</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G595" t="n">
-        <v>4.35687398910522</v>
+        <v>4.35687351226807</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G597" t="n">
-        <v>4.40627193450928</v>
+        <v>4.40627098083496</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G598" t="n">
-        <v>4.4951868057251</v>
+        <v>4.49518728256226</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G599" t="n">
-        <v>4.43590927124023</v>
+        <v>4.43590974807739</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G600" t="n">
-        <v>4.48530769348145</v>
+        <v>4.48530721664429</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G602" t="n">
-        <v>4.59398221969604</v>
+        <v>4.5939826965332</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G603" t="n">
-        <v>4.6433801651001</v>
+        <v>4.64337968826294</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G606" t="n">
-        <v>4.89036798477173</v>
+        <v>4.89036846160889</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G616" t="n">
-        <v>4.97928428649902</v>
+        <v>4.97928380966187</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16411,7 +16411,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G617" t="n">
-        <v>4.97928428649902</v>
+        <v>4.97928380966187</v>
       </c>
       <c r="H617" t="s">
         <v>8</v>
@@ -16463,7 +16463,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G619" t="n">
-        <v>4.97928428649902</v>
+        <v>4.97928380966187</v>
       </c>
       <c r="H619" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G620" t="n">
-        <v>4.99904346466064</v>
+        <v>4.99904298782349</v>
       </c>
       <c r="H620" t="s">
         <v>8</v>
@@ -16515,7 +16515,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G621" t="n">
-        <v>5.01880264282227</v>
+        <v>5.01880168914795</v>
       </c>
       <c r="H621" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G622" t="n">
-        <v>5.01880264282227</v>
+        <v>5.01880168914795</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16567,7 +16567,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G623" t="n">
-        <v>5.01880264282227</v>
+        <v>5.01880168914795</v>
       </c>
       <c r="H623" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G624" t="n">
-        <v>5.03856086730957</v>
+        <v>5.03856134414673</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16619,7 +16619,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G625" t="n">
-        <v>5.03856086730957</v>
+        <v>5.03856134414673</v>
       </c>
       <c r="H625" t="s">
         <v>8</v>
@@ -16801,7 +16801,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G632" t="n">
-        <v>4.75205421447754</v>
+        <v>4.7520546913147</v>
       </c>
       <c r="H632" t="s">
         <v>8</v>
@@ -16905,7 +16905,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G636" t="n">
-        <v>4.89036798477173</v>
+        <v>4.89036846160889</v>
       </c>
       <c r="H636" t="s">
         <v>8</v>
@@ -17087,7 +17087,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G643" t="n">
-        <v>4.73229551315308</v>
+        <v>4.73229598999023</v>
       </c>
       <c r="H643" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G645" t="n">
-        <v>4.4951868057251</v>
+        <v>4.49518728256226</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G647" t="n">
-        <v>4.34699440002441</v>
+        <v>4.34699392318726</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G648" t="n">
-        <v>4.34699440002441</v>
+        <v>4.34699392318726</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G649" t="n">
-        <v>4.39639139175415</v>
+        <v>4.39639186859131</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17269,7 +17269,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G650" t="n">
-        <v>4.52482604980469</v>
+        <v>4.52482509613037</v>
       </c>
       <c r="H650" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G652" t="n">
-        <v>4.68289804458618</v>
+        <v>4.68289756774902</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17477,7 +17477,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G658" t="n">
-        <v>4.80145263671875</v>
+        <v>4.80145215988159</v>
       </c>
       <c r="H658" t="s">
         <v>8</v>
@@ -17503,7 +17503,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G659" t="n">
-        <v>4.7421760559082</v>
+        <v>4.74217557907104</v>
       </c>
       <c r="H659" t="s">
         <v>8</v>
@@ -17529,7 +17529,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G660" t="n">
-        <v>4.7421760559082</v>
+        <v>4.74217557907104</v>
       </c>
       <c r="H660" t="s">
         <v>8</v>
@@ -17581,7 +17581,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G662" t="n">
-        <v>4.7421760559082</v>
+        <v>4.74217557907104</v>
       </c>
       <c r="H662" t="s">
         <v>8</v>
@@ -17607,7 +17607,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G663" t="n">
-        <v>4.9595251083374</v>
+        <v>4.95952558517456</v>
       </c>
       <c r="H663" t="s">
         <v>8</v>
@@ -17711,7 +17711,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G667" t="n">
-        <v>4.82121181488037</v>
+        <v>4.82121133804321</v>
       </c>
       <c r="H667" t="s">
         <v>8</v>
@@ -17737,7 +17737,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G668" t="n">
-        <v>5.03856086730957</v>
+        <v>5.03856134414673</v>
       </c>
       <c r="H668" t="s">
         <v>8</v>
@@ -17815,7 +17815,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G671" t="n">
-        <v>5.03856086730957</v>
+        <v>5.03856134414673</v>
       </c>
       <c r="H671" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G674" t="n">
-        <v>5.03856086730957</v>
+        <v>5.03856134414673</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G675" t="n">
-        <v>4.97928428649902</v>
+        <v>4.97928380966187</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G677" t="n">
-        <v>4.89036798477173</v>
+        <v>4.89036846160889</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G678" t="n">
-        <v>4.7421760559082</v>
+        <v>4.74217557907104</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18049,7 +18049,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G680" t="n">
-        <v>4.73229551315308</v>
+        <v>4.73229598999023</v>
       </c>
       <c r="H680" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>4.71000003814697</v>
       </c>
       <c r="G681" t="n">
-        <v>4.65325927734375</v>
+        <v>4.65325975418091</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18153,7 +18153,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G684" t="n">
-        <v>4.52482604980469</v>
+        <v>4.52482509613037</v>
       </c>
       <c r="H684" t="s">
         <v>8</v>
@@ -18179,7 +18179,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G685" t="n">
-        <v>4.34699440002441</v>
+        <v>4.34699392318726</v>
       </c>
       <c r="H685" t="s">
         <v>8</v>
@@ -18205,7 +18205,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G686" t="n">
-        <v>4.39639139175415</v>
+        <v>4.39639186859131</v>
       </c>
       <c r="H686" t="s">
         <v>8</v>
@@ -18309,7 +18309,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G690" t="n">
-        <v>4.71253681182861</v>
+        <v>4.71253633499146</v>
       </c>
       <c r="H690" t="s">
         <v>8</v>
@@ -18335,7 +18335,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G691" t="n">
-        <v>5.01880264282227</v>
+        <v>5.01880168914795</v>
       </c>
       <c r="H691" t="s">
         <v>8</v>
@@ -18361,7 +18361,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G692" t="n">
-        <v>5.03856086730957</v>
+        <v>5.03856134414673</v>
       </c>
       <c r="H692" t="s">
         <v>8</v>
@@ -18413,7 +18413,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G694" t="n">
-        <v>5.03856086730957</v>
+        <v>5.03856134414673</v>
       </c>
       <c r="H694" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G695" t="n">
-        <v>4.99904346466064</v>
+        <v>4.99904298782349</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18491,7 +18491,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G697" t="n">
-        <v>5.03856086730957</v>
+        <v>5.03856134414673</v>
       </c>
       <c r="H697" t="s">
         <v>8</v>
@@ -18569,7 +18569,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G700" t="n">
-        <v>5.03856086730957</v>
+        <v>5.03856134414673</v>
       </c>
       <c r="H700" t="s">
         <v>8</v>
@@ -18595,7 +18595,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G701" t="n">
-        <v>5.03856086730957</v>
+        <v>5.03856134414673</v>
       </c>
       <c r="H701" t="s">
         <v>8</v>
@@ -18621,7 +18621,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G702" t="n">
-        <v>5.03856086730957</v>
+        <v>5.03856134414673</v>
       </c>
       <c r="H702" t="s">
         <v>8</v>
@@ -18673,7 +18673,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G704" t="n">
-        <v>4.7421760559082</v>
+        <v>4.74217557907104</v>
       </c>
       <c r="H704" t="s">
         <v>8</v>
@@ -18907,7 +18907,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G713" t="n">
-        <v>4.71253681182861</v>
+        <v>4.71253633499146</v>
       </c>
       <c r="H713" t="s">
         <v>8</v>
@@ -18933,7 +18933,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G714" t="n">
-        <v>4.60386180877686</v>
+        <v>4.6038613319397</v>
       </c>
       <c r="H714" t="s">
         <v>8</v>
@@ -18959,7 +18959,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G715" t="n">
-        <v>4.71253681182861</v>
+        <v>4.71253633499146</v>
       </c>
       <c r="H715" t="s">
         <v>8</v>
@@ -19037,7 +19037,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G718" t="n">
-        <v>4.82121181488037</v>
+        <v>4.82121133804321</v>
       </c>
       <c r="H718" t="s">
         <v>8</v>
@@ -19063,7 +19063,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G719" t="n">
-        <v>4.9595251083374</v>
+        <v>4.95952558517456</v>
       </c>
       <c r="H719" t="s">
         <v>8</v>
@@ -19089,7 +19089,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G720" t="n">
-        <v>5.01880264282227</v>
+        <v>5.01880168914795</v>
       </c>
       <c r="H720" t="s">
         <v>8</v>
@@ -19115,7 +19115,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G721" t="n">
-        <v>5.09783840179443</v>
+        <v>5.09783792495728</v>
       </c>
       <c r="H721" t="s">
         <v>8</v>
@@ -19219,7 +19219,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G725" t="n">
-        <v>5.13735675811768</v>
+        <v>5.13735628128052</v>
       </c>
       <c r="H725" t="s">
         <v>8</v>
@@ -19245,7 +19245,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G726" t="n">
-        <v>5.03856086730957</v>
+        <v>5.03856134414673</v>
       </c>
       <c r="H726" t="s">
         <v>8</v>
@@ -19271,7 +19271,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G727" t="n">
-        <v>4.97928428649902</v>
+        <v>4.97928380966187</v>
       </c>
       <c r="H727" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G730" t="n">
-        <v>4.82121181488037</v>
+        <v>4.82121133804321</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19375,7 +19375,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G731" t="n">
-        <v>4.7421760559082</v>
+        <v>4.74217557907104</v>
       </c>
       <c r="H731" t="s">
         <v>8</v>
@@ -19531,7 +19531,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G737" t="n">
-        <v>4.89036798477173</v>
+        <v>4.89036846160889</v>
       </c>
       <c r="H737" t="s">
         <v>8</v>
@@ -19557,7 +19557,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G738" t="n">
-        <v>4.82121181488037</v>
+        <v>4.82121133804321</v>
       </c>
       <c r="H738" t="s">
         <v>8</v>
@@ -19583,7 +19583,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G739" t="n">
-        <v>4.82121181488037</v>
+        <v>4.82121133804321</v>
       </c>
       <c r="H739" t="s">
         <v>8</v>
@@ -19635,7 +19635,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G741" t="n">
-        <v>4.82121181488037</v>
+        <v>4.82121133804321</v>
       </c>
       <c r="H741" t="s">
         <v>8</v>
@@ -19791,7 +19791,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G747" t="n">
-        <v>4.7421760559082</v>
+        <v>4.74217557907104</v>
       </c>
       <c r="H747" t="s">
         <v>8</v>
@@ -19817,7 +19817,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G748" t="n">
-        <v>4.75205421447754</v>
+        <v>4.7520546913147</v>
       </c>
       <c r="H748" t="s">
         <v>8</v>
@@ -19999,7 +19999,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G755" t="n">
-        <v>4.1889214515686</v>
+        <v>4.18892097473145</v>
       </c>
       <c r="H755" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G756" t="n">
-        <v>4.1889214515686</v>
+        <v>4.18892097473145</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20077,7 +20077,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G758" t="n">
-        <v>4.14940357208252</v>
+        <v>4.14940309524536</v>
       </c>
       <c r="H758" t="s">
         <v>8</v>
@@ -20103,7 +20103,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G759" t="n">
-        <v>4.15928268432617</v>
+        <v>4.15928316116333</v>
       </c>
       <c r="H759" t="s">
         <v>8</v>
@@ -20181,7 +20181,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G762" t="n">
-        <v>4.15928268432617</v>
+        <v>4.15928316116333</v>
       </c>
       <c r="H762" t="s">
         <v>8</v>
@@ -20389,7 +20389,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G770" t="n">
-        <v>3.77398109436035</v>
+        <v>3.77398085594177</v>
       </c>
       <c r="H770" t="s">
         <v>8</v>
@@ -20545,7 +20545,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G776" t="n">
-        <v>3.69494485855103</v>
+        <v>3.6949450969696</v>
       </c>
       <c r="H776" t="s">
         <v>8</v>
@@ -20597,7 +20597,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G778" t="n">
-        <v>3.88265633583069</v>
+        <v>3.88265609741211</v>
       </c>
       <c r="H778" t="s">
         <v>8</v>
@@ -20805,7 +20805,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G786" t="n">
-        <v>3.96169257164001</v>
+        <v>3.96169233322144</v>
       </c>
       <c r="H786" t="s">
         <v>8</v>
@@ -20831,7 +20831,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G787" t="n">
-        <v>4.03084945678711</v>
+        <v>4.03084850311279</v>
       </c>
       <c r="H787" t="s">
         <v>8</v>
@@ -20883,7 +20883,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G789" t="n">
-        <v>3.92217397689819</v>
+        <v>3.92217421531677</v>
       </c>
       <c r="H789" t="s">
         <v>8</v>
@@ -20909,7 +20909,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G790" t="n">
-        <v>3.88265633583069</v>
+        <v>3.88265609741211</v>
       </c>
       <c r="H790" t="s">
         <v>8</v>
@@ -21221,7 +21221,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G802" t="n">
-        <v>3.92235207557678</v>
+        <v>3.92235159873962</v>
       </c>
       <c r="H802" t="s">
         <v>8</v>
@@ -21247,7 +21247,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G803" t="n">
-        <v>3.92235207557678</v>
+        <v>3.92235159873962</v>
       </c>
       <c r="H803" t="s">
         <v>8</v>
@@ -21299,7 +21299,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G805" t="n">
-        <v>3.80349254608154</v>
+        <v>3.80349278450012</v>
       </c>
       <c r="H805" t="s">
         <v>8</v>
@@ -21403,7 +21403,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G809" t="n">
-        <v>3.95206642150879</v>
+        <v>3.95206665992737</v>
       </c>
       <c r="H809" t="s">
         <v>8</v>
@@ -21429,7 +21429,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G810" t="n">
-        <v>3.95206642150879</v>
+        <v>3.95206665992737</v>
       </c>
       <c r="H810" t="s">
         <v>8</v>
@@ -21455,7 +21455,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G811" t="n">
-        <v>3.95206642150879</v>
+        <v>3.95206665992737</v>
       </c>
       <c r="H811" t="s">
         <v>8</v>
@@ -21481,7 +21481,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G812" t="n">
-        <v>3.94216156005859</v>
+        <v>3.94216179847717</v>
       </c>
       <c r="H812" t="s">
         <v>8</v>
@@ -21507,7 +21507,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G813" t="n">
-        <v>3.99168658256531</v>
+        <v>3.99168682098389</v>
       </c>
       <c r="H813" t="s">
         <v>8</v>
@@ -21533,7 +21533,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G814" t="n">
-        <v>3.94216156005859</v>
+        <v>3.94216179847717</v>
       </c>
       <c r="H814" t="s">
         <v>8</v>
@@ -21559,7 +21559,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G815" t="n">
-        <v>3.92235207557678</v>
+        <v>3.92235159873962</v>
       </c>
       <c r="H815" t="s">
         <v>8</v>
@@ -21611,7 +21611,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G817" t="n">
-        <v>3.95206642150879</v>
+        <v>3.95206665992737</v>
       </c>
       <c r="H817" t="s">
         <v>8</v>
@@ -21637,7 +21637,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G818" t="n">
-        <v>3.94216156005859</v>
+        <v>3.94216179847717</v>
       </c>
       <c r="H818" t="s">
         <v>8</v>
@@ -21715,7 +21715,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G821" t="n">
-        <v>4.14026021957397</v>
+        <v>4.14025974273682</v>
       </c>
       <c r="H821" t="s">
         <v>8</v>
@@ -21741,7 +21741,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G822" t="n">
-        <v>4.09073543548584</v>
+        <v>4.090735912323</v>
       </c>
       <c r="H822" t="s">
         <v>8</v>
@@ -21819,7 +21819,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G825" t="n">
-        <v>3.87282729148865</v>
+        <v>3.87282705307007</v>
       </c>
       <c r="H825" t="s">
         <v>8</v>
@@ -21871,7 +21871,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G827" t="n">
-        <v>4.03130626678467</v>
+        <v>4.03130578994751</v>
       </c>
       <c r="H827" t="s">
         <v>8</v>
@@ -21923,7 +21923,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G829" t="n">
-        <v>4.05111646652222</v>
+        <v>4.05111598968506</v>
       </c>
       <c r="H829" t="s">
         <v>8</v>
@@ -22001,7 +22001,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G832" t="n">
-        <v>4.05111646652222</v>
+        <v>4.05111598968506</v>
       </c>
       <c r="H832" t="s">
         <v>8</v>
@@ -22027,7 +22027,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G833" t="n">
-        <v>4.05111646652222</v>
+        <v>4.05111598968506</v>
       </c>
       <c r="H833" t="s">
         <v>8</v>
@@ -22079,7 +22079,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G835" t="n">
-        <v>4.02140140533447</v>
+        <v>4.02140092849731</v>
       </c>
       <c r="H835" t="s">
         <v>8</v>
@@ -22105,7 +22105,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G836" t="n">
-        <v>4.02140140533447</v>
+        <v>4.02140092849731</v>
       </c>
       <c r="H836" t="s">
         <v>8</v>
@@ -22157,7 +22157,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G838" t="n">
-        <v>4.05111646652222</v>
+        <v>4.05111598968506</v>
       </c>
       <c r="H838" t="s">
         <v>8</v>
@@ -22183,7 +22183,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G839" t="n">
-        <v>4.04121112823486</v>
+        <v>4.04121065139771</v>
       </c>
       <c r="H839" t="s">
         <v>8</v>
@@ -22209,7 +22209,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G840" t="n">
-        <v>4.04121112823486</v>
+        <v>4.04121065139771</v>
       </c>
       <c r="H840" t="s">
         <v>8</v>
@@ -22261,7 +22261,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G842" t="n">
-        <v>4.07092571258545</v>
+        <v>4.07092618942261</v>
       </c>
       <c r="H842" t="s">
         <v>8</v>
@@ -22287,7 +22287,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G843" t="n">
-        <v>4.02140140533447</v>
+        <v>4.02140092849731</v>
       </c>
       <c r="H843" t="s">
         <v>8</v>
@@ -22339,7 +22339,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G845" t="n">
-        <v>3.95206642150879</v>
+        <v>3.95206665992737</v>
       </c>
       <c r="H845" t="s">
         <v>8</v>
@@ -22417,7 +22417,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G848" t="n">
-        <v>4.0808310508728</v>
+        <v>4.08083057403564</v>
       </c>
       <c r="H848" t="s">
         <v>8</v>
@@ -22469,7 +22469,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G850" t="n">
-        <v>4.14026021957397</v>
+        <v>4.14025974273682</v>
       </c>
       <c r="H850" t="s">
         <v>8</v>
@@ -22495,7 +22495,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G851" t="n">
-        <v>4.16997480392456</v>
+        <v>4.16997528076172</v>
       </c>
       <c r="H851" t="s">
         <v>8</v>
@@ -22521,7 +22521,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G852" t="n">
-        <v>4.1996898651123</v>
+        <v>4.19968938827515</v>
       </c>
       <c r="H852" t="s">
         <v>8</v>
@@ -22573,7 +22573,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G854" t="n">
-        <v>4.16007041931152</v>
+        <v>4.16006994247437</v>
       </c>
       <c r="H854" t="s">
         <v>8</v>
@@ -22599,7 +22599,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G855" t="n">
-        <v>4.16007041931152</v>
+        <v>4.16006994247437</v>
       </c>
       <c r="H855" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G856" t="n">
-        <v>4.09073543548584</v>
+        <v>4.090735912323</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22651,7 +22651,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G857" t="n">
-        <v>4.07092571258545</v>
+        <v>4.07092618942261</v>
       </c>
       <c r="H857" t="s">
         <v>8</v>
@@ -22677,7 +22677,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G858" t="n">
-        <v>4.11054515838623</v>
+        <v>4.11054563522339</v>
       </c>
       <c r="H858" t="s">
         <v>8</v>
@@ -22729,7 +22729,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G860" t="n">
-        <v>4.07092571258545</v>
+        <v>4.07092618942261</v>
       </c>
       <c r="H860" t="s">
         <v>8</v>
@@ -22781,7 +22781,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G862" t="n">
-        <v>4.0808310508728</v>
+        <v>4.08083057403564</v>
       </c>
       <c r="H862" t="s">
         <v>8</v>
@@ -22807,7 +22807,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G863" t="n">
-        <v>4.11054515838623</v>
+        <v>4.11054563522339</v>
       </c>
       <c r="H863" t="s">
         <v>8</v>
@@ -22833,7 +22833,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G864" t="n">
-        <v>4.0808310508728</v>
+        <v>4.08083057403564</v>
       </c>
       <c r="H864" t="s">
         <v>8</v>
@@ -22859,7 +22859,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G865" t="n">
-        <v>4.0808310508728</v>
+        <v>4.08083057403564</v>
       </c>
       <c r="H865" t="s">
         <v>8</v>
@@ -22911,7 +22911,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G867" t="n">
-        <v>4.05111646652222</v>
+        <v>4.05111598968506</v>
       </c>
       <c r="H867" t="s">
         <v>8</v>
@@ -22989,7 +22989,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G870" t="n">
-        <v>4.02140140533447</v>
+        <v>4.02140092849731</v>
       </c>
       <c r="H870" t="s">
         <v>8</v>
@@ -23041,7 +23041,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G872" t="n">
-        <v>4.02140140533447</v>
+        <v>4.02140092849731</v>
       </c>
       <c r="H872" t="s">
         <v>8</v>
@@ -23145,7 +23145,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G876" t="n">
-        <v>4.0808310508728</v>
+        <v>4.08083057403564</v>
       </c>
       <c r="H876" t="s">
         <v>8</v>
@@ -23171,7 +23171,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G877" t="n">
-        <v>4.16997480392456</v>
+        <v>4.16997528076172</v>
       </c>
       <c r="H877" t="s">
         <v>8</v>
@@ -23223,7 +23223,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G879" t="n">
-        <v>4.29873991012573</v>
+        <v>4.29873943328857</v>
       </c>
       <c r="H879" t="s">
         <v>8</v>
@@ -23587,7 +23587,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G893" t="n">
-        <v>4.2393102645874</v>
+        <v>4.23930978775024</v>
       </c>
       <c r="H893" t="s">
         <v>8</v>
@@ -23769,7 +23769,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G900" t="n">
-        <v>4.25911998748779</v>
+        <v>4.25911951065063</v>
       </c>
       <c r="H900" t="s">
         <v>8</v>
@@ -23795,7 +23795,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G901" t="n">
-        <v>4.25911998748779</v>
+        <v>4.25911951065063</v>
       </c>
       <c r="H901" t="s">
         <v>8</v>
@@ -23821,7 +23821,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G902" t="n">
-        <v>4.1996898651123</v>
+        <v>4.19968938827515</v>
       </c>
       <c r="H902" t="s">
         <v>8</v>
@@ -23873,7 +23873,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G904" t="n">
-        <v>4.07092571258545</v>
+        <v>4.07092618942261</v>
       </c>
       <c r="H904" t="s">
         <v>8</v>
@@ -24003,7 +24003,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G909" t="n">
-        <v>4.11054515838623</v>
+        <v>4.11054563522339</v>
       </c>
       <c r="H909" t="s">
         <v>8</v>
@@ -24055,7 +24055,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G911" t="n">
-        <v>4.04121112823486</v>
+        <v>4.04121065139771</v>
       </c>
       <c r="H911" t="s">
         <v>8</v>
@@ -24081,7 +24081,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G912" t="n">
-        <v>4.04121112823486</v>
+        <v>4.04121065139771</v>
       </c>
       <c r="H912" t="s">
         <v>8</v>
@@ -24133,7 +24133,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G914" t="n">
-        <v>3.94216156005859</v>
+        <v>3.94216179847717</v>
       </c>
       <c r="H914" t="s">
         <v>8</v>
@@ -24159,7 +24159,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G915" t="n">
-        <v>3.78368282318115</v>
+        <v>3.78368258476257</v>
       </c>
       <c r="H915" t="s">
         <v>8</v>
@@ -24315,7 +24315,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G921" t="n">
-        <v>3.70444321632385</v>
+        <v>3.70444345474243</v>
       </c>
       <c r="H921" t="s">
         <v>8</v>
@@ -24341,7 +24341,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G922" t="n">
-        <v>3.69453835487366</v>
+        <v>3.69453859329224</v>
       </c>
       <c r="H922" t="s">
         <v>8</v>
@@ -24419,7 +24419,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G925" t="n">
-        <v>3.64501404762268</v>
+        <v>3.6450138092041</v>
       </c>
       <c r="H925" t="s">
         <v>8</v>
@@ -24471,7 +24471,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G927" t="n">
-        <v>3.56577444076538</v>
+        <v>3.5657742023468</v>
       </c>
       <c r="H927" t="s">
         <v>8</v>
@@ -24497,7 +24497,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G928" t="n">
-        <v>3.56577444076538</v>
+        <v>3.5657742023468</v>
       </c>
       <c r="H928" t="s">
         <v>8</v>
@@ -24575,7 +24575,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G931" t="n">
-        <v>3.56577444076538</v>
+        <v>3.5657742023468</v>
       </c>
       <c r="H931" t="s">
         <v>8</v>
@@ -24627,7 +24627,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G933" t="n">
-        <v>3.56577444076538</v>
+        <v>3.5657742023468</v>
       </c>
       <c r="H933" t="s">
         <v>8</v>
@@ -24653,7 +24653,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G934" t="n">
-        <v>3.56577444076538</v>
+        <v>3.5657742023468</v>
       </c>
       <c r="H934" t="s">
         <v>8</v>
@@ -24731,7 +24731,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G937" t="n">
-        <v>3.70444321632385</v>
+        <v>3.70444345474243</v>
       </c>
       <c r="H937" t="s">
         <v>8</v>
@@ -24757,7 +24757,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G938" t="n">
-        <v>3.70444321632385</v>
+        <v>3.70444345474243</v>
       </c>
       <c r="H938" t="s">
         <v>8</v>
@@ -24809,7 +24809,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G940" t="n">
-        <v>3.77377772331238</v>
+        <v>3.77377796173096</v>
       </c>
       <c r="H940" t="s">
         <v>8</v>
@@ -24965,7 +24965,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G946" t="n">
-        <v>4.04121112823486</v>
+        <v>4.04121065139771</v>
       </c>
       <c r="H946" t="s">
         <v>8</v>
@@ -25017,7 +25017,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G948" t="n">
-        <v>4.10064077377319</v>
+        <v>4.10064029693604</v>
       </c>
       <c r="H948" t="s">
         <v>8</v>
@@ -25069,7 +25069,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G950" t="n">
-        <v>4.10064077377319</v>
+        <v>4.10064029693604</v>
       </c>
       <c r="H950" t="s">
         <v>8</v>
@@ -25121,7 +25121,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G952" t="n">
-        <v>3.89263725280762</v>
+        <v>3.89263701438904</v>
       </c>
       <c r="H952" t="s">
         <v>8</v>
@@ -25147,7 +25147,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G953" t="n">
-        <v>4.03130626678467</v>
+        <v>4.03130578994751</v>
       </c>
       <c r="H953" t="s">
         <v>8</v>
@@ -25199,7 +25199,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G955" t="n">
-        <v>4.03130626678467</v>
+        <v>4.03130578994751</v>
       </c>
       <c r="H955" t="s">
         <v>8</v>
@@ -25225,7 +25225,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G956" t="n">
-        <v>3.99168658256531</v>
+        <v>3.99168682098389</v>
       </c>
       <c r="H956" t="s">
         <v>8</v>
@@ -25251,7 +25251,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G957" t="n">
-        <v>3.94216156005859</v>
+        <v>3.94216179847717</v>
       </c>
       <c r="H957" t="s">
         <v>8</v>
@@ -25303,7 +25303,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G959" t="n">
-        <v>3.94216156005859</v>
+        <v>3.94216179847717</v>
       </c>
       <c r="H959" t="s">
         <v>8</v>
@@ -25329,7 +25329,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G960" t="n">
-        <v>4.02140140533447</v>
+        <v>4.02140092849731</v>
       </c>
       <c r="H960" t="s">
         <v>8</v>
@@ -25355,7 +25355,7 @@
         <v>40.5999984741211</v>
       </c>
       <c r="G961" t="n">
-        <v>40.2140083312988</v>
+        <v>40.2140121459961</v>
       </c>
       <c r="H961" t="s">
         <v>8</v>
@@ -25459,7 +25459,7 @@
         <v>3.97849988937378</v>
       </c>
       <c r="G965" t="n">
-        <v>3.94067573547363</v>
+        <v>3.94067597389221</v>
       </c>
       <c r="H965" t="s">
         <v>8</v>
@@ -25511,7 +25511,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G967" t="n">
-        <v>3.95206642150879</v>
+        <v>3.95206665992737</v>
       </c>
       <c r="H967" t="s">
         <v>8</v>
@@ -25797,7 +25797,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G978" t="n">
-        <v>4.02140140533447</v>
+        <v>4.02140092849731</v>
       </c>
       <c r="H978" t="s">
         <v>8</v>
@@ -25823,7 +25823,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G979" t="n">
-        <v>3.99168658256531</v>
+        <v>3.99168682098389</v>
       </c>
       <c r="H979" t="s">
         <v>8</v>
@@ -25927,7 +25927,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G983" t="n">
-        <v>3.95206642150879</v>
+        <v>3.95206665992737</v>
       </c>
       <c r="H983" t="s">
         <v>8</v>
@@ -25953,7 +25953,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G984" t="n">
-        <v>3.94216156005859</v>
+        <v>3.94216179847717</v>
       </c>
       <c r="H984" t="s">
         <v>8</v>
@@ -26083,7 +26083,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G989" t="n">
-        <v>3.80349254608154</v>
+        <v>3.80349278450012</v>
       </c>
       <c r="H989" t="s">
         <v>8</v>
@@ -26109,7 +26109,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G990" t="n">
-        <v>3.80349254608154</v>
+        <v>3.80349278450012</v>
       </c>
       <c r="H990" t="s">
         <v>8</v>
@@ -26265,7 +26265,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G996" t="n">
-        <v>3.80349254608154</v>
+        <v>3.80349278450012</v>
       </c>
       <c r="H996" t="s">
         <v>8</v>
@@ -26291,7 +26291,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G997" t="n">
-        <v>3.80349254608154</v>
+        <v>3.80349278450012</v>
       </c>
       <c r="H997" t="s">
         <v>8</v>
@@ -26369,7 +26369,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G1000" t="n">
-        <v>3.94216156005859</v>
+        <v>3.94216179847717</v>
       </c>
       <c r="H1000" t="s">
         <v>8</v>
@@ -26473,7 +26473,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1004" t="n">
-        <v>3.78368282318115</v>
+        <v>3.78368258476257</v>
       </c>
       <c r="H1004" t="s">
         <v>8</v>
@@ -26863,7 +26863,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1019" t="n">
-        <v>3.64501404762268</v>
+        <v>3.6450138092041</v>
       </c>
       <c r="H1019" t="s">
         <v>8</v>
@@ -26915,7 +26915,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1021" t="n">
-        <v>3.64501404762268</v>
+        <v>3.6450138092041</v>
       </c>
       <c r="H1021" t="s">
         <v>8</v>
@@ -26993,7 +26993,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1024" t="n">
-        <v>3.61529922485352</v>
+        <v>3.61529898643494</v>
       </c>
       <c r="H1024" t="s">
         <v>8</v>
@@ -27019,7 +27019,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G1025" t="n">
-        <v>3.58558416366577</v>
+        <v>3.58558392524719</v>
       </c>
       <c r="H1025" t="s">
         <v>8</v>
@@ -27071,7 +27071,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1027" t="n">
-        <v>3.61529922485352</v>
+        <v>3.61529898643494</v>
       </c>
       <c r="H1027" t="s">
         <v>8</v>
@@ -27097,7 +27097,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1028" t="n">
-        <v>3.61529922485352</v>
+        <v>3.61529898643494</v>
       </c>
       <c r="H1028" t="s">
         <v>8</v>
@@ -27123,7 +27123,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1029" t="n">
-        <v>3.61529922485352</v>
+        <v>3.61529898643494</v>
       </c>
       <c r="H1029" t="s">
         <v>8</v>
@@ -27279,7 +27279,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1035" t="n">
-        <v>3.56577444076538</v>
+        <v>3.5657742023468</v>
       </c>
       <c r="H1035" t="s">
         <v>8</v>
@@ -27331,7 +27331,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G1037" t="n">
-        <v>3.52615451812744</v>
+        <v>3.52615475654602</v>
       </c>
       <c r="H1037" t="s">
         <v>8</v>
@@ -27565,7 +27565,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G1046" t="n">
-        <v>3.52615451812744</v>
+        <v>3.52615475654602</v>
       </c>
       <c r="H1046" t="s">
         <v>8</v>
@@ -27617,7 +27617,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1048" t="n">
-        <v>3.41720056533813</v>
+        <v>3.41720032691956</v>
       </c>
       <c r="H1048" t="s">
         <v>8</v>
@@ -27695,7 +27695,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G1051" t="n">
-        <v>3.45682001113892</v>
+        <v>3.4568202495575</v>
       </c>
       <c r="H1051" t="s">
         <v>8</v>
@@ -27773,7 +27773,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1054" t="n">
-        <v>3.56577444076538</v>
+        <v>3.5657742023468</v>
       </c>
       <c r="H1054" t="s">
         <v>8</v>
@@ -27799,7 +27799,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1055" t="n">
-        <v>3.56577444076538</v>
+        <v>3.5657742023468</v>
       </c>
       <c r="H1055" t="s">
         <v>8</v>
@@ -27929,7 +27929,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1060" t="n">
-        <v>3.56577444076538</v>
+        <v>3.5657742023468</v>
       </c>
       <c r="H1060" t="s">
         <v>8</v>
@@ -28007,7 +28007,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1063" t="n">
-        <v>3.80349254608154</v>
+        <v>3.80349278450012</v>
       </c>
       <c r="H1063" t="s">
         <v>8</v>
@@ -28033,7 +28033,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G1064" t="n">
-        <v>3.89263725280762</v>
+        <v>3.89263701438904</v>
       </c>
       <c r="H1064" t="s">
         <v>8</v>
@@ -28137,7 +28137,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1068" t="n">
-        <v>3.80349254608154</v>
+        <v>3.80349278450012</v>
       </c>
       <c r="H1068" t="s">
         <v>8</v>
@@ -28189,7 +28189,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1070" t="n">
-        <v>3.80349254608154</v>
+        <v>3.80349278450012</v>
       </c>
       <c r="H1070" t="s">
         <v>8</v>
@@ -28215,7 +28215,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1071" t="n">
-        <v>3.80349254608154</v>
+        <v>3.80349278450012</v>
       </c>
       <c r="H1071" t="s">
         <v>8</v>
@@ -28423,7 +28423,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1079" t="n">
-        <v>3.78368282318115</v>
+        <v>3.78368258476257</v>
       </c>
       <c r="H1079" t="s">
         <v>8</v>
@@ -43610,6 +43610,32 @@
         <v>3.29999995231628</v>
       </c>
       <c r="H1663" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1664">
+      <c r="A1664" s="1" t="n">
+        <v>46295.2916666667</v>
+      </c>
+      <c r="B1664" t="n">
+        <v>11119</v>
+      </c>
+      <c r="C1664" t="n">
+        <v>3.28999996185303</v>
+      </c>
+      <c r="D1664" t="n">
+        <v>3.23000001907349</v>
+      </c>
+      <c r="E1664" t="n">
+        <v>3.28999996185303</v>
+      </c>
+      <c r="F1664" t="n">
+        <v>3.23000001907349</v>
+      </c>
+      <c r="G1664" t="n">
+        <v>3.23000001907349</v>
+      </c>
+      <c r="H1664" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/UD.MI.xlsx
+++ b/data/UD.MI.xlsx
@@ -38706,8 +38706,31 @@
       <c r="E1667" t="n">
         <v>3.09999990463257</v>
       </c>
-      <c r="F1667"/>
+      <c r="F1667" t="n">
+        <v>3.125</v>
+      </c>
       <c r="G1667" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1668">
+      <c r="A1668" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B1668" t="n">
+        <v>29359</v>
+      </c>
+      <c r="C1668" t="n">
+        <v>3.23499989509583</v>
+      </c>
+      <c r="D1668" t="n">
+        <v>3.15499997138977</v>
+      </c>
+      <c r="E1668" t="n">
+        <v>3.19000005722046</v>
+      </c>
+      <c r="F1668"/>
+      <c r="G1668" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/UD.MI.xlsx
+++ b/data/UD.MI.xlsx
@@ -38729,8 +38729,31 @@
       <c r="E1668" t="n">
         <v>3.19000005722046</v>
       </c>
-      <c r="F1668"/>
+      <c r="F1668" t="n">
+        <v>3.17499995231628</v>
+      </c>
       <c r="G1668" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1669">
+      <c r="A1669" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B1669" t="n">
+        <v>37831</v>
+      </c>
+      <c r="C1669" t="n">
+        <v>3.22499990463257</v>
+      </c>
+      <c r="D1669" t="n">
+        <v>3.08500003814697</v>
+      </c>
+      <c r="E1669" t="n">
+        <v>3.11999988555908</v>
+      </c>
+      <c r="F1669"/>
+      <c r="G1669" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/UD.MI.xlsx
+++ b/data/UD.MI.xlsx
@@ -38752,8 +38752,31 @@
       <c r="E1669" t="n">
         <v>3.11999988555908</v>
       </c>
-      <c r="F1669"/>
+      <c r="F1669" t="n">
+        <v>3.13000011444092</v>
+      </c>
       <c r="G1669" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1670">
+      <c r="A1670" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B1670" t="n">
+        <v>48991</v>
+      </c>
+      <c r="C1670" t="n">
+        <v>3.20000004768372</v>
+      </c>
+      <c r="D1670" t="n">
+        <v>3.08500003814697</v>
+      </c>
+      <c r="E1670" t="n">
+        <v>3.08999991416931</v>
+      </c>
+      <c r="F1670"/>
+      <c r="G1670" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/UD.MI.xlsx
+++ b/data/UD.MI.xlsx
@@ -38775,8 +38775,31 @@
       <c r="E1670" t="n">
         <v>3.08999991416931</v>
       </c>
-      <c r="F1670"/>
+      <c r="F1670" t="n">
+        <v>3.09999990463257</v>
+      </c>
       <c r="G1670" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1671">
+      <c r="A1671" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B1671" t="n">
+        <v>22871</v>
+      </c>
+      <c r="C1671" t="n">
+        <v>3.1949999332428</v>
+      </c>
+      <c r="D1671" t="n">
+        <v>3.10999989509583</v>
+      </c>
+      <c r="E1671" t="n">
+        <v>3.13499999046326</v>
+      </c>
+      <c r="F1671"/>
+      <c r="G1671" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/UD.MI.xlsx
+++ b/data/UD.MI.xlsx
@@ -38805,6 +38805,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1672">
+      <c r="A1672" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B1672" t="n">
+        <v>28889</v>
+      </c>
+      <c r="C1672" t="n">
+        <v>3.23000001907349</v>
+      </c>
+      <c r="D1672" t="n">
+        <v>3.17000007629395</v>
+      </c>
+      <c r="E1672" t="n">
+        <v>3.20000004768372</v>
+      </c>
+      <c r="F1672" t="n">
+        <v>3.1800000667572</v>
+      </c>
+      <c r="G1672" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/UD.MI.xlsx
+++ b/data/UD.MI.xlsx
@@ -447,7 +447,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G3" t="n">
-        <v>1.43941915035248</v>
+        <v>1.43941903114319</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>1.56500005722046</v>
       </c>
       <c r="G6" t="n">
-        <v>1.5429390668869</v>
+        <v>1.54293894767761</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G8" t="n">
-        <v>1.53800940513611</v>
+        <v>1.53800928592682</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G9" t="n">
-        <v>1.55772757530212</v>
+        <v>1.55772745609283</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G10" t="n">
-        <v>1.53800940513611</v>
+        <v>1.53800928592682</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G13" t="n">
-        <v>1.55772757530212</v>
+        <v>1.55772745609283</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G17" t="n">
-        <v>1.66617691516876</v>
+        <v>1.66617703437805</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G18" t="n">
-        <v>1.67603576183319</v>
+        <v>1.67603588104248</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G19" t="n">
-        <v>1.67603576183319</v>
+        <v>1.67603588104248</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>1.67499995231628</v>
       </c>
       <c r="G20" t="n">
-        <v>1.65138828754425</v>
+        <v>1.65138816833496</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G22" t="n">
-        <v>1.62181127071381</v>
+        <v>1.62181115150452</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G23" t="n">
-        <v>1.59716367721558</v>
+        <v>1.59716355800629</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G25" t="n">
-        <v>1.58730471134186</v>
+        <v>1.58730459213257</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>1.59500002861023</v>
       </c>
       <c r="G28" t="n">
-        <v>1.57251620292664</v>
+        <v>1.57251608371735</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G31" t="n">
-        <v>1.63659977912903</v>
+        <v>1.63659965991974</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G32" t="n">
-        <v>1.59716367721558</v>
+        <v>1.59716355800629</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G33" t="n">
-        <v>1.61688160896301</v>
+        <v>1.6168817281723</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G37" t="n">
-        <v>1.70561301708221</v>
+        <v>1.70561289787292</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G38" t="n">
-        <v>1.70561301708221</v>
+        <v>1.70561289787292</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G39" t="n">
-        <v>1.67110657691956</v>
+        <v>1.67110633850098</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G45" t="n">
-        <v>1.66617691516876</v>
+        <v>1.66617703437805</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G46" t="n">
-        <v>1.67603576183319</v>
+        <v>1.67603588104248</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G50" t="n">
-        <v>1.74997866153717</v>
+        <v>1.74997854232788</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>1.75</v>
       </c>
       <c r="G51" t="n">
-        <v>1.72533106803894</v>
+        <v>1.72533094882965</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G57" t="n">
-        <v>1.67603576183319</v>
+        <v>1.67603588104248</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>1.67499995231628</v>
       </c>
       <c r="G62" t="n">
-        <v>1.65138828754425</v>
+        <v>1.65138816833496</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>1.67499995231628</v>
       </c>
       <c r="G64" t="n">
-        <v>1.65138828754425</v>
+        <v>1.65138816833496</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>1.67499995231628</v>
       </c>
       <c r="G65" t="n">
-        <v>1.65138828754425</v>
+        <v>1.65138816833496</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G66" t="n">
-        <v>1.67603576183319</v>
+        <v>1.67603588104248</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G67" t="n">
-        <v>1.66617691516876</v>
+        <v>1.66617703437805</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>1.65499997138977</v>
       </c>
       <c r="G73" t="n">
-        <v>1.63167011737823</v>
+        <v>1.63167023658752</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>1.67499995231628</v>
       </c>
       <c r="G75" t="n">
-        <v>1.65138828754425</v>
+        <v>1.65138816833496</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G76" t="n">
-        <v>1.67110657691956</v>
+        <v>1.67110633850098</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G79" t="n">
-        <v>1.67603576183319</v>
+        <v>1.67603588104248</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G80" t="n">
-        <v>1.67603576183319</v>
+        <v>1.67603588104248</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G81" t="n">
-        <v>1.67603576183319</v>
+        <v>1.67603588104248</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G84" t="n">
-        <v>1.63659977912903</v>
+        <v>1.63659965991974</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>1.59500002861023</v>
       </c>
       <c r="G90" t="n">
-        <v>1.57251620292664</v>
+        <v>1.57251608371735</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>1.59500002861023</v>
       </c>
       <c r="G91" t="n">
-        <v>1.57251620292664</v>
+        <v>1.57251608371735</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>1.59500002861023</v>
       </c>
       <c r="G93" t="n">
-        <v>1.57251620292664</v>
+        <v>1.57251608371735</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>1.59500002861023</v>
       </c>
       <c r="G94" t="n">
-        <v>1.57251620292664</v>
+        <v>1.57251608371735</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G95" t="n">
-        <v>1.58730471134186</v>
+        <v>1.58730459213257</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G96" t="n">
-        <v>1.62181127071381</v>
+        <v>1.62181115150452</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G97" t="n">
-        <v>1.58730471134186</v>
+        <v>1.58730459213257</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G98" t="n">
-        <v>1.58730471134186</v>
+        <v>1.58730459213257</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G103" t="n">
-        <v>1.63659977912903</v>
+        <v>1.63659965991974</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G104" t="n">
-        <v>1.63659977912903</v>
+        <v>1.63659965991974</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>1.63499999046326</v>
       </c>
       <c r="G105" t="n">
-        <v>1.6119521856308</v>
+        <v>1.61195206642151</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G109" t="n">
-        <v>1.66617691516876</v>
+        <v>1.66617703437805</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G110" t="n">
-        <v>1.67603576183319</v>
+        <v>1.67603588104248</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G111" t="n">
-        <v>1.67603576183319</v>
+        <v>1.67603588104248</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G112" t="n">
-        <v>1.67603576183319</v>
+        <v>1.67603588104248</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G113" t="n">
-        <v>1.67603576183319</v>
+        <v>1.67603588104248</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G114" t="n">
-        <v>1.67603576183319</v>
+        <v>1.67603588104248</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G115" t="n">
-        <v>1.67603576183319</v>
+        <v>1.67603588104248</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G120" t="n">
-        <v>1.89786410331726</v>
+        <v>1.89786398410797</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G124" t="n">
-        <v>1.85349857807159</v>
+        <v>1.85349833965302</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G126" t="n">
-        <v>1.83378040790558</v>
+        <v>1.83378052711487</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G127" t="n">
-        <v>1.82392144203186</v>
+        <v>1.82392132282257</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G128" t="n">
-        <v>1.82392144203186</v>
+        <v>1.82392132282257</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G129" t="n">
-        <v>1.82392144203186</v>
+        <v>1.82392132282257</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G131" t="n">
-        <v>1.83378040790558</v>
+        <v>1.83378052711487</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G132" t="n">
-        <v>1.78448522090912</v>
+        <v>1.78448534011841</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G133" t="n">
-        <v>1.85349857807159</v>
+        <v>1.85349833965302</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G134" t="n">
-        <v>1.85349857807159</v>
+        <v>1.85349833965302</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G135" t="n">
-        <v>1.85349857807159</v>
+        <v>1.85349833965302</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G137" t="n">
-        <v>1.88307547569275</v>
+        <v>1.88307559490204</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G138" t="n">
-        <v>1.88307547569275</v>
+        <v>1.88307559490204</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G141" t="n">
-        <v>1.82392144203186</v>
+        <v>1.82392132282257</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G142" t="n">
-        <v>1.82392144203186</v>
+        <v>1.82392132282257</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G152" t="n">
-        <v>1.7696967124939</v>
+        <v>1.76969659328461</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G155" t="n">
-        <v>1.82392144203186</v>
+        <v>1.82392132282257</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G156" t="n">
-        <v>1.82392144203186</v>
+        <v>1.82392132282257</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G158" t="n">
-        <v>1.83378040790558</v>
+        <v>1.83378052711487</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G168" t="n">
-        <v>1.74997866153717</v>
+        <v>1.74997854232788</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G172" t="n">
-        <v>1.81406235694885</v>
+        <v>1.81406247615814</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G173" t="n">
-        <v>1.82885098457336</v>
+        <v>1.82885086536407</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G174" t="n">
-        <v>1.82885098457336</v>
+        <v>1.82885086536407</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G178" t="n">
-        <v>1.87814617156982</v>
+        <v>1.87814605236053</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G179" t="n">
-        <v>1.88307547569275</v>
+        <v>1.88307559490204</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G181" t="n">
-        <v>1.90279376506805</v>
+        <v>1.90279364585876</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G182" t="n">
-        <v>1.91265273094177</v>
+        <v>1.91265296936035</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G183" t="n">
-        <v>2.03096103668213</v>
+        <v>2.03096127510071</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G184" t="n">
-        <v>2.01124310493469</v>
+        <v>2.01124286651611</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G185" t="n">
-        <v>2.03096103668213</v>
+        <v>2.03096127510071</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>1.99500000476837</v>
       </c>
       <c r="G186" t="n">
-        <v>1.96687734127045</v>
+        <v>1.96687746047974</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G187" t="n">
-        <v>1.95208895206451</v>
+        <v>1.95208883285522</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G188" t="n">
-        <v>2.01124310493469</v>
+        <v>2.01124286651611</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G189" t="n">
-        <v>2.01124310493469</v>
+        <v>2.01124286651611</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G194" t="n">
-        <v>1.92251181602478</v>
+        <v>1.92251169681549</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G197" t="n">
-        <v>1.91265273094177</v>
+        <v>1.91265296936035</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G198" t="n">
-        <v>1.91265273094177</v>
+        <v>1.91265296936035</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G200" t="n">
-        <v>1.92251181602478</v>
+        <v>1.92251169681549</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>1.95500004291534</v>
       </c>
       <c r="G201" t="n">
-        <v>1.92744135856628</v>
+        <v>1.92744123935699</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G202" t="n">
-        <v>1.91265273094177</v>
+        <v>1.91265296936035</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G204" t="n">
-        <v>1.92251181602478</v>
+        <v>1.92251169681549</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>1.95500004291534</v>
       </c>
       <c r="G206" t="n">
-        <v>1.92744135856628</v>
+        <v>1.92744123935699</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>1.95500004291534</v>
       </c>
       <c r="G207" t="n">
-        <v>1.92744135856628</v>
+        <v>1.92744123935699</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G208" t="n">
-        <v>1.95208895206451</v>
+        <v>1.95208883285522</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>1.9650000333786</v>
       </c>
       <c r="G209" t="n">
-        <v>1.93730020523071</v>
+        <v>1.93730044364929</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G212" t="n">
-        <v>1.94222974777222</v>
+        <v>1.94222986698151</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G213" t="n">
-        <v>1.92251181602478</v>
+        <v>1.92251169681549</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G214" t="n">
-        <v>1.92251181602478</v>
+        <v>1.92251169681549</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G216" t="n">
-        <v>1.91265273094177</v>
+        <v>1.91265296936035</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G217" t="n">
-        <v>1.89786410331726</v>
+        <v>1.89786398410797</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G220" t="n">
-        <v>1.89786410331726</v>
+        <v>1.89786398410797</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G221" t="n">
-        <v>1.92251181602478</v>
+        <v>1.92251169681549</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G222" t="n">
-        <v>1.92251181602478</v>
+        <v>1.92251169681549</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G223" t="n">
-        <v>1.92251181602478</v>
+        <v>1.92251169681549</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G224" t="n">
-        <v>1.92251181602478</v>
+        <v>1.92251169681549</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G225" t="n">
-        <v>1.94222974777222</v>
+        <v>1.94222986698151</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G226" t="n">
-        <v>1.99152517318726</v>
+        <v>1.99152493476868</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G227" t="n">
-        <v>1.98166608810425</v>
+        <v>1.98166584968567</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G230" t="n">
-        <v>2.02110195159912</v>
+        <v>2.0211021900177</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G232" t="n">
-        <v>2.267578125</v>
+        <v>2.26757788658142</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>2.25</v>
       </c>
       <c r="G233" t="n">
-        <v>2.21828293800354</v>
+        <v>2.21828269958496</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G236" t="n">
-        <v>2.19856476783752</v>
+        <v>2.19856452941895</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G237" t="n">
-        <v>2.1887059211731</v>
+        <v>2.18870568275452</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G238" t="n">
-        <v>2.23800110816956</v>
+        <v>2.23800086975098</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>2.25</v>
       </c>
       <c r="G239" t="n">
-        <v>2.21828293800354</v>
+        <v>2.21828269958496</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G240" t="n">
-        <v>2.20842385292053</v>
+        <v>2.20842361450195</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G243" t="n">
-        <v>2.267578125</v>
+        <v>2.26757788658142</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G246" t="n">
-        <v>2.28729581832886</v>
+        <v>2.28729605674744</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G247" t="n">
-        <v>2.28729581832886</v>
+        <v>2.28729605674744</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G256" t="n">
-        <v>2.55348992347717</v>
+        <v>2.55349016189575</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G257" t="n">
-        <v>2.55348992347717</v>
+        <v>2.55349016189575</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G259" t="n">
-        <v>2.5929262638092</v>
+        <v>2.59292650222778</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G260" t="n">
-        <v>2.74081158638</v>
+        <v>2.74081134796143</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G262" t="n">
-        <v>2.78024792671204</v>
+        <v>2.78024744987488</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G263" t="n">
-        <v>2.97742867469788</v>
+        <v>2.97742819786072</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G266" t="n">
-        <v>2.87883830070496</v>
+        <v>2.87883806228638</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G267" t="n">
-        <v>2.8394021987915</v>
+        <v>2.83940172195435</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G270" t="n">
-        <v>2.77038884162903</v>
+        <v>2.77038860321045</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G271" t="n">
-        <v>2.84926104545593</v>
+        <v>2.84926128387451</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G274" t="n">
-        <v>3.26334023475647</v>
+        <v>3.26334047317505</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G275" t="n">
-        <v>3.26334023475647</v>
+        <v>3.26334047317505</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G277" t="n">
-        <v>3.17460942268372</v>
+        <v>3.17460918426514</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G279" t="n">
-        <v>3.3027765750885</v>
+        <v>3.30277633666992</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G283" t="n">
-        <v>3.24362254142761</v>
+        <v>3.24362230300903</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G284" t="n">
-        <v>3.19432735443115</v>
+        <v>3.19432711601257</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G285" t="n">
-        <v>3.35207152366638</v>
+        <v>3.35207176208496</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G286" t="n">
-        <v>3.49995732307434</v>
+        <v>3.49995708465576</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G288" t="n">
-        <v>3.52953433990479</v>
+        <v>3.52953457832336</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G292" t="n">
-        <v>3.64784288406372</v>
+        <v>3.64784264564514</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G293" t="n">
-        <v>3.64784288406372</v>
+        <v>3.64784264564514</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G294" t="n">
-        <v>3.53939342498779</v>
+        <v>3.53939318656921</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G297" t="n">
-        <v>3.55911135673523</v>
+        <v>3.55911111831665</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G299" t="n">
-        <v>3.49995732307434</v>
+        <v>3.49995708465576</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G302" t="n">
-        <v>3.49995732307434</v>
+        <v>3.49995708465576</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G304" t="n">
-        <v>3.52953433990479</v>
+        <v>3.52953457832336</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G305" t="n">
-        <v>3.52953433990479</v>
+        <v>3.52953457832336</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G307" t="n">
-        <v>3.97319078445435</v>
+        <v>3.97319102287292</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G316" t="n">
-        <v>4.08164072036743</v>
+        <v>4.08163976669312</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G318" t="n">
-        <v>4.17037105560303</v>
+        <v>4.17037153244019</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G321" t="n">
-        <v>4.13093566894531</v>
+        <v>4.13093519210815</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G325" t="n">
-        <v>4.06192207336426</v>
+        <v>4.06192255020142</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G329" t="n">
-        <v>4.02248620986938</v>
+        <v>4.02248573303223</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G330" t="n">
-        <v>3.98305034637451</v>
+        <v>3.98304986953735</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G331" t="n">
-        <v>4.15065383911133</v>
+        <v>4.15065336227417</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G332" t="n">
-        <v>4.15065383911133</v>
+        <v>4.15065336227417</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G335" t="n">
-        <v>4.17037105560303</v>
+        <v>4.17037153244019</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G342" t="n">
-        <v>4.06192207336426</v>
+        <v>4.06192255020142</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G345" t="n">
-        <v>4.08164072036743</v>
+        <v>4.08163976669312</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G346" t="n">
-        <v>4.04220390319824</v>
+        <v>4.0422043800354</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G347" t="n">
-        <v>4.02248620986938</v>
+        <v>4.02248573303223</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G348" t="n">
-        <v>4.02248620986938</v>
+        <v>4.02248573303223</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G349" t="n">
-        <v>4.21966743469238</v>
+        <v>4.21966648101807</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G352" t="n">
-        <v>4.19994926452637</v>
+        <v>4.19994878768921</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G353" t="n">
-        <v>4.13093566894531</v>
+        <v>4.13093519210815</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>4.25</v>
       </c>
       <c r="G354" t="n">
-        <v>4.1900897026062</v>
+        <v>4.19009017944336</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G355" t="n">
-        <v>4.08164072036743</v>
+        <v>4.08163976669312</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G358" t="n">
-        <v>4.07178115844727</v>
+        <v>4.07178163528442</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G359" t="n">
-        <v>4.21966743469238</v>
+        <v>4.21966648101807</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G360" t="n">
-        <v>4.15065383911133</v>
+        <v>4.15065336227417</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G361" t="n">
-        <v>4.08164072036743</v>
+        <v>4.08163976669312</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G363" t="n">
-        <v>4.1210765838623</v>
+        <v>4.12107563018799</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G364" t="n">
-        <v>4.1210765838623</v>
+        <v>4.12107563018799</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G365" t="n">
-        <v>4.1210765838623</v>
+        <v>4.12107563018799</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G369" t="n">
-        <v>4.08164072036743</v>
+        <v>4.08163976669312</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G371" t="n">
-        <v>4.01262760162354</v>
+        <v>4.01262712478638</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G372" t="n">
-        <v>4.08164072036743</v>
+        <v>4.08163976669312</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G376" t="n">
-        <v>4.19994926452637</v>
+        <v>4.19994878768921</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G378" t="n">
-        <v>4.27882194519043</v>
+        <v>4.27882146835327</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G379" t="n">
-        <v>4.21966743469238</v>
+        <v>4.21966648101807</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G380" t="n">
-        <v>4.21966743469238</v>
+        <v>4.21966648101807</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G385" t="n">
-        <v>4.36755180358887</v>
+        <v>4.36755228042603</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G387" t="n">
-        <v>4.36755180358887</v>
+        <v>4.36755228042603</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G388" t="n">
-        <v>4.36755180358887</v>
+        <v>4.36755228042603</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>4.25</v>
       </c>
       <c r="G392" t="n">
-        <v>4.1900897026062</v>
+        <v>4.19009017944336</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G394" t="n">
-        <v>4.4069881439209</v>
+        <v>4.40698862075806</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>4.25</v>
       </c>
       <c r="G397" t="n">
-        <v>4.1900897026062</v>
+        <v>4.19009017944336</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G398" t="n">
-        <v>4.04220390319824</v>
+        <v>4.0422043800354</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G399" t="n">
-        <v>4.04220390319824</v>
+        <v>4.0422043800354</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G400" t="n">
-        <v>4.04220390319824</v>
+        <v>4.0422043800354</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G402" t="n">
-        <v>4.19994926452637</v>
+        <v>4.19994878768921</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G406" t="n">
-        <v>4.39712953567505</v>
+        <v>4.39712905883789</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G409" t="n">
-        <v>4.49571990966797</v>
+        <v>4.49571943283081</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G411" t="n">
-        <v>5.04782629013062</v>
+        <v>5.0478253364563</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G413" t="n">
-        <v>5.24500703811646</v>
+        <v>5.2450065612793</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G418" t="n">
-        <v>4.98867177963257</v>
+        <v>4.98867130279541</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G420" t="n">
-        <v>5.00838947296143</v>
+        <v>5.00838994979858</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G426" t="n">
-        <v>5.08726167678833</v>
+        <v>5.08726119995117</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G428" t="n">
-        <v>5.00838947296143</v>
+        <v>5.00838994979858</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G429" t="n">
-        <v>5.12669801712036</v>
+        <v>5.1266975402832</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G431" t="n">
-        <v>4.98867177963257</v>
+        <v>4.98867130279541</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G433" t="n">
-        <v>4.88022184371948</v>
+        <v>4.88022232055664</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G443" t="n">
-        <v>5.04782629013062</v>
+        <v>5.0478253364563</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G446" t="n">
-        <v>4.9492359161377</v>
+        <v>4.94923496246338</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G447" t="n">
-        <v>4.85064554214478</v>
+        <v>4.85064506530762</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G450" t="n">
-        <v>4.83092737197876</v>
+        <v>4.8309268951416</v>
       </c>
       <c r="H450" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G451" t="n">
-        <v>4.83092737197876</v>
+        <v>4.8309268951416</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G454" t="n">
-        <v>4.84078550338745</v>
+        <v>4.84078598022461</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G455" t="n">
-        <v>4.85064554214478</v>
+        <v>4.85064506530762</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G457" t="n">
-        <v>5.04782629013062</v>
+        <v>5.0478253364563</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G459" t="n">
-        <v>5.26472473144531</v>
+        <v>5.264723777771</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G460" t="n">
-        <v>5.34359693527222</v>
+        <v>5.34359645843506</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G464" t="n">
-        <v>5.04782629013062</v>
+        <v>5.0478253364563</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G465" t="n">
-        <v>5.16613435745239</v>
+        <v>5.16613340377808</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G466" t="n">
-        <v>5.12669801712036</v>
+        <v>5.1266975402832</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G467" t="n">
-        <v>5.12669801712036</v>
+        <v>5.1266975402832</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G468" t="n">
-        <v>5.16613435745239</v>
+        <v>5.16613340377808</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G470" t="n">
-        <v>5.08726167678833</v>
+        <v>5.08726119995117</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G473" t="n">
-        <v>5.20557022094727</v>
+        <v>5.20557069778442</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G474" t="n">
-        <v>4.98867177963257</v>
+        <v>4.98867130279541</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G477" t="n">
-        <v>5.00838947296143</v>
+        <v>5.00838994979858</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G482" t="n">
-        <v>5.10697984695435</v>
+        <v>5.1069803237915</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G483" t="n">
-        <v>5.12669801712036</v>
+        <v>5.1266975402832</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G484" t="n">
-        <v>5.12669801712036</v>
+        <v>5.1266975402832</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G485" t="n">
-        <v>5.12669801712036</v>
+        <v>5.1266975402832</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G486" t="n">
-        <v>5.04782629013062</v>
+        <v>5.0478253364563</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G487" t="n">
-        <v>5.16613435745239</v>
+        <v>5.16613340377808</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13083,7 +13083,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G489" t="n">
-        <v>4.98867177963257</v>
+        <v>4.98867130279541</v>
       </c>
       <c r="H489" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G490" t="n">
-        <v>5.12669801712036</v>
+        <v>5.1266975402832</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G491" t="n">
-        <v>4.98867177963257</v>
+        <v>4.98867130279541</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G493" t="n">
-        <v>5.16613435745239</v>
+        <v>5.16613340377808</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G494" t="n">
-        <v>5.10697984695435</v>
+        <v>5.1069803237915</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G495" t="n">
-        <v>5.08726167678833</v>
+        <v>5.08726119995117</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G496" t="n">
-        <v>4.9492359161377</v>
+        <v>4.94923496246338</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G497" t="n">
-        <v>4.87036323547363</v>
+        <v>4.87036275863647</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G500" t="n">
-        <v>5.04782629013062</v>
+        <v>5.0478253364563</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G502" t="n">
-        <v>5.08726167678833</v>
+        <v>5.08726119995117</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G504" t="n">
-        <v>4.83092737197876</v>
+        <v>4.8309268951416</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G505" t="n">
-        <v>4.98867177963257</v>
+        <v>4.98867130279541</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G506" t="n">
-        <v>5.12669801712036</v>
+        <v>5.1266975402832</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G507" t="n">
-        <v>5.10697984695435</v>
+        <v>5.1069803237915</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G510" t="n">
-        <v>4.98867177963257</v>
+        <v>4.98867130279541</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G512" t="n">
-        <v>5.08726167678833</v>
+        <v>5.08726119995117</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G513" t="n">
-        <v>5.00838947296143</v>
+        <v>5.00838994979858</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G515" t="n">
-        <v>4.9492359161377</v>
+        <v>4.94923496246338</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13785,7 +13785,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G516" t="n">
-        <v>5.00838947296143</v>
+        <v>5.00838994979858</v>
       </c>
       <c r="H516" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G518" t="n">
-        <v>5.00838947296143</v>
+        <v>5.00838994979858</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13915,7 +13915,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G521" t="n">
-        <v>5.20557022094727</v>
+        <v>5.20557069778442</v>
       </c>
       <c r="H521" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G522" t="n">
-        <v>5.04782629013062</v>
+        <v>5.0478253364563</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G524" t="n">
-        <v>4.9492359161377</v>
+        <v>4.94923496246338</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G525" t="n">
-        <v>4.88022184371948</v>
+        <v>4.88022232055664</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G526" t="n">
-        <v>5.00838947296143</v>
+        <v>5.00838994979858</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G527" t="n">
-        <v>4.85064554214478</v>
+        <v>4.85064506530762</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G528" t="n">
-        <v>4.80134963989258</v>
+        <v>4.80135011672974</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G529" t="n">
-        <v>4.77177286148071</v>
+        <v>4.77177333831787</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14175,7 +14175,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G531" t="n">
-        <v>4.80134963989258</v>
+        <v>4.80135011672974</v>
       </c>
       <c r="H531" t="s">
         <v>8</v>
@@ -14201,7 +14201,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G532" t="n">
-        <v>4.77177286148071</v>
+        <v>4.77177333831787</v>
       </c>
       <c r="H532" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G536" t="n">
-        <v>4.71261930465698</v>
+        <v>4.71261882781982</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G538" t="n">
-        <v>4.89993953704834</v>
+        <v>4.8999400138855</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G539" t="n">
-        <v>4.85064554214478</v>
+        <v>4.85064506530762</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G540" t="n">
-        <v>4.83092737197876</v>
+        <v>4.8309268951416</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G541" t="n">
-        <v>4.9492359161377</v>
+        <v>4.94923496246338</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G542" t="n">
-        <v>4.86050415039062</v>
+        <v>4.86050367355347</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G543" t="n">
-        <v>4.84078550338745</v>
+        <v>4.84078598022461</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G544" t="n">
-        <v>4.84078550338745</v>
+        <v>4.84078598022461</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G545" t="n">
-        <v>4.83092737197876</v>
+        <v>4.8309268951416</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G546" t="n">
-        <v>4.75205516815186</v>
+        <v>4.7520546913147</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G547" t="n">
-        <v>4.62362146377563</v>
+        <v>4.62362051010132</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G549" t="n">
-        <v>4.5939826965332</v>
+        <v>4.59398221969604</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G550" t="n">
-        <v>4.64337968826294</v>
+        <v>4.6433801651001</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G552" t="n">
-        <v>4.78169393539429</v>
+        <v>4.78169345855713</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G553" t="n">
-        <v>4.78169393539429</v>
+        <v>4.78169345855713</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G554" t="n">
-        <v>4.78169393539429</v>
+        <v>4.78169345855713</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>4.75</v>
       </c>
       <c r="G558" t="n">
-        <v>4.69277763366699</v>
+        <v>4.69277811050415</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>4.75</v>
       </c>
       <c r="G559" t="n">
-        <v>4.69277763366699</v>
+        <v>4.69277811050415</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G561" t="n">
-        <v>4.79157304763794</v>
+        <v>4.79157257080078</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G563" t="n">
-        <v>4.84097099304199</v>
+        <v>4.84097051620483</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G564" t="n">
-        <v>4.84097099304199</v>
+        <v>4.84097051620483</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G565" t="n">
-        <v>4.84097099304199</v>
+        <v>4.84097051620483</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G566" t="n">
-        <v>4.84097099304199</v>
+        <v>4.84097051620483</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G571" t="n">
-        <v>4.84097099304199</v>
+        <v>4.84097051620483</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G572" t="n">
-        <v>4.55446481704712</v>
+        <v>4.55446434020996</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G573" t="n">
-        <v>4.43590974807739</v>
+        <v>4.43590927124023</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15293,7 +15293,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G574" t="n">
-        <v>4.42603063583374</v>
+        <v>4.42603015899658</v>
       </c>
       <c r="H574" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>4.5</v>
       </c>
       <c r="G576" t="n">
-        <v>4.4457893371582</v>
+        <v>4.44578886032104</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15371,7 +15371,7 @@
         <v>4.5</v>
       </c>
       <c r="G577" t="n">
-        <v>4.4457893371582</v>
+        <v>4.44578886032104</v>
       </c>
       <c r="H577" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>4.5</v>
       </c>
       <c r="G578" t="n">
-        <v>4.4457893371582</v>
+        <v>4.44578886032104</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15423,7 +15423,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G579" t="n">
-        <v>4.27783727645874</v>
+        <v>4.2778377532959</v>
       </c>
       <c r="H579" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G583" t="n">
-        <v>4.64337968826294</v>
+        <v>4.6433801651001</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G584" t="n">
-        <v>4.78169393539429</v>
+        <v>4.78169345855713</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G585" t="n">
-        <v>4.5939826965332</v>
+        <v>4.59398221969604</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G587" t="n">
-        <v>4.43590974807739</v>
+        <v>4.43590927124023</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G589" t="n">
-        <v>4.43590974807739</v>
+        <v>4.43590927124023</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G590" t="n">
-        <v>4.38651275634766</v>
+        <v>4.38651180267334</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G591" t="n">
-        <v>4.34699392318726</v>
+        <v>4.34699440002441</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G592" t="n">
-        <v>4.34699392318726</v>
+        <v>4.34699440002441</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15787,7 +15787,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G593" t="n">
-        <v>4.34699392318726</v>
+        <v>4.34699440002441</v>
       </c>
       <c r="H593" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>4.5</v>
       </c>
       <c r="G596" t="n">
-        <v>4.4457893371582</v>
+        <v>4.44578886032104</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G599" t="n">
-        <v>4.43590974807739</v>
+        <v>4.43590927124023</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G602" t="n">
-        <v>4.5939826965332</v>
+        <v>4.59398221969604</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G603" t="n">
-        <v>4.64337968826294</v>
+        <v>4.6433801651001</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G604" t="n">
-        <v>4.84097099304199</v>
+        <v>4.84097051620483</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G607" t="n">
-        <v>4.70265769958496</v>
+        <v>4.7026572227478</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G608" t="n">
-        <v>4.70265769958496</v>
+        <v>4.7026572227478</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G610" t="n">
-        <v>4.84097099304199</v>
+        <v>4.84097051620483</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G611" t="n">
-        <v>4.72241687774658</v>
+        <v>4.72241592407227</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>4.75</v>
       </c>
       <c r="G612" t="n">
-        <v>4.69277763366699</v>
+        <v>4.69277811050415</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16307,7 +16307,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G613" t="n">
-        <v>4.78169393539429</v>
+        <v>4.78169345855713</v>
       </c>
       <c r="H613" t="s">
         <v>8</v>
@@ -16333,7 +16333,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G614" t="n">
-        <v>4.84097099304199</v>
+        <v>4.84097051620483</v>
       </c>
       <c r="H614" t="s">
         <v>8</v>
@@ -16359,7 +16359,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G615" t="n">
-        <v>4.88048887252808</v>
+        <v>4.88048839569092</v>
       </c>
       <c r="H615" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G616" t="n">
-        <v>4.97928380966187</v>
+        <v>4.97928428649902</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16411,7 +16411,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G617" t="n">
-        <v>4.97928380966187</v>
+        <v>4.97928428649902</v>
       </c>
       <c r="H617" t="s">
         <v>8</v>
@@ -16463,7 +16463,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G619" t="n">
-        <v>4.97928380966187</v>
+        <v>4.97928428649902</v>
       </c>
       <c r="H619" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G620" t="n">
-        <v>4.99904346466064</v>
+        <v>4.99904298782349</v>
       </c>
       <c r="H620" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G628" t="n">
-        <v>4.87060880661011</v>
+        <v>4.87060928344727</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -16801,7 +16801,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G632" t="n">
-        <v>4.7520546913147</v>
+        <v>4.75205421447754</v>
       </c>
       <c r="H632" t="s">
         <v>8</v>
@@ -16931,7 +16931,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G637" t="n">
-        <v>4.88048887252808</v>
+        <v>4.88048839569092</v>
       </c>
       <c r="H637" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G638" t="n">
-        <v>4.88048887252808</v>
+        <v>4.88048839569092</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G639" t="n">
-        <v>4.87060880661011</v>
+        <v>4.87060928344727</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G640" t="n">
-        <v>4.79157304763794</v>
+        <v>4.79157257080078</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17035,7 +17035,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G641" t="n">
-        <v>4.79157304763794</v>
+        <v>4.79157257080078</v>
       </c>
       <c r="H641" t="s">
         <v>8</v>
@@ -17061,7 +17061,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G642" t="n">
-        <v>4.79157304763794</v>
+        <v>4.79157257080078</v>
       </c>
       <c r="H642" t="s">
         <v>8</v>
@@ -17087,7 +17087,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G643" t="n">
-        <v>4.73229598999023</v>
+        <v>4.73229551315308</v>
       </c>
       <c r="H643" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>4.5</v>
       </c>
       <c r="G646" t="n">
-        <v>4.4457893371582</v>
+        <v>4.44578886032104</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G647" t="n">
-        <v>4.34699392318726</v>
+        <v>4.34699440002441</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G648" t="n">
-        <v>4.34699392318726</v>
+        <v>4.34699440002441</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G649" t="n">
-        <v>4.39639186859131</v>
+        <v>4.39639139175415</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G652" t="n">
-        <v>4.68289756774902</v>
+        <v>4.68289804458618</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17347,7 +17347,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G653" t="n">
-        <v>4.79157304763794</v>
+        <v>4.79157257080078</v>
       </c>
       <c r="H653" t="s">
         <v>8</v>
@@ -17399,7 +17399,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G655" t="n">
-        <v>4.84097099304199</v>
+        <v>4.84097051620483</v>
       </c>
       <c r="H655" t="s">
         <v>8</v>
@@ -17425,7 +17425,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G656" t="n">
-        <v>4.72241687774658</v>
+        <v>4.72241592407227</v>
       </c>
       <c r="H656" t="s">
         <v>8</v>
@@ -17451,7 +17451,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G657" t="n">
-        <v>4.72241687774658</v>
+        <v>4.72241592407227</v>
       </c>
       <c r="H657" t="s">
         <v>8</v>
@@ -17555,7 +17555,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G661" t="n">
-        <v>4.88048887252808</v>
+        <v>4.88048839569092</v>
       </c>
       <c r="H661" t="s">
         <v>8</v>
@@ -17607,7 +17607,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G663" t="n">
-        <v>4.95952558517456</v>
+        <v>4.95952463150024</v>
       </c>
       <c r="H663" t="s">
         <v>8</v>
@@ -17763,7 +17763,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G669" t="n">
-        <v>5.11759757995605</v>
+        <v>5.1175971031189</v>
       </c>
       <c r="H669" t="s">
         <v>8</v>
@@ -17789,7 +17789,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G670" t="n">
-        <v>5.11759757995605</v>
+        <v>5.1175971031189</v>
       </c>
       <c r="H670" t="s">
         <v>8</v>
@@ -17841,7 +17841,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G672" t="n">
-        <v>5.11759757995605</v>
+        <v>5.1175971031189</v>
       </c>
       <c r="H672" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G675" t="n">
-        <v>4.97928380966187</v>
+        <v>4.97928428649902</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -18023,7 +18023,7 @@
         <v>4.59000015258789</v>
       </c>
       <c r="G679" t="n">
-        <v>4.53470516204834</v>
+        <v>4.5347056388855</v>
       </c>
       <c r="H679" t="s">
         <v>8</v>
@@ -18049,7 +18049,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G680" t="n">
-        <v>4.73229598999023</v>
+        <v>4.73229551315308</v>
       </c>
       <c r="H680" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>4.71000003814697</v>
       </c>
       <c r="G681" t="n">
-        <v>4.65325975418091</v>
+        <v>4.65325927734375</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18101,7 +18101,7 @@
         <v>4.75</v>
       </c>
       <c r="G682" t="n">
-        <v>4.69277763366699</v>
+        <v>4.69277811050415</v>
       </c>
       <c r="H682" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>4.59000015258789</v>
       </c>
       <c r="G683" t="n">
-        <v>4.53470516204834</v>
+        <v>4.5347056388855</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18179,7 +18179,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G685" t="n">
-        <v>4.34699392318726</v>
+        <v>4.34699440002441</v>
       </c>
       <c r="H685" t="s">
         <v>8</v>
@@ -18205,7 +18205,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G686" t="n">
-        <v>4.39639186859131</v>
+        <v>4.39639139175415</v>
       </c>
       <c r="H686" t="s">
         <v>8</v>
@@ -18231,7 +18231,7 @@
         <v>4.5</v>
       </c>
       <c r="G687" t="n">
-        <v>4.4457893371582</v>
+        <v>4.44578886032104</v>
       </c>
       <c r="H687" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>4.5</v>
       </c>
       <c r="G688" t="n">
-        <v>4.4457893371582</v>
+        <v>4.44578886032104</v>
       </c>
       <c r="H688" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>4.75</v>
       </c>
       <c r="G689" t="n">
-        <v>4.69277763366699</v>
+        <v>4.69277811050415</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18309,7 +18309,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G690" t="n">
-        <v>4.71253633499146</v>
+        <v>4.71253728866577</v>
       </c>
       <c r="H690" t="s">
         <v>8</v>
@@ -18387,7 +18387,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G693" t="n">
-        <v>5.1571159362793</v>
+        <v>5.15711545944214</v>
       </c>
       <c r="H693" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G695" t="n">
-        <v>4.99904346466064</v>
+        <v>4.99904298782349</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G698" t="n">
-        <v>5.11759757995605</v>
+        <v>5.1175971031189</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18543,7 +18543,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G699" t="n">
-        <v>5.11759757995605</v>
+        <v>5.1175971031189</v>
       </c>
       <c r="H699" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G703" t="n">
-        <v>4.87060880661011</v>
+        <v>4.87060928344727</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -18699,7 +18699,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G705" t="n">
-        <v>4.84097099304199</v>
+        <v>4.84097051620483</v>
       </c>
       <c r="H705" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G706" t="n">
-        <v>4.84097099304199</v>
+        <v>4.84097051620483</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G707" t="n">
-        <v>4.85084962844849</v>
+        <v>4.8508505821228</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -18777,7 +18777,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G708" t="n">
-        <v>5.11759757995605</v>
+        <v>5.1175971031189</v>
       </c>
       <c r="H708" t="s">
         <v>8</v>
@@ -18855,7 +18855,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G711" t="n">
-        <v>4.88048887252808</v>
+        <v>4.88048839569092</v>
       </c>
       <c r="H711" t="s">
         <v>8</v>
@@ -18881,7 +18881,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G712" t="n">
-        <v>4.72241687774658</v>
+        <v>4.72241592407227</v>
       </c>
       <c r="H712" t="s">
         <v>8</v>
@@ -18907,7 +18907,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G713" t="n">
-        <v>4.71253633499146</v>
+        <v>4.71253728866577</v>
       </c>
       <c r="H713" t="s">
         <v>8</v>
@@ -18959,7 +18959,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G715" t="n">
-        <v>4.71253633499146</v>
+        <v>4.71253728866577</v>
       </c>
       <c r="H715" t="s">
         <v>8</v>
@@ -18985,7 +18985,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G716" t="n">
-        <v>4.72241687774658</v>
+        <v>4.72241592407227</v>
       </c>
       <c r="H716" t="s">
         <v>8</v>
@@ -19011,7 +19011,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G717" t="n">
-        <v>4.78169393539429</v>
+        <v>4.78169345855713</v>
       </c>
       <c r="H717" t="s">
         <v>8</v>
@@ -19063,7 +19063,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G719" t="n">
-        <v>4.95952558517456</v>
+        <v>4.95952463150024</v>
       </c>
       <c r="H719" t="s">
         <v>8</v>
@@ -19115,7 +19115,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G721" t="n">
-        <v>5.09783840179443</v>
+        <v>5.09783792495728</v>
       </c>
       <c r="H721" t="s">
         <v>8</v>
@@ -19167,7 +19167,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G723" t="n">
-        <v>5.11759757995605</v>
+        <v>5.1175971031189</v>
       </c>
       <c r="H723" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G724" t="n">
-        <v>5.11759757995605</v>
+        <v>5.1175971031189</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19271,7 +19271,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G727" t="n">
-        <v>4.97928380966187</v>
+        <v>4.97928428649902</v>
       </c>
       <c r="H727" t="s">
         <v>8</v>
@@ -19323,7 +19323,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G729" t="n">
-        <v>4.84097099304199</v>
+        <v>4.84097051620483</v>
       </c>
       <c r="H729" t="s">
         <v>8</v>
@@ -19427,7 +19427,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G733" t="n">
-        <v>4.88048887252808</v>
+        <v>4.88048839569092</v>
       </c>
       <c r="H733" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G734" t="n">
-        <v>4.78169393539429</v>
+        <v>4.78169345855713</v>
       </c>
       <c r="H734" t="s">
         <v>8</v>
@@ -19479,7 +19479,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G735" t="n">
-        <v>4.79157304763794</v>
+        <v>4.79157257080078</v>
       </c>
       <c r="H735" t="s">
         <v>8</v>
@@ -19505,7 +19505,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G736" t="n">
-        <v>4.88048887252808</v>
+        <v>4.88048839569092</v>
       </c>
       <c r="H736" t="s">
         <v>8</v>
@@ -19661,7 +19661,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G742" t="n">
-        <v>4.84097099304199</v>
+        <v>4.84097051620483</v>
       </c>
       <c r="H742" t="s">
         <v>8</v>
@@ -19687,7 +19687,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G743" t="n">
-        <v>4.85084962844849</v>
+        <v>4.8508505821228</v>
       </c>
       <c r="H743" t="s">
         <v>8</v>
@@ -19765,7 +19765,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G746" t="n">
-        <v>4.92000722885132</v>
+        <v>4.92000675201416</v>
       </c>
       <c r="H746" t="s">
         <v>8</v>
@@ -19817,7 +19817,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G748" t="n">
-        <v>4.7520546913147</v>
+        <v>4.75205421447754</v>
       </c>
       <c r="H748" t="s">
         <v>8</v>
@@ -19843,7 +19843,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G749" t="n">
-        <v>4.78169393539429</v>
+        <v>4.78169345855713</v>
       </c>
       <c r="H749" t="s">
         <v>8</v>
@@ -19869,7 +19869,7 @@
         <v>4.75</v>
       </c>
       <c r="G750" t="n">
-        <v>4.69277763366699</v>
+        <v>4.69277811050415</v>
       </c>
       <c r="H750" t="s">
         <v>8</v>
@@ -19895,7 +19895,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G751" t="n">
-        <v>4.17904138565063</v>
+        <v>4.17904186248779</v>
       </c>
       <c r="H751" t="s">
         <v>8</v>
@@ -19921,7 +19921,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G752" t="n">
-        <v>4.228440284729</v>
+        <v>4.22843933105469</v>
       </c>
       <c r="H752" t="s">
         <v>8</v>
@@ -19947,7 +19947,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G753" t="n">
-        <v>4.17904138565063</v>
+        <v>4.17904186248779</v>
       </c>
       <c r="H753" t="s">
         <v>8</v>
@@ -19973,7 +19973,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G754" t="n">
-        <v>4.17904138565063</v>
+        <v>4.17904186248779</v>
       </c>
       <c r="H754" t="s">
         <v>8</v>
@@ -20051,7 +20051,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G757" t="n">
-        <v>4.17904138565063</v>
+        <v>4.17904186248779</v>
       </c>
       <c r="H757" t="s">
         <v>8</v>
@@ -20077,7 +20077,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G758" t="n">
-        <v>4.14940309524536</v>
+        <v>4.14940357208252</v>
       </c>
       <c r="H758" t="s">
         <v>8</v>
@@ -20129,7 +20129,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G760" t="n">
-        <v>4.16916275024414</v>
+        <v>4.16916227340698</v>
       </c>
       <c r="H760" t="s">
         <v>8</v>
@@ -20155,7 +20155,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G761" t="n">
-        <v>4.16916275024414</v>
+        <v>4.16916227340698</v>
       </c>
       <c r="H761" t="s">
         <v>8</v>
@@ -20207,7 +20207,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G763" t="n">
-        <v>4.05060815811157</v>
+        <v>4.05060768127441</v>
       </c>
       <c r="H763" t="s">
         <v>8</v>
@@ -20337,7 +20337,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G768" t="n">
-        <v>3.89253544807434</v>
+        <v>3.89253568649292</v>
       </c>
       <c r="H768" t="s">
         <v>8</v>
@@ -20389,7 +20389,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G770" t="n">
-        <v>3.77398085594177</v>
+        <v>3.77398109436035</v>
       </c>
       <c r="H770" t="s">
         <v>8</v>
@@ -20415,7 +20415,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G771" t="n">
-        <v>3.76410174369812</v>
+        <v>3.76410150527954</v>
       </c>
       <c r="H771" t="s">
         <v>8</v>
@@ -20441,7 +20441,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G772" t="n">
-        <v>3.76410174369812</v>
+        <v>3.76410150527954</v>
       </c>
       <c r="H772" t="s">
         <v>8</v>
@@ -20467,7 +20467,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G773" t="n">
-        <v>3.8036196231842</v>
+        <v>3.80361986160278</v>
       </c>
       <c r="H773" t="s">
         <v>8</v>
@@ -20519,7 +20519,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G775" t="n">
-        <v>3.7443425655365</v>
+        <v>3.74434232711792</v>
       </c>
       <c r="H775" t="s">
         <v>8</v>
@@ -20545,7 +20545,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G776" t="n">
-        <v>3.6949450969696</v>
+        <v>3.69494485855103</v>
       </c>
       <c r="H776" t="s">
         <v>8</v>
@@ -20597,7 +20597,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G778" t="n">
-        <v>3.88265609741211</v>
+        <v>3.88265633583069</v>
       </c>
       <c r="H778" t="s">
         <v>8</v>
@@ -20623,7 +20623,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G779" t="n">
-        <v>3.99133133888245</v>
+        <v>3.99133086204529</v>
       </c>
       <c r="H779" t="s">
         <v>8</v>
@@ -20649,7 +20649,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G780" t="n">
-        <v>3.89253544807434</v>
+        <v>3.89253568649292</v>
       </c>
       <c r="H780" t="s">
         <v>8</v>
@@ -20675,7 +20675,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G781" t="n">
-        <v>3.99133133888245</v>
+        <v>3.99133086204529</v>
       </c>
       <c r="H781" t="s">
         <v>8</v>
@@ -20727,7 +20727,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G783" t="n">
-        <v>3.98145127296448</v>
+        <v>3.98145198822021</v>
       </c>
       <c r="H783" t="s">
         <v>8</v>
@@ -20753,7 +20753,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G784" t="n">
-        <v>3.99133133888245</v>
+        <v>3.99133086204529</v>
       </c>
       <c r="H784" t="s">
         <v>8</v>
@@ -20779,7 +20779,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G785" t="n">
-        <v>3.89253544807434</v>
+        <v>3.89253568649292</v>
       </c>
       <c r="H785" t="s">
         <v>8</v>
@@ -20805,7 +20805,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G786" t="n">
-        <v>3.96169257164001</v>
+        <v>3.96169233322144</v>
       </c>
       <c r="H786" t="s">
         <v>8</v>
@@ -20883,7 +20883,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G789" t="n">
-        <v>3.92217421531677</v>
+        <v>3.92217397689819</v>
       </c>
       <c r="H789" t="s">
         <v>8</v>
@@ -20909,7 +20909,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G790" t="n">
-        <v>3.88265609741211</v>
+        <v>3.88265633583069</v>
       </c>
       <c r="H790" t="s">
         <v>8</v>
@@ -21143,7 +21143,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G799" t="n">
-        <v>3.91229462623596</v>
+        <v>3.91229438781738</v>
       </c>
       <c r="H799" t="s">
         <v>8</v>
@@ -21195,7 +21195,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G801" t="n">
-        <v>3.85301756858826</v>
+        <v>3.85301733016968</v>
       </c>
       <c r="H801" t="s">
         <v>8</v>
@@ -21221,7 +21221,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G802" t="n">
-        <v>3.9223518371582</v>
+        <v>3.92235207557678</v>
       </c>
       <c r="H802" t="s">
         <v>8</v>
@@ -21247,7 +21247,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G803" t="n">
-        <v>3.9223518371582</v>
+        <v>3.92235207557678</v>
       </c>
       <c r="H803" t="s">
         <v>8</v>
@@ -21481,7 +21481,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G812" t="n">
-        <v>3.94216179847717</v>
+        <v>3.94216156005859</v>
       </c>
       <c r="H812" t="s">
         <v>8</v>
@@ -21507,7 +21507,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G813" t="n">
-        <v>3.99168634414673</v>
+        <v>3.99168658256531</v>
       </c>
       <c r="H813" t="s">
         <v>8</v>
@@ -21533,7 +21533,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G814" t="n">
-        <v>3.94216179847717</v>
+        <v>3.94216156005859</v>
       </c>
       <c r="H814" t="s">
         <v>8</v>
@@ -21559,7 +21559,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G815" t="n">
-        <v>3.9223518371582</v>
+        <v>3.92235207557678</v>
       </c>
       <c r="H815" t="s">
         <v>8</v>
@@ -21637,7 +21637,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G818" t="n">
-        <v>3.94216179847717</v>
+        <v>3.94216156005859</v>
       </c>
       <c r="H818" t="s">
         <v>8</v>
@@ -21715,7 +21715,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G821" t="n">
-        <v>4.14026021957397</v>
+        <v>4.14025974273682</v>
       </c>
       <c r="H821" t="s">
         <v>8</v>
@@ -21741,7 +21741,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G822" t="n">
-        <v>4.09073543548584</v>
+        <v>4.090735912323</v>
       </c>
       <c r="H822" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G823" t="n">
-        <v>4.06102085113525</v>
+        <v>4.0610203742981</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21793,7 +21793,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G824" t="n">
-        <v>4.00159168243408</v>
+        <v>4.00159120559692</v>
       </c>
       <c r="H824" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G828" t="n">
-        <v>4.06102085113525</v>
+        <v>4.0610203742981</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -21923,7 +21923,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G829" t="n">
-        <v>4.05111598968506</v>
+        <v>4.05111646652222</v>
       </c>
       <c r="H829" t="s">
         <v>8</v>
@@ -21949,7 +21949,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G830" t="n">
-        <v>4.06102085113525</v>
+        <v>4.0610203742981</v>
       </c>
       <c r="H830" t="s">
         <v>8</v>
@@ -21975,7 +21975,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G831" t="n">
-        <v>3.97187685966492</v>
+        <v>3.97187662124634</v>
       </c>
       <c r="H831" t="s">
         <v>8</v>
@@ -22001,7 +22001,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G832" t="n">
-        <v>4.05111598968506</v>
+        <v>4.05111646652222</v>
       </c>
       <c r="H832" t="s">
         <v>8</v>
@@ -22027,7 +22027,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G833" t="n">
-        <v>4.05111598968506</v>
+        <v>4.05111646652222</v>
       </c>
       <c r="H833" t="s">
         <v>8</v>
@@ -22053,7 +22053,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G834" t="n">
-        <v>4.06102085113525</v>
+        <v>4.0610203742981</v>
       </c>
       <c r="H834" t="s">
         <v>8</v>
@@ -22131,7 +22131,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G837" t="n">
-        <v>3.98178148269653</v>
+        <v>3.98178124427795</v>
       </c>
       <c r="H837" t="s">
         <v>8</v>
@@ -22157,7 +22157,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G838" t="n">
-        <v>4.05111598968506</v>
+        <v>4.05111646652222</v>
       </c>
       <c r="H838" t="s">
         <v>8</v>
@@ -22235,7 +22235,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G841" t="n">
-        <v>4.00159168243408</v>
+        <v>4.00159120559692</v>
       </c>
       <c r="H841" t="s">
         <v>8</v>
@@ -22261,7 +22261,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G842" t="n">
-        <v>4.07092618942261</v>
+        <v>4.07092571258545</v>
       </c>
       <c r="H842" t="s">
         <v>8</v>
@@ -22313,7 +22313,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G844" t="n">
-        <v>3.98178148269653</v>
+        <v>3.98178124427795</v>
       </c>
       <c r="H844" t="s">
         <v>8</v>
@@ -22365,7 +22365,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G846" t="n">
-        <v>4.00159168243408</v>
+        <v>4.00159120559692</v>
       </c>
       <c r="H846" t="s">
         <v>8</v>
@@ -22391,7 +22391,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G847" t="n">
-        <v>4.06102085113525</v>
+        <v>4.0610203742981</v>
       </c>
       <c r="H847" t="s">
         <v>8</v>
@@ -22443,7 +22443,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G849" t="n">
-        <v>4.13035583496094</v>
+        <v>4.13035535812378</v>
       </c>
       <c r="H849" t="s">
         <v>8</v>
@@ -22469,7 +22469,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G850" t="n">
-        <v>4.14026021957397</v>
+        <v>4.14025974273682</v>
       </c>
       <c r="H850" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G856" t="n">
-        <v>4.09073543548584</v>
+        <v>4.090735912323</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22651,7 +22651,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G857" t="n">
-        <v>4.07092618942261</v>
+        <v>4.07092571258545</v>
       </c>
       <c r="H857" t="s">
         <v>8</v>
@@ -22677,7 +22677,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G858" t="n">
-        <v>4.11054563522339</v>
+        <v>4.11054515838623</v>
       </c>
       <c r="H858" t="s">
         <v>8</v>
@@ -22729,7 +22729,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G860" t="n">
-        <v>4.07092618942261</v>
+        <v>4.07092571258545</v>
       </c>
       <c r="H860" t="s">
         <v>8</v>
@@ -22807,7 +22807,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G863" t="n">
-        <v>4.11054563522339</v>
+        <v>4.11054515838623</v>
       </c>
       <c r="H863" t="s">
         <v>8</v>
@@ -22911,7 +22911,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G867" t="n">
-        <v>4.05111598968506</v>
+        <v>4.05111646652222</v>
       </c>
       <c r="H867" t="s">
         <v>8</v>
@@ -22937,7 +22937,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G868" t="n">
-        <v>4.13035583496094</v>
+        <v>4.13035535812378</v>
       </c>
       <c r="H868" t="s">
         <v>8</v>
@@ -23119,7 +23119,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G875" t="n">
-        <v>4.06102085113525</v>
+        <v>4.0610203742981</v>
       </c>
       <c r="H875" t="s">
         <v>8</v>
@@ -23197,7 +23197,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G878" t="n">
-        <v>4.24921417236328</v>
+        <v>4.24921464920044</v>
       </c>
       <c r="H878" t="s">
         <v>8</v>
@@ -23223,7 +23223,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G879" t="n">
-        <v>4.29873991012573</v>
+        <v>4.29873943328857</v>
       </c>
       <c r="H879" t="s">
         <v>8</v>
@@ -23275,7 +23275,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G881" t="n">
-        <v>4.24921417236328</v>
+        <v>4.24921464920044</v>
       </c>
       <c r="H881" t="s">
         <v>8</v>
@@ -23327,7 +23327,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G883" t="n">
-        <v>4.33835935592651</v>
+        <v>4.3383584022522</v>
       </c>
       <c r="H883" t="s">
         <v>8</v>
@@ -23379,7 +23379,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G885" t="n">
-        <v>4.33835935592651</v>
+        <v>4.3383584022522</v>
       </c>
       <c r="H885" t="s">
         <v>8</v>
@@ -23587,7 +23587,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G893" t="n">
-        <v>4.2393102645874</v>
+        <v>4.23930978775024</v>
       </c>
       <c r="H893" t="s">
         <v>8</v>
@@ -23691,7 +23691,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G897" t="n">
-        <v>4.22940492630005</v>
+        <v>4.22940444946289</v>
       </c>
       <c r="H897" t="s">
         <v>8</v>
@@ -23847,7 +23847,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G903" t="n">
-        <v>4.24921417236328</v>
+        <v>4.24921464920044</v>
       </c>
       <c r="H903" t="s">
         <v>8</v>
@@ -23873,7 +23873,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G904" t="n">
-        <v>4.07092618942261</v>
+        <v>4.07092571258545</v>
       </c>
       <c r="H904" t="s">
         <v>8</v>
@@ -23899,7 +23899,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G905" t="n">
-        <v>4.24921417236328</v>
+        <v>4.24921464920044</v>
       </c>
       <c r="H905" t="s">
         <v>8</v>
@@ -23925,7 +23925,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G906" t="n">
-        <v>4.24921417236328</v>
+        <v>4.24921464920044</v>
       </c>
       <c r="H906" t="s">
         <v>8</v>
@@ -23951,7 +23951,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G907" t="n">
-        <v>4.17988014221191</v>
+        <v>4.17987966537476</v>
       </c>
       <c r="H907" t="s">
         <v>8</v>
@@ -23977,7 +23977,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G908" t="n">
-        <v>4.00159168243408</v>
+        <v>4.00159120559692</v>
       </c>
       <c r="H908" t="s">
         <v>8</v>
@@ -24003,7 +24003,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G909" t="n">
-        <v>4.11054563522339</v>
+        <v>4.11054515838623</v>
       </c>
       <c r="H909" t="s">
         <v>8</v>
@@ -24029,7 +24029,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G910" t="n">
-        <v>4.06102085113525</v>
+        <v>4.0610203742981</v>
       </c>
       <c r="H910" t="s">
         <v>8</v>
@@ -24107,7 +24107,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G913" t="n">
-        <v>3.84311246871948</v>
+        <v>3.84311270713806</v>
       </c>
       <c r="H913" t="s">
         <v>8</v>
@@ -24133,7 +24133,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G914" t="n">
-        <v>3.94216179847717</v>
+        <v>3.94216156005859</v>
       </c>
       <c r="H914" t="s">
         <v>8</v>
@@ -24159,7 +24159,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G915" t="n">
-        <v>3.78368258476257</v>
+        <v>3.78368282318115</v>
       </c>
       <c r="H915" t="s">
         <v>8</v>
@@ -24341,7 +24341,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G922" t="n">
-        <v>3.69453859329224</v>
+        <v>3.69453835487366</v>
       </c>
       <c r="H922" t="s">
         <v>8</v>
@@ -24419,7 +24419,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G925" t="n">
-        <v>3.6450138092041</v>
+        <v>3.64501404762268</v>
       </c>
       <c r="H925" t="s">
         <v>8</v>
@@ -24445,7 +24445,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G926" t="n">
-        <v>3.62520408630371</v>
+        <v>3.62520432472229</v>
       </c>
       <c r="H926" t="s">
         <v>8</v>
@@ -24471,7 +24471,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G927" t="n">
-        <v>3.5657742023468</v>
+        <v>3.56577444076538</v>
       </c>
       <c r="H927" t="s">
         <v>8</v>
@@ -24497,7 +24497,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G928" t="n">
-        <v>3.5657742023468</v>
+        <v>3.56577444076538</v>
       </c>
       <c r="H928" t="s">
         <v>8</v>
@@ -24549,7 +24549,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G930" t="n">
-        <v>3.66482377052307</v>
+        <v>3.66482400894165</v>
       </c>
       <c r="H930" t="s">
         <v>8</v>
@@ -24575,7 +24575,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G931" t="n">
-        <v>3.5657742023468</v>
+        <v>3.56577444076538</v>
       </c>
       <c r="H931" t="s">
         <v>8</v>
@@ -24627,7 +24627,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G933" t="n">
-        <v>3.5657742023468</v>
+        <v>3.56577444076538</v>
       </c>
       <c r="H933" t="s">
         <v>8</v>
@@ -24653,7 +24653,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G934" t="n">
-        <v>3.5657742023468</v>
+        <v>3.56577444076538</v>
       </c>
       <c r="H934" t="s">
         <v>8</v>
@@ -24809,7 +24809,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G940" t="n">
-        <v>3.77377796173096</v>
+        <v>3.77377772331238</v>
       </c>
       <c r="H940" t="s">
         <v>8</v>
@@ -24835,7 +24835,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G941" t="n">
-        <v>3.88273215293884</v>
+        <v>3.88273239135742</v>
       </c>
       <c r="H941" t="s">
         <v>8</v>
@@ -24939,7 +24939,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G945" t="n">
-        <v>3.90254187583923</v>
+        <v>3.90254211425781</v>
       </c>
       <c r="H945" t="s">
         <v>8</v>
@@ -24991,7 +24991,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G947" t="n">
-        <v>4.06102085113525</v>
+        <v>4.0610203742981</v>
       </c>
       <c r="H947" t="s">
         <v>8</v>
@@ -25017,7 +25017,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G948" t="n">
-        <v>4.10064077377319</v>
+        <v>4.10064029693604</v>
       </c>
       <c r="H948" t="s">
         <v>8</v>
@@ -25043,7 +25043,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G949" t="n">
-        <v>4.17988014221191</v>
+        <v>4.17987966537476</v>
       </c>
       <c r="H949" t="s">
         <v>8</v>
@@ -25069,7 +25069,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G950" t="n">
-        <v>4.10064077377319</v>
+        <v>4.10064029693604</v>
       </c>
       <c r="H950" t="s">
         <v>8</v>
@@ -25095,7 +25095,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G951" t="n">
-        <v>3.98178148269653</v>
+        <v>3.98178124427795</v>
       </c>
       <c r="H951" t="s">
         <v>8</v>
@@ -25121,7 +25121,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G952" t="n">
-        <v>3.89263701438904</v>
+        <v>3.89263725280762</v>
       </c>
       <c r="H952" t="s">
         <v>8</v>
@@ -25173,7 +25173,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G954" t="n">
-        <v>4.06102085113525</v>
+        <v>4.0610203742981</v>
       </c>
       <c r="H954" t="s">
         <v>8</v>
@@ -25225,7 +25225,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G956" t="n">
-        <v>3.99168634414673</v>
+        <v>3.99168658256531</v>
       </c>
       <c r="H956" t="s">
         <v>8</v>
@@ -25251,7 +25251,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G957" t="n">
-        <v>3.94216179847717</v>
+        <v>3.94216156005859</v>
       </c>
       <c r="H957" t="s">
         <v>8</v>
@@ -25277,7 +25277,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G958" t="n">
-        <v>3.97187685966492</v>
+        <v>3.97187662124634</v>
       </c>
       <c r="H958" t="s">
         <v>8</v>
@@ -25303,7 +25303,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G959" t="n">
-        <v>3.94216179847717</v>
+        <v>3.94216156005859</v>
       </c>
       <c r="H959" t="s">
         <v>8</v>
@@ -25355,7 +25355,7 @@
         <v>40.5999984741211</v>
       </c>
       <c r="G961" t="n">
-        <v>40.2140121459961</v>
+        <v>40.2140083312988</v>
       </c>
       <c r="H961" t="s">
         <v>8</v>
@@ -25459,7 +25459,7 @@
         <v>3.97849988937378</v>
       </c>
       <c r="G965" t="n">
-        <v>3.94067573547363</v>
+        <v>3.94067597389221</v>
       </c>
       <c r="H965" t="s">
         <v>8</v>
@@ -25537,7 +25537,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G968" t="n">
-        <v>3.90254187583923</v>
+        <v>3.90254211425781</v>
       </c>
       <c r="H968" t="s">
         <v>8</v>
@@ -25563,7 +25563,7 @@
         <v>3.99699997901917</v>
       </c>
       <c r="G969" t="n">
-        <v>3.95900011062622</v>
+        <v>3.95899987220764</v>
       </c>
       <c r="H969" t="s">
         <v>8</v>
@@ -25589,7 +25589,7 @@
         <v>3.95050001144409</v>
       </c>
       <c r="G970" t="n">
-        <v>3.91294240951538</v>
+        <v>3.9129421710968</v>
       </c>
       <c r="H970" t="s">
         <v>8</v>
@@ -25615,7 +25615,7 @@
         <v>3.99799990653992</v>
       </c>
       <c r="G971" t="n">
-        <v>3.95999050140381</v>
+        <v>3.95999026298523</v>
       </c>
       <c r="H971" t="s">
         <v>8</v>
@@ -25823,7 +25823,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G979" t="n">
-        <v>3.99168634414673</v>
+        <v>3.99168658256531</v>
       </c>
       <c r="H979" t="s">
         <v>8</v>
@@ -25953,7 +25953,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G984" t="n">
-        <v>3.94216179847717</v>
+        <v>3.94216156005859</v>
       </c>
       <c r="H984" t="s">
         <v>8</v>
@@ -26005,7 +26005,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G986" t="n">
-        <v>3.88273215293884</v>
+        <v>3.88273239135742</v>
       </c>
       <c r="H986" t="s">
         <v>8</v>
@@ -26369,7 +26369,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G1000" t="n">
-        <v>3.94216179847717</v>
+        <v>3.94216156005859</v>
       </c>
       <c r="H1000" t="s">
         <v>8</v>
@@ -26421,7 +26421,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G1002" t="n">
-        <v>3.90254187583923</v>
+        <v>3.90254211425781</v>
       </c>
       <c r="H1002" t="s">
         <v>8</v>
@@ -26473,7 +26473,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1004" t="n">
-        <v>3.78368258476257</v>
+        <v>3.78368282318115</v>
       </c>
       <c r="H1004" t="s">
         <v>8</v>
@@ -26733,7 +26733,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1014" t="n">
-        <v>3.66482377052307</v>
+        <v>3.66482400894165</v>
       </c>
       <c r="H1014" t="s">
         <v>8</v>
@@ -26759,7 +26759,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1015" t="n">
-        <v>3.66482377052307</v>
+        <v>3.66482400894165</v>
       </c>
       <c r="H1015" t="s">
         <v>8</v>
@@ -26863,7 +26863,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1019" t="n">
-        <v>3.6450138092041</v>
+        <v>3.64501404762268</v>
       </c>
       <c r="H1019" t="s">
         <v>8</v>
@@ -26915,7 +26915,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1021" t="n">
-        <v>3.6450138092041</v>
+        <v>3.64501404762268</v>
       </c>
       <c r="H1021" t="s">
         <v>8</v>
@@ -26967,7 +26967,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1023" t="n">
-        <v>3.66482377052307</v>
+        <v>3.66482400894165</v>
       </c>
       <c r="H1023" t="s">
         <v>8</v>
@@ -26993,7 +26993,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1024" t="n">
-        <v>3.61529898643494</v>
+        <v>3.61529922485352</v>
       </c>
       <c r="H1024" t="s">
         <v>8</v>
@@ -27071,7 +27071,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1027" t="n">
-        <v>3.61529898643494</v>
+        <v>3.61529922485352</v>
       </c>
       <c r="H1027" t="s">
         <v>8</v>
@@ -27097,7 +27097,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1028" t="n">
-        <v>3.61529898643494</v>
+        <v>3.61529922485352</v>
       </c>
       <c r="H1028" t="s">
         <v>8</v>
@@ -27123,7 +27123,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1029" t="n">
-        <v>3.61529898643494</v>
+        <v>3.61529922485352</v>
       </c>
       <c r="H1029" t="s">
         <v>8</v>
@@ -27279,7 +27279,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1035" t="n">
-        <v>3.5657742023468</v>
+        <v>3.56577444076538</v>
       </c>
       <c r="H1035" t="s">
         <v>8</v>
@@ -27331,7 +27331,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G1037" t="n">
-        <v>3.52615475654602</v>
+        <v>3.52615451812744</v>
       </c>
       <c r="H1037" t="s">
         <v>8</v>
@@ -27357,7 +27357,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1038" t="n">
-        <v>3.48653507232666</v>
+        <v>3.48653483390808</v>
       </c>
       <c r="H1038" t="s">
         <v>8</v>
@@ -27409,7 +27409,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1040" t="n">
-        <v>3.49643993377686</v>
+        <v>3.49643969535828</v>
       </c>
       <c r="H1040" t="s">
         <v>8</v>
@@ -27435,7 +27435,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1041" t="n">
-        <v>3.49643993377686</v>
+        <v>3.49643969535828</v>
       </c>
       <c r="H1041" t="s">
         <v>8</v>
@@ -27539,7 +27539,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1045" t="n">
-        <v>3.50634479522705</v>
+        <v>3.50634455680847</v>
       </c>
       <c r="H1045" t="s">
         <v>8</v>
@@ -27565,7 +27565,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G1046" t="n">
-        <v>3.52615475654602</v>
+        <v>3.52615451812744</v>
       </c>
       <c r="H1046" t="s">
         <v>8</v>
@@ -27617,7 +27617,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1048" t="n">
-        <v>3.41720032691956</v>
+        <v>3.41720056533813</v>
       </c>
       <c r="H1048" t="s">
         <v>8</v>
@@ -27643,7 +27643,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1049" t="n">
-        <v>3.4370105266571</v>
+        <v>3.43701028823853</v>
       </c>
       <c r="H1049" t="s">
         <v>8</v>
@@ -27669,7 +27669,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1050" t="n">
-        <v>3.4370105266571</v>
+        <v>3.43701028823853</v>
       </c>
       <c r="H1050" t="s">
         <v>8</v>
@@ -27695,7 +27695,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G1051" t="n">
-        <v>3.4568202495575</v>
+        <v>3.45682001113892</v>
       </c>
       <c r="H1051" t="s">
         <v>8</v>
@@ -27721,7 +27721,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1052" t="n">
-        <v>3.49643993377686</v>
+        <v>3.49643969535828</v>
       </c>
       <c r="H1052" t="s">
         <v>8</v>
@@ -27773,7 +27773,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1054" t="n">
-        <v>3.5657742023468</v>
+        <v>3.56577444076538</v>
       </c>
       <c r="H1054" t="s">
         <v>8</v>
@@ -27799,7 +27799,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1055" t="n">
-        <v>3.5657742023468</v>
+        <v>3.56577444076538</v>
       </c>
       <c r="H1055" t="s">
         <v>8</v>
@@ -27851,7 +27851,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1057" t="n">
-        <v>3.48653507232666</v>
+        <v>3.48653483390808</v>
       </c>
       <c r="H1057" t="s">
         <v>8</v>
@@ -27929,7 +27929,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1060" t="n">
-        <v>3.5657742023468</v>
+        <v>3.56577444076538</v>
       </c>
       <c r="H1060" t="s">
         <v>8</v>
@@ -27955,7 +27955,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G1061" t="n">
-        <v>3.90254187583923</v>
+        <v>3.90254211425781</v>
       </c>
       <c r="H1061" t="s">
         <v>8</v>
@@ -28033,7 +28033,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G1064" t="n">
-        <v>3.89263701438904</v>
+        <v>3.89263725280762</v>
       </c>
       <c r="H1064" t="s">
         <v>8</v>
@@ -28059,7 +28059,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G1065" t="n">
-        <v>3.98178148269653</v>
+        <v>3.98178124427795</v>
       </c>
       <c r="H1065" t="s">
         <v>8</v>
@@ -28085,7 +28085,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G1066" t="n">
-        <v>4.00159168243408</v>
+        <v>4.00159120559692</v>
       </c>
       <c r="H1066" t="s">
         <v>8</v>
@@ -28423,7 +28423,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1079" t="n">
-        <v>3.78368258476257</v>
+        <v>3.78368282318115</v>
       </c>
       <c r="H1079" t="s">
         <v>8</v>
@@ -28553,7 +28553,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1084" t="n">
-        <v>3.6347188949585</v>
+        <v>3.63471913337708</v>
       </c>
       <c r="H1084" t="s">
         <v>8</v>
@@ -28865,7 +28865,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1096" t="n">
-        <v>3.6347188949585</v>
+        <v>3.63471913337708</v>
       </c>
       <c r="H1096" t="s">
         <v>8</v>
@@ -28943,7 +28943,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1099" t="n">
-        <v>3.6347188949585</v>
+        <v>3.63471913337708</v>
       </c>
       <c r="H1099" t="s">
         <v>8</v>
@@ -29073,7 +29073,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G1104" t="n">
-        <v>3.55527138710022</v>
+        <v>3.55527114868164</v>
       </c>
       <c r="H1104" t="s">
         <v>8</v>
@@ -29099,7 +29099,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1105" t="n">
-        <v>3.67444252967834</v>
+        <v>3.67444276809692</v>
       </c>
       <c r="H1105" t="s">
         <v>8</v>
@@ -29281,7 +29281,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1112" t="n">
-        <v>3.50561690330505</v>
+        <v>3.50561666488647</v>
       </c>
       <c r="H1112" t="s">
         <v>8</v>
@@ -29307,7 +29307,7 @@
         <v>3.5</v>
       </c>
       <c r="G1113" t="n">
-        <v>3.47582411766052</v>
+        <v>3.47582387924194</v>
       </c>
       <c r="H1113" t="s">
         <v>8</v>
@@ -29333,7 +29333,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1114" t="n">
-        <v>3.43610048294067</v>
+        <v>3.43610024452209</v>
       </c>
       <c r="H1114" t="s">
         <v>8</v>
@@ -29359,7 +29359,7 @@
         <v>3.5</v>
       </c>
       <c r="G1115" t="n">
-        <v>3.47582411766052</v>
+        <v>3.47582387924194</v>
       </c>
       <c r="H1115" t="s">
         <v>8</v>
@@ -29385,7 +29385,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1116" t="n">
-        <v>3.43610048294067</v>
+        <v>3.43610024452209</v>
       </c>
       <c r="H1116" t="s">
         <v>8</v>
@@ -29437,7 +29437,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1118" t="n">
-        <v>3.51554775238037</v>
+        <v>3.51554751396179</v>
       </c>
       <c r="H1118" t="s">
         <v>8</v>
@@ -29515,7 +29515,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1121" t="n">
-        <v>3.50561690330505</v>
+        <v>3.50561666488647</v>
       </c>
       <c r="H1121" t="s">
         <v>8</v>
@@ -29541,7 +29541,7 @@
         <v>3.5</v>
       </c>
       <c r="G1122" t="n">
-        <v>3.47582411766052</v>
+        <v>3.47582387924194</v>
       </c>
       <c r="H1122" t="s">
         <v>8</v>
@@ -29567,7 +29567,7 @@
         <v>3.5</v>
       </c>
       <c r="G1123" t="n">
-        <v>3.47582411766052</v>
+        <v>3.47582387924194</v>
       </c>
       <c r="H1123" t="s">
         <v>8</v>
@@ -29619,7 +29619,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1125" t="n">
-        <v>3.41623854637146</v>
+        <v>3.41623830795288</v>
       </c>
       <c r="H1125" t="s">
         <v>8</v>
@@ -29645,7 +29645,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1126" t="n">
-        <v>3.41623854637146</v>
+        <v>3.41623830795288</v>
       </c>
       <c r="H1126" t="s">
         <v>8</v>
@@ -29671,7 +29671,7 @@
         <v>3.5</v>
       </c>
       <c r="G1127" t="n">
-        <v>3.47582411766052</v>
+        <v>3.47582387924194</v>
       </c>
       <c r="H1127" t="s">
         <v>8</v>
@@ -29697,7 +29697,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1128" t="n">
-        <v>3.51554775238037</v>
+        <v>3.51554751396179</v>
       </c>
       <c r="H1128" t="s">
         <v>8</v>
@@ -29801,7 +29801,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1132" t="n">
-        <v>3.41623854637146</v>
+        <v>3.41623830795288</v>
       </c>
       <c r="H1132" t="s">
         <v>8</v>
@@ -29931,7 +29931,7 @@
         <v>3.5</v>
       </c>
       <c r="G1137" t="n">
-        <v>3.47582411766052</v>
+        <v>3.47582387924194</v>
       </c>
       <c r="H1137" t="s">
         <v>8</v>
@@ -30009,7 +30009,7 @@
         <v>3.5</v>
       </c>
       <c r="G1140" t="n">
-        <v>3.47582411766052</v>
+        <v>3.47582387924194</v>
       </c>
       <c r="H1140" t="s">
         <v>8</v>
@@ -30087,7 +30087,7 @@
         <v>3.5</v>
       </c>
       <c r="G1143" t="n">
-        <v>3.47582411766052</v>
+        <v>3.47582387924194</v>
       </c>
       <c r="H1143" t="s">
         <v>8</v>
@@ -30139,7 +30139,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G1145" t="n">
-        <v>3.55527138710022</v>
+        <v>3.55527114868164</v>
       </c>
       <c r="H1145" t="s">
         <v>8</v>
@@ -30165,7 +30165,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1146" t="n">
-        <v>3.67444252967834</v>
+        <v>3.67444276809692</v>
       </c>
       <c r="H1146" t="s">
         <v>8</v>
@@ -30191,7 +30191,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1147" t="n">
-        <v>3.71416616439819</v>
+        <v>3.71416640281677</v>
       </c>
       <c r="H1147" t="s">
         <v>8</v>
@@ -30269,7 +30269,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1150" t="n">
-        <v>3.67444252967834</v>
+        <v>3.67444276809692</v>
       </c>
       <c r="H1150" t="s">
         <v>8</v>
@@ -30321,7 +30321,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1152" t="n">
-        <v>3.67444252967834</v>
+        <v>3.67444276809692</v>
       </c>
       <c r="H1152" t="s">
         <v>8</v>
@@ -30555,7 +30555,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G1161" t="n">
-        <v>3.55527138710022</v>
+        <v>3.55527114868164</v>
       </c>
       <c r="H1161" t="s">
         <v>8</v>
@@ -30763,7 +30763,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G1169" t="n">
-        <v>3.55527138710022</v>
+        <v>3.55527114868164</v>
       </c>
       <c r="H1169" t="s">
         <v>8</v>
@@ -30789,7 +30789,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1170" t="n">
-        <v>3.6347188949585</v>
+        <v>3.63471913337708</v>
       </c>
       <c r="H1170" t="s">
         <v>8</v>
@@ -30815,7 +30815,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1171" t="n">
-        <v>3.6347188949585</v>
+        <v>3.63471913337708</v>
       </c>
       <c r="H1171" t="s">
         <v>8</v>
@@ -31049,7 +31049,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G1180" t="n">
-        <v>3.55527138710022</v>
+        <v>3.55527114868164</v>
       </c>
       <c r="H1180" t="s">
         <v>8</v>
@@ -31101,7 +31101,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1182" t="n">
-        <v>3.50561690330505</v>
+        <v>3.50561666488647</v>
       </c>
       <c r="H1182" t="s">
         <v>8</v>
@@ -31127,7 +31127,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1183" t="n">
-        <v>3.50561690330505</v>
+        <v>3.50561666488647</v>
       </c>
       <c r="H1183" t="s">
         <v>8</v>
@@ -31179,7 +31179,7 @@
         <v>3.5</v>
       </c>
       <c r="G1185" t="n">
-        <v>3.47582411766052</v>
+        <v>3.47582387924194</v>
       </c>
       <c r="H1185" t="s">
         <v>8</v>
@@ -31257,7 +31257,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1188" t="n">
-        <v>3.41623854637146</v>
+        <v>3.41623830795288</v>
       </c>
       <c r="H1188" t="s">
         <v>8</v>
@@ -31413,7 +31413,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G1194" t="n">
-        <v>2.93955421447754</v>
+        <v>2.93955397605896</v>
       </c>
       <c r="H1194" t="s">
         <v>8</v>
@@ -31751,7 +31751,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G1207" t="n">
-        <v>2.76079750061035</v>
+        <v>2.76079726219177</v>
       </c>
       <c r="H1207" t="s">
         <v>8</v>
@@ -31777,7 +31777,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G1208" t="n">
-        <v>2.70121192932129</v>
+        <v>2.70121169090271</v>
       </c>
       <c r="H1208" t="s">
         <v>8</v>
@@ -32245,7 +32245,7 @@
         <v>3</v>
       </c>
       <c r="G1226" t="n">
-        <v>2.97927784919739</v>
+        <v>2.97927761077881</v>
       </c>
       <c r="H1226" t="s">
         <v>8</v>
@@ -32297,7 +32297,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G1228" t="n">
-        <v>2.93955421447754</v>
+        <v>2.93955397605896</v>
       </c>
       <c r="H1228" t="s">
         <v>8</v>
@@ -32349,7 +32349,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G1230" t="n">
-        <v>2.93955421447754</v>
+        <v>2.93955397605896</v>
       </c>
       <c r="H1230" t="s">
         <v>8</v>
@@ -32375,7 +32375,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G1231" t="n">
-        <v>2.93955421447754</v>
+        <v>2.93955397605896</v>
       </c>
       <c r="H1231" t="s">
         <v>8</v>
@@ -32401,7 +32401,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G1232" t="n">
-        <v>2.93955421447754</v>
+        <v>2.93955397605896</v>
       </c>
       <c r="H1232" t="s">
         <v>8</v>
@@ -32479,7 +32479,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1235" t="n">
-        <v>2.87996864318848</v>
+        <v>2.8799684047699</v>
       </c>
       <c r="H1235" t="s">
         <v>8</v>
@@ -32765,7 +32765,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G1246" t="n">
-        <v>2.58204078674316</v>
+        <v>2.58204054832458</v>
       </c>
       <c r="H1246" t="s">
         <v>8</v>
@@ -32999,7 +32999,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G1255" t="n">
-        <v>2.66148829460144</v>
+        <v>2.66148805618286</v>
       </c>
       <c r="H1255" t="s">
         <v>8</v>
@@ -33155,7 +33155,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1261" t="n">
-        <v>2.87996864318848</v>
+        <v>2.8799684047699</v>
       </c>
       <c r="H1261" t="s">
         <v>8</v>
@@ -33207,7 +33207,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G1263" t="n">
-        <v>2.84024477005005</v>
+        <v>2.84024453163147</v>
       </c>
       <c r="H1263" t="s">
         <v>8</v>
@@ -33233,7 +33233,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1264" t="n">
-        <v>2.87996864318848</v>
+        <v>2.8799684047699</v>
       </c>
       <c r="H1264" t="s">
         <v>8</v>
@@ -33389,7 +33389,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G1270" t="n">
-        <v>2.76079750061035</v>
+        <v>2.76079726219177</v>
       </c>
       <c r="H1270" t="s">
         <v>8</v>
@@ -33441,7 +33441,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G1272" t="n">
-        <v>2.76079750061035</v>
+        <v>2.76079726219177</v>
       </c>
       <c r="H1272" t="s">
         <v>8</v>
@@ -33493,7 +33493,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G1274" t="n">
-        <v>2.84024477005005</v>
+        <v>2.84024453163147</v>
       </c>
       <c r="H1274" t="s">
         <v>8</v>
@@ -33675,7 +33675,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G1281" t="n">
-        <v>2.84024477005005</v>
+        <v>2.84024453163147</v>
       </c>
       <c r="H1281" t="s">
         <v>8</v>
@@ -33831,7 +33831,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G1287" t="n">
-        <v>2.66148829460144</v>
+        <v>2.66148805618286</v>
       </c>
       <c r="H1287" t="s">
         <v>8</v>
@@ -33857,7 +33857,7 @@
         <v>2.5</v>
       </c>
       <c r="G1288" t="n">
-        <v>2.48273158073425</v>
+        <v>2.48273134231567</v>
       </c>
       <c r="H1288" t="s">
         <v>8</v>
@@ -34013,7 +34013,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G1294" t="n">
-        <v>2.62176465988159</v>
+        <v>2.62176442146301</v>
       </c>
       <c r="H1294" t="s">
         <v>8</v>
@@ -34247,7 +34247,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1303" t="n">
-        <v>2.87996864318848</v>
+        <v>2.8799684047699</v>
       </c>
       <c r="H1303" t="s">
         <v>8</v>
@@ -34377,7 +34377,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G1308" t="n">
-        <v>2.84024477005005</v>
+        <v>2.84024453163147</v>
       </c>
       <c r="H1308" t="s">
         <v>8</v>
@@ -34429,7 +34429,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G1310" t="n">
-        <v>2.8005211353302</v>
+        <v>2.80052089691162</v>
       </c>
       <c r="H1310" t="s">
         <v>8</v>
@@ -34533,7 +34533,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G1314" t="n">
-        <v>2.93955421447754</v>
+        <v>2.93955397605896</v>
       </c>
       <c r="H1314" t="s">
         <v>8</v>
@@ -43896,6 +43896,32 @@
         <v>3.23499989509583</v>
       </c>
       <c r="H1674" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1675">
+      <c r="A1675" s="1" t="n">
+        <v>46310.2916666667</v>
+      </c>
+      <c r="B1675" t="n">
+        <v>23148</v>
+      </c>
+      <c r="C1675" t="n">
+        <v>3.23000001907349</v>
+      </c>
+      <c r="D1675" t="n">
+        <v>3.13499999046326</v>
+      </c>
+      <c r="E1675" t="n">
+        <v>3.13499999046326</v>
+      </c>
+      <c r="F1675" t="n">
+        <v>3.20000004768372</v>
+      </c>
+      <c r="G1675" t="n">
+        <v>3.20000004768372</v>
+      </c>
+      <c r="H1675" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/UD.MI.xlsx
+++ b/data/UD.MI.xlsx
@@ -421,7 +421,7 @@
         <v>1.5</v>
       </c>
       <c r="G2" t="n">
-        <v>1.47885525226593</v>
+        <v>1.47885513305664</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G4" t="n">
-        <v>1.4591372013092</v>
+        <v>1.45913696289062</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>1.56500005722046</v>
       </c>
       <c r="G6" t="n">
-        <v>1.54293894767761</v>
+        <v>1.54293882846832</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G7" t="n">
-        <v>1.51829135417938</v>
+        <v>1.51829123497009</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G8" t="n">
-        <v>1.53800928592682</v>
+        <v>1.5380095243454</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G9" t="n">
-        <v>1.55772745609283</v>
+        <v>1.55772757530212</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G10" t="n">
-        <v>1.53800928592682</v>
+        <v>1.5380095243454</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G11" t="n">
-        <v>1.56265699863434</v>
+        <v>1.56265687942505</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G13" t="n">
-        <v>1.55772745609283</v>
+        <v>1.55772757530212</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G15" t="n">
-        <v>1.64645874500275</v>
+        <v>1.64645862579346</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G16" t="n">
-        <v>1.65631783008575</v>
+        <v>1.65631771087646</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G17" t="n">
-        <v>1.66617703437805</v>
+        <v>1.66617691516876</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G18" t="n">
-        <v>1.67603588104248</v>
+        <v>1.67603600025177</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G19" t="n">
-        <v>1.67603588104248</v>
+        <v>1.67603600025177</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G21" t="n">
-        <v>1.65631783008575</v>
+        <v>1.65631771087646</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G30" t="n">
-        <v>1.62674069404602</v>
+        <v>1.62674081325531</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G34" t="n">
-        <v>1.62674069404602</v>
+        <v>1.62674081325531</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G35" t="n">
-        <v>1.62674069404602</v>
+        <v>1.62674081325531</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G36" t="n">
-        <v>1.65631783008575</v>
+        <v>1.65631771087646</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G37" t="n">
-        <v>1.70561289787292</v>
+        <v>1.70561301708221</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G38" t="n">
-        <v>1.70561289787292</v>
+        <v>1.70561301708221</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G39" t="n">
-        <v>1.67110633850098</v>
+        <v>1.67110657691956</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G40" t="n">
-        <v>1.6957540512085</v>
+        <v>1.69575393199921</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G44" t="n">
-        <v>1.65631783008575</v>
+        <v>1.65631771087646</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G45" t="n">
-        <v>1.66617703437805</v>
+        <v>1.66617691516876</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G46" t="n">
-        <v>1.67603588104248</v>
+        <v>1.67603600025177</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G47" t="n">
-        <v>1.65631783008575</v>
+        <v>1.65631771087646</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G48" t="n">
-        <v>1.65631783008575</v>
+        <v>1.65631771087646</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>1.75</v>
       </c>
       <c r="G51" t="n">
-        <v>1.72533094882965</v>
+        <v>1.72533106803894</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G52" t="n">
-        <v>1.74011969566345</v>
+        <v>1.74011957645416</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G56" t="n">
-        <v>1.6957540512085</v>
+        <v>1.69575393199921</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G57" t="n">
-        <v>1.67603588104248</v>
+        <v>1.67603600025177</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G60" t="n">
-        <v>1.71547198295593</v>
+        <v>1.71547210216522</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G61" t="n">
-        <v>1.71547198295593</v>
+        <v>1.71547210216522</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>1.68499994277954</v>
       </c>
       <c r="G63" t="n">
-        <v>1.66124725341797</v>
+        <v>1.66124737262726</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G66" t="n">
-        <v>1.67603588104248</v>
+        <v>1.67603600025177</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G67" t="n">
-        <v>1.66617703437805</v>
+        <v>1.66617691516876</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G69" t="n">
-        <v>1.65631783008575</v>
+        <v>1.65631771087646</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G70" t="n">
-        <v>1.62674069404602</v>
+        <v>1.62674081325531</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G71" t="n">
-        <v>1.62674069404602</v>
+        <v>1.62674081325531</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G72" t="n">
-        <v>1.64645874500275</v>
+        <v>1.64645862579346</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>1.65499997138977</v>
       </c>
       <c r="G73" t="n">
-        <v>1.63167023658752</v>
+        <v>1.63167011737823</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G74" t="n">
-        <v>1.64645874500275</v>
+        <v>1.64645862579346</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G76" t="n">
-        <v>1.67110633850098</v>
+        <v>1.67110657691956</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G78" t="n">
-        <v>1.64645874500275</v>
+        <v>1.64645862579346</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G79" t="n">
-        <v>1.67603588104248</v>
+        <v>1.67603600025177</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G80" t="n">
-        <v>1.67603588104248</v>
+        <v>1.67603600025177</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G81" t="n">
-        <v>1.67603588104248</v>
+        <v>1.67603600025177</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G82" t="n">
-        <v>1.65631783008575</v>
+        <v>1.65631771087646</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G83" t="n">
-        <v>1.65631783008575</v>
+        <v>1.65631771087646</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G85" t="n">
-        <v>1.62674069404602</v>
+        <v>1.62674081325531</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G86" t="n">
-        <v>1.62674069404602</v>
+        <v>1.62674081325531</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G99" t="n">
-        <v>1.62674069404602</v>
+        <v>1.62674081325531</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G100" t="n">
-        <v>1.62674069404602</v>
+        <v>1.62674081325531</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G101" t="n">
-        <v>1.65631783008575</v>
+        <v>1.65631771087646</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G102" t="n">
-        <v>1.62674069404602</v>
+        <v>1.62674081325531</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>1.66499996185303</v>
       </c>
       <c r="G106" t="n">
-        <v>1.64152932167053</v>
+        <v>1.64152920246124</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G107" t="n">
-        <v>1.62674069404602</v>
+        <v>1.62674081325531</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G108" t="n">
-        <v>1.62674069404602</v>
+        <v>1.62674081325531</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G109" t="n">
-        <v>1.66617703437805</v>
+        <v>1.66617691516876</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G110" t="n">
-        <v>1.67603588104248</v>
+        <v>1.67603600025177</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G111" t="n">
-        <v>1.67603588104248</v>
+        <v>1.67603600025177</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G112" t="n">
-        <v>1.67603588104248</v>
+        <v>1.67603600025177</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G113" t="n">
-        <v>1.67603588104248</v>
+        <v>1.67603600025177</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G114" t="n">
-        <v>1.67603588104248</v>
+        <v>1.67603600025177</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G115" t="n">
-        <v>1.67603588104248</v>
+        <v>1.67603600025177</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G116" t="n">
-        <v>1.71547198295593</v>
+        <v>1.71547210216522</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G120" t="n">
-        <v>1.89786398410797</v>
+        <v>1.89786410331726</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G121" t="n">
-        <v>1.87321650981903</v>
+        <v>1.87321639060974</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G122" t="n">
-        <v>1.87321650981903</v>
+        <v>1.87321639060974</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>1.875</v>
       </c>
       <c r="G123" t="n">
-        <v>1.84856903553009</v>
+        <v>1.84856915473938</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G124" t="n">
-        <v>1.85349833965302</v>
+        <v>1.85349857807159</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G127" t="n">
-        <v>1.82392132282257</v>
+        <v>1.82392144203186</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G128" t="n">
-        <v>1.82392132282257</v>
+        <v>1.82392144203186</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G129" t="n">
-        <v>1.82392132282257</v>
+        <v>1.82392144203186</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G130" t="n">
-        <v>1.83871006965637</v>
+        <v>1.83870995044708</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G132" t="n">
-        <v>1.78448534011841</v>
+        <v>1.78448510169983</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G133" t="n">
-        <v>1.85349833965302</v>
+        <v>1.85349857807159</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G134" t="n">
-        <v>1.85349833965302</v>
+        <v>1.85349857807159</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G135" t="n">
-        <v>1.85349833965302</v>
+        <v>1.85349857807159</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G136" t="n">
-        <v>1.87321650981903</v>
+        <v>1.87321639060974</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G139" t="n">
-        <v>1.87321650981903</v>
+        <v>1.87321639060974</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G140" t="n">
-        <v>1.87321650981903</v>
+        <v>1.87321639060974</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G141" t="n">
-        <v>1.82392132282257</v>
+        <v>1.82392144203186</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G142" t="n">
-        <v>1.82392132282257</v>
+        <v>1.82392144203186</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G145" t="n">
-        <v>1.79434442520142</v>
+        <v>1.79434430599213</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G146" t="n">
-        <v>1.79434442520142</v>
+        <v>1.79434430599213</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G147" t="n">
-        <v>1.79434442520142</v>
+        <v>1.79434430599213</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G149" t="n">
-        <v>1.79434442520142</v>
+        <v>1.79434430599213</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G150" t="n">
-        <v>1.79434442520142</v>
+        <v>1.79434430599213</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G151" t="n">
-        <v>1.74011969566345</v>
+        <v>1.74011957645416</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>1.81500005722046</v>
       </c>
       <c r="G154" t="n">
-        <v>1.78941488265991</v>
+        <v>1.78941476345062</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G155" t="n">
-        <v>1.82392132282257</v>
+        <v>1.82392144203186</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G156" t="n">
-        <v>1.82392132282257</v>
+        <v>1.82392144203186</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G157" t="n">
-        <v>1.83871006965637</v>
+        <v>1.83870995044708</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>1.81500005722046</v>
       </c>
       <c r="G159" t="n">
-        <v>1.78941488265991</v>
+        <v>1.78941476345062</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G164" t="n">
-        <v>1.71547198295593</v>
+        <v>1.71547210216522</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>1.81500005722046</v>
       </c>
       <c r="G167" t="n">
-        <v>1.78941488265991</v>
+        <v>1.78941476345062</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G170" t="n">
-        <v>1.83871006965637</v>
+        <v>1.83870995044708</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G171" t="n">
-        <v>1.83871006965637</v>
+        <v>1.83870995044708</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G176" t="n">
-        <v>1.83871006965637</v>
+        <v>1.83870995044708</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>1.875</v>
       </c>
       <c r="G177" t="n">
-        <v>1.84856903553009</v>
+        <v>1.84856915473938</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G182" t="n">
-        <v>1.91265296936035</v>
+        <v>1.91265273094177</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G183" t="n">
-        <v>2.03096127510071</v>
+        <v>2.03096103668213</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G184" t="n">
-        <v>2.01124286651611</v>
+        <v>2.01124310493469</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G185" t="n">
-        <v>2.03096127510071</v>
+        <v>2.03096103668213</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>1.99500000476837</v>
       </c>
       <c r="G186" t="n">
-        <v>1.96687746047974</v>
+        <v>1.96687734127045</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G187" t="n">
-        <v>1.95208883285522</v>
+        <v>1.95208895206451</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G188" t="n">
-        <v>2.01124286651611</v>
+        <v>2.01124310493469</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G189" t="n">
-        <v>2.01124286651611</v>
+        <v>2.01124310493469</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G197" t="n">
-        <v>1.91265296936035</v>
+        <v>1.91265273094177</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G198" t="n">
-        <v>1.91265296936035</v>
+        <v>1.91265273094177</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>1.95500004291534</v>
       </c>
       <c r="G201" t="n">
-        <v>1.92744123935699</v>
+        <v>1.92744135856628</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G202" t="n">
-        <v>1.91265296936035</v>
+        <v>1.91265273094177</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G203" t="n">
-        <v>1.90772306919098</v>
+        <v>1.90772318840027</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>1.95500004291534</v>
       </c>
       <c r="G206" t="n">
-        <v>1.92744123935699</v>
+        <v>1.92744135856628</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>1.95500004291534</v>
       </c>
       <c r="G207" t="n">
-        <v>1.92744123935699</v>
+        <v>1.92744135856628</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G208" t="n">
-        <v>1.95208883285522</v>
+        <v>1.95208895206451</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G212" t="n">
-        <v>1.94222986698151</v>
+        <v>1.94222974777222</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G216" t="n">
-        <v>1.91265296936035</v>
+        <v>1.91265273094177</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G217" t="n">
-        <v>1.89786398410797</v>
+        <v>1.89786410331726</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G220" t="n">
-        <v>1.89786398410797</v>
+        <v>1.89786410331726</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G225" t="n">
-        <v>1.94222986698151</v>
+        <v>1.94222974777222</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G230" t="n">
-        <v>2.0211021900177</v>
+        <v>2.02110195159912</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G232" t="n">
-        <v>2.26757788658142</v>
+        <v>2.267578125</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G234" t="n">
-        <v>2.16898775100708</v>
+        <v>2.1689875125885</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G238" t="n">
-        <v>2.23800086975098</v>
+        <v>2.2380006313324</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G242" t="n">
-        <v>2.25771903991699</v>
+        <v>2.25771856307983</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G243" t="n">
-        <v>2.26757788658142</v>
+        <v>2.267578125</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G244" t="n">
-        <v>2.29715514183044</v>
+        <v>2.29715490341187</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G245" t="n">
-        <v>2.29715514183044</v>
+        <v>2.29715490341187</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G251" t="n">
-        <v>2.33659100532532</v>
+        <v>2.3365912437439</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G252" t="n">
-        <v>2.33659100532532</v>
+        <v>2.3365912437439</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>2.5</v>
       </c>
       <c r="G255" t="n">
-        <v>2.46475887298584</v>
+        <v>2.46475839614868</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G256" t="n">
-        <v>2.55349016189575</v>
+        <v>2.55348968505859</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G257" t="n">
-        <v>2.55349016189575</v>
+        <v>2.55348968505859</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G259" t="n">
-        <v>2.59292650222778</v>
+        <v>2.59292602539062</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G260" t="n">
-        <v>2.74081134796143</v>
+        <v>2.74081158638</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G261" t="n">
-        <v>2.66193962097168</v>
+        <v>2.6619393825531</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G262" t="n">
-        <v>2.78024744987488</v>
+        <v>2.78024768829346</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G263" t="n">
-        <v>2.97742819786072</v>
+        <v>2.97742867469788</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>3</v>
       </c>
       <c r="G265" t="n">
-        <v>2.95771050453186</v>
+        <v>2.95771026611328</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G267" t="n">
-        <v>2.83940172195435</v>
+        <v>2.8394021987915</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G271" t="n">
-        <v>2.84926128387451</v>
+        <v>2.84926104545593</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G273" t="n">
-        <v>2.96756935119629</v>
+        <v>2.96756958961487</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G274" t="n">
-        <v>3.26334047317505</v>
+        <v>3.26334023475647</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G275" t="n">
-        <v>3.26334047317505</v>
+        <v>3.26334023475647</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G276" t="n">
-        <v>3.29291749000549</v>
+        <v>3.29291725158691</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G278" t="n">
-        <v>3.18446826934814</v>
+        <v>3.18446803092957</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G280" t="n">
-        <v>3.25348138809204</v>
+        <v>3.25348162651062</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G281" t="n">
-        <v>3.18446826934814</v>
+        <v>3.18446803092957</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G285" t="n">
-        <v>3.35207176208496</v>
+        <v>3.35207200050354</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G288" t="n">
-        <v>3.52953457832336</v>
+        <v>3.52953433990479</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>3.75</v>
       </c>
       <c r="G289" t="n">
-        <v>3.69713807106018</v>
+        <v>3.69713830947876</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>3.75</v>
       </c>
       <c r="G291" t="n">
-        <v>3.69713807106018</v>
+        <v>3.69713830947876</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G292" t="n">
-        <v>3.64784264564514</v>
+        <v>3.64784288406372</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G293" t="n">
-        <v>3.64784264564514</v>
+        <v>3.64784288406372</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G297" t="n">
-        <v>3.55911111831665</v>
+        <v>3.55911135673523</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G300" t="n">
-        <v>3.4802393913269</v>
+        <v>3.48023915290833</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G304" t="n">
-        <v>3.52953457832336</v>
+        <v>3.52953433990479</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G305" t="n">
-        <v>3.52953457832336</v>
+        <v>3.52953433990479</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>3.75</v>
       </c>
       <c r="G306" t="n">
-        <v>3.69713807106018</v>
+        <v>3.69713830947876</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G310" t="n">
-        <v>4.33797550201416</v>
+        <v>4.337975025177</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G311" t="n">
-        <v>4.14079475402832</v>
+        <v>4.14079427719116</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G312" t="n">
-        <v>3.99290943145752</v>
+        <v>3.99290871620178</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G314" t="n">
-        <v>4.05206346511841</v>
+        <v>4.05206394195557</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G315" t="n">
-        <v>4.09149932861328</v>
+        <v>4.09149980545044</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G316" t="n">
-        <v>4.08163976669312</v>
+        <v>4.08164024353027</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G317" t="n">
-        <v>4.14079475402832</v>
+        <v>4.14079427719116</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G318" t="n">
-        <v>4.17037153244019</v>
+        <v>4.17037105560303</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G321" t="n">
-        <v>4.13093519210815</v>
+        <v>4.13093614578247</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G323" t="n">
-        <v>4.18023061752319</v>
+        <v>4.18023014068604</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G324" t="n">
-        <v>4.18023061752319</v>
+        <v>4.18023014068604</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G325" t="n">
-        <v>4.06192255020142</v>
+        <v>4.06192207336426</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G329" t="n">
-        <v>4.02248573303223</v>
+        <v>4.02248620986938</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G335" t="n">
-        <v>4.17037153244019</v>
+        <v>4.17037105560303</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G340" t="n">
-        <v>4.14079475402832</v>
+        <v>4.14079427719116</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G341" t="n">
-        <v>4.14079475402832</v>
+        <v>4.14079427719116</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G342" t="n">
-        <v>4.06192255020142</v>
+        <v>4.06192207336426</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G343" t="n">
-        <v>4.14079475402832</v>
+        <v>4.14079427719116</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G344" t="n">
-        <v>4.11121797561646</v>
+        <v>4.1112174987793</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G345" t="n">
-        <v>4.08163976669312</v>
+        <v>4.08164024353027</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G346" t="n">
-        <v>4.0422043800354</v>
+        <v>4.04220390319824</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G347" t="n">
-        <v>4.02248573303223</v>
+        <v>4.02248620986938</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G348" t="n">
-        <v>4.02248573303223</v>
+        <v>4.02248620986938</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G352" t="n">
-        <v>4.19994878768921</v>
+        <v>4.19994926452637</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G353" t="n">
-        <v>4.13093519210815</v>
+        <v>4.13093614578247</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>4.25</v>
       </c>
       <c r="G354" t="n">
-        <v>4.19009017944336</v>
+        <v>4.1900897026062</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G355" t="n">
-        <v>4.08163976669312</v>
+        <v>4.08164024353027</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G356" t="n">
-        <v>4.14079475402832</v>
+        <v>4.14079427719116</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G357" t="n">
-        <v>4.05206346511841</v>
+        <v>4.05206394195557</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G361" t="n">
-        <v>4.08163976669312</v>
+        <v>4.08164024353027</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G362" t="n">
-        <v>4.09149932861328</v>
+        <v>4.09149980545044</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G363" t="n">
-        <v>4.12107563018799</v>
+        <v>4.1210765838623</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G364" t="n">
-        <v>4.12107563018799</v>
+        <v>4.1210765838623</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G365" t="n">
-        <v>4.12107563018799</v>
+        <v>4.1210765838623</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G366" t="n">
-        <v>4.14079475402832</v>
+        <v>4.14079427719116</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G367" t="n">
-        <v>4.14079475402832</v>
+        <v>4.14079427719116</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G368" t="n">
-        <v>4.14079475402832</v>
+        <v>4.14079427719116</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G369" t="n">
-        <v>4.08163976669312</v>
+        <v>4.08164024353027</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G372" t="n">
-        <v>4.08163976669312</v>
+        <v>4.08164024353027</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G373" t="n">
-        <v>4.14079475402832</v>
+        <v>4.14079427719116</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G374" t="n">
-        <v>4.14079475402832</v>
+        <v>4.14079427719116</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G375" t="n">
-        <v>4.14079475402832</v>
+        <v>4.14079427719116</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G376" t="n">
-        <v>4.19994878768921</v>
+        <v>4.19994926452637</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G377" t="n">
-        <v>4.22952556610107</v>
+        <v>4.22952604293823</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G383" t="n">
-        <v>4.30839776992798</v>
+        <v>4.30839824676514</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G384" t="n">
-        <v>4.33797550201416</v>
+        <v>4.337975025177</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G385" t="n">
-        <v>4.36755228042603</v>
+        <v>4.36755180358887</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G386" t="n">
-        <v>4.30839776992798</v>
+        <v>4.30839824676514</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G387" t="n">
-        <v>4.36755228042603</v>
+        <v>4.36755180358887</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G388" t="n">
-        <v>4.36755228042603</v>
+        <v>4.36755180358887</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G390" t="n">
-        <v>4.33797550201416</v>
+        <v>4.337975025177</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G391" t="n">
-        <v>4.30839776992798</v>
+        <v>4.30839824676514</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>4.25</v>
       </c>
       <c r="G392" t="n">
-        <v>4.19009017944336</v>
+        <v>4.1900897026062</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G393" t="n">
-        <v>4.33797550201416</v>
+        <v>4.337975025177</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G394" t="n">
-        <v>4.40698862075806</v>
+        <v>4.4069881439209</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G396" t="n">
-        <v>4.22952556610107</v>
+        <v>4.22952604293823</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>4.25</v>
       </c>
       <c r="G397" t="n">
-        <v>4.19009017944336</v>
+        <v>4.1900897026062</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G398" t="n">
-        <v>4.0422043800354</v>
+        <v>4.04220390319824</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G399" t="n">
-        <v>4.0422043800354</v>
+        <v>4.04220390319824</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G400" t="n">
-        <v>4.0422043800354</v>
+        <v>4.04220390319824</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G401" t="n">
-        <v>4.18023061752319</v>
+        <v>4.18023014068604</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G402" t="n">
-        <v>4.19994878768921</v>
+        <v>4.19994926452637</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G404" t="n">
-        <v>4.33797550201416</v>
+        <v>4.337975025177</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G405" t="n">
-        <v>4.38727045059204</v>
+        <v>4.38726997375488</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G407" t="n">
-        <v>4.38727045059204</v>
+        <v>4.38726997375488</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G408" t="n">
-        <v>4.38727045059204</v>
+        <v>4.38726997375488</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G413" t="n">
-        <v>5.2450065612793</v>
+        <v>5.24500703811646</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>5</v>
       </c>
       <c r="G414" t="n">
-        <v>4.92951774597168</v>
+        <v>4.92951679229736</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>5</v>
       </c>
       <c r="G415" t="n">
-        <v>4.92951774597168</v>
+        <v>4.92951679229736</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>5</v>
       </c>
       <c r="G417" t="n">
-        <v>4.92951774597168</v>
+        <v>4.92951679229736</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G418" t="n">
-        <v>4.98867130279541</v>
+        <v>4.98867177963257</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G420" t="n">
-        <v>5.00838994979858</v>
+        <v>5.00838899612427</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>5</v>
       </c>
       <c r="G421" t="n">
-        <v>4.92951774597168</v>
+        <v>4.92951679229736</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>5</v>
       </c>
       <c r="G422" t="n">
-        <v>4.92951774597168</v>
+        <v>4.92951679229736</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>5</v>
       </c>
       <c r="G423" t="n">
-        <v>4.92951774597168</v>
+        <v>4.92951679229736</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G424" t="n">
-        <v>4.89008140563965</v>
+        <v>4.89008092880249</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G426" t="n">
-        <v>5.08726119995117</v>
+        <v>5.08726167678833</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G428" t="n">
-        <v>5.00838994979858</v>
+        <v>5.00838899612427</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>5</v>
       </c>
       <c r="G430" t="n">
-        <v>4.92951774597168</v>
+        <v>4.92951679229736</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G431" t="n">
-        <v>4.98867130279541</v>
+        <v>4.98867177963257</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>5</v>
       </c>
       <c r="G432" t="n">
-        <v>4.92951774597168</v>
+        <v>4.92951679229736</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G433" t="n">
-        <v>4.88022232055664</v>
+        <v>4.88022184371948</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>5</v>
       </c>
       <c r="G434" t="n">
-        <v>4.92951774597168</v>
+        <v>4.92951679229736</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G437" t="n">
-        <v>4.90979957580566</v>
+        <v>4.90979909896851</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>5</v>
       </c>
       <c r="G438" t="n">
-        <v>4.92951774597168</v>
+        <v>4.92951679229736</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G439" t="n">
-        <v>4.89008140563965</v>
+        <v>4.89008092880249</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>5</v>
       </c>
       <c r="G440" t="n">
-        <v>4.92951774597168</v>
+        <v>4.92951679229736</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G441" t="n">
-        <v>4.89008140563965</v>
+        <v>4.89008092880249</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G442" t="n">
-        <v>4.90979957580566</v>
+        <v>4.90979909896851</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G446" t="n">
-        <v>4.94923496246338</v>
+        <v>4.94923543930054</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>5</v>
       </c>
       <c r="G448" t="n">
-        <v>4.92951774597168</v>
+        <v>4.92951679229736</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>5</v>
       </c>
       <c r="G449" t="n">
-        <v>4.92951774597168</v>
+        <v>4.92951679229736</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>5</v>
       </c>
       <c r="G452" t="n">
-        <v>4.92951774597168</v>
+        <v>4.92951679229736</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12147,7 +12147,7 @@
         <v>5</v>
       </c>
       <c r="G453" t="n">
-        <v>4.92951774597168</v>
+        <v>4.92951679229736</v>
       </c>
       <c r="H453" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>5</v>
       </c>
       <c r="G456" t="n">
-        <v>4.92951774597168</v>
+        <v>4.92951679229736</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G459" t="n">
-        <v>5.264723777771</v>
+        <v>5.26472473144531</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G460" t="n">
-        <v>5.34359645843506</v>
+        <v>5.34359693527222</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G465" t="n">
-        <v>5.16613340377808</v>
+        <v>5.16613388061523</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G468" t="n">
-        <v>5.16613340377808</v>
+        <v>5.16613388061523</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G470" t="n">
-        <v>5.08726119995117</v>
+        <v>5.08726167678833</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G473" t="n">
-        <v>5.20557069778442</v>
+        <v>5.20557022094727</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G474" t="n">
-        <v>4.98867130279541</v>
+        <v>4.98867177963257</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G475" t="n">
-        <v>5.14641618728638</v>
+        <v>5.14641571044922</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G477" t="n">
-        <v>5.00838994979858</v>
+        <v>5.00838899612427</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G480" t="n">
-        <v>5.14641618728638</v>
+        <v>5.14641571044922</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G481" t="n">
-        <v>5.14641618728638</v>
+        <v>5.14641571044922</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G482" t="n">
-        <v>5.1069803237915</v>
+        <v>5.10697937011719</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G487" t="n">
-        <v>5.16613340377808</v>
+        <v>5.16613388061523</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13083,7 +13083,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G489" t="n">
-        <v>4.98867130279541</v>
+        <v>4.98867177963257</v>
       </c>
       <c r="H489" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G491" t="n">
-        <v>4.98867130279541</v>
+        <v>4.98867177963257</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G493" t="n">
-        <v>5.16613340377808</v>
+        <v>5.16613388061523</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G494" t="n">
-        <v>5.1069803237915</v>
+        <v>5.10697937011719</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G495" t="n">
-        <v>5.08726119995117</v>
+        <v>5.08726167678833</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G496" t="n">
-        <v>4.94923496246338</v>
+        <v>4.94923543930054</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G497" t="n">
-        <v>4.87036275863647</v>
+        <v>4.87036323547363</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G502" t="n">
-        <v>5.08726119995117</v>
+        <v>5.08726167678833</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G505" t="n">
-        <v>4.98867130279541</v>
+        <v>4.98867177963257</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G507" t="n">
-        <v>5.1069803237915</v>
+        <v>5.10697937011719</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13577,7 +13577,7 @@
         <v>5</v>
       </c>
       <c r="G508" t="n">
-        <v>4.92951774597168</v>
+        <v>4.92951679229736</v>
       </c>
       <c r="H508" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G510" t="n">
-        <v>4.98867130279541</v>
+        <v>4.98867177963257</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G512" t="n">
-        <v>5.08726119995117</v>
+        <v>5.08726167678833</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G513" t="n">
-        <v>5.00838994979858</v>
+        <v>5.00838899612427</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G515" t="n">
-        <v>4.94923496246338</v>
+        <v>4.94923543930054</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13785,7 +13785,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G516" t="n">
-        <v>5.00838994979858</v>
+        <v>5.00838899612427</v>
       </c>
       <c r="H516" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G518" t="n">
-        <v>5.00838994979858</v>
+        <v>5.00838899612427</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>5</v>
       </c>
       <c r="G519" t="n">
-        <v>4.92951774597168</v>
+        <v>4.92951679229736</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13915,7 +13915,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G521" t="n">
-        <v>5.20557069778442</v>
+        <v>5.20557022094727</v>
       </c>
       <c r="H521" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G524" t="n">
-        <v>4.94923496246338</v>
+        <v>4.94923543930054</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G525" t="n">
-        <v>4.88022232055664</v>
+        <v>4.88022184371948</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G526" t="n">
-        <v>5.00838994979858</v>
+        <v>5.00838899612427</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G528" t="n">
-        <v>4.80135011672974</v>
+        <v>4.80134963989258</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G529" t="n">
-        <v>4.77177333831787</v>
+        <v>4.77177286148071</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14175,7 +14175,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G531" t="n">
-        <v>4.80135011672974</v>
+        <v>4.80134963989258</v>
       </c>
       <c r="H531" t="s">
         <v>8</v>
@@ -14201,7 +14201,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G532" t="n">
-        <v>4.77177333831787</v>
+        <v>4.77177286148071</v>
       </c>
       <c r="H532" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G538" t="n">
-        <v>4.8999400138855</v>
+        <v>4.89993953704834</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G541" t="n">
-        <v>4.94923496246338</v>
+        <v>4.94923543930054</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G542" t="n">
-        <v>4.86050367355347</v>
+        <v>4.86050415039062</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G547" t="n">
-        <v>4.62362051010132</v>
+        <v>4.62362098693848</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G549" t="n">
-        <v>4.59398221969604</v>
+        <v>4.5939826965332</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G550" t="n">
-        <v>4.6433801651001</v>
+        <v>4.64337968826294</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G561" t="n">
-        <v>4.79157257080078</v>
+        <v>4.79157304763794</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G573" t="n">
-        <v>4.43590927124023</v>
+        <v>4.43590974807739</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15319,7 +15319,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G575" t="n">
-        <v>4.32723569869995</v>
+        <v>4.32723522186279</v>
       </c>
       <c r="H575" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>4.5</v>
       </c>
       <c r="G576" t="n">
-        <v>4.44578886032104</v>
+        <v>4.4457893371582</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15371,7 +15371,7 @@
         <v>4.5</v>
       </c>
       <c r="G577" t="n">
-        <v>4.44578886032104</v>
+        <v>4.4457893371582</v>
       </c>
       <c r="H577" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>4.5</v>
       </c>
       <c r="G578" t="n">
-        <v>4.44578886032104</v>
+        <v>4.4457893371582</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15423,7 +15423,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G579" t="n">
-        <v>4.2778377532959</v>
+        <v>4.27783727645874</v>
       </c>
       <c r="H579" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G582" t="n">
-        <v>4.45566940307617</v>
+        <v>4.45566892623901</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G583" t="n">
-        <v>4.6433801651001</v>
+        <v>4.64337968826294</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G585" t="n">
-        <v>4.59398221969604</v>
+        <v>4.5939826965332</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G587" t="n">
-        <v>4.43590927124023</v>
+        <v>4.43590974807739</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G589" t="n">
-        <v>4.43590927124023</v>
+        <v>4.43590974807739</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G590" t="n">
-        <v>4.38651180267334</v>
+        <v>4.3865122795105</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G591" t="n">
-        <v>4.34699440002441</v>
+        <v>4.34699392318726</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G592" t="n">
-        <v>4.34699440002441</v>
+        <v>4.34699392318726</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15787,7 +15787,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G593" t="n">
-        <v>4.34699440002441</v>
+        <v>4.34699392318726</v>
       </c>
       <c r="H593" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G594" t="n">
-        <v>4.48530769348145</v>
+        <v>4.48530721664429</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G595" t="n">
-        <v>4.35687351226807</v>
+        <v>4.35687303543091</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>4.5</v>
       </c>
       <c r="G596" t="n">
-        <v>4.44578886032104</v>
+        <v>4.4457893371582</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G599" t="n">
-        <v>4.43590927124023</v>
+        <v>4.43590974807739</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G600" t="n">
-        <v>4.48530769348145</v>
+        <v>4.48530721664429</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G602" t="n">
-        <v>4.59398221969604</v>
+        <v>4.5939826965332</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G603" t="n">
-        <v>4.6433801651001</v>
+        <v>4.64337968826294</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G606" t="n">
-        <v>4.89036846160889</v>
+        <v>4.89036798477173</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G607" t="n">
-        <v>4.7026572227478</v>
+        <v>4.70265769958496</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G608" t="n">
-        <v>4.7026572227478</v>
+        <v>4.70265769958496</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G611" t="n">
-        <v>4.72241592407227</v>
+        <v>4.72241640090942</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16359,7 +16359,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G615" t="n">
-        <v>4.88048839569092</v>
+        <v>4.88048887252808</v>
       </c>
       <c r="H615" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G616" t="n">
-        <v>4.97928428649902</v>
+        <v>4.97928380966187</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16411,7 +16411,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G617" t="n">
-        <v>4.97928428649902</v>
+        <v>4.97928380966187</v>
       </c>
       <c r="H617" t="s">
         <v>8</v>
@@ -16437,7 +16437,7 @@
         <v>5</v>
       </c>
       <c r="G618" t="n">
-        <v>4.93976593017578</v>
+        <v>4.93976545333862</v>
       </c>
       <c r="H618" t="s">
         <v>8</v>
@@ -16463,7 +16463,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G619" t="n">
-        <v>4.97928428649902</v>
+        <v>4.97928380966187</v>
       </c>
       <c r="H619" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G620" t="n">
-        <v>4.99904298782349</v>
+        <v>4.99904346466064</v>
       </c>
       <c r="H620" t="s">
         <v>8</v>
@@ -16515,7 +16515,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G621" t="n">
-        <v>5.01880216598511</v>
+        <v>5.01880168914795</v>
       </c>
       <c r="H621" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G622" t="n">
-        <v>5.01880216598511</v>
+        <v>5.01880168914795</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16567,7 +16567,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G623" t="n">
-        <v>5.01880216598511</v>
+        <v>5.01880168914795</v>
       </c>
       <c r="H623" t="s">
         <v>8</v>
@@ -16801,7 +16801,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G632" t="n">
-        <v>4.75205421447754</v>
+        <v>4.7520546913147</v>
       </c>
       <c r="H632" t="s">
         <v>8</v>
@@ -16879,7 +16879,7 @@
         <v>5</v>
       </c>
       <c r="G635" t="n">
-        <v>4.93976593017578</v>
+        <v>4.93976545333862</v>
       </c>
       <c r="H635" t="s">
         <v>8</v>
@@ -16905,7 +16905,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G636" t="n">
-        <v>4.89036846160889</v>
+        <v>4.89036798477173</v>
       </c>
       <c r="H636" t="s">
         <v>8</v>
@@ -16931,7 +16931,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G637" t="n">
-        <v>4.88048839569092</v>
+        <v>4.88048887252808</v>
       </c>
       <c r="H637" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G638" t="n">
-        <v>4.88048839569092</v>
+        <v>4.88048887252808</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G640" t="n">
-        <v>4.79157257080078</v>
+        <v>4.79157304763794</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17035,7 +17035,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G641" t="n">
-        <v>4.79157257080078</v>
+        <v>4.79157304763794</v>
       </c>
       <c r="H641" t="s">
         <v>8</v>
@@ -17061,7 +17061,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G642" t="n">
-        <v>4.79157257080078</v>
+        <v>4.79157304763794</v>
       </c>
       <c r="H642" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>4.5</v>
       </c>
       <c r="G646" t="n">
-        <v>4.44578886032104</v>
+        <v>4.4457893371582</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G647" t="n">
-        <v>4.34699440002441</v>
+        <v>4.34699392318726</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G648" t="n">
-        <v>4.34699440002441</v>
+        <v>4.34699392318726</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17269,7 +17269,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G650" t="n">
-        <v>4.52482557296753</v>
+        <v>4.52482509613037</v>
       </c>
       <c r="H650" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G651" t="n">
-        <v>4.61374139785767</v>
+        <v>4.61374187469482</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17347,7 +17347,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G653" t="n">
-        <v>4.79157257080078</v>
+        <v>4.79157304763794</v>
       </c>
       <c r="H653" t="s">
         <v>8</v>
@@ -17425,7 +17425,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G656" t="n">
-        <v>4.72241592407227</v>
+        <v>4.72241640090942</v>
       </c>
       <c r="H656" t="s">
         <v>8</v>
@@ -17451,7 +17451,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G657" t="n">
-        <v>4.72241592407227</v>
+        <v>4.72241640090942</v>
       </c>
       <c r="H657" t="s">
         <v>8</v>
@@ -17555,7 +17555,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G661" t="n">
-        <v>4.88048839569092</v>
+        <v>4.88048887252808</v>
       </c>
       <c r="H661" t="s">
         <v>8</v>
@@ -17607,7 +17607,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G663" t="n">
-        <v>4.95952463150024</v>
+        <v>4.9595251083374</v>
       </c>
       <c r="H663" t="s">
         <v>8</v>
@@ -17633,7 +17633,7 @@
         <v>5</v>
       </c>
       <c r="G664" t="n">
-        <v>4.93976593017578</v>
+        <v>4.93976545333862</v>
       </c>
       <c r="H664" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G675" t="n">
-        <v>4.97928428649902</v>
+        <v>4.97928380966187</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -17945,7 +17945,7 @@
         <v>5</v>
       </c>
       <c r="G676" t="n">
-        <v>4.93976593017578</v>
+        <v>4.93976545333862</v>
       </c>
       <c r="H676" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G677" t="n">
-        <v>4.89036846160889</v>
+        <v>4.89036798477173</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -18023,7 +18023,7 @@
         <v>4.59000015258789</v>
       </c>
       <c r="G679" t="n">
-        <v>4.5347056388855</v>
+        <v>4.53470468521118</v>
       </c>
       <c r="H679" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>4.71000003814697</v>
       </c>
       <c r="G681" t="n">
-        <v>4.65325927734375</v>
+        <v>4.65325975418091</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>4.59000015258789</v>
       </c>
       <c r="G683" t="n">
-        <v>4.5347056388855</v>
+        <v>4.53470468521118</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18153,7 +18153,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G684" t="n">
-        <v>4.52482557296753</v>
+        <v>4.52482509613037</v>
       </c>
       <c r="H684" t="s">
         <v>8</v>
@@ -18179,7 +18179,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G685" t="n">
-        <v>4.34699440002441</v>
+        <v>4.34699392318726</v>
       </c>
       <c r="H685" t="s">
         <v>8</v>
@@ -18231,7 +18231,7 @@
         <v>4.5</v>
       </c>
       <c r="G687" t="n">
-        <v>4.44578886032104</v>
+        <v>4.4457893371582</v>
       </c>
       <c r="H687" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>4.5</v>
       </c>
       <c r="G688" t="n">
-        <v>4.44578886032104</v>
+        <v>4.4457893371582</v>
       </c>
       <c r="H688" t="s">
         <v>8</v>
@@ -18309,7 +18309,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G690" t="n">
-        <v>4.71253728866577</v>
+        <v>4.7125358581543</v>
       </c>
       <c r="H690" t="s">
         <v>8</v>
@@ -18335,7 +18335,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G691" t="n">
-        <v>5.01880216598511</v>
+        <v>5.01880168914795</v>
       </c>
       <c r="H691" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G695" t="n">
-        <v>4.99904298782349</v>
+        <v>4.99904346466064</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G707" t="n">
-        <v>4.8508505821228</v>
+        <v>4.85085010528564</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -18855,7 +18855,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G711" t="n">
-        <v>4.88048839569092</v>
+        <v>4.88048887252808</v>
       </c>
       <c r="H711" t="s">
         <v>8</v>
@@ -18881,7 +18881,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G712" t="n">
-        <v>4.72241592407227</v>
+        <v>4.72241640090942</v>
       </c>
       <c r="H712" t="s">
         <v>8</v>
@@ -18907,7 +18907,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G713" t="n">
-        <v>4.71253728866577</v>
+        <v>4.7125358581543</v>
       </c>
       <c r="H713" t="s">
         <v>8</v>
@@ -18933,7 +18933,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G714" t="n">
-        <v>4.60386180877686</v>
+        <v>4.6038613319397</v>
       </c>
       <c r="H714" t="s">
         <v>8</v>
@@ -18959,7 +18959,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G715" t="n">
-        <v>4.71253728866577</v>
+        <v>4.7125358581543</v>
       </c>
       <c r="H715" t="s">
         <v>8</v>
@@ -18985,7 +18985,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G716" t="n">
-        <v>4.72241592407227</v>
+        <v>4.72241640090942</v>
       </c>
       <c r="H716" t="s">
         <v>8</v>
@@ -19063,7 +19063,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G719" t="n">
-        <v>4.95952463150024</v>
+        <v>4.9595251083374</v>
       </c>
       <c r="H719" t="s">
         <v>8</v>
@@ -19089,7 +19089,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G720" t="n">
-        <v>5.01880216598511</v>
+        <v>5.01880168914795</v>
       </c>
       <c r="H720" t="s">
         <v>8</v>
@@ -19115,7 +19115,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G721" t="n">
-        <v>5.09783792495728</v>
+        <v>5.09783840179443</v>
       </c>
       <c r="H721" t="s">
         <v>8</v>
@@ -19271,7 +19271,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G727" t="n">
-        <v>4.97928428649902</v>
+        <v>4.97928380966187</v>
       </c>
       <c r="H727" t="s">
         <v>8</v>
@@ -19297,7 +19297,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G728" t="n">
-        <v>4.76193475723267</v>
+        <v>4.76193428039551</v>
       </c>
       <c r="H728" t="s">
         <v>8</v>
@@ -19427,7 +19427,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G733" t="n">
-        <v>4.88048839569092</v>
+        <v>4.88048887252808</v>
       </c>
       <c r="H733" t="s">
         <v>8</v>
@@ -19479,7 +19479,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G735" t="n">
-        <v>4.79157257080078</v>
+        <v>4.79157304763794</v>
       </c>
       <c r="H735" t="s">
         <v>8</v>
@@ -19505,7 +19505,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G736" t="n">
-        <v>4.88048839569092</v>
+        <v>4.88048887252808</v>
       </c>
       <c r="H736" t="s">
         <v>8</v>
@@ -19531,7 +19531,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G737" t="n">
-        <v>4.89036846160889</v>
+        <v>4.89036798477173</v>
       </c>
       <c r="H737" t="s">
         <v>8</v>
@@ -19687,7 +19687,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G743" t="n">
-        <v>4.8508505821228</v>
+        <v>4.85085010528564</v>
       </c>
       <c r="H743" t="s">
         <v>8</v>
@@ -19739,7 +19739,7 @@
         <v>5</v>
       </c>
       <c r="G745" t="n">
-        <v>4.93976593017578</v>
+        <v>4.93976545333862</v>
       </c>
       <c r="H745" t="s">
         <v>8</v>
@@ -19817,7 +19817,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G748" t="n">
-        <v>4.75205421447754</v>
+        <v>4.7520546913147</v>
       </c>
       <c r="H748" t="s">
         <v>8</v>
@@ -19895,7 +19895,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G751" t="n">
-        <v>4.17904186248779</v>
+        <v>4.17904138565063</v>
       </c>
       <c r="H751" t="s">
         <v>8</v>
@@ -19947,7 +19947,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G753" t="n">
-        <v>4.17904186248779</v>
+        <v>4.17904138565063</v>
       </c>
       <c r="H753" t="s">
         <v>8</v>
@@ -19973,7 +19973,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G754" t="n">
-        <v>4.17904186248779</v>
+        <v>4.17904138565063</v>
       </c>
       <c r="H754" t="s">
         <v>8</v>
@@ -19999,7 +19999,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G755" t="n">
-        <v>4.1889214515686</v>
+        <v>4.18892097473145</v>
       </c>
       <c r="H755" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G756" t="n">
-        <v>4.1889214515686</v>
+        <v>4.18892097473145</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20051,7 +20051,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G757" t="n">
-        <v>4.17904186248779</v>
+        <v>4.17904138565063</v>
       </c>
       <c r="H757" t="s">
         <v>8</v>
@@ -20077,7 +20077,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G758" t="n">
-        <v>4.14940357208252</v>
+        <v>4.14940309524536</v>
       </c>
       <c r="H758" t="s">
         <v>8</v>
@@ -20103,7 +20103,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G759" t="n">
-        <v>4.15928316116333</v>
+        <v>4.15928268432617</v>
       </c>
       <c r="H759" t="s">
         <v>8</v>
@@ -20181,7 +20181,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G762" t="n">
-        <v>4.15928316116333</v>
+        <v>4.15928268432617</v>
       </c>
       <c r="H762" t="s">
         <v>8</v>
@@ -20233,7 +20233,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G764" t="n">
-        <v>4.0209698677063</v>
+        <v>4.02096939086914</v>
       </c>
       <c r="H764" t="s">
         <v>8</v>
@@ -20337,7 +20337,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G768" t="n">
-        <v>3.89253568649292</v>
+        <v>3.89253544807434</v>
       </c>
       <c r="H768" t="s">
         <v>8</v>
@@ -20467,7 +20467,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G773" t="n">
-        <v>3.80361986160278</v>
+        <v>3.8036196231842</v>
       </c>
       <c r="H773" t="s">
         <v>8</v>
@@ -20493,7 +20493,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G774" t="n">
-        <v>3.75422191619873</v>
+        <v>3.75422167778015</v>
       </c>
       <c r="H774" t="s">
         <v>8</v>
@@ -20519,7 +20519,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G775" t="n">
-        <v>3.74434232711792</v>
+        <v>3.7443425655365</v>
       </c>
       <c r="H775" t="s">
         <v>8</v>
@@ -20545,7 +20545,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G776" t="n">
-        <v>3.69494485855103</v>
+        <v>3.6949450969696</v>
       </c>
       <c r="H776" t="s">
         <v>8</v>
@@ -20571,7 +20571,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G777" t="n">
-        <v>3.75422191619873</v>
+        <v>3.75422167778015</v>
       </c>
       <c r="H777" t="s">
         <v>8</v>
@@ -20649,7 +20649,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G780" t="n">
-        <v>3.89253568649292</v>
+        <v>3.89253544807434</v>
       </c>
       <c r="H780" t="s">
         <v>8</v>
@@ -20727,7 +20727,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G783" t="n">
-        <v>3.98145198822021</v>
+        <v>3.98145151138306</v>
       </c>
       <c r="H783" t="s">
         <v>8</v>
@@ -20779,7 +20779,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G785" t="n">
-        <v>3.89253568649292</v>
+        <v>3.89253544807434</v>
       </c>
       <c r="H785" t="s">
         <v>8</v>
@@ -20883,7 +20883,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G789" t="n">
-        <v>3.92217397689819</v>
+        <v>3.92217421531677</v>
       </c>
       <c r="H789" t="s">
         <v>8</v>
@@ -20987,7 +20987,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G793" t="n">
-        <v>3.93205380439758</v>
+        <v>3.932053565979</v>
       </c>
       <c r="H793" t="s">
         <v>8</v>
@@ -21143,7 +21143,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G799" t="n">
-        <v>3.91229438781738</v>
+        <v>3.91229486465454</v>
       </c>
       <c r="H799" t="s">
         <v>8</v>
@@ -21273,7 +21273,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G804" t="n">
-        <v>3.86292243003845</v>
+        <v>3.86292219161987</v>
       </c>
       <c r="H804" t="s">
         <v>8</v>
@@ -21325,7 +21325,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G806" t="n">
-        <v>3.86292243003845</v>
+        <v>3.86292219161987</v>
       </c>
       <c r="H806" t="s">
         <v>8</v>
@@ -21351,7 +21351,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G807" t="n">
-        <v>4.01149654388428</v>
+        <v>4.01149606704712</v>
       </c>
       <c r="H807" t="s">
         <v>8</v>
@@ -21715,7 +21715,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G821" t="n">
-        <v>4.14025974273682</v>
+        <v>4.14026021957397</v>
       </c>
       <c r="H821" t="s">
         <v>8</v>
@@ -21871,7 +21871,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G827" t="n">
-        <v>4.03130626678467</v>
+        <v>4.03130578994751</v>
       </c>
       <c r="H827" t="s">
         <v>8</v>
@@ -21923,7 +21923,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G829" t="n">
-        <v>4.05111646652222</v>
+        <v>4.05111598968506</v>
       </c>
       <c r="H829" t="s">
         <v>8</v>
@@ -22001,7 +22001,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G832" t="n">
-        <v>4.05111646652222</v>
+        <v>4.05111598968506</v>
       </c>
       <c r="H832" t="s">
         <v>8</v>
@@ -22027,7 +22027,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G833" t="n">
-        <v>4.05111646652222</v>
+        <v>4.05111598968506</v>
       </c>
       <c r="H833" t="s">
         <v>8</v>
@@ -22157,7 +22157,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G838" t="n">
-        <v>4.05111646652222</v>
+        <v>4.05111598968506</v>
       </c>
       <c r="H838" t="s">
         <v>8</v>
@@ -22261,7 +22261,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G842" t="n">
-        <v>4.07092571258545</v>
+        <v>4.07092618942261</v>
       </c>
       <c r="H842" t="s">
         <v>8</v>
@@ -22469,7 +22469,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G850" t="n">
-        <v>4.14025974273682</v>
+        <v>4.14026021957397</v>
       </c>
       <c r="H850" t="s">
         <v>8</v>
@@ -22495,7 +22495,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G851" t="n">
-        <v>4.16997528076172</v>
+        <v>4.16997480392456</v>
       </c>
       <c r="H851" t="s">
         <v>8</v>
@@ -22521,7 +22521,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G852" t="n">
-        <v>4.1996898651123</v>
+        <v>4.19968938827515</v>
       </c>
       <c r="H852" t="s">
         <v>8</v>
@@ -22651,7 +22651,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G857" t="n">
-        <v>4.07092571258545</v>
+        <v>4.07092618942261</v>
       </c>
       <c r="H857" t="s">
         <v>8</v>
@@ -22677,7 +22677,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G858" t="n">
-        <v>4.11054515838623</v>
+        <v>4.11054563522339</v>
       </c>
       <c r="H858" t="s">
         <v>8</v>
@@ -22729,7 +22729,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G860" t="n">
-        <v>4.07092571258545</v>
+        <v>4.07092618942261</v>
       </c>
       <c r="H860" t="s">
         <v>8</v>
@@ -22807,7 +22807,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G863" t="n">
-        <v>4.11054515838623</v>
+        <v>4.11054563522339</v>
       </c>
       <c r="H863" t="s">
         <v>8</v>
@@ -22911,7 +22911,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G867" t="n">
-        <v>4.05111646652222</v>
+        <v>4.05111598968506</v>
       </c>
       <c r="H867" t="s">
         <v>8</v>
@@ -22963,7 +22963,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G869" t="n">
-        <v>4.01149654388428</v>
+        <v>4.01149606704712</v>
       </c>
       <c r="H869" t="s">
         <v>8</v>
@@ -23171,7 +23171,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G877" t="n">
-        <v>4.16997528076172</v>
+        <v>4.16997480392456</v>
       </c>
       <c r="H877" t="s">
         <v>8</v>
@@ -23327,7 +23327,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G883" t="n">
-        <v>4.3383584022522</v>
+        <v>4.33835887908936</v>
       </c>
       <c r="H883" t="s">
         <v>8</v>
@@ -23353,7 +23353,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G884" t="n">
-        <v>4.36807346343994</v>
+        <v>4.36807298660278</v>
       </c>
       <c r="H884" t="s">
         <v>8</v>
@@ -23379,7 +23379,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G885" t="n">
-        <v>4.3383584022522</v>
+        <v>4.33835887908936</v>
       </c>
       <c r="H885" t="s">
         <v>8</v>
@@ -23535,7 +23535,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G891" t="n">
-        <v>4.36807346343994</v>
+        <v>4.36807298660278</v>
       </c>
       <c r="H891" t="s">
         <v>8</v>
@@ -23561,7 +23561,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G892" t="n">
-        <v>4.36807346343994</v>
+        <v>4.36807298660278</v>
       </c>
       <c r="H892" t="s">
         <v>8</v>
@@ -23587,7 +23587,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G893" t="n">
-        <v>4.23930978775024</v>
+        <v>4.23930931091309</v>
       </c>
       <c r="H893" t="s">
         <v>8</v>
@@ -23821,7 +23821,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G902" t="n">
-        <v>4.1996898651123</v>
+        <v>4.19968938827515</v>
       </c>
       <c r="H902" t="s">
         <v>8</v>
@@ -23873,7 +23873,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G904" t="n">
-        <v>4.07092571258545</v>
+        <v>4.07092618942261</v>
       </c>
       <c r="H904" t="s">
         <v>8</v>
@@ -24003,7 +24003,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G909" t="n">
-        <v>4.11054515838623</v>
+        <v>4.11054563522339</v>
       </c>
       <c r="H909" t="s">
         <v>8</v>
@@ -24107,7 +24107,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G913" t="n">
-        <v>3.84311270713806</v>
+        <v>3.84311246871948</v>
       </c>
       <c r="H913" t="s">
         <v>8</v>
@@ -24445,7 +24445,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G926" t="n">
-        <v>3.62520432472229</v>
+        <v>3.62520408630371</v>
       </c>
       <c r="H926" t="s">
         <v>8</v>
@@ -24471,7 +24471,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G927" t="n">
-        <v>3.56577444076538</v>
+        <v>3.5657742023468</v>
       </c>
       <c r="H927" t="s">
         <v>8</v>
@@ -24497,7 +24497,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G928" t="n">
-        <v>3.56577444076538</v>
+        <v>3.5657742023468</v>
       </c>
       <c r="H928" t="s">
         <v>8</v>
@@ -24523,7 +24523,7 @@
         <v>3.75</v>
       </c>
       <c r="G929" t="n">
-        <v>3.71434831619263</v>
+        <v>3.71434855461121</v>
       </c>
       <c r="H929" t="s">
         <v>8</v>
@@ -24549,7 +24549,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G930" t="n">
-        <v>3.66482400894165</v>
+        <v>3.66482377052307</v>
       </c>
       <c r="H930" t="s">
         <v>8</v>
@@ -24575,7 +24575,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G931" t="n">
-        <v>3.56577444076538</v>
+        <v>3.5657742023468</v>
       </c>
       <c r="H931" t="s">
         <v>8</v>
@@ -24601,7 +24601,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G932" t="n">
-        <v>3.60539436340332</v>
+        <v>3.60539412498474</v>
       </c>
       <c r="H932" t="s">
         <v>8</v>
@@ -24627,7 +24627,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G933" t="n">
-        <v>3.56577444076538</v>
+        <v>3.5657742023468</v>
       </c>
       <c r="H933" t="s">
         <v>8</v>
@@ -24653,7 +24653,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G934" t="n">
-        <v>3.56577444076538</v>
+        <v>3.5657742023468</v>
       </c>
       <c r="H934" t="s">
         <v>8</v>
@@ -24705,7 +24705,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G936" t="n">
-        <v>3.67472863197327</v>
+        <v>3.67472839355469</v>
       </c>
       <c r="H936" t="s">
         <v>8</v>
@@ -24783,7 +24783,7 @@
         <v>3.75</v>
       </c>
       <c r="G939" t="n">
-        <v>3.71434831619263</v>
+        <v>3.71434855461121</v>
       </c>
       <c r="H939" t="s">
         <v>8</v>
@@ -24835,7 +24835,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G941" t="n">
-        <v>3.88273239135742</v>
+        <v>3.88273215293884</v>
       </c>
       <c r="H941" t="s">
         <v>8</v>
@@ -24939,7 +24939,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G945" t="n">
-        <v>3.90254211425781</v>
+        <v>3.90254187583923</v>
       </c>
       <c r="H945" t="s">
         <v>8</v>
@@ -25147,7 +25147,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G953" t="n">
-        <v>4.03130626678467</v>
+        <v>4.03130578994751</v>
       </c>
       <c r="H953" t="s">
         <v>8</v>
@@ -25199,7 +25199,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G955" t="n">
-        <v>4.03130626678467</v>
+        <v>4.03130578994751</v>
       </c>
       <c r="H955" t="s">
         <v>8</v>
@@ -25355,7 +25355,7 @@
         <v>40.5999984741211</v>
       </c>
       <c r="G961" t="n">
-        <v>40.2140083312988</v>
+        <v>40.2140121459961</v>
       </c>
       <c r="H961" t="s">
         <v>8</v>
@@ -25381,7 +25381,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G962" t="n">
-        <v>3.86292243003845</v>
+        <v>3.86292219161987</v>
       </c>
       <c r="H962" t="s">
         <v>8</v>
@@ -25407,7 +25407,7 @@
         <v>3.94400000572205</v>
       </c>
       <c r="G963" t="n">
-        <v>3.90650391578674</v>
+        <v>3.90650415420532</v>
       </c>
       <c r="H963" t="s">
         <v>8</v>
@@ -25537,7 +25537,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G968" t="n">
-        <v>3.90254211425781</v>
+        <v>3.90254187583923</v>
       </c>
       <c r="H968" t="s">
         <v>8</v>
@@ -25563,7 +25563,7 @@
         <v>3.99699997901917</v>
       </c>
       <c r="G969" t="n">
-        <v>3.95899987220764</v>
+        <v>3.95900011062622</v>
       </c>
       <c r="H969" t="s">
         <v>8</v>
@@ -25615,7 +25615,7 @@
         <v>3.99799990653992</v>
       </c>
       <c r="G971" t="n">
-        <v>3.95999026298523</v>
+        <v>3.95999050140381</v>
       </c>
       <c r="H971" t="s">
         <v>8</v>
@@ -25693,7 +25693,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G974" t="n">
-        <v>4.01149654388428</v>
+        <v>4.01149606704712</v>
       </c>
       <c r="H974" t="s">
         <v>8</v>
@@ -26005,7 +26005,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G986" t="n">
-        <v>3.88273239135742</v>
+        <v>3.88273215293884</v>
       </c>
       <c r="H986" t="s">
         <v>8</v>
@@ -26187,7 +26187,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G993" t="n">
-        <v>3.86292243003845</v>
+        <v>3.86292219161987</v>
       </c>
       <c r="H993" t="s">
         <v>8</v>
@@ -26395,7 +26395,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1001" t="n">
-        <v>3.86292243003845</v>
+        <v>3.86292219161987</v>
       </c>
       <c r="H1001" t="s">
         <v>8</v>
@@ -26421,7 +26421,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G1002" t="n">
-        <v>3.90254211425781</v>
+        <v>3.90254187583923</v>
       </c>
       <c r="H1002" t="s">
         <v>8</v>
@@ -26499,7 +26499,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1005" t="n">
-        <v>3.76387286186218</v>
+        <v>3.7638726234436</v>
       </c>
       <c r="H1005" t="s">
         <v>8</v>
@@ -26551,7 +26551,7 @@
         <v>3.75</v>
       </c>
       <c r="G1007" t="n">
-        <v>3.71434831619263</v>
+        <v>3.71434855461121</v>
       </c>
       <c r="H1007" t="s">
         <v>8</v>
@@ -26629,7 +26629,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G1010" t="n">
-        <v>3.73415803909302</v>
+        <v>3.7341582775116</v>
       </c>
       <c r="H1010" t="s">
         <v>8</v>
@@ -26655,7 +26655,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G1011" t="n">
-        <v>3.73415803909302</v>
+        <v>3.7341582775116</v>
       </c>
       <c r="H1011" t="s">
         <v>8</v>
@@ -26681,7 +26681,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1012" t="n">
-        <v>3.76387286186218</v>
+        <v>3.7638726234436</v>
       </c>
       <c r="H1012" t="s">
         <v>8</v>
@@ -26707,7 +26707,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1013" t="n">
-        <v>3.67472863197327</v>
+        <v>3.67472839355469</v>
       </c>
       <c r="H1013" t="s">
         <v>8</v>
@@ -26733,7 +26733,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1014" t="n">
-        <v>3.66482400894165</v>
+        <v>3.66482377052307</v>
       </c>
       <c r="H1014" t="s">
         <v>8</v>
@@ -26759,7 +26759,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1015" t="n">
-        <v>3.66482400894165</v>
+        <v>3.66482377052307</v>
       </c>
       <c r="H1015" t="s">
         <v>8</v>
@@ -26837,7 +26837,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G1018" t="n">
-        <v>3.60539436340332</v>
+        <v>3.60539412498474</v>
       </c>
       <c r="H1018" t="s">
         <v>8</v>
@@ -26889,7 +26889,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G1020" t="n">
-        <v>3.60539436340332</v>
+        <v>3.60539412498474</v>
       </c>
       <c r="H1020" t="s">
         <v>8</v>
@@ -26941,7 +26941,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G1022" t="n">
-        <v>3.60539436340332</v>
+        <v>3.60539412498474</v>
       </c>
       <c r="H1022" t="s">
         <v>8</v>
@@ -26967,7 +26967,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1023" t="n">
-        <v>3.66482400894165</v>
+        <v>3.66482377052307</v>
       </c>
       <c r="H1023" t="s">
         <v>8</v>
@@ -27019,7 +27019,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G1025" t="n">
-        <v>3.58558416366577</v>
+        <v>3.58558392524719</v>
       </c>
       <c r="H1025" t="s">
         <v>8</v>
@@ -27175,7 +27175,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G1031" t="n">
-        <v>3.65491890907288</v>
+        <v>3.6549186706543</v>
       </c>
       <c r="H1031" t="s">
         <v>8</v>
@@ -27201,7 +27201,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G1032" t="n">
-        <v>3.65491890907288</v>
+        <v>3.6549186706543</v>
       </c>
       <c r="H1032" t="s">
         <v>8</v>
@@ -27227,7 +27227,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1033" t="n">
-        <v>3.67472863197327</v>
+        <v>3.67472839355469</v>
       </c>
       <c r="H1033" t="s">
         <v>8</v>
@@ -27279,7 +27279,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1035" t="n">
-        <v>3.56577444076538</v>
+        <v>3.5657742023468</v>
       </c>
       <c r="H1035" t="s">
         <v>8</v>
@@ -27331,7 +27331,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G1037" t="n">
-        <v>3.52615451812744</v>
+        <v>3.52615475654602</v>
       </c>
       <c r="H1037" t="s">
         <v>8</v>
@@ -27539,7 +27539,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1045" t="n">
-        <v>3.50634455680847</v>
+        <v>3.50634479522705</v>
       </c>
       <c r="H1045" t="s">
         <v>8</v>
@@ -27565,7 +27565,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G1046" t="n">
-        <v>3.52615451812744</v>
+        <v>3.52615475654602</v>
       </c>
       <c r="H1046" t="s">
         <v>8</v>
@@ -27591,7 +27591,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1047" t="n">
-        <v>3.44691514968872</v>
+        <v>3.4469153881073</v>
       </c>
       <c r="H1047" t="s">
         <v>8</v>
@@ -27617,7 +27617,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1048" t="n">
-        <v>3.41720056533813</v>
+        <v>3.41720032691956</v>
       </c>
       <c r="H1048" t="s">
         <v>8</v>
@@ -27643,7 +27643,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1049" t="n">
-        <v>3.43701028823853</v>
+        <v>3.4370105266571</v>
       </c>
       <c r="H1049" t="s">
         <v>8</v>
@@ -27669,7 +27669,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1050" t="n">
-        <v>3.43701028823853</v>
+        <v>3.4370105266571</v>
       </c>
       <c r="H1050" t="s">
         <v>8</v>
@@ -27695,7 +27695,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G1051" t="n">
-        <v>3.45682001113892</v>
+        <v>3.4568202495575</v>
       </c>
       <c r="H1051" t="s">
         <v>8</v>
@@ -27773,7 +27773,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1054" t="n">
-        <v>3.56577444076538</v>
+        <v>3.5657742023468</v>
       </c>
       <c r="H1054" t="s">
         <v>8</v>
@@ -27799,7 +27799,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1055" t="n">
-        <v>3.56577444076538</v>
+        <v>3.5657742023468</v>
       </c>
       <c r="H1055" t="s">
         <v>8</v>
@@ -27929,7 +27929,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1060" t="n">
-        <v>3.56577444076538</v>
+        <v>3.5657742023468</v>
       </c>
       <c r="H1060" t="s">
         <v>8</v>
@@ -27955,7 +27955,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G1061" t="n">
-        <v>3.90254211425781</v>
+        <v>3.90254187583923</v>
       </c>
       <c r="H1061" t="s">
         <v>8</v>
@@ -27981,7 +27981,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1062" t="n">
-        <v>3.76387286186218</v>
+        <v>3.7638726234436</v>
       </c>
       <c r="H1062" t="s">
         <v>8</v>
@@ -28111,7 +28111,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G1067" t="n">
-        <v>4.01149654388428</v>
+        <v>4.01149606704712</v>
       </c>
       <c r="H1067" t="s">
         <v>8</v>
@@ -28163,7 +28163,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1069" t="n">
-        <v>3.86292243003845</v>
+        <v>3.86292219161987</v>
       </c>
       <c r="H1069" t="s">
         <v>8</v>
@@ -28267,7 +28267,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1073" t="n">
-        <v>3.76387286186218</v>
+        <v>3.7638726234436</v>
       </c>
       <c r="H1073" t="s">
         <v>8</v>
@@ -28397,7 +28397,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G1078" t="n">
-        <v>3.73415803909302</v>
+        <v>3.7341582775116</v>
       </c>
       <c r="H1078" t="s">
         <v>8</v>
@@ -43922,6 +43922,32 @@
         <v>3.20000004768372</v>
       </c>
       <c r="H1675" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1676">
+      <c r="A1676" s="1" t="n">
+        <v>46311.2916666667</v>
+      </c>
+      <c r="B1676" t="n">
+        <v>14618</v>
+      </c>
+      <c r="C1676" t="n">
+        <v>3.23000001907349</v>
+      </c>
+      <c r="D1676" t="n">
+        <v>3.20000004768372</v>
+      </c>
+      <c r="E1676" t="n">
+        <v>3.21499991416931</v>
+      </c>
+      <c r="F1676" t="n">
+        <v>3.19000005722046</v>
+      </c>
+      <c r="G1676" t="n">
+        <v>3.19000005722046</v>
+      </c>
+      <c r="H1676" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/UD.MI.xlsx
+++ b/data/UD.MI.xlsx
@@ -427,7 +427,7 @@
         <v>1.5</v>
       </c>
       <c r="G2" t="n">
-        <v>1.47885525226593</v>
+        <v>1.47885513305664</v>
       </c>
       <c r="H2" t="n">
         <v>159000</v>
@@ -456,7 +456,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G3" t="n">
-        <v>1.43941903114319</v>
+        <v>1.43941915035248</v>
       </c>
       <c r="H3" t="n">
         <v>78000</v>
@@ -485,7 +485,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G4" t="n">
-        <v>1.4591372013092</v>
+        <v>1.45913708209991</v>
       </c>
       <c r="H4" t="n">
         <v>240000</v>
@@ -572,7 +572,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G7" t="n">
-        <v>1.5182911157608</v>
+        <v>1.51829135417938</v>
       </c>
       <c r="H7" t="n">
         <v>61000</v>
@@ -601,7 +601,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G8" t="n">
-        <v>1.53800940513611</v>
+        <v>1.53800928592682</v>
       </c>
       <c r="H8" t="n">
         <v>19000</v>
@@ -659,7 +659,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G10" t="n">
-        <v>1.53800940513611</v>
+        <v>1.53800928592682</v>
       </c>
       <c r="H10" t="n">
         <v>17000</v>
@@ -688,7 +688,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G11" t="n">
-        <v>1.56265711784363</v>
+        <v>1.56265687942505</v>
       </c>
       <c r="H11" t="n">
         <v>16000</v>
@@ -862,7 +862,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G17" t="n">
-        <v>1.66617691516876</v>
+        <v>1.66617679595947</v>
       </c>
       <c r="H17" t="n">
         <v>14000</v>
@@ -891,7 +891,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G18" t="n">
-        <v>1.67603600025177</v>
+        <v>1.67603588104248</v>
       </c>
       <c r="H18" t="n">
         <v>36000</v>
@@ -920,7 +920,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G19" t="n">
-        <v>1.67603600025177</v>
+        <v>1.67603588104248</v>
       </c>
       <c r="H19" t="n">
         <v>18000</v>
@@ -1036,7 +1036,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G23" t="n">
-        <v>1.59716379642487</v>
+        <v>1.59716367721558</v>
       </c>
       <c r="H23" t="n">
         <v>43000</v>
@@ -1065,7 +1065,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G24" t="n">
-        <v>1.57744550704956</v>
+        <v>1.57744562625885</v>
       </c>
       <c r="H24" t="n">
         <v>2000</v>
@@ -1094,7 +1094,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G25" t="n">
-        <v>1.58730447292328</v>
+        <v>1.58730459213257</v>
       </c>
       <c r="H25" t="n">
         <v>22000</v>
@@ -1123,7 +1123,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G26" t="n">
-        <v>1.57744550704956</v>
+        <v>1.57744562625885</v>
       </c>
       <c r="H26" t="n">
         <v>8000</v>
@@ -1152,7 +1152,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G27" t="n">
-        <v>1.57744550704956</v>
+        <v>1.57744562625885</v>
       </c>
       <c r="H27" t="n">
         <v>3000</v>
@@ -1181,7 +1181,7 @@
         <v>1.59500002861023</v>
       </c>
       <c r="G28" t="n">
-        <v>1.57251620292664</v>
+        <v>1.57251608371735</v>
       </c>
       <c r="H28" t="n">
         <v>22000</v>
@@ -1210,7 +1210,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G29" t="n">
-        <v>1.57744550704956</v>
+        <v>1.57744562625885</v>
       </c>
       <c r="H29" t="n">
         <v>11000</v>
@@ -1268,7 +1268,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G31" t="n">
-        <v>1.63659965991974</v>
+        <v>1.63659977912903</v>
       </c>
       <c r="H31" t="n">
         <v>32000</v>
@@ -1297,7 +1297,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G32" t="n">
-        <v>1.59716379642487</v>
+        <v>1.59716367721558</v>
       </c>
       <c r="H32" t="n">
         <v>4000</v>
@@ -1326,7 +1326,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G33" t="n">
-        <v>1.61688160896301</v>
+        <v>1.6168817281723</v>
       </c>
       <c r="H33" t="n">
         <v>1000</v>
@@ -1529,7 +1529,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G40" t="n">
-        <v>1.6957540512085</v>
+        <v>1.69575393199921</v>
       </c>
       <c r="H40" t="n">
         <v>7000</v>
@@ -1558,7 +1558,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G41" t="n">
-        <v>1.6858948469162</v>
+        <v>1.68589496612549</v>
       </c>
       <c r="H41" t="n">
         <v>14000</v>
@@ -1616,7 +1616,7 @@
         <v>1.72500002384186</v>
       </c>
       <c r="G43" t="n">
-        <v>1.70068359375</v>
+        <v>1.70068347454071</v>
       </c>
       <c r="H43" t="n">
         <v>21000</v>
@@ -1674,7 +1674,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G45" t="n">
-        <v>1.66617691516876</v>
+        <v>1.66617679595947</v>
       </c>
       <c r="H45" t="n">
         <v>1000</v>
@@ -1703,7 +1703,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G46" t="n">
-        <v>1.67603600025177</v>
+        <v>1.67603588104248</v>
       </c>
       <c r="H46" t="n">
         <v>12000</v>
@@ -1790,7 +1790,7 @@
         <v>1.72500002384186</v>
       </c>
       <c r="G49" t="n">
-        <v>1.70068359375</v>
+        <v>1.70068347454071</v>
       </c>
       <c r="H49" t="n">
         <v>18000</v>
@@ -1848,7 +1848,7 @@
         <v>1.75</v>
       </c>
       <c r="G51" t="n">
-        <v>1.72533118724823</v>
+        <v>1.72533106803894</v>
       </c>
       <c r="H51" t="n">
         <v>12000</v>
@@ -1935,7 +1935,7 @@
         <v>1.72500002384186</v>
       </c>
       <c r="G54" t="n">
-        <v>1.70068359375</v>
+        <v>1.70068347454071</v>
       </c>
       <c r="H54" t="n">
         <v>10000</v>
@@ -1964,7 +1964,7 @@
         <v>1.72500002384186</v>
       </c>
       <c r="G55" t="n">
-        <v>1.70068359375</v>
+        <v>1.70068347454071</v>
       </c>
       <c r="H55" t="n">
         <v>15000</v>
@@ -1993,7 +1993,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G56" t="n">
-        <v>1.6957540512085</v>
+        <v>1.69575393199921</v>
       </c>
       <c r="H56" t="n">
         <v>8000</v>
@@ -2022,7 +2022,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G57" t="n">
-        <v>1.67603600025177</v>
+        <v>1.67603588104248</v>
       </c>
       <c r="H57" t="n">
         <v>30000</v>
@@ -2196,7 +2196,7 @@
         <v>1.68499994277954</v>
       </c>
       <c r="G63" t="n">
-        <v>1.66124737262726</v>
+        <v>1.66124713420868</v>
       </c>
       <c r="H63" t="n">
         <v>5000</v>
@@ -2283,7 +2283,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G66" t="n">
-        <v>1.67603600025177</v>
+        <v>1.67603588104248</v>
       </c>
       <c r="H66" t="n">
         <v>3000</v>
@@ -2312,7 +2312,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G67" t="n">
-        <v>1.66617691516876</v>
+        <v>1.66617679595947</v>
       </c>
       <c r="H67" t="n">
         <v>10000</v>
@@ -2341,7 +2341,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G68" t="n">
-        <v>1.6858948469162</v>
+        <v>1.68589496612549</v>
       </c>
       <c r="H68" t="n">
         <v>7000</v>
@@ -2486,7 +2486,7 @@
         <v>1.65499997138977</v>
       </c>
       <c r="G73" t="n">
-        <v>1.63167035579681</v>
+        <v>1.63167023658752</v>
       </c>
       <c r="H73" t="n">
         <v>176000</v>
@@ -2602,7 +2602,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G77" t="n">
-        <v>1.6858948469162</v>
+        <v>1.68589496612549</v>
       </c>
       <c r="H77" t="n">
         <v>3000</v>
@@ -2660,7 +2660,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G79" t="n">
-        <v>1.67603600025177</v>
+        <v>1.67603588104248</v>
       </c>
       <c r="H79" t="n">
         <v>16000</v>
@@ -2689,7 +2689,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G80" t="n">
-        <v>1.67603600025177</v>
+        <v>1.67603588104248</v>
       </c>
       <c r="H80" t="n">
         <v>0</v>
@@ -2718,7 +2718,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G81" t="n">
-        <v>1.67603600025177</v>
+        <v>1.67603588104248</v>
       </c>
       <c r="H81" t="n">
         <v>0</v>
@@ -2805,7 +2805,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G84" t="n">
-        <v>1.63659965991974</v>
+        <v>1.63659977912903</v>
       </c>
       <c r="H84" t="n">
         <v>8000</v>
@@ -2921,7 +2921,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G88" t="n">
-        <v>1.57744550704956</v>
+        <v>1.57744562625885</v>
       </c>
       <c r="H88" t="n">
         <v>94000</v>
@@ -2950,7 +2950,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G89" t="n">
-        <v>1.57744550704956</v>
+        <v>1.57744562625885</v>
       </c>
       <c r="H89" t="n">
         <v>0</v>
@@ -2979,7 +2979,7 @@
         <v>1.59500002861023</v>
       </c>
       <c r="G90" t="n">
-        <v>1.57251620292664</v>
+        <v>1.57251608371735</v>
       </c>
       <c r="H90" t="n">
         <v>4000</v>
@@ -3008,7 +3008,7 @@
         <v>1.59500002861023</v>
       </c>
       <c r="G91" t="n">
-        <v>1.57251620292664</v>
+        <v>1.57251608371735</v>
       </c>
       <c r="H91" t="n">
         <v>2000</v>
@@ -3037,7 +3037,7 @@
         <v>1.62999999523163</v>
       </c>
       <c r="G92" t="n">
-        <v>1.60702264308929</v>
+        <v>1.60702252388</v>
       </c>
       <c r="H92" t="n">
         <v>32000</v>
@@ -3066,7 +3066,7 @@
         <v>1.59500002861023</v>
       </c>
       <c r="G93" t="n">
-        <v>1.57251620292664</v>
+        <v>1.57251608371735</v>
       </c>
       <c r="H93" t="n">
         <v>9000</v>
@@ -3095,7 +3095,7 @@
         <v>1.59500002861023</v>
       </c>
       <c r="G94" t="n">
-        <v>1.57251620292664</v>
+        <v>1.57251608371735</v>
       </c>
       <c r="H94" t="n">
         <v>11000</v>
@@ -3124,7 +3124,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G95" t="n">
-        <v>1.58730447292328</v>
+        <v>1.58730459213257</v>
       </c>
       <c r="H95" t="n">
         <v>11000</v>
@@ -3182,7 +3182,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G97" t="n">
-        <v>1.58730447292328</v>
+        <v>1.58730459213257</v>
       </c>
       <c r="H97" t="n">
         <v>31000</v>
@@ -3211,7 +3211,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G98" t="n">
-        <v>1.58730447292328</v>
+        <v>1.58730459213257</v>
       </c>
       <c r="H98" t="n">
         <v>11000</v>
@@ -3356,7 +3356,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G103" t="n">
-        <v>1.63659965991974</v>
+        <v>1.63659977912903</v>
       </c>
       <c r="H103" t="n">
         <v>35000</v>
@@ -3385,7 +3385,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G104" t="n">
-        <v>1.63659965991974</v>
+        <v>1.63659977912903</v>
       </c>
       <c r="H104" t="n">
         <v>14000</v>
@@ -3414,7 +3414,7 @@
         <v>1.63499999046326</v>
       </c>
       <c r="G105" t="n">
-        <v>1.61195206642151</v>
+        <v>1.6119521856308</v>
       </c>
       <c r="H105" t="n">
         <v>26000</v>
@@ -3443,7 +3443,7 @@
         <v>1.66499996185303</v>
       </c>
       <c r="G106" t="n">
-        <v>1.64152920246124</v>
+        <v>1.64152908325195</v>
       </c>
       <c r="H106" t="n">
         <v>2000</v>
@@ -3530,7 +3530,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G109" t="n">
-        <v>1.66617691516876</v>
+        <v>1.66617679595947</v>
       </c>
       <c r="H109" t="n">
         <v>15000</v>
@@ -3559,7 +3559,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G110" t="n">
-        <v>1.67603600025177</v>
+        <v>1.67603588104248</v>
       </c>
       <c r="H110" t="n">
         <v>26000</v>
@@ -3588,7 +3588,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G111" t="n">
-        <v>1.67603600025177</v>
+        <v>1.67603588104248</v>
       </c>
       <c r="H111" t="n">
         <v>53000</v>
@@ -3617,7 +3617,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G112" t="n">
-        <v>1.67603600025177</v>
+        <v>1.67603588104248</v>
       </c>
       <c r="H112" t="n">
         <v>10000</v>
@@ -3646,7 +3646,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G113" t="n">
-        <v>1.67603600025177</v>
+        <v>1.67603588104248</v>
       </c>
       <c r="H113" t="n">
         <v>6000</v>
@@ -3675,7 +3675,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G114" t="n">
-        <v>1.67603600025177</v>
+        <v>1.67603588104248</v>
       </c>
       <c r="H114" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G115" t="n">
-        <v>1.67603600025177</v>
+        <v>1.67603588104248</v>
       </c>
       <c r="H115" t="n">
         <v>22000</v>
@@ -3762,7 +3762,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G117" t="n">
-        <v>1.6858948469162</v>
+        <v>1.68589496612549</v>
       </c>
       <c r="H117" t="n">
         <v>22000</v>
@@ -3791,7 +3791,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G118" t="n">
-        <v>1.6858948469162</v>
+        <v>1.68589496612549</v>
       </c>
       <c r="H118" t="n">
         <v>0</v>
@@ -3878,7 +3878,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G121" t="n">
-        <v>1.87321650981903</v>
+        <v>1.87321662902832</v>
       </c>
       <c r="H121" t="n">
         <v>50000</v>
@@ -3907,7 +3907,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G122" t="n">
-        <v>1.87321650981903</v>
+        <v>1.87321662902832</v>
       </c>
       <c r="H122" t="n">
         <v>39000</v>
@@ -3936,7 +3936,7 @@
         <v>1.875</v>
       </c>
       <c r="G123" t="n">
-        <v>1.84856903553009</v>
+        <v>1.8485689163208</v>
       </c>
       <c r="H123" t="n">
         <v>45000</v>
@@ -4052,7 +4052,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G127" t="n">
-        <v>1.82392132282257</v>
+        <v>1.82392144203186</v>
       </c>
       <c r="H127" t="n">
         <v>7000</v>
@@ -4081,7 +4081,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G128" t="n">
-        <v>1.82392132282257</v>
+        <v>1.82392144203186</v>
       </c>
       <c r="H128" t="n">
         <v>0</v>
@@ -4110,7 +4110,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G129" t="n">
-        <v>1.82392132282257</v>
+        <v>1.82392144203186</v>
       </c>
       <c r="H129" t="n">
         <v>0</v>
@@ -4313,7 +4313,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G136" t="n">
-        <v>1.87321650981903</v>
+        <v>1.87321662902832</v>
       </c>
       <c r="H136" t="n">
         <v>4000</v>
@@ -4400,7 +4400,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G139" t="n">
-        <v>1.87321650981903</v>
+        <v>1.87321662902832</v>
       </c>
       <c r="H139" t="n">
         <v>5000</v>
@@ -4429,7 +4429,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G140" t="n">
-        <v>1.87321650981903</v>
+        <v>1.87321662902832</v>
       </c>
       <c r="H140" t="n">
         <v>18000</v>
@@ -4458,7 +4458,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G141" t="n">
-        <v>1.82392132282257</v>
+        <v>1.82392144203186</v>
       </c>
       <c r="H141" t="n">
         <v>12000</v>
@@ -4487,7 +4487,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G142" t="n">
-        <v>1.82392132282257</v>
+        <v>1.82392144203186</v>
       </c>
       <c r="H142" t="n">
         <v>13000</v>
@@ -4661,7 +4661,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G148" t="n">
-        <v>1.75983774662018</v>
+        <v>1.75983762741089</v>
       </c>
       <c r="H148" t="n">
         <v>12000</v>
@@ -4777,7 +4777,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G152" t="n">
-        <v>1.76969683170319</v>
+        <v>1.76969659328461</v>
       </c>
       <c r="H152" t="n">
         <v>4000</v>
@@ -4835,7 +4835,7 @@
         <v>1.81500005722046</v>
       </c>
       <c r="G154" t="n">
-        <v>1.78941488265991</v>
+        <v>1.78941476345062</v>
       </c>
       <c r="H154" t="n">
         <v>10000</v>
@@ -4864,7 +4864,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G155" t="n">
-        <v>1.82392132282257</v>
+        <v>1.82392144203186</v>
       </c>
       <c r="H155" t="n">
         <v>13000</v>
@@ -4893,7 +4893,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G156" t="n">
-        <v>1.82392132282257</v>
+        <v>1.82392144203186</v>
       </c>
       <c r="H156" t="n">
         <v>0</v>
@@ -4980,7 +4980,7 @@
         <v>1.81500005722046</v>
       </c>
       <c r="G159" t="n">
-        <v>1.78941488265991</v>
+        <v>1.78941476345062</v>
       </c>
       <c r="H159" t="n">
         <v>5000</v>
@@ -5212,7 +5212,7 @@
         <v>1.81500005722046</v>
       </c>
       <c r="G167" t="n">
-        <v>1.78941488265991</v>
+        <v>1.78941476345062</v>
       </c>
       <c r="H167" t="n">
         <v>3000</v>
@@ -5386,7 +5386,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G173" t="n">
-        <v>1.82885110378265</v>
+        <v>1.82885098457336</v>
       </c>
       <c r="H173" t="n">
         <v>18000</v>
@@ -5415,7 +5415,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G174" t="n">
-        <v>1.82885110378265</v>
+        <v>1.82885098457336</v>
       </c>
       <c r="H174" t="n">
         <v>28000</v>
@@ -5502,7 +5502,7 @@
         <v>1.875</v>
       </c>
       <c r="G177" t="n">
-        <v>1.84856903553009</v>
+        <v>1.8485689163208</v>
       </c>
       <c r="H177" t="n">
         <v>20000</v>
@@ -5531,7 +5531,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G178" t="n">
-        <v>1.87814617156982</v>
+        <v>1.87814605236053</v>
       </c>
       <c r="H178" t="n">
         <v>75000</v>
@@ -5618,7 +5618,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G181" t="n">
-        <v>1.90279364585876</v>
+        <v>1.90279352664948</v>
       </c>
       <c r="H181" t="n">
         <v>23000</v>
@@ -5676,7 +5676,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G183" t="n">
-        <v>2.03096103668213</v>
+        <v>2.03096127510071</v>
       </c>
       <c r="H183" t="n">
         <v>24000</v>
@@ -5705,7 +5705,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G184" t="n">
-        <v>2.01124286651611</v>
+        <v>2.01124310493469</v>
       </c>
       <c r="H184" t="n">
         <v>3000</v>
@@ -5734,7 +5734,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G185" t="n">
-        <v>2.03096103668213</v>
+        <v>2.03096127510071</v>
       </c>
       <c r="H185" t="n">
         <v>54000</v>
@@ -5821,7 +5821,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G188" t="n">
-        <v>2.01124286651611</v>
+        <v>2.01124310493469</v>
       </c>
       <c r="H188" t="n">
         <v>4000</v>
@@ -5850,7 +5850,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G189" t="n">
-        <v>2.01124286651611</v>
+        <v>2.01124310493469</v>
       </c>
       <c r="H189" t="n">
         <v>0</v>
@@ -5879,7 +5879,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G190" t="n">
-        <v>1.91758227348328</v>
+        <v>1.91758239269257</v>
       </c>
       <c r="H190" t="n">
         <v>76000</v>
@@ -5908,7 +5908,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G191" t="n">
-        <v>1.9323707818985</v>
+        <v>1.93237090110779</v>
       </c>
       <c r="H191" t="n">
         <v>8000</v>
@@ -5937,7 +5937,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G192" t="n">
-        <v>1.9323707818985</v>
+        <v>1.93237090110779</v>
       </c>
       <c r="H192" t="n">
         <v>2000</v>
@@ -5966,7 +5966,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G193" t="n">
-        <v>1.9323707818985</v>
+        <v>1.93237090110779</v>
       </c>
       <c r="H193" t="n">
         <v>0</v>
@@ -6053,7 +6053,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G196" t="n">
-        <v>1.89293467998505</v>
+        <v>1.89293456077576</v>
       </c>
       <c r="H196" t="n">
         <v>23000</v>
@@ -6140,7 +6140,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G199" t="n">
-        <v>1.91758227348328</v>
+        <v>1.91758239269257</v>
       </c>
       <c r="H199" t="n">
         <v>3000</v>
@@ -6198,7 +6198,7 @@
         <v>1.95500004291534</v>
       </c>
       <c r="G201" t="n">
-        <v>1.92744135856628</v>
+        <v>1.92744123935699</v>
       </c>
       <c r="H201" t="n">
         <v>9000</v>
@@ -6256,7 +6256,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G203" t="n">
-        <v>1.90772318840027</v>
+        <v>1.90772306919098</v>
       </c>
       <c r="H203" t="n">
         <v>39000</v>
@@ -6314,7 +6314,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G205" t="n">
-        <v>1.9323707818985</v>
+        <v>1.93237090110779</v>
       </c>
       <c r="H205" t="n">
         <v>12000</v>
@@ -6343,7 +6343,7 @@
         <v>1.95500004291534</v>
       </c>
       <c r="G206" t="n">
-        <v>1.92744135856628</v>
+        <v>1.92744123935699</v>
       </c>
       <c r="H206" t="n">
         <v>7000</v>
@@ -6372,7 +6372,7 @@
         <v>1.95500004291534</v>
       </c>
       <c r="G207" t="n">
-        <v>1.92744135856628</v>
+        <v>1.92744123935699</v>
       </c>
       <c r="H207" t="n">
         <v>0</v>
@@ -6430,7 +6430,7 @@
         <v>1.9650000333786</v>
       </c>
       <c r="G209" t="n">
-        <v>1.93730056285858</v>
+        <v>1.93730032444</v>
       </c>
       <c r="H209" t="n">
         <v>11000</v>
@@ -6459,7 +6459,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G210" t="n">
-        <v>1.95701837539673</v>
+        <v>1.95701825618744</v>
       </c>
       <c r="H210" t="n">
         <v>16000</v>
@@ -6604,7 +6604,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G215" t="n">
-        <v>1.95701837539673</v>
+        <v>1.95701825618744</v>
       </c>
       <c r="H215" t="n">
         <v>1000</v>
@@ -6691,7 +6691,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G218" t="n">
-        <v>1.89293467998505</v>
+        <v>1.89293456077576</v>
       </c>
       <c r="H218" t="n">
         <v>8000</v>
@@ -6720,7 +6720,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G219" t="n">
-        <v>1.89293467998505</v>
+        <v>1.89293456077576</v>
       </c>
       <c r="H219" t="n">
         <v>1000</v>
@@ -6952,7 +6952,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G227" t="n">
-        <v>1.98166596889496</v>
+        <v>1.98166608810425</v>
       </c>
       <c r="H227" t="n">
         <v>10000</v>
@@ -6981,7 +6981,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G228" t="n">
-        <v>2.00138425827026</v>
+        <v>2.00138378143311</v>
       </c>
       <c r="H228" t="n">
         <v>18000</v>
@@ -7068,7 +7068,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G231" t="n">
-        <v>2.22814178466797</v>
+        <v>2.22814154624939</v>
       </c>
       <c r="H231" t="n">
         <v>86000</v>
@@ -7097,7 +7097,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G232" t="n">
-        <v>2.26757788658142</v>
+        <v>2.267578125</v>
       </c>
       <c r="H232" t="n">
         <v>41000</v>
@@ -7155,7 +7155,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G234" t="n">
-        <v>2.1689875125885</v>
+        <v>2.16898798942566</v>
       </c>
       <c r="H234" t="n">
         <v>85000</v>
@@ -7184,7 +7184,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G235" t="n">
-        <v>2.14926958084106</v>
+        <v>2.14926981925964</v>
       </c>
       <c r="H235" t="n">
         <v>11000</v>
@@ -7213,7 +7213,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G236" t="n">
-        <v>2.19856476783752</v>
+        <v>2.19856452941895</v>
       </c>
       <c r="H236" t="n">
         <v>9000</v>
@@ -7329,7 +7329,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G240" t="n">
-        <v>2.20842385292053</v>
+        <v>2.20842361450195</v>
       </c>
       <c r="H240" t="n">
         <v>35000</v>
@@ -7358,7 +7358,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G241" t="n">
-        <v>2.22814178466797</v>
+        <v>2.22814154624939</v>
       </c>
       <c r="H241" t="n">
         <v>5000</v>
@@ -7416,7 +7416,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G243" t="n">
-        <v>2.26757788658142</v>
+        <v>2.267578125</v>
       </c>
       <c r="H243" t="n">
         <v>5000</v>
@@ -7503,7 +7503,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G246" t="n">
-        <v>2.28729581832886</v>
+        <v>2.28729605674744</v>
       </c>
       <c r="H246" t="n">
         <v>12000</v>
@@ -7532,7 +7532,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G247" t="n">
-        <v>2.28729581832886</v>
+        <v>2.28729605674744</v>
       </c>
       <c r="H247" t="n">
         <v>2000</v>
@@ -7561,7 +7561,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G248" t="n">
-        <v>2.27743721008301</v>
+        <v>2.27743697166443</v>
       </c>
       <c r="H248" t="n">
         <v>7000</v>
@@ -7590,7 +7590,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G249" t="n">
-        <v>2.27743721008301</v>
+        <v>2.27743697166443</v>
       </c>
       <c r="H249" t="n">
         <v>9000</v>
@@ -7619,7 +7619,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G250" t="n">
-        <v>2.27743721008301</v>
+        <v>2.27743697166443</v>
       </c>
       <c r="H250" t="n">
         <v>0</v>
@@ -7706,7 +7706,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G253" t="n">
-        <v>2.40560436248779</v>
+        <v>2.40560460090637</v>
       </c>
       <c r="H253" t="n">
         <v>26000</v>
@@ -7735,7 +7735,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G254" t="n">
-        <v>2.48447680473328</v>
+        <v>2.4844765663147</v>
       </c>
       <c r="H254" t="n">
         <v>14000</v>
@@ -7764,7 +7764,7 @@
         <v>2.5</v>
       </c>
       <c r="G255" t="n">
-        <v>2.46475887298584</v>
+        <v>2.46475863456726</v>
       </c>
       <c r="H255" t="n">
         <v>11000</v>
@@ -7793,7 +7793,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G256" t="n">
-        <v>2.55348992347717</v>
+        <v>2.55348968505859</v>
       </c>
       <c r="H256" t="n">
         <v>21000</v>
@@ -7822,7 +7822,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G257" t="n">
-        <v>2.55348992347717</v>
+        <v>2.55348968505859</v>
       </c>
       <c r="H257" t="n">
         <v>6000</v>
@@ -7851,7 +7851,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G258" t="n">
-        <v>2.61264443397522</v>
+        <v>2.61264419555664</v>
       </c>
       <c r="H258" t="n">
         <v>6000</v>
@@ -7880,7 +7880,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G259" t="n">
-        <v>2.5929262638092</v>
+        <v>2.59292602539062</v>
       </c>
       <c r="H259" t="n">
         <v>5000</v>
@@ -7909,7 +7909,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G260" t="n">
-        <v>2.74081158638</v>
+        <v>2.74081182479858</v>
       </c>
       <c r="H260" t="n">
         <v>51000</v>
@@ -8025,7 +8025,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G264" t="n">
-        <v>3.15489101409912</v>
+        <v>3.1548912525177</v>
       </c>
       <c r="H264" t="n">
         <v>21000</v>
@@ -8054,7 +8054,7 @@
         <v>3</v>
       </c>
       <c r="G265" t="n">
-        <v>2.95771050453186</v>
+        <v>2.95771026611328</v>
       </c>
       <c r="H265" t="n">
         <v>85000</v>
@@ -8083,7 +8083,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G266" t="n">
-        <v>2.87883806228638</v>
+        <v>2.87883830070496</v>
       </c>
       <c r="H266" t="n">
         <v>27000</v>
@@ -8228,7 +8228,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G271" t="n">
-        <v>2.84926128387451</v>
+        <v>2.84926104545593</v>
       </c>
       <c r="H271" t="n">
         <v>21000</v>
@@ -8257,7 +8257,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G272" t="n">
-        <v>2.99714660644531</v>
+        <v>2.99714684486389</v>
       </c>
       <c r="H272" t="n">
         <v>21000</v>
@@ -8286,7 +8286,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G273" t="n">
-        <v>2.96756935119629</v>
+        <v>2.96756958961487</v>
       </c>
       <c r="H273" t="n">
         <v>22000</v>
@@ -8315,7 +8315,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G274" t="n">
-        <v>3.26334071159363</v>
+        <v>3.26334047317505</v>
       </c>
       <c r="H274" t="n">
         <v>121000</v>
@@ -8344,7 +8344,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G275" t="n">
-        <v>3.26334071159363</v>
+        <v>3.26334047317505</v>
       </c>
       <c r="H275" t="n">
         <v>74000</v>
@@ -8402,7 +8402,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G277" t="n">
-        <v>3.17460894584656</v>
+        <v>3.17460918426514</v>
       </c>
       <c r="H277" t="n">
         <v>36000</v>
@@ -8431,7 +8431,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G278" t="n">
-        <v>3.18446826934814</v>
+        <v>3.18446803092957</v>
       </c>
       <c r="H278" t="n">
         <v>19000</v>
@@ -8518,7 +8518,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G281" t="n">
-        <v>3.18446826934814</v>
+        <v>3.18446803092957</v>
       </c>
       <c r="H281" t="n">
         <v>10000</v>
@@ -8547,7 +8547,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G282" t="n">
-        <v>3.21404528617859</v>
+        <v>3.21404504776001</v>
       </c>
       <c r="H282" t="n">
         <v>6000</v>
@@ -8605,7 +8605,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G284" t="n">
-        <v>3.19432759284973</v>
+        <v>3.19432735443115</v>
       </c>
       <c r="H284" t="n">
         <v>4000</v>
@@ -8634,7 +8634,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G285" t="n">
-        <v>3.35207200050354</v>
+        <v>3.35207176208496</v>
       </c>
       <c r="H285" t="n">
         <v>25000</v>
@@ -8692,7 +8692,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G287" t="n">
-        <v>3.60840678215027</v>
+        <v>3.60840702056885</v>
       </c>
       <c r="H287" t="n">
         <v>86000</v>
@@ -8721,7 +8721,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G288" t="n">
-        <v>3.52953410148621</v>
+        <v>3.52953433990479</v>
       </c>
       <c r="H288" t="n">
         <v>19000</v>
@@ -8750,7 +8750,7 @@
         <v>3.75</v>
       </c>
       <c r="G289" t="n">
-        <v>3.69713807106018</v>
+        <v>3.6971378326416</v>
       </c>
       <c r="H289" t="n">
         <v>24000</v>
@@ -8808,7 +8808,7 @@
         <v>3.75</v>
       </c>
       <c r="G291" t="n">
-        <v>3.69713807106018</v>
+        <v>3.6971378326416</v>
       </c>
       <c r="H291" t="n">
         <v>16000</v>
@@ -8837,7 +8837,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G292" t="n">
-        <v>3.64784264564514</v>
+        <v>3.64784288406372</v>
       </c>
       <c r="H292" t="n">
         <v>5000</v>
@@ -8866,7 +8866,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G293" t="n">
-        <v>3.64784264564514</v>
+        <v>3.64784288406372</v>
       </c>
       <c r="H293" t="n">
         <v>16000</v>
@@ -8895,7 +8895,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G294" t="n">
-        <v>3.53939366340637</v>
+        <v>3.53939318656921</v>
       </c>
       <c r="H294" t="n">
         <v>30000</v>
@@ -8924,7 +8924,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G295" t="n">
-        <v>3.51967549324036</v>
+        <v>3.51967525482178</v>
       </c>
       <c r="H295" t="n">
         <v>95000</v>
@@ -9185,7 +9185,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G304" t="n">
-        <v>3.52953410148621</v>
+        <v>3.52953433990479</v>
       </c>
       <c r="H304" t="n">
         <v>2000</v>
@@ -9214,7 +9214,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G305" t="n">
-        <v>3.52953410148621</v>
+        <v>3.52953433990479</v>
       </c>
       <c r="H305" t="n">
         <v>1000</v>
@@ -9243,7 +9243,7 @@
         <v>3.75</v>
       </c>
       <c r="G306" t="n">
-        <v>3.69713807106018</v>
+        <v>3.6971378326416</v>
       </c>
       <c r="H306" t="n">
         <v>16000</v>
@@ -9272,7 +9272,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G307" t="n">
-        <v>3.9731912612915</v>
+        <v>3.97319102287292</v>
       </c>
       <c r="H307" t="n">
         <v>45000</v>
@@ -9330,7 +9330,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G309" t="n">
-        <v>4.35769414901733</v>
+        <v>4.35769367218018</v>
       </c>
       <c r="H309" t="n">
         <v>26000</v>
@@ -9359,7 +9359,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G310" t="n">
-        <v>4.337975025177</v>
+        <v>4.33797597885132</v>
       </c>
       <c r="H310" t="n">
         <v>1000</v>
@@ -9446,7 +9446,7 @@
         <v>4</v>
       </c>
       <c r="G313" t="n">
-        <v>3.94361400604248</v>
+        <v>3.9436137676239</v>
       </c>
       <c r="H313" t="n">
         <v>19000</v>
@@ -9504,7 +9504,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G315" t="n">
-        <v>4.09149932861328</v>
+        <v>4.09149980545044</v>
       </c>
       <c r="H315" t="n">
         <v>8000</v>
@@ -9591,7 +9591,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G318" t="n">
-        <v>4.17037153244019</v>
+        <v>4.17037200927734</v>
       </c>
       <c r="H318" t="n">
         <v>10000</v>
@@ -9649,7 +9649,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G320" t="n">
-        <v>4.23938608169556</v>
+        <v>4.23938512802124</v>
       </c>
       <c r="H320" t="n">
         <v>9000</v>
@@ -9678,7 +9678,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G321" t="n">
-        <v>4.130934715271</v>
+        <v>4.13093519210815</v>
       </c>
       <c r="H321" t="n">
         <v>4000</v>
@@ -9707,7 +9707,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G322" t="n">
-        <v>4.10135793685913</v>
+        <v>4.10135841369629</v>
       </c>
       <c r="H322" t="n">
         <v>4000</v>
@@ -9736,7 +9736,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G323" t="n">
-        <v>4.18023061752319</v>
+        <v>4.18023014068604</v>
       </c>
       <c r="H323" t="n">
         <v>2000</v>
@@ -9765,7 +9765,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G324" t="n">
-        <v>4.18023061752319</v>
+        <v>4.18023014068604</v>
       </c>
       <c r="H324" t="n">
         <v>0</v>
@@ -9794,7 +9794,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G325" t="n">
-        <v>4.06192207336426</v>
+        <v>4.06192255020142</v>
       </c>
       <c r="H325" t="n">
         <v>7000</v>
@@ -9823,7 +9823,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G326" t="n">
-        <v>4.00276851654053</v>
+        <v>4.00276756286621</v>
       </c>
       <c r="H326" t="n">
         <v>5000</v>
@@ -9910,7 +9910,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G329" t="n">
-        <v>4.02248573303223</v>
+        <v>4.02248620986938</v>
       </c>
       <c r="H329" t="n">
         <v>5000</v>
@@ -10084,7 +10084,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G335" t="n">
-        <v>4.17037153244019</v>
+        <v>4.17037200927734</v>
       </c>
       <c r="H335" t="n">
         <v>3000</v>
@@ -10113,7 +10113,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G336" t="n">
-        <v>4.00276851654053</v>
+        <v>4.00276756286621</v>
       </c>
       <c r="H336" t="n">
         <v>3000</v>
@@ -10142,7 +10142,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G337" t="n">
-        <v>4.00276851654053</v>
+        <v>4.00276756286621</v>
       </c>
       <c r="H337" t="n">
         <v>0</v>
@@ -10287,7 +10287,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G342" t="n">
-        <v>4.06192207336426</v>
+        <v>4.06192255020142</v>
       </c>
       <c r="H342" t="n">
         <v>5000</v>
@@ -10432,7 +10432,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G347" t="n">
-        <v>4.02248573303223</v>
+        <v>4.02248620986938</v>
       </c>
       <c r="H347" t="n">
         <v>3000</v>
@@ -10461,7 +10461,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G348" t="n">
-        <v>4.02248573303223</v>
+        <v>4.02248620986938</v>
       </c>
       <c r="H348" t="n">
         <v>16500</v>
@@ -10490,7 +10490,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G349" t="n">
-        <v>4.21966648101807</v>
+        <v>4.21966695785522</v>
       </c>
       <c r="H349" t="n">
         <v>21000</v>
@@ -10519,7 +10519,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G350" t="n">
-        <v>4.23938608169556</v>
+        <v>4.23938512802124</v>
       </c>
       <c r="H350" t="n">
         <v>24000</v>
@@ -10548,7 +10548,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G351" t="n">
-        <v>4.23938608169556</v>
+        <v>4.23938512802124</v>
       </c>
       <c r="H351" t="n">
         <v>4500</v>
@@ -10606,7 +10606,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G353" t="n">
-        <v>4.130934715271</v>
+        <v>4.13093519210815</v>
       </c>
       <c r="H353" t="n">
         <v>9000</v>
@@ -10780,7 +10780,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G359" t="n">
-        <v>4.21966648101807</v>
+        <v>4.21966695785522</v>
       </c>
       <c r="H359" t="n">
         <v>14500</v>
@@ -10867,7 +10867,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G362" t="n">
-        <v>4.09149932861328</v>
+        <v>4.09149980545044</v>
       </c>
       <c r="H362" t="n">
         <v>4500</v>
@@ -10896,7 +10896,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G363" t="n">
-        <v>4.1210765838623</v>
+        <v>4.12107610702515</v>
       </c>
       <c r="H363" t="n">
         <v>500</v>
@@ -10925,7 +10925,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G364" t="n">
-        <v>4.1210765838623</v>
+        <v>4.12107610702515</v>
       </c>
       <c r="H364" t="n">
         <v>0</v>
@@ -10954,7 +10954,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G365" t="n">
-        <v>4.1210765838623</v>
+        <v>4.12107610702515</v>
       </c>
       <c r="H365" t="n">
         <v>0</v>
@@ -11099,7 +11099,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G370" t="n">
-        <v>4.10135793685913</v>
+        <v>4.10135841369629</v>
       </c>
       <c r="H370" t="n">
         <v>4500</v>
@@ -11128,7 +11128,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G371" t="n">
-        <v>4.01262712478638</v>
+        <v>4.01262760162354</v>
       </c>
       <c r="H371" t="n">
         <v>6000</v>
@@ -11360,7 +11360,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G379" t="n">
-        <v>4.21966648101807</v>
+        <v>4.21966695785522</v>
       </c>
       <c r="H379" t="n">
         <v>67000</v>
@@ -11389,7 +11389,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G380" t="n">
-        <v>4.21966648101807</v>
+        <v>4.21966695785522</v>
       </c>
       <c r="H380" t="n">
         <v>3000</v>
@@ -11447,7 +11447,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G382" t="n">
-        <v>4.29853916168213</v>
+        <v>4.29853963851929</v>
       </c>
       <c r="H382" t="n">
         <v>35000</v>
@@ -11505,7 +11505,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G384" t="n">
-        <v>4.337975025177</v>
+        <v>4.33797597885132</v>
       </c>
       <c r="H384" t="n">
         <v>17000</v>
@@ -11534,7 +11534,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G385" t="n">
-        <v>4.36755180358887</v>
+        <v>4.36755228042603</v>
       </c>
       <c r="H385" t="n">
         <v>4000</v>
@@ -11592,7 +11592,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G387" t="n">
-        <v>4.36755180358887</v>
+        <v>4.36755228042603</v>
       </c>
       <c r="H387" t="n">
         <v>6000</v>
@@ -11621,7 +11621,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G388" t="n">
-        <v>4.36755180358887</v>
+        <v>4.36755228042603</v>
       </c>
       <c r="H388" t="n">
         <v>13500</v>
@@ -11679,7 +11679,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G390" t="n">
-        <v>4.337975025177</v>
+        <v>4.33797597885132</v>
       </c>
       <c r="H390" t="n">
         <v>15000</v>
@@ -11766,7 +11766,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G393" t="n">
-        <v>4.337975025177</v>
+        <v>4.33797597885132</v>
       </c>
       <c r="H393" t="n">
         <v>6000</v>
@@ -11795,7 +11795,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G394" t="n">
-        <v>4.40698766708374</v>
+        <v>4.40698862075806</v>
       </c>
       <c r="H394" t="n">
         <v>2000</v>
@@ -11998,7 +11998,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G401" t="n">
-        <v>4.18023061752319</v>
+        <v>4.18023014068604</v>
       </c>
       <c r="H401" t="n">
         <v>33500</v>
@@ -12056,7 +12056,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G403" t="n">
-        <v>4.29853916168213</v>
+        <v>4.29853963851929</v>
       </c>
       <c r="H403" t="n">
         <v>26500</v>
@@ -12085,7 +12085,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G404" t="n">
-        <v>4.337975025177</v>
+        <v>4.33797597885132</v>
       </c>
       <c r="H404" t="n">
         <v>37500</v>
@@ -12114,7 +12114,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G405" t="n">
-        <v>4.38727045059204</v>
+        <v>4.38726997375488</v>
       </c>
       <c r="H405" t="n">
         <v>13000</v>
@@ -12143,7 +12143,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G406" t="n">
-        <v>4.39712953567505</v>
+        <v>4.39712905883789</v>
       </c>
       <c r="H406" t="n">
         <v>19500</v>
@@ -12172,7 +12172,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G407" t="n">
-        <v>4.38727045059204</v>
+        <v>4.38726997375488</v>
       </c>
       <c r="H407" t="n">
         <v>6000</v>
@@ -12201,7 +12201,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G408" t="n">
-        <v>4.38727045059204</v>
+        <v>4.38726997375488</v>
       </c>
       <c r="H408" t="n">
         <v>85000</v>
@@ -12230,7 +12230,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G409" t="n">
-        <v>4.49571990966797</v>
+        <v>4.49571943283081</v>
       </c>
       <c r="H409" t="n">
         <v>23000</v>
@@ -12259,7 +12259,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G410" t="n">
-        <v>4.63374662399292</v>
+        <v>4.63374614715576</v>
       </c>
       <c r="H410" t="n">
         <v>92000</v>
@@ -12317,7 +12317,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G412" t="n">
-        <v>5.30416107177734</v>
+        <v>5.30416059494019</v>
       </c>
       <c r="H412" t="n">
         <v>82500</v>
@@ -12375,7 +12375,7 @@
         <v>5</v>
       </c>
       <c r="G414" t="n">
-        <v>4.92951774597168</v>
+        <v>4.92951726913452</v>
       </c>
       <c r="H414" t="n">
         <v>45500</v>
@@ -12404,7 +12404,7 @@
         <v>5</v>
       </c>
       <c r="G415" t="n">
-        <v>4.92951774597168</v>
+        <v>4.92951726913452</v>
       </c>
       <c r="H415" t="n">
         <v>14500</v>
@@ -12433,7 +12433,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G416" t="n">
-        <v>4.96895360946655</v>
+        <v>4.96895313262939</v>
       </c>
       <c r="H416" t="n">
         <v>6000</v>
@@ -12462,7 +12462,7 @@
         <v>5</v>
       </c>
       <c r="G417" t="n">
-        <v>4.92951774597168</v>
+        <v>4.92951726913452</v>
       </c>
       <c r="H417" t="n">
         <v>7500</v>
@@ -12491,7 +12491,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G418" t="n">
-        <v>4.98867177963257</v>
+        <v>4.98867130279541</v>
       </c>
       <c r="H418" t="n">
         <v>23500</v>
@@ -12549,7 +12549,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G420" t="n">
-        <v>5.00838899612427</v>
+        <v>5.00838947296143</v>
       </c>
       <c r="H420" t="n">
         <v>4500</v>
@@ -12578,7 +12578,7 @@
         <v>5</v>
       </c>
       <c r="G421" t="n">
-        <v>4.92951774597168</v>
+        <v>4.92951726913452</v>
       </c>
       <c r="H421" t="n">
         <v>8500</v>
@@ -12607,7 +12607,7 @@
         <v>5</v>
       </c>
       <c r="G422" t="n">
-        <v>4.92951774597168</v>
+        <v>4.92951726913452</v>
       </c>
       <c r="H422" t="n">
         <v>9500</v>
@@ -12636,7 +12636,7 @@
         <v>5</v>
       </c>
       <c r="G423" t="n">
-        <v>4.92951774597168</v>
+        <v>4.92951726913452</v>
       </c>
       <c r="H423" t="n">
         <v>38500</v>
@@ -12723,7 +12723,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G426" t="n">
-        <v>5.08726119995117</v>
+        <v>5.08726167678833</v>
       </c>
       <c r="H426" t="n">
         <v>1500</v>
@@ -12781,7 +12781,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G428" t="n">
-        <v>5.00838899612427</v>
+        <v>5.00838947296143</v>
       </c>
       <c r="H428" t="n">
         <v>2500</v>
@@ -12810,7 +12810,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G429" t="n">
-        <v>5.12669801712036</v>
+        <v>5.1266975402832</v>
       </c>
       <c r="H429" t="n">
         <v>7000</v>
@@ -12839,7 +12839,7 @@
         <v>5</v>
       </c>
       <c r="G430" t="n">
-        <v>4.92951774597168</v>
+        <v>4.92951726913452</v>
       </c>
       <c r="H430" t="n">
         <v>8500</v>
@@ -12868,7 +12868,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G431" t="n">
-        <v>4.98867177963257</v>
+        <v>4.98867130279541</v>
       </c>
       <c r="H431" t="n">
         <v>8000</v>
@@ -12897,7 +12897,7 @@
         <v>5</v>
       </c>
       <c r="G432" t="n">
-        <v>4.92951774597168</v>
+        <v>4.92951726913452</v>
       </c>
       <c r="H432" t="n">
         <v>1000</v>
@@ -12955,7 +12955,7 @@
         <v>5</v>
       </c>
       <c r="G434" t="n">
-        <v>4.92951774597168</v>
+        <v>4.92951726913452</v>
       </c>
       <c r="H434" t="n">
         <v>7000</v>
@@ -12984,7 +12984,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G435" t="n">
-        <v>4.78163146972656</v>
+        <v>4.78163194656372</v>
       </c>
       <c r="H435" t="n">
         <v>22500</v>
@@ -13042,7 +13042,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G437" t="n">
-        <v>4.90979957580566</v>
+        <v>4.90979862213135</v>
       </c>
       <c r="H437" t="n">
         <v>16000</v>
@@ -13071,7 +13071,7 @@
         <v>5</v>
       </c>
       <c r="G438" t="n">
-        <v>4.92951774597168</v>
+        <v>4.92951726913452</v>
       </c>
       <c r="H438" t="n">
         <v>7500</v>
@@ -13129,7 +13129,7 @@
         <v>5</v>
       </c>
       <c r="G440" t="n">
-        <v>4.92951774597168</v>
+        <v>4.92951726913452</v>
       </c>
       <c r="H440" t="n">
         <v>2000</v>
@@ -13187,7 +13187,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G442" t="n">
-        <v>4.90979957580566</v>
+        <v>4.90979862213135</v>
       </c>
       <c r="H442" t="n">
         <v>11000</v>
@@ -13274,7 +13274,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G445" t="n">
-        <v>4.96895360946655</v>
+        <v>4.96895313262939</v>
       </c>
       <c r="H445" t="n">
         <v>2500</v>
@@ -13361,7 +13361,7 @@
         <v>5</v>
       </c>
       <c r="G448" t="n">
-        <v>4.92951774597168</v>
+        <v>4.92951726913452</v>
       </c>
       <c r="H448" t="n">
         <v>19060</v>
@@ -13390,7 +13390,7 @@
         <v>5</v>
       </c>
       <c r="G449" t="n">
-        <v>4.92951774597168</v>
+        <v>4.92951726913452</v>
       </c>
       <c r="H449" t="n">
         <v>10200</v>
@@ -13419,7 +13419,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G450" t="n">
-        <v>4.83092737197876</v>
+        <v>4.8309268951416</v>
       </c>
       <c r="H450" t="n">
         <v>30540</v>
@@ -13448,7 +13448,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G451" t="n">
-        <v>4.83092737197876</v>
+        <v>4.8309268951416</v>
       </c>
       <c r="H451" t="n">
         <v>3150</v>
@@ -13477,7 +13477,7 @@
         <v>5</v>
       </c>
       <c r="G452" t="n">
-        <v>4.92951774597168</v>
+        <v>4.92951726913452</v>
       </c>
       <c r="H452" t="n">
         <v>1500</v>
@@ -13506,7 +13506,7 @@
         <v>5</v>
       </c>
       <c r="G453" t="n">
-        <v>4.92951774597168</v>
+        <v>4.92951726913452</v>
       </c>
       <c r="H453" t="n">
         <v>900</v>
@@ -13593,7 +13593,7 @@
         <v>5</v>
       </c>
       <c r="G456" t="n">
-        <v>4.92951774597168</v>
+        <v>4.92951726913452</v>
       </c>
       <c r="H456" t="n">
         <v>2220</v>
@@ -13651,7 +13651,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G458" t="n">
-        <v>5.50134134292603</v>
+        <v>5.50134086608887</v>
       </c>
       <c r="H458" t="n">
         <v>75450</v>
@@ -13680,7 +13680,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G459" t="n">
-        <v>5.26472473144531</v>
+        <v>5.26472520828247</v>
       </c>
       <c r="H459" t="n">
         <v>23670</v>
@@ -13738,7 +13738,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G461" t="n">
-        <v>5.30416107177734</v>
+        <v>5.30416059494019</v>
       </c>
       <c r="H461" t="n">
         <v>2900</v>
@@ -13767,7 +13767,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G462" t="n">
-        <v>5.22528886795044</v>
+        <v>5.22528839111328</v>
       </c>
       <c r="H462" t="n">
         <v>3000</v>
@@ -13796,7 +13796,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G463" t="n">
-        <v>5.22528886795044</v>
+        <v>5.22528839111328</v>
       </c>
       <c r="H463" t="n">
         <v>2000</v>
@@ -13854,7 +13854,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G465" t="n">
-        <v>5.16613435745239</v>
+        <v>5.16613388061523</v>
       </c>
       <c r="H465" t="n">
         <v>650</v>
@@ -13883,7 +13883,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G466" t="n">
-        <v>5.12669801712036</v>
+        <v>5.1266975402832</v>
       </c>
       <c r="H466" t="n">
         <v>7070</v>
@@ -13912,7 +13912,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G467" t="n">
-        <v>5.12669801712036</v>
+        <v>5.1266975402832</v>
       </c>
       <c r="H467" t="n">
         <v>200</v>
@@ -13941,7 +13941,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G468" t="n">
-        <v>5.16613435745239</v>
+        <v>5.16613388061523</v>
       </c>
       <c r="H468" t="n">
         <v>10280</v>
@@ -13970,7 +13970,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G469" t="n">
-        <v>5.22528886795044</v>
+        <v>5.22528839111328</v>
       </c>
       <c r="H469" t="n">
         <v>3400</v>
@@ -13999,7 +13999,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G470" t="n">
-        <v>5.08726119995117</v>
+        <v>5.08726167678833</v>
       </c>
       <c r="H470" t="n">
         <v>2920</v>
@@ -14028,7 +14028,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G471" t="n">
-        <v>5.22528886795044</v>
+        <v>5.22528839111328</v>
       </c>
       <c r="H471" t="n">
         <v>450</v>
@@ -14057,7 +14057,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G472" t="n">
-        <v>5.22528886795044</v>
+        <v>5.22528839111328</v>
       </c>
       <c r="H472" t="n">
         <v>0</v>
@@ -14115,7 +14115,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G474" t="n">
-        <v>4.98867177963257</v>
+        <v>4.98867130279541</v>
       </c>
       <c r="H474" t="n">
         <v>17780</v>
@@ -14202,7 +14202,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G477" t="n">
-        <v>5.00838899612427</v>
+        <v>5.00838947296143</v>
       </c>
       <c r="H477" t="n">
         <v>1250</v>
@@ -14231,7 +14231,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G478" t="n">
-        <v>4.96895360946655</v>
+        <v>4.96895313262939</v>
       </c>
       <c r="H478" t="n">
         <v>3060</v>
@@ -14347,7 +14347,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G482" t="n">
-        <v>5.10697984695435</v>
+        <v>5.10697937011719</v>
       </c>
       <c r="H482" t="n">
         <v>7170</v>
@@ -14376,7 +14376,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G483" t="n">
-        <v>5.12669801712036</v>
+        <v>5.1266975402832</v>
       </c>
       <c r="H483" t="n">
         <v>4620</v>
@@ -14405,7 +14405,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G484" t="n">
-        <v>5.12669801712036</v>
+        <v>5.1266975402832</v>
       </c>
       <c r="H484" t="n">
         <v>6620</v>
@@ -14434,7 +14434,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G485" t="n">
-        <v>5.12669801712036</v>
+        <v>5.1266975402832</v>
       </c>
       <c r="H485" t="n">
         <v>11880</v>
@@ -14492,7 +14492,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G487" t="n">
-        <v>5.16613435745239</v>
+        <v>5.16613388061523</v>
       </c>
       <c r="H487" t="n">
         <v>18380</v>
@@ -14550,7 +14550,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G489" t="n">
-        <v>4.98867177963257</v>
+        <v>4.98867130279541</v>
       </c>
       <c r="H489" t="n">
         <v>21530</v>
@@ -14579,7 +14579,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G490" t="n">
-        <v>5.12669801712036</v>
+        <v>5.1266975402832</v>
       </c>
       <c r="H490" t="n">
         <v>26550</v>
@@ -14608,7 +14608,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G491" t="n">
-        <v>4.98867177963257</v>
+        <v>4.98867130279541</v>
       </c>
       <c r="H491" t="n">
         <v>28100</v>
@@ -14637,7 +14637,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G492" t="n">
-        <v>4.96895360946655</v>
+        <v>4.96895313262939</v>
       </c>
       <c r="H492" t="n">
         <v>10980</v>
@@ -14666,7 +14666,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G493" t="n">
-        <v>5.16613435745239</v>
+        <v>5.16613388061523</v>
       </c>
       <c r="H493" t="n">
         <v>5990</v>
@@ -14695,7 +14695,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G494" t="n">
-        <v>5.10697984695435</v>
+        <v>5.10697937011719</v>
       </c>
       <c r="H494" t="n">
         <v>11420</v>
@@ -14724,7 +14724,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G495" t="n">
-        <v>5.08726119995117</v>
+        <v>5.08726167678833</v>
       </c>
       <c r="H495" t="n">
         <v>6900</v>
@@ -14927,7 +14927,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G502" t="n">
-        <v>5.08726119995117</v>
+        <v>5.08726167678833</v>
       </c>
       <c r="H502" t="n">
         <v>5550</v>
@@ -14985,7 +14985,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G504" t="n">
-        <v>4.83092737197876</v>
+        <v>4.8309268951416</v>
       </c>
       <c r="H504" t="n">
         <v>16000</v>
@@ -15014,7 +15014,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G505" t="n">
-        <v>4.98867177963257</v>
+        <v>4.98867130279541</v>
       </c>
       <c r="H505" t="n">
         <v>4800</v>
@@ -15043,7 +15043,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G506" t="n">
-        <v>5.12669801712036</v>
+        <v>5.1266975402832</v>
       </c>
       <c r="H506" t="n">
         <v>5270</v>
@@ -15072,7 +15072,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G507" t="n">
-        <v>5.10697984695435</v>
+        <v>5.10697937011719</v>
       </c>
       <c r="H507" t="n">
         <v>3690</v>
@@ -15101,7 +15101,7 @@
         <v>5</v>
       </c>
       <c r="G508" t="n">
-        <v>4.92951774597168</v>
+        <v>4.92951726913452</v>
       </c>
       <c r="H508" t="n">
         <v>5700</v>
@@ -15159,7 +15159,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G510" t="n">
-        <v>4.98867177963257</v>
+        <v>4.98867130279541</v>
       </c>
       <c r="H510" t="n">
         <v>1110</v>
@@ -15217,7 +15217,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G512" t="n">
-        <v>5.08726119995117</v>
+        <v>5.08726167678833</v>
       </c>
       <c r="H512" t="n">
         <v>14440</v>
@@ -15246,7 +15246,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G513" t="n">
-        <v>5.00838899612427</v>
+        <v>5.00838947296143</v>
       </c>
       <c r="H513" t="n">
         <v>10130</v>
@@ -15275,7 +15275,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G514" t="n">
-        <v>4.96895360946655</v>
+        <v>4.96895313262939</v>
       </c>
       <c r="H514" t="n">
         <v>2590</v>
@@ -15333,7 +15333,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G516" t="n">
-        <v>5.00838899612427</v>
+        <v>5.00838947296143</v>
       </c>
       <c r="H516" t="n">
         <v>640</v>
@@ -15391,7 +15391,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G518" t="n">
-        <v>5.00838899612427</v>
+        <v>5.00838947296143</v>
       </c>
       <c r="H518" t="n">
         <v>3020</v>
@@ -15420,7 +15420,7 @@
         <v>5</v>
       </c>
       <c r="G519" t="n">
-        <v>4.92951774597168</v>
+        <v>4.92951726913452</v>
       </c>
       <c r="H519" t="n">
         <v>12340</v>
@@ -15623,7 +15623,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G526" t="n">
-        <v>5.00838899612427</v>
+        <v>5.00838947296143</v>
       </c>
       <c r="H526" t="n">
         <v>2400</v>
@@ -15681,7 +15681,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G528" t="n">
-        <v>4.80134916305542</v>
+        <v>4.80134963989258</v>
       </c>
       <c r="H528" t="n">
         <v>15650</v>
@@ -15739,7 +15739,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G530" t="n">
-        <v>4.73233699798584</v>
+        <v>4.73233652114868</v>
       </c>
       <c r="H530" t="n">
         <v>6730</v>
@@ -15768,7 +15768,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G531" t="n">
-        <v>4.80134916305542</v>
+        <v>4.80134963989258</v>
       </c>
       <c r="H531" t="n">
         <v>6500</v>
@@ -15826,7 +15826,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G533" t="n">
-        <v>4.79149150848389</v>
+        <v>4.79149103164673</v>
       </c>
       <c r="H533" t="n">
         <v>6340</v>
@@ -15855,7 +15855,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G534" t="n">
-        <v>4.73233699798584</v>
+        <v>4.73233652114868</v>
       </c>
       <c r="H534" t="n">
         <v>13910</v>
@@ -15884,7 +15884,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G535" t="n">
-        <v>4.73233699798584</v>
+        <v>4.73233652114868</v>
       </c>
       <c r="H535" t="n">
         <v>3100</v>
@@ -15942,7 +15942,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G537" t="n">
-        <v>4.73233699798584</v>
+        <v>4.73233652114868</v>
       </c>
       <c r="H537" t="n">
         <v>2420</v>
@@ -15971,7 +15971,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G538" t="n">
-        <v>4.8999400138855</v>
+        <v>4.89993953704834</v>
       </c>
       <c r="H538" t="n">
         <v>2830</v>
@@ -16029,7 +16029,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G540" t="n">
-        <v>4.83092737197876</v>
+        <v>4.8309268951416</v>
       </c>
       <c r="H540" t="n">
         <v>1600</v>
@@ -16174,7 +16174,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G545" t="n">
-        <v>4.83092737197876</v>
+        <v>4.8309268951416</v>
       </c>
       <c r="H545" t="n">
         <v>1200</v>
@@ -16203,7 +16203,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G546" t="n">
-        <v>4.75205516815186</v>
+        <v>4.75205564498901</v>
       </c>
       <c r="H546" t="n">
         <v>6100</v>
@@ -16261,7 +16261,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G548" t="n">
-        <v>4.57422351837158</v>
+        <v>4.57422399520874</v>
       </c>
       <c r="H548" t="n">
         <v>17160</v>
@@ -16348,7 +16348,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G551" t="n">
-        <v>4.74217510223389</v>
+        <v>4.7421760559082</v>
       </c>
       <c r="H551" t="n">
         <v>730</v>
@@ -16377,7 +16377,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G552" t="n">
-        <v>4.78169393539429</v>
+        <v>4.78169345855713</v>
       </c>
       <c r="H552" t="n">
         <v>1640</v>
@@ -16406,7 +16406,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G553" t="n">
-        <v>4.78169393539429</v>
+        <v>4.78169345855713</v>
       </c>
       <c r="H553" t="n">
         <v>0</v>
@@ -16435,7 +16435,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G554" t="n">
-        <v>4.78169393539429</v>
+        <v>4.78169345855713</v>
       </c>
       <c r="H554" t="n">
         <v>0</v>
@@ -16493,7 +16493,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G556" t="n">
-        <v>4.74217510223389</v>
+        <v>4.7421760559082</v>
       </c>
       <c r="H556" t="n">
         <v>13120</v>
@@ -16522,7 +16522,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G557" t="n">
-        <v>4.74217510223389</v>
+        <v>4.7421760559082</v>
       </c>
       <c r="H557" t="n">
         <v>260</v>
@@ -16638,7 +16638,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G561" t="n">
-        <v>4.79157257080078</v>
+        <v>4.79157304763794</v>
       </c>
       <c r="H561" t="n">
         <v>2000</v>
@@ -16667,7 +16667,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G562" t="n">
-        <v>4.92988634109497</v>
+        <v>4.92988681793213</v>
       </c>
       <c r="H562" t="n">
         <v>2500</v>
@@ -16957,7 +16957,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G572" t="n">
-        <v>4.55446434020996</v>
+        <v>4.55446481704712</v>
       </c>
       <c r="H572" t="n">
         <v>2940</v>
@@ -17073,7 +17073,7 @@
         <v>4.5</v>
       </c>
       <c r="G576" t="n">
-        <v>4.4457893371582</v>
+        <v>4.44578981399536</v>
       </c>
       <c r="H576" t="n">
         <v>2400</v>
@@ -17102,7 +17102,7 @@
         <v>4.5</v>
       </c>
       <c r="G577" t="n">
-        <v>4.4457893371582</v>
+        <v>4.44578981399536</v>
       </c>
       <c r="H577" t="n">
         <v>1890</v>
@@ -17131,7 +17131,7 @@
         <v>4.5</v>
       </c>
       <c r="G578" t="n">
-        <v>4.4457893371582</v>
+        <v>4.44578981399536</v>
       </c>
       <c r="H578" t="n">
         <v>550</v>
@@ -17305,7 +17305,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G584" t="n">
-        <v>4.78169393539429</v>
+        <v>4.78169345855713</v>
       </c>
       <c r="H584" t="n">
         <v>3210</v>
@@ -17363,7 +17363,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G586" t="n">
-        <v>4.74217510223389</v>
+        <v>4.7421760559082</v>
       </c>
       <c r="H586" t="n">
         <v>200</v>
@@ -17508,7 +17508,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G591" t="n">
-        <v>4.34699392318726</v>
+        <v>4.34699440002441</v>
       </c>
       <c r="H591" t="n">
         <v>420</v>
@@ -17537,7 +17537,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G592" t="n">
-        <v>4.34699392318726</v>
+        <v>4.34699440002441</v>
       </c>
       <c r="H592" t="n">
         <v>35740</v>
@@ -17566,7 +17566,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G593" t="n">
-        <v>4.34699392318726</v>
+        <v>4.34699440002441</v>
       </c>
       <c r="H593" t="n">
         <v>10500</v>
@@ -17595,7 +17595,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G594" t="n">
-        <v>4.48530721664429</v>
+        <v>4.48530769348145</v>
       </c>
       <c r="H594" t="n">
         <v>1520</v>
@@ -17653,7 +17653,7 @@
         <v>4.5</v>
       </c>
       <c r="G596" t="n">
-        <v>4.4457893371582</v>
+        <v>4.44578981399536</v>
       </c>
       <c r="H596" t="n">
         <v>3880</v>
@@ -17769,7 +17769,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G600" t="n">
-        <v>4.48530721664429</v>
+        <v>4.48530769348145</v>
       </c>
       <c r="H600" t="n">
         <v>1360</v>
@@ -17914,7 +17914,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G605" t="n">
-        <v>4.83109092712402</v>
+        <v>4.83109140396118</v>
       </c>
       <c r="H605" t="n">
         <v>9220</v>
@@ -18030,7 +18030,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G609" t="n">
-        <v>4.81133127212524</v>
+        <v>4.8113317489624</v>
       </c>
       <c r="H609" t="n">
         <v>1910</v>
@@ -18088,7 +18088,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G611" t="n">
-        <v>4.72241592407227</v>
+        <v>4.72241640090942</v>
       </c>
       <c r="H611" t="n">
         <v>4980</v>
@@ -18146,7 +18146,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G613" t="n">
-        <v>4.78169393539429</v>
+        <v>4.78169345855713</v>
       </c>
       <c r="H613" t="n">
         <v>1500</v>
@@ -18204,7 +18204,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G615" t="n">
-        <v>4.88048839569092</v>
+        <v>4.88048887252808</v>
       </c>
       <c r="H615" t="n">
         <v>1500</v>
@@ -18465,7 +18465,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G624" t="n">
-        <v>5.03856182098389</v>
+        <v>5.03856134414673</v>
       </c>
       <c r="H624" t="n">
         <v>200</v>
@@ -18494,7 +18494,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G625" t="n">
-        <v>5.03856182098389</v>
+        <v>5.03856134414673</v>
       </c>
       <c r="H625" t="n">
         <v>2500</v>
@@ -18523,7 +18523,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G626" t="n">
-        <v>4.92988634109497</v>
+        <v>4.92988681793213</v>
       </c>
       <c r="H626" t="n">
         <v>49150</v>
@@ -18726,7 +18726,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G633" t="n">
-        <v>4.81133127212524</v>
+        <v>4.8113317489624</v>
       </c>
       <c r="H633" t="n">
         <v>200</v>
@@ -18755,7 +18755,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G634" t="n">
-        <v>4.92988634109497</v>
+        <v>4.92988681793213</v>
       </c>
       <c r="H634" t="n">
         <v>4840</v>
@@ -18842,7 +18842,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G637" t="n">
-        <v>4.88048839569092</v>
+        <v>4.88048887252808</v>
       </c>
       <c r="H637" t="n">
         <v>1800</v>
@@ -18871,7 +18871,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G638" t="n">
-        <v>4.88048839569092</v>
+        <v>4.88048887252808</v>
       </c>
       <c r="H638" t="n">
         <v>0</v>
@@ -18929,7 +18929,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G640" t="n">
-        <v>4.79157257080078</v>
+        <v>4.79157304763794</v>
       </c>
       <c r="H640" t="n">
         <v>4000</v>
@@ -18958,7 +18958,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G641" t="n">
-        <v>4.79157257080078</v>
+        <v>4.79157304763794</v>
       </c>
       <c r="H641" t="n">
         <v>0</v>
@@ -18987,7 +18987,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G642" t="n">
-        <v>4.79157257080078</v>
+        <v>4.79157304763794</v>
       </c>
       <c r="H642" t="n">
         <v>4040</v>
@@ -19103,7 +19103,7 @@
         <v>4.5</v>
       </c>
       <c r="G646" t="n">
-        <v>4.4457893371582</v>
+        <v>4.44578981399536</v>
       </c>
       <c r="H646" t="n">
         <v>8070</v>
@@ -19132,7 +19132,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G647" t="n">
-        <v>4.34699392318726</v>
+        <v>4.34699440002441</v>
       </c>
       <c r="H647" t="n">
         <v>89070</v>
@@ -19161,7 +19161,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G648" t="n">
-        <v>4.34699392318726</v>
+        <v>4.34699440002441</v>
       </c>
       <c r="H648" t="n">
         <v>66390</v>
@@ -19190,7 +19190,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G649" t="n">
-        <v>4.39639139175415</v>
+        <v>4.39639186859131</v>
       </c>
       <c r="H649" t="n">
         <v>7440</v>
@@ -19219,7 +19219,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G650" t="n">
-        <v>4.52482509613037</v>
+        <v>4.52482557296753</v>
       </c>
       <c r="H650" t="n">
         <v>11950</v>
@@ -19306,7 +19306,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G653" t="n">
-        <v>4.79157257080078</v>
+        <v>4.79157304763794</v>
       </c>
       <c r="H653" t="n">
         <v>2680</v>
@@ -19393,7 +19393,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G656" t="n">
-        <v>4.72241592407227</v>
+        <v>4.72241640090942</v>
       </c>
       <c r="H656" t="n">
         <v>2060</v>
@@ -19422,7 +19422,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G657" t="n">
-        <v>4.72241592407227</v>
+        <v>4.72241640090942</v>
       </c>
       <c r="H657" t="n">
         <v>0</v>
@@ -19480,7 +19480,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G659" t="n">
-        <v>4.74217510223389</v>
+        <v>4.7421760559082</v>
       </c>
       <c r="H659" t="n">
         <v>60</v>
@@ -19509,7 +19509,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G660" t="n">
-        <v>4.74217510223389</v>
+        <v>4.7421760559082</v>
       </c>
       <c r="H660" t="n">
         <v>12790</v>
@@ -19538,7 +19538,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G661" t="n">
-        <v>4.88048839569092</v>
+        <v>4.88048887252808</v>
       </c>
       <c r="H661" t="n">
         <v>1600</v>
@@ -19567,7 +19567,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G662" t="n">
-        <v>4.74217510223389</v>
+        <v>4.7421760559082</v>
       </c>
       <c r="H662" t="n">
         <v>10540</v>
@@ -19683,7 +19683,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G666" t="n">
-        <v>4.81133127212524</v>
+        <v>4.8113317489624</v>
       </c>
       <c r="H666" t="n">
         <v>13530</v>
@@ -19741,7 +19741,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G668" t="n">
-        <v>5.03856182098389</v>
+        <v>5.03856134414673</v>
       </c>
       <c r="H668" t="n">
         <v>8110</v>
@@ -19828,7 +19828,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G671" t="n">
-        <v>5.03856182098389</v>
+        <v>5.03856134414673</v>
       </c>
       <c r="H671" t="n">
         <v>4620</v>
@@ -19915,7 +19915,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G674" t="n">
-        <v>5.03856182098389</v>
+        <v>5.03856134414673</v>
       </c>
       <c r="H674" t="n">
         <v>1320</v>
@@ -20031,7 +20031,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G678" t="n">
-        <v>4.74217510223389</v>
+        <v>4.7421760559082</v>
       </c>
       <c r="H678" t="n">
         <v>42730</v>
@@ -20205,7 +20205,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G684" t="n">
-        <v>4.52482509613037</v>
+        <v>4.52482557296753</v>
       </c>
       <c r="H684" t="n">
         <v>1210</v>
@@ -20234,7 +20234,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G685" t="n">
-        <v>4.34699392318726</v>
+        <v>4.34699440002441</v>
       </c>
       <c r="H685" t="n">
         <v>19270</v>
@@ -20263,7 +20263,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G686" t="n">
-        <v>4.39639139175415</v>
+        <v>4.39639186859131</v>
       </c>
       <c r="H686" t="n">
         <v>17560</v>
@@ -20292,7 +20292,7 @@
         <v>4.5</v>
       </c>
       <c r="G687" t="n">
-        <v>4.4457893371582</v>
+        <v>4.44578981399536</v>
       </c>
       <c r="H687" t="n">
         <v>5450</v>
@@ -20321,7 +20321,7 @@
         <v>4.5</v>
       </c>
       <c r="G688" t="n">
-        <v>4.4457893371582</v>
+        <v>4.44578981399536</v>
       </c>
       <c r="H688" t="n">
         <v>6510</v>
@@ -20437,7 +20437,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G692" t="n">
-        <v>5.03856182098389</v>
+        <v>5.03856134414673</v>
       </c>
       <c r="H692" t="n">
         <v>52130</v>
@@ -20466,7 +20466,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G693" t="n">
-        <v>5.15711498260498</v>
+        <v>5.15711545944214</v>
       </c>
       <c r="H693" t="n">
         <v>19970</v>
@@ -20495,7 +20495,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G694" t="n">
-        <v>5.03856182098389</v>
+        <v>5.03856134414673</v>
       </c>
       <c r="H694" t="n">
         <v>39050</v>
@@ -20553,7 +20553,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G696" t="n">
-        <v>5.216392993927</v>
+        <v>5.21639251708984</v>
       </c>
       <c r="H696" t="n">
         <v>1320</v>
@@ -20582,7 +20582,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G697" t="n">
-        <v>5.03856182098389</v>
+        <v>5.03856134414673</v>
       </c>
       <c r="H697" t="n">
         <v>10770</v>
@@ -20669,7 +20669,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G700" t="n">
-        <v>5.03856182098389</v>
+        <v>5.03856134414673</v>
       </c>
       <c r="H700" t="n">
         <v>300</v>
@@ -20698,7 +20698,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G701" t="n">
-        <v>5.03856182098389</v>
+        <v>5.03856134414673</v>
       </c>
       <c r="H701" t="n">
         <v>1190</v>
@@ -20727,7 +20727,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G702" t="n">
-        <v>5.03856182098389</v>
+        <v>5.03856134414673</v>
       </c>
       <c r="H702" t="n">
         <v>110</v>
@@ -20785,7 +20785,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G704" t="n">
-        <v>4.74217510223389</v>
+        <v>4.7421760559082</v>
       </c>
       <c r="H704" t="n">
         <v>5760</v>
@@ -20930,7 +20930,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G709" t="n">
-        <v>4.92988634109497</v>
+        <v>4.92988681793213</v>
       </c>
       <c r="H709" t="n">
         <v>2230</v>
@@ -20959,7 +20959,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G710" t="n">
-        <v>4.92988634109497</v>
+        <v>4.92988681793213</v>
       </c>
       <c r="H710" t="n">
         <v>2210</v>
@@ -20988,7 +20988,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G711" t="n">
-        <v>4.88048839569092</v>
+        <v>4.88048887252808</v>
       </c>
       <c r="H711" t="n">
         <v>1130</v>
@@ -21017,7 +21017,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G712" t="n">
-        <v>4.72241592407227</v>
+        <v>4.72241640090942</v>
       </c>
       <c r="H712" t="n">
         <v>10280</v>
@@ -21133,7 +21133,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G716" t="n">
-        <v>4.72241592407227</v>
+        <v>4.72241640090942</v>
       </c>
       <c r="H716" t="n">
         <v>10940</v>
@@ -21162,7 +21162,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G717" t="n">
-        <v>4.78169393539429</v>
+        <v>4.78169345855713</v>
       </c>
       <c r="H717" t="n">
         <v>2530</v>
@@ -21278,7 +21278,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G721" t="n">
-        <v>5.09783792495728</v>
+        <v>5.09783840179443</v>
       </c>
       <c r="H721" t="n">
         <v>3950</v>
@@ -21423,7 +21423,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G726" t="n">
-        <v>5.03856182098389</v>
+        <v>5.03856134414673</v>
       </c>
       <c r="H726" t="n">
         <v>3700</v>
@@ -21568,7 +21568,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G731" t="n">
-        <v>4.74217510223389</v>
+        <v>4.7421760559082</v>
       </c>
       <c r="H731" t="n">
         <v>2850</v>
@@ -21626,7 +21626,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G733" t="n">
-        <v>4.88048839569092</v>
+        <v>4.88048887252808</v>
       </c>
       <c r="H733" t="n">
         <v>7390</v>
@@ -21655,7 +21655,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G734" t="n">
-        <v>4.78169393539429</v>
+        <v>4.78169345855713</v>
       </c>
       <c r="H734" t="n">
         <v>2150</v>
@@ -21684,7 +21684,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G735" t="n">
-        <v>4.79157257080078</v>
+        <v>4.79157304763794</v>
       </c>
       <c r="H735" t="n">
         <v>1520</v>
@@ -21713,7 +21713,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G736" t="n">
-        <v>4.88048839569092</v>
+        <v>4.88048887252808</v>
       </c>
       <c r="H736" t="n">
         <v>3780</v>
@@ -21829,7 +21829,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G740" t="n">
-        <v>4.81133127212524</v>
+        <v>4.8113317489624</v>
       </c>
       <c r="H740" t="n">
         <v>13020</v>
@@ -22032,7 +22032,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G747" t="n">
-        <v>4.74217510223389</v>
+        <v>4.7421760559082</v>
       </c>
       <c r="H747" t="n">
         <v>63650</v>
@@ -22090,7 +22090,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G749" t="n">
-        <v>4.78169393539429</v>
+        <v>4.78169345855713</v>
       </c>
       <c r="H749" t="n">
         <v>10810</v>
@@ -22177,7 +22177,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G752" t="n">
-        <v>4.22843933105469</v>
+        <v>4.228440284729</v>
       </c>
       <c r="H752" t="n">
         <v>104770</v>
@@ -22380,7 +22380,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G759" t="n">
-        <v>4.15928268432617</v>
+        <v>4.15928316116333</v>
       </c>
       <c r="H759" t="n">
         <v>8420</v>
@@ -22409,7 +22409,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G760" t="n">
-        <v>4.16916275024414</v>
+        <v>4.16916227340698</v>
       </c>
       <c r="H760" t="n">
         <v>13670</v>
@@ -22438,7 +22438,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G761" t="n">
-        <v>4.16916275024414</v>
+        <v>4.16916227340698</v>
       </c>
       <c r="H761" t="n">
         <v>5710</v>
@@ -22467,7 +22467,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G762" t="n">
-        <v>4.15928268432617</v>
+        <v>4.15928316116333</v>
       </c>
       <c r="H762" t="n">
         <v>1760</v>
@@ -22496,7 +22496,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G763" t="n">
-        <v>4.05060815811157</v>
+        <v>4.05060863494873</v>
       </c>
       <c r="H763" t="n">
         <v>55200</v>
@@ -22525,7 +22525,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G764" t="n">
-        <v>4.02096891403198</v>
+        <v>4.0209698677063</v>
       </c>
       <c r="H764" t="n">
         <v>16670</v>
@@ -22612,7 +22612,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G767" t="n">
-        <v>3.86289715766907</v>
+        <v>3.86289691925049</v>
       </c>
       <c r="H767" t="n">
         <v>15840</v>
@@ -22641,7 +22641,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G768" t="n">
-        <v>3.89253544807434</v>
+        <v>3.89253568649292</v>
       </c>
       <c r="H768" t="n">
         <v>17930</v>
@@ -22699,7 +22699,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G770" t="n">
-        <v>3.77398085594177</v>
+        <v>3.77398109436035</v>
       </c>
       <c r="H770" t="n">
         <v>16120</v>
@@ -22728,7 +22728,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G771" t="n">
-        <v>3.76410150527954</v>
+        <v>3.76410174369812</v>
       </c>
       <c r="H771" t="n">
         <v>37320</v>
@@ -22757,7 +22757,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G772" t="n">
-        <v>3.76410150527954</v>
+        <v>3.76410174369812</v>
       </c>
       <c r="H772" t="n">
         <v>37840</v>
@@ -22873,7 +22873,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G776" t="n">
-        <v>3.6949450969696</v>
+        <v>3.69494485855103</v>
       </c>
       <c r="H776" t="n">
         <v>5950</v>
@@ -22960,7 +22960,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G779" t="n">
-        <v>3.99133110046387</v>
+        <v>3.99133086204529</v>
       </c>
       <c r="H779" t="n">
         <v>29300</v>
@@ -22989,7 +22989,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G780" t="n">
-        <v>3.89253544807434</v>
+        <v>3.89253568649292</v>
       </c>
       <c r="H780" t="n">
         <v>38090</v>
@@ -23018,7 +23018,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G781" t="n">
-        <v>3.99133110046387</v>
+        <v>3.99133086204529</v>
       </c>
       <c r="H781" t="n">
         <v>10190</v>
@@ -23047,7 +23047,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G782" t="n">
-        <v>4.04072856903076</v>
+        <v>4.04072904586792</v>
       </c>
       <c r="H782" t="n">
         <v>14490</v>
@@ -23105,7 +23105,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G784" t="n">
-        <v>3.99133110046387</v>
+        <v>3.99133086204529</v>
       </c>
       <c r="H784" t="n">
         <v>7770</v>
@@ -23134,7 +23134,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G785" t="n">
-        <v>3.89253544807434</v>
+        <v>3.89253568649292</v>
       </c>
       <c r="H785" t="n">
         <v>13400</v>
@@ -23366,7 +23366,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G793" t="n">
-        <v>3.93205404281616</v>
+        <v>3.93205380439758</v>
       </c>
       <c r="H793" t="n">
         <v>9740</v>
@@ -23424,7 +23424,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G795" t="n">
-        <v>3.86289715766907</v>
+        <v>3.86289691925049</v>
       </c>
       <c r="H795" t="n">
         <v>15070</v>
@@ -23598,7 +23598,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G801" t="n">
-        <v>3.85301733016968</v>
+        <v>3.85301756858826</v>
       </c>
       <c r="H801" t="n">
         <v>47190</v>
@@ -23627,7 +23627,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G802" t="n">
-        <v>3.9223518371582</v>
+        <v>3.92235159873962</v>
       </c>
       <c r="H802" t="n">
         <v>6080</v>
@@ -23656,7 +23656,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G803" t="n">
-        <v>3.9223518371582</v>
+        <v>3.92235159873962</v>
       </c>
       <c r="H803" t="n">
         <v>2580</v>
@@ -23685,7 +23685,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G804" t="n">
-        <v>3.86292219161987</v>
+        <v>3.86292243003845</v>
       </c>
       <c r="H804" t="n">
         <v>1300</v>
@@ -23743,7 +23743,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G806" t="n">
-        <v>3.86292219161987</v>
+        <v>3.86292243003845</v>
       </c>
       <c r="H806" t="n">
         <v>2310</v>
@@ -23772,7 +23772,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G807" t="n">
-        <v>4.01149606704712</v>
+        <v>4.01149654388428</v>
       </c>
       <c r="H807" t="n">
         <v>6240</v>
@@ -23946,7 +23946,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G813" t="n">
-        <v>3.99168658256531</v>
+        <v>3.99168682098389</v>
       </c>
       <c r="H813" t="n">
         <v>8200</v>
@@ -24004,7 +24004,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G815" t="n">
-        <v>3.9223518371582</v>
+        <v>3.92235159873962</v>
       </c>
       <c r="H815" t="n">
         <v>8350</v>
@@ -24178,7 +24178,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G821" t="n">
-        <v>4.14026021957397</v>
+        <v>4.14025974273682</v>
       </c>
       <c r="H821" t="n">
         <v>24790</v>
@@ -24294,7 +24294,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G825" t="n">
-        <v>3.87282729148865</v>
+        <v>3.87282705307007</v>
       </c>
       <c r="H825" t="n">
         <v>85340</v>
@@ -25019,7 +25019,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G850" t="n">
-        <v>4.14026021957397</v>
+        <v>4.14025974273682</v>
       </c>
       <c r="H850" t="n">
         <v>11320</v>
@@ -25048,7 +25048,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G851" t="n">
-        <v>4.16997480392456</v>
+        <v>4.16997528076172</v>
       </c>
       <c r="H851" t="n">
         <v>9220</v>
@@ -25135,7 +25135,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G854" t="n">
-        <v>4.16007041931152</v>
+        <v>4.16006994247437</v>
       </c>
       <c r="H854" t="n">
         <v>31610</v>
@@ -25164,7 +25164,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G855" t="n">
-        <v>4.16007041931152</v>
+        <v>4.16006994247437</v>
       </c>
       <c r="H855" t="n">
         <v>8120</v>
@@ -25570,7 +25570,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G869" t="n">
-        <v>4.01149606704712</v>
+        <v>4.01149654388428</v>
       </c>
       <c r="H869" t="n">
         <v>10970</v>
@@ -25628,7 +25628,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G871" t="n">
-        <v>3.93225646018982</v>
+        <v>3.9322566986084</v>
       </c>
       <c r="H871" t="n">
         <v>7010</v>
@@ -25802,7 +25802,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G877" t="n">
-        <v>4.16997480392456</v>
+        <v>4.16997528076172</v>
       </c>
       <c r="H877" t="n">
         <v>14160</v>
@@ -25889,7 +25889,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G880" t="n">
-        <v>4.30864429473877</v>
+        <v>4.30864381790161</v>
       </c>
       <c r="H880" t="n">
         <v>45530</v>
@@ -26266,7 +26266,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G893" t="n">
-        <v>4.23930931091309</v>
+        <v>4.23930978775024</v>
       </c>
       <c r="H893" t="n">
         <v>42450</v>
@@ -26295,7 +26295,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G894" t="n">
-        <v>4.34826326370239</v>
+        <v>4.34826374053955</v>
       </c>
       <c r="H894" t="n">
         <v>9130</v>
@@ -26353,7 +26353,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G896" t="n">
-        <v>4.2194995880127</v>
+        <v>4.21950006484985</v>
       </c>
       <c r="H896" t="n">
         <v>6250</v>
@@ -26469,7 +26469,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G900" t="n">
-        <v>4.25911998748779</v>
+        <v>4.25911951065063</v>
       </c>
       <c r="H900" t="n">
         <v>2300</v>
@@ -26498,7 +26498,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G901" t="n">
-        <v>4.25911998748779</v>
+        <v>4.25911951065063</v>
       </c>
       <c r="H901" t="n">
         <v>7230</v>
@@ -26672,7 +26672,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G907" t="n">
-        <v>4.17987966537476</v>
+        <v>4.17988014221191</v>
       </c>
       <c r="H907" t="n">
         <v>9490</v>
@@ -27020,7 +27020,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G919" t="n">
-        <v>3.85301733016968</v>
+        <v>3.85301756858826</v>
       </c>
       <c r="H919" t="n">
         <v>5620</v>
@@ -27194,7 +27194,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G925" t="n">
-        <v>3.64501404762268</v>
+        <v>3.6450138092041</v>
       </c>
       <c r="H925" t="n">
         <v>3530</v>
@@ -27339,7 +27339,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G930" t="n">
-        <v>3.66482353210449</v>
+        <v>3.66482377052307</v>
       </c>
       <c r="H930" t="n">
         <v>17040</v>
@@ -27629,7 +27629,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G940" t="n">
-        <v>3.77377772331238</v>
+        <v>3.77377796173096</v>
       </c>
       <c r="H940" t="n">
         <v>14330</v>
@@ -27687,7 +27687,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G942" t="n">
-        <v>3.74406337738037</v>
+        <v>3.74406313896179</v>
       </c>
       <c r="H942" t="n">
         <v>34380</v>
@@ -27890,7 +27890,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G949" t="n">
-        <v>4.17987966537476</v>
+        <v>4.17988014221191</v>
       </c>
       <c r="H949" t="n">
         <v>41290</v>
@@ -27977,7 +27977,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G952" t="n">
-        <v>3.89263725280762</v>
+        <v>3.89263701438904</v>
       </c>
       <c r="H952" t="n">
         <v>18360</v>
@@ -28093,7 +28093,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G956" t="n">
-        <v>3.99168658256531</v>
+        <v>3.99168682098389</v>
       </c>
       <c r="H956" t="n">
         <v>5970</v>
@@ -28267,7 +28267,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G962" t="n">
-        <v>3.86292219161987</v>
+        <v>3.86292243003845</v>
       </c>
       <c r="H962" t="n">
         <v>46304</v>
@@ -28296,7 +28296,7 @@
         <v>3.94400000572205</v>
       </c>
       <c r="G963" t="n">
-        <v>3.90650415420532</v>
+        <v>3.90650391578674</v>
       </c>
       <c r="H963" t="n">
         <v>21357</v>
@@ -28499,7 +28499,7 @@
         <v>3.95050001144409</v>
       </c>
       <c r="G970" t="n">
-        <v>3.91294193267822</v>
+        <v>3.9129421710968</v>
       </c>
       <c r="H970" t="n">
         <v>6820</v>
@@ -28615,7 +28615,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G974" t="n">
-        <v>4.01149606704712</v>
+        <v>4.01149654388428</v>
       </c>
       <c r="H974" t="n">
         <v>41355</v>
@@ -28760,7 +28760,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G979" t="n">
-        <v>3.99168658256531</v>
+        <v>3.99168682098389</v>
       </c>
       <c r="H979" t="n">
         <v>7285</v>
@@ -28847,7 +28847,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G982" t="n">
-        <v>3.93225646018982</v>
+        <v>3.9322566986084</v>
       </c>
       <c r="H982" t="n">
         <v>2119</v>
@@ -28992,7 +28992,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G987" t="n">
-        <v>3.85301733016968</v>
+        <v>3.85301756858826</v>
       </c>
       <c r="H987" t="n">
         <v>3417</v>
@@ -29021,7 +29021,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G988" t="n">
-        <v>3.85301733016968</v>
+        <v>3.85301756858826</v>
       </c>
       <c r="H988" t="n">
         <v>9092</v>
@@ -29166,7 +29166,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G993" t="n">
-        <v>3.86292219161987</v>
+        <v>3.86292243003845</v>
       </c>
       <c r="H993" t="n">
         <v>19637</v>
@@ -29195,7 +29195,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G994" t="n">
-        <v>3.85301733016968</v>
+        <v>3.85301756858826</v>
       </c>
       <c r="H994" t="n">
         <v>2361</v>
@@ -29224,7 +29224,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G995" t="n">
-        <v>3.81339764595032</v>
+        <v>3.81339740753174</v>
       </c>
       <c r="H995" t="n">
         <v>7114</v>
@@ -29398,7 +29398,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1001" t="n">
-        <v>3.86292219161987</v>
+        <v>3.86292243003845</v>
       </c>
       <c r="H1001" t="n">
         <v>9557</v>
@@ -29775,7 +29775,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1014" t="n">
-        <v>3.66482353210449</v>
+        <v>3.66482377052307</v>
       </c>
       <c r="H1014" t="n">
         <v>19950</v>
@@ -29804,7 +29804,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1015" t="n">
-        <v>3.66482353210449</v>
+        <v>3.66482377052307</v>
       </c>
       <c r="H1015" t="n">
         <v>2750</v>
@@ -29833,7 +29833,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G1016" t="n">
-        <v>3.575679063797</v>
+        <v>3.57567930221558</v>
       </c>
       <c r="H1016" t="n">
         <v>16853</v>
@@ -29920,7 +29920,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1019" t="n">
-        <v>3.64501404762268</v>
+        <v>3.6450138092041</v>
       </c>
       <c r="H1019" t="n">
         <v>452</v>
@@ -29978,7 +29978,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1021" t="n">
-        <v>3.64501404762268</v>
+        <v>3.6450138092041</v>
       </c>
       <c r="H1021" t="n">
         <v>19653</v>
@@ -30036,7 +30036,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1023" t="n">
-        <v>3.66482353210449</v>
+        <v>3.66482377052307</v>
       </c>
       <c r="H1023" t="n">
         <v>846</v>
@@ -30065,7 +30065,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1024" t="n">
-        <v>3.61529922485352</v>
+        <v>3.61529898643494</v>
       </c>
       <c r="H1024" t="n">
         <v>8732</v>
@@ -30152,7 +30152,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1027" t="n">
-        <v>3.61529922485352</v>
+        <v>3.61529898643494</v>
       </c>
       <c r="H1027" t="n">
         <v>4783</v>
@@ -30181,7 +30181,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1028" t="n">
-        <v>3.61529922485352</v>
+        <v>3.61529898643494</v>
       </c>
       <c r="H1028" t="n">
         <v>4537</v>
@@ -30210,7 +30210,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1029" t="n">
-        <v>3.61529922485352</v>
+        <v>3.61529898643494</v>
       </c>
       <c r="H1029" t="n">
         <v>2959</v>
@@ -30268,7 +30268,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G1031" t="n">
-        <v>3.6549186706543</v>
+        <v>3.65491890907288</v>
       </c>
       <c r="H1031" t="n">
         <v>22295</v>
@@ -30297,7 +30297,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G1032" t="n">
-        <v>3.6549186706543</v>
+        <v>3.65491890907288</v>
       </c>
       <c r="H1032" t="n">
         <v>32428</v>
@@ -30413,7 +30413,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G1036" t="n">
-        <v>3.55586957931519</v>
+        <v>3.55586934089661</v>
       </c>
       <c r="H1036" t="n">
         <v>10707</v>
@@ -30442,7 +30442,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G1037" t="n">
-        <v>3.52615451812744</v>
+        <v>3.52615475654602</v>
       </c>
       <c r="H1037" t="n">
         <v>5035</v>
@@ -30529,7 +30529,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1040" t="n">
-        <v>3.49643969535828</v>
+        <v>3.49643993377686</v>
       </c>
       <c r="H1040" t="n">
         <v>2950</v>
@@ -30558,7 +30558,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1041" t="n">
-        <v>3.49643969535828</v>
+        <v>3.49643993377686</v>
       </c>
       <c r="H1041" t="n">
         <v>1858</v>
@@ -30703,7 +30703,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G1046" t="n">
-        <v>3.52615451812744</v>
+        <v>3.52615475654602</v>
       </c>
       <c r="H1046" t="n">
         <v>4465</v>
@@ -30761,7 +30761,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1048" t="n">
-        <v>3.41720056533813</v>
+        <v>3.41720032691956</v>
       </c>
       <c r="H1048" t="n">
         <v>10706</v>
@@ -30877,7 +30877,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1052" t="n">
-        <v>3.49643969535828</v>
+        <v>3.49643993377686</v>
       </c>
       <c r="H1052" t="n">
         <v>3617</v>
@@ -30906,7 +30906,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G1053" t="n">
-        <v>3.55586957931519</v>
+        <v>3.55586934089661</v>
       </c>
       <c r="H1053" t="n">
         <v>13118</v>
@@ -31225,7 +31225,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G1064" t="n">
-        <v>3.89263725280762</v>
+        <v>3.89263701438904</v>
       </c>
       <c r="H1064" t="n">
         <v>23123</v>
@@ -31312,7 +31312,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G1067" t="n">
-        <v>4.01149606704712</v>
+        <v>4.01149654388428</v>
       </c>
       <c r="H1067" t="n">
         <v>6753</v>
@@ -31370,7 +31370,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1069" t="n">
-        <v>3.86292219161987</v>
+        <v>3.86292243003845</v>
       </c>
       <c r="H1069" t="n">
         <v>9275</v>
@@ -31602,7 +31602,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G1077" t="n">
-        <v>3.74406337738037</v>
+        <v>3.74406313896179</v>
       </c>
       <c r="H1077" t="n">
         <v>2981</v>
@@ -31805,7 +31805,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1084" t="n">
-        <v>3.63471913337708</v>
+        <v>3.6347188949585</v>
       </c>
       <c r="H1084" t="n">
         <v>5698</v>
@@ -32153,7 +32153,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1096" t="n">
-        <v>3.63471913337708</v>
+        <v>3.6347188949585</v>
       </c>
       <c r="H1096" t="n">
         <v>1083</v>
@@ -32240,7 +32240,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1099" t="n">
-        <v>3.63471913337708</v>
+        <v>3.6347188949585</v>
       </c>
       <c r="H1099" t="n">
         <v>560</v>
@@ -32385,7 +32385,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G1104" t="n">
-        <v>3.55527114868164</v>
+        <v>3.55527138710022</v>
       </c>
       <c r="H1104" t="n">
         <v>4500</v>
@@ -32414,7 +32414,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1105" t="n">
-        <v>3.67444276809692</v>
+        <v>3.67444252967834</v>
       </c>
       <c r="H1105" t="n">
         <v>3701</v>
@@ -32617,7 +32617,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1112" t="n">
-        <v>3.50561666488647</v>
+        <v>3.50561690330505</v>
       </c>
       <c r="H1112" t="n">
         <v>5210</v>
@@ -32646,7 +32646,7 @@
         <v>3.5</v>
       </c>
       <c r="G1113" t="n">
-        <v>3.47582387924194</v>
+        <v>3.47582411766052</v>
       </c>
       <c r="H1113" t="n">
         <v>278</v>
@@ -32675,7 +32675,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1114" t="n">
-        <v>3.43610024452209</v>
+        <v>3.43610048294067</v>
       </c>
       <c r="H1114" t="n">
         <v>2139</v>
@@ -32704,7 +32704,7 @@
         <v>3.5</v>
       </c>
       <c r="G1115" t="n">
-        <v>3.47582387924194</v>
+        <v>3.47582411766052</v>
       </c>
       <c r="H1115" t="n">
         <v>6298</v>
@@ -32733,7 +32733,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1116" t="n">
-        <v>3.43610024452209</v>
+        <v>3.43610048294067</v>
       </c>
       <c r="H1116" t="n">
         <v>5346</v>
@@ -32791,7 +32791,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1118" t="n">
-        <v>3.51554751396179</v>
+        <v>3.51554775238037</v>
       </c>
       <c r="H1118" t="n">
         <v>6544</v>
@@ -32878,7 +32878,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1121" t="n">
-        <v>3.50561666488647</v>
+        <v>3.50561690330505</v>
       </c>
       <c r="H1121" t="n">
         <v>5808</v>
@@ -32907,7 +32907,7 @@
         <v>3.5</v>
       </c>
       <c r="G1122" t="n">
-        <v>3.47582387924194</v>
+        <v>3.47582411766052</v>
       </c>
       <c r="H1122" t="n">
         <v>1849</v>
@@ -32936,7 +32936,7 @@
         <v>3.5</v>
       </c>
       <c r="G1123" t="n">
-        <v>3.47582387924194</v>
+        <v>3.47582411766052</v>
       </c>
       <c r="H1123" t="n">
         <v>0</v>
@@ -32994,7 +32994,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1125" t="n">
-        <v>3.41623830795288</v>
+        <v>3.41623854637146</v>
       </c>
       <c r="H1125" t="n">
         <v>3101</v>
@@ -33023,7 +33023,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1126" t="n">
-        <v>3.41623830795288</v>
+        <v>3.41623854637146</v>
       </c>
       <c r="H1126" t="n">
         <v>4223</v>
@@ -33052,7 +33052,7 @@
         <v>3.5</v>
       </c>
       <c r="G1127" t="n">
-        <v>3.47582387924194</v>
+        <v>3.47582411766052</v>
       </c>
       <c r="H1127" t="n">
         <v>1000</v>
@@ -33081,7 +33081,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1128" t="n">
-        <v>3.51554751396179</v>
+        <v>3.51554775238037</v>
       </c>
       <c r="H1128" t="n">
         <v>14737</v>
@@ -33197,7 +33197,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1132" t="n">
-        <v>3.41623830795288</v>
+        <v>3.41623854637146</v>
       </c>
       <c r="H1132" t="n">
         <v>145</v>
@@ -33342,7 +33342,7 @@
         <v>3.5</v>
       </c>
       <c r="G1137" t="n">
-        <v>3.47582387924194</v>
+        <v>3.47582411766052</v>
       </c>
       <c r="H1137" t="n">
         <v>18829</v>
@@ -33429,7 +33429,7 @@
         <v>3.5</v>
       </c>
       <c r="G1140" t="n">
-        <v>3.47582387924194</v>
+        <v>3.47582411766052</v>
       </c>
       <c r="H1140" t="n">
         <v>14559</v>
@@ -33516,7 +33516,7 @@
         <v>3.5</v>
       </c>
       <c r="G1143" t="n">
-        <v>3.47582387924194</v>
+        <v>3.47582411766052</v>
       </c>
       <c r="H1143" t="n">
         <v>19008</v>
@@ -33574,7 +33574,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G1145" t="n">
-        <v>3.55527114868164</v>
+        <v>3.55527138710022</v>
       </c>
       <c r="H1145" t="n">
         <v>1675</v>
@@ -33603,7 +33603,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1146" t="n">
-        <v>3.67444276809692</v>
+        <v>3.67444252967834</v>
       </c>
       <c r="H1146" t="n">
         <v>42177</v>
@@ -33632,7 +33632,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1147" t="n">
-        <v>3.71416640281677</v>
+        <v>3.71416616439819</v>
       </c>
       <c r="H1147" t="n">
         <v>30404</v>
@@ -33719,7 +33719,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1150" t="n">
-        <v>3.67444276809692</v>
+        <v>3.67444252967834</v>
       </c>
       <c r="H1150" t="n">
         <v>11747</v>
@@ -33777,7 +33777,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1152" t="n">
-        <v>3.67444276809692</v>
+        <v>3.67444252967834</v>
       </c>
       <c r="H1152" t="n">
         <v>6905</v>
@@ -34038,7 +34038,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G1161" t="n">
-        <v>3.55527114868164</v>
+        <v>3.55527138710022</v>
       </c>
       <c r="H1161" t="n">
         <v>3572</v>
@@ -34270,7 +34270,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G1169" t="n">
-        <v>3.55527114868164</v>
+        <v>3.55527138710022</v>
       </c>
       <c r="H1169" t="n">
         <v>5878</v>
@@ -34299,7 +34299,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1170" t="n">
-        <v>3.63471913337708</v>
+        <v>3.6347188949585</v>
       </c>
       <c r="H1170" t="n">
         <v>17287</v>
@@ -34328,7 +34328,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1171" t="n">
-        <v>3.63471913337708</v>
+        <v>3.6347188949585</v>
       </c>
       <c r="H1171" t="n">
         <v>25873</v>
@@ -34589,7 +34589,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G1180" t="n">
-        <v>3.55527114868164</v>
+        <v>3.55527138710022</v>
       </c>
       <c r="H1180" t="n">
         <v>30518</v>
@@ -34647,7 +34647,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1182" t="n">
-        <v>3.50561666488647</v>
+        <v>3.50561690330505</v>
       </c>
       <c r="H1182" t="n">
         <v>20828</v>
@@ -34676,7 +34676,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1183" t="n">
-        <v>3.50561666488647</v>
+        <v>3.50561690330505</v>
       </c>
       <c r="H1183" t="n">
         <v>540</v>
@@ -34734,7 +34734,7 @@
         <v>3.5</v>
       </c>
       <c r="G1185" t="n">
-        <v>3.47582387924194</v>
+        <v>3.47582411766052</v>
       </c>
       <c r="H1185" t="n">
         <v>1141</v>
@@ -34821,7 +34821,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1188" t="n">
-        <v>3.41623830795288</v>
+        <v>3.41623854637146</v>
       </c>
       <c r="H1188" t="n">
         <v>16937</v>
@@ -34995,7 +34995,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G1194" t="n">
-        <v>2.93955397605896</v>
+        <v>2.93955421447754</v>
       </c>
       <c r="H1194" t="n">
         <v>2442</v>
@@ -35372,7 +35372,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G1207" t="n">
-        <v>2.76079726219177</v>
+        <v>2.76079750061035</v>
       </c>
       <c r="H1207" t="n">
         <v>85019</v>
@@ -35401,7 +35401,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G1208" t="n">
-        <v>2.70121169090271</v>
+        <v>2.70121192932129</v>
       </c>
       <c r="H1208" t="n">
         <v>36383</v>
@@ -35923,7 +35923,7 @@
         <v>3</v>
       </c>
       <c r="G1226" t="n">
-        <v>2.97927761077881</v>
+        <v>2.97927784919739</v>
       </c>
       <c r="H1226" t="n">
         <v>103705</v>
@@ -35981,7 +35981,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G1228" t="n">
-        <v>2.93955397605896</v>
+        <v>2.93955421447754</v>
       </c>
       <c r="H1228" t="n">
         <v>12630</v>
@@ -36039,7 +36039,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G1230" t="n">
-        <v>2.93955397605896</v>
+        <v>2.93955421447754</v>
       </c>
       <c r="H1230" t="n">
         <v>12379</v>
@@ -36068,7 +36068,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G1231" t="n">
-        <v>2.93955397605896</v>
+        <v>2.93955421447754</v>
       </c>
       <c r="H1231" t="n">
         <v>21752</v>
@@ -36097,7 +36097,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G1232" t="n">
-        <v>2.93955397605896</v>
+        <v>2.93955421447754</v>
       </c>
       <c r="H1232" t="n">
         <v>51075</v>
@@ -36184,7 +36184,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1235" t="n">
-        <v>2.8799684047699</v>
+        <v>2.87996864318848</v>
       </c>
       <c r="H1235" t="n">
         <v>33074</v>
@@ -36503,7 +36503,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G1246" t="n">
-        <v>2.58204054832458</v>
+        <v>2.58204078674316</v>
       </c>
       <c r="H1246" t="n">
         <v>34890</v>
@@ -36764,7 +36764,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G1255" t="n">
-        <v>2.66148805618286</v>
+        <v>2.66148829460144</v>
       </c>
       <c r="H1255" t="n">
         <v>14426</v>
@@ -36938,7 +36938,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1261" t="n">
-        <v>2.8799684047699</v>
+        <v>2.87996864318848</v>
       </c>
       <c r="H1261" t="n">
         <v>23099</v>
@@ -36996,7 +36996,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G1263" t="n">
-        <v>2.84024453163147</v>
+        <v>2.84024477005005</v>
       </c>
       <c r="H1263" t="n">
         <v>24196</v>
@@ -37025,7 +37025,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1264" t="n">
-        <v>2.8799684047699</v>
+        <v>2.87996864318848</v>
       </c>
       <c r="H1264" t="n">
         <v>44232</v>
@@ -37199,7 +37199,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G1270" t="n">
-        <v>2.76079726219177</v>
+        <v>2.76079750061035</v>
       </c>
       <c r="H1270" t="n">
         <v>16790</v>
@@ -37257,7 +37257,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G1272" t="n">
-        <v>2.76079726219177</v>
+        <v>2.76079750061035</v>
       </c>
       <c r="H1272" t="n">
         <v>7158</v>
@@ -37315,7 +37315,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G1274" t="n">
-        <v>2.84024453163147</v>
+        <v>2.84024477005005</v>
       </c>
       <c r="H1274" t="n">
         <v>4036</v>
@@ -37518,7 +37518,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G1281" t="n">
-        <v>2.84024453163147</v>
+        <v>2.84024477005005</v>
       </c>
       <c r="H1281" t="n">
         <v>4934</v>
@@ -37692,7 +37692,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G1287" t="n">
-        <v>2.66148805618286</v>
+        <v>2.66148829460144</v>
       </c>
       <c r="H1287" t="n">
         <v>11470</v>
@@ -37721,7 +37721,7 @@
         <v>2.5</v>
       </c>
       <c r="G1288" t="n">
-        <v>2.48273134231567</v>
+        <v>2.48273158073425</v>
       </c>
       <c r="H1288" t="n">
         <v>44014</v>
@@ -37895,7 +37895,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G1294" t="n">
-        <v>2.62176442146301</v>
+        <v>2.62176465988159</v>
       </c>
       <c r="H1294" t="n">
         <v>12855</v>
@@ -38156,7 +38156,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1303" t="n">
-        <v>2.8799684047699</v>
+        <v>2.87996864318848</v>
       </c>
       <c r="H1303" t="n">
         <v>10021</v>
@@ -38301,7 +38301,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G1308" t="n">
-        <v>2.84024453163147</v>
+        <v>2.84024477005005</v>
       </c>
       <c r="H1308" t="n">
         <v>4956</v>
@@ -38359,7 +38359,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G1310" t="n">
-        <v>2.80052089691162</v>
+        <v>2.8005211353302</v>
       </c>
       <c r="H1310" t="n">
         <v>28928</v>
@@ -38475,7 +38475,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G1314" t="n">
-        <v>2.93955397605896</v>
+        <v>2.93955421447754</v>
       </c>
       <c r="H1314" t="n">
         <v>43179</v>
@@ -48979,6 +48979,64 @@
         <v>14618</v>
       </c>
       <c r="I1676" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1677">
+      <c r="A1677" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1677" s="1" t="n">
+        <v>46314.2916666667</v>
+      </c>
+      <c r="C1677" t="n">
+        <v>3.22499990463257</v>
+      </c>
+      <c r="D1677" t="n">
+        <v>3.22499990463257</v>
+      </c>
+      <c r="E1677" t="n">
+        <v>3.15000009536743</v>
+      </c>
+      <c r="F1677" t="n">
+        <v>3.17000007629395</v>
+      </c>
+      <c r="G1677" t="n">
+        <v>3.17000007629395</v>
+      </c>
+      <c r="H1677" t="n">
+        <v>25020</v>
+      </c>
+      <c r="I1677" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1678">
+      <c r="A1678" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1678" s="1" t="n">
+        <v>46315.2916666667</v>
+      </c>
+      <c r="C1678" t="n">
+        <v>3.14000010490417</v>
+      </c>
+      <c r="D1678" t="n">
+        <v>3.18499994277954</v>
+      </c>
+      <c r="E1678" t="n">
+        <v>3.09999990463257</v>
+      </c>
+      <c r="F1678" t="n">
+        <v>3.11999988555908</v>
+      </c>
+      <c r="G1678" t="n">
+        <v>3.11999988555908</v>
+      </c>
+      <c r="H1678" t="n">
+        <v>40723</v>
+      </c>
+      <c r="I1678" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/UD.MI.xlsx
+++ b/data/UD.MI.xlsx
@@ -427,7 +427,7 @@
         <v>1.5</v>
       </c>
       <c r="G2" t="n">
-        <v>1.47885513305664</v>
+        <v>1.47885525226593</v>
       </c>
       <c r="H2" t="n">
         <v>159000</v>
@@ -456,7 +456,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G3" t="n">
-        <v>1.43941915035248</v>
+        <v>1.43941903114319</v>
       </c>
       <c r="H3" t="n">
         <v>78000</v>
@@ -485,7 +485,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G4" t="n">
-        <v>1.45913708209991</v>
+        <v>1.4591372013092</v>
       </c>
       <c r="H4" t="n">
         <v>240000</v>
@@ -543,7 +543,7 @@
         <v>1.56500005722046</v>
       </c>
       <c r="G6" t="n">
-        <v>1.54293894767761</v>
+        <v>1.5429390668869</v>
       </c>
       <c r="H6" t="n">
         <v>55000</v>
@@ -572,7 +572,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G7" t="n">
-        <v>1.51829135417938</v>
+        <v>1.51829123497009</v>
       </c>
       <c r="H7" t="n">
         <v>61000</v>
@@ -688,7 +688,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G11" t="n">
-        <v>1.56265687942505</v>
+        <v>1.56265699863434</v>
       </c>
       <c r="H11" t="n">
         <v>16000</v>
@@ -862,7 +862,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G17" t="n">
-        <v>1.66617679595947</v>
+        <v>1.66617691516876</v>
       </c>
       <c r="H17" t="n">
         <v>14000</v>
@@ -1094,7 +1094,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G25" t="n">
-        <v>1.58730459213257</v>
+        <v>1.58730447292328</v>
       </c>
       <c r="H25" t="n">
         <v>22000</v>
@@ -1181,7 +1181,7 @@
         <v>1.59500002861023</v>
       </c>
       <c r="G28" t="n">
-        <v>1.57251608371735</v>
+        <v>1.57251620292664</v>
       </c>
       <c r="H28" t="n">
         <v>22000</v>
@@ -1268,7 +1268,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G31" t="n">
-        <v>1.63659977912903</v>
+        <v>1.63659965991974</v>
       </c>
       <c r="H31" t="n">
         <v>32000</v>
@@ -1326,7 +1326,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G33" t="n">
-        <v>1.6168817281723</v>
+        <v>1.61688160896301</v>
       </c>
       <c r="H33" t="n">
         <v>1000</v>
@@ -1500,7 +1500,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G39" t="n">
-        <v>1.67110645771027</v>
+        <v>1.67110657691956</v>
       </c>
       <c r="H39" t="n">
         <v>3000</v>
@@ -1529,7 +1529,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G40" t="n">
-        <v>1.69575393199921</v>
+        <v>1.6957540512085</v>
       </c>
       <c r="H40" t="n">
         <v>7000</v>
@@ -1558,7 +1558,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G41" t="n">
-        <v>1.68589496612549</v>
+        <v>1.6858948469162</v>
       </c>
       <c r="H41" t="n">
         <v>14000</v>
@@ -1616,7 +1616,7 @@
         <v>1.72500002384186</v>
       </c>
       <c r="G43" t="n">
-        <v>1.70068347454071</v>
+        <v>1.70068359375</v>
       </c>
       <c r="H43" t="n">
         <v>21000</v>
@@ -1674,7 +1674,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G45" t="n">
-        <v>1.66617679595947</v>
+        <v>1.66617691516876</v>
       </c>
       <c r="H45" t="n">
         <v>1000</v>
@@ -1790,7 +1790,7 @@
         <v>1.72500002384186</v>
       </c>
       <c r="G49" t="n">
-        <v>1.70068347454071</v>
+        <v>1.70068359375</v>
       </c>
       <c r="H49" t="n">
         <v>18000</v>
@@ -1877,7 +1877,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G52" t="n">
-        <v>1.74011957645416</v>
+        <v>1.74011969566345</v>
       </c>
       <c r="H52" t="n">
         <v>6000</v>
@@ -1906,7 +1906,7 @@
         <v>1.74500000476837</v>
       </c>
       <c r="G53" t="n">
-        <v>1.72040152549744</v>
+        <v>1.72040164470673</v>
       </c>
       <c r="H53" t="n">
         <v>7000</v>
@@ -1935,7 +1935,7 @@
         <v>1.72500002384186</v>
       </c>
       <c r="G54" t="n">
-        <v>1.70068347454071</v>
+        <v>1.70068359375</v>
       </c>
       <c r="H54" t="n">
         <v>10000</v>
@@ -1964,7 +1964,7 @@
         <v>1.72500002384186</v>
       </c>
       <c r="G55" t="n">
-        <v>1.70068347454071</v>
+        <v>1.70068359375</v>
       </c>
       <c r="H55" t="n">
         <v>15000</v>
@@ -1993,7 +1993,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G56" t="n">
-        <v>1.69575393199921</v>
+        <v>1.6957540512085</v>
       </c>
       <c r="H56" t="n">
         <v>8000</v>
@@ -2196,7 +2196,7 @@
         <v>1.68499994277954</v>
       </c>
       <c r="G63" t="n">
-        <v>1.66124713420868</v>
+        <v>1.66124725341797</v>
       </c>
       <c r="H63" t="n">
         <v>5000</v>
@@ -2312,7 +2312,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G67" t="n">
-        <v>1.66617679595947</v>
+        <v>1.66617691516876</v>
       </c>
       <c r="H67" t="n">
         <v>10000</v>
@@ -2341,7 +2341,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G68" t="n">
-        <v>1.68589496612549</v>
+        <v>1.6858948469162</v>
       </c>
       <c r="H68" t="n">
         <v>7000</v>
@@ -2573,7 +2573,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G76" t="n">
-        <v>1.67110645771027</v>
+        <v>1.67110657691956</v>
       </c>
       <c r="H76" t="n">
         <v>2000</v>
@@ -2602,7 +2602,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G77" t="n">
-        <v>1.68589496612549</v>
+        <v>1.6858948469162</v>
       </c>
       <c r="H77" t="n">
         <v>3000</v>
@@ -2805,7 +2805,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G84" t="n">
-        <v>1.63659977912903</v>
+        <v>1.63659965991974</v>
       </c>
       <c r="H84" t="n">
         <v>8000</v>
@@ -2979,7 +2979,7 @@
         <v>1.59500002861023</v>
       </c>
       <c r="G90" t="n">
-        <v>1.57251608371735</v>
+        <v>1.57251620292664</v>
       </c>
       <c r="H90" t="n">
         <v>4000</v>
@@ -3008,7 +3008,7 @@
         <v>1.59500002861023</v>
       </c>
       <c r="G91" t="n">
-        <v>1.57251608371735</v>
+        <v>1.57251620292664</v>
       </c>
       <c r="H91" t="n">
         <v>2000</v>
@@ -3037,7 +3037,7 @@
         <v>1.62999999523163</v>
       </c>
       <c r="G92" t="n">
-        <v>1.60702252388</v>
+        <v>1.60702264308929</v>
       </c>
       <c r="H92" t="n">
         <v>32000</v>
@@ -3066,7 +3066,7 @@
         <v>1.59500002861023</v>
       </c>
       <c r="G93" t="n">
-        <v>1.57251608371735</v>
+        <v>1.57251620292664</v>
       </c>
       <c r="H93" t="n">
         <v>9000</v>
@@ -3095,7 +3095,7 @@
         <v>1.59500002861023</v>
       </c>
       <c r="G94" t="n">
-        <v>1.57251608371735</v>
+        <v>1.57251620292664</v>
       </c>
       <c r="H94" t="n">
         <v>11000</v>
@@ -3124,7 +3124,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G95" t="n">
-        <v>1.58730459213257</v>
+        <v>1.58730447292328</v>
       </c>
       <c r="H95" t="n">
         <v>11000</v>
@@ -3182,7 +3182,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G97" t="n">
-        <v>1.58730459213257</v>
+        <v>1.58730447292328</v>
       </c>
       <c r="H97" t="n">
         <v>31000</v>
@@ -3211,7 +3211,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G98" t="n">
-        <v>1.58730459213257</v>
+        <v>1.58730447292328</v>
       </c>
       <c r="H98" t="n">
         <v>11000</v>
@@ -3356,7 +3356,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G103" t="n">
-        <v>1.63659977912903</v>
+        <v>1.63659965991974</v>
       </c>
       <c r="H103" t="n">
         <v>35000</v>
@@ -3385,7 +3385,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G104" t="n">
-        <v>1.63659977912903</v>
+        <v>1.63659965991974</v>
       </c>
       <c r="H104" t="n">
         <v>14000</v>
@@ -3414,7 +3414,7 @@
         <v>1.63499999046326</v>
       </c>
       <c r="G105" t="n">
-        <v>1.6119521856308</v>
+        <v>1.61195206642151</v>
       </c>
       <c r="H105" t="n">
         <v>26000</v>
@@ -3443,7 +3443,7 @@
         <v>1.66499996185303</v>
       </c>
       <c r="G106" t="n">
-        <v>1.64152908325195</v>
+        <v>1.64152932167053</v>
       </c>
       <c r="H106" t="n">
         <v>2000</v>
@@ -3530,7 +3530,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G109" t="n">
-        <v>1.66617679595947</v>
+        <v>1.66617691516876</v>
       </c>
       <c r="H109" t="n">
         <v>15000</v>
@@ -3762,7 +3762,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G117" t="n">
-        <v>1.68589496612549</v>
+        <v>1.6858948469162</v>
       </c>
       <c r="H117" t="n">
         <v>22000</v>
@@ -3791,7 +3791,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G118" t="n">
-        <v>1.68589496612549</v>
+        <v>1.6858948469162</v>
       </c>
       <c r="H118" t="n">
         <v>0</v>
@@ -3878,7 +3878,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G121" t="n">
-        <v>1.87321662902832</v>
+        <v>1.87321650981903</v>
       </c>
       <c r="H121" t="n">
         <v>50000</v>
@@ -3907,7 +3907,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G122" t="n">
-        <v>1.87321662902832</v>
+        <v>1.87321650981903</v>
       </c>
       <c r="H122" t="n">
         <v>39000</v>
@@ -3936,7 +3936,7 @@
         <v>1.875</v>
       </c>
       <c r="G123" t="n">
-        <v>1.8485689163208</v>
+        <v>1.84856903553009</v>
       </c>
       <c r="H123" t="n">
         <v>45000</v>
@@ -4052,7 +4052,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G127" t="n">
-        <v>1.82392144203186</v>
+        <v>1.82392132282257</v>
       </c>
       <c r="H127" t="n">
         <v>7000</v>
@@ -4081,7 +4081,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G128" t="n">
-        <v>1.82392144203186</v>
+        <v>1.82392132282257</v>
       </c>
       <c r="H128" t="n">
         <v>0</v>
@@ -4110,7 +4110,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G129" t="n">
-        <v>1.82392144203186</v>
+        <v>1.82392132282257</v>
       </c>
       <c r="H129" t="n">
         <v>0</v>
@@ -4139,7 +4139,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G130" t="n">
-        <v>1.83871006965637</v>
+        <v>1.83871018886566</v>
       </c>
       <c r="H130" t="n">
         <v>8000</v>
@@ -4197,7 +4197,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G132" t="n">
-        <v>1.78448522090912</v>
+        <v>1.78448510169983</v>
       </c>
       <c r="H132" t="n">
         <v>9000</v>
@@ -4313,7 +4313,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G136" t="n">
-        <v>1.87321662902832</v>
+        <v>1.87321650981903</v>
       </c>
       <c r="H136" t="n">
         <v>4000</v>
@@ -4400,7 +4400,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G139" t="n">
-        <v>1.87321662902832</v>
+        <v>1.87321650981903</v>
       </c>
       <c r="H139" t="n">
         <v>5000</v>
@@ -4429,7 +4429,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G140" t="n">
-        <v>1.87321662902832</v>
+        <v>1.87321650981903</v>
       </c>
       <c r="H140" t="n">
         <v>18000</v>
@@ -4458,7 +4458,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G141" t="n">
-        <v>1.82392144203186</v>
+        <v>1.82392132282257</v>
       </c>
       <c r="H141" t="n">
         <v>12000</v>
@@ -4487,7 +4487,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G142" t="n">
-        <v>1.82392144203186</v>
+        <v>1.82392132282257</v>
       </c>
       <c r="H142" t="n">
         <v>13000</v>
@@ -4748,7 +4748,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G151" t="n">
-        <v>1.74011957645416</v>
+        <v>1.74011969566345</v>
       </c>
       <c r="H151" t="n">
         <v>30000</v>
@@ -4777,7 +4777,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G152" t="n">
-        <v>1.76969659328461</v>
+        <v>1.76969683170319</v>
       </c>
       <c r="H152" t="n">
         <v>4000</v>
@@ -4835,7 +4835,7 @@
         <v>1.81500005722046</v>
       </c>
       <c r="G154" t="n">
-        <v>1.78941476345062</v>
+        <v>1.7894150018692</v>
       </c>
       <c r="H154" t="n">
         <v>10000</v>
@@ -4864,7 +4864,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G155" t="n">
-        <v>1.82392144203186</v>
+        <v>1.82392132282257</v>
       </c>
       <c r="H155" t="n">
         <v>13000</v>
@@ -4893,7 +4893,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G156" t="n">
-        <v>1.82392144203186</v>
+        <v>1.82392132282257</v>
       </c>
       <c r="H156" t="n">
         <v>0</v>
@@ -4922,7 +4922,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G157" t="n">
-        <v>1.83871006965637</v>
+        <v>1.83871018886566</v>
       </c>
       <c r="H157" t="n">
         <v>2000</v>
@@ -4980,7 +4980,7 @@
         <v>1.81500005722046</v>
       </c>
       <c r="G159" t="n">
-        <v>1.78941476345062</v>
+        <v>1.7894150018692</v>
       </c>
       <c r="H159" t="n">
         <v>5000</v>
@@ -5212,7 +5212,7 @@
         <v>1.81500005722046</v>
       </c>
       <c r="G167" t="n">
-        <v>1.78941476345062</v>
+        <v>1.7894150018692</v>
       </c>
       <c r="H167" t="n">
         <v>3000</v>
@@ -5299,7 +5299,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G170" t="n">
-        <v>1.83871006965637</v>
+        <v>1.83871018886566</v>
       </c>
       <c r="H170" t="n">
         <v>39000</v>
@@ -5328,7 +5328,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G171" t="n">
-        <v>1.83871006965637</v>
+        <v>1.83871018886566</v>
       </c>
       <c r="H171" t="n">
         <v>0</v>
@@ -5444,7 +5444,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G175" t="n">
-        <v>1.86828708648682</v>
+        <v>1.86828720569611</v>
       </c>
       <c r="H175" t="n">
         <v>17000</v>
@@ -5473,7 +5473,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G176" t="n">
-        <v>1.83871006965637</v>
+        <v>1.83871018886566</v>
       </c>
       <c r="H176" t="n">
         <v>47000</v>
@@ -5502,7 +5502,7 @@
         <v>1.875</v>
       </c>
       <c r="G177" t="n">
-        <v>1.8485689163208</v>
+        <v>1.84856903553009</v>
       </c>
       <c r="H177" t="n">
         <v>20000</v>
@@ -5589,7 +5589,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G180" t="n">
-        <v>1.88800513744354</v>
+        <v>1.88800525665283</v>
       </c>
       <c r="H180" t="n">
         <v>73000</v>
@@ -5618,7 +5618,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G181" t="n">
-        <v>1.90279352664948</v>
+        <v>1.90279364585876</v>
       </c>
       <c r="H181" t="n">
         <v>23000</v>
@@ -5676,7 +5676,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G183" t="n">
-        <v>2.03096127510071</v>
+        <v>2.03096103668213</v>
       </c>
       <c r="H183" t="n">
         <v>24000</v>
@@ -5705,7 +5705,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G184" t="n">
-        <v>2.01124310493469</v>
+        <v>2.01124286651611</v>
       </c>
       <c r="H184" t="n">
         <v>3000</v>
@@ -5734,7 +5734,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G185" t="n">
-        <v>2.03096127510071</v>
+        <v>2.03096103668213</v>
       </c>
       <c r="H185" t="n">
         <v>54000</v>
@@ -5763,7 +5763,7 @@
         <v>1.99500000476837</v>
       </c>
       <c r="G186" t="n">
-        <v>1.96687746047974</v>
+        <v>1.96687757968903</v>
       </c>
       <c r="H186" t="n">
         <v>28000</v>
@@ -5821,7 +5821,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G188" t="n">
-        <v>2.01124310493469</v>
+        <v>2.01124286651611</v>
       </c>
       <c r="H188" t="n">
         <v>4000</v>
@@ -5850,7 +5850,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G189" t="n">
-        <v>2.01124310493469</v>
+        <v>2.01124286651611</v>
       </c>
       <c r="H189" t="n">
         <v>0</v>
@@ -5908,7 +5908,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G191" t="n">
-        <v>1.93237090110779</v>
+        <v>1.9323707818985</v>
       </c>
       <c r="H191" t="n">
         <v>8000</v>
@@ -5937,7 +5937,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G192" t="n">
-        <v>1.93237090110779</v>
+        <v>1.9323707818985</v>
       </c>
       <c r="H192" t="n">
         <v>2000</v>
@@ -5966,7 +5966,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G193" t="n">
-        <v>1.93237090110779</v>
+        <v>1.9323707818985</v>
       </c>
       <c r="H193" t="n">
         <v>0</v>
@@ -5995,7 +5995,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G194" t="n">
-        <v>1.92251181602478</v>
+        <v>1.92251169681549</v>
       </c>
       <c r="H194" t="n">
         <v>6000</v>
@@ -6053,7 +6053,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G196" t="n">
-        <v>1.89293456077576</v>
+        <v>1.89293467998505</v>
       </c>
       <c r="H196" t="n">
         <v>23000</v>
@@ -6169,7 +6169,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G200" t="n">
-        <v>1.92251181602478</v>
+        <v>1.92251169681549</v>
       </c>
       <c r="H200" t="n">
         <v>18000</v>
@@ -6198,7 +6198,7 @@
         <v>1.95500004291534</v>
       </c>
       <c r="G201" t="n">
-        <v>1.92744123935699</v>
+        <v>1.92744135856628</v>
       </c>
       <c r="H201" t="n">
         <v>9000</v>
@@ -6285,7 +6285,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G204" t="n">
-        <v>1.92251181602478</v>
+        <v>1.92251169681549</v>
       </c>
       <c r="H204" t="n">
         <v>8000</v>
@@ -6314,7 +6314,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G205" t="n">
-        <v>1.93237090110779</v>
+        <v>1.9323707818985</v>
       </c>
       <c r="H205" t="n">
         <v>12000</v>
@@ -6343,7 +6343,7 @@
         <v>1.95500004291534</v>
       </c>
       <c r="G206" t="n">
-        <v>1.92744123935699</v>
+        <v>1.92744135856628</v>
       </c>
       <c r="H206" t="n">
         <v>7000</v>
@@ -6372,7 +6372,7 @@
         <v>1.95500004291534</v>
       </c>
       <c r="G207" t="n">
-        <v>1.92744123935699</v>
+        <v>1.92744135856628</v>
       </c>
       <c r="H207" t="n">
         <v>0</v>
@@ -6430,7 +6430,7 @@
         <v>1.9650000333786</v>
       </c>
       <c r="G209" t="n">
-        <v>1.93730032444</v>
+        <v>1.93730044364929</v>
       </c>
       <c r="H209" t="n">
         <v>11000</v>
@@ -6546,7 +6546,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G213" t="n">
-        <v>1.92251181602478</v>
+        <v>1.92251169681549</v>
       </c>
       <c r="H213" t="n">
         <v>20000</v>
@@ -6575,7 +6575,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G214" t="n">
-        <v>1.92251181602478</v>
+        <v>1.92251169681549</v>
       </c>
       <c r="H214" t="n">
         <v>1000</v>
@@ -6691,7 +6691,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G218" t="n">
-        <v>1.89293456077576</v>
+        <v>1.89293467998505</v>
       </c>
       <c r="H218" t="n">
         <v>8000</v>
@@ -6720,7 +6720,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G219" t="n">
-        <v>1.89293456077576</v>
+        <v>1.89293467998505</v>
       </c>
       <c r="H219" t="n">
         <v>1000</v>
@@ -6778,7 +6778,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G221" t="n">
-        <v>1.92251181602478</v>
+        <v>1.92251169681549</v>
       </c>
       <c r="H221" t="n">
         <v>2000</v>
@@ -6807,7 +6807,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G222" t="n">
-        <v>1.92251181602478</v>
+        <v>1.92251169681549</v>
       </c>
       <c r="H222" t="n">
         <v>0</v>
@@ -6836,7 +6836,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G223" t="n">
-        <v>1.92251181602478</v>
+        <v>1.92251169681549</v>
       </c>
       <c r="H223" t="n">
         <v>0</v>
@@ -6865,7 +6865,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G224" t="n">
-        <v>1.92251181602478</v>
+        <v>1.92251169681549</v>
       </c>
       <c r="H224" t="n">
         <v>3000</v>
@@ -6952,7 +6952,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G227" t="n">
-        <v>1.98166608810425</v>
+        <v>1.98166596889496</v>
       </c>
       <c r="H227" t="n">
         <v>10000</v>
@@ -6981,7 +6981,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G228" t="n">
-        <v>2.00138378143311</v>
+        <v>2.00138425827026</v>
       </c>
       <c r="H228" t="n">
         <v>18000</v>
@@ -7068,7 +7068,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G231" t="n">
-        <v>2.22814154624939</v>
+        <v>2.22814178466797</v>
       </c>
       <c r="H231" t="n">
         <v>86000</v>
@@ -7155,7 +7155,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G234" t="n">
-        <v>2.16898798942566</v>
+        <v>2.16898775100708</v>
       </c>
       <c r="H234" t="n">
         <v>85000</v>
@@ -7184,7 +7184,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G235" t="n">
-        <v>2.14926981925964</v>
+        <v>2.14926958084106</v>
       </c>
       <c r="H235" t="n">
         <v>11000</v>
@@ -7213,7 +7213,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G236" t="n">
-        <v>2.19856452941895</v>
+        <v>2.1985650062561</v>
       </c>
       <c r="H236" t="n">
         <v>9000</v>
@@ -7242,7 +7242,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G237" t="n">
-        <v>2.1887059211731</v>
+        <v>2.18870568275452</v>
       </c>
       <c r="H237" t="n">
         <v>5000</v>
@@ -7358,7 +7358,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G241" t="n">
-        <v>2.22814154624939</v>
+        <v>2.22814178466797</v>
       </c>
       <c r="H241" t="n">
         <v>5000</v>
@@ -7445,7 +7445,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G244" t="n">
-        <v>2.29715490341187</v>
+        <v>2.29715514183044</v>
       </c>
       <c r="H244" t="n">
         <v>6000</v>
@@ -7474,7 +7474,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G245" t="n">
-        <v>2.29715490341187</v>
+        <v>2.29715514183044</v>
       </c>
       <c r="H245" t="n">
         <v>0</v>
@@ -7503,7 +7503,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G246" t="n">
-        <v>2.28729605674744</v>
+        <v>2.28729581832886</v>
       </c>
       <c r="H246" t="n">
         <v>12000</v>
@@ -7532,7 +7532,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G247" t="n">
-        <v>2.28729605674744</v>
+        <v>2.28729581832886</v>
       </c>
       <c r="H247" t="n">
         <v>2000</v>
@@ -7706,7 +7706,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G253" t="n">
-        <v>2.40560460090637</v>
+        <v>2.40560436248779</v>
       </c>
       <c r="H253" t="n">
         <v>26000</v>
@@ -7764,7 +7764,7 @@
         <v>2.5</v>
       </c>
       <c r="G255" t="n">
-        <v>2.46475863456726</v>
+        <v>2.46475887298584</v>
       </c>
       <c r="H255" t="n">
         <v>11000</v>
@@ -7793,7 +7793,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G256" t="n">
-        <v>2.55348968505859</v>
+        <v>2.55348992347717</v>
       </c>
       <c r="H256" t="n">
         <v>21000</v>
@@ -7822,7 +7822,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G257" t="n">
-        <v>2.55348968505859</v>
+        <v>2.55348992347717</v>
       </c>
       <c r="H257" t="n">
         <v>6000</v>
@@ -7851,7 +7851,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G258" t="n">
-        <v>2.61264419555664</v>
+        <v>2.61264443397522</v>
       </c>
       <c r="H258" t="n">
         <v>6000</v>
@@ -7880,7 +7880,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G259" t="n">
-        <v>2.59292602539062</v>
+        <v>2.59292650222778</v>
       </c>
       <c r="H259" t="n">
         <v>5000</v>
@@ -7909,7 +7909,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G260" t="n">
-        <v>2.74081182479858</v>
+        <v>2.74081158638</v>
       </c>
       <c r="H260" t="n">
         <v>51000</v>
@@ -7938,7 +7938,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G261" t="n">
-        <v>2.6619393825531</v>
+        <v>2.66193962097168</v>
       </c>
       <c r="H261" t="n">
         <v>22000</v>
@@ -8054,7 +8054,7 @@
         <v>3</v>
       </c>
       <c r="G265" t="n">
-        <v>2.95771026611328</v>
+        <v>2.95771050453186</v>
       </c>
       <c r="H265" t="n">
         <v>85000</v>
@@ -8083,7 +8083,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G266" t="n">
-        <v>2.87883830070496</v>
+        <v>2.87883806228638</v>
       </c>
       <c r="H266" t="n">
         <v>27000</v>
@@ -8141,7 +8141,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G268" t="n">
-        <v>2.76052951812744</v>
+        <v>2.76052975654602</v>
       </c>
       <c r="H268" t="n">
         <v>35000</v>
@@ -8170,7 +8170,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G269" t="n">
-        <v>2.76052951812744</v>
+        <v>2.76052975654602</v>
       </c>
       <c r="H269" t="n">
         <v>3000</v>
@@ -8199,7 +8199,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G270" t="n">
-        <v>2.77038884162903</v>
+        <v>2.77038860321045</v>
       </c>
       <c r="H270" t="n">
         <v>11000</v>
@@ -8228,7 +8228,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G271" t="n">
-        <v>2.84926104545593</v>
+        <v>2.84926152229309</v>
       </c>
       <c r="H271" t="n">
         <v>21000</v>
@@ -8257,7 +8257,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G272" t="n">
-        <v>2.99714684486389</v>
+        <v>2.99714660644531</v>
       </c>
       <c r="H272" t="n">
         <v>21000</v>
@@ -8286,7 +8286,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G273" t="n">
-        <v>2.96756958961487</v>
+        <v>2.96756935119629</v>
       </c>
       <c r="H273" t="n">
         <v>22000</v>
@@ -8402,7 +8402,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G277" t="n">
-        <v>3.17460918426514</v>
+        <v>3.17460894584656</v>
       </c>
       <c r="H277" t="n">
         <v>36000</v>
@@ -8431,7 +8431,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G278" t="n">
-        <v>3.18446803092957</v>
+        <v>3.18446850776672</v>
       </c>
       <c r="H278" t="n">
         <v>19000</v>
@@ -8518,7 +8518,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G281" t="n">
-        <v>3.18446803092957</v>
+        <v>3.18446850776672</v>
       </c>
       <c r="H281" t="n">
         <v>10000</v>
@@ -8547,7 +8547,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G282" t="n">
-        <v>3.21404504776001</v>
+        <v>3.21404528617859</v>
       </c>
       <c r="H282" t="n">
         <v>6000</v>
@@ -8692,7 +8692,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G287" t="n">
-        <v>3.60840702056885</v>
+        <v>3.60840678215027</v>
       </c>
       <c r="H287" t="n">
         <v>86000</v>
@@ -8750,7 +8750,7 @@
         <v>3.75</v>
       </c>
       <c r="G289" t="n">
-        <v>3.6971378326416</v>
+        <v>3.69713807106018</v>
       </c>
       <c r="H289" t="n">
         <v>24000</v>
@@ -8808,7 +8808,7 @@
         <v>3.75</v>
       </c>
       <c r="G291" t="n">
-        <v>3.6971378326416</v>
+        <v>3.69713807106018</v>
       </c>
       <c r="H291" t="n">
         <v>16000</v>
@@ -8837,7 +8837,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G292" t="n">
-        <v>3.64784288406372</v>
+        <v>3.64784264564514</v>
       </c>
       <c r="H292" t="n">
         <v>5000</v>
@@ -8866,7 +8866,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G293" t="n">
-        <v>3.64784288406372</v>
+        <v>3.64784264564514</v>
       </c>
       <c r="H293" t="n">
         <v>16000</v>
@@ -8895,7 +8895,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G294" t="n">
-        <v>3.53939318656921</v>
+        <v>3.53939366340637</v>
       </c>
       <c r="H294" t="n">
         <v>30000</v>
@@ -9069,7 +9069,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G300" t="n">
-        <v>3.48023915290833</v>
+        <v>3.4802393913269</v>
       </c>
       <c r="H300" t="n">
         <v>15000</v>
@@ -9243,7 +9243,7 @@
         <v>3.75</v>
       </c>
       <c r="G306" t="n">
-        <v>3.6971378326416</v>
+        <v>3.69713807106018</v>
       </c>
       <c r="H306" t="n">
         <v>16000</v>
@@ -9272,7 +9272,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G307" t="n">
-        <v>3.97319102287292</v>
+        <v>3.9731912612915</v>
       </c>
       <c r="H307" t="n">
         <v>45000</v>
@@ -9359,7 +9359,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G310" t="n">
-        <v>4.33797597885132</v>
+        <v>4.33797550201416</v>
       </c>
       <c r="H310" t="n">
         <v>1000</v>
@@ -9417,7 +9417,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G312" t="n">
-        <v>3.99290919303894</v>
+        <v>3.99290943145752</v>
       </c>
       <c r="H312" t="n">
         <v>51000</v>
@@ -9504,7 +9504,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G315" t="n">
-        <v>4.09149980545044</v>
+        <v>4.09149932861328</v>
       </c>
       <c r="H315" t="n">
         <v>8000</v>
@@ -9591,7 +9591,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G318" t="n">
-        <v>4.17037200927734</v>
+        <v>4.17037153244019</v>
       </c>
       <c r="H318" t="n">
         <v>10000</v>
@@ -9649,7 +9649,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G320" t="n">
-        <v>4.23938512802124</v>
+        <v>4.2393856048584</v>
       </c>
       <c r="H320" t="n">
         <v>9000</v>
@@ -9794,7 +9794,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G325" t="n">
-        <v>4.06192255020142</v>
+        <v>4.06192207336426</v>
       </c>
       <c r="H325" t="n">
         <v>7000</v>
@@ -9823,7 +9823,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G326" t="n">
-        <v>4.00276756286621</v>
+        <v>4.00276851654053</v>
       </c>
       <c r="H326" t="n">
         <v>5000</v>
@@ -9910,7 +9910,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G329" t="n">
-        <v>4.02248620986938</v>
+        <v>4.02248573303223</v>
       </c>
       <c r="H329" t="n">
         <v>5000</v>
@@ -10084,7 +10084,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G335" t="n">
-        <v>4.17037200927734</v>
+        <v>4.17037153244019</v>
       </c>
       <c r="H335" t="n">
         <v>3000</v>
@@ -10113,7 +10113,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G336" t="n">
-        <v>4.00276756286621</v>
+        <v>4.00276851654053</v>
       </c>
       <c r="H336" t="n">
         <v>3000</v>
@@ -10142,7 +10142,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G337" t="n">
-        <v>4.00276756286621</v>
+        <v>4.00276851654053</v>
       </c>
       <c r="H337" t="n">
         <v>0</v>
@@ -10287,7 +10287,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G342" t="n">
-        <v>4.06192255020142</v>
+        <v>4.06192207336426</v>
       </c>
       <c r="H342" t="n">
         <v>5000</v>
@@ -10432,7 +10432,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G347" t="n">
-        <v>4.02248620986938</v>
+        <v>4.02248573303223</v>
       </c>
       <c r="H347" t="n">
         <v>3000</v>
@@ -10461,7 +10461,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G348" t="n">
-        <v>4.02248620986938</v>
+        <v>4.02248573303223</v>
       </c>
       <c r="H348" t="n">
         <v>16500</v>
@@ -10490,7 +10490,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G349" t="n">
-        <v>4.21966695785522</v>
+        <v>4.21966648101807</v>
       </c>
       <c r="H349" t="n">
         <v>21000</v>
@@ -10519,7 +10519,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G350" t="n">
-        <v>4.23938512802124</v>
+        <v>4.2393856048584</v>
       </c>
       <c r="H350" t="n">
         <v>24000</v>
@@ -10548,7 +10548,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G351" t="n">
-        <v>4.23938512802124</v>
+        <v>4.2393856048584</v>
       </c>
       <c r="H351" t="n">
         <v>4500</v>
@@ -10577,7 +10577,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G352" t="n">
-        <v>4.19994878768921</v>
+        <v>4.19994926452637</v>
       </c>
       <c r="H352" t="n">
         <v>8000</v>
@@ -10635,7 +10635,7 @@
         <v>4.25</v>
       </c>
       <c r="G354" t="n">
-        <v>4.1900897026062</v>
+        <v>4.19009017944336</v>
       </c>
       <c r="H354" t="n">
         <v>20500</v>
@@ -10780,7 +10780,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G359" t="n">
-        <v>4.21966695785522</v>
+        <v>4.21966648101807</v>
       </c>
       <c r="H359" t="n">
         <v>14500</v>
@@ -10867,7 +10867,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G362" t="n">
-        <v>4.09149980545044</v>
+        <v>4.09149932861328</v>
       </c>
       <c r="H362" t="n">
         <v>4500</v>
@@ -10896,7 +10896,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G363" t="n">
-        <v>4.12107610702515</v>
+        <v>4.1210765838623</v>
       </c>
       <c r="H363" t="n">
         <v>500</v>
@@ -10925,7 +10925,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G364" t="n">
-        <v>4.12107610702515</v>
+        <v>4.1210765838623</v>
       </c>
       <c r="H364" t="n">
         <v>0</v>
@@ -10954,7 +10954,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G365" t="n">
-        <v>4.12107610702515</v>
+        <v>4.1210765838623</v>
       </c>
       <c r="H365" t="n">
         <v>0</v>
@@ -11128,7 +11128,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G371" t="n">
-        <v>4.01262760162354</v>
+        <v>4.01262712478638</v>
       </c>
       <c r="H371" t="n">
         <v>6000</v>
@@ -11273,7 +11273,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G376" t="n">
-        <v>4.19994878768921</v>
+        <v>4.19994926452637</v>
       </c>
       <c r="H376" t="n">
         <v>7500</v>
@@ -11360,7 +11360,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G379" t="n">
-        <v>4.21966695785522</v>
+        <v>4.21966648101807</v>
       </c>
       <c r="H379" t="n">
         <v>67000</v>
@@ -11389,7 +11389,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G380" t="n">
-        <v>4.21966695785522</v>
+        <v>4.21966648101807</v>
       </c>
       <c r="H380" t="n">
         <v>3000</v>
@@ -11447,7 +11447,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G382" t="n">
-        <v>4.29853963851929</v>
+        <v>4.29853916168213</v>
       </c>
       <c r="H382" t="n">
         <v>35000</v>
@@ -11505,7 +11505,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G384" t="n">
-        <v>4.33797597885132</v>
+        <v>4.33797550201416</v>
       </c>
       <c r="H384" t="n">
         <v>17000</v>
@@ -11534,7 +11534,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G385" t="n">
-        <v>4.36755228042603</v>
+        <v>4.36755180358887</v>
       </c>
       <c r="H385" t="n">
         <v>4000</v>
@@ -11592,7 +11592,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G387" t="n">
-        <v>4.36755228042603</v>
+        <v>4.36755180358887</v>
       </c>
       <c r="H387" t="n">
         <v>6000</v>
@@ -11621,7 +11621,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G388" t="n">
-        <v>4.36755228042603</v>
+        <v>4.36755180358887</v>
       </c>
       <c r="H388" t="n">
         <v>13500</v>
@@ -11679,7 +11679,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G390" t="n">
-        <v>4.33797597885132</v>
+        <v>4.33797550201416</v>
       </c>
       <c r="H390" t="n">
         <v>15000</v>
@@ -11737,7 +11737,7 @@
         <v>4.25</v>
       </c>
       <c r="G392" t="n">
-        <v>4.1900897026062</v>
+        <v>4.19009017944336</v>
       </c>
       <c r="H392" t="n">
         <v>8000</v>
@@ -11766,7 +11766,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G393" t="n">
-        <v>4.33797597885132</v>
+        <v>4.33797550201416</v>
       </c>
       <c r="H393" t="n">
         <v>6000</v>
@@ -11795,7 +11795,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G394" t="n">
-        <v>4.40698862075806</v>
+        <v>4.4069881439209</v>
       </c>
       <c r="H394" t="n">
         <v>2000</v>
@@ -11882,7 +11882,7 @@
         <v>4.25</v>
       </c>
       <c r="G397" t="n">
-        <v>4.1900897026062</v>
+        <v>4.19009017944336</v>
       </c>
       <c r="H397" t="n">
         <v>7500</v>
@@ -12027,7 +12027,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G402" t="n">
-        <v>4.19994878768921</v>
+        <v>4.19994926452637</v>
       </c>
       <c r="H402" t="n">
         <v>23500</v>
@@ -12056,7 +12056,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G403" t="n">
-        <v>4.29853963851929</v>
+        <v>4.29853916168213</v>
       </c>
       <c r="H403" t="n">
         <v>26500</v>
@@ -12085,7 +12085,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G404" t="n">
-        <v>4.33797597885132</v>
+        <v>4.33797550201416</v>
       </c>
       <c r="H404" t="n">
         <v>37500</v>
@@ -12114,7 +12114,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G405" t="n">
-        <v>4.38726997375488</v>
+        <v>4.38727045059204</v>
       </c>
       <c r="H405" t="n">
         <v>13000</v>
@@ -12143,7 +12143,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G406" t="n">
-        <v>4.39712905883789</v>
+        <v>4.39713001251221</v>
       </c>
       <c r="H406" t="n">
         <v>19500</v>
@@ -12172,7 +12172,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G407" t="n">
-        <v>4.38726997375488</v>
+        <v>4.38727045059204</v>
       </c>
       <c r="H407" t="n">
         <v>6000</v>
@@ -12201,7 +12201,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G408" t="n">
-        <v>4.38726997375488</v>
+        <v>4.38727045059204</v>
       </c>
       <c r="H408" t="n">
         <v>85000</v>
@@ -12230,7 +12230,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G409" t="n">
-        <v>4.49571943283081</v>
+        <v>4.49571990966797</v>
       </c>
       <c r="H409" t="n">
         <v>23000</v>
@@ -12259,7 +12259,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G410" t="n">
-        <v>4.63374614715576</v>
+        <v>4.63374662399292</v>
       </c>
       <c r="H410" t="n">
         <v>92000</v>
@@ -12317,7 +12317,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G412" t="n">
-        <v>5.30416059494019</v>
+        <v>5.30416107177734</v>
       </c>
       <c r="H412" t="n">
         <v>82500</v>
@@ -12375,7 +12375,7 @@
         <v>5</v>
       </c>
       <c r="G414" t="n">
-        <v>4.92951726913452</v>
+        <v>4.92951774597168</v>
       </c>
       <c r="H414" t="n">
         <v>45500</v>
@@ -12404,7 +12404,7 @@
         <v>5</v>
       </c>
       <c r="G415" t="n">
-        <v>4.92951726913452</v>
+        <v>4.92951774597168</v>
       </c>
       <c r="H415" t="n">
         <v>14500</v>
@@ -12462,7 +12462,7 @@
         <v>5</v>
       </c>
       <c r="G417" t="n">
-        <v>4.92951726913452</v>
+        <v>4.92951774597168</v>
       </c>
       <c r="H417" t="n">
         <v>7500</v>
@@ -12491,7 +12491,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G418" t="n">
-        <v>4.98867130279541</v>
+        <v>4.98867177963257</v>
       </c>
       <c r="H418" t="n">
         <v>23500</v>
@@ -12549,7 +12549,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G420" t="n">
-        <v>5.00838947296143</v>
+        <v>5.00838899612427</v>
       </c>
       <c r="H420" t="n">
         <v>4500</v>
@@ -12578,7 +12578,7 @@
         <v>5</v>
       </c>
       <c r="G421" t="n">
-        <v>4.92951726913452</v>
+        <v>4.92951774597168</v>
       </c>
       <c r="H421" t="n">
         <v>8500</v>
@@ -12607,7 +12607,7 @@
         <v>5</v>
       </c>
       <c r="G422" t="n">
-        <v>4.92951726913452</v>
+        <v>4.92951774597168</v>
       </c>
       <c r="H422" t="n">
         <v>9500</v>
@@ -12636,7 +12636,7 @@
         <v>5</v>
       </c>
       <c r="G423" t="n">
-        <v>4.92951726913452</v>
+        <v>4.92951774597168</v>
       </c>
       <c r="H423" t="n">
         <v>38500</v>
@@ -12781,7 +12781,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G428" t="n">
-        <v>5.00838947296143</v>
+        <v>5.00838899612427</v>
       </c>
       <c r="H428" t="n">
         <v>2500</v>
@@ -12810,7 +12810,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G429" t="n">
-        <v>5.1266975402832</v>
+        <v>5.12669801712036</v>
       </c>
       <c r="H429" t="n">
         <v>7000</v>
@@ -12839,7 +12839,7 @@
         <v>5</v>
       </c>
       <c r="G430" t="n">
-        <v>4.92951726913452</v>
+        <v>4.92951774597168</v>
       </c>
       <c r="H430" t="n">
         <v>8500</v>
@@ -12868,7 +12868,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G431" t="n">
-        <v>4.98867130279541</v>
+        <v>4.98867177963257</v>
       </c>
       <c r="H431" t="n">
         <v>8000</v>
@@ -12897,7 +12897,7 @@
         <v>5</v>
       </c>
       <c r="G432" t="n">
-        <v>4.92951726913452</v>
+        <v>4.92951774597168</v>
       </c>
       <c r="H432" t="n">
         <v>1000</v>
@@ -12955,7 +12955,7 @@
         <v>5</v>
       </c>
       <c r="G434" t="n">
-        <v>4.92951726913452</v>
+        <v>4.92951774597168</v>
       </c>
       <c r="H434" t="n">
         <v>7000</v>
@@ -13042,7 +13042,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G437" t="n">
-        <v>4.90979862213135</v>
+        <v>4.90979957580566</v>
       </c>
       <c r="H437" t="n">
         <v>16000</v>
@@ -13071,7 +13071,7 @@
         <v>5</v>
       </c>
       <c r="G438" t="n">
-        <v>4.92951726913452</v>
+        <v>4.92951774597168</v>
       </c>
       <c r="H438" t="n">
         <v>7500</v>
@@ -13129,7 +13129,7 @@
         <v>5</v>
       </c>
       <c r="G440" t="n">
-        <v>4.92951726913452</v>
+        <v>4.92951774597168</v>
       </c>
       <c r="H440" t="n">
         <v>2000</v>
@@ -13187,7 +13187,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G442" t="n">
-        <v>4.90979862213135</v>
+        <v>4.90979957580566</v>
       </c>
       <c r="H442" t="n">
         <v>11000</v>
@@ -13361,7 +13361,7 @@
         <v>5</v>
       </c>
       <c r="G448" t="n">
-        <v>4.92951726913452</v>
+        <v>4.92951774597168</v>
       </c>
       <c r="H448" t="n">
         <v>19060</v>
@@ -13390,7 +13390,7 @@
         <v>5</v>
       </c>
       <c r="G449" t="n">
-        <v>4.92951726913452</v>
+        <v>4.92951774597168</v>
       </c>
       <c r="H449" t="n">
         <v>10200</v>
@@ -13419,7 +13419,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G450" t="n">
-        <v>4.8309268951416</v>
+        <v>4.83092737197876</v>
       </c>
       <c r="H450" t="n">
         <v>30540</v>
@@ -13448,7 +13448,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G451" t="n">
-        <v>4.8309268951416</v>
+        <v>4.83092737197876</v>
       </c>
       <c r="H451" t="n">
         <v>3150</v>
@@ -13477,7 +13477,7 @@
         <v>5</v>
       </c>
       <c r="G452" t="n">
-        <v>4.92951726913452</v>
+        <v>4.92951774597168</v>
       </c>
       <c r="H452" t="n">
         <v>1500</v>
@@ -13506,7 +13506,7 @@
         <v>5</v>
       </c>
       <c r="G453" t="n">
-        <v>4.92951726913452</v>
+        <v>4.92951774597168</v>
       </c>
       <c r="H453" t="n">
         <v>900</v>
@@ -13593,7 +13593,7 @@
         <v>5</v>
       </c>
       <c r="G456" t="n">
-        <v>4.92951726913452</v>
+        <v>4.92951774597168</v>
       </c>
       <c r="H456" t="n">
         <v>2220</v>
@@ -13651,7 +13651,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G458" t="n">
-        <v>5.50134086608887</v>
+        <v>5.50134134292603</v>
       </c>
       <c r="H458" t="n">
         <v>75450</v>
@@ -13680,7 +13680,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G459" t="n">
-        <v>5.26472520828247</v>
+        <v>5.26472425460815</v>
       </c>
       <c r="H459" t="n">
         <v>23670</v>
@@ -13709,7 +13709,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G460" t="n">
-        <v>5.34359741210938</v>
+        <v>5.34359693527222</v>
       </c>
       <c r="H460" t="n">
         <v>6980</v>
@@ -13738,7 +13738,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G461" t="n">
-        <v>5.30416059494019</v>
+        <v>5.30416107177734</v>
       </c>
       <c r="H461" t="n">
         <v>2900</v>
@@ -13767,7 +13767,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G462" t="n">
-        <v>5.22528839111328</v>
+        <v>5.22528886795044</v>
       </c>
       <c r="H462" t="n">
         <v>3000</v>
@@ -13796,7 +13796,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G463" t="n">
-        <v>5.22528839111328</v>
+        <v>5.22528886795044</v>
       </c>
       <c r="H463" t="n">
         <v>2000</v>
@@ -13883,7 +13883,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G466" t="n">
-        <v>5.1266975402832</v>
+        <v>5.12669801712036</v>
       </c>
       <c r="H466" t="n">
         <v>7070</v>
@@ -13912,7 +13912,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G467" t="n">
-        <v>5.1266975402832</v>
+        <v>5.12669801712036</v>
       </c>
       <c r="H467" t="n">
         <v>200</v>
@@ -13970,7 +13970,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G469" t="n">
-        <v>5.22528839111328</v>
+        <v>5.22528886795044</v>
       </c>
       <c r="H469" t="n">
         <v>3400</v>
@@ -14028,7 +14028,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G471" t="n">
-        <v>5.22528839111328</v>
+        <v>5.22528886795044</v>
       </c>
       <c r="H471" t="n">
         <v>450</v>
@@ -14057,7 +14057,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G472" t="n">
-        <v>5.22528839111328</v>
+        <v>5.22528886795044</v>
       </c>
       <c r="H472" t="n">
         <v>0</v>
@@ -14115,7 +14115,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G474" t="n">
-        <v>4.98867130279541</v>
+        <v>4.98867177963257</v>
       </c>
       <c r="H474" t="n">
         <v>17780</v>
@@ -14202,7 +14202,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G477" t="n">
-        <v>5.00838947296143</v>
+        <v>5.00838899612427</v>
       </c>
       <c r="H477" t="n">
         <v>1250</v>
@@ -14347,7 +14347,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G482" t="n">
-        <v>5.10697937011719</v>
+        <v>5.10697984695435</v>
       </c>
       <c r="H482" t="n">
         <v>7170</v>
@@ -14376,7 +14376,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G483" t="n">
-        <v>5.1266975402832</v>
+        <v>5.12669801712036</v>
       </c>
       <c r="H483" t="n">
         <v>4620</v>
@@ -14405,7 +14405,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G484" t="n">
-        <v>5.1266975402832</v>
+        <v>5.12669801712036</v>
       </c>
       <c r="H484" t="n">
         <v>6620</v>
@@ -14434,7 +14434,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G485" t="n">
-        <v>5.1266975402832</v>
+        <v>5.12669801712036</v>
       </c>
       <c r="H485" t="n">
         <v>11880</v>
@@ -14550,7 +14550,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G489" t="n">
-        <v>4.98867130279541</v>
+        <v>4.98867177963257</v>
       </c>
       <c r="H489" t="n">
         <v>21530</v>
@@ -14579,7 +14579,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G490" t="n">
-        <v>5.1266975402832</v>
+        <v>5.12669801712036</v>
       </c>
       <c r="H490" t="n">
         <v>26550</v>
@@ -14608,7 +14608,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G491" t="n">
-        <v>4.98867130279541</v>
+        <v>4.98867177963257</v>
       </c>
       <c r="H491" t="n">
         <v>28100</v>
@@ -14695,7 +14695,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G494" t="n">
-        <v>5.10697937011719</v>
+        <v>5.10697984695435</v>
       </c>
       <c r="H494" t="n">
         <v>11420</v>
@@ -14985,7 +14985,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G504" t="n">
-        <v>4.8309268951416</v>
+        <v>4.83092737197876</v>
       </c>
       <c r="H504" t="n">
         <v>16000</v>
@@ -15014,7 +15014,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G505" t="n">
-        <v>4.98867130279541</v>
+        <v>4.98867177963257</v>
       </c>
       <c r="H505" t="n">
         <v>4800</v>
@@ -15043,7 +15043,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G506" t="n">
-        <v>5.1266975402832</v>
+        <v>5.12669801712036</v>
       </c>
       <c r="H506" t="n">
         <v>5270</v>
@@ -15072,7 +15072,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G507" t="n">
-        <v>5.10697937011719</v>
+        <v>5.10697984695435</v>
       </c>
       <c r="H507" t="n">
         <v>3690</v>
@@ -15101,7 +15101,7 @@
         <v>5</v>
       </c>
       <c r="G508" t="n">
-        <v>4.92951726913452</v>
+        <v>4.92951774597168</v>
       </c>
       <c r="H508" t="n">
         <v>5700</v>
@@ -15159,7 +15159,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G510" t="n">
-        <v>4.98867130279541</v>
+        <v>4.98867177963257</v>
       </c>
       <c r="H510" t="n">
         <v>1110</v>
@@ -15246,7 +15246,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G513" t="n">
-        <v>5.00838947296143</v>
+        <v>5.00838899612427</v>
       </c>
       <c r="H513" t="n">
         <v>10130</v>
@@ -15333,7 +15333,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G516" t="n">
-        <v>5.00838947296143</v>
+        <v>5.00838899612427</v>
       </c>
       <c r="H516" t="n">
         <v>640</v>
@@ -15391,7 +15391,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G518" t="n">
-        <v>5.00838947296143</v>
+        <v>5.00838899612427</v>
       </c>
       <c r="H518" t="n">
         <v>3020</v>
@@ -15420,7 +15420,7 @@
         <v>5</v>
       </c>
       <c r="G519" t="n">
-        <v>4.92951726913452</v>
+        <v>4.92951774597168</v>
       </c>
       <c r="H519" t="n">
         <v>12340</v>
@@ -15623,7 +15623,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G526" t="n">
-        <v>5.00838947296143</v>
+        <v>5.00838899612427</v>
       </c>
       <c r="H526" t="n">
         <v>2400</v>
@@ -15739,7 +15739,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G530" t="n">
-        <v>4.73233652114868</v>
+        <v>4.73233699798584</v>
       </c>
       <c r="H530" t="n">
         <v>6730</v>
@@ -15826,7 +15826,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G533" t="n">
-        <v>4.79149103164673</v>
+        <v>4.79149150848389</v>
       </c>
       <c r="H533" t="n">
         <v>6340</v>
@@ -15855,7 +15855,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G534" t="n">
-        <v>4.73233652114868</v>
+        <v>4.73233699798584</v>
       </c>
       <c r="H534" t="n">
         <v>13910</v>
@@ -15884,7 +15884,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G535" t="n">
-        <v>4.73233652114868</v>
+        <v>4.73233699798584</v>
       </c>
       <c r="H535" t="n">
         <v>3100</v>
@@ -15913,7 +15913,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G536" t="n">
-        <v>4.71261835098267</v>
+        <v>4.71261882781982</v>
       </c>
       <c r="H536" t="n">
         <v>153850</v>
@@ -15942,7 +15942,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G537" t="n">
-        <v>4.73233652114868</v>
+        <v>4.73233699798584</v>
       </c>
       <c r="H537" t="n">
         <v>2420</v>
@@ -15971,7 +15971,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G538" t="n">
-        <v>4.89993953704834</v>
+        <v>4.8999400138855</v>
       </c>
       <c r="H538" t="n">
         <v>2830</v>
@@ -16029,7 +16029,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G540" t="n">
-        <v>4.8309268951416</v>
+        <v>4.83092737197876</v>
       </c>
       <c r="H540" t="n">
         <v>1600</v>
@@ -16174,7 +16174,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G545" t="n">
-        <v>4.8309268951416</v>
+        <v>4.83092737197876</v>
       </c>
       <c r="H545" t="n">
         <v>1200</v>
@@ -16203,7 +16203,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G546" t="n">
-        <v>4.75205564498901</v>
+        <v>4.7520546913147</v>
       </c>
       <c r="H546" t="n">
         <v>6100</v>
@@ -16261,7 +16261,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G548" t="n">
-        <v>4.57422399520874</v>
+        <v>4.57422351837158</v>
       </c>
       <c r="H548" t="n">
         <v>17160</v>
@@ -16290,7 +16290,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G549" t="n">
-        <v>4.59398221969604</v>
+        <v>4.5939826965332</v>
       </c>
       <c r="H549" t="n">
         <v>3190</v>
@@ -16348,7 +16348,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G551" t="n">
-        <v>4.7421760559082</v>
+        <v>4.74217557907104</v>
       </c>
       <c r="H551" t="n">
         <v>730</v>
@@ -16377,7 +16377,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G552" t="n">
-        <v>4.78169345855713</v>
+        <v>4.78169393539429</v>
       </c>
       <c r="H552" t="n">
         <v>1640</v>
@@ -16406,7 +16406,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G553" t="n">
-        <v>4.78169345855713</v>
+        <v>4.78169393539429</v>
       </c>
       <c r="H553" t="n">
         <v>0</v>
@@ -16435,7 +16435,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G554" t="n">
-        <v>4.78169345855713</v>
+        <v>4.78169393539429</v>
       </c>
       <c r="H554" t="n">
         <v>0</v>
@@ -16493,7 +16493,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G556" t="n">
-        <v>4.7421760559082</v>
+        <v>4.74217557907104</v>
       </c>
       <c r="H556" t="n">
         <v>13120</v>
@@ -16522,7 +16522,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G557" t="n">
-        <v>4.7421760559082</v>
+        <v>4.74217557907104</v>
       </c>
       <c r="H557" t="n">
         <v>260</v>
@@ -16638,7 +16638,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G561" t="n">
-        <v>4.79157304763794</v>
+        <v>4.79157257080078</v>
       </c>
       <c r="H561" t="n">
         <v>2000</v>
@@ -16667,7 +16667,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G562" t="n">
-        <v>4.92988681793213</v>
+        <v>4.92988634109497</v>
       </c>
       <c r="H562" t="n">
         <v>2500</v>
@@ -16812,7 +16812,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G567" t="n">
-        <v>4.82121181488037</v>
+        <v>4.82121133804321</v>
       </c>
       <c r="H567" t="n">
         <v>2600</v>
@@ -16841,7 +16841,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G568" t="n">
-        <v>4.82121181488037</v>
+        <v>4.82121133804321</v>
       </c>
       <c r="H568" t="n">
         <v>0</v>
@@ -16870,7 +16870,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G569" t="n">
-        <v>4.82121181488037</v>
+        <v>4.82121133804321</v>
       </c>
       <c r="H569" t="n">
         <v>50</v>
@@ -16899,7 +16899,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G570" t="n">
-        <v>4.82121181488037</v>
+        <v>4.82121133804321</v>
       </c>
       <c r="H570" t="n">
         <v>0</v>
@@ -16957,7 +16957,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G572" t="n">
-        <v>4.55446481704712</v>
+        <v>4.55446434020996</v>
       </c>
       <c r="H572" t="n">
         <v>2940</v>
@@ -16986,7 +16986,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G573" t="n">
-        <v>4.43590927124023</v>
+        <v>4.43590974807739</v>
       </c>
       <c r="H573" t="n">
         <v>4370</v>
@@ -17044,7 +17044,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G575" t="n">
-        <v>4.32723474502563</v>
+        <v>4.32723522186279</v>
       </c>
       <c r="H575" t="n">
         <v>1010</v>
@@ -17073,7 +17073,7 @@
         <v>4.5</v>
       </c>
       <c r="G576" t="n">
-        <v>4.44578981399536</v>
+        <v>4.4457893371582</v>
       </c>
       <c r="H576" t="n">
         <v>2400</v>
@@ -17102,7 +17102,7 @@
         <v>4.5</v>
       </c>
       <c r="G577" t="n">
-        <v>4.44578981399536</v>
+        <v>4.4457893371582</v>
       </c>
       <c r="H577" t="n">
         <v>1890</v>
@@ -17131,7 +17131,7 @@
         <v>4.5</v>
       </c>
       <c r="G578" t="n">
-        <v>4.44578981399536</v>
+        <v>4.4457893371582</v>
       </c>
       <c r="H578" t="n">
         <v>550</v>
@@ -17218,7 +17218,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G581" t="n">
-        <v>4.40627145767212</v>
+        <v>4.40627098083496</v>
       </c>
       <c r="H581" t="n">
         <v>1200</v>
@@ -17305,7 +17305,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G584" t="n">
-        <v>4.78169345855713</v>
+        <v>4.78169393539429</v>
       </c>
       <c r="H584" t="n">
         <v>3210</v>
@@ -17334,7 +17334,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G585" t="n">
-        <v>4.59398221969604</v>
+        <v>4.5939826965332</v>
       </c>
       <c r="H585" t="n">
         <v>4270</v>
@@ -17363,7 +17363,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G586" t="n">
-        <v>4.7421760559082</v>
+        <v>4.74217557907104</v>
       </c>
       <c r="H586" t="n">
         <v>200</v>
@@ -17392,7 +17392,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G587" t="n">
-        <v>4.43590927124023</v>
+        <v>4.43590974807739</v>
       </c>
       <c r="H587" t="n">
         <v>18770</v>
@@ -17450,7 +17450,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G589" t="n">
-        <v>4.43590927124023</v>
+        <v>4.43590974807739</v>
       </c>
       <c r="H589" t="n">
         <v>3330</v>
@@ -17479,7 +17479,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G590" t="n">
-        <v>4.38651275634766</v>
+        <v>4.3865122795105</v>
       </c>
       <c r="H590" t="n">
         <v>37290</v>
@@ -17508,7 +17508,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G591" t="n">
-        <v>4.34699440002441</v>
+        <v>4.34699392318726</v>
       </c>
       <c r="H591" t="n">
         <v>420</v>
@@ -17537,7 +17537,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G592" t="n">
-        <v>4.34699440002441</v>
+        <v>4.34699392318726</v>
       </c>
       <c r="H592" t="n">
         <v>35740</v>
@@ -17566,7 +17566,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G593" t="n">
-        <v>4.34699440002441</v>
+        <v>4.34699392318726</v>
       </c>
       <c r="H593" t="n">
         <v>10500</v>
@@ -17595,7 +17595,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G594" t="n">
-        <v>4.48530769348145</v>
+        <v>4.48530721664429</v>
       </c>
       <c r="H594" t="n">
         <v>1520</v>
@@ -17653,7 +17653,7 @@
         <v>4.5</v>
       </c>
       <c r="G596" t="n">
-        <v>4.44578981399536</v>
+        <v>4.4457893371582</v>
       </c>
       <c r="H596" t="n">
         <v>3880</v>
@@ -17682,7 +17682,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G597" t="n">
-        <v>4.40627145767212</v>
+        <v>4.40627098083496</v>
       </c>
       <c r="H597" t="n">
         <v>1930</v>
@@ -17740,7 +17740,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G599" t="n">
-        <v>4.43590927124023</v>
+        <v>4.43590974807739</v>
       </c>
       <c r="H599" t="n">
         <v>690</v>
@@ -17769,7 +17769,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G600" t="n">
-        <v>4.48530769348145</v>
+        <v>4.48530721664429</v>
       </c>
       <c r="H600" t="n">
         <v>1360</v>
@@ -17827,7 +17827,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G602" t="n">
-        <v>4.59398221969604</v>
+        <v>4.5939826965332</v>
       </c>
       <c r="H602" t="n">
         <v>1680</v>
@@ -17914,7 +17914,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G605" t="n">
-        <v>4.83109140396118</v>
+        <v>4.83109092712402</v>
       </c>
       <c r="H605" t="n">
         <v>9220</v>
@@ -17972,7 +17972,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G607" t="n">
-        <v>4.7026572227478</v>
+        <v>4.70265769958496</v>
       </c>
       <c r="H607" t="n">
         <v>2440</v>
@@ -18001,7 +18001,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G608" t="n">
-        <v>4.7026572227478</v>
+        <v>4.70265769958496</v>
       </c>
       <c r="H608" t="n">
         <v>8050</v>
@@ -18088,7 +18088,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G611" t="n">
-        <v>4.72241640090942</v>
+        <v>4.72241592407227</v>
       </c>
       <c r="H611" t="n">
         <v>4980</v>
@@ -18146,7 +18146,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G613" t="n">
-        <v>4.78169345855713</v>
+        <v>4.78169393539429</v>
       </c>
       <c r="H613" t="n">
         <v>1500</v>
@@ -18233,7 +18233,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G616" t="n">
-        <v>4.97928428649902</v>
+        <v>4.97928380966187</v>
       </c>
       <c r="H616" t="n">
         <v>13050</v>
@@ -18262,7 +18262,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G617" t="n">
-        <v>4.97928428649902</v>
+        <v>4.97928380966187</v>
       </c>
       <c r="H617" t="n">
         <v>2400</v>
@@ -18320,7 +18320,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G619" t="n">
-        <v>4.97928428649902</v>
+        <v>4.97928380966187</v>
       </c>
       <c r="H619" t="n">
         <v>1000</v>
@@ -18465,7 +18465,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G624" t="n">
-        <v>5.03856134414673</v>
+        <v>5.03856182098389</v>
       </c>
       <c r="H624" t="n">
         <v>200</v>
@@ -18494,7 +18494,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G625" t="n">
-        <v>5.03856134414673</v>
+        <v>5.03856182098389</v>
       </c>
       <c r="H625" t="n">
         <v>2500</v>
@@ -18523,7 +18523,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G626" t="n">
-        <v>4.92988681793213</v>
+        <v>4.92988634109497</v>
       </c>
       <c r="H626" t="n">
         <v>49150</v>
@@ -18697,7 +18697,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G632" t="n">
-        <v>4.75205516815186</v>
+        <v>4.7520546913147</v>
       </c>
       <c r="H632" t="n">
         <v>3780</v>
@@ -18755,7 +18755,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G634" t="n">
-        <v>4.92988681793213</v>
+        <v>4.92988634109497</v>
       </c>
       <c r="H634" t="n">
         <v>4840</v>
@@ -18929,7 +18929,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G640" t="n">
-        <v>4.79157304763794</v>
+        <v>4.79157257080078</v>
       </c>
       <c r="H640" t="n">
         <v>4000</v>
@@ -18958,7 +18958,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G641" t="n">
-        <v>4.79157304763794</v>
+        <v>4.79157257080078</v>
       </c>
       <c r="H641" t="n">
         <v>0</v>
@@ -18987,7 +18987,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G642" t="n">
-        <v>4.79157304763794</v>
+        <v>4.79157257080078</v>
       </c>
       <c r="H642" t="n">
         <v>4040</v>
@@ -19103,7 +19103,7 @@
         <v>4.5</v>
       </c>
       <c r="G646" t="n">
-        <v>4.44578981399536</v>
+        <v>4.4457893371582</v>
       </c>
       <c r="H646" t="n">
         <v>8070</v>
@@ -19132,7 +19132,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G647" t="n">
-        <v>4.34699440002441</v>
+        <v>4.34699392318726</v>
       </c>
       <c r="H647" t="n">
         <v>89070</v>
@@ -19161,7 +19161,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G648" t="n">
-        <v>4.34699440002441</v>
+        <v>4.34699392318726</v>
       </c>
       <c r="H648" t="n">
         <v>66390</v>
@@ -19190,7 +19190,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G649" t="n">
-        <v>4.39639186859131</v>
+        <v>4.39639139175415</v>
       </c>
       <c r="H649" t="n">
         <v>7440</v>
@@ -19219,7 +19219,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G650" t="n">
-        <v>4.52482557296753</v>
+        <v>4.52482509613037</v>
       </c>
       <c r="H650" t="n">
         <v>11950</v>
@@ -19306,7 +19306,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G653" t="n">
-        <v>4.79157304763794</v>
+        <v>4.79157257080078</v>
       </c>
       <c r="H653" t="n">
         <v>2680</v>
@@ -19393,7 +19393,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G656" t="n">
-        <v>4.72241640090942</v>
+        <v>4.72241592407227</v>
       </c>
       <c r="H656" t="n">
         <v>2060</v>
@@ -19422,7 +19422,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G657" t="n">
-        <v>4.72241640090942</v>
+        <v>4.72241592407227</v>
       </c>
       <c r="H657" t="n">
         <v>0</v>
@@ -19480,7 +19480,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G659" t="n">
-        <v>4.7421760559082</v>
+        <v>4.74217557907104</v>
       </c>
       <c r="H659" t="n">
         <v>60</v>
@@ -19509,7 +19509,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G660" t="n">
-        <v>4.7421760559082</v>
+        <v>4.74217557907104</v>
       </c>
       <c r="H660" t="n">
         <v>12790</v>
@@ -19567,7 +19567,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G662" t="n">
-        <v>4.7421760559082</v>
+        <v>4.74217557907104</v>
       </c>
       <c r="H662" t="n">
         <v>10540</v>
@@ -19712,7 +19712,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G667" t="n">
-        <v>4.82121181488037</v>
+        <v>4.82121133804321</v>
       </c>
       <c r="H667" t="n">
         <v>8350</v>
@@ -19741,7 +19741,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G668" t="n">
-        <v>5.03856134414673</v>
+        <v>5.03856182098389</v>
       </c>
       <c r="H668" t="n">
         <v>8110</v>
@@ -19828,7 +19828,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G671" t="n">
-        <v>5.03856134414673</v>
+        <v>5.03856182098389</v>
       </c>
       <c r="H671" t="n">
         <v>4620</v>
@@ -19915,7 +19915,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G674" t="n">
-        <v>5.03856134414673</v>
+        <v>5.03856182098389</v>
       </c>
       <c r="H674" t="n">
         <v>1320</v>
@@ -19944,7 +19944,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G675" t="n">
-        <v>4.97928428649902</v>
+        <v>4.97928380966187</v>
       </c>
       <c r="H675" t="n">
         <v>177850</v>
@@ -20031,7 +20031,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G678" t="n">
-        <v>4.7421760559082</v>
+        <v>4.74217557907104</v>
       </c>
       <c r="H678" t="n">
         <v>42730</v>
@@ -20060,7 +20060,7 @@
         <v>4.59000015258789</v>
       </c>
       <c r="G679" t="n">
-        <v>4.53470516204834</v>
+        <v>4.53470468521118</v>
       </c>
       <c r="H679" t="n">
         <v>78600</v>
@@ -20176,7 +20176,7 @@
         <v>4.59000015258789</v>
       </c>
       <c r="G683" t="n">
-        <v>4.53470516204834</v>
+        <v>4.53470468521118</v>
       </c>
       <c r="H683" t="n">
         <v>94970</v>
@@ -20205,7 +20205,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G684" t="n">
-        <v>4.52482557296753</v>
+        <v>4.52482509613037</v>
       </c>
       <c r="H684" t="n">
         <v>1210</v>
@@ -20234,7 +20234,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G685" t="n">
-        <v>4.34699440002441</v>
+        <v>4.34699392318726</v>
       </c>
       <c r="H685" t="n">
         <v>19270</v>
@@ -20263,7 +20263,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G686" t="n">
-        <v>4.39639186859131</v>
+        <v>4.39639139175415</v>
       </c>
       <c r="H686" t="n">
         <v>17560</v>
@@ -20292,7 +20292,7 @@
         <v>4.5</v>
       </c>
       <c r="G687" t="n">
-        <v>4.44578981399536</v>
+        <v>4.4457893371582</v>
       </c>
       <c r="H687" t="n">
         <v>5450</v>
@@ -20321,7 +20321,7 @@
         <v>4.5</v>
       </c>
       <c r="G688" t="n">
-        <v>4.44578981399536</v>
+        <v>4.4457893371582</v>
       </c>
       <c r="H688" t="n">
         <v>6510</v>
@@ -20379,7 +20379,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G690" t="n">
-        <v>4.71253681182861</v>
+        <v>4.71253633499146</v>
       </c>
       <c r="H690" t="n">
         <v>19330</v>
@@ -20437,7 +20437,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G692" t="n">
-        <v>5.03856134414673</v>
+        <v>5.03856182098389</v>
       </c>
       <c r="H692" t="n">
         <v>52130</v>
@@ -20495,7 +20495,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G694" t="n">
-        <v>5.03856134414673</v>
+        <v>5.03856182098389</v>
       </c>
       <c r="H694" t="n">
         <v>39050</v>
@@ -20553,7 +20553,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G696" t="n">
-        <v>5.21639251708984</v>
+        <v>5.216392993927</v>
       </c>
       <c r="H696" t="n">
         <v>1320</v>
@@ -20582,7 +20582,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G697" t="n">
-        <v>5.03856134414673</v>
+        <v>5.03856182098389</v>
       </c>
       <c r="H697" t="n">
         <v>10770</v>
@@ -20669,7 +20669,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G700" t="n">
-        <v>5.03856134414673</v>
+        <v>5.03856182098389</v>
       </c>
       <c r="H700" t="n">
         <v>300</v>
@@ -20698,7 +20698,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G701" t="n">
-        <v>5.03856134414673</v>
+        <v>5.03856182098389</v>
       </c>
       <c r="H701" t="n">
         <v>1190</v>
@@ -20727,7 +20727,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G702" t="n">
-        <v>5.03856134414673</v>
+        <v>5.03856182098389</v>
       </c>
       <c r="H702" t="n">
         <v>110</v>
@@ -20785,7 +20785,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G704" t="n">
-        <v>4.7421760559082</v>
+        <v>4.74217557907104</v>
       </c>
       <c r="H704" t="n">
         <v>5760</v>
@@ -20872,7 +20872,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G707" t="n">
-        <v>4.85085010528564</v>
+        <v>4.8508505821228</v>
       </c>
       <c r="H707" t="n">
         <v>250</v>
@@ -20930,7 +20930,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G709" t="n">
-        <v>4.92988681793213</v>
+        <v>4.92988634109497</v>
       </c>
       <c r="H709" t="n">
         <v>2230</v>
@@ -20959,7 +20959,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G710" t="n">
-        <v>4.92988681793213</v>
+        <v>4.92988634109497</v>
       </c>
       <c r="H710" t="n">
         <v>2210</v>
@@ -21017,7 +21017,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G712" t="n">
-        <v>4.72241640090942</v>
+        <v>4.72241592407227</v>
       </c>
       <c r="H712" t="n">
         <v>10280</v>
@@ -21046,7 +21046,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G713" t="n">
-        <v>4.71253681182861</v>
+        <v>4.71253633499146</v>
       </c>
       <c r="H713" t="n">
         <v>4900</v>
@@ -21075,7 +21075,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G714" t="n">
-        <v>4.60386180877686</v>
+        <v>4.6038613319397</v>
       </c>
       <c r="H714" t="n">
         <v>5550</v>
@@ -21104,7 +21104,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G715" t="n">
-        <v>4.71253681182861</v>
+        <v>4.71253633499146</v>
       </c>
       <c r="H715" t="n">
         <v>4150</v>
@@ -21133,7 +21133,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G716" t="n">
-        <v>4.72241640090942</v>
+        <v>4.72241592407227</v>
       </c>
       <c r="H716" t="n">
         <v>10940</v>
@@ -21162,7 +21162,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G717" t="n">
-        <v>4.78169345855713</v>
+        <v>4.78169393539429</v>
       </c>
       <c r="H717" t="n">
         <v>2530</v>
@@ -21191,7 +21191,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G718" t="n">
-        <v>4.82121181488037</v>
+        <v>4.82121133804321</v>
       </c>
       <c r="H718" t="n">
         <v>3100</v>
@@ -21278,7 +21278,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G721" t="n">
-        <v>5.09783840179443</v>
+        <v>5.09783792495728</v>
       </c>
       <c r="H721" t="n">
         <v>3950</v>
@@ -21423,7 +21423,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G726" t="n">
-        <v>5.03856134414673</v>
+        <v>5.03856182098389</v>
       </c>
       <c r="H726" t="n">
         <v>3700</v>
@@ -21452,7 +21452,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G727" t="n">
-        <v>4.97928428649902</v>
+        <v>4.97928380966187</v>
       </c>
       <c r="H727" t="n">
         <v>1500</v>
@@ -21481,7 +21481,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G728" t="n">
-        <v>4.76193475723267</v>
+        <v>4.76193428039551</v>
       </c>
       <c r="H728" t="n">
         <v>8770</v>
@@ -21539,7 +21539,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G730" t="n">
-        <v>4.82121181488037</v>
+        <v>4.82121133804321</v>
       </c>
       <c r="H730" t="n">
         <v>29580</v>
@@ -21568,7 +21568,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G731" t="n">
-        <v>4.7421760559082</v>
+        <v>4.74217557907104</v>
       </c>
       <c r="H731" t="n">
         <v>2850</v>
@@ -21655,7 +21655,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G734" t="n">
-        <v>4.78169345855713</v>
+        <v>4.78169393539429</v>
       </c>
       <c r="H734" t="n">
         <v>2150</v>
@@ -21684,7 +21684,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G735" t="n">
-        <v>4.79157304763794</v>
+        <v>4.79157257080078</v>
       </c>
       <c r="H735" t="n">
         <v>1520</v>
@@ -21771,7 +21771,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G738" t="n">
-        <v>4.82121181488037</v>
+        <v>4.82121133804321</v>
       </c>
       <c r="H738" t="n">
         <v>6100</v>
@@ -21800,7 +21800,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G739" t="n">
-        <v>4.82121181488037</v>
+        <v>4.82121133804321</v>
       </c>
       <c r="H739" t="n">
         <v>8640</v>
@@ -21858,7 +21858,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G741" t="n">
-        <v>4.82121181488037</v>
+        <v>4.82121133804321</v>
       </c>
       <c r="H741" t="n">
         <v>3340</v>
@@ -21916,7 +21916,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G743" t="n">
-        <v>4.85085010528564</v>
+        <v>4.8508505821228</v>
       </c>
       <c r="H743" t="n">
         <v>3070</v>
@@ -22032,7 +22032,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G747" t="n">
-        <v>4.7421760559082</v>
+        <v>4.74217557907104</v>
       </c>
       <c r="H747" t="n">
         <v>63650</v>
@@ -22061,7 +22061,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G748" t="n">
-        <v>4.75205516815186</v>
+        <v>4.7520546913147</v>
       </c>
       <c r="H748" t="n">
         <v>39170</v>
@@ -22090,7 +22090,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G749" t="n">
-        <v>4.78169345855713</v>
+        <v>4.78169393539429</v>
       </c>
       <c r="H749" t="n">
         <v>10810</v>
@@ -22148,7 +22148,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G751" t="n">
-        <v>4.17904233932495</v>
+        <v>4.17904186248779</v>
       </c>
       <c r="H751" t="n">
         <v>518850</v>
@@ -22177,7 +22177,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G752" t="n">
-        <v>4.228440284729</v>
+        <v>4.22843933105469</v>
       </c>
       <c r="H752" t="n">
         <v>104770</v>
@@ -22206,7 +22206,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G753" t="n">
-        <v>4.17904233932495</v>
+        <v>4.17904186248779</v>
       </c>
       <c r="H753" t="n">
         <v>125670</v>
@@ -22235,7 +22235,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G754" t="n">
-        <v>4.17904233932495</v>
+        <v>4.17904186248779</v>
       </c>
       <c r="H754" t="n">
         <v>21070</v>
@@ -22264,7 +22264,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G755" t="n">
-        <v>4.1889214515686</v>
+        <v>4.18892097473145</v>
       </c>
       <c r="H755" t="n">
         <v>62780</v>
@@ -22293,7 +22293,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G756" t="n">
-        <v>4.1889214515686</v>
+        <v>4.18892097473145</v>
       </c>
       <c r="H756" t="n">
         <v>28570</v>
@@ -22322,7 +22322,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G757" t="n">
-        <v>4.17904233932495</v>
+        <v>4.17904186248779</v>
       </c>
       <c r="H757" t="n">
         <v>17930</v>
@@ -22380,7 +22380,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G759" t="n">
-        <v>4.15928316116333</v>
+        <v>4.15928268432617</v>
       </c>
       <c r="H759" t="n">
         <v>8420</v>
@@ -22467,7 +22467,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G762" t="n">
-        <v>4.15928316116333</v>
+        <v>4.15928268432617</v>
       </c>
       <c r="H762" t="n">
         <v>1760</v>
@@ -22496,7 +22496,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G763" t="n">
-        <v>4.05060863494873</v>
+        <v>4.05060815811157</v>
       </c>
       <c r="H763" t="n">
         <v>55200</v>
@@ -22525,7 +22525,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G764" t="n">
-        <v>4.0209698677063</v>
+        <v>4.02096939086914</v>
       </c>
       <c r="H764" t="n">
         <v>16670</v>
@@ -22612,7 +22612,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G767" t="n">
-        <v>3.86289691925049</v>
+        <v>3.86289715766907</v>
       </c>
       <c r="H767" t="n">
         <v>15840</v>
@@ -22670,7 +22670,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G769" t="n">
-        <v>3.83325862884521</v>
+        <v>3.83325839042664</v>
       </c>
       <c r="H769" t="n">
         <v>12950</v>
@@ -22699,7 +22699,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G770" t="n">
-        <v>3.77398109436035</v>
+        <v>3.77398085594177</v>
       </c>
       <c r="H770" t="n">
         <v>16120</v>
@@ -22728,7 +22728,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G771" t="n">
-        <v>3.76410174369812</v>
+        <v>3.76410150527954</v>
       </c>
       <c r="H771" t="n">
         <v>37320</v>
@@ -22757,7 +22757,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G772" t="n">
-        <v>3.76410174369812</v>
+        <v>3.76410150527954</v>
       </c>
       <c r="H772" t="n">
         <v>37840</v>
@@ -22815,7 +22815,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G774" t="n">
-        <v>3.75422215461731</v>
+        <v>3.75422191619873</v>
       </c>
       <c r="H774" t="n">
         <v>58020</v>
@@ -22873,7 +22873,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G776" t="n">
-        <v>3.69494485855103</v>
+        <v>3.6949450969696</v>
       </c>
       <c r="H776" t="n">
         <v>5950</v>
@@ -22902,7 +22902,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G777" t="n">
-        <v>3.75422215461731</v>
+        <v>3.75422191619873</v>
       </c>
       <c r="H777" t="n">
         <v>185950</v>
@@ -22931,7 +22931,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G778" t="n">
-        <v>3.88265609741211</v>
+        <v>3.88265633583069</v>
       </c>
       <c r="H778" t="n">
         <v>6390</v>
@@ -23047,7 +23047,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G782" t="n">
-        <v>4.04072904586792</v>
+        <v>4.04072856903076</v>
       </c>
       <c r="H782" t="n">
         <v>14490</v>
@@ -23192,7 +23192,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G787" t="n">
-        <v>4.03084897994995</v>
+        <v>4.03084850311279</v>
       </c>
       <c r="H787" t="n">
         <v>5350</v>
@@ -23279,7 +23279,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G790" t="n">
-        <v>3.88265609741211</v>
+        <v>3.88265633583069</v>
       </c>
       <c r="H790" t="n">
         <v>7320</v>
@@ -23424,7 +23424,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G795" t="n">
-        <v>3.86289691925049</v>
+        <v>3.86289715766907</v>
       </c>
       <c r="H795" t="n">
         <v>15070</v>
@@ -23511,7 +23511,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G798" t="n">
-        <v>3.83325862884521</v>
+        <v>3.83325839042664</v>
       </c>
       <c r="H798" t="n">
         <v>3250</v>
@@ -23598,7 +23598,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G801" t="n">
-        <v>3.85301756858826</v>
+        <v>3.85301733016968</v>
       </c>
       <c r="H801" t="n">
         <v>47190</v>
@@ -23627,7 +23627,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G802" t="n">
-        <v>3.92235159873962</v>
+        <v>3.9223518371582</v>
       </c>
       <c r="H802" t="n">
         <v>6080</v>
@@ -23656,7 +23656,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G803" t="n">
-        <v>3.92235159873962</v>
+        <v>3.9223518371582</v>
       </c>
       <c r="H803" t="n">
         <v>2580</v>
@@ -23685,7 +23685,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G804" t="n">
-        <v>3.86292243003845</v>
+        <v>3.86292219161987</v>
       </c>
       <c r="H804" t="n">
         <v>1300</v>
@@ -23743,7 +23743,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G806" t="n">
-        <v>3.86292243003845</v>
+        <v>3.86292219161987</v>
       </c>
       <c r="H806" t="n">
         <v>2310</v>
@@ -23772,7 +23772,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G807" t="n">
-        <v>4.01149654388428</v>
+        <v>4.01149606704712</v>
       </c>
       <c r="H807" t="n">
         <v>6240</v>
@@ -23946,7 +23946,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G813" t="n">
-        <v>3.99168682098389</v>
+        <v>3.99168658256531</v>
       </c>
       <c r="H813" t="n">
         <v>8200</v>
@@ -24004,7 +24004,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G815" t="n">
-        <v>3.92235159873962</v>
+        <v>3.9223518371582</v>
       </c>
       <c r="H815" t="n">
         <v>8350</v>
@@ -24178,7 +24178,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G821" t="n">
-        <v>4.14025974273682</v>
+        <v>4.14026021957397</v>
       </c>
       <c r="H821" t="n">
         <v>24790</v>
@@ -24294,7 +24294,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G825" t="n">
-        <v>3.87282705307007</v>
+        <v>3.87282729148865</v>
       </c>
       <c r="H825" t="n">
         <v>85340</v>
@@ -25019,7 +25019,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G850" t="n">
-        <v>4.14025974273682</v>
+        <v>4.14026021957397</v>
       </c>
       <c r="H850" t="n">
         <v>11320</v>
@@ -25048,7 +25048,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G851" t="n">
-        <v>4.16997528076172</v>
+        <v>4.16997480392456</v>
       </c>
       <c r="H851" t="n">
         <v>9220</v>
@@ -25135,7 +25135,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G854" t="n">
-        <v>4.16006994247437</v>
+        <v>4.16007041931152</v>
       </c>
       <c r="H854" t="n">
         <v>31610</v>
@@ -25164,7 +25164,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G855" t="n">
-        <v>4.16006994247437</v>
+        <v>4.16007041931152</v>
       </c>
       <c r="H855" t="n">
         <v>8120</v>
@@ -25570,7 +25570,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G869" t="n">
-        <v>4.01149654388428</v>
+        <v>4.01149606704712</v>
       </c>
       <c r="H869" t="n">
         <v>10970</v>
@@ -25628,7 +25628,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G871" t="n">
-        <v>3.9322566986084</v>
+        <v>3.93225646018982</v>
       </c>
       <c r="H871" t="n">
         <v>7010</v>
@@ -25802,7 +25802,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G877" t="n">
-        <v>4.16997528076172</v>
+        <v>4.16997480392456</v>
       </c>
       <c r="H877" t="n">
         <v>14160</v>
@@ -25889,7 +25889,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G880" t="n">
-        <v>4.30864381790161</v>
+        <v>4.30864429473877</v>
       </c>
       <c r="H880" t="n">
         <v>45530</v>
@@ -26266,7 +26266,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G893" t="n">
-        <v>4.23930978775024</v>
+        <v>4.23930931091309</v>
       </c>
       <c r="H893" t="n">
         <v>42450</v>
@@ -26295,7 +26295,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G894" t="n">
-        <v>4.34826374053955</v>
+        <v>4.34826326370239</v>
       </c>
       <c r="H894" t="n">
         <v>9130</v>
@@ -26353,7 +26353,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G896" t="n">
-        <v>4.21950006484985</v>
+        <v>4.2194995880127</v>
       </c>
       <c r="H896" t="n">
         <v>6250</v>
@@ -26469,7 +26469,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G900" t="n">
-        <v>4.25911951065063</v>
+        <v>4.25911998748779</v>
       </c>
       <c r="H900" t="n">
         <v>2300</v>
@@ -26498,7 +26498,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G901" t="n">
-        <v>4.25911951065063</v>
+        <v>4.25911998748779</v>
       </c>
       <c r="H901" t="n">
         <v>7230</v>
@@ -26672,7 +26672,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G907" t="n">
-        <v>4.17988014221191</v>
+        <v>4.17987966537476</v>
       </c>
       <c r="H907" t="n">
         <v>9490</v>
@@ -27020,7 +27020,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G919" t="n">
-        <v>3.85301756858826</v>
+        <v>3.85301733016968</v>
       </c>
       <c r="H919" t="n">
         <v>5620</v>
@@ -27194,7 +27194,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G925" t="n">
-        <v>3.6450138092041</v>
+        <v>3.64501404762268</v>
       </c>
       <c r="H925" t="n">
         <v>3530</v>
@@ -27339,7 +27339,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G930" t="n">
-        <v>3.66482377052307</v>
+        <v>3.66482353210449</v>
       </c>
       <c r="H930" t="n">
         <v>17040</v>
@@ -27629,7 +27629,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G940" t="n">
-        <v>3.77377796173096</v>
+        <v>3.77377772331238</v>
       </c>
       <c r="H940" t="n">
         <v>14330</v>
@@ -27687,7 +27687,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G942" t="n">
-        <v>3.74406313896179</v>
+        <v>3.74406337738037</v>
       </c>
       <c r="H942" t="n">
         <v>34380</v>
@@ -27890,7 +27890,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G949" t="n">
-        <v>4.17988014221191</v>
+        <v>4.17987966537476</v>
       </c>
       <c r="H949" t="n">
         <v>41290</v>
@@ -27977,7 +27977,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G952" t="n">
-        <v>3.89263701438904</v>
+        <v>3.89263725280762</v>
       </c>
       <c r="H952" t="n">
         <v>18360</v>
@@ -28093,7 +28093,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G956" t="n">
-        <v>3.99168682098389</v>
+        <v>3.99168658256531</v>
       </c>
       <c r="H956" t="n">
         <v>5970</v>
@@ -28267,7 +28267,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G962" t="n">
-        <v>3.86292243003845</v>
+        <v>3.86292219161987</v>
       </c>
       <c r="H962" t="n">
         <v>46304</v>
@@ -28296,7 +28296,7 @@
         <v>3.94400000572205</v>
       </c>
       <c r="G963" t="n">
-        <v>3.90650391578674</v>
+        <v>3.90650415420532</v>
       </c>
       <c r="H963" t="n">
         <v>21357</v>
@@ -28499,7 +28499,7 @@
         <v>3.95050001144409</v>
       </c>
       <c r="G970" t="n">
-        <v>3.9129421710968</v>
+        <v>3.91294193267822</v>
       </c>
       <c r="H970" t="n">
         <v>6820</v>
@@ -28615,7 +28615,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G974" t="n">
-        <v>4.01149654388428</v>
+        <v>4.01149606704712</v>
       </c>
       <c r="H974" t="n">
         <v>41355</v>
@@ -28760,7 +28760,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G979" t="n">
-        <v>3.99168682098389</v>
+        <v>3.99168658256531</v>
       </c>
       <c r="H979" t="n">
         <v>7285</v>
@@ -28847,7 +28847,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G982" t="n">
-        <v>3.9322566986084</v>
+        <v>3.93225646018982</v>
       </c>
       <c r="H982" t="n">
         <v>2119</v>
@@ -28992,7 +28992,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G987" t="n">
-        <v>3.85301756858826</v>
+        <v>3.85301733016968</v>
       </c>
       <c r="H987" t="n">
         <v>3417</v>
@@ -29021,7 +29021,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G988" t="n">
-        <v>3.85301756858826</v>
+        <v>3.85301733016968</v>
       </c>
       <c r="H988" t="n">
         <v>9092</v>
@@ -29166,7 +29166,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G993" t="n">
-        <v>3.86292243003845</v>
+        <v>3.86292219161987</v>
       </c>
       <c r="H993" t="n">
         <v>19637</v>
@@ -29195,7 +29195,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G994" t="n">
-        <v>3.85301756858826</v>
+        <v>3.85301733016968</v>
       </c>
       <c r="H994" t="n">
         <v>2361</v>
@@ -29224,7 +29224,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G995" t="n">
-        <v>3.81339740753174</v>
+        <v>3.81339764595032</v>
       </c>
       <c r="H995" t="n">
         <v>7114</v>
@@ -29398,7 +29398,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1001" t="n">
-        <v>3.86292243003845</v>
+        <v>3.86292219161987</v>
       </c>
       <c r="H1001" t="n">
         <v>9557</v>
@@ -29775,7 +29775,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1014" t="n">
-        <v>3.66482377052307</v>
+        <v>3.66482353210449</v>
       </c>
       <c r="H1014" t="n">
         <v>19950</v>
@@ -29804,7 +29804,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1015" t="n">
-        <v>3.66482377052307</v>
+        <v>3.66482353210449</v>
       </c>
       <c r="H1015" t="n">
         <v>2750</v>
@@ -29833,7 +29833,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G1016" t="n">
-        <v>3.57567930221558</v>
+        <v>3.575679063797</v>
       </c>
       <c r="H1016" t="n">
         <v>16853</v>
@@ -29920,7 +29920,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1019" t="n">
-        <v>3.6450138092041</v>
+        <v>3.64501404762268</v>
       </c>
       <c r="H1019" t="n">
         <v>452</v>
@@ -29978,7 +29978,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1021" t="n">
-        <v>3.6450138092041</v>
+        <v>3.64501404762268</v>
       </c>
       <c r="H1021" t="n">
         <v>19653</v>
@@ -30036,7 +30036,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1023" t="n">
-        <v>3.66482377052307</v>
+        <v>3.66482353210449</v>
       </c>
       <c r="H1023" t="n">
         <v>846</v>
@@ -30065,7 +30065,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1024" t="n">
-        <v>3.61529898643494</v>
+        <v>3.61529922485352</v>
       </c>
       <c r="H1024" t="n">
         <v>8732</v>
@@ -30152,7 +30152,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1027" t="n">
-        <v>3.61529898643494</v>
+        <v>3.61529922485352</v>
       </c>
       <c r="H1027" t="n">
         <v>4783</v>
@@ -30181,7 +30181,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1028" t="n">
-        <v>3.61529898643494</v>
+        <v>3.61529922485352</v>
       </c>
       <c r="H1028" t="n">
         <v>4537</v>
@@ -30210,7 +30210,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1029" t="n">
-        <v>3.61529898643494</v>
+        <v>3.61529922485352</v>
       </c>
       <c r="H1029" t="n">
         <v>2959</v>
@@ -30268,7 +30268,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G1031" t="n">
-        <v>3.65491890907288</v>
+        <v>3.6549186706543</v>
       </c>
       <c r="H1031" t="n">
         <v>22295</v>
@@ -30297,7 +30297,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G1032" t="n">
-        <v>3.65491890907288</v>
+        <v>3.6549186706543</v>
       </c>
       <c r="H1032" t="n">
         <v>32428</v>
@@ -30413,7 +30413,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G1036" t="n">
-        <v>3.55586934089661</v>
+        <v>3.55586957931519</v>
       </c>
       <c r="H1036" t="n">
         <v>10707</v>
@@ -30442,7 +30442,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G1037" t="n">
-        <v>3.52615475654602</v>
+        <v>3.52615451812744</v>
       </c>
       <c r="H1037" t="n">
         <v>5035</v>
@@ -30529,7 +30529,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1040" t="n">
-        <v>3.49643993377686</v>
+        <v>3.49643969535828</v>
       </c>
       <c r="H1040" t="n">
         <v>2950</v>
@@ -30558,7 +30558,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1041" t="n">
-        <v>3.49643993377686</v>
+        <v>3.49643969535828</v>
       </c>
       <c r="H1041" t="n">
         <v>1858</v>
@@ -30703,7 +30703,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G1046" t="n">
-        <v>3.52615475654602</v>
+        <v>3.52615451812744</v>
       </c>
       <c r="H1046" t="n">
         <v>4465</v>
@@ -30761,7 +30761,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1048" t="n">
-        <v>3.41720032691956</v>
+        <v>3.41720056533813</v>
       </c>
       <c r="H1048" t="n">
         <v>10706</v>
@@ -30877,7 +30877,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1052" t="n">
-        <v>3.49643993377686</v>
+        <v>3.49643969535828</v>
       </c>
       <c r="H1052" t="n">
         <v>3617</v>
@@ -30906,7 +30906,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G1053" t="n">
-        <v>3.55586934089661</v>
+        <v>3.55586957931519</v>
       </c>
       <c r="H1053" t="n">
         <v>13118</v>
@@ -31225,7 +31225,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G1064" t="n">
-        <v>3.89263701438904</v>
+        <v>3.89263725280762</v>
       </c>
       <c r="H1064" t="n">
         <v>23123</v>
@@ -31312,7 +31312,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G1067" t="n">
-        <v>4.01149654388428</v>
+        <v>4.01149606704712</v>
       </c>
       <c r="H1067" t="n">
         <v>6753</v>
@@ -31370,7 +31370,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1069" t="n">
-        <v>3.86292243003845</v>
+        <v>3.86292219161987</v>
       </c>
       <c r="H1069" t="n">
         <v>9275</v>
@@ -31602,7 +31602,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G1077" t="n">
-        <v>3.74406313896179</v>
+        <v>3.74406337738037</v>
       </c>
       <c r="H1077" t="n">
         <v>2981</v>
@@ -31805,7 +31805,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1084" t="n">
-        <v>3.6347188949585</v>
+        <v>3.63471913337708</v>
       </c>
       <c r="H1084" t="n">
         <v>5698</v>
@@ -32153,7 +32153,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1096" t="n">
-        <v>3.6347188949585</v>
+        <v>3.63471913337708</v>
       </c>
       <c r="H1096" t="n">
         <v>1083</v>
@@ -32240,7 +32240,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1099" t="n">
-        <v>3.6347188949585</v>
+        <v>3.63471913337708</v>
       </c>
       <c r="H1099" t="n">
         <v>560</v>
@@ -32385,7 +32385,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G1104" t="n">
-        <v>3.55527138710022</v>
+        <v>3.55527114868164</v>
       </c>
       <c r="H1104" t="n">
         <v>4500</v>
@@ -32414,7 +32414,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1105" t="n">
-        <v>3.67444252967834</v>
+        <v>3.67444276809692</v>
       </c>
       <c r="H1105" t="n">
         <v>3701</v>
@@ -32617,7 +32617,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1112" t="n">
-        <v>3.50561690330505</v>
+        <v>3.50561666488647</v>
       </c>
       <c r="H1112" t="n">
         <v>5210</v>
@@ -32646,7 +32646,7 @@
         <v>3.5</v>
       </c>
       <c r="G1113" t="n">
-        <v>3.47582411766052</v>
+        <v>3.47582387924194</v>
       </c>
       <c r="H1113" t="n">
         <v>278</v>
@@ -32675,7 +32675,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1114" t="n">
-        <v>3.43610048294067</v>
+        <v>3.43610024452209</v>
       </c>
       <c r="H1114" t="n">
         <v>2139</v>
@@ -32704,7 +32704,7 @@
         <v>3.5</v>
       </c>
       <c r="G1115" t="n">
-        <v>3.47582411766052</v>
+        <v>3.47582387924194</v>
       </c>
       <c r="H1115" t="n">
         <v>6298</v>
@@ -32733,7 +32733,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1116" t="n">
-        <v>3.43610048294067</v>
+        <v>3.43610024452209</v>
       </c>
       <c r="H1116" t="n">
         <v>5346</v>
@@ -32791,7 +32791,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1118" t="n">
-        <v>3.51554775238037</v>
+        <v>3.51554751396179</v>
       </c>
       <c r="H1118" t="n">
         <v>6544</v>
@@ -32878,7 +32878,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1121" t="n">
-        <v>3.50561690330505</v>
+        <v>3.50561666488647</v>
       </c>
       <c r="H1121" t="n">
         <v>5808</v>
@@ -32907,7 +32907,7 @@
         <v>3.5</v>
       </c>
       <c r="G1122" t="n">
-        <v>3.47582411766052</v>
+        <v>3.47582387924194</v>
       </c>
       <c r="H1122" t="n">
         <v>1849</v>
@@ -32936,7 +32936,7 @@
         <v>3.5</v>
       </c>
       <c r="G1123" t="n">
-        <v>3.47582411766052</v>
+        <v>3.47582387924194</v>
       </c>
       <c r="H1123" t="n">
         <v>0</v>
@@ -32994,7 +32994,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1125" t="n">
-        <v>3.41623854637146</v>
+        <v>3.41623830795288</v>
       </c>
       <c r="H1125" t="n">
         <v>3101</v>
@@ -33023,7 +33023,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1126" t="n">
-        <v>3.41623854637146</v>
+        <v>3.41623830795288</v>
       </c>
       <c r="H1126" t="n">
         <v>4223</v>
@@ -33052,7 +33052,7 @@
         <v>3.5</v>
       </c>
       <c r="G1127" t="n">
-        <v>3.47582411766052</v>
+        <v>3.47582387924194</v>
       </c>
       <c r="H1127" t="n">
         <v>1000</v>
@@ -33081,7 +33081,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1128" t="n">
-        <v>3.51554775238037</v>
+        <v>3.51554751396179</v>
       </c>
       <c r="H1128" t="n">
         <v>14737</v>
@@ -33197,7 +33197,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1132" t="n">
-        <v>3.41623854637146</v>
+        <v>3.41623830795288</v>
       </c>
       <c r="H1132" t="n">
         <v>145</v>
@@ -33342,7 +33342,7 @@
         <v>3.5</v>
       </c>
       <c r="G1137" t="n">
-        <v>3.47582411766052</v>
+        <v>3.47582387924194</v>
       </c>
       <c r="H1137" t="n">
         <v>18829</v>
@@ -33429,7 +33429,7 @@
         <v>3.5</v>
       </c>
       <c r="G1140" t="n">
-        <v>3.47582411766052</v>
+        <v>3.47582387924194</v>
       </c>
       <c r="H1140" t="n">
         <v>14559</v>
@@ -33516,7 +33516,7 @@
         <v>3.5</v>
       </c>
       <c r="G1143" t="n">
-        <v>3.47582411766052</v>
+        <v>3.47582387924194</v>
       </c>
       <c r="H1143" t="n">
         <v>19008</v>
@@ -33574,7 +33574,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G1145" t="n">
-        <v>3.55527138710022</v>
+        <v>3.55527114868164</v>
       </c>
       <c r="H1145" t="n">
         <v>1675</v>
@@ -33603,7 +33603,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1146" t="n">
-        <v>3.67444252967834</v>
+        <v>3.67444276809692</v>
       </c>
       <c r="H1146" t="n">
         <v>42177</v>
@@ -33632,7 +33632,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1147" t="n">
-        <v>3.71416616439819</v>
+        <v>3.71416640281677</v>
       </c>
       <c r="H1147" t="n">
         <v>30404</v>
@@ -33719,7 +33719,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1150" t="n">
-        <v>3.67444252967834</v>
+        <v>3.67444276809692</v>
       </c>
       <c r="H1150" t="n">
         <v>11747</v>
@@ -33777,7 +33777,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1152" t="n">
-        <v>3.67444252967834</v>
+        <v>3.67444276809692</v>
       </c>
       <c r="H1152" t="n">
         <v>6905</v>
@@ -34038,7 +34038,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G1161" t="n">
-        <v>3.55527138710022</v>
+        <v>3.55527114868164</v>
       </c>
       <c r="H1161" t="n">
         <v>3572</v>
@@ -34270,7 +34270,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G1169" t="n">
-        <v>3.55527138710022</v>
+        <v>3.55527114868164</v>
       </c>
       <c r="H1169" t="n">
         <v>5878</v>
@@ -34299,7 +34299,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1170" t="n">
-        <v>3.6347188949585</v>
+        <v>3.63471913337708</v>
       </c>
       <c r="H1170" t="n">
         <v>17287</v>
@@ -34328,7 +34328,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1171" t="n">
-        <v>3.6347188949585</v>
+        <v>3.63471913337708</v>
       </c>
       <c r="H1171" t="n">
         <v>25873</v>
@@ -34589,7 +34589,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G1180" t="n">
-        <v>3.55527138710022</v>
+        <v>3.55527114868164</v>
       </c>
       <c r="H1180" t="n">
         <v>30518</v>
@@ -34647,7 +34647,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1182" t="n">
-        <v>3.50561690330505</v>
+        <v>3.50561666488647</v>
       </c>
       <c r="H1182" t="n">
         <v>20828</v>
@@ -34676,7 +34676,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1183" t="n">
-        <v>3.50561690330505</v>
+        <v>3.50561666488647</v>
       </c>
       <c r="H1183" t="n">
         <v>540</v>
@@ -34734,7 +34734,7 @@
         <v>3.5</v>
       </c>
       <c r="G1185" t="n">
-        <v>3.47582411766052</v>
+        <v>3.47582387924194</v>
       </c>
       <c r="H1185" t="n">
         <v>1141</v>
@@ -34821,7 +34821,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1188" t="n">
-        <v>3.41623854637146</v>
+        <v>3.41623830795288</v>
       </c>
       <c r="H1188" t="n">
         <v>16937</v>
@@ -34995,7 +34995,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G1194" t="n">
-        <v>2.93955421447754</v>
+        <v>2.93955397605896</v>
       </c>
       <c r="H1194" t="n">
         <v>2442</v>
@@ -35372,7 +35372,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G1207" t="n">
-        <v>2.76079750061035</v>
+        <v>2.76079726219177</v>
       </c>
       <c r="H1207" t="n">
         <v>85019</v>
@@ -35401,7 +35401,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G1208" t="n">
-        <v>2.70121192932129</v>
+        <v>2.70121169090271</v>
       </c>
       <c r="H1208" t="n">
         <v>36383</v>
@@ -35923,7 +35923,7 @@
         <v>3</v>
       </c>
       <c r="G1226" t="n">
-        <v>2.97927784919739</v>
+        <v>2.97927761077881</v>
       </c>
       <c r="H1226" t="n">
         <v>103705</v>
@@ -35981,7 +35981,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G1228" t="n">
-        <v>2.93955421447754</v>
+        <v>2.93955397605896</v>
       </c>
       <c r="H1228" t="n">
         <v>12630</v>
@@ -36039,7 +36039,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G1230" t="n">
-        <v>2.93955421447754</v>
+        <v>2.93955397605896</v>
       </c>
       <c r="H1230" t="n">
         <v>12379</v>
@@ -36068,7 +36068,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G1231" t="n">
-        <v>2.93955421447754</v>
+        <v>2.93955397605896</v>
       </c>
       <c r="H1231" t="n">
         <v>21752</v>
@@ -36097,7 +36097,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G1232" t="n">
-        <v>2.93955421447754</v>
+        <v>2.93955397605896</v>
       </c>
       <c r="H1232" t="n">
         <v>51075</v>
@@ -36184,7 +36184,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1235" t="n">
-        <v>2.87996864318848</v>
+        <v>2.8799684047699</v>
       </c>
       <c r="H1235" t="n">
         <v>33074</v>
@@ -36503,7 +36503,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G1246" t="n">
-        <v>2.58204078674316</v>
+        <v>2.58204054832458</v>
       </c>
       <c r="H1246" t="n">
         <v>34890</v>
@@ -36764,7 +36764,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G1255" t="n">
-        <v>2.66148829460144</v>
+        <v>2.66148805618286</v>
       </c>
       <c r="H1255" t="n">
         <v>14426</v>
@@ -36938,7 +36938,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1261" t="n">
-        <v>2.87996864318848</v>
+        <v>2.8799684047699</v>
       </c>
       <c r="H1261" t="n">
         <v>23099</v>
@@ -36996,7 +36996,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G1263" t="n">
-        <v>2.84024477005005</v>
+        <v>2.84024453163147</v>
       </c>
       <c r="H1263" t="n">
         <v>24196</v>
@@ -37025,7 +37025,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1264" t="n">
-        <v>2.87996864318848</v>
+        <v>2.8799684047699</v>
       </c>
       <c r="H1264" t="n">
         <v>44232</v>
@@ -37199,7 +37199,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G1270" t="n">
-        <v>2.76079750061035</v>
+        <v>2.76079726219177</v>
       </c>
       <c r="H1270" t="n">
         <v>16790</v>
@@ -37257,7 +37257,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G1272" t="n">
-        <v>2.76079750061035</v>
+        <v>2.76079726219177</v>
       </c>
       <c r="H1272" t="n">
         <v>7158</v>
@@ -37315,7 +37315,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G1274" t="n">
-        <v>2.84024477005005</v>
+        <v>2.84024453163147</v>
       </c>
       <c r="H1274" t="n">
         <v>4036</v>
@@ -37518,7 +37518,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G1281" t="n">
-        <v>2.84024477005005</v>
+        <v>2.84024453163147</v>
       </c>
       <c r="H1281" t="n">
         <v>4934</v>
@@ -37692,7 +37692,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G1287" t="n">
-        <v>2.66148829460144</v>
+        <v>2.66148805618286</v>
       </c>
       <c r="H1287" t="n">
         <v>11470</v>
@@ -37721,7 +37721,7 @@
         <v>2.5</v>
       </c>
       <c r="G1288" t="n">
-        <v>2.48273158073425</v>
+        <v>2.48273134231567</v>
       </c>
       <c r="H1288" t="n">
         <v>44014</v>
@@ -37895,7 +37895,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G1294" t="n">
-        <v>2.62176465988159</v>
+        <v>2.62176442146301</v>
       </c>
       <c r="H1294" t="n">
         <v>12855</v>
@@ -38156,7 +38156,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1303" t="n">
-        <v>2.87996864318848</v>
+        <v>2.8799684047699</v>
       </c>
       <c r="H1303" t="n">
         <v>10021</v>
@@ -38301,7 +38301,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G1308" t="n">
-        <v>2.84024477005005</v>
+        <v>2.84024453163147</v>
       </c>
       <c r="H1308" t="n">
         <v>4956</v>
@@ -38359,7 +38359,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G1310" t="n">
-        <v>2.8005211353302</v>
+        <v>2.80052089691162</v>
       </c>
       <c r="H1310" t="n">
         <v>28928</v>
@@ -38475,7 +38475,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G1314" t="n">
-        <v>2.93955421447754</v>
+        <v>2.93955397605896</v>
       </c>
       <c r="H1314" t="n">
         <v>43179</v>
@@ -49037,6 +49037,35 @@
         <v>40723</v>
       </c>
       <c r="I1678" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1679">
+      <c r="A1679" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1679" s="1" t="n">
+        <v>46316.2916666667</v>
+      </c>
+      <c r="C1679" t="n">
+        <v>3.15499997138977</v>
+      </c>
+      <c r="D1679" t="n">
+        <v>3.20499992370605</v>
+      </c>
+      <c r="E1679" t="n">
+        <v>3.15000009536743</v>
+      </c>
+      <c r="F1679" t="n">
+        <v>3.15000009536743</v>
+      </c>
+      <c r="G1679" t="n">
+        <v>3.15000009536743</v>
+      </c>
+      <c r="H1679" t="n">
+        <v>5756</v>
+      </c>
+      <c r="I1679" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/UD.MI.xlsx
+++ b/data/UD.MI.xlsx
@@ -427,7 +427,7 @@
         <v>1.5</v>
       </c>
       <c r="G2" t="n">
-        <v>1.47885525226593</v>
+        <v>1.47885513305664</v>
       </c>
       <c r="H2" t="n">
         <v>159000</v>
@@ -485,7 +485,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G4" t="n">
-        <v>1.4591372013092</v>
+        <v>1.45913708209991</v>
       </c>
       <c r="H4" t="n">
         <v>240000</v>
@@ -514,7 +514,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G5" t="n">
-        <v>1.50843226909637</v>
+        <v>1.50843214988708</v>
       </c>
       <c r="H5" t="n">
         <v>88000</v>
@@ -572,7 +572,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G7" t="n">
-        <v>1.51829123497009</v>
+        <v>1.51829135417938</v>
       </c>
       <c r="H7" t="n">
         <v>61000</v>
@@ -601,7 +601,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G8" t="n">
-        <v>1.53800928592682</v>
+        <v>1.53800940513611</v>
       </c>
       <c r="H8" t="n">
         <v>19000</v>
@@ -630,7 +630,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G9" t="n">
-        <v>1.55772757530212</v>
+        <v>1.55772745609283</v>
       </c>
       <c r="H9" t="n">
         <v>13000</v>
@@ -659,7 +659,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G10" t="n">
-        <v>1.53800928592682</v>
+        <v>1.53800940513611</v>
       </c>
       <c r="H10" t="n">
         <v>17000</v>
@@ -688,7 +688,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G11" t="n">
-        <v>1.56265699863434</v>
+        <v>1.56265711784363</v>
       </c>
       <c r="H11" t="n">
         <v>16000</v>
@@ -717,7 +717,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G12" t="n">
-        <v>1.56758654117584</v>
+        <v>1.56758666038513</v>
       </c>
       <c r="H12" t="n">
         <v>3000</v>
@@ -746,7 +746,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G13" t="n">
-        <v>1.55772757530212</v>
+        <v>1.55772745609283</v>
       </c>
       <c r="H13" t="n">
         <v>2000</v>
@@ -775,7 +775,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G14" t="n">
-        <v>1.56758654117584</v>
+        <v>1.56758666038513</v>
       </c>
       <c r="H14" t="n">
         <v>1000</v>
@@ -804,7 +804,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G15" t="n">
-        <v>1.64645874500275</v>
+        <v>1.64645862579346</v>
       </c>
       <c r="H15" t="n">
         <v>31000</v>
@@ -949,7 +949,7 @@
         <v>1.67499995231628</v>
       </c>
       <c r="G20" t="n">
-        <v>1.65138828754425</v>
+        <v>1.65138816833496</v>
       </c>
       <c r="H20" t="n">
         <v>17000</v>
@@ -1094,7 +1094,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G25" t="n">
-        <v>1.58730447292328</v>
+        <v>1.58730459213257</v>
       </c>
       <c r="H25" t="n">
         <v>22000</v>
@@ -1181,7 +1181,7 @@
         <v>1.59500002861023</v>
       </c>
       <c r="G28" t="n">
-        <v>1.57251620292664</v>
+        <v>1.57251608371735</v>
       </c>
       <c r="H28" t="n">
         <v>22000</v>
@@ -1500,7 +1500,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G39" t="n">
-        <v>1.67110657691956</v>
+        <v>1.67110645771027</v>
       </c>
       <c r="H39" t="n">
         <v>3000</v>
@@ -1529,7 +1529,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G40" t="n">
-        <v>1.6957540512085</v>
+        <v>1.69575381278992</v>
       </c>
       <c r="H40" t="n">
         <v>7000</v>
@@ -1558,7 +1558,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G41" t="n">
-        <v>1.6858948469162</v>
+        <v>1.68589496612549</v>
       </c>
       <c r="H41" t="n">
         <v>14000</v>
@@ -1587,7 +1587,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G42" t="n">
-        <v>1.74504911899567</v>
+        <v>1.74504899978638</v>
       </c>
       <c r="H42" t="n">
         <v>49000</v>
@@ -1616,7 +1616,7 @@
         <v>1.72500002384186</v>
       </c>
       <c r="G43" t="n">
-        <v>1.70068359375</v>
+        <v>1.70068347454071</v>
       </c>
       <c r="H43" t="n">
         <v>21000</v>
@@ -1790,7 +1790,7 @@
         <v>1.72500002384186</v>
       </c>
       <c r="G49" t="n">
-        <v>1.70068359375</v>
+        <v>1.70068347454071</v>
       </c>
       <c r="H49" t="n">
         <v>18000</v>
@@ -1877,7 +1877,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G52" t="n">
-        <v>1.74011969566345</v>
+        <v>1.74011957645416</v>
       </c>
       <c r="H52" t="n">
         <v>6000</v>
@@ -1935,7 +1935,7 @@
         <v>1.72500002384186</v>
       </c>
       <c r="G54" t="n">
-        <v>1.70068359375</v>
+        <v>1.70068347454071</v>
       </c>
       <c r="H54" t="n">
         <v>10000</v>
@@ -1964,7 +1964,7 @@
         <v>1.72500002384186</v>
       </c>
       <c r="G55" t="n">
-        <v>1.70068359375</v>
+        <v>1.70068347454071</v>
       </c>
       <c r="H55" t="n">
         <v>15000</v>
@@ -1993,7 +1993,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G56" t="n">
-        <v>1.6957540512085</v>
+        <v>1.69575381278992</v>
       </c>
       <c r="H56" t="n">
         <v>8000</v>
@@ -2051,7 +2051,7 @@
         <v>1.7150000333786</v>
       </c>
       <c r="G58" t="n">
-        <v>1.69082450866699</v>
+        <v>1.6908243894577</v>
       </c>
       <c r="H58" t="n">
         <v>7000</v>
@@ -2080,7 +2080,7 @@
         <v>1.7150000333786</v>
       </c>
       <c r="G59" t="n">
-        <v>1.69082450866699</v>
+        <v>1.6908243894577</v>
       </c>
       <c r="H59" t="n">
         <v>0</v>
@@ -2109,7 +2109,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G60" t="n">
-        <v>1.71547198295593</v>
+        <v>1.71547210216522</v>
       </c>
       <c r="H60" t="n">
         <v>17000</v>
@@ -2138,7 +2138,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G61" t="n">
-        <v>1.71547198295593</v>
+        <v>1.71547210216522</v>
       </c>
       <c r="H61" t="n">
         <v>4000</v>
@@ -2167,7 +2167,7 @@
         <v>1.67499995231628</v>
       </c>
       <c r="G62" t="n">
-        <v>1.65138828754425</v>
+        <v>1.65138816833496</v>
       </c>
       <c r="H62" t="n">
         <v>8000</v>
@@ -2225,7 +2225,7 @@
         <v>1.67499995231628</v>
       </c>
       <c r="G64" t="n">
-        <v>1.65138828754425</v>
+        <v>1.65138816833496</v>
       </c>
       <c r="H64" t="n">
         <v>9000</v>
@@ -2254,7 +2254,7 @@
         <v>1.67499995231628</v>
       </c>
       <c r="G65" t="n">
-        <v>1.65138828754425</v>
+        <v>1.65138816833496</v>
       </c>
       <c r="H65" t="n">
         <v>0</v>
@@ -2341,7 +2341,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G68" t="n">
-        <v>1.6858948469162</v>
+        <v>1.68589496612549</v>
       </c>
       <c r="H68" t="n">
         <v>7000</v>
@@ -2457,7 +2457,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G72" t="n">
-        <v>1.64645874500275</v>
+        <v>1.64645862579346</v>
       </c>
       <c r="H72" t="n">
         <v>1000</v>
@@ -2515,7 +2515,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G74" t="n">
-        <v>1.64645874500275</v>
+        <v>1.64645862579346</v>
       </c>
       <c r="H74" t="n">
         <v>1000</v>
@@ -2544,7 +2544,7 @@
         <v>1.67499995231628</v>
       </c>
       <c r="G75" t="n">
-        <v>1.65138828754425</v>
+        <v>1.65138816833496</v>
       </c>
       <c r="H75" t="n">
         <v>4000</v>
@@ -2573,7 +2573,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G76" t="n">
-        <v>1.67110657691956</v>
+        <v>1.67110645771027</v>
       </c>
       <c r="H76" t="n">
         <v>2000</v>
@@ -2602,7 +2602,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G77" t="n">
-        <v>1.6858948469162</v>
+        <v>1.68589496612549</v>
       </c>
       <c r="H77" t="n">
         <v>3000</v>
@@ -2631,7 +2631,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G78" t="n">
-        <v>1.64645874500275</v>
+        <v>1.64645862579346</v>
       </c>
       <c r="H78" t="n">
         <v>4000</v>
@@ -2892,7 +2892,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G87" t="n">
-        <v>1.56758654117584</v>
+        <v>1.56758666038513</v>
       </c>
       <c r="H87" t="n">
         <v>26000</v>
@@ -2979,7 +2979,7 @@
         <v>1.59500002861023</v>
       </c>
       <c r="G90" t="n">
-        <v>1.57251620292664</v>
+        <v>1.57251608371735</v>
       </c>
       <c r="H90" t="n">
         <v>4000</v>
@@ -3008,7 +3008,7 @@
         <v>1.59500002861023</v>
       </c>
       <c r="G91" t="n">
-        <v>1.57251620292664</v>
+        <v>1.57251608371735</v>
       </c>
       <c r="H91" t="n">
         <v>2000</v>
@@ -3037,7 +3037,7 @@
         <v>1.62999999523163</v>
       </c>
       <c r="G92" t="n">
-        <v>1.60702264308929</v>
+        <v>1.60702252388</v>
       </c>
       <c r="H92" t="n">
         <v>32000</v>
@@ -3066,7 +3066,7 @@
         <v>1.59500002861023</v>
       </c>
       <c r="G93" t="n">
-        <v>1.57251620292664</v>
+        <v>1.57251608371735</v>
       </c>
       <c r="H93" t="n">
         <v>9000</v>
@@ -3095,7 +3095,7 @@
         <v>1.59500002861023</v>
       </c>
       <c r="G94" t="n">
-        <v>1.57251620292664</v>
+        <v>1.57251608371735</v>
       </c>
       <c r="H94" t="n">
         <v>11000</v>
@@ -3124,7 +3124,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G95" t="n">
-        <v>1.58730447292328</v>
+        <v>1.58730459213257</v>
       </c>
       <c r="H95" t="n">
         <v>11000</v>
@@ -3182,7 +3182,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G97" t="n">
-        <v>1.58730447292328</v>
+        <v>1.58730459213257</v>
       </c>
       <c r="H97" t="n">
         <v>31000</v>
@@ -3211,7 +3211,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G98" t="n">
-        <v>1.58730447292328</v>
+        <v>1.58730459213257</v>
       </c>
       <c r="H98" t="n">
         <v>11000</v>
@@ -3443,7 +3443,7 @@
         <v>1.66499996185303</v>
       </c>
       <c r="G106" t="n">
-        <v>1.64152932167053</v>
+        <v>1.64152920246124</v>
       </c>
       <c r="H106" t="n">
         <v>2000</v>
@@ -3733,7 +3733,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G116" t="n">
-        <v>1.71547198295593</v>
+        <v>1.71547210216522</v>
       </c>
       <c r="H116" t="n">
         <v>23000</v>
@@ -3762,7 +3762,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G117" t="n">
-        <v>1.6858948469162</v>
+        <v>1.68589496612549</v>
       </c>
       <c r="H117" t="n">
         <v>22000</v>
@@ -3791,7 +3791,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G118" t="n">
-        <v>1.6858948469162</v>
+        <v>1.68589496612549</v>
       </c>
       <c r="H118" t="n">
         <v>0</v>
@@ -3849,7 +3849,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G120" t="n">
-        <v>1.89786422252655</v>
+        <v>1.89786410331726</v>
       </c>
       <c r="H120" t="n">
         <v>60000</v>
@@ -3965,7 +3965,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G124" t="n">
-        <v>1.8534984588623</v>
+        <v>1.85349833965302</v>
       </c>
       <c r="H124" t="n">
         <v>32000</v>
@@ -4023,7 +4023,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G126" t="n">
-        <v>1.83378040790558</v>
+        <v>1.83378052711487</v>
       </c>
       <c r="H126" t="n">
         <v>15000</v>
@@ -4052,7 +4052,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G127" t="n">
-        <v>1.82392132282257</v>
+        <v>1.82392144203186</v>
       </c>
       <c r="H127" t="n">
         <v>7000</v>
@@ -4081,7 +4081,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G128" t="n">
-        <v>1.82392132282257</v>
+        <v>1.82392144203186</v>
       </c>
       <c r="H128" t="n">
         <v>0</v>
@@ -4110,7 +4110,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G129" t="n">
-        <v>1.82392132282257</v>
+        <v>1.82392144203186</v>
       </c>
       <c r="H129" t="n">
         <v>0</v>
@@ -4139,7 +4139,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G130" t="n">
-        <v>1.83871018886566</v>
+        <v>1.83870995044708</v>
       </c>
       <c r="H130" t="n">
         <v>8000</v>
@@ -4168,7 +4168,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G131" t="n">
-        <v>1.83378040790558</v>
+        <v>1.83378052711487</v>
       </c>
       <c r="H131" t="n">
         <v>1000</v>
@@ -4197,7 +4197,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G132" t="n">
-        <v>1.78448510169983</v>
+        <v>1.78448522090912</v>
       </c>
       <c r="H132" t="n">
         <v>9000</v>
@@ -4226,7 +4226,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G133" t="n">
-        <v>1.8534984588623</v>
+        <v>1.85349833965302</v>
       </c>
       <c r="H133" t="n">
         <v>6000</v>
@@ -4255,7 +4255,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G134" t="n">
-        <v>1.8534984588623</v>
+        <v>1.85349833965302</v>
       </c>
       <c r="H134" t="n">
         <v>0</v>
@@ -4284,7 +4284,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G135" t="n">
-        <v>1.8534984588623</v>
+        <v>1.85349833965302</v>
       </c>
       <c r="H135" t="n">
         <v>3000</v>
@@ -4342,7 +4342,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G137" t="n">
-        <v>1.88307547569275</v>
+        <v>1.88307559490204</v>
       </c>
       <c r="H137" t="n">
         <v>1000</v>
@@ -4371,7 +4371,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G138" t="n">
-        <v>1.88307547569275</v>
+        <v>1.88307559490204</v>
       </c>
       <c r="H138" t="n">
         <v>0</v>
@@ -4458,7 +4458,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G141" t="n">
-        <v>1.82392132282257</v>
+        <v>1.82392144203186</v>
       </c>
       <c r="H141" t="n">
         <v>12000</v>
@@ -4487,7 +4487,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G142" t="n">
-        <v>1.82392132282257</v>
+        <v>1.82392144203186</v>
       </c>
       <c r="H142" t="n">
         <v>13000</v>
@@ -4574,7 +4574,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G145" t="n">
-        <v>1.79434442520142</v>
+        <v>1.79434430599213</v>
       </c>
       <c r="H145" t="n">
         <v>23000</v>
@@ -4603,7 +4603,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G146" t="n">
-        <v>1.79434442520142</v>
+        <v>1.79434430599213</v>
       </c>
       <c r="H146" t="n">
         <v>0</v>
@@ -4632,7 +4632,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G147" t="n">
-        <v>1.79434442520142</v>
+        <v>1.79434430599213</v>
       </c>
       <c r="H147" t="n">
         <v>29000</v>
@@ -4690,7 +4690,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G149" t="n">
-        <v>1.79434442520142</v>
+        <v>1.79434430599213</v>
       </c>
       <c r="H149" t="n">
         <v>10000</v>
@@ -4719,7 +4719,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G150" t="n">
-        <v>1.79434442520142</v>
+        <v>1.79434430599213</v>
       </c>
       <c r="H150" t="n">
         <v>0</v>
@@ -4748,7 +4748,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G151" t="n">
-        <v>1.74011969566345</v>
+        <v>1.74011957645416</v>
       </c>
       <c r="H151" t="n">
         <v>30000</v>
@@ -4777,7 +4777,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G152" t="n">
-        <v>1.76969683170319</v>
+        <v>1.7696967124939</v>
       </c>
       <c r="H152" t="n">
         <v>4000</v>
@@ -4806,7 +4806,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G153" t="n">
-        <v>1.74504911899567</v>
+        <v>1.74504899978638</v>
       </c>
       <c r="H153" t="n">
         <v>90000</v>
@@ -4835,7 +4835,7 @@
         <v>1.81500005722046</v>
       </c>
       <c r="G154" t="n">
-        <v>1.7894150018692</v>
+        <v>1.78941488265991</v>
       </c>
       <c r="H154" t="n">
         <v>10000</v>
@@ -4864,7 +4864,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G155" t="n">
-        <v>1.82392132282257</v>
+        <v>1.82392144203186</v>
       </c>
       <c r="H155" t="n">
         <v>13000</v>
@@ -4893,7 +4893,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G156" t="n">
-        <v>1.82392132282257</v>
+        <v>1.82392144203186</v>
       </c>
       <c r="H156" t="n">
         <v>0</v>
@@ -4922,7 +4922,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G157" t="n">
-        <v>1.83871018886566</v>
+        <v>1.83870995044708</v>
       </c>
       <c r="H157" t="n">
         <v>2000</v>
@@ -4951,7 +4951,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G158" t="n">
-        <v>1.83378040790558</v>
+        <v>1.83378052711487</v>
       </c>
       <c r="H158" t="n">
         <v>7000</v>
@@ -4980,7 +4980,7 @@
         <v>1.81500005722046</v>
       </c>
       <c r="G159" t="n">
-        <v>1.7894150018692</v>
+        <v>1.78941488265991</v>
       </c>
       <c r="H159" t="n">
         <v>5000</v>
@@ -5067,7 +5067,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G162" t="n">
-        <v>1.74504911899567</v>
+        <v>1.74504899978638</v>
       </c>
       <c r="H162" t="n">
         <v>2000</v>
@@ -5096,7 +5096,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G163" t="n">
-        <v>1.74504911899567</v>
+        <v>1.74504899978638</v>
       </c>
       <c r="H163" t="n">
         <v>0</v>
@@ -5125,7 +5125,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G164" t="n">
-        <v>1.71547198295593</v>
+        <v>1.71547210216522</v>
       </c>
       <c r="H164" t="n">
         <v>6000</v>
@@ -5212,7 +5212,7 @@
         <v>1.81500005722046</v>
       </c>
       <c r="G167" t="n">
-        <v>1.7894150018692</v>
+        <v>1.78941488265991</v>
       </c>
       <c r="H167" t="n">
         <v>3000</v>
@@ -5299,7 +5299,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G170" t="n">
-        <v>1.83871018886566</v>
+        <v>1.83870995044708</v>
       </c>
       <c r="H170" t="n">
         <v>39000</v>
@@ -5328,7 +5328,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G171" t="n">
-        <v>1.83871018886566</v>
+        <v>1.83870995044708</v>
       </c>
       <c r="H171" t="n">
         <v>0</v>
@@ -5357,7 +5357,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G172" t="n">
-        <v>1.81406247615814</v>
+        <v>1.81406259536743</v>
       </c>
       <c r="H172" t="n">
         <v>3000</v>
@@ -5386,7 +5386,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G173" t="n">
-        <v>1.82885098457336</v>
+        <v>1.82885110378265</v>
       </c>
       <c r="H173" t="n">
         <v>18000</v>
@@ -5415,7 +5415,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G174" t="n">
-        <v>1.82885098457336</v>
+        <v>1.82885110378265</v>
       </c>
       <c r="H174" t="n">
         <v>28000</v>
@@ -5444,7 +5444,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G175" t="n">
-        <v>1.86828720569611</v>
+        <v>1.86828708648682</v>
       </c>
       <c r="H175" t="n">
         <v>17000</v>
@@ -5473,7 +5473,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G176" t="n">
-        <v>1.83871018886566</v>
+        <v>1.83870995044708</v>
       </c>
       <c r="H176" t="n">
         <v>47000</v>
@@ -5560,7 +5560,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G179" t="n">
-        <v>1.88307547569275</v>
+        <v>1.88307559490204</v>
       </c>
       <c r="H179" t="n">
         <v>30000</v>
@@ -5589,7 +5589,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G180" t="n">
-        <v>1.88800525665283</v>
+        <v>1.88800501823425</v>
       </c>
       <c r="H180" t="n">
         <v>73000</v>
@@ -5618,7 +5618,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G181" t="n">
-        <v>1.90279364585876</v>
+        <v>1.90279352664948</v>
       </c>
       <c r="H181" t="n">
         <v>23000</v>
@@ -5676,7 +5676,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G183" t="n">
-        <v>2.03096103668213</v>
+        <v>2.03096079826355</v>
       </c>
       <c r="H183" t="n">
         <v>24000</v>
@@ -5705,7 +5705,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G184" t="n">
-        <v>2.01124286651611</v>
+        <v>2.01124310493469</v>
       </c>
       <c r="H184" t="n">
         <v>3000</v>
@@ -5734,7 +5734,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G185" t="n">
-        <v>2.03096103668213</v>
+        <v>2.03096079826355</v>
       </c>
       <c r="H185" t="n">
         <v>54000</v>
@@ -5763,7 +5763,7 @@
         <v>1.99500000476837</v>
       </c>
       <c r="G186" t="n">
-        <v>1.96687757968903</v>
+        <v>1.96687746047974</v>
       </c>
       <c r="H186" t="n">
         <v>28000</v>
@@ -5821,7 +5821,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G188" t="n">
-        <v>2.01124286651611</v>
+        <v>2.01124310493469</v>
       </c>
       <c r="H188" t="n">
         <v>4000</v>
@@ -5850,7 +5850,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G189" t="n">
-        <v>2.01124286651611</v>
+        <v>2.01124310493469</v>
       </c>
       <c r="H189" t="n">
         <v>0</v>
@@ -5879,7 +5879,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G190" t="n">
-        <v>1.91758239269257</v>
+        <v>1.91758227348328</v>
       </c>
       <c r="H190" t="n">
         <v>76000</v>
@@ -5995,7 +5995,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G194" t="n">
-        <v>1.92251169681549</v>
+        <v>1.92251181602478</v>
       </c>
       <c r="H194" t="n">
         <v>6000</v>
@@ -6024,7 +6024,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G195" t="n">
-        <v>1.8633576631546</v>
+        <v>1.86335754394531</v>
       </c>
       <c r="H195" t="n">
         <v>42000</v>
@@ -6053,7 +6053,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G196" t="n">
-        <v>1.89293467998505</v>
+        <v>1.89293456077576</v>
       </c>
       <c r="H196" t="n">
         <v>23000</v>
@@ -6140,7 +6140,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G199" t="n">
-        <v>1.91758239269257</v>
+        <v>1.91758227348328</v>
       </c>
       <c r="H199" t="n">
         <v>3000</v>
@@ -6169,7 +6169,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G200" t="n">
-        <v>1.92251169681549</v>
+        <v>1.92251181602478</v>
       </c>
       <c r="H200" t="n">
         <v>18000</v>
@@ -6198,7 +6198,7 @@
         <v>1.95500004291534</v>
       </c>
       <c r="G201" t="n">
-        <v>1.92744135856628</v>
+        <v>1.92744123935699</v>
       </c>
       <c r="H201" t="n">
         <v>9000</v>
@@ -6285,7 +6285,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G204" t="n">
-        <v>1.92251169681549</v>
+        <v>1.92251181602478</v>
       </c>
       <c r="H204" t="n">
         <v>8000</v>
@@ -6343,7 +6343,7 @@
         <v>1.95500004291534</v>
       </c>
       <c r="G206" t="n">
-        <v>1.92744135856628</v>
+        <v>1.92744123935699</v>
       </c>
       <c r="H206" t="n">
         <v>7000</v>
@@ -6372,7 +6372,7 @@
         <v>1.95500004291534</v>
       </c>
       <c r="G207" t="n">
-        <v>1.92744135856628</v>
+        <v>1.92744123935699</v>
       </c>
       <c r="H207" t="n">
         <v>0</v>
@@ -6430,7 +6430,7 @@
         <v>1.9650000333786</v>
       </c>
       <c r="G209" t="n">
-        <v>1.93730044364929</v>
+        <v>1.93730020523071</v>
       </c>
       <c r="H209" t="n">
         <v>11000</v>
@@ -6459,7 +6459,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G210" t="n">
-        <v>1.95701825618744</v>
+        <v>1.95701837539673</v>
       </c>
       <c r="H210" t="n">
         <v>16000</v>
@@ -6488,7 +6488,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G211" t="n">
-        <v>1.94715940952301</v>
+        <v>1.94715929031372</v>
       </c>
       <c r="H211" t="n">
         <v>7000</v>
@@ -6517,7 +6517,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G212" t="n">
-        <v>1.94222986698151</v>
+        <v>1.94222974777222</v>
       </c>
       <c r="H212" t="n">
         <v>31000</v>
@@ -6546,7 +6546,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G213" t="n">
-        <v>1.92251169681549</v>
+        <v>1.92251181602478</v>
       </c>
       <c r="H213" t="n">
         <v>20000</v>
@@ -6575,7 +6575,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G214" t="n">
-        <v>1.92251169681549</v>
+        <v>1.92251181602478</v>
       </c>
       <c r="H214" t="n">
         <v>1000</v>
@@ -6604,7 +6604,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G215" t="n">
-        <v>1.95701825618744</v>
+        <v>1.95701837539673</v>
       </c>
       <c r="H215" t="n">
         <v>1000</v>
@@ -6662,7 +6662,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G217" t="n">
-        <v>1.89786422252655</v>
+        <v>1.89786410331726</v>
       </c>
       <c r="H217" t="n">
         <v>3000</v>
@@ -6691,7 +6691,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G218" t="n">
-        <v>1.89293467998505</v>
+        <v>1.89293456077576</v>
       </c>
       <c r="H218" t="n">
         <v>8000</v>
@@ -6720,7 +6720,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G219" t="n">
-        <v>1.89293467998505</v>
+        <v>1.89293456077576</v>
       </c>
       <c r="H219" t="n">
         <v>1000</v>
@@ -6749,7 +6749,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G220" t="n">
-        <v>1.89786422252655</v>
+        <v>1.89786410331726</v>
       </c>
       <c r="H220" t="n">
         <v>3000</v>
@@ -6778,7 +6778,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G221" t="n">
-        <v>1.92251169681549</v>
+        <v>1.92251181602478</v>
       </c>
       <c r="H221" t="n">
         <v>2000</v>
@@ -6807,7 +6807,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G222" t="n">
-        <v>1.92251169681549</v>
+        <v>1.92251181602478</v>
       </c>
       <c r="H222" t="n">
         <v>0</v>
@@ -6836,7 +6836,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G223" t="n">
-        <v>1.92251169681549</v>
+        <v>1.92251181602478</v>
       </c>
       <c r="H223" t="n">
         <v>0</v>
@@ -6865,7 +6865,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G224" t="n">
-        <v>1.92251169681549</v>
+        <v>1.92251181602478</v>
       </c>
       <c r="H224" t="n">
         <v>3000</v>
@@ -6894,7 +6894,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G225" t="n">
-        <v>1.94222986698151</v>
+        <v>1.94222974777222</v>
       </c>
       <c r="H225" t="n">
         <v>5000</v>
@@ -6923,7 +6923,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G226" t="n">
-        <v>1.99152505397797</v>
+        <v>1.99152493476868</v>
       </c>
       <c r="H226" t="n">
         <v>9000</v>
@@ -6981,7 +6981,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G228" t="n">
-        <v>2.00138425827026</v>
+        <v>2.00138378143311</v>
       </c>
       <c r="H228" t="n">
         <v>18000</v>
@@ -7010,7 +7010,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G229" t="n">
-        <v>2.08025622367859</v>
+        <v>2.08025646209717</v>
       </c>
       <c r="H229" t="n">
         <v>20000</v>
@@ -7039,7 +7039,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G230" t="n">
-        <v>2.0211021900177</v>
+        <v>2.02110195159912</v>
       </c>
       <c r="H230" t="n">
         <v>46000</v>
@@ -7068,7 +7068,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G231" t="n">
-        <v>2.22814178466797</v>
+        <v>2.22814130783081</v>
       </c>
       <c r="H231" t="n">
         <v>86000</v>
@@ -7126,7 +7126,7 @@
         <v>2.25</v>
       </c>
       <c r="G233" t="n">
-        <v>2.21828293800354</v>
+        <v>2.21828246116638</v>
       </c>
       <c r="H233" t="n">
         <v>47000</v>
@@ -7155,7 +7155,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G234" t="n">
-        <v>2.16898775100708</v>
+        <v>2.16898798942566</v>
       </c>
       <c r="H234" t="n">
         <v>85000</v>
@@ -7184,7 +7184,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G235" t="n">
-        <v>2.14926958084106</v>
+        <v>2.14926981925964</v>
       </c>
       <c r="H235" t="n">
         <v>11000</v>
@@ -7213,7 +7213,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G236" t="n">
-        <v>2.1985650062561</v>
+        <v>2.19856452941895</v>
       </c>
       <c r="H236" t="n">
         <v>9000</v>
@@ -7300,7 +7300,7 @@
         <v>2.25</v>
       </c>
       <c r="G239" t="n">
-        <v>2.21828293800354</v>
+        <v>2.21828246116638</v>
       </c>
       <c r="H239" t="n">
         <v>19000</v>
@@ -7329,7 +7329,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G240" t="n">
-        <v>2.20842361450195</v>
+        <v>2.20842385292053</v>
       </c>
       <c r="H240" t="n">
         <v>35000</v>
@@ -7358,7 +7358,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G241" t="n">
-        <v>2.22814178466797</v>
+        <v>2.22814130783081</v>
       </c>
       <c r="H241" t="n">
         <v>5000</v>
@@ -7387,7 +7387,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G242" t="n">
-        <v>2.25771903991699</v>
+        <v>2.25771880149841</v>
       </c>
       <c r="H242" t="n">
         <v>19000</v>
@@ -7445,7 +7445,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G244" t="n">
-        <v>2.29715514183044</v>
+        <v>2.29715490341187</v>
       </c>
       <c r="H244" t="n">
         <v>6000</v>
@@ -7474,7 +7474,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G245" t="n">
-        <v>2.29715514183044</v>
+        <v>2.29715490341187</v>
       </c>
       <c r="H245" t="n">
         <v>0</v>
@@ -7735,7 +7735,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G254" t="n">
-        <v>2.4844765663147</v>
+        <v>2.48447680473328</v>
       </c>
       <c r="H254" t="n">
         <v>14000</v>
@@ -7764,7 +7764,7 @@
         <v>2.5</v>
       </c>
       <c r="G255" t="n">
-        <v>2.46475887298584</v>
+        <v>2.46475863456726</v>
       </c>
       <c r="H255" t="n">
         <v>11000</v>
@@ -7880,7 +7880,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G259" t="n">
-        <v>2.59292650222778</v>
+        <v>2.5929262638092</v>
       </c>
       <c r="H259" t="n">
         <v>5000</v>
@@ -7909,7 +7909,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G260" t="n">
-        <v>2.74081158638</v>
+        <v>2.74081182479858</v>
       </c>
       <c r="H260" t="n">
         <v>51000</v>
@@ -7938,7 +7938,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G261" t="n">
-        <v>2.66193962097168</v>
+        <v>2.6619393825531</v>
       </c>
       <c r="H261" t="n">
         <v>22000</v>
@@ -7996,7 +7996,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G263" t="n">
-        <v>2.97742819786072</v>
+        <v>2.9774284362793</v>
       </c>
       <c r="H263" t="n">
         <v>41000</v>
@@ -8054,7 +8054,7 @@
         <v>3</v>
       </c>
       <c r="G265" t="n">
-        <v>2.95771050453186</v>
+        <v>2.95771026611328</v>
       </c>
       <c r="H265" t="n">
         <v>85000</v>
@@ -8112,7 +8112,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G267" t="n">
-        <v>2.83940196037292</v>
+        <v>2.8394021987915</v>
       </c>
       <c r="H267" t="n">
         <v>62000</v>
@@ -8141,7 +8141,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G268" t="n">
-        <v>2.76052975654602</v>
+        <v>2.76052951812744</v>
       </c>
       <c r="H268" t="n">
         <v>35000</v>
@@ -8170,7 +8170,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G269" t="n">
-        <v>2.76052975654602</v>
+        <v>2.76052951812744</v>
       </c>
       <c r="H269" t="n">
         <v>3000</v>
@@ -8199,7 +8199,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G270" t="n">
-        <v>2.77038860321045</v>
+        <v>2.77038884162903</v>
       </c>
       <c r="H270" t="n">
         <v>11000</v>
@@ -8228,7 +8228,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G271" t="n">
-        <v>2.84926152229309</v>
+        <v>2.84926104545593</v>
       </c>
       <c r="H271" t="n">
         <v>21000</v>
@@ -8286,7 +8286,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G273" t="n">
-        <v>2.96756935119629</v>
+        <v>2.96756958961487</v>
       </c>
       <c r="H273" t="n">
         <v>22000</v>
@@ -8373,7 +8373,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G276" t="n">
-        <v>3.29291749000549</v>
+        <v>3.29291725158691</v>
       </c>
       <c r="H276" t="n">
         <v>39000</v>
@@ -8402,7 +8402,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G277" t="n">
-        <v>3.17460894584656</v>
+        <v>3.17460918426514</v>
       </c>
       <c r="H277" t="n">
         <v>36000</v>
@@ -8431,7 +8431,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G278" t="n">
-        <v>3.18446850776672</v>
+        <v>3.18446826934814</v>
       </c>
       <c r="H278" t="n">
         <v>19000</v>
@@ -8460,7 +8460,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G279" t="n">
-        <v>3.3027765750885</v>
+        <v>3.30277633666992</v>
       </c>
       <c r="H279" t="n">
         <v>14000</v>
@@ -8518,7 +8518,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G281" t="n">
-        <v>3.18446850776672</v>
+        <v>3.18446826934814</v>
       </c>
       <c r="H281" t="n">
         <v>10000</v>
@@ -8547,7 +8547,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G282" t="n">
-        <v>3.21404528617859</v>
+        <v>3.21404504776001</v>
       </c>
       <c r="H282" t="n">
         <v>6000</v>
@@ -8721,7 +8721,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G288" t="n">
-        <v>3.52953433990479</v>
+        <v>3.52953457832336</v>
       </c>
       <c r="H288" t="n">
         <v>19000</v>
@@ -8779,7 +8779,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G290" t="n">
-        <v>3.7267153263092</v>
+        <v>3.72671508789062</v>
       </c>
       <c r="H290" t="n">
         <v>11000</v>
@@ -8837,7 +8837,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G292" t="n">
-        <v>3.64784264564514</v>
+        <v>3.64784288406372</v>
       </c>
       <c r="H292" t="n">
         <v>5000</v>
@@ -8866,7 +8866,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G293" t="n">
-        <v>3.64784264564514</v>
+        <v>3.64784288406372</v>
       </c>
       <c r="H293" t="n">
         <v>16000</v>
@@ -8895,7 +8895,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G294" t="n">
-        <v>3.53939366340637</v>
+        <v>3.53939342498779</v>
       </c>
       <c r="H294" t="n">
         <v>30000</v>
@@ -9011,7 +9011,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G298" t="n">
-        <v>3.49009823799133</v>
+        <v>3.49009799957275</v>
       </c>
       <c r="H298" t="n">
         <v>27000</v>
@@ -9069,7 +9069,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G300" t="n">
-        <v>3.4802393913269</v>
+        <v>3.48023915290833</v>
       </c>
       <c r="H300" t="n">
         <v>15000</v>
@@ -9098,7 +9098,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G301" t="n">
-        <v>3.49009823799133</v>
+        <v>3.49009799957275</v>
       </c>
       <c r="H301" t="n">
         <v>1000</v>
@@ -9156,7 +9156,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G303" t="n">
-        <v>3.49009823799133</v>
+        <v>3.49009799957275</v>
       </c>
       <c r="H303" t="n">
         <v>1000</v>
@@ -9185,7 +9185,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G304" t="n">
-        <v>3.52953433990479</v>
+        <v>3.52953457832336</v>
       </c>
       <c r="H304" t="n">
         <v>2000</v>
@@ -9214,7 +9214,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G305" t="n">
-        <v>3.52953433990479</v>
+        <v>3.52953457832336</v>
       </c>
       <c r="H305" t="n">
         <v>1000</v>
@@ -9272,7 +9272,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G307" t="n">
-        <v>3.9731912612915</v>
+        <v>3.97319078445435</v>
       </c>
       <c r="H307" t="n">
         <v>45000</v>
@@ -9301,7 +9301,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G308" t="n">
-        <v>4.26896190643311</v>
+        <v>4.26896142959595</v>
       </c>
       <c r="H308" t="n">
         <v>57000</v>
@@ -9359,7 +9359,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G310" t="n">
-        <v>4.33797550201416</v>
+        <v>4.33797597885132</v>
       </c>
       <c r="H310" t="n">
         <v>1000</v>
@@ -9388,7 +9388,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G311" t="n">
-        <v>4.14079475402832</v>
+        <v>4.14079427719116</v>
       </c>
       <c r="H311" t="n">
         <v>40000</v>
@@ -9417,7 +9417,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G312" t="n">
-        <v>3.99290943145752</v>
+        <v>3.9929096698761</v>
       </c>
       <c r="H312" t="n">
         <v>51000</v>
@@ -9446,7 +9446,7 @@
         <v>4</v>
       </c>
       <c r="G313" t="n">
-        <v>3.9436137676239</v>
+        <v>3.94361400604248</v>
       </c>
       <c r="H313" t="n">
         <v>19000</v>
@@ -9533,7 +9533,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G316" t="n">
-        <v>4.08164024353027</v>
+        <v>4.08164072036743</v>
       </c>
       <c r="H316" t="n">
         <v>8000</v>
@@ -9562,7 +9562,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G317" t="n">
-        <v>4.14079475402832</v>
+        <v>4.14079427719116</v>
       </c>
       <c r="H317" t="n">
         <v>21000</v>
@@ -9649,7 +9649,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G320" t="n">
-        <v>4.2393856048584</v>
+        <v>4.23938512802124</v>
       </c>
       <c r="H320" t="n">
         <v>9000</v>
@@ -9736,7 +9736,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G323" t="n">
-        <v>4.18023014068604</v>
+        <v>4.18023061752319</v>
       </c>
       <c r="H323" t="n">
         <v>2000</v>
@@ -9765,7 +9765,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G324" t="n">
-        <v>4.18023014068604</v>
+        <v>4.18023061752319</v>
       </c>
       <c r="H324" t="n">
         <v>0</v>
@@ -9794,7 +9794,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G325" t="n">
-        <v>4.06192207336426</v>
+        <v>4.0619215965271</v>
       </c>
       <c r="H325" t="n">
         <v>7000</v>
@@ -9823,7 +9823,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G326" t="n">
-        <v>4.00276851654053</v>
+        <v>4.00276756286621</v>
       </c>
       <c r="H326" t="n">
         <v>5000</v>
@@ -9852,7 +9852,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G327" t="n">
-        <v>4.16051244735718</v>
+        <v>4.16051292419434</v>
       </c>
       <c r="H327" t="n">
         <v>7000</v>
@@ -9881,7 +9881,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G328" t="n">
-        <v>4.16051244735718</v>
+        <v>4.16051292419434</v>
       </c>
       <c r="H328" t="n">
         <v>2000</v>
@@ -9910,7 +9910,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G329" t="n">
-        <v>4.02248573303223</v>
+        <v>4.02248620986938</v>
       </c>
       <c r="H329" t="n">
         <v>5000</v>
@@ -9939,7 +9939,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G330" t="n">
-        <v>3.98305010795593</v>
+        <v>3.98304986953735</v>
       </c>
       <c r="H330" t="n">
         <v>3000</v>
@@ -9968,7 +9968,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G331" t="n">
-        <v>4.15065383911133</v>
+        <v>4.15065336227417</v>
       </c>
       <c r="H331" t="n">
         <v>10000</v>
@@ -9997,7 +9997,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G332" t="n">
-        <v>4.15065383911133</v>
+        <v>4.15065336227417</v>
       </c>
       <c r="H332" t="n">
         <v>1000</v>
@@ -10026,7 +10026,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G333" t="n">
-        <v>4.16051244735718</v>
+        <v>4.16051292419434</v>
       </c>
       <c r="H333" t="n">
         <v>5000</v>
@@ -10055,7 +10055,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G334" t="n">
-        <v>4.16051244735718</v>
+        <v>4.16051292419434</v>
       </c>
       <c r="H334" t="n">
         <v>14000</v>
@@ -10113,7 +10113,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G336" t="n">
-        <v>4.00276851654053</v>
+        <v>4.00276756286621</v>
       </c>
       <c r="H336" t="n">
         <v>3000</v>
@@ -10142,7 +10142,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G337" t="n">
-        <v>4.00276851654053</v>
+        <v>4.00276756286621</v>
       </c>
       <c r="H337" t="n">
         <v>0</v>
@@ -10171,7 +10171,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G338" t="n">
-        <v>4.16051244735718</v>
+        <v>4.16051292419434</v>
       </c>
       <c r="H338" t="n">
         <v>5000</v>
@@ -10200,7 +10200,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G339" t="n">
-        <v>4.16051244735718</v>
+        <v>4.16051292419434</v>
       </c>
       <c r="H339" t="n">
         <v>0</v>
@@ -10229,7 +10229,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G340" t="n">
-        <v>4.14079475402832</v>
+        <v>4.14079427719116</v>
       </c>
       <c r="H340" t="n">
         <v>16000</v>
@@ -10258,7 +10258,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G341" t="n">
-        <v>4.14079475402832</v>
+        <v>4.14079427719116</v>
       </c>
       <c r="H341" t="n">
         <v>15500</v>
@@ -10287,7 +10287,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G342" t="n">
-        <v>4.06192207336426</v>
+        <v>4.0619215965271</v>
       </c>
       <c r="H342" t="n">
         <v>5000</v>
@@ -10316,7 +10316,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G343" t="n">
-        <v>4.14079475402832</v>
+        <v>4.14079427719116</v>
       </c>
       <c r="H343" t="n">
         <v>3500</v>
@@ -10345,7 +10345,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G344" t="n">
-        <v>4.1112174987793</v>
+        <v>4.11121702194214</v>
       </c>
       <c r="H344" t="n">
         <v>1000</v>
@@ -10374,7 +10374,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G345" t="n">
-        <v>4.08164024353027</v>
+        <v>4.08164072036743</v>
       </c>
       <c r="H345" t="n">
         <v>1000</v>
@@ -10403,7 +10403,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G346" t="n">
-        <v>4.0422043800354</v>
+        <v>4.04220390319824</v>
       </c>
       <c r="H346" t="n">
         <v>2500</v>
@@ -10432,7 +10432,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G347" t="n">
-        <v>4.02248573303223</v>
+        <v>4.02248620986938</v>
       </c>
       <c r="H347" t="n">
         <v>3000</v>
@@ -10461,7 +10461,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G348" t="n">
-        <v>4.02248573303223</v>
+        <v>4.02248620986938</v>
       </c>
       <c r="H348" t="n">
         <v>16500</v>
@@ -10490,7 +10490,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G349" t="n">
-        <v>4.21966648101807</v>
+        <v>4.21966743469238</v>
       </c>
       <c r="H349" t="n">
         <v>21000</v>
@@ -10519,7 +10519,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G350" t="n">
-        <v>4.2393856048584</v>
+        <v>4.23938512802124</v>
       </c>
       <c r="H350" t="n">
         <v>24000</v>
@@ -10548,7 +10548,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G351" t="n">
-        <v>4.2393856048584</v>
+        <v>4.23938512802124</v>
       </c>
       <c r="H351" t="n">
         <v>4500</v>
@@ -10577,7 +10577,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G352" t="n">
-        <v>4.19994926452637</v>
+        <v>4.19994878768921</v>
       </c>
       <c r="H352" t="n">
         <v>8000</v>
@@ -10635,7 +10635,7 @@
         <v>4.25</v>
       </c>
       <c r="G354" t="n">
-        <v>4.19009017944336</v>
+        <v>4.1900897026062</v>
       </c>
       <c r="H354" t="n">
         <v>20500</v>
@@ -10664,7 +10664,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G355" t="n">
-        <v>4.08164024353027</v>
+        <v>4.08164072036743</v>
       </c>
       <c r="H355" t="n">
         <v>21000</v>
@@ -10693,7 +10693,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G356" t="n">
-        <v>4.14079475402832</v>
+        <v>4.14079427719116</v>
       </c>
       <c r="H356" t="n">
         <v>8500</v>
@@ -10780,7 +10780,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G359" t="n">
-        <v>4.21966648101807</v>
+        <v>4.21966743469238</v>
       </c>
       <c r="H359" t="n">
         <v>14500</v>
@@ -10809,7 +10809,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G360" t="n">
-        <v>4.15065383911133</v>
+        <v>4.15065336227417</v>
       </c>
       <c r="H360" t="n">
         <v>5000</v>
@@ -10838,7 +10838,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G361" t="n">
-        <v>4.08164024353027</v>
+        <v>4.08164072036743</v>
       </c>
       <c r="H361" t="n">
         <v>10500</v>
@@ -10896,7 +10896,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G363" t="n">
-        <v>4.1210765838623</v>
+        <v>4.12107610702515</v>
       </c>
       <c r="H363" t="n">
         <v>500</v>
@@ -10925,7 +10925,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G364" t="n">
-        <v>4.1210765838623</v>
+        <v>4.12107610702515</v>
       </c>
       <c r="H364" t="n">
         <v>0</v>
@@ -10954,7 +10954,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G365" t="n">
-        <v>4.1210765838623</v>
+        <v>4.12107610702515</v>
       </c>
       <c r="H365" t="n">
         <v>0</v>
@@ -10983,7 +10983,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G366" t="n">
-        <v>4.14079475402832</v>
+        <v>4.14079427719116</v>
       </c>
       <c r="H366" t="n">
         <v>1500</v>
@@ -11012,7 +11012,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G367" t="n">
-        <v>4.14079475402832</v>
+        <v>4.14079427719116</v>
       </c>
       <c r="H367" t="n">
         <v>1000</v>
@@ -11041,7 +11041,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G368" t="n">
-        <v>4.14079475402832</v>
+        <v>4.14079427719116</v>
       </c>
       <c r="H368" t="n">
         <v>0</v>
@@ -11070,7 +11070,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G369" t="n">
-        <v>4.08164024353027</v>
+        <v>4.08164072036743</v>
       </c>
       <c r="H369" t="n">
         <v>1500</v>
@@ -11128,7 +11128,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G371" t="n">
-        <v>4.01262712478638</v>
+        <v>4.01262760162354</v>
       </c>
       <c r="H371" t="n">
         <v>6000</v>
@@ -11157,7 +11157,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G372" t="n">
-        <v>4.08164024353027</v>
+        <v>4.08164072036743</v>
       </c>
       <c r="H372" t="n">
         <v>8500</v>
@@ -11186,7 +11186,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G373" t="n">
-        <v>4.14079475402832</v>
+        <v>4.14079427719116</v>
       </c>
       <c r="H373" t="n">
         <v>500</v>
@@ -11215,7 +11215,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G374" t="n">
-        <v>4.14079475402832</v>
+        <v>4.14079427719116</v>
       </c>
       <c r="H374" t="n">
         <v>0</v>
@@ -11244,7 +11244,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G375" t="n">
-        <v>4.14079475402832</v>
+        <v>4.14079427719116</v>
       </c>
       <c r="H375" t="n">
         <v>0</v>
@@ -11273,7 +11273,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G376" t="n">
-        <v>4.19994926452637</v>
+        <v>4.19994878768921</v>
       </c>
       <c r="H376" t="n">
         <v>7500</v>
@@ -11331,7 +11331,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G378" t="n">
-        <v>4.27882146835327</v>
+        <v>4.27882194519043</v>
       </c>
       <c r="H378" t="n">
         <v>7000</v>
@@ -11360,7 +11360,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G379" t="n">
-        <v>4.21966648101807</v>
+        <v>4.21966743469238</v>
       </c>
       <c r="H379" t="n">
         <v>67000</v>
@@ -11389,7 +11389,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G380" t="n">
-        <v>4.21966648101807</v>
+        <v>4.21966743469238</v>
       </c>
       <c r="H380" t="n">
         <v>3000</v>
@@ -11418,7 +11418,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G381" t="n">
-        <v>4.25910329818726</v>
+        <v>4.2591028213501</v>
       </c>
       <c r="H381" t="n">
         <v>2500</v>
@@ -11447,7 +11447,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G382" t="n">
-        <v>4.29853916168213</v>
+        <v>4.29853963851929</v>
       </c>
       <c r="H382" t="n">
         <v>35000</v>
@@ -11476,7 +11476,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G383" t="n">
-        <v>4.30839824676514</v>
+        <v>4.30839776992798</v>
       </c>
       <c r="H383" t="n">
         <v>2500</v>
@@ -11505,7 +11505,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G384" t="n">
-        <v>4.33797550201416</v>
+        <v>4.33797597885132</v>
       </c>
       <c r="H384" t="n">
         <v>17000</v>
@@ -11534,7 +11534,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G385" t="n">
-        <v>4.36755180358887</v>
+        <v>4.36755275726318</v>
       </c>
       <c r="H385" t="n">
         <v>4000</v>
@@ -11563,7 +11563,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G386" t="n">
-        <v>4.30839824676514</v>
+        <v>4.30839776992798</v>
       </c>
       <c r="H386" t="n">
         <v>255000</v>
@@ -11592,7 +11592,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G387" t="n">
-        <v>4.36755180358887</v>
+        <v>4.36755275726318</v>
       </c>
       <c r="H387" t="n">
         <v>6000</v>
@@ -11621,7 +11621,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G388" t="n">
-        <v>4.36755180358887</v>
+        <v>4.36755275726318</v>
       </c>
       <c r="H388" t="n">
         <v>13500</v>
@@ -11650,7 +11650,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G389" t="n">
-        <v>4.26896190643311</v>
+        <v>4.26896142959595</v>
       </c>
       <c r="H389" t="n">
         <v>15000</v>
@@ -11679,7 +11679,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G390" t="n">
-        <v>4.33797550201416</v>
+        <v>4.33797597885132</v>
       </c>
       <c r="H390" t="n">
         <v>15000</v>
@@ -11708,7 +11708,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G391" t="n">
-        <v>4.30839824676514</v>
+        <v>4.30839776992798</v>
       </c>
       <c r="H391" t="n">
         <v>34000</v>
@@ -11737,7 +11737,7 @@
         <v>4.25</v>
       </c>
       <c r="G392" t="n">
-        <v>4.19009017944336</v>
+        <v>4.1900897026062</v>
       </c>
       <c r="H392" t="n">
         <v>8000</v>
@@ -11766,7 +11766,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G393" t="n">
-        <v>4.33797550201416</v>
+        <v>4.33797597885132</v>
       </c>
       <c r="H393" t="n">
         <v>6000</v>
@@ -11795,7 +11795,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G394" t="n">
-        <v>4.4069881439209</v>
+        <v>4.40698862075806</v>
       </c>
       <c r="H394" t="n">
         <v>2000</v>
@@ -11882,7 +11882,7 @@
         <v>4.25</v>
       </c>
       <c r="G397" t="n">
-        <v>4.19009017944336</v>
+        <v>4.1900897026062</v>
       </c>
       <c r="H397" t="n">
         <v>7500</v>
@@ -11911,7 +11911,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G398" t="n">
-        <v>4.0422043800354</v>
+        <v>4.04220390319824</v>
       </c>
       <c r="H398" t="n">
         <v>6000</v>
@@ -11940,7 +11940,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G399" t="n">
-        <v>4.0422043800354</v>
+        <v>4.04220390319824</v>
       </c>
       <c r="H399" t="n">
         <v>7500</v>
@@ -11969,7 +11969,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G400" t="n">
-        <v>4.0422043800354</v>
+        <v>4.04220390319824</v>
       </c>
       <c r="H400" t="n">
         <v>0</v>
@@ -11998,7 +11998,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G401" t="n">
-        <v>4.18023014068604</v>
+        <v>4.18023061752319</v>
       </c>
       <c r="H401" t="n">
         <v>33500</v>
@@ -12027,7 +12027,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G402" t="n">
-        <v>4.19994926452637</v>
+        <v>4.19994878768921</v>
       </c>
       <c r="H402" t="n">
         <v>23500</v>
@@ -12056,7 +12056,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G403" t="n">
-        <v>4.29853916168213</v>
+        <v>4.29853963851929</v>
       </c>
       <c r="H403" t="n">
         <v>26500</v>
@@ -12085,7 +12085,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G404" t="n">
-        <v>4.33797550201416</v>
+        <v>4.33797597885132</v>
       </c>
       <c r="H404" t="n">
         <v>37500</v>
@@ -12143,7 +12143,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G406" t="n">
-        <v>4.39713001251221</v>
+        <v>4.39712905883789</v>
       </c>
       <c r="H406" t="n">
         <v>19500</v>
@@ -12259,7 +12259,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G410" t="n">
-        <v>4.63374662399292</v>
+        <v>4.6337456703186</v>
       </c>
       <c r="H410" t="n">
         <v>92000</v>
@@ -12288,7 +12288,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G411" t="n">
-        <v>5.04782581329346</v>
+        <v>5.0478253364563</v>
       </c>
       <c r="H411" t="n">
         <v>104000</v>
@@ -12375,7 +12375,7 @@
         <v>5</v>
       </c>
       <c r="G414" t="n">
-        <v>4.92951774597168</v>
+        <v>4.92951726913452</v>
       </c>
       <c r="H414" t="n">
         <v>45500</v>
@@ -12404,7 +12404,7 @@
         <v>5</v>
       </c>
       <c r="G415" t="n">
-        <v>4.92951774597168</v>
+        <v>4.92951726913452</v>
       </c>
       <c r="H415" t="n">
         <v>14500</v>
@@ -12433,7 +12433,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G416" t="n">
-        <v>4.96895313262939</v>
+        <v>4.96895360946655</v>
       </c>
       <c r="H416" t="n">
         <v>6000</v>
@@ -12462,7 +12462,7 @@
         <v>5</v>
       </c>
       <c r="G417" t="n">
-        <v>4.92951774597168</v>
+        <v>4.92951726913452</v>
       </c>
       <c r="H417" t="n">
         <v>7500</v>
@@ -12491,7 +12491,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G418" t="n">
-        <v>4.98867177963257</v>
+        <v>4.98867130279541</v>
       </c>
       <c r="H418" t="n">
         <v>23500</v>
@@ -12520,7 +12520,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G419" t="n">
-        <v>5.0281081199646</v>
+        <v>5.02810716629028</v>
       </c>
       <c r="H419" t="n">
         <v>5500</v>
@@ -12549,7 +12549,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G420" t="n">
-        <v>5.00838899612427</v>
+        <v>5.00838947296143</v>
       </c>
       <c r="H420" t="n">
         <v>4500</v>
@@ -12578,7 +12578,7 @@
         <v>5</v>
       </c>
       <c r="G421" t="n">
-        <v>4.92951774597168</v>
+        <v>4.92951726913452</v>
       </c>
       <c r="H421" t="n">
         <v>8500</v>
@@ -12607,7 +12607,7 @@
         <v>5</v>
       </c>
       <c r="G422" t="n">
-        <v>4.92951774597168</v>
+        <v>4.92951726913452</v>
       </c>
       <c r="H422" t="n">
         <v>9500</v>
@@ -12636,7 +12636,7 @@
         <v>5</v>
       </c>
       <c r="G423" t="n">
-        <v>4.92951774597168</v>
+        <v>4.92951726913452</v>
       </c>
       <c r="H423" t="n">
         <v>38500</v>
@@ -12694,7 +12694,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G425" t="n">
-        <v>5.0281081199646</v>
+        <v>5.02810716629028</v>
       </c>
       <c r="H425" t="n">
         <v>4500</v>
@@ -12752,7 +12752,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G427" t="n">
-        <v>5.0281081199646</v>
+        <v>5.02810716629028</v>
       </c>
       <c r="H427" t="n">
         <v>1500</v>
@@ -12781,7 +12781,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G428" t="n">
-        <v>5.00838899612427</v>
+        <v>5.00838947296143</v>
       </c>
       <c r="H428" t="n">
         <v>2500</v>
@@ -12810,7 +12810,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G429" t="n">
-        <v>5.12669801712036</v>
+        <v>5.1266975402832</v>
       </c>
       <c r="H429" t="n">
         <v>7000</v>
@@ -12839,7 +12839,7 @@
         <v>5</v>
       </c>
       <c r="G430" t="n">
-        <v>4.92951774597168</v>
+        <v>4.92951726913452</v>
       </c>
       <c r="H430" t="n">
         <v>8500</v>
@@ -12868,7 +12868,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G431" t="n">
-        <v>4.98867177963257</v>
+        <v>4.98867130279541</v>
       </c>
       <c r="H431" t="n">
         <v>8000</v>
@@ -12897,7 +12897,7 @@
         <v>5</v>
       </c>
       <c r="G432" t="n">
-        <v>4.92951774597168</v>
+        <v>4.92951726913452</v>
       </c>
       <c r="H432" t="n">
         <v>1000</v>
@@ -12926,7 +12926,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G433" t="n">
-        <v>4.88022184371948</v>
+        <v>4.88022232055664</v>
       </c>
       <c r="H433" t="n">
         <v>500</v>
@@ -12955,7 +12955,7 @@
         <v>5</v>
       </c>
       <c r="G434" t="n">
-        <v>4.92951774597168</v>
+        <v>4.92951726913452</v>
       </c>
       <c r="H434" t="n">
         <v>7000</v>
@@ -13013,7 +13013,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G436" t="n">
-        <v>4.91965818405151</v>
+        <v>4.91965770721436</v>
       </c>
       <c r="H436" t="n">
         <v>17500</v>
@@ -13071,7 +13071,7 @@
         <v>5</v>
       </c>
       <c r="G438" t="n">
-        <v>4.92951774597168</v>
+        <v>4.92951726913452</v>
       </c>
       <c r="H438" t="n">
         <v>7500</v>
@@ -13129,7 +13129,7 @@
         <v>5</v>
       </c>
       <c r="G440" t="n">
-        <v>4.92951774597168</v>
+        <v>4.92951726913452</v>
       </c>
       <c r="H440" t="n">
         <v>2000</v>
@@ -13216,7 +13216,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G443" t="n">
-        <v>5.04782581329346</v>
+        <v>5.0478253364563</v>
       </c>
       <c r="H443" t="n">
         <v>5500</v>
@@ -13245,7 +13245,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G444" t="n">
-        <v>5.0281081199646</v>
+        <v>5.02810716629028</v>
       </c>
       <c r="H444" t="n">
         <v>6500</v>
@@ -13274,7 +13274,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G445" t="n">
-        <v>4.96895313262939</v>
+        <v>4.96895360946655</v>
       </c>
       <c r="H445" t="n">
         <v>2500</v>
@@ -13361,7 +13361,7 @@
         <v>5</v>
       </c>
       <c r="G448" t="n">
-        <v>4.92951774597168</v>
+        <v>4.92951726913452</v>
       </c>
       <c r="H448" t="n">
         <v>19060</v>
@@ -13390,7 +13390,7 @@
         <v>5</v>
       </c>
       <c r="G449" t="n">
-        <v>4.92951774597168</v>
+        <v>4.92951726913452</v>
       </c>
       <c r="H449" t="n">
         <v>10200</v>
@@ -13419,7 +13419,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G450" t="n">
-        <v>4.83092737197876</v>
+        <v>4.8309268951416</v>
       </c>
       <c r="H450" t="n">
         <v>30540</v>
@@ -13448,7 +13448,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G451" t="n">
-        <v>4.83092737197876</v>
+        <v>4.8309268951416</v>
       </c>
       <c r="H451" t="n">
         <v>3150</v>
@@ -13477,7 +13477,7 @@
         <v>5</v>
       </c>
       <c r="G452" t="n">
-        <v>4.92951774597168</v>
+        <v>4.92951726913452</v>
       </c>
       <c r="H452" t="n">
         <v>1500</v>
@@ -13506,7 +13506,7 @@
         <v>5</v>
       </c>
       <c r="G453" t="n">
-        <v>4.92951774597168</v>
+        <v>4.92951726913452</v>
       </c>
       <c r="H453" t="n">
         <v>900</v>
@@ -13593,7 +13593,7 @@
         <v>5</v>
       </c>
       <c r="G456" t="n">
-        <v>4.92951774597168</v>
+        <v>4.92951726913452</v>
       </c>
       <c r="H456" t="n">
         <v>2220</v>
@@ -13622,7 +13622,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G457" t="n">
-        <v>5.04782581329346</v>
+        <v>5.0478253364563</v>
       </c>
       <c r="H457" t="n">
         <v>26170</v>
@@ -13680,7 +13680,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G459" t="n">
-        <v>5.26472425460815</v>
+        <v>5.26472520828247</v>
       </c>
       <c r="H459" t="n">
         <v>23670</v>
@@ -13825,7 +13825,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G464" t="n">
-        <v>5.04782581329346</v>
+        <v>5.0478253364563</v>
       </c>
       <c r="H464" t="n">
         <v>3580</v>
@@ -13854,7 +13854,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G465" t="n">
-        <v>5.16613388061523</v>
+        <v>5.16613435745239</v>
       </c>
       <c r="H465" t="n">
         <v>650</v>
@@ -13883,7 +13883,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G466" t="n">
-        <v>5.12669801712036</v>
+        <v>5.1266975402832</v>
       </c>
       <c r="H466" t="n">
         <v>7070</v>
@@ -13912,7 +13912,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G467" t="n">
-        <v>5.12669801712036</v>
+        <v>5.1266975402832</v>
       </c>
       <c r="H467" t="n">
         <v>200</v>
@@ -13941,7 +13941,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G468" t="n">
-        <v>5.16613388061523</v>
+        <v>5.16613435745239</v>
       </c>
       <c r="H468" t="n">
         <v>10280</v>
@@ -14086,7 +14086,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G473" t="n">
-        <v>5.20557022094727</v>
+        <v>5.20557069778442</v>
       </c>
       <c r="H473" t="n">
         <v>9950</v>
@@ -14115,7 +14115,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G474" t="n">
-        <v>4.98867177963257</v>
+        <v>4.98867130279541</v>
       </c>
       <c r="H474" t="n">
         <v>17780</v>
@@ -14173,7 +14173,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G476" t="n">
-        <v>5.0281081199646</v>
+        <v>5.02810716629028</v>
       </c>
       <c r="H476" t="n">
         <v>2700</v>
@@ -14202,7 +14202,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G477" t="n">
-        <v>5.00838899612427</v>
+        <v>5.00838947296143</v>
       </c>
       <c r="H477" t="n">
         <v>1250</v>
@@ -14231,7 +14231,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G478" t="n">
-        <v>4.96895313262939</v>
+        <v>4.96895360946655</v>
       </c>
       <c r="H478" t="n">
         <v>3060</v>
@@ -14260,7 +14260,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G479" t="n">
-        <v>5.0281081199646</v>
+        <v>5.02810716629028</v>
       </c>
       <c r="H479" t="n">
         <v>12190</v>
@@ -14376,7 +14376,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G483" t="n">
-        <v>5.12669801712036</v>
+        <v>5.1266975402832</v>
       </c>
       <c r="H483" t="n">
         <v>4620</v>
@@ -14405,7 +14405,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G484" t="n">
-        <v>5.12669801712036</v>
+        <v>5.1266975402832</v>
       </c>
       <c r="H484" t="n">
         <v>6620</v>
@@ -14434,7 +14434,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G485" t="n">
-        <v>5.12669801712036</v>
+        <v>5.1266975402832</v>
       </c>
       <c r="H485" t="n">
         <v>11880</v>
@@ -14463,7 +14463,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G486" t="n">
-        <v>5.04782581329346</v>
+        <v>5.0478253364563</v>
       </c>
       <c r="H486" t="n">
         <v>5290</v>
@@ -14492,7 +14492,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G487" t="n">
-        <v>5.16613388061523</v>
+        <v>5.16613435745239</v>
       </c>
       <c r="H487" t="n">
         <v>18380</v>
@@ -14550,7 +14550,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G489" t="n">
-        <v>4.98867177963257</v>
+        <v>4.98867130279541</v>
       </c>
       <c r="H489" t="n">
         <v>21530</v>
@@ -14579,7 +14579,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G490" t="n">
-        <v>5.12669801712036</v>
+        <v>5.1266975402832</v>
       </c>
       <c r="H490" t="n">
         <v>26550</v>
@@ -14608,7 +14608,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G491" t="n">
-        <v>4.98867177963257</v>
+        <v>4.98867130279541</v>
       </c>
       <c r="H491" t="n">
         <v>28100</v>
@@ -14637,7 +14637,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G492" t="n">
-        <v>4.96895313262939</v>
+        <v>4.96895360946655</v>
       </c>
       <c r="H492" t="n">
         <v>10980</v>
@@ -14666,7 +14666,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G493" t="n">
-        <v>5.16613388061523</v>
+        <v>5.16613435745239</v>
       </c>
       <c r="H493" t="n">
         <v>5990</v>
@@ -14782,7 +14782,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G497" t="n">
-        <v>4.87036323547363</v>
+        <v>4.87036371231079</v>
       </c>
       <c r="H497" t="n">
         <v>20640</v>
@@ -14811,7 +14811,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G498" t="n">
-        <v>5.0281081199646</v>
+        <v>5.02810716629028</v>
       </c>
       <c r="H498" t="n">
         <v>7720</v>
@@ -14840,7 +14840,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G499" t="n">
-        <v>5.0281081199646</v>
+        <v>5.02810716629028</v>
       </c>
       <c r="H499" t="n">
         <v>4040</v>
@@ -14869,7 +14869,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G500" t="n">
-        <v>5.04782581329346</v>
+        <v>5.0478253364563</v>
       </c>
       <c r="H500" t="n">
         <v>4690</v>
@@ -14956,7 +14956,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G503" t="n">
-        <v>5.0281081199646</v>
+        <v>5.02810716629028</v>
       </c>
       <c r="H503" t="n">
         <v>14170</v>
@@ -14985,7 +14985,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G504" t="n">
-        <v>4.83092737197876</v>
+        <v>4.8309268951416</v>
       </c>
       <c r="H504" t="n">
         <v>16000</v>
@@ -15014,7 +15014,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G505" t="n">
-        <v>4.98867177963257</v>
+        <v>4.98867130279541</v>
       </c>
       <c r="H505" t="n">
         <v>4800</v>
@@ -15043,7 +15043,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G506" t="n">
-        <v>5.12669801712036</v>
+        <v>5.1266975402832</v>
       </c>
       <c r="H506" t="n">
         <v>5270</v>
@@ -15101,7 +15101,7 @@
         <v>5</v>
       </c>
       <c r="G508" t="n">
-        <v>4.92951774597168</v>
+        <v>4.92951726913452</v>
       </c>
       <c r="H508" t="n">
         <v>5700</v>
@@ -15159,7 +15159,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G510" t="n">
-        <v>4.98867177963257</v>
+        <v>4.98867130279541</v>
       </c>
       <c r="H510" t="n">
         <v>1110</v>
@@ -15188,7 +15188,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G511" t="n">
-        <v>5.0281081199646</v>
+        <v>5.02810716629028</v>
       </c>
       <c r="H511" t="n">
         <v>2710</v>
@@ -15246,7 +15246,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G513" t="n">
-        <v>5.00838899612427</v>
+        <v>5.00838947296143</v>
       </c>
       <c r="H513" t="n">
         <v>10130</v>
@@ -15275,7 +15275,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G514" t="n">
-        <v>4.96895313262939</v>
+        <v>4.96895360946655</v>
       </c>
       <c r="H514" t="n">
         <v>2590</v>
@@ -15333,7 +15333,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G516" t="n">
-        <v>5.00838899612427</v>
+        <v>5.00838947296143</v>
       </c>
       <c r="H516" t="n">
         <v>640</v>
@@ -15362,7 +15362,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G517" t="n">
-        <v>5.0281081199646</v>
+        <v>5.02810716629028</v>
       </c>
       <c r="H517" t="n">
         <v>80</v>
@@ -15391,7 +15391,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G518" t="n">
-        <v>5.00838899612427</v>
+        <v>5.00838947296143</v>
       </c>
       <c r="H518" t="n">
         <v>3020</v>
@@ -15420,7 +15420,7 @@
         <v>5</v>
       </c>
       <c r="G519" t="n">
-        <v>4.92951774597168</v>
+        <v>4.92951726913452</v>
       </c>
       <c r="H519" t="n">
         <v>12340</v>
@@ -15449,7 +15449,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G520" t="n">
-        <v>5.0281081199646</v>
+        <v>5.02810716629028</v>
       </c>
       <c r="H520" t="n">
         <v>18090</v>
@@ -15478,7 +15478,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G521" t="n">
-        <v>5.20557022094727</v>
+        <v>5.20557069778442</v>
       </c>
       <c r="H521" t="n">
         <v>4650</v>
@@ -15507,7 +15507,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G522" t="n">
-        <v>5.04782581329346</v>
+        <v>5.0478253364563</v>
       </c>
       <c r="H522" t="n">
         <v>27900</v>
@@ -15536,7 +15536,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G523" t="n">
-        <v>5.0281081199646</v>
+        <v>5.02810716629028</v>
       </c>
       <c r="H523" t="n">
         <v>1940</v>
@@ -15594,7 +15594,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G525" t="n">
-        <v>4.88022184371948</v>
+        <v>4.88022232055664</v>
       </c>
       <c r="H525" t="n">
         <v>11030</v>
@@ -15623,7 +15623,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G526" t="n">
-        <v>5.00838899612427</v>
+        <v>5.00838947296143</v>
       </c>
       <c r="H526" t="n">
         <v>2400</v>
@@ -15681,7 +15681,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G528" t="n">
-        <v>4.80134963989258</v>
+        <v>4.80135011672974</v>
       </c>
       <c r="H528" t="n">
         <v>15650</v>
@@ -15710,7 +15710,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G529" t="n">
-        <v>4.77177286148071</v>
+        <v>4.77177238464355</v>
       </c>
       <c r="H529" t="n">
         <v>14510</v>
@@ -15739,7 +15739,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G530" t="n">
-        <v>4.73233699798584</v>
+        <v>4.73233652114868</v>
       </c>
       <c r="H530" t="n">
         <v>6730</v>
@@ -15768,7 +15768,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G531" t="n">
-        <v>4.80134963989258</v>
+        <v>4.80135011672974</v>
       </c>
       <c r="H531" t="n">
         <v>6500</v>
@@ -15797,7 +15797,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G532" t="n">
-        <v>4.77177286148071</v>
+        <v>4.77177238464355</v>
       </c>
       <c r="H532" t="n">
         <v>4310</v>
@@ -15826,7 +15826,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G533" t="n">
-        <v>4.79149150848389</v>
+        <v>4.79149055480957</v>
       </c>
       <c r="H533" t="n">
         <v>6340</v>
@@ -15855,7 +15855,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G534" t="n">
-        <v>4.73233699798584</v>
+        <v>4.73233652114868</v>
       </c>
       <c r="H534" t="n">
         <v>13910</v>
@@ -15884,7 +15884,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G535" t="n">
-        <v>4.73233699798584</v>
+        <v>4.73233652114868</v>
       </c>
       <c r="H535" t="n">
         <v>3100</v>
@@ -15913,7 +15913,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G536" t="n">
-        <v>4.71261882781982</v>
+        <v>4.71261835098267</v>
       </c>
       <c r="H536" t="n">
         <v>153850</v>
@@ -15942,7 +15942,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G537" t="n">
-        <v>4.73233699798584</v>
+        <v>4.73233652114868</v>
       </c>
       <c r="H537" t="n">
         <v>2420</v>
@@ -16029,7 +16029,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G540" t="n">
-        <v>4.83092737197876</v>
+        <v>4.8309268951416</v>
       </c>
       <c r="H540" t="n">
         <v>1600</v>
@@ -16087,7 +16087,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G542" t="n">
-        <v>4.86050415039062</v>
+        <v>4.86050367355347</v>
       </c>
       <c r="H542" t="n">
         <v>200</v>
@@ -16174,7 +16174,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G545" t="n">
-        <v>4.83092737197876</v>
+        <v>4.8309268951416</v>
       </c>
       <c r="H545" t="n">
         <v>1200</v>
@@ -16232,7 +16232,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G547" t="n">
-        <v>4.62362051010132</v>
+        <v>4.62362098693848</v>
       </c>
       <c r="H547" t="n">
         <v>10330</v>
@@ -16348,7 +16348,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G551" t="n">
-        <v>4.74217557907104</v>
+        <v>4.7421760559082</v>
       </c>
       <c r="H551" t="n">
         <v>730</v>
@@ -16464,7 +16464,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G555" t="n">
-        <v>4.86072969436646</v>
+        <v>4.86073017120361</v>
       </c>
       <c r="H555" t="n">
         <v>50</v>
@@ -16493,7 +16493,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G556" t="n">
-        <v>4.74217557907104</v>
+        <v>4.7421760559082</v>
       </c>
       <c r="H556" t="n">
         <v>13120</v>
@@ -16522,7 +16522,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G557" t="n">
-        <v>4.74217557907104</v>
+        <v>4.7421760559082</v>
       </c>
       <c r="H557" t="n">
         <v>260</v>
@@ -16638,7 +16638,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G561" t="n">
-        <v>4.79157257080078</v>
+        <v>4.79157304763794</v>
       </c>
       <c r="H561" t="n">
         <v>2000</v>
@@ -16812,7 +16812,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G567" t="n">
-        <v>4.82121133804321</v>
+        <v>4.82121181488037</v>
       </c>
       <c r="H567" t="n">
         <v>2600</v>
@@ -16841,7 +16841,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G568" t="n">
-        <v>4.82121133804321</v>
+        <v>4.82121181488037</v>
       </c>
       <c r="H568" t="n">
         <v>0</v>
@@ -16870,7 +16870,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G569" t="n">
-        <v>4.82121133804321</v>
+        <v>4.82121181488037</v>
       </c>
       <c r="H569" t="n">
         <v>50</v>
@@ -16899,7 +16899,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G570" t="n">
-        <v>4.82121133804321</v>
+        <v>4.82121181488037</v>
       </c>
       <c r="H570" t="n">
         <v>0</v>
@@ -17015,7 +17015,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G574" t="n">
-        <v>4.42603015899658</v>
+        <v>4.42603063583374</v>
       </c>
       <c r="H574" t="n">
         <v>2090</v>
@@ -17218,7 +17218,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G581" t="n">
-        <v>4.40627098083496</v>
+        <v>4.40627193450928</v>
       </c>
       <c r="H581" t="n">
         <v>1200</v>
@@ -17363,7 +17363,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G586" t="n">
-        <v>4.74217557907104</v>
+        <v>4.7421760559082</v>
       </c>
       <c r="H586" t="n">
         <v>200</v>
@@ -17479,7 +17479,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G590" t="n">
-        <v>4.3865122795105</v>
+        <v>4.38651275634766</v>
       </c>
       <c r="H590" t="n">
         <v>37290</v>
@@ -17508,7 +17508,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G591" t="n">
-        <v>4.34699392318726</v>
+        <v>4.34699440002441</v>
       </c>
       <c r="H591" t="n">
         <v>420</v>
@@ -17537,7 +17537,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G592" t="n">
-        <v>4.34699392318726</v>
+        <v>4.34699440002441</v>
       </c>
       <c r="H592" t="n">
         <v>35740</v>
@@ -17566,7 +17566,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G593" t="n">
-        <v>4.34699392318726</v>
+        <v>4.34699440002441</v>
       </c>
       <c r="H593" t="n">
         <v>10500</v>
@@ -17595,7 +17595,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G594" t="n">
-        <v>4.48530721664429</v>
+        <v>4.48530769348145</v>
       </c>
       <c r="H594" t="n">
         <v>1520</v>
@@ -17624,7 +17624,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G595" t="n">
-        <v>4.35687351226807</v>
+        <v>4.35687398910522</v>
       </c>
       <c r="H595" t="n">
         <v>30</v>
@@ -17682,7 +17682,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G597" t="n">
-        <v>4.40627098083496</v>
+        <v>4.40627193450928</v>
       </c>
       <c r="H597" t="n">
         <v>1930</v>
@@ -17769,7 +17769,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G600" t="n">
-        <v>4.48530721664429</v>
+        <v>4.48530769348145</v>
       </c>
       <c r="H600" t="n">
         <v>1360</v>
@@ -17798,7 +17798,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G601" t="n">
-        <v>4.54458475112915</v>
+        <v>4.54458522796631</v>
       </c>
       <c r="H601" t="n">
         <v>3410</v>
@@ -18030,7 +18030,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G609" t="n">
-        <v>4.8113317489624</v>
+        <v>4.81133222579956</v>
       </c>
       <c r="H609" t="n">
         <v>1910</v>
@@ -18088,7 +18088,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G611" t="n">
-        <v>4.72241592407227</v>
+        <v>4.72241687774658</v>
       </c>
       <c r="H611" t="n">
         <v>4980</v>
@@ -18204,7 +18204,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G615" t="n">
-        <v>4.88048887252808</v>
+        <v>4.88048934936523</v>
       </c>
       <c r="H615" t="n">
         <v>1500</v>
@@ -18233,7 +18233,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G616" t="n">
-        <v>4.97928380966187</v>
+        <v>4.97928428649902</v>
       </c>
       <c r="H616" t="n">
         <v>13050</v>
@@ -18262,7 +18262,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G617" t="n">
-        <v>4.97928380966187</v>
+        <v>4.97928428649902</v>
       </c>
       <c r="H617" t="n">
         <v>2400</v>
@@ -18320,7 +18320,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G619" t="n">
-        <v>4.97928380966187</v>
+        <v>4.97928428649902</v>
       </c>
       <c r="H619" t="n">
         <v>1000</v>
@@ -18349,7 +18349,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G620" t="n">
-        <v>4.99904298782349</v>
+        <v>4.99904346466064</v>
       </c>
       <c r="H620" t="n">
         <v>3460</v>
@@ -18378,7 +18378,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G621" t="n">
-        <v>5.01880168914795</v>
+        <v>5.01880264282227</v>
       </c>
       <c r="H621" t="n">
         <v>5130</v>
@@ -18407,7 +18407,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G622" t="n">
-        <v>5.01880168914795</v>
+        <v>5.01880264282227</v>
       </c>
       <c r="H622" t="n">
         <v>2300</v>
@@ -18436,7 +18436,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G623" t="n">
-        <v>5.01880168914795</v>
+        <v>5.01880264282227</v>
       </c>
       <c r="H623" t="n">
         <v>0</v>
@@ -18465,7 +18465,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G624" t="n">
-        <v>5.03856182098389</v>
+        <v>5.03856134414673</v>
       </c>
       <c r="H624" t="n">
         <v>200</v>
@@ -18494,7 +18494,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G625" t="n">
-        <v>5.03856182098389</v>
+        <v>5.03856134414673</v>
       </c>
       <c r="H625" t="n">
         <v>2500</v>
@@ -18552,7 +18552,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G627" t="n">
-        <v>4.86072969436646</v>
+        <v>4.86073017120361</v>
       </c>
       <c r="H627" t="n">
         <v>14440</v>
@@ -18581,7 +18581,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G628" t="n">
-        <v>4.87060928344727</v>
+        <v>4.87060880661011</v>
       </c>
       <c r="H628" t="n">
         <v>1000</v>
@@ -18610,7 +18610,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G629" t="n">
-        <v>4.86072969436646</v>
+        <v>4.86073017120361</v>
       </c>
       <c r="H629" t="n">
         <v>6500</v>
@@ -18639,7 +18639,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G630" t="n">
-        <v>4.86072969436646</v>
+        <v>4.86073017120361</v>
       </c>
       <c r="H630" t="n">
         <v>2660</v>
@@ -18668,7 +18668,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G631" t="n">
-        <v>4.86072969436646</v>
+        <v>4.86073017120361</v>
       </c>
       <c r="H631" t="n">
         <v>820</v>
@@ -18726,7 +18726,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G633" t="n">
-        <v>4.8113317489624</v>
+        <v>4.81133222579956</v>
       </c>
       <c r="H633" t="n">
         <v>200</v>
@@ -18842,7 +18842,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G637" t="n">
-        <v>4.88048887252808</v>
+        <v>4.88048934936523</v>
       </c>
       <c r="H637" t="n">
         <v>1800</v>
@@ -18871,7 +18871,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G638" t="n">
-        <v>4.88048887252808</v>
+        <v>4.88048934936523</v>
       </c>
       <c r="H638" t="n">
         <v>0</v>
@@ -18900,7 +18900,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G639" t="n">
-        <v>4.87060928344727</v>
+        <v>4.87060880661011</v>
       </c>
       <c r="H639" t="n">
         <v>6120</v>
@@ -18929,7 +18929,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G640" t="n">
-        <v>4.79157257080078</v>
+        <v>4.79157304763794</v>
       </c>
       <c r="H640" t="n">
         <v>4000</v>
@@ -18958,7 +18958,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G641" t="n">
-        <v>4.79157257080078</v>
+        <v>4.79157304763794</v>
       </c>
       <c r="H641" t="n">
         <v>0</v>
@@ -18987,7 +18987,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G642" t="n">
-        <v>4.79157257080078</v>
+        <v>4.79157304763794</v>
       </c>
       <c r="H642" t="n">
         <v>4040</v>
@@ -19045,7 +19045,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G644" t="n">
-        <v>4.54458475112915</v>
+        <v>4.54458522796631</v>
       </c>
       <c r="H644" t="n">
         <v>7280</v>
@@ -19132,7 +19132,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G647" t="n">
-        <v>4.34699392318726</v>
+        <v>4.34699440002441</v>
       </c>
       <c r="H647" t="n">
         <v>89070</v>
@@ -19161,7 +19161,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G648" t="n">
-        <v>4.34699392318726</v>
+        <v>4.34699440002441</v>
       </c>
       <c r="H648" t="n">
         <v>66390</v>
@@ -19219,7 +19219,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G650" t="n">
-        <v>4.52482509613037</v>
+        <v>4.52482604980469</v>
       </c>
       <c r="H650" t="n">
         <v>11950</v>
@@ -19306,7 +19306,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G653" t="n">
-        <v>4.79157257080078</v>
+        <v>4.79157304763794</v>
       </c>
       <c r="H653" t="n">
         <v>2680</v>
@@ -19335,7 +19335,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G654" t="n">
-        <v>4.86072969436646</v>
+        <v>4.86073017120361</v>
       </c>
       <c r="H654" t="n">
         <v>410</v>
@@ -19393,7 +19393,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G656" t="n">
-        <v>4.72241592407227</v>
+        <v>4.72241687774658</v>
       </c>
       <c r="H656" t="n">
         <v>2060</v>
@@ -19422,7 +19422,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G657" t="n">
-        <v>4.72241592407227</v>
+        <v>4.72241687774658</v>
       </c>
       <c r="H657" t="n">
         <v>0</v>
@@ -19480,7 +19480,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G659" t="n">
-        <v>4.74217557907104</v>
+        <v>4.7421760559082</v>
       </c>
       <c r="H659" t="n">
         <v>60</v>
@@ -19509,7 +19509,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G660" t="n">
-        <v>4.74217557907104</v>
+        <v>4.7421760559082</v>
       </c>
       <c r="H660" t="n">
         <v>12790</v>
@@ -19538,7 +19538,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G661" t="n">
-        <v>4.88048887252808</v>
+        <v>4.88048934936523</v>
       </c>
       <c r="H661" t="n">
         <v>1600</v>
@@ -19567,7 +19567,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G662" t="n">
-        <v>4.74217557907104</v>
+        <v>4.7421760559082</v>
       </c>
       <c r="H662" t="n">
         <v>10540</v>
@@ -19654,7 +19654,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G665" t="n">
-        <v>4.86072969436646</v>
+        <v>4.86073017120361</v>
       </c>
       <c r="H665" t="n">
         <v>3680</v>
@@ -19683,7 +19683,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G666" t="n">
-        <v>4.8113317489624</v>
+        <v>4.81133222579956</v>
       </c>
       <c r="H666" t="n">
         <v>13530</v>
@@ -19712,7 +19712,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G667" t="n">
-        <v>4.82121133804321</v>
+        <v>4.82121181488037</v>
       </c>
       <c r="H667" t="n">
         <v>8350</v>
@@ -19741,7 +19741,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G668" t="n">
-        <v>5.03856182098389</v>
+        <v>5.03856134414673</v>
       </c>
       <c r="H668" t="n">
         <v>8110</v>
@@ -19770,7 +19770,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G669" t="n">
-        <v>5.1175971031189</v>
+        <v>5.11759757995605</v>
       </c>
       <c r="H669" t="n">
         <v>13730</v>
@@ -19799,7 +19799,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G670" t="n">
-        <v>5.1175971031189</v>
+        <v>5.11759757995605</v>
       </c>
       <c r="H670" t="n">
         <v>340</v>
@@ -19828,7 +19828,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G671" t="n">
-        <v>5.03856182098389</v>
+        <v>5.03856134414673</v>
       </c>
       <c r="H671" t="n">
         <v>4620</v>
@@ -19857,7 +19857,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G672" t="n">
-        <v>5.1175971031189</v>
+        <v>5.11759757995605</v>
       </c>
       <c r="H672" t="n">
         <v>3970</v>
@@ -19915,7 +19915,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G674" t="n">
-        <v>5.03856182098389</v>
+        <v>5.03856134414673</v>
       </c>
       <c r="H674" t="n">
         <v>1320</v>
@@ -19944,7 +19944,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G675" t="n">
-        <v>4.97928380966187</v>
+        <v>4.97928428649902</v>
       </c>
       <c r="H675" t="n">
         <v>177850</v>
@@ -20031,7 +20031,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G678" t="n">
-        <v>4.74217557907104</v>
+        <v>4.7421760559082</v>
       </c>
       <c r="H678" t="n">
         <v>42730</v>
@@ -20060,7 +20060,7 @@
         <v>4.59000015258789</v>
       </c>
       <c r="G679" t="n">
-        <v>4.53470468521118</v>
+        <v>4.53470516204834</v>
       </c>
       <c r="H679" t="n">
         <v>78600</v>
@@ -20176,7 +20176,7 @@
         <v>4.59000015258789</v>
       </c>
       <c r="G683" t="n">
-        <v>4.53470468521118</v>
+        <v>4.53470516204834</v>
       </c>
       <c r="H683" t="n">
         <v>94970</v>
@@ -20205,7 +20205,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G684" t="n">
-        <v>4.52482509613037</v>
+        <v>4.52482604980469</v>
       </c>
       <c r="H684" t="n">
         <v>1210</v>
@@ -20234,7 +20234,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G685" t="n">
-        <v>4.34699392318726</v>
+        <v>4.34699440002441</v>
       </c>
       <c r="H685" t="n">
         <v>19270</v>
@@ -20379,7 +20379,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G690" t="n">
-        <v>4.71253633499146</v>
+        <v>4.71253681182861</v>
       </c>
       <c r="H690" t="n">
         <v>19330</v>
@@ -20408,7 +20408,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G691" t="n">
-        <v>5.01880168914795</v>
+        <v>5.01880264282227</v>
       </c>
       <c r="H691" t="n">
         <v>40840</v>
@@ -20437,7 +20437,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G692" t="n">
-        <v>5.03856182098389</v>
+        <v>5.03856134414673</v>
       </c>
       <c r="H692" t="n">
         <v>52130</v>
@@ -20495,7 +20495,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G694" t="n">
-        <v>5.03856182098389</v>
+        <v>5.03856134414673</v>
       </c>
       <c r="H694" t="n">
         <v>39050</v>
@@ -20524,7 +20524,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G695" t="n">
-        <v>4.99904298782349</v>
+        <v>4.99904346466064</v>
       </c>
       <c r="H695" t="n">
         <v>25780</v>
@@ -20582,7 +20582,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G697" t="n">
-        <v>5.03856182098389</v>
+        <v>5.03856134414673</v>
       </c>
       <c r="H697" t="n">
         <v>10770</v>
@@ -20611,7 +20611,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G698" t="n">
-        <v>5.1175971031189</v>
+        <v>5.11759757995605</v>
       </c>
       <c r="H698" t="n">
         <v>3510</v>
@@ -20640,7 +20640,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G699" t="n">
-        <v>5.1175971031189</v>
+        <v>5.11759757995605</v>
       </c>
       <c r="H699" t="n">
         <v>0</v>
@@ -20669,7 +20669,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G700" t="n">
-        <v>5.03856182098389</v>
+        <v>5.03856134414673</v>
       </c>
       <c r="H700" t="n">
         <v>300</v>
@@ -20698,7 +20698,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G701" t="n">
-        <v>5.03856182098389</v>
+        <v>5.03856134414673</v>
       </c>
       <c r="H701" t="n">
         <v>1190</v>
@@ -20727,7 +20727,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G702" t="n">
-        <v>5.03856182098389</v>
+        <v>5.03856134414673</v>
       </c>
       <c r="H702" t="n">
         <v>110</v>
@@ -20756,7 +20756,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G703" t="n">
-        <v>4.87060928344727</v>
+        <v>4.87060880661011</v>
       </c>
       <c r="H703" t="n">
         <v>5400</v>
@@ -20785,7 +20785,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G704" t="n">
-        <v>4.74217557907104</v>
+        <v>4.7421760559082</v>
       </c>
       <c r="H704" t="n">
         <v>5760</v>
@@ -20872,7 +20872,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G707" t="n">
-        <v>4.8508505821228</v>
+        <v>4.85084962844849</v>
       </c>
       <c r="H707" t="n">
         <v>250</v>
@@ -20901,7 +20901,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G708" t="n">
-        <v>5.1175971031189</v>
+        <v>5.11759757995605</v>
       </c>
       <c r="H708" t="n">
         <v>8710</v>
@@ -20988,7 +20988,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G711" t="n">
-        <v>4.88048887252808</v>
+        <v>4.88048934936523</v>
       </c>
       <c r="H711" t="n">
         <v>1130</v>
@@ -21017,7 +21017,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G712" t="n">
-        <v>4.72241592407227</v>
+        <v>4.72241687774658</v>
       </c>
       <c r="H712" t="n">
         <v>10280</v>
@@ -21046,7 +21046,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G713" t="n">
-        <v>4.71253633499146</v>
+        <v>4.71253681182861</v>
       </c>
       <c r="H713" t="n">
         <v>4900</v>
@@ -21075,7 +21075,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G714" t="n">
-        <v>4.6038613319397</v>
+        <v>4.60386180877686</v>
       </c>
       <c r="H714" t="n">
         <v>5550</v>
@@ -21104,7 +21104,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G715" t="n">
-        <v>4.71253633499146</v>
+        <v>4.71253681182861</v>
       </c>
       <c r="H715" t="n">
         <v>4150</v>
@@ -21133,7 +21133,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G716" t="n">
-        <v>4.72241592407227</v>
+        <v>4.72241687774658</v>
       </c>
       <c r="H716" t="n">
         <v>10940</v>
@@ -21191,7 +21191,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G718" t="n">
-        <v>4.82121133804321</v>
+        <v>4.82121181488037</v>
       </c>
       <c r="H718" t="n">
         <v>3100</v>
@@ -21249,7 +21249,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G720" t="n">
-        <v>5.01880168914795</v>
+        <v>5.01880264282227</v>
       </c>
       <c r="H720" t="n">
         <v>5570</v>
@@ -21278,7 +21278,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G721" t="n">
-        <v>5.09783792495728</v>
+        <v>5.09783840179443</v>
       </c>
       <c r="H721" t="n">
         <v>3950</v>
@@ -21336,7 +21336,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G723" t="n">
-        <v>5.1175971031189</v>
+        <v>5.11759757995605</v>
       </c>
       <c r="H723" t="n">
         <v>6040</v>
@@ -21365,7 +21365,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G724" t="n">
-        <v>5.1175971031189</v>
+        <v>5.11759757995605</v>
       </c>
       <c r="H724" t="n">
         <v>3650</v>
@@ -21394,7 +21394,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G725" t="n">
-        <v>5.13735628128052</v>
+        <v>5.13735675811768</v>
       </c>
       <c r="H725" t="n">
         <v>3650</v>
@@ -21423,7 +21423,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G726" t="n">
-        <v>5.03856182098389</v>
+        <v>5.03856134414673</v>
       </c>
       <c r="H726" t="n">
         <v>3700</v>
@@ -21452,7 +21452,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G727" t="n">
-        <v>4.97928380966187</v>
+        <v>4.97928428649902</v>
       </c>
       <c r="H727" t="n">
         <v>1500</v>
@@ -21481,7 +21481,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G728" t="n">
-        <v>4.76193428039551</v>
+        <v>4.76193475723267</v>
       </c>
       <c r="H728" t="n">
         <v>8770</v>
@@ -21539,7 +21539,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G730" t="n">
-        <v>4.82121133804321</v>
+        <v>4.82121181488037</v>
       </c>
       <c r="H730" t="n">
         <v>29580</v>
@@ -21568,7 +21568,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G731" t="n">
-        <v>4.74217557907104</v>
+        <v>4.7421760559082</v>
       </c>
       <c r="H731" t="n">
         <v>2850</v>
@@ -21597,7 +21597,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G732" t="n">
-        <v>4.86072969436646</v>
+        <v>4.86073017120361</v>
       </c>
       <c r="H732" t="n">
         <v>4460</v>
@@ -21626,7 +21626,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G733" t="n">
-        <v>4.88048887252808</v>
+        <v>4.88048934936523</v>
       </c>
       <c r="H733" t="n">
         <v>7390</v>
@@ -21684,7 +21684,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G735" t="n">
-        <v>4.79157257080078</v>
+        <v>4.79157304763794</v>
       </c>
       <c r="H735" t="n">
         <v>1520</v>
@@ -21713,7 +21713,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G736" t="n">
-        <v>4.88048887252808</v>
+        <v>4.88048934936523</v>
       </c>
       <c r="H736" t="n">
         <v>3780</v>
@@ -21771,7 +21771,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G738" t="n">
-        <v>4.82121133804321</v>
+        <v>4.82121181488037</v>
       </c>
       <c r="H738" t="n">
         <v>6100</v>
@@ -21800,7 +21800,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G739" t="n">
-        <v>4.82121133804321</v>
+        <v>4.82121181488037</v>
       </c>
       <c r="H739" t="n">
         <v>8640</v>
@@ -21829,7 +21829,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G740" t="n">
-        <v>4.8113317489624</v>
+        <v>4.81133222579956</v>
       </c>
       <c r="H740" t="n">
         <v>13020</v>
@@ -21858,7 +21858,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G741" t="n">
-        <v>4.82121133804321</v>
+        <v>4.82121181488037</v>
       </c>
       <c r="H741" t="n">
         <v>3340</v>
@@ -21916,7 +21916,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G743" t="n">
-        <v>4.8508505821228</v>
+        <v>4.85084962844849</v>
       </c>
       <c r="H743" t="n">
         <v>3070</v>
@@ -21945,7 +21945,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G744" t="n">
-        <v>4.86072969436646</v>
+        <v>4.86073017120361</v>
       </c>
       <c r="H744" t="n">
         <v>3440</v>
@@ -22032,7 +22032,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G747" t="n">
-        <v>4.74217557907104</v>
+        <v>4.7421760559082</v>
       </c>
       <c r="H747" t="n">
         <v>63650</v>
@@ -22148,7 +22148,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G751" t="n">
-        <v>4.17904186248779</v>
+        <v>4.17904233932495</v>
       </c>
       <c r="H751" t="n">
         <v>518850</v>
@@ -22177,7 +22177,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G752" t="n">
-        <v>4.22843933105469</v>
+        <v>4.228440284729</v>
       </c>
       <c r="H752" t="n">
         <v>104770</v>
@@ -22206,7 +22206,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G753" t="n">
-        <v>4.17904186248779</v>
+        <v>4.17904233932495</v>
       </c>
       <c r="H753" t="n">
         <v>125670</v>
@@ -22235,7 +22235,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G754" t="n">
-        <v>4.17904186248779</v>
+        <v>4.17904233932495</v>
       </c>
       <c r="H754" t="n">
         <v>21070</v>
@@ -22264,7 +22264,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G755" t="n">
-        <v>4.18892097473145</v>
+        <v>4.1889214515686</v>
       </c>
       <c r="H755" t="n">
         <v>62780</v>
@@ -22293,7 +22293,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G756" t="n">
-        <v>4.18892097473145</v>
+        <v>4.1889214515686</v>
       </c>
       <c r="H756" t="n">
         <v>28570</v>
@@ -22322,7 +22322,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G757" t="n">
-        <v>4.17904186248779</v>
+        <v>4.17904233932495</v>
       </c>
       <c r="H757" t="n">
         <v>17930</v>
@@ -22380,7 +22380,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G759" t="n">
-        <v>4.15928268432617</v>
+        <v>4.15928316116333</v>
       </c>
       <c r="H759" t="n">
         <v>8420</v>
@@ -22409,7 +22409,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G760" t="n">
-        <v>4.16916227340698</v>
+        <v>4.16916275024414</v>
       </c>
       <c r="H760" t="n">
         <v>13670</v>
@@ -22438,7 +22438,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G761" t="n">
-        <v>4.16916227340698</v>
+        <v>4.16916275024414</v>
       </c>
       <c r="H761" t="n">
         <v>5710</v>
@@ -22467,7 +22467,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G762" t="n">
-        <v>4.15928268432617</v>
+        <v>4.15928316116333</v>
       </c>
       <c r="H762" t="n">
         <v>1760</v>
@@ -22496,7 +22496,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G763" t="n">
-        <v>4.05060815811157</v>
+        <v>4.05060863494873</v>
       </c>
       <c r="H763" t="n">
         <v>55200</v>
@@ -22525,7 +22525,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G764" t="n">
-        <v>4.02096939086914</v>
+        <v>4.0209698677063</v>
       </c>
       <c r="H764" t="n">
         <v>16670</v>
@@ -22612,7 +22612,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G767" t="n">
-        <v>3.86289715766907</v>
+        <v>3.86289691925049</v>
       </c>
       <c r="H767" t="n">
         <v>15840</v>
@@ -22670,7 +22670,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G769" t="n">
-        <v>3.83325839042664</v>
+        <v>3.83325862884521</v>
       </c>
       <c r="H769" t="n">
         <v>12950</v>
@@ -22699,7 +22699,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G770" t="n">
-        <v>3.77398085594177</v>
+        <v>3.77398133277893</v>
       </c>
       <c r="H770" t="n">
         <v>16120</v>
@@ -22728,7 +22728,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G771" t="n">
-        <v>3.76410150527954</v>
+        <v>3.76410174369812</v>
       </c>
       <c r="H771" t="n">
         <v>37320</v>
@@ -22757,7 +22757,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G772" t="n">
-        <v>3.76410150527954</v>
+        <v>3.76410174369812</v>
       </c>
       <c r="H772" t="n">
         <v>37840</v>
@@ -22786,7 +22786,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G773" t="n">
-        <v>3.80361986160278</v>
+        <v>3.8036196231842</v>
       </c>
       <c r="H773" t="n">
         <v>4390</v>
@@ -22815,7 +22815,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G774" t="n">
-        <v>3.75422191619873</v>
+        <v>3.75422215461731</v>
       </c>
       <c r="H774" t="n">
         <v>58020</v>
@@ -22902,7 +22902,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G777" t="n">
-        <v>3.75422191619873</v>
+        <v>3.75422215461731</v>
       </c>
       <c r="H777" t="n">
         <v>185950</v>
@@ -22931,7 +22931,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G778" t="n">
-        <v>3.88265633583069</v>
+        <v>3.88265609741211</v>
       </c>
       <c r="H778" t="n">
         <v>6390</v>
@@ -23047,7 +23047,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G782" t="n">
-        <v>4.04072856903076</v>
+        <v>4.04072904586792</v>
       </c>
       <c r="H782" t="n">
         <v>14490</v>
@@ -23076,7 +23076,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G783" t="n">
-        <v>3.98145151138306</v>
+        <v>3.98145174980164</v>
       </c>
       <c r="H783" t="n">
         <v>8720</v>
@@ -23163,7 +23163,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G786" t="n">
-        <v>3.96169233322144</v>
+        <v>3.96169257164001</v>
       </c>
       <c r="H786" t="n">
         <v>3050</v>
@@ -23192,7 +23192,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G787" t="n">
-        <v>4.03084850311279</v>
+        <v>4.03084945678711</v>
       </c>
       <c r="H787" t="n">
         <v>5350</v>
@@ -23250,7 +23250,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G789" t="n">
-        <v>3.92217397689819</v>
+        <v>3.92217421531677</v>
       </c>
       <c r="H789" t="n">
         <v>12190</v>
@@ -23279,7 +23279,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G790" t="n">
-        <v>3.88265633583069</v>
+        <v>3.88265609741211</v>
       </c>
       <c r="H790" t="n">
         <v>7320</v>
@@ -23366,7 +23366,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G793" t="n">
-        <v>3.93205380439758</v>
+        <v>3.932053565979</v>
       </c>
       <c r="H793" t="n">
         <v>9740</v>
@@ -23424,7 +23424,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G795" t="n">
-        <v>3.86289715766907</v>
+        <v>3.86289691925049</v>
       </c>
       <c r="H795" t="n">
         <v>15070</v>
@@ -23511,7 +23511,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G798" t="n">
-        <v>3.83325839042664</v>
+        <v>3.83325862884521</v>
       </c>
       <c r="H798" t="n">
         <v>3250</v>
@@ -23685,7 +23685,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G804" t="n">
-        <v>3.86292219161987</v>
+        <v>3.86292243003845</v>
       </c>
       <c r="H804" t="n">
         <v>1300</v>
@@ -23743,7 +23743,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G806" t="n">
-        <v>3.86292219161987</v>
+        <v>3.86292243003845</v>
       </c>
       <c r="H806" t="n">
         <v>2310</v>
@@ -23772,7 +23772,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G807" t="n">
-        <v>4.01149606704712</v>
+        <v>4.01149654388428</v>
       </c>
       <c r="H807" t="n">
         <v>6240</v>
@@ -23830,7 +23830,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G809" t="n">
-        <v>3.95206665992737</v>
+        <v>3.95206642150879</v>
       </c>
       <c r="H809" t="n">
         <v>8670</v>
@@ -23859,7 +23859,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G810" t="n">
-        <v>3.95206665992737</v>
+        <v>3.95206642150879</v>
       </c>
       <c r="H810" t="n">
         <v>0</v>
@@ -23888,7 +23888,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G811" t="n">
-        <v>3.95206665992737</v>
+        <v>3.95206642150879</v>
       </c>
       <c r="H811" t="n">
         <v>2110</v>
@@ -23946,7 +23946,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G813" t="n">
-        <v>3.99168658256531</v>
+        <v>3.99168634414673</v>
       </c>
       <c r="H813" t="n">
         <v>8200</v>
@@ -24062,7 +24062,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G817" t="n">
-        <v>3.95206665992737</v>
+        <v>3.95206642150879</v>
       </c>
       <c r="H817" t="n">
         <v>50</v>
@@ -24207,7 +24207,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G822" t="n">
-        <v>4.090735912323</v>
+        <v>4.09073543548584</v>
       </c>
       <c r="H822" t="n">
         <v>17180</v>
@@ -24265,7 +24265,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G824" t="n">
-        <v>4.00159120559692</v>
+        <v>4.00159168243408</v>
       </c>
       <c r="H824" t="n">
         <v>4360</v>
@@ -24352,7 +24352,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G827" t="n">
-        <v>4.03130578994751</v>
+        <v>4.03130626678467</v>
       </c>
       <c r="H827" t="n">
         <v>14010</v>
@@ -24468,7 +24468,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G831" t="n">
-        <v>3.97187662124634</v>
+        <v>3.97187685966492</v>
       </c>
       <c r="H831" t="n">
         <v>7140</v>
@@ -24700,7 +24700,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G839" t="n">
-        <v>4.04121065139771</v>
+        <v>4.04121112823486</v>
       </c>
       <c r="H839" t="n">
         <v>14500</v>
@@ -24729,7 +24729,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G840" t="n">
-        <v>4.04121065139771</v>
+        <v>4.04121112823486</v>
       </c>
       <c r="H840" t="n">
         <v>0</v>
@@ -24758,7 +24758,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G841" t="n">
-        <v>4.00159120559692</v>
+        <v>4.00159168243408</v>
       </c>
       <c r="H841" t="n">
         <v>4090</v>
@@ -24874,7 +24874,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G845" t="n">
-        <v>3.95206665992737</v>
+        <v>3.95206642150879</v>
       </c>
       <c r="H845" t="n">
         <v>11870</v>
@@ -24903,7 +24903,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G846" t="n">
-        <v>4.00159120559692</v>
+        <v>4.00159168243408</v>
       </c>
       <c r="H846" t="n">
         <v>1050</v>
@@ -24990,7 +24990,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G849" t="n">
-        <v>4.13035535812378</v>
+        <v>4.13035583496094</v>
       </c>
       <c r="H849" t="n">
         <v>6470</v>
@@ -25048,7 +25048,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G851" t="n">
-        <v>4.16997480392456</v>
+        <v>4.16997528076172</v>
       </c>
       <c r="H851" t="n">
         <v>9220</v>
@@ -25077,7 +25077,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G852" t="n">
-        <v>4.19968938827515</v>
+        <v>4.1996898651123</v>
       </c>
       <c r="H852" t="n">
         <v>8340</v>
@@ -25135,7 +25135,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G854" t="n">
-        <v>4.16007041931152</v>
+        <v>4.16006994247437</v>
       </c>
       <c r="H854" t="n">
         <v>31610</v>
@@ -25164,7 +25164,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G855" t="n">
-        <v>4.16007041931152</v>
+        <v>4.16006994247437</v>
       </c>
       <c r="H855" t="n">
         <v>8120</v>
@@ -25193,7 +25193,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G856" t="n">
-        <v>4.090735912323</v>
+        <v>4.09073543548584</v>
       </c>
       <c r="H856" t="n">
         <v>19870</v>
@@ -25541,7 +25541,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G868" t="n">
-        <v>4.13035535812378</v>
+        <v>4.13035583496094</v>
       </c>
       <c r="H868" t="n">
         <v>4840</v>
@@ -25570,7 +25570,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G869" t="n">
-        <v>4.01149606704712</v>
+        <v>4.01149654388428</v>
       </c>
       <c r="H869" t="n">
         <v>10970</v>
@@ -25628,7 +25628,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G871" t="n">
-        <v>3.93225646018982</v>
+        <v>3.9322566986084</v>
       </c>
       <c r="H871" t="n">
         <v>7010</v>
@@ -25802,7 +25802,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G877" t="n">
-        <v>4.16997480392456</v>
+        <v>4.16997528076172</v>
       </c>
       <c r="H877" t="n">
         <v>14160</v>
@@ -25860,7 +25860,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G879" t="n">
-        <v>4.29873943328857</v>
+        <v>4.29873991012573</v>
       </c>
       <c r="H879" t="n">
         <v>31140</v>
@@ -25889,7 +25889,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G880" t="n">
-        <v>4.30864429473877</v>
+        <v>4.30864381790161</v>
       </c>
       <c r="H880" t="n">
         <v>45530</v>
@@ -25976,7 +25976,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G883" t="n">
-        <v>4.33835887908936</v>
+        <v>4.33835935592651</v>
       </c>
       <c r="H883" t="n">
         <v>5580</v>
@@ -26034,7 +26034,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G885" t="n">
-        <v>4.33835887908936</v>
+        <v>4.33835935592651</v>
       </c>
       <c r="H885" t="n">
         <v>3590</v>
@@ -26266,7 +26266,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G893" t="n">
-        <v>4.23930931091309</v>
+        <v>4.2393102645874</v>
       </c>
       <c r="H893" t="n">
         <v>42450</v>
@@ -26295,7 +26295,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G894" t="n">
-        <v>4.34826326370239</v>
+        <v>4.34826374053955</v>
       </c>
       <c r="H894" t="n">
         <v>9130</v>
@@ -26353,7 +26353,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G896" t="n">
-        <v>4.2194995880127</v>
+        <v>4.21950006484985</v>
       </c>
       <c r="H896" t="n">
         <v>6250</v>
@@ -26382,7 +26382,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G897" t="n">
-        <v>4.22940444946289</v>
+        <v>4.22940492630005</v>
       </c>
       <c r="H897" t="n">
         <v>3150</v>
@@ -26469,7 +26469,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G900" t="n">
-        <v>4.25911998748779</v>
+        <v>4.25911951065063</v>
       </c>
       <c r="H900" t="n">
         <v>2300</v>
@@ -26498,7 +26498,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G901" t="n">
-        <v>4.25911998748779</v>
+        <v>4.25911951065063</v>
       </c>
       <c r="H901" t="n">
         <v>7230</v>
@@ -26527,7 +26527,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G902" t="n">
-        <v>4.19968938827515</v>
+        <v>4.1996898651123</v>
       </c>
       <c r="H902" t="n">
         <v>2510</v>
@@ -26672,7 +26672,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G907" t="n">
-        <v>4.17987966537476</v>
+        <v>4.17988014221191</v>
       </c>
       <c r="H907" t="n">
         <v>9490</v>
@@ -26701,7 +26701,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G908" t="n">
-        <v>4.00159120559692</v>
+        <v>4.00159168243408</v>
       </c>
       <c r="H908" t="n">
         <v>14460</v>
@@ -26788,7 +26788,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G911" t="n">
-        <v>4.04121065139771</v>
+        <v>4.04121112823486</v>
       </c>
       <c r="H911" t="n">
         <v>1150</v>
@@ -26817,7 +26817,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G912" t="n">
-        <v>4.04121065139771</v>
+        <v>4.04121112823486</v>
       </c>
       <c r="H912" t="n">
         <v>0</v>
@@ -27194,7 +27194,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G925" t="n">
-        <v>3.64501404762268</v>
+        <v>3.6450138092041</v>
       </c>
       <c r="H925" t="n">
         <v>3530</v>
@@ -27339,7 +27339,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G930" t="n">
-        <v>3.66482353210449</v>
+        <v>3.66482377052307</v>
       </c>
       <c r="H930" t="n">
         <v>17040</v>
@@ -27629,7 +27629,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G940" t="n">
-        <v>3.77377772331238</v>
+        <v>3.77377796173096</v>
       </c>
       <c r="H940" t="n">
         <v>14330</v>
@@ -27687,7 +27687,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G942" t="n">
-        <v>3.74406337738037</v>
+        <v>3.74406313896179</v>
       </c>
       <c r="H942" t="n">
         <v>34380</v>
@@ -27774,7 +27774,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G945" t="n">
-        <v>3.90254211425781</v>
+        <v>3.90254187583923</v>
       </c>
       <c r="H945" t="n">
         <v>8060</v>
@@ -27803,7 +27803,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G946" t="n">
-        <v>4.04121065139771</v>
+        <v>4.04121112823486</v>
       </c>
       <c r="H946" t="n">
         <v>34120</v>
@@ -27861,7 +27861,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G948" t="n">
-        <v>4.10064029693604</v>
+        <v>4.10064077377319</v>
       </c>
       <c r="H948" t="n">
         <v>66300</v>
@@ -27890,7 +27890,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G949" t="n">
-        <v>4.17987966537476</v>
+        <v>4.17988014221191</v>
       </c>
       <c r="H949" t="n">
         <v>41290</v>
@@ -27919,7 +27919,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G950" t="n">
-        <v>4.10064029693604</v>
+        <v>4.10064077377319</v>
       </c>
       <c r="H950" t="n">
         <v>21380</v>
@@ -27977,7 +27977,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G952" t="n">
-        <v>3.89263725280762</v>
+        <v>3.89263701438904</v>
       </c>
       <c r="H952" t="n">
         <v>18360</v>
@@ -28006,7 +28006,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G953" t="n">
-        <v>4.03130578994751</v>
+        <v>4.03130626678467</v>
       </c>
       <c r="H953" t="n">
         <v>13820</v>
@@ -28064,7 +28064,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G955" t="n">
-        <v>4.03130578994751</v>
+        <v>4.03130626678467</v>
       </c>
       <c r="H955" t="n">
         <v>5030</v>
@@ -28093,7 +28093,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G956" t="n">
-        <v>3.99168658256531</v>
+        <v>3.99168634414673</v>
       </c>
       <c r="H956" t="n">
         <v>5970</v>
@@ -28151,7 +28151,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G958" t="n">
-        <v>3.97187662124634</v>
+        <v>3.97187685966492</v>
       </c>
       <c r="H958" t="n">
         <v>46140</v>
@@ -28267,7 +28267,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G962" t="n">
-        <v>3.86292219161987</v>
+        <v>3.86292243003845</v>
       </c>
       <c r="H962" t="n">
         <v>46304</v>
@@ -28296,7 +28296,7 @@
         <v>3.94400000572205</v>
       </c>
       <c r="G963" t="n">
-        <v>3.90650415420532</v>
+        <v>3.90650391578674</v>
       </c>
       <c r="H963" t="n">
         <v>21357</v>
@@ -28354,7 +28354,7 @@
         <v>3.97849988937378</v>
       </c>
       <c r="G965" t="n">
-        <v>3.94067597389221</v>
+        <v>3.94067573547363</v>
       </c>
       <c r="H965" t="n">
         <v>9527</v>
@@ -28412,7 +28412,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G967" t="n">
-        <v>3.95206665992737</v>
+        <v>3.95206642150879</v>
       </c>
       <c r="H967" t="n">
         <v>6708</v>
@@ -28441,7 +28441,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G968" t="n">
-        <v>3.90254211425781</v>
+        <v>3.90254187583923</v>
       </c>
       <c r="H968" t="n">
         <v>4990</v>
@@ -28499,7 +28499,7 @@
         <v>3.95050001144409</v>
       </c>
       <c r="G970" t="n">
-        <v>3.91294193267822</v>
+        <v>3.91294240951538</v>
       </c>
       <c r="H970" t="n">
         <v>6820</v>
@@ -28615,7 +28615,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G974" t="n">
-        <v>4.01149606704712</v>
+        <v>4.01149654388428</v>
       </c>
       <c r="H974" t="n">
         <v>41355</v>
@@ -28760,7 +28760,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G979" t="n">
-        <v>3.99168658256531</v>
+        <v>3.99168634414673</v>
       </c>
       <c r="H979" t="n">
         <v>7285</v>
@@ -28847,7 +28847,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G982" t="n">
-        <v>3.93225646018982</v>
+        <v>3.9322566986084</v>
       </c>
       <c r="H982" t="n">
         <v>2119</v>
@@ -28876,7 +28876,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G983" t="n">
-        <v>3.95206665992737</v>
+        <v>3.95206642150879</v>
       </c>
       <c r="H983" t="n">
         <v>1600</v>
@@ -29166,7 +29166,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G993" t="n">
-        <v>3.86292219161987</v>
+        <v>3.86292243003845</v>
       </c>
       <c r="H993" t="n">
         <v>19637</v>
@@ -29224,7 +29224,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G995" t="n">
-        <v>3.81339764595032</v>
+        <v>3.81339740753174</v>
       </c>
       <c r="H995" t="n">
         <v>7114</v>
@@ -29398,7 +29398,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1001" t="n">
-        <v>3.86292219161987</v>
+        <v>3.86292243003845</v>
       </c>
       <c r="H1001" t="n">
         <v>9557</v>
@@ -29427,7 +29427,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G1002" t="n">
-        <v>3.90254211425781</v>
+        <v>3.90254187583923</v>
       </c>
       <c r="H1002" t="n">
         <v>11713</v>
@@ -29775,7 +29775,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1014" t="n">
-        <v>3.66482353210449</v>
+        <v>3.66482377052307</v>
       </c>
       <c r="H1014" t="n">
         <v>19950</v>
@@ -29804,7 +29804,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1015" t="n">
-        <v>3.66482353210449</v>
+        <v>3.66482377052307</v>
       </c>
       <c r="H1015" t="n">
         <v>2750</v>
@@ -29833,7 +29833,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G1016" t="n">
-        <v>3.575679063797</v>
+        <v>3.57567930221558</v>
       </c>
       <c r="H1016" t="n">
         <v>16853</v>
@@ -29920,7 +29920,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1019" t="n">
-        <v>3.64501404762268</v>
+        <v>3.6450138092041</v>
       </c>
       <c r="H1019" t="n">
         <v>452</v>
@@ -29978,7 +29978,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1021" t="n">
-        <v>3.64501404762268</v>
+        <v>3.6450138092041</v>
       </c>
       <c r="H1021" t="n">
         <v>19653</v>
@@ -30036,7 +30036,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1023" t="n">
-        <v>3.66482353210449</v>
+        <v>3.66482377052307</v>
       </c>
       <c r="H1023" t="n">
         <v>846</v>
@@ -30065,7 +30065,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1024" t="n">
-        <v>3.61529922485352</v>
+        <v>3.61529898643494</v>
       </c>
       <c r="H1024" t="n">
         <v>8732</v>
@@ -30094,7 +30094,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G1025" t="n">
-        <v>3.58558392524719</v>
+        <v>3.58558416366577</v>
       </c>
       <c r="H1025" t="n">
         <v>2637</v>
@@ -30152,7 +30152,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1027" t="n">
-        <v>3.61529922485352</v>
+        <v>3.61529898643494</v>
       </c>
       <c r="H1027" t="n">
         <v>4783</v>
@@ -30181,7 +30181,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1028" t="n">
-        <v>3.61529922485352</v>
+        <v>3.61529898643494</v>
       </c>
       <c r="H1028" t="n">
         <v>4537</v>
@@ -30210,7 +30210,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1029" t="n">
-        <v>3.61529922485352</v>
+        <v>3.61529898643494</v>
       </c>
       <c r="H1029" t="n">
         <v>2959</v>
@@ -30268,7 +30268,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G1031" t="n">
-        <v>3.6549186706543</v>
+        <v>3.65491890907288</v>
       </c>
       <c r="H1031" t="n">
         <v>22295</v>
@@ -30297,7 +30297,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G1032" t="n">
-        <v>3.6549186706543</v>
+        <v>3.65491890907288</v>
       </c>
       <c r="H1032" t="n">
         <v>32428</v>
@@ -30413,7 +30413,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G1036" t="n">
-        <v>3.55586957931519</v>
+        <v>3.55586934089661</v>
       </c>
       <c r="H1036" t="n">
         <v>10707</v>
@@ -30442,7 +30442,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G1037" t="n">
-        <v>3.52615451812744</v>
+        <v>3.52615475654602</v>
       </c>
       <c r="H1037" t="n">
         <v>5035</v>
@@ -30471,7 +30471,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1038" t="n">
-        <v>3.48653483390808</v>
+        <v>3.48653507232666</v>
       </c>
       <c r="H1038" t="n">
         <v>11040</v>
@@ -30529,7 +30529,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1040" t="n">
-        <v>3.49643969535828</v>
+        <v>3.49643993377686</v>
       </c>
       <c r="H1040" t="n">
         <v>2950</v>
@@ -30558,7 +30558,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1041" t="n">
-        <v>3.49643969535828</v>
+        <v>3.49643993377686</v>
       </c>
       <c r="H1041" t="n">
         <v>1858</v>
@@ -30703,7 +30703,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G1046" t="n">
-        <v>3.52615451812744</v>
+        <v>3.52615475654602</v>
       </c>
       <c r="H1046" t="n">
         <v>4465</v>
@@ -30761,7 +30761,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1048" t="n">
-        <v>3.41720056533813</v>
+        <v>3.41720032691956</v>
       </c>
       <c r="H1048" t="n">
         <v>10706</v>
@@ -30790,7 +30790,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1049" t="n">
-        <v>3.43701028823853</v>
+        <v>3.4370105266571</v>
       </c>
       <c r="H1049" t="n">
         <v>4178</v>
@@ -30819,7 +30819,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1050" t="n">
-        <v>3.43701028823853</v>
+        <v>3.4370105266571</v>
       </c>
       <c r="H1050" t="n">
         <v>15067</v>
@@ -30877,7 +30877,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1052" t="n">
-        <v>3.49643969535828</v>
+        <v>3.49643993377686</v>
       </c>
       <c r="H1052" t="n">
         <v>3617</v>
@@ -30906,7 +30906,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G1053" t="n">
-        <v>3.55586957931519</v>
+        <v>3.55586934089661</v>
       </c>
       <c r="H1053" t="n">
         <v>13118</v>
@@ -31022,7 +31022,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1057" t="n">
-        <v>3.48653483390808</v>
+        <v>3.48653507232666</v>
       </c>
       <c r="H1057" t="n">
         <v>18503</v>
@@ -31138,7 +31138,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G1061" t="n">
-        <v>3.90254211425781</v>
+        <v>3.90254187583923</v>
       </c>
       <c r="H1061" t="n">
         <v>105352</v>
@@ -31225,7 +31225,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G1064" t="n">
-        <v>3.89263725280762</v>
+        <v>3.89263701438904</v>
       </c>
       <c r="H1064" t="n">
         <v>23123</v>
@@ -31283,7 +31283,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G1066" t="n">
-        <v>4.00159120559692</v>
+        <v>4.00159168243408</v>
       </c>
       <c r="H1066" t="n">
         <v>8852</v>
@@ -31312,7 +31312,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G1067" t="n">
-        <v>4.01149606704712</v>
+        <v>4.01149654388428</v>
       </c>
       <c r="H1067" t="n">
         <v>6753</v>
@@ -31370,7 +31370,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1069" t="n">
-        <v>3.86292219161987</v>
+        <v>3.86292243003845</v>
       </c>
       <c r="H1069" t="n">
         <v>9275</v>
@@ -31602,7 +31602,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G1077" t="n">
-        <v>3.74406337738037</v>
+        <v>3.74406313896179</v>
       </c>
       <c r="H1077" t="n">
         <v>2981</v>
@@ -31805,7 +31805,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1084" t="n">
-        <v>3.63471913337708</v>
+        <v>3.6347188949585</v>
       </c>
       <c r="H1084" t="n">
         <v>5698</v>
@@ -32153,7 +32153,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1096" t="n">
-        <v>3.63471913337708</v>
+        <v>3.6347188949585</v>
       </c>
       <c r="H1096" t="n">
         <v>1083</v>
@@ -32240,7 +32240,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1099" t="n">
-        <v>3.63471913337708</v>
+        <v>3.6347188949585</v>
       </c>
       <c r="H1099" t="n">
         <v>560</v>
@@ -32385,7 +32385,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G1104" t="n">
-        <v>3.55527114868164</v>
+        <v>3.55527138710022</v>
       </c>
       <c r="H1104" t="n">
         <v>4500</v>
@@ -32414,7 +32414,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1105" t="n">
-        <v>3.67444276809692</v>
+        <v>3.67444252967834</v>
       </c>
       <c r="H1105" t="n">
         <v>3701</v>
@@ -32617,7 +32617,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1112" t="n">
-        <v>3.50561666488647</v>
+        <v>3.50561690330505</v>
       </c>
       <c r="H1112" t="n">
         <v>5210</v>
@@ -32646,7 +32646,7 @@
         <v>3.5</v>
       </c>
       <c r="G1113" t="n">
-        <v>3.47582387924194</v>
+        <v>3.47582411766052</v>
       </c>
       <c r="H1113" t="n">
         <v>278</v>
@@ -32675,7 +32675,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1114" t="n">
-        <v>3.43610024452209</v>
+        <v>3.43610048294067</v>
       </c>
       <c r="H1114" t="n">
         <v>2139</v>
@@ -32704,7 +32704,7 @@
         <v>3.5</v>
       </c>
       <c r="G1115" t="n">
-        <v>3.47582387924194</v>
+        <v>3.47582411766052</v>
       </c>
       <c r="H1115" t="n">
         <v>6298</v>
@@ -32733,7 +32733,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1116" t="n">
-        <v>3.43610024452209</v>
+        <v>3.43610048294067</v>
       </c>
       <c r="H1116" t="n">
         <v>5346</v>
@@ -32791,7 +32791,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1118" t="n">
-        <v>3.51554751396179</v>
+        <v>3.51554775238037</v>
       </c>
       <c r="H1118" t="n">
         <v>6544</v>
@@ -32878,7 +32878,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1121" t="n">
-        <v>3.50561666488647</v>
+        <v>3.50561690330505</v>
       </c>
       <c r="H1121" t="n">
         <v>5808</v>
@@ -32907,7 +32907,7 @@
         <v>3.5</v>
       </c>
       <c r="G1122" t="n">
-        <v>3.47582387924194</v>
+        <v>3.47582411766052</v>
       </c>
       <c r="H1122" t="n">
         <v>1849</v>
@@ -32936,7 +32936,7 @@
         <v>3.5</v>
       </c>
       <c r="G1123" t="n">
-        <v>3.47582387924194</v>
+        <v>3.47582411766052</v>
       </c>
       <c r="H1123" t="n">
         <v>0</v>
@@ -32994,7 +32994,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1125" t="n">
-        <v>3.41623830795288</v>
+        <v>3.41623854637146</v>
       </c>
       <c r="H1125" t="n">
         <v>3101</v>
@@ -33023,7 +33023,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1126" t="n">
-        <v>3.41623830795288</v>
+        <v>3.41623854637146</v>
       </c>
       <c r="H1126" t="n">
         <v>4223</v>
@@ -33052,7 +33052,7 @@
         <v>3.5</v>
       </c>
       <c r="G1127" t="n">
-        <v>3.47582387924194</v>
+        <v>3.47582411766052</v>
       </c>
       <c r="H1127" t="n">
         <v>1000</v>
@@ -33081,7 +33081,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1128" t="n">
-        <v>3.51554751396179</v>
+        <v>3.51554775238037</v>
       </c>
       <c r="H1128" t="n">
         <v>14737</v>
@@ -33197,7 +33197,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1132" t="n">
-        <v>3.41623830795288</v>
+        <v>3.41623854637146</v>
       </c>
       <c r="H1132" t="n">
         <v>145</v>
@@ -33342,7 +33342,7 @@
         <v>3.5</v>
       </c>
       <c r="G1137" t="n">
-        <v>3.47582387924194</v>
+        <v>3.47582411766052</v>
       </c>
       <c r="H1137" t="n">
         <v>18829</v>
@@ -33429,7 +33429,7 @@
         <v>3.5</v>
       </c>
       <c r="G1140" t="n">
-        <v>3.47582387924194</v>
+        <v>3.47582411766052</v>
       </c>
       <c r="H1140" t="n">
         <v>14559</v>
@@ -33516,7 +33516,7 @@
         <v>3.5</v>
       </c>
       <c r="G1143" t="n">
-        <v>3.47582387924194</v>
+        <v>3.47582411766052</v>
       </c>
       <c r="H1143" t="n">
         <v>19008</v>
@@ -33574,7 +33574,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G1145" t="n">
-        <v>3.55527114868164</v>
+        <v>3.55527138710022</v>
       </c>
       <c r="H1145" t="n">
         <v>1675</v>
@@ -33603,7 +33603,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1146" t="n">
-        <v>3.67444276809692</v>
+        <v>3.67444252967834</v>
       </c>
       <c r="H1146" t="n">
         <v>42177</v>
@@ -33632,7 +33632,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1147" t="n">
-        <v>3.71416640281677</v>
+        <v>3.71416616439819</v>
       </c>
       <c r="H1147" t="n">
         <v>30404</v>
@@ -33719,7 +33719,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1150" t="n">
-        <v>3.67444276809692</v>
+        <v>3.67444252967834</v>
       </c>
       <c r="H1150" t="n">
         <v>11747</v>
@@ -33777,7 +33777,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1152" t="n">
-        <v>3.67444276809692</v>
+        <v>3.67444252967834</v>
       </c>
       <c r="H1152" t="n">
         <v>6905</v>
@@ -34038,7 +34038,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G1161" t="n">
-        <v>3.55527114868164</v>
+        <v>3.55527138710022</v>
       </c>
       <c r="H1161" t="n">
         <v>3572</v>
@@ -34270,7 +34270,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G1169" t="n">
-        <v>3.55527114868164</v>
+        <v>3.55527138710022</v>
       </c>
       <c r="H1169" t="n">
         <v>5878</v>
@@ -34299,7 +34299,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1170" t="n">
-        <v>3.63471913337708</v>
+        <v>3.6347188949585</v>
       </c>
       <c r="H1170" t="n">
         <v>17287</v>
@@ -34328,7 +34328,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1171" t="n">
-        <v>3.63471913337708</v>
+        <v>3.6347188949585</v>
       </c>
       <c r="H1171" t="n">
         <v>25873</v>
@@ -34589,7 +34589,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G1180" t="n">
-        <v>3.55527114868164</v>
+        <v>3.55527138710022</v>
       </c>
       <c r="H1180" t="n">
         <v>30518</v>
@@ -34647,7 +34647,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1182" t="n">
-        <v>3.50561666488647</v>
+        <v>3.50561690330505</v>
       </c>
       <c r="H1182" t="n">
         <v>20828</v>
@@ -34676,7 +34676,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1183" t="n">
-        <v>3.50561666488647</v>
+        <v>3.50561690330505</v>
       </c>
       <c r="H1183" t="n">
         <v>540</v>
@@ -34734,7 +34734,7 @@
         <v>3.5</v>
       </c>
       <c r="G1185" t="n">
-        <v>3.47582387924194</v>
+        <v>3.47582411766052</v>
       </c>
       <c r="H1185" t="n">
         <v>1141</v>
@@ -34821,7 +34821,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1188" t="n">
-        <v>3.41623830795288</v>
+        <v>3.41623854637146</v>
       </c>
       <c r="H1188" t="n">
         <v>16937</v>
@@ -34995,7 +34995,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G1194" t="n">
-        <v>2.93955397605896</v>
+        <v>2.93955421447754</v>
       </c>
       <c r="H1194" t="n">
         <v>2442</v>
@@ -35372,7 +35372,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G1207" t="n">
-        <v>2.76079726219177</v>
+        <v>2.76079750061035</v>
       </c>
       <c r="H1207" t="n">
         <v>85019</v>
@@ -35401,7 +35401,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G1208" t="n">
-        <v>2.70121169090271</v>
+        <v>2.70121192932129</v>
       </c>
       <c r="H1208" t="n">
         <v>36383</v>
@@ -35923,7 +35923,7 @@
         <v>3</v>
       </c>
       <c r="G1226" t="n">
-        <v>2.97927761077881</v>
+        <v>2.97927784919739</v>
       </c>
       <c r="H1226" t="n">
         <v>103705</v>
@@ -35981,7 +35981,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G1228" t="n">
-        <v>2.93955397605896</v>
+        <v>2.93955421447754</v>
       </c>
       <c r="H1228" t="n">
         <v>12630</v>
@@ -36039,7 +36039,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G1230" t="n">
-        <v>2.93955397605896</v>
+        <v>2.93955421447754</v>
       </c>
       <c r="H1230" t="n">
         <v>12379</v>
@@ -36068,7 +36068,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G1231" t="n">
-        <v>2.93955397605896</v>
+        <v>2.93955421447754</v>
       </c>
       <c r="H1231" t="n">
         <v>21752</v>
@@ -36097,7 +36097,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G1232" t="n">
-        <v>2.93955397605896</v>
+        <v>2.93955421447754</v>
       </c>
       <c r="H1232" t="n">
         <v>51075</v>
@@ -36184,7 +36184,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1235" t="n">
-        <v>2.8799684047699</v>
+        <v>2.87996864318848</v>
       </c>
       <c r="H1235" t="n">
         <v>33074</v>
@@ -36503,7 +36503,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G1246" t="n">
-        <v>2.58204054832458</v>
+        <v>2.58204078674316</v>
       </c>
       <c r="H1246" t="n">
         <v>34890</v>
@@ -36764,7 +36764,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G1255" t="n">
-        <v>2.66148805618286</v>
+        <v>2.66148829460144</v>
       </c>
       <c r="H1255" t="n">
         <v>14426</v>
@@ -36938,7 +36938,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1261" t="n">
-        <v>2.8799684047699</v>
+        <v>2.87996864318848</v>
       </c>
       <c r="H1261" t="n">
         <v>23099</v>
@@ -36996,7 +36996,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G1263" t="n">
-        <v>2.84024453163147</v>
+        <v>2.84024477005005</v>
       </c>
       <c r="H1263" t="n">
         <v>24196</v>
@@ -37025,7 +37025,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1264" t="n">
-        <v>2.8799684047699</v>
+        <v>2.87996864318848</v>
       </c>
       <c r="H1264" t="n">
         <v>44232</v>
@@ -37199,7 +37199,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G1270" t="n">
-        <v>2.76079726219177</v>
+        <v>2.76079750061035</v>
       </c>
       <c r="H1270" t="n">
         <v>16790</v>
@@ -37257,7 +37257,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G1272" t="n">
-        <v>2.76079726219177</v>
+        <v>2.76079750061035</v>
       </c>
       <c r="H1272" t="n">
         <v>7158</v>
@@ -37315,7 +37315,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G1274" t="n">
-        <v>2.84024453163147</v>
+        <v>2.84024477005005</v>
       </c>
       <c r="H1274" t="n">
         <v>4036</v>
@@ -37518,7 +37518,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G1281" t="n">
-        <v>2.84024453163147</v>
+        <v>2.84024477005005</v>
       </c>
       <c r="H1281" t="n">
         <v>4934</v>
@@ -37692,7 +37692,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G1287" t="n">
-        <v>2.66148805618286</v>
+        <v>2.66148829460144</v>
       </c>
       <c r="H1287" t="n">
         <v>11470</v>
@@ -37721,7 +37721,7 @@
         <v>2.5</v>
       </c>
       <c r="G1288" t="n">
-        <v>2.48273134231567</v>
+        <v>2.48273158073425</v>
       </c>
       <c r="H1288" t="n">
         <v>44014</v>
@@ -37895,7 +37895,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G1294" t="n">
-        <v>2.62176442146301</v>
+        <v>2.62176465988159</v>
       </c>
       <c r="H1294" t="n">
         <v>12855</v>
@@ -38156,7 +38156,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1303" t="n">
-        <v>2.8799684047699</v>
+        <v>2.87996864318848</v>
       </c>
       <c r="H1303" t="n">
         <v>10021</v>
@@ -38301,7 +38301,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G1308" t="n">
-        <v>2.84024453163147</v>
+        <v>2.84024477005005</v>
       </c>
       <c r="H1308" t="n">
         <v>4956</v>
@@ -38359,7 +38359,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G1310" t="n">
-        <v>2.80052089691162</v>
+        <v>2.8005211353302</v>
       </c>
       <c r="H1310" t="n">
         <v>28928</v>
@@ -38475,7 +38475,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G1314" t="n">
-        <v>2.93955397605896</v>
+        <v>2.93955421447754</v>
       </c>
       <c r="H1314" t="n">
         <v>43179</v>
@@ -49066,6 +49066,35 @@
         <v>5756</v>
       </c>
       <c r="I1679" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1680">
+      <c r="A1680" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1680" s="1" t="n">
+        <v>46317.2916666667</v>
+      </c>
+      <c r="C1680" t="n">
+        <v>3.0699999332428</v>
+      </c>
+      <c r="D1680" t="n">
+        <v>3.17000007629395</v>
+      </c>
+      <c r="E1680" t="n">
+        <v>3.05999994277954</v>
+      </c>
+      <c r="F1680" t="n">
+        <v>3.14000010490417</v>
+      </c>
+      <c r="G1680" t="n">
+        <v>3.14000010490417</v>
+      </c>
+      <c r="H1680" t="n">
+        <v>107846</v>
+      </c>
+      <c r="I1680" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/UD.MI.xlsx
+++ b/data/UD.MI.xlsx
@@ -427,7 +427,7 @@
         <v>1.5</v>
       </c>
       <c r="G2" t="n">
-        <v>1.47885513305664</v>
+        <v>1.47885501384735</v>
       </c>
       <c r="H2" t="n">
         <v>159000</v>
@@ -514,7 +514,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G5" t="n">
-        <v>1.50843214988708</v>
+        <v>1.50843226909637</v>
       </c>
       <c r="H5" t="n">
         <v>88000</v>
@@ -543,7 +543,7 @@
         <v>1.56500005722046</v>
       </c>
       <c r="G6" t="n">
-        <v>1.5429390668869</v>
+        <v>1.54293882846832</v>
       </c>
       <c r="H6" t="n">
         <v>55000</v>
@@ -630,7 +630,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G9" t="n">
-        <v>1.55772745609283</v>
+        <v>1.55772757530212</v>
       </c>
       <c r="H9" t="n">
         <v>13000</v>
@@ -688,7 +688,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G11" t="n">
-        <v>1.56265711784363</v>
+        <v>1.56265699863434</v>
       </c>
       <c r="H11" t="n">
         <v>16000</v>
@@ -746,7 +746,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G13" t="n">
-        <v>1.55772745609283</v>
+        <v>1.55772757530212</v>
       </c>
       <c r="H13" t="n">
         <v>2000</v>
@@ -862,7 +862,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G17" t="n">
-        <v>1.66617691516876</v>
+        <v>1.66617703437805</v>
       </c>
       <c r="H17" t="n">
         <v>14000</v>
@@ -891,7 +891,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G18" t="n">
-        <v>1.67603588104248</v>
+        <v>1.67603600025177</v>
       </c>
       <c r="H18" t="n">
         <v>36000</v>
@@ -920,7 +920,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G19" t="n">
-        <v>1.67603588104248</v>
+        <v>1.67603600025177</v>
       </c>
       <c r="H19" t="n">
         <v>18000</v>
@@ -1094,7 +1094,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G25" t="n">
-        <v>1.58730459213257</v>
+        <v>1.58730471134186</v>
       </c>
       <c r="H25" t="n">
         <v>22000</v>
@@ -1268,7 +1268,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G31" t="n">
-        <v>1.63659965991974</v>
+        <v>1.63659977912903</v>
       </c>
       <c r="H31" t="n">
         <v>32000</v>
@@ -1326,7 +1326,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G33" t="n">
-        <v>1.61688160896301</v>
+        <v>1.6168817281723</v>
       </c>
       <c r="H33" t="n">
         <v>1000</v>
@@ -1442,7 +1442,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G37" t="n">
-        <v>1.70561301708221</v>
+        <v>1.70561289787292</v>
       </c>
       <c r="H37" t="n">
         <v>16000</v>
@@ -1471,7 +1471,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G38" t="n">
-        <v>1.70561301708221</v>
+        <v>1.70561289787292</v>
       </c>
       <c r="H38" t="n">
         <v>2000</v>
@@ -1500,7 +1500,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G39" t="n">
-        <v>1.67110645771027</v>
+        <v>1.67110633850098</v>
       </c>
       <c r="H39" t="n">
         <v>3000</v>
@@ -1529,7 +1529,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G40" t="n">
-        <v>1.69575381278992</v>
+        <v>1.69575393199921</v>
       </c>
       <c r="H40" t="n">
         <v>7000</v>
@@ -1558,7 +1558,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G41" t="n">
-        <v>1.68589496612549</v>
+        <v>1.68589508533478</v>
       </c>
       <c r="H41" t="n">
         <v>14000</v>
@@ -1674,7 +1674,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G45" t="n">
-        <v>1.66617691516876</v>
+        <v>1.66617703437805</v>
       </c>
       <c r="H45" t="n">
         <v>1000</v>
@@ -1703,7 +1703,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G46" t="n">
-        <v>1.67603588104248</v>
+        <v>1.67603600025177</v>
       </c>
       <c r="H46" t="n">
         <v>12000</v>
@@ -1819,7 +1819,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G50" t="n">
-        <v>1.74997866153717</v>
+        <v>1.74997878074646</v>
       </c>
       <c r="H50" t="n">
         <v>20000</v>
@@ -1877,7 +1877,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G52" t="n">
-        <v>1.74011957645416</v>
+        <v>1.74011969566345</v>
       </c>
       <c r="H52" t="n">
         <v>6000</v>
@@ -1906,7 +1906,7 @@
         <v>1.74500000476837</v>
       </c>
       <c r="G53" t="n">
-        <v>1.72040164470673</v>
+        <v>1.72040152549744</v>
       </c>
       <c r="H53" t="n">
         <v>7000</v>
@@ -1993,7 +1993,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G56" t="n">
-        <v>1.69575381278992</v>
+        <v>1.69575393199921</v>
       </c>
       <c r="H56" t="n">
         <v>8000</v>
@@ -2022,7 +2022,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G57" t="n">
-        <v>1.67603588104248</v>
+        <v>1.67603600025177</v>
       </c>
       <c r="H57" t="n">
         <v>30000</v>
@@ -2283,7 +2283,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G66" t="n">
-        <v>1.67603588104248</v>
+        <v>1.67603600025177</v>
       </c>
       <c r="H66" t="n">
         <v>3000</v>
@@ -2312,7 +2312,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G67" t="n">
-        <v>1.66617691516876</v>
+        <v>1.66617703437805</v>
       </c>
       <c r="H67" t="n">
         <v>10000</v>
@@ -2341,7 +2341,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G68" t="n">
-        <v>1.68589496612549</v>
+        <v>1.68589508533478</v>
       </c>
       <c r="H68" t="n">
         <v>7000</v>
@@ -2573,7 +2573,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G76" t="n">
-        <v>1.67110645771027</v>
+        <v>1.67110633850098</v>
       </c>
       <c r="H76" t="n">
         <v>2000</v>
@@ -2602,7 +2602,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G77" t="n">
-        <v>1.68589496612549</v>
+        <v>1.68589508533478</v>
       </c>
       <c r="H77" t="n">
         <v>3000</v>
@@ -2660,7 +2660,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G79" t="n">
-        <v>1.67603588104248</v>
+        <v>1.67603600025177</v>
       </c>
       <c r="H79" t="n">
         <v>16000</v>
@@ -2689,7 +2689,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G80" t="n">
-        <v>1.67603588104248</v>
+        <v>1.67603600025177</v>
       </c>
       <c r="H80" t="n">
         <v>0</v>
@@ -2718,7 +2718,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G81" t="n">
-        <v>1.67603588104248</v>
+        <v>1.67603600025177</v>
       </c>
       <c r="H81" t="n">
         <v>0</v>
@@ -2805,7 +2805,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G84" t="n">
-        <v>1.63659965991974</v>
+        <v>1.63659977912903</v>
       </c>
       <c r="H84" t="n">
         <v>8000</v>
@@ -3124,7 +3124,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G95" t="n">
-        <v>1.58730459213257</v>
+        <v>1.58730471134186</v>
       </c>
       <c r="H95" t="n">
         <v>11000</v>
@@ -3182,7 +3182,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G97" t="n">
-        <v>1.58730459213257</v>
+        <v>1.58730471134186</v>
       </c>
       <c r="H97" t="n">
         <v>31000</v>
@@ -3211,7 +3211,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G98" t="n">
-        <v>1.58730459213257</v>
+        <v>1.58730471134186</v>
       </c>
       <c r="H98" t="n">
         <v>11000</v>
@@ -3356,7 +3356,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G103" t="n">
-        <v>1.63659965991974</v>
+        <v>1.63659977912903</v>
       </c>
       <c r="H103" t="n">
         <v>35000</v>
@@ -3385,7 +3385,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G104" t="n">
-        <v>1.63659965991974</v>
+        <v>1.63659977912903</v>
       </c>
       <c r="H104" t="n">
         <v>14000</v>
@@ -3414,7 +3414,7 @@
         <v>1.63499999046326</v>
       </c>
       <c r="G105" t="n">
-        <v>1.61195206642151</v>
+        <v>1.6119521856308</v>
       </c>
       <c r="H105" t="n">
         <v>26000</v>
@@ -3530,7 +3530,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G109" t="n">
-        <v>1.66617691516876</v>
+        <v>1.66617703437805</v>
       </c>
       <c r="H109" t="n">
         <v>15000</v>
@@ -3559,7 +3559,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G110" t="n">
-        <v>1.67603588104248</v>
+        <v>1.67603600025177</v>
       </c>
       <c r="H110" t="n">
         <v>26000</v>
@@ -3588,7 +3588,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G111" t="n">
-        <v>1.67603588104248</v>
+        <v>1.67603600025177</v>
       </c>
       <c r="H111" t="n">
         <v>53000</v>
@@ -3617,7 +3617,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G112" t="n">
-        <v>1.67603588104248</v>
+        <v>1.67603600025177</v>
       </c>
       <c r="H112" t="n">
         <v>10000</v>
@@ -3646,7 +3646,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G113" t="n">
-        <v>1.67603588104248</v>
+        <v>1.67603600025177</v>
       </c>
       <c r="H113" t="n">
         <v>6000</v>
@@ -3675,7 +3675,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G114" t="n">
-        <v>1.67603588104248</v>
+        <v>1.67603600025177</v>
       </c>
       <c r="H114" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G115" t="n">
-        <v>1.67603588104248</v>
+        <v>1.67603600025177</v>
       </c>
       <c r="H115" t="n">
         <v>22000</v>
@@ -3762,7 +3762,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G117" t="n">
-        <v>1.68589496612549</v>
+        <v>1.68589508533478</v>
       </c>
       <c r="H117" t="n">
         <v>22000</v>
@@ -3791,7 +3791,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G118" t="n">
-        <v>1.68589496612549</v>
+        <v>1.68589508533478</v>
       </c>
       <c r="H118" t="n">
         <v>0</v>
@@ -3965,7 +3965,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G124" t="n">
-        <v>1.85349833965302</v>
+        <v>1.8534984588623</v>
       </c>
       <c r="H124" t="n">
         <v>32000</v>
@@ -4023,7 +4023,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G126" t="n">
-        <v>1.83378052711487</v>
+        <v>1.83378040790558</v>
       </c>
       <c r="H126" t="n">
         <v>15000</v>
@@ -4052,7 +4052,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G127" t="n">
-        <v>1.82392144203186</v>
+        <v>1.82392132282257</v>
       </c>
       <c r="H127" t="n">
         <v>7000</v>
@@ -4081,7 +4081,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G128" t="n">
-        <v>1.82392144203186</v>
+        <v>1.82392132282257</v>
       </c>
       <c r="H128" t="n">
         <v>0</v>
@@ -4110,7 +4110,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G129" t="n">
-        <v>1.82392144203186</v>
+        <v>1.82392132282257</v>
       </c>
       <c r="H129" t="n">
         <v>0</v>
@@ -4168,7 +4168,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G131" t="n">
-        <v>1.83378052711487</v>
+        <v>1.83378040790558</v>
       </c>
       <c r="H131" t="n">
         <v>1000</v>
@@ -4226,7 +4226,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G133" t="n">
-        <v>1.85349833965302</v>
+        <v>1.8534984588623</v>
       </c>
       <c r="H133" t="n">
         <v>6000</v>
@@ -4255,7 +4255,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G134" t="n">
-        <v>1.85349833965302</v>
+        <v>1.8534984588623</v>
       </c>
       <c r="H134" t="n">
         <v>0</v>
@@ -4284,7 +4284,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G135" t="n">
-        <v>1.85349833965302</v>
+        <v>1.8534984588623</v>
       </c>
       <c r="H135" t="n">
         <v>3000</v>
@@ -4458,7 +4458,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G141" t="n">
-        <v>1.82392144203186</v>
+        <v>1.82392132282257</v>
       </c>
       <c r="H141" t="n">
         <v>12000</v>
@@ -4487,7 +4487,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G142" t="n">
-        <v>1.82392144203186</v>
+        <v>1.82392132282257</v>
       </c>
       <c r="H142" t="n">
         <v>13000</v>
@@ -4516,7 +4516,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G143" t="n">
-        <v>1.79927396774292</v>
+        <v>1.79927384853363</v>
       </c>
       <c r="H143" t="n">
         <v>10000</v>
@@ -4748,7 +4748,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G151" t="n">
-        <v>1.74011957645416</v>
+        <v>1.74011969566345</v>
       </c>
       <c r="H151" t="n">
         <v>30000</v>
@@ -4864,7 +4864,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G155" t="n">
-        <v>1.82392144203186</v>
+        <v>1.82392132282257</v>
       </c>
       <c r="H155" t="n">
         <v>13000</v>
@@ -4893,7 +4893,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G156" t="n">
-        <v>1.82392144203186</v>
+        <v>1.82392132282257</v>
       </c>
       <c r="H156" t="n">
         <v>0</v>
@@ -4951,7 +4951,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G158" t="n">
-        <v>1.83378052711487</v>
+        <v>1.83378040790558</v>
       </c>
       <c r="H158" t="n">
         <v>7000</v>
@@ -5241,7 +5241,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G168" t="n">
-        <v>1.74997866153717</v>
+        <v>1.74997878074646</v>
       </c>
       <c r="H168" t="n">
         <v>2000</v>
@@ -5357,7 +5357,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G172" t="n">
-        <v>1.81406259536743</v>
+        <v>1.81406247615814</v>
       </c>
       <c r="H172" t="n">
         <v>3000</v>
@@ -5705,7 +5705,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G184" t="n">
-        <v>2.01124310493469</v>
+        <v>2.01124286651611</v>
       </c>
       <c r="H184" t="n">
         <v>3000</v>
@@ -5821,7 +5821,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G188" t="n">
-        <v>2.01124310493469</v>
+        <v>2.01124286651611</v>
       </c>
       <c r="H188" t="n">
         <v>4000</v>
@@ -5850,7 +5850,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G189" t="n">
-        <v>2.01124310493469</v>
+        <v>2.01124286651611</v>
       </c>
       <c r="H189" t="n">
         <v>0</v>
@@ -5879,7 +5879,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G190" t="n">
-        <v>1.91758227348328</v>
+        <v>1.91758239269257</v>
       </c>
       <c r="H190" t="n">
         <v>76000</v>
@@ -5995,7 +5995,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G194" t="n">
-        <v>1.92251181602478</v>
+        <v>1.92251169681549</v>
       </c>
       <c r="H194" t="n">
         <v>6000</v>
@@ -6140,7 +6140,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G199" t="n">
-        <v>1.91758227348328</v>
+        <v>1.91758239269257</v>
       </c>
       <c r="H199" t="n">
         <v>3000</v>
@@ -6169,7 +6169,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G200" t="n">
-        <v>1.92251181602478</v>
+        <v>1.92251169681549</v>
       </c>
       <c r="H200" t="n">
         <v>18000</v>
@@ -6285,7 +6285,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G204" t="n">
-        <v>1.92251181602478</v>
+        <v>1.92251169681549</v>
       </c>
       <c r="H204" t="n">
         <v>8000</v>
@@ -6430,7 +6430,7 @@
         <v>1.9650000333786</v>
       </c>
       <c r="G209" t="n">
-        <v>1.93730020523071</v>
+        <v>1.93730032444</v>
       </c>
       <c r="H209" t="n">
         <v>11000</v>
@@ -6488,7 +6488,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G211" t="n">
-        <v>1.94715929031372</v>
+        <v>1.94715940952301</v>
       </c>
       <c r="H211" t="n">
         <v>7000</v>
@@ -6517,7 +6517,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G212" t="n">
-        <v>1.94222974777222</v>
+        <v>1.94222986698151</v>
       </c>
       <c r="H212" t="n">
         <v>31000</v>
@@ -6546,7 +6546,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G213" t="n">
-        <v>1.92251181602478</v>
+        <v>1.92251169681549</v>
       </c>
       <c r="H213" t="n">
         <v>20000</v>
@@ -6575,7 +6575,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G214" t="n">
-        <v>1.92251181602478</v>
+        <v>1.92251169681549</v>
       </c>
       <c r="H214" t="n">
         <v>1000</v>
@@ -6778,7 +6778,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G221" t="n">
-        <v>1.92251181602478</v>
+        <v>1.92251169681549</v>
       </c>
       <c r="H221" t="n">
         <v>2000</v>
@@ -6807,7 +6807,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G222" t="n">
-        <v>1.92251181602478</v>
+        <v>1.92251169681549</v>
       </c>
       <c r="H222" t="n">
         <v>0</v>
@@ -6836,7 +6836,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G223" t="n">
-        <v>1.92251181602478</v>
+        <v>1.92251169681549</v>
       </c>
       <c r="H223" t="n">
         <v>0</v>
@@ -6865,7 +6865,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G224" t="n">
-        <v>1.92251181602478</v>
+        <v>1.92251169681549</v>
       </c>
       <c r="H224" t="n">
         <v>3000</v>
@@ -6894,7 +6894,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G225" t="n">
-        <v>1.94222974777222</v>
+        <v>1.94222986698151</v>
       </c>
       <c r="H225" t="n">
         <v>5000</v>
@@ -7010,7 +7010,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G229" t="n">
-        <v>2.08025646209717</v>
+        <v>2.08025622367859</v>
       </c>
       <c r="H229" t="n">
         <v>20000</v>
@@ -7068,7 +7068,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G231" t="n">
-        <v>2.22814130783081</v>
+        <v>2.22814178466797</v>
       </c>
       <c r="H231" t="n">
         <v>86000</v>
@@ -7126,7 +7126,7 @@
         <v>2.25</v>
       </c>
       <c r="G233" t="n">
-        <v>2.21828246116638</v>
+        <v>2.21828269958496</v>
       </c>
       <c r="H233" t="n">
         <v>47000</v>
@@ -7184,7 +7184,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G235" t="n">
-        <v>2.14926981925964</v>
+        <v>2.14926958084106</v>
       </c>
       <c r="H235" t="n">
         <v>11000</v>
@@ -7300,7 +7300,7 @@
         <v>2.25</v>
       </c>
       <c r="G239" t="n">
-        <v>2.21828246116638</v>
+        <v>2.21828269958496</v>
       </c>
       <c r="H239" t="n">
         <v>19000</v>
@@ -7358,7 +7358,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G241" t="n">
-        <v>2.22814130783081</v>
+        <v>2.22814178466797</v>
       </c>
       <c r="H241" t="n">
         <v>5000</v>
@@ -7503,7 +7503,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G246" t="n">
-        <v>2.28729581832886</v>
+        <v>2.28729605674744</v>
       </c>
       <c r="H246" t="n">
         <v>12000</v>
@@ -7532,7 +7532,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G247" t="n">
-        <v>2.28729581832886</v>
+        <v>2.28729605674744</v>
       </c>
       <c r="H247" t="n">
         <v>2000</v>
@@ -7706,7 +7706,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G253" t="n">
-        <v>2.40560436248779</v>
+        <v>2.40560460090637</v>
       </c>
       <c r="H253" t="n">
         <v>26000</v>
@@ -7909,7 +7909,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G260" t="n">
-        <v>2.74081182479858</v>
+        <v>2.74081158638</v>
       </c>
       <c r="H260" t="n">
         <v>51000</v>
@@ -7967,7 +7967,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G262" t="n">
-        <v>2.78024768829346</v>
+        <v>2.78024744987488</v>
       </c>
       <c r="H262" t="n">
         <v>23000</v>
@@ -7996,7 +7996,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G263" t="n">
-        <v>2.9774284362793</v>
+        <v>2.97742819786072</v>
       </c>
       <c r="H263" t="n">
         <v>41000</v>
@@ -8054,7 +8054,7 @@
         <v>3</v>
       </c>
       <c r="G265" t="n">
-        <v>2.95771026611328</v>
+        <v>2.9577100276947</v>
       </c>
       <c r="H265" t="n">
         <v>85000</v>
@@ -8257,7 +8257,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G272" t="n">
-        <v>2.99714660644531</v>
+        <v>2.99714636802673</v>
       </c>
       <c r="H272" t="n">
         <v>21000</v>
@@ -8402,7 +8402,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G277" t="n">
-        <v>3.17460918426514</v>
+        <v>3.17460942268372</v>
       </c>
       <c r="H277" t="n">
         <v>36000</v>
@@ -8431,7 +8431,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G278" t="n">
-        <v>3.18446826934814</v>
+        <v>3.18446803092957</v>
       </c>
       <c r="H278" t="n">
         <v>19000</v>
@@ -8518,7 +8518,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G281" t="n">
-        <v>3.18446826934814</v>
+        <v>3.18446803092957</v>
       </c>
       <c r="H281" t="n">
         <v>10000</v>
@@ -8634,7 +8634,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G285" t="n">
-        <v>3.35207176208496</v>
+        <v>3.35207200050354</v>
       </c>
       <c r="H285" t="n">
         <v>25000</v>
@@ -8663,7 +8663,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G286" t="n">
-        <v>3.49995732307434</v>
+        <v>3.49995756149292</v>
       </c>
       <c r="H286" t="n">
         <v>86000</v>
@@ -8837,7 +8837,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G292" t="n">
-        <v>3.64784288406372</v>
+        <v>3.64784264564514</v>
       </c>
       <c r="H292" t="n">
         <v>5000</v>
@@ -8866,7 +8866,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G293" t="n">
-        <v>3.64784288406372</v>
+        <v>3.64784264564514</v>
       </c>
       <c r="H293" t="n">
         <v>16000</v>
@@ -8982,7 +8982,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G297" t="n">
-        <v>3.55911135673523</v>
+        <v>3.55911159515381</v>
       </c>
       <c r="H297" t="n">
         <v>30000</v>
@@ -9040,7 +9040,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G299" t="n">
-        <v>3.49995732307434</v>
+        <v>3.49995756149292</v>
       </c>
       <c r="H299" t="n">
         <v>12000</v>
@@ -9069,7 +9069,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G300" t="n">
-        <v>3.48023915290833</v>
+        <v>3.4802393913269</v>
       </c>
       <c r="H300" t="n">
         <v>15000</v>
@@ -9127,7 +9127,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G302" t="n">
-        <v>3.49995732307434</v>
+        <v>3.49995756149292</v>
       </c>
       <c r="H302" t="n">
         <v>12000</v>
@@ -9272,7 +9272,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G307" t="n">
-        <v>3.97319078445435</v>
+        <v>3.9731912612915</v>
       </c>
       <c r="H307" t="n">
         <v>45000</v>
@@ -9301,7 +9301,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G308" t="n">
-        <v>4.26896142959595</v>
+        <v>4.26896190643311</v>
       </c>
       <c r="H308" t="n">
         <v>57000</v>
@@ -9388,7 +9388,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G311" t="n">
-        <v>4.14079427719116</v>
+        <v>4.14079475402832</v>
       </c>
       <c r="H311" t="n">
         <v>40000</v>
@@ -9417,7 +9417,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G312" t="n">
-        <v>3.9929096698761</v>
+        <v>3.99290919303894</v>
       </c>
       <c r="H312" t="n">
         <v>51000</v>
@@ -9475,7 +9475,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G314" t="n">
-        <v>4.05206346511841</v>
+        <v>4.05206394195557</v>
       </c>
       <c r="H314" t="n">
         <v>6000</v>
@@ -9562,7 +9562,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G317" t="n">
-        <v>4.14079427719116</v>
+        <v>4.14079475402832</v>
       </c>
       <c r="H317" t="n">
         <v>21000</v>
@@ -9591,7 +9591,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G318" t="n">
-        <v>4.17037153244019</v>
+        <v>4.17037200927734</v>
       </c>
       <c r="H318" t="n">
         <v>10000</v>
@@ -9736,7 +9736,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G323" t="n">
-        <v>4.18023061752319</v>
+        <v>4.18023014068604</v>
       </c>
       <c r="H323" t="n">
         <v>2000</v>
@@ -9765,7 +9765,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G324" t="n">
-        <v>4.18023061752319</v>
+        <v>4.18023014068604</v>
       </c>
       <c r="H324" t="n">
         <v>0</v>
@@ -9852,7 +9852,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G327" t="n">
-        <v>4.16051292419434</v>
+        <v>4.16051244735718</v>
       </c>
       <c r="H327" t="n">
         <v>7000</v>
@@ -9881,7 +9881,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G328" t="n">
-        <v>4.16051292419434</v>
+        <v>4.16051244735718</v>
       </c>
       <c r="H328" t="n">
         <v>2000</v>
@@ -9910,7 +9910,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G329" t="n">
-        <v>4.02248620986938</v>
+        <v>4.02248573303223</v>
       </c>
       <c r="H329" t="n">
         <v>5000</v>
@@ -10026,7 +10026,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G333" t="n">
-        <v>4.16051292419434</v>
+        <v>4.16051244735718</v>
       </c>
       <c r="H333" t="n">
         <v>5000</v>
@@ -10055,7 +10055,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G334" t="n">
-        <v>4.16051292419434</v>
+        <v>4.16051244735718</v>
       </c>
       <c r="H334" t="n">
         <v>14000</v>
@@ -10084,7 +10084,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G335" t="n">
-        <v>4.17037153244019</v>
+        <v>4.17037200927734</v>
       </c>
       <c r="H335" t="n">
         <v>3000</v>
@@ -10171,7 +10171,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G338" t="n">
-        <v>4.16051292419434</v>
+        <v>4.16051244735718</v>
       </c>
       <c r="H338" t="n">
         <v>5000</v>
@@ -10200,7 +10200,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G339" t="n">
-        <v>4.16051292419434</v>
+        <v>4.16051244735718</v>
       </c>
       <c r="H339" t="n">
         <v>0</v>
@@ -10229,7 +10229,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G340" t="n">
-        <v>4.14079427719116</v>
+        <v>4.14079475402832</v>
       </c>
       <c r="H340" t="n">
         <v>16000</v>
@@ -10258,7 +10258,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G341" t="n">
-        <v>4.14079427719116</v>
+        <v>4.14079475402832</v>
       </c>
       <c r="H341" t="n">
         <v>15500</v>
@@ -10316,7 +10316,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G343" t="n">
-        <v>4.14079427719116</v>
+        <v>4.14079475402832</v>
       </c>
       <c r="H343" t="n">
         <v>3500</v>
@@ -10345,7 +10345,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G344" t="n">
-        <v>4.11121702194214</v>
+        <v>4.1112174987793</v>
       </c>
       <c r="H344" t="n">
         <v>1000</v>
@@ -10432,7 +10432,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G347" t="n">
-        <v>4.02248620986938</v>
+        <v>4.02248573303223</v>
       </c>
       <c r="H347" t="n">
         <v>3000</v>
@@ -10461,7 +10461,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G348" t="n">
-        <v>4.02248620986938</v>
+        <v>4.02248573303223</v>
       </c>
       <c r="H348" t="n">
         <v>16500</v>
@@ -10490,7 +10490,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G349" t="n">
-        <v>4.21966743469238</v>
+        <v>4.21966648101807</v>
       </c>
       <c r="H349" t="n">
         <v>21000</v>
@@ -10693,7 +10693,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G356" t="n">
-        <v>4.14079427719116</v>
+        <v>4.14079475402832</v>
       </c>
       <c r="H356" t="n">
         <v>8500</v>
@@ -10722,7 +10722,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G357" t="n">
-        <v>4.05206346511841</v>
+        <v>4.05206394195557</v>
       </c>
       <c r="H357" t="n">
         <v>10000</v>
@@ -10780,7 +10780,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G359" t="n">
-        <v>4.21966743469238</v>
+        <v>4.21966648101807</v>
       </c>
       <c r="H359" t="n">
         <v>14500</v>
@@ -10983,7 +10983,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G366" t="n">
-        <v>4.14079427719116</v>
+        <v>4.14079475402832</v>
       </c>
       <c r="H366" t="n">
         <v>1500</v>
@@ -11012,7 +11012,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G367" t="n">
-        <v>4.14079427719116</v>
+        <v>4.14079475402832</v>
       </c>
       <c r="H367" t="n">
         <v>1000</v>
@@ -11041,7 +11041,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G368" t="n">
-        <v>4.14079427719116</v>
+        <v>4.14079475402832</v>
       </c>
       <c r="H368" t="n">
         <v>0</v>
@@ -11128,7 +11128,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G371" t="n">
-        <v>4.01262760162354</v>
+        <v>4.01262807846069</v>
       </c>
       <c r="H371" t="n">
         <v>6000</v>
@@ -11186,7 +11186,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G373" t="n">
-        <v>4.14079427719116</v>
+        <v>4.14079475402832</v>
       </c>
       <c r="H373" t="n">
         <v>500</v>
@@ -11215,7 +11215,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G374" t="n">
-        <v>4.14079427719116</v>
+        <v>4.14079475402832</v>
       </c>
       <c r="H374" t="n">
         <v>0</v>
@@ -11244,7 +11244,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G375" t="n">
-        <v>4.14079427719116</v>
+        <v>4.14079475402832</v>
       </c>
       <c r="H375" t="n">
         <v>0</v>
@@ -11302,7 +11302,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G377" t="n">
-        <v>4.22952556610107</v>
+        <v>4.22952604293823</v>
       </c>
       <c r="H377" t="n">
         <v>3500</v>
@@ -11331,7 +11331,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G378" t="n">
-        <v>4.27882194519043</v>
+        <v>4.27882146835327</v>
       </c>
       <c r="H378" t="n">
         <v>7000</v>
@@ -11360,7 +11360,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G379" t="n">
-        <v>4.21966743469238</v>
+        <v>4.21966648101807</v>
       </c>
       <c r="H379" t="n">
         <v>67000</v>
@@ -11389,7 +11389,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G380" t="n">
-        <v>4.21966743469238</v>
+        <v>4.21966648101807</v>
       </c>
       <c r="H380" t="n">
         <v>3000</v>
@@ -11418,7 +11418,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G381" t="n">
-        <v>4.2591028213501</v>
+        <v>4.25910234451294</v>
       </c>
       <c r="H381" t="n">
         <v>2500</v>
@@ -11447,7 +11447,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G382" t="n">
-        <v>4.29853963851929</v>
+        <v>4.29853916168213</v>
       </c>
       <c r="H382" t="n">
         <v>35000</v>
@@ -11650,7 +11650,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G389" t="n">
-        <v>4.26896142959595</v>
+        <v>4.26896190643311</v>
       </c>
       <c r="H389" t="n">
         <v>15000</v>
@@ -11853,7 +11853,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G396" t="n">
-        <v>4.22952556610107</v>
+        <v>4.22952604293823</v>
       </c>
       <c r="H396" t="n">
         <v>1500</v>
@@ -11998,7 +11998,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G401" t="n">
-        <v>4.18023061752319</v>
+        <v>4.18023014068604</v>
       </c>
       <c r="H401" t="n">
         <v>33500</v>
@@ -12056,7 +12056,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G403" t="n">
-        <v>4.29853963851929</v>
+        <v>4.29853916168213</v>
       </c>
       <c r="H403" t="n">
         <v>26500</v>
@@ -12114,7 +12114,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G405" t="n">
-        <v>4.38727045059204</v>
+        <v>4.38726997375488</v>
       </c>
       <c r="H405" t="n">
         <v>13000</v>
@@ -12172,7 +12172,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G407" t="n">
-        <v>4.38727045059204</v>
+        <v>4.38726997375488</v>
       </c>
       <c r="H407" t="n">
         <v>6000</v>
@@ -12201,7 +12201,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G408" t="n">
-        <v>4.38727045059204</v>
+        <v>4.38726997375488</v>
       </c>
       <c r="H408" t="n">
         <v>85000</v>
@@ -12230,7 +12230,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G409" t="n">
-        <v>4.49571990966797</v>
+        <v>4.49572038650513</v>
       </c>
       <c r="H409" t="n">
         <v>23000</v>
@@ -12288,7 +12288,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G411" t="n">
-        <v>5.0478253364563</v>
+        <v>5.04782485961914</v>
       </c>
       <c r="H411" t="n">
         <v>104000</v>
@@ -12317,7 +12317,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G412" t="n">
-        <v>5.30416107177734</v>
+        <v>5.30416059494019</v>
       </c>
       <c r="H412" t="n">
         <v>82500</v>
@@ -12346,7 +12346,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G413" t="n">
-        <v>5.2450065612793</v>
+        <v>5.24500608444214</v>
       </c>
       <c r="H413" t="n">
         <v>33000</v>
@@ -12491,7 +12491,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G418" t="n">
-        <v>4.98867130279541</v>
+        <v>4.98867082595825</v>
       </c>
       <c r="H418" t="n">
         <v>23500</v>
@@ -12549,7 +12549,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G420" t="n">
-        <v>5.00838947296143</v>
+        <v>5.00838994979858</v>
       </c>
       <c r="H420" t="n">
         <v>4500</v>
@@ -12781,7 +12781,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G428" t="n">
-        <v>5.00838947296143</v>
+        <v>5.00838994979858</v>
       </c>
       <c r="H428" t="n">
         <v>2500</v>
@@ -12868,7 +12868,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G431" t="n">
-        <v>4.98867130279541</v>
+        <v>4.98867082595825</v>
       </c>
       <c r="H431" t="n">
         <v>8000</v>
@@ -13042,7 +13042,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G437" t="n">
-        <v>4.90979957580566</v>
+        <v>4.90979909896851</v>
       </c>
       <c r="H437" t="n">
         <v>16000</v>
@@ -13187,7 +13187,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G442" t="n">
-        <v>4.90979957580566</v>
+        <v>4.90979909896851</v>
       </c>
       <c r="H442" t="n">
         <v>11000</v>
@@ -13216,7 +13216,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G443" t="n">
-        <v>5.0478253364563</v>
+        <v>5.04782485961914</v>
       </c>
       <c r="H443" t="n">
         <v>5500</v>
@@ -13419,7 +13419,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G450" t="n">
-        <v>4.8309268951416</v>
+        <v>4.83092641830444</v>
       </c>
       <c r="H450" t="n">
         <v>30540</v>
@@ -13448,7 +13448,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G451" t="n">
-        <v>4.8309268951416</v>
+        <v>4.83092641830444</v>
       </c>
       <c r="H451" t="n">
         <v>3150</v>
@@ -13622,7 +13622,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G457" t="n">
-        <v>5.0478253364563</v>
+        <v>5.04782485961914</v>
       </c>
       <c r="H457" t="n">
         <v>26170</v>
@@ -13738,7 +13738,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G461" t="n">
-        <v>5.30416107177734</v>
+        <v>5.30416059494019</v>
       </c>
       <c r="H461" t="n">
         <v>2900</v>
@@ -13825,7 +13825,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G464" t="n">
-        <v>5.0478253364563</v>
+        <v>5.04782485961914</v>
       </c>
       <c r="H464" t="n">
         <v>3580</v>
@@ -13854,7 +13854,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G465" t="n">
-        <v>5.16613435745239</v>
+        <v>5.16613388061523</v>
       </c>
       <c r="H465" t="n">
         <v>650</v>
@@ -13941,7 +13941,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G468" t="n">
-        <v>5.16613435745239</v>
+        <v>5.16613388061523</v>
       </c>
       <c r="H468" t="n">
         <v>10280</v>
@@ -14115,7 +14115,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G474" t="n">
-        <v>4.98867130279541</v>
+        <v>4.98867082595825</v>
       </c>
       <c r="H474" t="n">
         <v>17780</v>
@@ -14202,7 +14202,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G477" t="n">
-        <v>5.00838947296143</v>
+        <v>5.00838994979858</v>
       </c>
       <c r="H477" t="n">
         <v>1250</v>
@@ -14463,7 +14463,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G486" t="n">
-        <v>5.0478253364563</v>
+        <v>5.04782485961914</v>
       </c>
       <c r="H486" t="n">
         <v>5290</v>
@@ -14492,7 +14492,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G487" t="n">
-        <v>5.16613435745239</v>
+        <v>5.16613388061523</v>
       </c>
       <c r="H487" t="n">
         <v>18380</v>
@@ -14550,7 +14550,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G489" t="n">
-        <v>4.98867130279541</v>
+        <v>4.98867082595825</v>
       </c>
       <c r="H489" t="n">
         <v>21530</v>
@@ -14608,7 +14608,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G491" t="n">
-        <v>4.98867130279541</v>
+        <v>4.98867082595825</v>
       </c>
       <c r="H491" t="n">
         <v>28100</v>
@@ -14666,7 +14666,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G493" t="n">
-        <v>5.16613435745239</v>
+        <v>5.16613388061523</v>
       </c>
       <c r="H493" t="n">
         <v>5990</v>
@@ -14782,7 +14782,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G497" t="n">
-        <v>4.87036371231079</v>
+        <v>4.87036323547363</v>
       </c>
       <c r="H497" t="n">
         <v>20640</v>
@@ -14869,7 +14869,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G500" t="n">
-        <v>5.0478253364563</v>
+        <v>5.04782485961914</v>
       </c>
       <c r="H500" t="n">
         <v>4690</v>
@@ -14985,7 +14985,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G504" t="n">
-        <v>4.8309268951416</v>
+        <v>4.83092641830444</v>
       </c>
       <c r="H504" t="n">
         <v>16000</v>
@@ -15014,7 +15014,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G505" t="n">
-        <v>4.98867130279541</v>
+        <v>4.98867082595825</v>
       </c>
       <c r="H505" t="n">
         <v>4800</v>
@@ -15159,7 +15159,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G510" t="n">
-        <v>4.98867130279541</v>
+        <v>4.98867082595825</v>
       </c>
       <c r="H510" t="n">
         <v>1110</v>
@@ -15246,7 +15246,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G513" t="n">
-        <v>5.00838947296143</v>
+        <v>5.00838994979858</v>
       </c>
       <c r="H513" t="n">
         <v>10130</v>
@@ -15333,7 +15333,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G516" t="n">
-        <v>5.00838947296143</v>
+        <v>5.00838994979858</v>
       </c>
       <c r="H516" t="n">
         <v>640</v>
@@ -15391,7 +15391,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G518" t="n">
-        <v>5.00838947296143</v>
+        <v>5.00838994979858</v>
       </c>
       <c r="H518" t="n">
         <v>3020</v>
@@ -15507,7 +15507,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G522" t="n">
-        <v>5.0478253364563</v>
+        <v>5.04782485961914</v>
       </c>
       <c r="H522" t="n">
         <v>27900</v>
@@ -15623,7 +15623,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G526" t="n">
-        <v>5.00838947296143</v>
+        <v>5.00838994979858</v>
       </c>
       <c r="H526" t="n">
         <v>2400</v>
@@ -15710,7 +15710,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G529" t="n">
-        <v>4.77177238464355</v>
+        <v>4.77177286148071</v>
       </c>
       <c r="H529" t="n">
         <v>14510</v>
@@ -15797,7 +15797,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G532" t="n">
-        <v>4.77177238464355</v>
+        <v>4.77177286148071</v>
       </c>
       <c r="H532" t="n">
         <v>4310</v>
@@ -15913,7 +15913,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G536" t="n">
-        <v>4.71261835098267</v>
+        <v>4.71261882781982</v>
       </c>
       <c r="H536" t="n">
         <v>153850</v>
@@ -16029,7 +16029,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G540" t="n">
-        <v>4.8309268951416</v>
+        <v>4.83092641830444</v>
       </c>
       <c r="H540" t="n">
         <v>1600</v>
@@ -16174,7 +16174,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G545" t="n">
-        <v>4.8309268951416</v>
+        <v>4.83092641830444</v>
       </c>
       <c r="H545" t="n">
         <v>1200</v>
@@ -16203,7 +16203,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G546" t="n">
-        <v>4.7520546913147</v>
+        <v>4.75205516815186</v>
       </c>
       <c r="H546" t="n">
         <v>6100</v>
@@ -16232,7 +16232,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G547" t="n">
-        <v>4.62362098693848</v>
+        <v>4.62362051010132</v>
       </c>
       <c r="H547" t="n">
         <v>10330</v>
@@ -16319,7 +16319,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G550" t="n">
-        <v>4.6433801651001</v>
+        <v>4.64337968826294</v>
       </c>
       <c r="H550" t="n">
         <v>1990</v>
@@ -16348,7 +16348,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G551" t="n">
-        <v>4.7421760559082</v>
+        <v>4.74217557907104</v>
       </c>
       <c r="H551" t="n">
         <v>730</v>
@@ -16377,7 +16377,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G552" t="n">
-        <v>4.78169393539429</v>
+        <v>4.78169345855713</v>
       </c>
       <c r="H552" t="n">
         <v>1640</v>
@@ -16406,7 +16406,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G553" t="n">
-        <v>4.78169393539429</v>
+        <v>4.78169345855713</v>
       </c>
       <c r="H553" t="n">
         <v>0</v>
@@ -16435,7 +16435,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G554" t="n">
-        <v>4.78169393539429</v>
+        <v>4.78169345855713</v>
       </c>
       <c r="H554" t="n">
         <v>0</v>
@@ -16493,7 +16493,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G556" t="n">
-        <v>4.7421760559082</v>
+        <v>4.74217557907104</v>
       </c>
       <c r="H556" t="n">
         <v>13120</v>
@@ -16522,7 +16522,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G557" t="n">
-        <v>4.7421760559082</v>
+        <v>4.74217557907104</v>
       </c>
       <c r="H557" t="n">
         <v>260</v>
@@ -16696,7 +16696,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G563" t="n">
-        <v>4.84097099304199</v>
+        <v>4.84097051620483</v>
       </c>
       <c r="H563" t="n">
         <v>4490</v>
@@ -16725,7 +16725,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G564" t="n">
-        <v>4.84097099304199</v>
+        <v>4.84097051620483</v>
       </c>
       <c r="H564" t="n">
         <v>0</v>
@@ -16754,7 +16754,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G565" t="n">
-        <v>4.84097099304199</v>
+        <v>4.84097051620483</v>
       </c>
       <c r="H565" t="n">
         <v>0</v>
@@ -16783,7 +16783,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G566" t="n">
-        <v>4.84097099304199</v>
+        <v>4.84097051620483</v>
       </c>
       <c r="H566" t="n">
         <v>0</v>
@@ -16928,7 +16928,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G571" t="n">
-        <v>4.84097099304199</v>
+        <v>4.84097051620483</v>
       </c>
       <c r="H571" t="n">
         <v>2630</v>
@@ -17160,7 +17160,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G579" t="n">
-        <v>4.27783727645874</v>
+        <v>4.2778377532959</v>
       </c>
       <c r="H579" t="n">
         <v>2300</v>
@@ -17218,7 +17218,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G581" t="n">
-        <v>4.40627193450928</v>
+        <v>4.40627145767212</v>
       </c>
       <c r="H581" t="n">
         <v>1200</v>
@@ -17276,7 +17276,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G583" t="n">
-        <v>4.6433801651001</v>
+        <v>4.64337968826294</v>
       </c>
       <c r="H583" t="n">
         <v>1100</v>
@@ -17305,7 +17305,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G584" t="n">
-        <v>4.78169393539429</v>
+        <v>4.78169345855713</v>
       </c>
       <c r="H584" t="n">
         <v>3210</v>
@@ -17363,7 +17363,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G586" t="n">
-        <v>4.7421760559082</v>
+        <v>4.74217557907104</v>
       </c>
       <c r="H586" t="n">
         <v>200</v>
@@ -17421,7 +17421,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G588" t="n">
-        <v>4.49518728256226</v>
+        <v>4.49518775939941</v>
       </c>
       <c r="H588" t="n">
         <v>1140</v>
@@ -17479,7 +17479,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G590" t="n">
-        <v>4.38651275634766</v>
+        <v>4.3865122795105</v>
       </c>
       <c r="H590" t="n">
         <v>37290</v>
@@ -17595,7 +17595,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G594" t="n">
-        <v>4.48530769348145</v>
+        <v>4.48530721664429</v>
       </c>
       <c r="H594" t="n">
         <v>1520</v>
@@ -17624,7 +17624,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G595" t="n">
-        <v>4.35687398910522</v>
+        <v>4.35687351226807</v>
       </c>
       <c r="H595" t="n">
         <v>30</v>
@@ -17682,7 +17682,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G597" t="n">
-        <v>4.40627193450928</v>
+        <v>4.40627145767212</v>
       </c>
       <c r="H597" t="n">
         <v>1930</v>
@@ -17711,7 +17711,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G598" t="n">
-        <v>4.49518728256226</v>
+        <v>4.49518775939941</v>
       </c>
       <c r="H598" t="n">
         <v>1400</v>
@@ -17769,7 +17769,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G600" t="n">
-        <v>4.48530769348145</v>
+        <v>4.48530721664429</v>
       </c>
       <c r="H600" t="n">
         <v>1360</v>
@@ -17798,7 +17798,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G601" t="n">
-        <v>4.54458522796631</v>
+        <v>4.54458475112915</v>
       </c>
       <c r="H601" t="n">
         <v>3410</v>
@@ -17856,7 +17856,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G603" t="n">
-        <v>4.6433801651001</v>
+        <v>4.64337968826294</v>
       </c>
       <c r="H603" t="n">
         <v>1550</v>
@@ -17885,7 +17885,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G604" t="n">
-        <v>4.84097099304199</v>
+        <v>4.84097051620483</v>
       </c>
       <c r="H604" t="n">
         <v>7020</v>
@@ -17943,7 +17943,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G606" t="n">
-        <v>4.89036798477173</v>
+        <v>4.89036846160889</v>
       </c>
       <c r="H606" t="n">
         <v>2760</v>
@@ -18059,7 +18059,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G610" t="n">
-        <v>4.84097099304199</v>
+        <v>4.84097051620483</v>
       </c>
       <c r="H610" t="n">
         <v>3200</v>
@@ -18146,7 +18146,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G613" t="n">
-        <v>4.78169393539429</v>
+        <v>4.78169345855713</v>
       </c>
       <c r="H613" t="n">
         <v>1500</v>
@@ -18175,7 +18175,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G614" t="n">
-        <v>4.84097099304199</v>
+        <v>4.84097051620483</v>
       </c>
       <c r="H614" t="n">
         <v>3250</v>
@@ -18204,7 +18204,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G615" t="n">
-        <v>4.88048934936523</v>
+        <v>4.88048887252808</v>
       </c>
       <c r="H615" t="n">
         <v>1500</v>
@@ -18349,7 +18349,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G620" t="n">
-        <v>4.99904346466064</v>
+        <v>4.99904298782349</v>
       </c>
       <c r="H620" t="n">
         <v>3460</v>
@@ -18813,7 +18813,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G636" t="n">
-        <v>4.89036798477173</v>
+        <v>4.89036846160889</v>
       </c>
       <c r="H636" t="n">
         <v>1500</v>
@@ -18842,7 +18842,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G637" t="n">
-        <v>4.88048934936523</v>
+        <v>4.88048887252808</v>
       </c>
       <c r="H637" t="n">
         <v>1800</v>
@@ -18871,7 +18871,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G638" t="n">
-        <v>4.88048934936523</v>
+        <v>4.88048887252808</v>
       </c>
       <c r="H638" t="n">
         <v>0</v>
@@ -19016,7 +19016,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G643" t="n">
-        <v>4.73229551315308</v>
+        <v>4.73229598999023</v>
       </c>
       <c r="H643" t="n">
         <v>4150</v>
@@ -19045,7 +19045,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G644" t="n">
-        <v>4.54458522796631</v>
+        <v>4.54458475112915</v>
       </c>
       <c r="H644" t="n">
         <v>7280</v>
@@ -19074,7 +19074,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G645" t="n">
-        <v>4.49518728256226</v>
+        <v>4.49518775939941</v>
       </c>
       <c r="H645" t="n">
         <v>3250</v>
@@ -19219,7 +19219,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G650" t="n">
-        <v>4.52482604980469</v>
+        <v>4.52482557296753</v>
       </c>
       <c r="H650" t="n">
         <v>11950</v>
@@ -19364,7 +19364,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G655" t="n">
-        <v>4.84097099304199</v>
+        <v>4.84097051620483</v>
       </c>
       <c r="H655" t="n">
         <v>2980</v>
@@ -19480,7 +19480,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G659" t="n">
-        <v>4.7421760559082</v>
+        <v>4.74217557907104</v>
       </c>
       <c r="H659" t="n">
         <v>60</v>
@@ -19509,7 +19509,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G660" t="n">
-        <v>4.7421760559082</v>
+        <v>4.74217557907104</v>
       </c>
       <c r="H660" t="n">
         <v>12790</v>
@@ -19538,7 +19538,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G661" t="n">
-        <v>4.88048934936523</v>
+        <v>4.88048887252808</v>
       </c>
       <c r="H661" t="n">
         <v>1600</v>
@@ -19567,7 +19567,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G662" t="n">
-        <v>4.7421760559082</v>
+        <v>4.74217557907104</v>
       </c>
       <c r="H662" t="n">
         <v>10540</v>
@@ -20002,7 +20002,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G677" t="n">
-        <v>4.89036798477173</v>
+        <v>4.89036846160889</v>
       </c>
       <c r="H677" t="n">
         <v>54910</v>
@@ -20031,7 +20031,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G678" t="n">
-        <v>4.7421760559082</v>
+        <v>4.74217557907104</v>
       </c>
       <c r="H678" t="n">
         <v>42730</v>
@@ -20089,7 +20089,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G680" t="n">
-        <v>4.73229551315308</v>
+        <v>4.73229598999023</v>
       </c>
       <c r="H680" t="n">
         <v>23420</v>
@@ -20205,7 +20205,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G684" t="n">
-        <v>4.52482604980469</v>
+        <v>4.52482557296753</v>
       </c>
       <c r="H684" t="n">
         <v>1210</v>
@@ -20524,7 +20524,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G695" t="n">
-        <v>4.99904346466064</v>
+        <v>4.99904298782349</v>
       </c>
       <c r="H695" t="n">
         <v>25780</v>
@@ -20785,7 +20785,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G704" t="n">
-        <v>4.7421760559082</v>
+        <v>4.74217557907104</v>
       </c>
       <c r="H704" t="n">
         <v>5760</v>
@@ -20814,7 +20814,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G705" t="n">
-        <v>4.84097099304199</v>
+        <v>4.84097051620483</v>
       </c>
       <c r="H705" t="n">
         <v>1870</v>
@@ -20843,7 +20843,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G706" t="n">
-        <v>4.84097099304199</v>
+        <v>4.84097051620483</v>
       </c>
       <c r="H706" t="n">
         <v>0</v>
@@ -20872,7 +20872,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G707" t="n">
-        <v>4.85084962844849</v>
+        <v>4.85085010528564</v>
       </c>
       <c r="H707" t="n">
         <v>250</v>
@@ -20988,7 +20988,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G711" t="n">
-        <v>4.88048934936523</v>
+        <v>4.88048887252808</v>
       </c>
       <c r="H711" t="n">
         <v>1130</v>
@@ -21162,7 +21162,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G717" t="n">
-        <v>4.78169393539429</v>
+        <v>4.78169345855713</v>
       </c>
       <c r="H717" t="n">
         <v>2530</v>
@@ -21278,7 +21278,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G721" t="n">
-        <v>5.09783840179443</v>
+        <v>5.09783792495728</v>
       </c>
       <c r="H721" t="n">
         <v>3950</v>
@@ -21394,7 +21394,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G725" t="n">
-        <v>5.13735675811768</v>
+        <v>5.13735628128052</v>
       </c>
       <c r="H725" t="n">
         <v>3650</v>
@@ -21510,7 +21510,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G729" t="n">
-        <v>4.84097099304199</v>
+        <v>4.84097051620483</v>
       </c>
       <c r="H729" t="n">
         <v>2100</v>
@@ -21568,7 +21568,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G731" t="n">
-        <v>4.7421760559082</v>
+        <v>4.74217557907104</v>
       </c>
       <c r="H731" t="n">
         <v>2850</v>
@@ -21626,7 +21626,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G733" t="n">
-        <v>4.88048934936523</v>
+        <v>4.88048887252808</v>
       </c>
       <c r="H733" t="n">
         <v>7390</v>
@@ -21655,7 +21655,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G734" t="n">
-        <v>4.78169393539429</v>
+        <v>4.78169345855713</v>
       </c>
       <c r="H734" t="n">
         <v>2150</v>
@@ -21713,7 +21713,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G736" t="n">
-        <v>4.88048934936523</v>
+        <v>4.88048887252808</v>
       </c>
       <c r="H736" t="n">
         <v>3780</v>
@@ -21742,7 +21742,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G737" t="n">
-        <v>4.89036798477173</v>
+        <v>4.89036846160889</v>
       </c>
       <c r="H737" t="n">
         <v>3100</v>
@@ -21887,7 +21887,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G742" t="n">
-        <v>4.84097099304199</v>
+        <v>4.84097051620483</v>
       </c>
       <c r="H742" t="n">
         <v>8310</v>
@@ -21916,7 +21916,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G743" t="n">
-        <v>4.85084962844849</v>
+        <v>4.85085010528564</v>
       </c>
       <c r="H743" t="n">
         <v>3070</v>
@@ -22032,7 +22032,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G747" t="n">
-        <v>4.7421760559082</v>
+        <v>4.74217557907104</v>
       </c>
       <c r="H747" t="n">
         <v>63650</v>
@@ -22090,7 +22090,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G749" t="n">
-        <v>4.78169393539429</v>
+        <v>4.78169345855713</v>
       </c>
       <c r="H749" t="n">
         <v>10810</v>
@@ -22177,7 +22177,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G752" t="n">
-        <v>4.228440284729</v>
+        <v>4.22843980789185</v>
       </c>
       <c r="H752" t="n">
         <v>104770</v>
@@ -22409,7 +22409,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G760" t="n">
-        <v>4.16916275024414</v>
+        <v>4.16916227340698</v>
       </c>
       <c r="H760" t="n">
         <v>13670</v>
@@ -22438,7 +22438,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G761" t="n">
-        <v>4.16916275024414</v>
+        <v>4.16916227340698</v>
       </c>
       <c r="H761" t="n">
         <v>5710</v>
@@ -22496,7 +22496,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G763" t="n">
-        <v>4.05060863494873</v>
+        <v>4.05060815811157</v>
       </c>
       <c r="H763" t="n">
         <v>55200</v>
@@ -22525,7 +22525,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G764" t="n">
-        <v>4.0209698677063</v>
+        <v>4.02097034454346</v>
       </c>
       <c r="H764" t="n">
         <v>16670</v>
@@ -23163,7 +23163,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G786" t="n">
-        <v>3.96169257164001</v>
+        <v>3.96169233322144</v>
       </c>
       <c r="H786" t="n">
         <v>3050</v>
@@ -23192,7 +23192,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G787" t="n">
-        <v>4.03084945678711</v>
+        <v>4.03084897994995</v>
       </c>
       <c r="H787" t="n">
         <v>5350</v>
@@ -23250,7 +23250,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G789" t="n">
-        <v>3.92217421531677</v>
+        <v>3.92217445373535</v>
       </c>
       <c r="H789" t="n">
         <v>12190</v>
@@ -49092,9 +49092,38 @@
         <v>3.14000010490417</v>
       </c>
       <c r="H1680" t="n">
-        <v>107846</v>
+        <v>109680</v>
       </c>
       <c r="I1680" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1681">
+      <c r="A1681" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1681" s="1" t="n">
+        <v>46318.2916666667</v>
+      </c>
+      <c r="C1681" t="n">
+        <v>3.14499998092651</v>
+      </c>
+      <c r="D1681" t="n">
+        <v>3.16000008583069</v>
+      </c>
+      <c r="E1681" t="n">
+        <v>3.09999990463257</v>
+      </c>
+      <c r="F1681" t="n">
+        <v>3.11999988555908</v>
+      </c>
+      <c r="G1681" t="n">
+        <v>3.11999988555908</v>
+      </c>
+      <c r="H1681" t="n">
+        <v>12226</v>
+      </c>
+      <c r="I1681" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/UD.MI.xlsx
+++ b/data/UD.MI.xlsx
@@ -572,7 +572,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G7" t="n">
-        <v>1.51829135417938</v>
+        <v>1.51829123497009</v>
       </c>
       <c r="H7" t="n">
         <v>61000</v>
@@ -601,7 +601,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G8" t="n">
-        <v>1.53800940513611</v>
+        <v>1.53800928592682</v>
       </c>
       <c r="H8" t="n">
         <v>19000</v>
@@ -659,7 +659,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G10" t="n">
-        <v>1.53800940513611</v>
+        <v>1.53800928592682</v>
       </c>
       <c r="H10" t="n">
         <v>17000</v>
@@ -862,7 +862,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G17" t="n">
-        <v>1.66617703437805</v>
+        <v>1.66617691516876</v>
       </c>
       <c r="H17" t="n">
         <v>14000</v>
@@ -1065,7 +1065,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G24" t="n">
-        <v>1.57744562625885</v>
+        <v>1.57744550704956</v>
       </c>
       <c r="H24" t="n">
         <v>2000</v>
@@ -1123,7 +1123,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G26" t="n">
-        <v>1.57744562625885</v>
+        <v>1.57744550704956</v>
       </c>
       <c r="H26" t="n">
         <v>8000</v>
@@ -1152,7 +1152,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G27" t="n">
-        <v>1.57744562625885</v>
+        <v>1.57744550704956</v>
       </c>
       <c r="H27" t="n">
         <v>3000</v>
@@ -1210,7 +1210,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G29" t="n">
-        <v>1.57744562625885</v>
+        <v>1.57744550704956</v>
       </c>
       <c r="H29" t="n">
         <v>11000</v>
@@ -1239,7 +1239,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G30" t="n">
-        <v>1.62674069404602</v>
+        <v>1.62674057483673</v>
       </c>
       <c r="H30" t="n">
         <v>12000</v>
@@ -1326,7 +1326,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G33" t="n">
-        <v>1.6168817281723</v>
+        <v>1.61688160896301</v>
       </c>
       <c r="H33" t="n">
         <v>1000</v>
@@ -1355,7 +1355,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G34" t="n">
-        <v>1.62674069404602</v>
+        <v>1.62674057483673</v>
       </c>
       <c r="H34" t="n">
         <v>84000</v>
@@ -1384,7 +1384,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G35" t="n">
-        <v>1.62674069404602</v>
+        <v>1.62674057483673</v>
       </c>
       <c r="H35" t="n">
         <v>0</v>
@@ -1616,7 +1616,7 @@
         <v>1.72500002384186</v>
       </c>
       <c r="G43" t="n">
-        <v>1.70068347454071</v>
+        <v>1.70068359375</v>
       </c>
       <c r="H43" t="n">
         <v>21000</v>
@@ -1674,7 +1674,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G45" t="n">
-        <v>1.66617703437805</v>
+        <v>1.66617691516876</v>
       </c>
       <c r="H45" t="n">
         <v>1000</v>
@@ -1790,7 +1790,7 @@
         <v>1.72500002384186</v>
       </c>
       <c r="G49" t="n">
-        <v>1.70068347454071</v>
+        <v>1.70068359375</v>
       </c>
       <c r="H49" t="n">
         <v>18000</v>
@@ -1877,7 +1877,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G52" t="n">
-        <v>1.74011969566345</v>
+        <v>1.74011957645416</v>
       </c>
       <c r="H52" t="n">
         <v>6000</v>
@@ -1906,7 +1906,7 @@
         <v>1.74500000476837</v>
       </c>
       <c r="G53" t="n">
-        <v>1.72040152549744</v>
+        <v>1.72040164470673</v>
       </c>
       <c r="H53" t="n">
         <v>7000</v>
@@ -1935,7 +1935,7 @@
         <v>1.72500002384186</v>
       </c>
       <c r="G54" t="n">
-        <v>1.70068347454071</v>
+        <v>1.70068359375</v>
       </c>
       <c r="H54" t="n">
         <v>10000</v>
@@ -1964,7 +1964,7 @@
         <v>1.72500002384186</v>
       </c>
       <c r="G55" t="n">
-        <v>1.70068347454071</v>
+        <v>1.70068359375</v>
       </c>
       <c r="H55" t="n">
         <v>15000</v>
@@ -2312,7 +2312,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G67" t="n">
-        <v>1.66617703437805</v>
+        <v>1.66617691516876</v>
       </c>
       <c r="H67" t="n">
         <v>10000</v>
@@ -2399,7 +2399,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G70" t="n">
-        <v>1.62674069404602</v>
+        <v>1.62674057483673</v>
       </c>
       <c r="H70" t="n">
         <v>41000</v>
@@ -2428,7 +2428,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G71" t="n">
-        <v>1.62674069404602</v>
+        <v>1.62674057483673</v>
       </c>
       <c r="H71" t="n">
         <v>0</v>
@@ -2834,7 +2834,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G85" t="n">
-        <v>1.62674069404602</v>
+        <v>1.62674057483673</v>
       </c>
       <c r="H85" t="n">
         <v>7000</v>
@@ -2863,7 +2863,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G86" t="n">
-        <v>1.62674069404602</v>
+        <v>1.62674057483673</v>
       </c>
       <c r="H86" t="n">
         <v>0</v>
@@ -2921,7 +2921,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G88" t="n">
-        <v>1.57744562625885</v>
+        <v>1.57744550704956</v>
       </c>
       <c r="H88" t="n">
         <v>94000</v>
@@ -2950,7 +2950,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G89" t="n">
-        <v>1.57744562625885</v>
+        <v>1.57744550704956</v>
       </c>
       <c r="H89" t="n">
         <v>0</v>
@@ -3037,7 +3037,7 @@
         <v>1.62999999523163</v>
       </c>
       <c r="G92" t="n">
-        <v>1.60702252388</v>
+        <v>1.60702264308929</v>
       </c>
       <c r="H92" t="n">
         <v>32000</v>
@@ -3240,7 +3240,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G99" t="n">
-        <v>1.62674069404602</v>
+        <v>1.62674057483673</v>
       </c>
       <c r="H99" t="n">
         <v>7000</v>
@@ -3269,7 +3269,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G100" t="n">
-        <v>1.62674069404602</v>
+        <v>1.62674057483673</v>
       </c>
       <c r="H100" t="n">
         <v>0</v>
@@ -3327,7 +3327,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G102" t="n">
-        <v>1.62674069404602</v>
+        <v>1.62674057483673</v>
       </c>
       <c r="H102" t="n">
         <v>9000</v>
@@ -3414,7 +3414,7 @@
         <v>1.63499999046326</v>
       </c>
       <c r="G105" t="n">
-        <v>1.6119521856308</v>
+        <v>1.61195206642151</v>
       </c>
       <c r="H105" t="n">
         <v>26000</v>
@@ -3443,7 +3443,7 @@
         <v>1.66499996185303</v>
       </c>
       <c r="G106" t="n">
-        <v>1.64152920246124</v>
+        <v>1.64152932167053</v>
       </c>
       <c r="H106" t="n">
         <v>2000</v>
@@ -3472,7 +3472,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G107" t="n">
-        <v>1.62674069404602</v>
+        <v>1.62674057483673</v>
       </c>
       <c r="H107" t="n">
         <v>3000</v>
@@ -3501,7 +3501,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G108" t="n">
-        <v>1.62674069404602</v>
+        <v>1.62674057483673</v>
       </c>
       <c r="H108" t="n">
         <v>1000</v>
@@ -3530,7 +3530,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G109" t="n">
-        <v>1.66617703437805</v>
+        <v>1.66617691516876</v>
       </c>
       <c r="H109" t="n">
         <v>15000</v>
@@ -4342,7 +4342,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G137" t="n">
-        <v>1.88307559490204</v>
+        <v>1.88307571411133</v>
       </c>
       <c r="H137" t="n">
         <v>1000</v>
@@ -4371,7 +4371,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G138" t="n">
-        <v>1.88307559490204</v>
+        <v>1.88307571411133</v>
       </c>
       <c r="H138" t="n">
         <v>0</v>
@@ -4574,7 +4574,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G145" t="n">
-        <v>1.79434430599213</v>
+        <v>1.79434442520142</v>
       </c>
       <c r="H145" t="n">
         <v>23000</v>
@@ -4603,7 +4603,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G146" t="n">
-        <v>1.79434430599213</v>
+        <v>1.79434442520142</v>
       </c>
       <c r="H146" t="n">
         <v>0</v>
@@ -4632,7 +4632,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G147" t="n">
-        <v>1.79434430599213</v>
+        <v>1.79434442520142</v>
       </c>
       <c r="H147" t="n">
         <v>29000</v>
@@ -4661,7 +4661,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G148" t="n">
-        <v>1.75983762741089</v>
+        <v>1.7598375082016</v>
       </c>
       <c r="H148" t="n">
         <v>12000</v>
@@ -4690,7 +4690,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G149" t="n">
-        <v>1.79434430599213</v>
+        <v>1.79434442520142</v>
       </c>
       <c r="H149" t="n">
         <v>10000</v>
@@ -4719,7 +4719,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G150" t="n">
-        <v>1.79434430599213</v>
+        <v>1.79434442520142</v>
       </c>
       <c r="H150" t="n">
         <v>0</v>
@@ -4748,7 +4748,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G151" t="n">
-        <v>1.74011969566345</v>
+        <v>1.74011957645416</v>
       </c>
       <c r="H151" t="n">
         <v>30000</v>
@@ -4777,7 +4777,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G152" t="n">
-        <v>1.7696967124939</v>
+        <v>1.76969659328461</v>
       </c>
       <c r="H152" t="n">
         <v>4000</v>
@@ -5560,7 +5560,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G179" t="n">
-        <v>1.88307559490204</v>
+        <v>1.88307571411133</v>
       </c>
       <c r="H179" t="n">
         <v>30000</v>
@@ -5618,7 +5618,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G181" t="n">
-        <v>1.90279352664948</v>
+        <v>1.90279364585876</v>
       </c>
       <c r="H181" t="n">
         <v>23000</v>
@@ -5676,7 +5676,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G183" t="n">
-        <v>2.03096079826355</v>
+        <v>2.03096103668213</v>
       </c>
       <c r="H183" t="n">
         <v>24000</v>
@@ -5705,7 +5705,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G184" t="n">
-        <v>2.01124286651611</v>
+        <v>2.01124310493469</v>
       </c>
       <c r="H184" t="n">
         <v>3000</v>
@@ -5734,7 +5734,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G185" t="n">
-        <v>2.03096079826355</v>
+        <v>2.03096103668213</v>
       </c>
       <c r="H185" t="n">
         <v>54000</v>
@@ -5763,7 +5763,7 @@
         <v>1.99500000476837</v>
       </c>
       <c r="G186" t="n">
-        <v>1.96687746047974</v>
+        <v>1.96687734127045</v>
       </c>
       <c r="H186" t="n">
         <v>28000</v>
@@ -5821,7 +5821,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G188" t="n">
-        <v>2.01124286651611</v>
+        <v>2.01124310493469</v>
       </c>
       <c r="H188" t="n">
         <v>4000</v>
@@ -5850,7 +5850,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G189" t="n">
-        <v>2.01124286651611</v>
+        <v>2.01124310493469</v>
       </c>
       <c r="H189" t="n">
         <v>0</v>
@@ -6256,7 +6256,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G203" t="n">
-        <v>1.90772306919098</v>
+        <v>1.90772318840027</v>
       </c>
       <c r="H203" t="n">
         <v>39000</v>
@@ -6459,7 +6459,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G210" t="n">
-        <v>1.95701837539673</v>
+        <v>1.95701849460602</v>
       </c>
       <c r="H210" t="n">
         <v>16000</v>
@@ -6604,7 +6604,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G215" t="n">
-        <v>1.95701837539673</v>
+        <v>1.95701849460602</v>
       </c>
       <c r="H215" t="n">
         <v>1000</v>
@@ -7155,7 +7155,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G234" t="n">
-        <v>2.16898798942566</v>
+        <v>2.16898775100708</v>
       </c>
       <c r="H234" t="n">
         <v>85000</v>
@@ -7213,7 +7213,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G236" t="n">
-        <v>2.19856452941895</v>
+        <v>2.19856476783752</v>
       </c>
       <c r="H236" t="n">
         <v>9000</v>
@@ -7271,7 +7271,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G238" t="n">
-        <v>2.23800086975098</v>
+        <v>2.2380006313324</v>
       </c>
       <c r="H238" t="n">
         <v>13000</v>
@@ -7764,7 +7764,7 @@
         <v>2.5</v>
       </c>
       <c r="G255" t="n">
-        <v>2.46475863456726</v>
+        <v>2.46475839614868</v>
       </c>
       <c r="H255" t="n">
         <v>11000</v>
@@ -7996,7 +7996,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G263" t="n">
-        <v>2.97742819786072</v>
+        <v>2.9774284362793</v>
       </c>
       <c r="H263" t="n">
         <v>41000</v>
@@ -8025,7 +8025,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G264" t="n">
-        <v>3.1548912525177</v>
+        <v>3.15489101409912</v>
       </c>
       <c r="H264" t="n">
         <v>21000</v>
@@ -8199,7 +8199,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G270" t="n">
-        <v>2.77038884162903</v>
+        <v>2.77038860321045</v>
       </c>
       <c r="H270" t="n">
         <v>11000</v>
@@ -8228,7 +8228,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G271" t="n">
-        <v>2.84926104545593</v>
+        <v>2.84926080703735</v>
       </c>
       <c r="H271" t="n">
         <v>21000</v>
@@ -8489,7 +8489,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G280" t="n">
-        <v>3.25348138809204</v>
+        <v>3.25348114967346</v>
       </c>
       <c r="H280" t="n">
         <v>4000</v>
@@ -8547,7 +8547,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G282" t="n">
-        <v>3.21404504776001</v>
+        <v>3.21404528617859</v>
       </c>
       <c r="H282" t="n">
         <v>6000</v>
@@ -8692,7 +8692,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G287" t="n">
-        <v>3.60840678215027</v>
+        <v>3.60840702056885</v>
       </c>
       <c r="H287" t="n">
         <v>86000</v>
@@ -8895,7 +8895,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G294" t="n">
-        <v>3.53939342498779</v>
+        <v>3.53939318656921</v>
       </c>
       <c r="H294" t="n">
         <v>30000</v>
@@ -8924,7 +8924,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G295" t="n">
-        <v>3.51967525482178</v>
+        <v>3.5196750164032</v>
       </c>
       <c r="H295" t="n">
         <v>95000</v>
@@ -8982,7 +8982,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G297" t="n">
-        <v>3.55911159515381</v>
+        <v>3.55911135673523</v>
       </c>
       <c r="H297" t="n">
         <v>30000</v>
@@ -9069,7 +9069,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G300" t="n">
-        <v>3.4802393913269</v>
+        <v>3.48023915290833</v>
       </c>
       <c r="H300" t="n">
         <v>15000</v>
@@ -9359,7 +9359,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G310" t="n">
-        <v>4.33797597885132</v>
+        <v>4.33797550201416</v>
       </c>
       <c r="H310" t="n">
         <v>1000</v>
@@ -9446,7 +9446,7 @@
         <v>4</v>
       </c>
       <c r="G313" t="n">
-        <v>3.94361400604248</v>
+        <v>3.9436137676239</v>
       </c>
       <c r="H313" t="n">
         <v>19000</v>
@@ -9475,7 +9475,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G314" t="n">
-        <v>4.05206394195557</v>
+        <v>4.05206346511841</v>
       </c>
       <c r="H314" t="n">
         <v>6000</v>
@@ -9649,7 +9649,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G320" t="n">
-        <v>4.23938512802124</v>
+        <v>4.2393856048584</v>
       </c>
       <c r="H320" t="n">
         <v>9000</v>
@@ -9794,7 +9794,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G325" t="n">
-        <v>4.0619215965271</v>
+        <v>4.06192207336426</v>
       </c>
       <c r="H325" t="n">
         <v>7000</v>
@@ -9910,7 +9910,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G329" t="n">
-        <v>4.02248573303223</v>
+        <v>4.02248620986938</v>
       </c>
       <c r="H329" t="n">
         <v>5000</v>
@@ -9968,7 +9968,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G331" t="n">
-        <v>4.15065336227417</v>
+        <v>4.15065383911133</v>
       </c>
       <c r="H331" t="n">
         <v>10000</v>
@@ -9997,7 +9997,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G332" t="n">
-        <v>4.15065336227417</v>
+        <v>4.15065383911133</v>
       </c>
       <c r="H332" t="n">
         <v>1000</v>
@@ -10287,7 +10287,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G342" t="n">
-        <v>4.0619215965271</v>
+        <v>4.06192207336426</v>
       </c>
       <c r="H342" t="n">
         <v>5000</v>
@@ -10432,7 +10432,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G347" t="n">
-        <v>4.02248573303223</v>
+        <v>4.02248620986938</v>
       </c>
       <c r="H347" t="n">
         <v>3000</v>
@@ -10461,7 +10461,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G348" t="n">
-        <v>4.02248573303223</v>
+        <v>4.02248620986938</v>
       </c>
       <c r="H348" t="n">
         <v>16500</v>
@@ -10490,7 +10490,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G349" t="n">
-        <v>4.21966648101807</v>
+        <v>4.21966695785522</v>
       </c>
       <c r="H349" t="n">
         <v>21000</v>
@@ -10519,7 +10519,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G350" t="n">
-        <v>4.23938512802124</v>
+        <v>4.2393856048584</v>
       </c>
       <c r="H350" t="n">
         <v>24000</v>
@@ -10548,7 +10548,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G351" t="n">
-        <v>4.23938512802124</v>
+        <v>4.2393856048584</v>
       </c>
       <c r="H351" t="n">
         <v>4500</v>
@@ -10722,7 +10722,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G357" t="n">
-        <v>4.05206394195557</v>
+        <v>4.05206346511841</v>
       </c>
       <c r="H357" t="n">
         <v>10000</v>
@@ -10780,7 +10780,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G359" t="n">
-        <v>4.21966648101807</v>
+        <v>4.21966695785522</v>
       </c>
       <c r="H359" t="n">
         <v>14500</v>
@@ -10809,7 +10809,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G360" t="n">
-        <v>4.15065336227417</v>
+        <v>4.15065383911133</v>
       </c>
       <c r="H360" t="n">
         <v>5000</v>
@@ -10896,7 +10896,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G363" t="n">
-        <v>4.12107610702515</v>
+        <v>4.12107563018799</v>
       </c>
       <c r="H363" t="n">
         <v>500</v>
@@ -10925,7 +10925,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G364" t="n">
-        <v>4.12107610702515</v>
+        <v>4.12107563018799</v>
       </c>
       <c r="H364" t="n">
         <v>0</v>
@@ -10954,7 +10954,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G365" t="n">
-        <v>4.12107610702515</v>
+        <v>4.12107563018799</v>
       </c>
       <c r="H365" t="n">
         <v>0</v>
@@ -11331,7 +11331,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G378" t="n">
-        <v>4.27882146835327</v>
+        <v>4.27882099151611</v>
       </c>
       <c r="H378" t="n">
         <v>7000</v>
@@ -11360,7 +11360,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G379" t="n">
-        <v>4.21966648101807</v>
+        <v>4.21966695785522</v>
       </c>
       <c r="H379" t="n">
         <v>67000</v>
@@ -11389,7 +11389,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G380" t="n">
-        <v>4.21966648101807</v>
+        <v>4.21966695785522</v>
       </c>
       <c r="H380" t="n">
         <v>3000</v>
@@ -11418,7 +11418,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G381" t="n">
-        <v>4.25910234451294</v>
+        <v>4.2591028213501</v>
       </c>
       <c r="H381" t="n">
         <v>2500</v>
@@ -11476,7 +11476,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G383" t="n">
-        <v>4.30839776992798</v>
+        <v>4.30839824676514</v>
       </c>
       <c r="H383" t="n">
         <v>2500</v>
@@ -11505,7 +11505,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G384" t="n">
-        <v>4.33797597885132</v>
+        <v>4.33797550201416</v>
       </c>
       <c r="H384" t="n">
         <v>17000</v>
@@ -11534,7 +11534,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G385" t="n">
-        <v>4.36755275726318</v>
+        <v>4.36755228042603</v>
       </c>
       <c r="H385" t="n">
         <v>4000</v>
@@ -11563,7 +11563,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G386" t="n">
-        <v>4.30839776992798</v>
+        <v>4.30839824676514</v>
       </c>
       <c r="H386" t="n">
         <v>255000</v>
@@ -11592,7 +11592,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G387" t="n">
-        <v>4.36755275726318</v>
+        <v>4.36755228042603</v>
       </c>
       <c r="H387" t="n">
         <v>6000</v>
@@ -11621,7 +11621,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G388" t="n">
-        <v>4.36755275726318</v>
+        <v>4.36755228042603</v>
       </c>
       <c r="H388" t="n">
         <v>13500</v>
@@ -11679,7 +11679,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G390" t="n">
-        <v>4.33797597885132</v>
+        <v>4.33797550201416</v>
       </c>
       <c r="H390" t="n">
         <v>15000</v>
@@ -11708,7 +11708,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G391" t="n">
-        <v>4.30839776992798</v>
+        <v>4.30839824676514</v>
       </c>
       <c r="H391" t="n">
         <v>34000</v>
@@ -11766,7 +11766,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G393" t="n">
-        <v>4.33797597885132</v>
+        <v>4.33797550201416</v>
       </c>
       <c r="H393" t="n">
         <v>6000</v>
@@ -11795,7 +11795,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G394" t="n">
-        <v>4.40698862075806</v>
+        <v>4.4069881439209</v>
       </c>
       <c r="H394" t="n">
         <v>2000</v>
@@ -12085,7 +12085,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G404" t="n">
-        <v>4.33797597885132</v>
+        <v>4.33797550201416</v>
       </c>
       <c r="H404" t="n">
         <v>37500</v>
@@ -12143,7 +12143,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G406" t="n">
-        <v>4.39712905883789</v>
+        <v>4.39712953567505</v>
       </c>
       <c r="H406" t="n">
         <v>19500</v>
@@ -12230,7 +12230,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G409" t="n">
-        <v>4.49572038650513</v>
+        <v>4.49571990966797</v>
       </c>
       <c r="H409" t="n">
         <v>23000</v>
@@ -12288,7 +12288,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G411" t="n">
-        <v>5.04782485961914</v>
+        <v>5.0478253364563</v>
       </c>
       <c r="H411" t="n">
         <v>104000</v>
@@ -12317,7 +12317,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G412" t="n">
-        <v>5.30416059494019</v>
+        <v>5.30416011810303</v>
       </c>
       <c r="H412" t="n">
         <v>82500</v>
@@ -12375,7 +12375,7 @@
         <v>5</v>
       </c>
       <c r="G414" t="n">
-        <v>4.92951726913452</v>
+        <v>4.92951679229736</v>
       </c>
       <c r="H414" t="n">
         <v>45500</v>
@@ -12404,7 +12404,7 @@
         <v>5</v>
       </c>
       <c r="G415" t="n">
-        <v>4.92951726913452</v>
+        <v>4.92951679229736</v>
       </c>
       <c r="H415" t="n">
         <v>14500</v>
@@ -12462,7 +12462,7 @@
         <v>5</v>
       </c>
       <c r="G417" t="n">
-        <v>4.92951726913452</v>
+        <v>4.92951679229736</v>
       </c>
       <c r="H417" t="n">
         <v>7500</v>
@@ -12491,7 +12491,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G418" t="n">
-        <v>4.98867082595825</v>
+        <v>4.98867130279541</v>
       </c>
       <c r="H418" t="n">
         <v>23500</v>
@@ -12520,7 +12520,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G419" t="n">
-        <v>5.02810716629028</v>
+        <v>5.02810764312744</v>
       </c>
       <c r="H419" t="n">
         <v>5500</v>
@@ -12578,7 +12578,7 @@
         <v>5</v>
       </c>
       <c r="G421" t="n">
-        <v>4.92951726913452</v>
+        <v>4.92951679229736</v>
       </c>
       <c r="H421" t="n">
         <v>8500</v>
@@ -12607,7 +12607,7 @@
         <v>5</v>
       </c>
       <c r="G422" t="n">
-        <v>4.92951726913452</v>
+        <v>4.92951679229736</v>
       </c>
       <c r="H422" t="n">
         <v>9500</v>
@@ -12636,7 +12636,7 @@
         <v>5</v>
       </c>
       <c r="G423" t="n">
-        <v>4.92951726913452</v>
+        <v>4.92951679229736</v>
       </c>
       <c r="H423" t="n">
         <v>38500</v>
@@ -12694,7 +12694,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G425" t="n">
-        <v>5.02810716629028</v>
+        <v>5.02810764312744</v>
       </c>
       <c r="H425" t="n">
         <v>4500</v>
@@ -12723,7 +12723,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G426" t="n">
-        <v>5.08726167678833</v>
+        <v>5.08726119995117</v>
       </c>
       <c r="H426" t="n">
         <v>1500</v>
@@ -12752,7 +12752,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G427" t="n">
-        <v>5.02810716629028</v>
+        <v>5.02810764312744</v>
       </c>
       <c r="H427" t="n">
         <v>1500</v>
@@ -12839,7 +12839,7 @@
         <v>5</v>
       </c>
       <c r="G430" t="n">
-        <v>4.92951726913452</v>
+        <v>4.92951679229736</v>
       </c>
       <c r="H430" t="n">
         <v>8500</v>
@@ -12868,7 +12868,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G431" t="n">
-        <v>4.98867082595825</v>
+        <v>4.98867130279541</v>
       </c>
       <c r="H431" t="n">
         <v>8000</v>
@@ -12897,7 +12897,7 @@
         <v>5</v>
       </c>
       <c r="G432" t="n">
-        <v>4.92951726913452</v>
+        <v>4.92951679229736</v>
       </c>
       <c r="H432" t="n">
         <v>1000</v>
@@ -12955,7 +12955,7 @@
         <v>5</v>
       </c>
       <c r="G434" t="n">
-        <v>4.92951726913452</v>
+        <v>4.92951679229736</v>
       </c>
       <c r="H434" t="n">
         <v>7000</v>
@@ -12984,7 +12984,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G435" t="n">
-        <v>4.78163194656372</v>
+        <v>4.78163146972656</v>
       </c>
       <c r="H435" t="n">
         <v>22500</v>
@@ -13013,7 +13013,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G436" t="n">
-        <v>4.91965770721436</v>
+        <v>4.91965818405151</v>
       </c>
       <c r="H436" t="n">
         <v>17500</v>
@@ -13071,7 +13071,7 @@
         <v>5</v>
       </c>
       <c r="G438" t="n">
-        <v>4.92951726913452</v>
+        <v>4.92951679229736</v>
       </c>
       <c r="H438" t="n">
         <v>7500</v>
@@ -13129,7 +13129,7 @@
         <v>5</v>
       </c>
       <c r="G440" t="n">
-        <v>4.92951726913452</v>
+        <v>4.92951679229736</v>
       </c>
       <c r="H440" t="n">
         <v>2000</v>
@@ -13216,7 +13216,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G443" t="n">
-        <v>5.04782485961914</v>
+        <v>5.0478253364563</v>
       </c>
       <c r="H443" t="n">
         <v>5500</v>
@@ -13245,7 +13245,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G444" t="n">
-        <v>5.02810716629028</v>
+        <v>5.02810764312744</v>
       </c>
       <c r="H444" t="n">
         <v>6500</v>
@@ -13332,7 +13332,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G447" t="n">
-        <v>4.85064506530762</v>
+        <v>4.85064554214478</v>
       </c>
       <c r="H447" t="n">
         <v>3500</v>
@@ -13361,7 +13361,7 @@
         <v>5</v>
       </c>
       <c r="G448" t="n">
-        <v>4.92951726913452</v>
+        <v>4.92951679229736</v>
       </c>
       <c r="H448" t="n">
         <v>19060</v>
@@ -13390,7 +13390,7 @@
         <v>5</v>
       </c>
       <c r="G449" t="n">
-        <v>4.92951726913452</v>
+        <v>4.92951679229736</v>
       </c>
       <c r="H449" t="n">
         <v>10200</v>
@@ -13419,7 +13419,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G450" t="n">
-        <v>4.83092641830444</v>
+        <v>4.8309268951416</v>
       </c>
       <c r="H450" t="n">
         <v>30540</v>
@@ -13448,7 +13448,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G451" t="n">
-        <v>4.83092641830444</v>
+        <v>4.8309268951416</v>
       </c>
       <c r="H451" t="n">
         <v>3150</v>
@@ -13477,7 +13477,7 @@
         <v>5</v>
       </c>
       <c r="G452" t="n">
-        <v>4.92951726913452</v>
+        <v>4.92951679229736</v>
       </c>
       <c r="H452" t="n">
         <v>1500</v>
@@ -13506,7 +13506,7 @@
         <v>5</v>
       </c>
       <c r="G453" t="n">
-        <v>4.92951726913452</v>
+        <v>4.92951679229736</v>
       </c>
       <c r="H453" t="n">
         <v>900</v>
@@ -13564,7 +13564,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G455" t="n">
-        <v>4.85064506530762</v>
+        <v>4.85064554214478</v>
       </c>
       <c r="H455" t="n">
         <v>1650</v>
@@ -13593,7 +13593,7 @@
         <v>5</v>
       </c>
       <c r="G456" t="n">
-        <v>4.92951726913452</v>
+        <v>4.92951679229736</v>
       </c>
       <c r="H456" t="n">
         <v>2220</v>
@@ -13622,7 +13622,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G457" t="n">
-        <v>5.04782485961914</v>
+        <v>5.0478253364563</v>
       </c>
       <c r="H457" t="n">
         <v>26170</v>
@@ -13680,7 +13680,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G459" t="n">
-        <v>5.26472520828247</v>
+        <v>5.26472473144531</v>
       </c>
       <c r="H459" t="n">
         <v>23670</v>
@@ -13738,7 +13738,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G461" t="n">
-        <v>5.30416059494019</v>
+        <v>5.30416011810303</v>
       </c>
       <c r="H461" t="n">
         <v>2900</v>
@@ -13825,7 +13825,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G464" t="n">
-        <v>5.04782485961914</v>
+        <v>5.0478253364563</v>
       </c>
       <c r="H464" t="n">
         <v>3580</v>
@@ -13999,7 +13999,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G470" t="n">
-        <v>5.08726167678833</v>
+        <v>5.08726119995117</v>
       </c>
       <c r="H470" t="n">
         <v>2920</v>
@@ -14115,7 +14115,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G474" t="n">
-        <v>4.98867082595825</v>
+        <v>4.98867130279541</v>
       </c>
       <c r="H474" t="n">
         <v>17780</v>
@@ -14144,7 +14144,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G475" t="n">
-        <v>5.14641571044922</v>
+        <v>5.14641618728638</v>
       </c>
       <c r="H475" t="n">
         <v>14970</v>
@@ -14173,7 +14173,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G476" t="n">
-        <v>5.02810716629028</v>
+        <v>5.02810764312744</v>
       </c>
       <c r="H476" t="n">
         <v>2700</v>
@@ -14260,7 +14260,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G479" t="n">
-        <v>5.02810716629028</v>
+        <v>5.02810764312744</v>
       </c>
       <c r="H479" t="n">
         <v>12190</v>
@@ -14289,7 +14289,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G480" t="n">
-        <v>5.14641571044922</v>
+        <v>5.14641618728638</v>
       </c>
       <c r="H480" t="n">
         <v>11670</v>
@@ -14318,7 +14318,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G481" t="n">
-        <v>5.14641571044922</v>
+        <v>5.14641618728638</v>
       </c>
       <c r="H481" t="n">
         <v>7130</v>
@@ -14463,7 +14463,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G486" t="n">
-        <v>5.04782485961914</v>
+        <v>5.0478253364563</v>
       </c>
       <c r="H486" t="n">
         <v>5290</v>
@@ -14550,7 +14550,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G489" t="n">
-        <v>4.98867082595825</v>
+        <v>4.98867130279541</v>
       </c>
       <c r="H489" t="n">
         <v>21530</v>
@@ -14608,7 +14608,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G491" t="n">
-        <v>4.98867082595825</v>
+        <v>4.98867130279541</v>
       </c>
       <c r="H491" t="n">
         <v>28100</v>
@@ -14724,7 +14724,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G495" t="n">
-        <v>5.08726167678833</v>
+        <v>5.08726119995117</v>
       </c>
       <c r="H495" t="n">
         <v>6900</v>
@@ -14811,7 +14811,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G498" t="n">
-        <v>5.02810716629028</v>
+        <v>5.02810764312744</v>
       </c>
       <c r="H498" t="n">
         <v>7720</v>
@@ -14840,7 +14840,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G499" t="n">
-        <v>5.02810716629028</v>
+        <v>5.02810764312744</v>
       </c>
       <c r="H499" t="n">
         <v>4040</v>
@@ -14869,7 +14869,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G500" t="n">
-        <v>5.04782485961914</v>
+        <v>5.0478253364563</v>
       </c>
       <c r="H500" t="n">
         <v>4690</v>
@@ -14927,7 +14927,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G502" t="n">
-        <v>5.08726167678833</v>
+        <v>5.08726119995117</v>
       </c>
       <c r="H502" t="n">
         <v>5550</v>
@@ -14956,7 +14956,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G503" t="n">
-        <v>5.02810716629028</v>
+        <v>5.02810764312744</v>
       </c>
       <c r="H503" t="n">
         <v>14170</v>
@@ -14985,7 +14985,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G504" t="n">
-        <v>4.83092641830444</v>
+        <v>4.8309268951416</v>
       </c>
       <c r="H504" t="n">
         <v>16000</v>
@@ -15014,7 +15014,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G505" t="n">
-        <v>4.98867082595825</v>
+        <v>4.98867130279541</v>
       </c>
       <c r="H505" t="n">
         <v>4800</v>
@@ -15101,7 +15101,7 @@
         <v>5</v>
       </c>
       <c r="G508" t="n">
-        <v>4.92951726913452</v>
+        <v>4.92951679229736</v>
       </c>
       <c r="H508" t="n">
         <v>5700</v>
@@ -15159,7 +15159,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G510" t="n">
-        <v>4.98867082595825</v>
+        <v>4.98867130279541</v>
       </c>
       <c r="H510" t="n">
         <v>1110</v>
@@ -15188,7 +15188,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G511" t="n">
-        <v>5.02810716629028</v>
+        <v>5.02810764312744</v>
       </c>
       <c r="H511" t="n">
         <v>2710</v>
@@ -15217,7 +15217,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G512" t="n">
-        <v>5.08726167678833</v>
+        <v>5.08726119995117</v>
       </c>
       <c r="H512" t="n">
         <v>14440</v>
@@ -15362,7 +15362,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G517" t="n">
-        <v>5.02810716629028</v>
+        <v>5.02810764312744</v>
       </c>
       <c r="H517" t="n">
         <v>80</v>
@@ -15420,7 +15420,7 @@
         <v>5</v>
       </c>
       <c r="G519" t="n">
-        <v>4.92951726913452</v>
+        <v>4.92951679229736</v>
       </c>
       <c r="H519" t="n">
         <v>12340</v>
@@ -15449,7 +15449,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G520" t="n">
-        <v>5.02810716629028</v>
+        <v>5.02810764312744</v>
       </c>
       <c r="H520" t="n">
         <v>18090</v>
@@ -15507,7 +15507,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G522" t="n">
-        <v>5.04782485961914</v>
+        <v>5.0478253364563</v>
       </c>
       <c r="H522" t="n">
         <v>27900</v>
@@ -15536,7 +15536,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G523" t="n">
-        <v>5.02810716629028</v>
+        <v>5.02810764312744</v>
       </c>
       <c r="H523" t="n">
         <v>1940</v>
@@ -15652,7 +15652,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G527" t="n">
-        <v>4.85064506530762</v>
+        <v>4.85064554214478</v>
       </c>
       <c r="H527" t="n">
         <v>12990</v>
@@ -16000,7 +16000,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G539" t="n">
-        <v>4.85064506530762</v>
+        <v>4.85064554214478</v>
       </c>
       <c r="H539" t="n">
         <v>610</v>
@@ -16029,7 +16029,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G540" t="n">
-        <v>4.83092641830444</v>
+        <v>4.8309268951416</v>
       </c>
       <c r="H540" t="n">
         <v>1600</v>
@@ -16087,7 +16087,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G542" t="n">
-        <v>4.86050367355347</v>
+        <v>4.86050319671631</v>
       </c>
       <c r="H542" t="n">
         <v>200</v>
@@ -16174,7 +16174,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G545" t="n">
-        <v>4.83092641830444</v>
+        <v>4.8309268951416</v>
       </c>
       <c r="H545" t="n">
         <v>1200</v>
@@ -49124,6 +49124,35 @@
         <v>12226</v>
       </c>
       <c r="I1681" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1682">
+      <c r="A1682" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1682" s="1" t="n">
+        <v>46321.3333333333</v>
+      </c>
+      <c r="C1682" t="n">
+        <v>3.08999991416931</v>
+      </c>
+      <c r="D1682" t="n">
+        <v>3.1800000667572</v>
+      </c>
+      <c r="E1682" t="n">
+        <v>3.08999991416931</v>
+      </c>
+      <c r="F1682" t="n">
+        <v>3.11999988555908</v>
+      </c>
+      <c r="G1682" t="n">
+        <v>3.11999988555908</v>
+      </c>
+      <c r="H1682" t="n">
+        <v>18768</v>
+      </c>
+      <c r="I1682" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/UD.MI.xlsx
+++ b/data/UD.MI.xlsx
@@ -427,7 +427,7 @@
         <v>1.5</v>
       </c>
       <c r="G2" t="n">
-        <v>1.47885501384735</v>
+        <v>1.47885525226593</v>
       </c>
       <c r="H2" t="n">
         <v>159000</v>
@@ -456,7 +456,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G3" t="n">
-        <v>1.43941903114319</v>
+        <v>1.43941915035248</v>
       </c>
       <c r="H3" t="n">
         <v>78000</v>
@@ -485,7 +485,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G4" t="n">
-        <v>1.45913708209991</v>
+        <v>1.4591372013092</v>
       </c>
       <c r="H4" t="n">
         <v>240000</v>
@@ -543,7 +543,7 @@
         <v>1.56500005722046</v>
       </c>
       <c r="G6" t="n">
-        <v>1.54293882846832</v>
+        <v>1.5429390668869</v>
       </c>
       <c r="H6" t="n">
         <v>55000</v>
@@ -688,7 +688,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G11" t="n">
-        <v>1.56265699863434</v>
+        <v>1.56265687942505</v>
       </c>
       <c r="H11" t="n">
         <v>16000</v>
@@ -717,7 +717,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G12" t="n">
-        <v>1.56758666038513</v>
+        <v>1.56758654117584</v>
       </c>
       <c r="H12" t="n">
         <v>3000</v>
@@ -775,7 +775,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G14" t="n">
-        <v>1.56758666038513</v>
+        <v>1.56758654117584</v>
       </c>
       <c r="H14" t="n">
         <v>1000</v>
@@ -804,7 +804,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G15" t="n">
-        <v>1.64645862579346</v>
+        <v>1.64645874500275</v>
       </c>
       <c r="H15" t="n">
         <v>31000</v>
@@ -833,7 +833,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G16" t="n">
-        <v>1.65631771087646</v>
+        <v>1.65631783008575</v>
       </c>
       <c r="H16" t="n">
         <v>28000</v>
@@ -891,7 +891,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G18" t="n">
-        <v>1.67603600025177</v>
+        <v>1.67603576183319</v>
       </c>
       <c r="H18" t="n">
         <v>36000</v>
@@ -920,7 +920,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G19" t="n">
-        <v>1.67603600025177</v>
+        <v>1.67603576183319</v>
       </c>
       <c r="H19" t="n">
         <v>18000</v>
@@ -949,7 +949,7 @@
         <v>1.67499995231628</v>
       </c>
       <c r="G20" t="n">
-        <v>1.65138816833496</v>
+        <v>1.65138828754425</v>
       </c>
       <c r="H20" t="n">
         <v>17000</v>
@@ -978,7 +978,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G21" t="n">
-        <v>1.65631771087646</v>
+        <v>1.65631783008575</v>
       </c>
       <c r="H21" t="n">
         <v>29000</v>
@@ -1065,7 +1065,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G24" t="n">
-        <v>1.57744550704956</v>
+        <v>1.57744562625885</v>
       </c>
       <c r="H24" t="n">
         <v>2000</v>
@@ -1094,7 +1094,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G25" t="n">
-        <v>1.58730471134186</v>
+        <v>1.58730459213257</v>
       </c>
       <c r="H25" t="n">
         <v>22000</v>
@@ -1123,7 +1123,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G26" t="n">
-        <v>1.57744550704956</v>
+        <v>1.57744562625885</v>
       </c>
       <c r="H26" t="n">
         <v>8000</v>
@@ -1152,7 +1152,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G27" t="n">
-        <v>1.57744550704956</v>
+        <v>1.57744562625885</v>
       </c>
       <c r="H27" t="n">
         <v>3000</v>
@@ -1181,7 +1181,7 @@
         <v>1.59500002861023</v>
       </c>
       <c r="G28" t="n">
-        <v>1.57251608371735</v>
+        <v>1.57251620292664</v>
       </c>
       <c r="H28" t="n">
         <v>22000</v>
@@ -1210,7 +1210,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G29" t="n">
-        <v>1.57744550704956</v>
+        <v>1.57744562625885</v>
       </c>
       <c r="H29" t="n">
         <v>11000</v>
@@ -1239,7 +1239,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G30" t="n">
-        <v>1.62674057483673</v>
+        <v>1.62674069404602</v>
       </c>
       <c r="H30" t="n">
         <v>12000</v>
@@ -1268,7 +1268,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G31" t="n">
-        <v>1.63659977912903</v>
+        <v>1.63659965991974</v>
       </c>
       <c r="H31" t="n">
         <v>32000</v>
@@ -1355,7 +1355,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G34" t="n">
-        <v>1.62674057483673</v>
+        <v>1.62674069404602</v>
       </c>
       <c r="H34" t="n">
         <v>84000</v>
@@ -1384,7 +1384,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G35" t="n">
-        <v>1.62674057483673</v>
+        <v>1.62674069404602</v>
       </c>
       <c r="H35" t="n">
         <v>0</v>
@@ -1413,7 +1413,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G36" t="n">
-        <v>1.65631771087646</v>
+        <v>1.65631783008575</v>
       </c>
       <c r="H36" t="n">
         <v>8000</v>
@@ -1442,7 +1442,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G37" t="n">
-        <v>1.70561289787292</v>
+        <v>1.70561301708221</v>
       </c>
       <c r="H37" t="n">
         <v>16000</v>
@@ -1471,7 +1471,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G38" t="n">
-        <v>1.70561289787292</v>
+        <v>1.70561301708221</v>
       </c>
       <c r="H38" t="n">
         <v>2000</v>
@@ -1500,7 +1500,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G39" t="n">
-        <v>1.67110633850098</v>
+        <v>1.67110657691956</v>
       </c>
       <c r="H39" t="n">
         <v>3000</v>
@@ -1529,7 +1529,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G40" t="n">
-        <v>1.69575393199921</v>
+        <v>1.6957540512085</v>
       </c>
       <c r="H40" t="n">
         <v>7000</v>
@@ -1558,7 +1558,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G41" t="n">
-        <v>1.68589508533478</v>
+        <v>1.6858948469162</v>
       </c>
       <c r="H41" t="n">
         <v>14000</v>
@@ -1587,7 +1587,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G42" t="n">
-        <v>1.74504899978638</v>
+        <v>1.74504911899567</v>
       </c>
       <c r="H42" t="n">
         <v>49000</v>
@@ -1616,7 +1616,7 @@
         <v>1.72500002384186</v>
       </c>
       <c r="G43" t="n">
-        <v>1.70068359375</v>
+        <v>1.70068347454071</v>
       </c>
       <c r="H43" t="n">
         <v>21000</v>
@@ -1645,7 +1645,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G44" t="n">
-        <v>1.65631771087646</v>
+        <v>1.65631783008575</v>
       </c>
       <c r="H44" t="n">
         <v>21000</v>
@@ -1703,7 +1703,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G46" t="n">
-        <v>1.67603600025177</v>
+        <v>1.67603576183319</v>
       </c>
       <c r="H46" t="n">
         <v>12000</v>
@@ -1732,7 +1732,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G47" t="n">
-        <v>1.65631771087646</v>
+        <v>1.65631783008575</v>
       </c>
       <c r="H47" t="n">
         <v>5000</v>
@@ -1761,7 +1761,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G48" t="n">
-        <v>1.65631771087646</v>
+        <v>1.65631783008575</v>
       </c>
       <c r="H48" t="n">
         <v>0</v>
@@ -1790,7 +1790,7 @@
         <v>1.72500002384186</v>
       </c>
       <c r="G49" t="n">
-        <v>1.70068359375</v>
+        <v>1.70068347454071</v>
       </c>
       <c r="H49" t="n">
         <v>18000</v>
@@ -1819,7 +1819,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G50" t="n">
-        <v>1.74997878074646</v>
+        <v>1.74997866153717</v>
       </c>
       <c r="H50" t="n">
         <v>20000</v>
@@ -1877,7 +1877,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G52" t="n">
-        <v>1.74011957645416</v>
+        <v>1.74011969566345</v>
       </c>
       <c r="H52" t="n">
         <v>6000</v>
@@ -1935,7 +1935,7 @@
         <v>1.72500002384186</v>
       </c>
       <c r="G54" t="n">
-        <v>1.70068359375</v>
+        <v>1.70068347454071</v>
       </c>
       <c r="H54" t="n">
         <v>10000</v>
@@ -1964,7 +1964,7 @@
         <v>1.72500002384186</v>
       </c>
       <c r="G55" t="n">
-        <v>1.70068359375</v>
+        <v>1.70068347454071</v>
       </c>
       <c r="H55" t="n">
         <v>15000</v>
@@ -1993,7 +1993,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G56" t="n">
-        <v>1.69575393199921</v>
+        <v>1.6957540512085</v>
       </c>
       <c r="H56" t="n">
         <v>8000</v>
@@ -2022,7 +2022,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G57" t="n">
-        <v>1.67603600025177</v>
+        <v>1.67603576183319</v>
       </c>
       <c r="H57" t="n">
         <v>30000</v>
@@ -2051,7 +2051,7 @@
         <v>1.7150000333786</v>
       </c>
       <c r="G58" t="n">
-        <v>1.6908243894577</v>
+        <v>1.69082450866699</v>
       </c>
       <c r="H58" t="n">
         <v>7000</v>
@@ -2080,7 +2080,7 @@
         <v>1.7150000333786</v>
       </c>
       <c r="G59" t="n">
-        <v>1.6908243894577</v>
+        <v>1.69082450866699</v>
       </c>
       <c r="H59" t="n">
         <v>0</v>
@@ -2109,7 +2109,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G60" t="n">
-        <v>1.71547210216522</v>
+        <v>1.71547198295593</v>
       </c>
       <c r="H60" t="n">
         <v>17000</v>
@@ -2138,7 +2138,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G61" t="n">
-        <v>1.71547210216522</v>
+        <v>1.71547198295593</v>
       </c>
       <c r="H61" t="n">
         <v>4000</v>
@@ -2167,7 +2167,7 @@
         <v>1.67499995231628</v>
       </c>
       <c r="G62" t="n">
-        <v>1.65138816833496</v>
+        <v>1.65138828754425</v>
       </c>
       <c r="H62" t="n">
         <v>8000</v>
@@ -2196,7 +2196,7 @@
         <v>1.68499994277954</v>
       </c>
       <c r="G63" t="n">
-        <v>1.66124725341797</v>
+        <v>1.66124713420868</v>
       </c>
       <c r="H63" t="n">
         <v>5000</v>
@@ -2225,7 +2225,7 @@
         <v>1.67499995231628</v>
       </c>
       <c r="G64" t="n">
-        <v>1.65138816833496</v>
+        <v>1.65138828754425</v>
       </c>
       <c r="H64" t="n">
         <v>9000</v>
@@ -2254,7 +2254,7 @@
         <v>1.67499995231628</v>
       </c>
       <c r="G65" t="n">
-        <v>1.65138816833496</v>
+        <v>1.65138828754425</v>
       </c>
       <c r="H65" t="n">
         <v>0</v>
@@ -2283,7 +2283,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G66" t="n">
-        <v>1.67603600025177</v>
+        <v>1.67603576183319</v>
       </c>
       <c r="H66" t="n">
         <v>3000</v>
@@ -2341,7 +2341,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G68" t="n">
-        <v>1.68589508533478</v>
+        <v>1.6858948469162</v>
       </c>
       <c r="H68" t="n">
         <v>7000</v>
@@ -2370,7 +2370,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G69" t="n">
-        <v>1.65631771087646</v>
+        <v>1.65631783008575</v>
       </c>
       <c r="H69" t="n">
         <v>19000</v>
@@ -2399,7 +2399,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G70" t="n">
-        <v>1.62674057483673</v>
+        <v>1.62674069404602</v>
       </c>
       <c r="H70" t="n">
         <v>41000</v>
@@ -2428,7 +2428,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G71" t="n">
-        <v>1.62674057483673</v>
+        <v>1.62674069404602</v>
       </c>
       <c r="H71" t="n">
         <v>0</v>
@@ -2457,7 +2457,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G72" t="n">
-        <v>1.64645862579346</v>
+        <v>1.64645874500275</v>
       </c>
       <c r="H72" t="n">
         <v>1000</v>
@@ -2486,7 +2486,7 @@
         <v>1.65499997138977</v>
       </c>
       <c r="G73" t="n">
-        <v>1.63167023658752</v>
+        <v>1.63167011737823</v>
       </c>
       <c r="H73" t="n">
         <v>176000</v>
@@ -2515,7 +2515,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G74" t="n">
-        <v>1.64645862579346</v>
+        <v>1.64645874500275</v>
       </c>
       <c r="H74" t="n">
         <v>1000</v>
@@ -2544,7 +2544,7 @@
         <v>1.67499995231628</v>
       </c>
       <c r="G75" t="n">
-        <v>1.65138816833496</v>
+        <v>1.65138828754425</v>
       </c>
       <c r="H75" t="n">
         <v>4000</v>
@@ -2573,7 +2573,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G76" t="n">
-        <v>1.67110633850098</v>
+        <v>1.67110657691956</v>
       </c>
       <c r="H76" t="n">
         <v>2000</v>
@@ -2602,7 +2602,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G77" t="n">
-        <v>1.68589508533478</v>
+        <v>1.6858948469162</v>
       </c>
       <c r="H77" t="n">
         <v>3000</v>
@@ -2631,7 +2631,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G78" t="n">
-        <v>1.64645862579346</v>
+        <v>1.64645874500275</v>
       </c>
       <c r="H78" t="n">
         <v>4000</v>
@@ -2660,7 +2660,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G79" t="n">
-        <v>1.67603600025177</v>
+        <v>1.67603576183319</v>
       </c>
       <c r="H79" t="n">
         <v>16000</v>
@@ -2689,7 +2689,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G80" t="n">
-        <v>1.67603600025177</v>
+        <v>1.67603576183319</v>
       </c>
       <c r="H80" t="n">
         <v>0</v>
@@ -2718,7 +2718,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G81" t="n">
-        <v>1.67603600025177</v>
+        <v>1.67603576183319</v>
       </c>
       <c r="H81" t="n">
         <v>0</v>
@@ -2747,7 +2747,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G82" t="n">
-        <v>1.65631771087646</v>
+        <v>1.65631783008575</v>
       </c>
       <c r="H82" t="n">
         <v>1000</v>
@@ -2776,7 +2776,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G83" t="n">
-        <v>1.65631771087646</v>
+        <v>1.65631783008575</v>
       </c>
       <c r="H83" t="n">
         <v>8000</v>
@@ -2805,7 +2805,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G84" t="n">
-        <v>1.63659977912903</v>
+        <v>1.63659965991974</v>
       </c>
       <c r="H84" t="n">
         <v>8000</v>
@@ -2834,7 +2834,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G85" t="n">
-        <v>1.62674057483673</v>
+        <v>1.62674069404602</v>
       </c>
       <c r="H85" t="n">
         <v>7000</v>
@@ -2863,7 +2863,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G86" t="n">
-        <v>1.62674057483673</v>
+        <v>1.62674069404602</v>
       </c>
       <c r="H86" t="n">
         <v>0</v>
@@ -2892,7 +2892,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G87" t="n">
-        <v>1.56758666038513</v>
+        <v>1.56758654117584</v>
       </c>
       <c r="H87" t="n">
         <v>26000</v>
@@ -2921,7 +2921,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G88" t="n">
-        <v>1.57744550704956</v>
+        <v>1.57744562625885</v>
       </c>
       <c r="H88" t="n">
         <v>94000</v>
@@ -2950,7 +2950,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G89" t="n">
-        <v>1.57744550704956</v>
+        <v>1.57744562625885</v>
       </c>
       <c r="H89" t="n">
         <v>0</v>
@@ -2979,7 +2979,7 @@
         <v>1.59500002861023</v>
       </c>
       <c r="G90" t="n">
-        <v>1.57251608371735</v>
+        <v>1.57251620292664</v>
       </c>
       <c r="H90" t="n">
         <v>4000</v>
@@ -3008,7 +3008,7 @@
         <v>1.59500002861023</v>
       </c>
       <c r="G91" t="n">
-        <v>1.57251608371735</v>
+        <v>1.57251620292664</v>
       </c>
       <c r="H91" t="n">
         <v>2000</v>
@@ -3066,7 +3066,7 @@
         <v>1.59500002861023</v>
       </c>
       <c r="G93" t="n">
-        <v>1.57251608371735</v>
+        <v>1.57251620292664</v>
       </c>
       <c r="H93" t="n">
         <v>9000</v>
@@ -3095,7 +3095,7 @@
         <v>1.59500002861023</v>
       </c>
       <c r="G94" t="n">
-        <v>1.57251608371735</v>
+        <v>1.57251620292664</v>
       </c>
       <c r="H94" t="n">
         <v>11000</v>
@@ -3124,7 +3124,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G95" t="n">
-        <v>1.58730471134186</v>
+        <v>1.58730459213257</v>
       </c>
       <c r="H95" t="n">
         <v>11000</v>
@@ -3182,7 +3182,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G97" t="n">
-        <v>1.58730471134186</v>
+        <v>1.58730459213257</v>
       </c>
       <c r="H97" t="n">
         <v>31000</v>
@@ -3211,7 +3211,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G98" t="n">
-        <v>1.58730471134186</v>
+        <v>1.58730459213257</v>
       </c>
       <c r="H98" t="n">
         <v>11000</v>
@@ -3240,7 +3240,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G99" t="n">
-        <v>1.62674057483673</v>
+        <v>1.62674069404602</v>
       </c>
       <c r="H99" t="n">
         <v>7000</v>
@@ -3269,7 +3269,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G100" t="n">
-        <v>1.62674057483673</v>
+        <v>1.62674069404602</v>
       </c>
       <c r="H100" t="n">
         <v>0</v>
@@ -3298,7 +3298,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G101" t="n">
-        <v>1.65631771087646</v>
+        <v>1.65631783008575</v>
       </c>
       <c r="H101" t="n">
         <v>50000</v>
@@ -3327,7 +3327,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G102" t="n">
-        <v>1.62674057483673</v>
+        <v>1.62674069404602</v>
       </c>
       <c r="H102" t="n">
         <v>9000</v>
@@ -3356,7 +3356,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G103" t="n">
-        <v>1.63659977912903</v>
+        <v>1.63659965991974</v>
       </c>
       <c r="H103" t="n">
         <v>35000</v>
@@ -3385,7 +3385,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G104" t="n">
-        <v>1.63659977912903</v>
+        <v>1.63659965991974</v>
       </c>
       <c r="H104" t="n">
         <v>14000</v>
@@ -3472,7 +3472,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G107" t="n">
-        <v>1.62674057483673</v>
+        <v>1.62674069404602</v>
       </c>
       <c r="H107" t="n">
         <v>3000</v>
@@ -3501,7 +3501,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G108" t="n">
-        <v>1.62674057483673</v>
+        <v>1.62674069404602</v>
       </c>
       <c r="H108" t="n">
         <v>1000</v>
@@ -3559,7 +3559,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G110" t="n">
-        <v>1.67603600025177</v>
+        <v>1.67603576183319</v>
       </c>
       <c r="H110" t="n">
         <v>26000</v>
@@ -3588,7 +3588,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G111" t="n">
-        <v>1.67603600025177</v>
+        <v>1.67603576183319</v>
       </c>
       <c r="H111" t="n">
         <v>53000</v>
@@ -3617,7 +3617,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G112" t="n">
-        <v>1.67603600025177</v>
+        <v>1.67603576183319</v>
       </c>
       <c r="H112" t="n">
         <v>10000</v>
@@ -3646,7 +3646,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G113" t="n">
-        <v>1.67603600025177</v>
+        <v>1.67603576183319</v>
       </c>
       <c r="H113" t="n">
         <v>6000</v>
@@ -3675,7 +3675,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G114" t="n">
-        <v>1.67603600025177</v>
+        <v>1.67603576183319</v>
       </c>
       <c r="H114" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G115" t="n">
-        <v>1.67603600025177</v>
+        <v>1.67603576183319</v>
       </c>
       <c r="H115" t="n">
         <v>22000</v>
@@ -3733,7 +3733,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G116" t="n">
-        <v>1.71547210216522</v>
+        <v>1.71547198295593</v>
       </c>
       <c r="H116" t="n">
         <v>23000</v>
@@ -3762,7 +3762,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G117" t="n">
-        <v>1.68589508533478</v>
+        <v>1.6858948469162</v>
       </c>
       <c r="H117" t="n">
         <v>22000</v>
@@ -3791,7 +3791,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G118" t="n">
-        <v>1.68589508533478</v>
+        <v>1.6858948469162</v>
       </c>
       <c r="H118" t="n">
         <v>0</v>
@@ -3965,7 +3965,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G124" t="n">
-        <v>1.8534984588623</v>
+        <v>1.85349857807159</v>
       </c>
       <c r="H124" t="n">
         <v>32000</v>
@@ -4052,7 +4052,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G127" t="n">
-        <v>1.82392132282257</v>
+        <v>1.82392144203186</v>
       </c>
       <c r="H127" t="n">
         <v>7000</v>
@@ -4081,7 +4081,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G128" t="n">
-        <v>1.82392132282257</v>
+        <v>1.82392144203186</v>
       </c>
       <c r="H128" t="n">
         <v>0</v>
@@ -4110,7 +4110,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G129" t="n">
-        <v>1.82392132282257</v>
+        <v>1.82392144203186</v>
       </c>
       <c r="H129" t="n">
         <v>0</v>
@@ -4139,7 +4139,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G130" t="n">
-        <v>1.83870995044708</v>
+        <v>1.83871006965637</v>
       </c>
       <c r="H130" t="n">
         <v>8000</v>
@@ -4197,7 +4197,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G132" t="n">
-        <v>1.78448522090912</v>
+        <v>1.78448510169983</v>
       </c>
       <c r="H132" t="n">
         <v>9000</v>
@@ -4226,7 +4226,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G133" t="n">
-        <v>1.8534984588623</v>
+        <v>1.85349857807159</v>
       </c>
       <c r="H133" t="n">
         <v>6000</v>
@@ -4255,7 +4255,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G134" t="n">
-        <v>1.8534984588623</v>
+        <v>1.85349857807159</v>
       </c>
       <c r="H134" t="n">
         <v>0</v>
@@ -4284,7 +4284,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G135" t="n">
-        <v>1.8534984588623</v>
+        <v>1.85349857807159</v>
       </c>
       <c r="H135" t="n">
         <v>3000</v>
@@ -4342,7 +4342,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G137" t="n">
-        <v>1.88307571411133</v>
+        <v>1.88307547569275</v>
       </c>
       <c r="H137" t="n">
         <v>1000</v>
@@ -4371,7 +4371,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G138" t="n">
-        <v>1.88307571411133</v>
+        <v>1.88307547569275</v>
       </c>
       <c r="H138" t="n">
         <v>0</v>
@@ -4458,7 +4458,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G141" t="n">
-        <v>1.82392132282257</v>
+        <v>1.82392144203186</v>
       </c>
       <c r="H141" t="n">
         <v>12000</v>
@@ -4487,7 +4487,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G142" t="n">
-        <v>1.82392132282257</v>
+        <v>1.82392144203186</v>
       </c>
       <c r="H142" t="n">
         <v>13000</v>
@@ -4748,7 +4748,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G151" t="n">
-        <v>1.74011957645416</v>
+        <v>1.74011969566345</v>
       </c>
       <c r="H151" t="n">
         <v>30000</v>
@@ -4777,7 +4777,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G152" t="n">
-        <v>1.76969659328461</v>
+        <v>1.7696967124939</v>
       </c>
       <c r="H152" t="n">
         <v>4000</v>
@@ -4806,7 +4806,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G153" t="n">
-        <v>1.74504899978638</v>
+        <v>1.74504911899567</v>
       </c>
       <c r="H153" t="n">
         <v>90000</v>
@@ -4864,7 +4864,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G155" t="n">
-        <v>1.82392132282257</v>
+        <v>1.82392144203186</v>
       </c>
       <c r="H155" t="n">
         <v>13000</v>
@@ -4893,7 +4893,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G156" t="n">
-        <v>1.82392132282257</v>
+        <v>1.82392144203186</v>
       </c>
       <c r="H156" t="n">
         <v>0</v>
@@ -4922,7 +4922,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G157" t="n">
-        <v>1.83870995044708</v>
+        <v>1.83871006965637</v>
       </c>
       <c r="H157" t="n">
         <v>2000</v>
@@ -5067,7 +5067,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G162" t="n">
-        <v>1.74504899978638</v>
+        <v>1.74504911899567</v>
       </c>
       <c r="H162" t="n">
         <v>2000</v>
@@ -5096,7 +5096,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G163" t="n">
-        <v>1.74504899978638</v>
+        <v>1.74504911899567</v>
       </c>
       <c r="H163" t="n">
         <v>0</v>
@@ -5125,7 +5125,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G164" t="n">
-        <v>1.71547210216522</v>
+        <v>1.71547198295593</v>
       </c>
       <c r="H164" t="n">
         <v>6000</v>
@@ -5241,7 +5241,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G168" t="n">
-        <v>1.74997878074646</v>
+        <v>1.74997866153717</v>
       </c>
       <c r="H168" t="n">
         <v>2000</v>
@@ -5299,7 +5299,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G170" t="n">
-        <v>1.83870995044708</v>
+        <v>1.83871006965637</v>
       </c>
       <c r="H170" t="n">
         <v>39000</v>
@@ -5328,7 +5328,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G171" t="n">
-        <v>1.83870995044708</v>
+        <v>1.83871006965637</v>
       </c>
       <c r="H171" t="n">
         <v>0</v>
@@ -5357,7 +5357,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G172" t="n">
-        <v>1.81406247615814</v>
+        <v>1.81406235694885</v>
       </c>
       <c r="H172" t="n">
         <v>3000</v>
@@ -5386,7 +5386,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G173" t="n">
-        <v>1.82885110378265</v>
+        <v>1.82885098457336</v>
       </c>
       <c r="H173" t="n">
         <v>18000</v>
@@ -5415,7 +5415,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G174" t="n">
-        <v>1.82885110378265</v>
+        <v>1.82885098457336</v>
       </c>
       <c r="H174" t="n">
         <v>28000</v>
@@ -5473,7 +5473,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G176" t="n">
-        <v>1.83870995044708</v>
+        <v>1.83871006965637</v>
       </c>
       <c r="H176" t="n">
         <v>47000</v>
@@ -5531,7 +5531,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G178" t="n">
-        <v>1.87814605236053</v>
+        <v>1.87814617156982</v>
       </c>
       <c r="H178" t="n">
         <v>75000</v>
@@ -5560,7 +5560,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G179" t="n">
-        <v>1.88307571411133</v>
+        <v>1.88307547569275</v>
       </c>
       <c r="H179" t="n">
         <v>30000</v>
@@ -5589,7 +5589,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G180" t="n">
-        <v>1.88800501823425</v>
+        <v>1.88800513744354</v>
       </c>
       <c r="H180" t="n">
         <v>73000</v>
@@ -5618,7 +5618,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G181" t="n">
-        <v>1.90279364585876</v>
+        <v>1.90279376506805</v>
       </c>
       <c r="H181" t="n">
         <v>23000</v>
@@ -5647,7 +5647,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G182" t="n">
-        <v>1.91265285015106</v>
+        <v>1.91265273094177</v>
       </c>
       <c r="H182" t="n">
         <v>6000</v>
@@ -5705,7 +5705,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G184" t="n">
-        <v>2.01124310493469</v>
+        <v>2.01124286651611</v>
       </c>
       <c r="H184" t="n">
         <v>3000</v>
@@ -5763,7 +5763,7 @@
         <v>1.99500000476837</v>
       </c>
       <c r="G186" t="n">
-        <v>1.96687734127045</v>
+        <v>1.96687746047974</v>
       </c>
       <c r="H186" t="n">
         <v>28000</v>
@@ -5821,7 +5821,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G188" t="n">
-        <v>2.01124310493469</v>
+        <v>2.01124286651611</v>
       </c>
       <c r="H188" t="n">
         <v>4000</v>
@@ -5850,7 +5850,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G189" t="n">
-        <v>2.01124310493469</v>
+        <v>2.01124286651611</v>
       </c>
       <c r="H189" t="n">
         <v>0</v>
@@ -5995,7 +5995,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G194" t="n">
-        <v>1.92251169681549</v>
+        <v>1.92251181602478</v>
       </c>
       <c r="H194" t="n">
         <v>6000</v>
@@ -6053,7 +6053,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G196" t="n">
-        <v>1.89293456077576</v>
+        <v>1.89293467998505</v>
       </c>
       <c r="H196" t="n">
         <v>23000</v>
@@ -6082,7 +6082,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G197" t="n">
-        <v>1.91265285015106</v>
+        <v>1.91265273094177</v>
       </c>
       <c r="H197" t="n">
         <v>24000</v>
@@ -6111,7 +6111,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G198" t="n">
-        <v>1.91265285015106</v>
+        <v>1.91265273094177</v>
       </c>
       <c r="H198" t="n">
         <v>17000</v>
@@ -6169,7 +6169,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G200" t="n">
-        <v>1.92251169681549</v>
+        <v>1.92251181602478</v>
       </c>
       <c r="H200" t="n">
         <v>18000</v>
@@ -6227,7 +6227,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G202" t="n">
-        <v>1.91265285015106</v>
+        <v>1.91265273094177</v>
       </c>
       <c r="H202" t="n">
         <v>18000</v>
@@ -6256,7 +6256,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G203" t="n">
-        <v>1.90772318840027</v>
+        <v>1.90772306919098</v>
       </c>
       <c r="H203" t="n">
         <v>39000</v>
@@ -6285,7 +6285,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G204" t="n">
-        <v>1.92251169681549</v>
+        <v>1.92251181602478</v>
       </c>
       <c r="H204" t="n">
         <v>8000</v>
@@ -6430,7 +6430,7 @@
         <v>1.9650000333786</v>
       </c>
       <c r="G209" t="n">
-        <v>1.93730032444</v>
+        <v>1.93730020523071</v>
       </c>
       <c r="H209" t="n">
         <v>11000</v>
@@ -6459,7 +6459,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G210" t="n">
-        <v>1.95701849460602</v>
+        <v>1.95701837539673</v>
       </c>
       <c r="H210" t="n">
         <v>16000</v>
@@ -6546,7 +6546,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G213" t="n">
-        <v>1.92251169681549</v>
+        <v>1.92251181602478</v>
       </c>
       <c r="H213" t="n">
         <v>20000</v>
@@ -6575,7 +6575,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G214" t="n">
-        <v>1.92251169681549</v>
+        <v>1.92251181602478</v>
       </c>
       <c r="H214" t="n">
         <v>1000</v>
@@ -6604,7 +6604,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G215" t="n">
-        <v>1.95701849460602</v>
+        <v>1.95701837539673</v>
       </c>
       <c r="H215" t="n">
         <v>1000</v>
@@ -6633,7 +6633,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G216" t="n">
-        <v>1.91265285015106</v>
+        <v>1.91265273094177</v>
       </c>
       <c r="H216" t="n">
         <v>9000</v>
@@ -6691,7 +6691,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G218" t="n">
-        <v>1.89293456077576</v>
+        <v>1.89293467998505</v>
       </c>
       <c r="H218" t="n">
         <v>8000</v>
@@ -6720,7 +6720,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G219" t="n">
-        <v>1.89293456077576</v>
+        <v>1.89293467998505</v>
       </c>
       <c r="H219" t="n">
         <v>1000</v>
@@ -6778,7 +6778,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G221" t="n">
-        <v>1.92251169681549</v>
+        <v>1.92251181602478</v>
       </c>
       <c r="H221" t="n">
         <v>2000</v>
@@ -6807,7 +6807,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G222" t="n">
-        <v>1.92251169681549</v>
+        <v>1.92251181602478</v>
       </c>
       <c r="H222" t="n">
         <v>0</v>
@@ -6836,7 +6836,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G223" t="n">
-        <v>1.92251169681549</v>
+        <v>1.92251181602478</v>
       </c>
       <c r="H223" t="n">
         <v>0</v>
@@ -6865,7 +6865,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G224" t="n">
-        <v>1.92251169681549</v>
+        <v>1.92251181602478</v>
       </c>
       <c r="H224" t="n">
         <v>3000</v>
@@ -6952,7 +6952,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G227" t="n">
-        <v>1.98166596889496</v>
+        <v>1.98166608810425</v>
       </c>
       <c r="H227" t="n">
         <v>10000</v>
@@ -6981,7 +6981,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G228" t="n">
-        <v>2.00138378143311</v>
+        <v>2.00138401985168</v>
       </c>
       <c r="H228" t="n">
         <v>18000</v>
@@ -7126,7 +7126,7 @@
         <v>2.25</v>
       </c>
       <c r="G233" t="n">
-        <v>2.21828269958496</v>
+        <v>2.21828293800354</v>
       </c>
       <c r="H233" t="n">
         <v>47000</v>
@@ -7271,7 +7271,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G238" t="n">
-        <v>2.2380006313324</v>
+        <v>2.23800086975098</v>
       </c>
       <c r="H238" t="n">
         <v>13000</v>
@@ -7300,7 +7300,7 @@
         <v>2.25</v>
       </c>
       <c r="G239" t="n">
-        <v>2.21828269958496</v>
+        <v>2.21828293800354</v>
       </c>
       <c r="H239" t="n">
         <v>19000</v>
@@ -7329,7 +7329,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G240" t="n">
-        <v>2.20842385292053</v>
+        <v>2.20842361450195</v>
       </c>
       <c r="H240" t="n">
         <v>35000</v>
@@ -7503,7 +7503,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G246" t="n">
-        <v>2.28729605674744</v>
+        <v>2.28729581832886</v>
       </c>
       <c r="H246" t="n">
         <v>12000</v>
@@ -7532,7 +7532,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G247" t="n">
-        <v>2.28729605674744</v>
+        <v>2.28729581832886</v>
       </c>
       <c r="H247" t="n">
         <v>2000</v>
@@ -7648,7 +7648,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G251" t="n">
-        <v>2.3365912437439</v>
+        <v>2.33659100532532</v>
       </c>
       <c r="H251" t="n">
         <v>8000</v>
@@ -7677,7 +7677,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G252" t="n">
-        <v>2.3365912437439</v>
+        <v>2.33659100532532</v>
       </c>
       <c r="H252" t="n">
         <v>0</v>
@@ -7706,7 +7706,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G253" t="n">
-        <v>2.40560460090637</v>
+        <v>2.40560436248779</v>
       </c>
       <c r="H253" t="n">
         <v>26000</v>
@@ -7735,7 +7735,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G254" t="n">
-        <v>2.48447680473328</v>
+        <v>2.4844765663147</v>
       </c>
       <c r="H254" t="n">
         <v>14000</v>
@@ -7764,7 +7764,7 @@
         <v>2.5</v>
       </c>
       <c r="G255" t="n">
-        <v>2.46475839614868</v>
+        <v>2.46475887298584</v>
       </c>
       <c r="H255" t="n">
         <v>11000</v>
@@ -7880,7 +7880,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G259" t="n">
-        <v>2.5929262638092</v>
+        <v>2.59292602539062</v>
       </c>
       <c r="H259" t="n">
         <v>5000</v>
@@ -7909,7 +7909,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G260" t="n">
-        <v>2.74081158638</v>
+        <v>2.74081134796143</v>
       </c>
       <c r="H260" t="n">
         <v>51000</v>
@@ -7938,7 +7938,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G261" t="n">
-        <v>2.6619393825531</v>
+        <v>2.66193962097168</v>
       </c>
       <c r="H261" t="n">
         <v>22000</v>
@@ -7967,7 +7967,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G262" t="n">
-        <v>2.78024744987488</v>
+        <v>2.78024792671204</v>
       </c>
       <c r="H262" t="n">
         <v>23000</v>
@@ -7996,7 +7996,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G263" t="n">
-        <v>2.9774284362793</v>
+        <v>2.97742867469788</v>
       </c>
       <c r="H263" t="n">
         <v>41000</v>
@@ -8025,7 +8025,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G264" t="n">
-        <v>3.15489101409912</v>
+        <v>3.1548912525177</v>
       </c>
       <c r="H264" t="n">
         <v>21000</v>
@@ -8054,7 +8054,7 @@
         <v>3</v>
       </c>
       <c r="G265" t="n">
-        <v>2.9577100276947</v>
+        <v>2.95771050453186</v>
       </c>
       <c r="H265" t="n">
         <v>85000</v>
@@ -8083,7 +8083,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G266" t="n">
-        <v>2.87883806228638</v>
+        <v>2.87883830070496</v>
       </c>
       <c r="H266" t="n">
         <v>27000</v>
@@ -8112,7 +8112,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G267" t="n">
-        <v>2.8394021987915</v>
+        <v>2.83940196037292</v>
       </c>
       <c r="H267" t="n">
         <v>62000</v>
@@ -8141,7 +8141,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G268" t="n">
-        <v>2.76052951812744</v>
+        <v>2.76052975654602</v>
       </c>
       <c r="H268" t="n">
         <v>35000</v>
@@ -8170,7 +8170,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G269" t="n">
-        <v>2.76052951812744</v>
+        <v>2.76052975654602</v>
       </c>
       <c r="H269" t="n">
         <v>3000</v>
@@ -8228,7 +8228,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G271" t="n">
-        <v>2.84926080703735</v>
+        <v>2.84926104545593</v>
       </c>
       <c r="H271" t="n">
         <v>21000</v>
@@ -8286,7 +8286,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G273" t="n">
-        <v>2.96756958961487</v>
+        <v>2.96756935119629</v>
       </c>
       <c r="H273" t="n">
         <v>22000</v>
@@ -8315,7 +8315,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G274" t="n">
-        <v>3.26334047317505</v>
+        <v>3.26334023475647</v>
       </c>
       <c r="H274" t="n">
         <v>121000</v>
@@ -8344,7 +8344,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G275" t="n">
-        <v>3.26334047317505</v>
+        <v>3.26334023475647</v>
       </c>
       <c r="H275" t="n">
         <v>74000</v>
@@ -8373,7 +8373,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G276" t="n">
-        <v>3.29291725158691</v>
+        <v>3.29291749000549</v>
       </c>
       <c r="H276" t="n">
         <v>39000</v>
@@ -8402,7 +8402,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G277" t="n">
-        <v>3.17460942268372</v>
+        <v>3.17460918426514</v>
       </c>
       <c r="H277" t="n">
         <v>36000</v>
@@ -8431,7 +8431,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G278" t="n">
-        <v>3.18446803092957</v>
+        <v>3.18446826934814</v>
       </c>
       <c r="H278" t="n">
         <v>19000</v>
@@ -8460,7 +8460,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G279" t="n">
-        <v>3.30277633666992</v>
+        <v>3.3027765750885</v>
       </c>
       <c r="H279" t="n">
         <v>14000</v>
@@ -8489,7 +8489,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G280" t="n">
-        <v>3.25348114967346</v>
+        <v>3.25348138809204</v>
       </c>
       <c r="H280" t="n">
         <v>4000</v>
@@ -8518,7 +8518,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G281" t="n">
-        <v>3.18446803092957</v>
+        <v>3.18446826934814</v>
       </c>
       <c r="H281" t="n">
         <v>10000</v>
@@ -8634,7 +8634,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G285" t="n">
-        <v>3.35207200050354</v>
+        <v>3.35207152366638</v>
       </c>
       <c r="H285" t="n">
         <v>25000</v>
@@ -8663,7 +8663,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G286" t="n">
-        <v>3.49995756149292</v>
+        <v>3.49995732307434</v>
       </c>
       <c r="H286" t="n">
         <v>86000</v>
@@ -8692,7 +8692,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G287" t="n">
-        <v>3.60840702056885</v>
+        <v>3.60840678215027</v>
       </c>
       <c r="H287" t="n">
         <v>86000</v>
@@ -8721,7 +8721,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G288" t="n">
-        <v>3.52953457832336</v>
+        <v>3.52953433990479</v>
       </c>
       <c r="H288" t="n">
         <v>19000</v>
@@ -8837,7 +8837,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G292" t="n">
-        <v>3.64784264564514</v>
+        <v>3.64784288406372</v>
       </c>
       <c r="H292" t="n">
         <v>5000</v>
@@ -8866,7 +8866,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G293" t="n">
-        <v>3.64784264564514</v>
+        <v>3.64784288406372</v>
       </c>
       <c r="H293" t="n">
         <v>16000</v>
@@ -8895,7 +8895,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G294" t="n">
-        <v>3.53939318656921</v>
+        <v>3.53939342498779</v>
       </c>
       <c r="H294" t="n">
         <v>30000</v>
@@ -9011,7 +9011,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G298" t="n">
-        <v>3.49009799957275</v>
+        <v>3.49009823799133</v>
       </c>
       <c r="H298" t="n">
         <v>27000</v>
@@ -9040,7 +9040,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G299" t="n">
-        <v>3.49995756149292</v>
+        <v>3.49995732307434</v>
       </c>
       <c r="H299" t="n">
         <v>12000</v>
@@ -9069,7 +9069,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G300" t="n">
-        <v>3.48023915290833</v>
+        <v>3.4802393913269</v>
       </c>
       <c r="H300" t="n">
         <v>15000</v>
@@ -9098,7 +9098,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G301" t="n">
-        <v>3.49009799957275</v>
+        <v>3.49009823799133</v>
       </c>
       <c r="H301" t="n">
         <v>1000</v>
@@ -9127,7 +9127,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G302" t="n">
-        <v>3.49995756149292</v>
+        <v>3.49995732307434</v>
       </c>
       <c r="H302" t="n">
         <v>12000</v>
@@ -9156,7 +9156,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G303" t="n">
-        <v>3.49009799957275</v>
+        <v>3.49009823799133</v>
       </c>
       <c r="H303" t="n">
         <v>1000</v>
@@ -9185,7 +9185,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G304" t="n">
-        <v>3.52953457832336</v>
+        <v>3.52953433990479</v>
       </c>
       <c r="H304" t="n">
         <v>2000</v>
@@ -9214,7 +9214,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G305" t="n">
-        <v>3.52953457832336</v>
+        <v>3.52953433990479</v>
       </c>
       <c r="H305" t="n">
         <v>1000</v>
@@ -9330,7 +9330,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G309" t="n">
-        <v>4.35769367218018</v>
+        <v>4.35769319534302</v>
       </c>
       <c r="H309" t="n">
         <v>26000</v>
@@ -9417,7 +9417,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G312" t="n">
-        <v>3.99290919303894</v>
+        <v>3.99290943145752</v>
       </c>
       <c r="H312" t="n">
         <v>51000</v>
@@ -9533,7 +9533,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G316" t="n">
-        <v>4.08164072036743</v>
+        <v>4.08164024353027</v>
       </c>
       <c r="H316" t="n">
         <v>8000</v>
@@ -9591,7 +9591,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G318" t="n">
-        <v>4.17037200927734</v>
+        <v>4.17037153244019</v>
       </c>
       <c r="H318" t="n">
         <v>10000</v>
@@ -9649,7 +9649,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G320" t="n">
-        <v>4.2393856048584</v>
+        <v>4.23938512802124</v>
       </c>
       <c r="H320" t="n">
         <v>9000</v>
@@ -9678,7 +9678,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G321" t="n">
-        <v>4.13093519210815</v>
+        <v>4.13093566894531</v>
       </c>
       <c r="H321" t="n">
         <v>4000</v>
@@ -9823,7 +9823,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G326" t="n">
-        <v>4.00276756286621</v>
+        <v>4.00276803970337</v>
       </c>
       <c r="H326" t="n">
         <v>5000</v>
@@ -9910,7 +9910,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G329" t="n">
-        <v>4.02248620986938</v>
+        <v>4.02248573303223</v>
       </c>
       <c r="H329" t="n">
         <v>5000</v>
@@ -10084,7 +10084,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G335" t="n">
-        <v>4.17037200927734</v>
+        <v>4.17037153244019</v>
       </c>
       <c r="H335" t="n">
         <v>3000</v>
@@ -10113,7 +10113,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G336" t="n">
-        <v>4.00276756286621</v>
+        <v>4.00276803970337</v>
       </c>
       <c r="H336" t="n">
         <v>3000</v>
@@ -10142,7 +10142,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G337" t="n">
-        <v>4.00276756286621</v>
+        <v>4.00276803970337</v>
       </c>
       <c r="H337" t="n">
         <v>0</v>
@@ -10374,7 +10374,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G345" t="n">
-        <v>4.08164072036743</v>
+        <v>4.08164024353027</v>
       </c>
       <c r="H345" t="n">
         <v>1000</v>
@@ -10432,7 +10432,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G347" t="n">
-        <v>4.02248620986938</v>
+        <v>4.02248573303223</v>
       </c>
       <c r="H347" t="n">
         <v>3000</v>
@@ -10461,7 +10461,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G348" t="n">
-        <v>4.02248620986938</v>
+        <v>4.02248573303223</v>
       </c>
       <c r="H348" t="n">
         <v>16500</v>
@@ -10519,7 +10519,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G350" t="n">
-        <v>4.2393856048584</v>
+        <v>4.23938512802124</v>
       </c>
       <c r="H350" t="n">
         <v>24000</v>
@@ -10548,7 +10548,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G351" t="n">
-        <v>4.2393856048584</v>
+        <v>4.23938512802124</v>
       </c>
       <c r="H351" t="n">
         <v>4500</v>
@@ -10577,7 +10577,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G352" t="n">
-        <v>4.19994878768921</v>
+        <v>4.19994926452637</v>
       </c>
       <c r="H352" t="n">
         <v>8000</v>
@@ -10606,7 +10606,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G353" t="n">
-        <v>4.13093519210815</v>
+        <v>4.13093566894531</v>
       </c>
       <c r="H353" t="n">
         <v>9000</v>
@@ -10664,7 +10664,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G355" t="n">
-        <v>4.08164072036743</v>
+        <v>4.08164024353027</v>
       </c>
       <c r="H355" t="n">
         <v>21000</v>
@@ -10838,7 +10838,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G361" t="n">
-        <v>4.08164072036743</v>
+        <v>4.08164024353027</v>
       </c>
       <c r="H361" t="n">
         <v>10500</v>
@@ -10896,7 +10896,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G363" t="n">
-        <v>4.12107563018799</v>
+        <v>4.12107610702515</v>
       </c>
       <c r="H363" t="n">
         <v>500</v>
@@ -10925,7 +10925,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G364" t="n">
-        <v>4.12107563018799</v>
+        <v>4.12107610702515</v>
       </c>
       <c r="H364" t="n">
         <v>0</v>
@@ -10954,7 +10954,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G365" t="n">
-        <v>4.12107563018799</v>
+        <v>4.12107610702515</v>
       </c>
       <c r="H365" t="n">
         <v>0</v>
@@ -11070,7 +11070,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G369" t="n">
-        <v>4.08164072036743</v>
+        <v>4.08164024353027</v>
       </c>
       <c r="H369" t="n">
         <v>1500</v>
@@ -11128,7 +11128,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G371" t="n">
-        <v>4.01262807846069</v>
+        <v>4.01262712478638</v>
       </c>
       <c r="H371" t="n">
         <v>6000</v>
@@ -11157,7 +11157,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G372" t="n">
-        <v>4.08164072036743</v>
+        <v>4.08164024353027</v>
       </c>
       <c r="H372" t="n">
         <v>8500</v>
@@ -11273,7 +11273,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G376" t="n">
-        <v>4.19994878768921</v>
+        <v>4.19994926452637</v>
       </c>
       <c r="H376" t="n">
         <v>7500</v>
@@ -11302,7 +11302,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G377" t="n">
-        <v>4.22952604293823</v>
+        <v>4.22952556610107</v>
       </c>
       <c r="H377" t="n">
         <v>3500</v>
@@ -11331,7 +11331,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G378" t="n">
-        <v>4.27882099151611</v>
+        <v>4.27882146835327</v>
       </c>
       <c r="H378" t="n">
         <v>7000</v>
@@ -11418,7 +11418,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G381" t="n">
-        <v>4.2591028213501</v>
+        <v>4.25910329818726</v>
       </c>
       <c r="H381" t="n">
         <v>2500</v>
@@ -11476,7 +11476,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G383" t="n">
-        <v>4.30839824676514</v>
+        <v>4.30839776992798</v>
       </c>
       <c r="H383" t="n">
         <v>2500</v>
@@ -11534,7 +11534,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G385" t="n">
-        <v>4.36755228042603</v>
+        <v>4.36755180358887</v>
       </c>
       <c r="H385" t="n">
         <v>4000</v>
@@ -11563,7 +11563,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G386" t="n">
-        <v>4.30839824676514</v>
+        <v>4.30839776992798</v>
       </c>
       <c r="H386" t="n">
         <v>255000</v>
@@ -11592,7 +11592,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G387" t="n">
-        <v>4.36755228042603</v>
+        <v>4.36755180358887</v>
       </c>
       <c r="H387" t="n">
         <v>6000</v>
@@ -11621,7 +11621,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G388" t="n">
-        <v>4.36755228042603</v>
+        <v>4.36755180358887</v>
       </c>
       <c r="H388" t="n">
         <v>13500</v>
@@ -11708,7 +11708,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G391" t="n">
-        <v>4.30839824676514</v>
+        <v>4.30839776992798</v>
       </c>
       <c r="H391" t="n">
         <v>34000</v>
@@ -11853,7 +11853,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G396" t="n">
-        <v>4.22952604293823</v>
+        <v>4.22952556610107</v>
       </c>
       <c r="H396" t="n">
         <v>1500</v>
@@ -12027,7 +12027,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G402" t="n">
-        <v>4.19994878768921</v>
+        <v>4.19994926452637</v>
       </c>
       <c r="H402" t="n">
         <v>23500</v>
@@ -12114,7 +12114,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G405" t="n">
-        <v>4.38726997375488</v>
+        <v>4.38727045059204</v>
       </c>
       <c r="H405" t="n">
         <v>13000</v>
@@ -12172,7 +12172,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G407" t="n">
-        <v>4.38726997375488</v>
+        <v>4.38727045059204</v>
       </c>
       <c r="H407" t="n">
         <v>6000</v>
@@ -12201,7 +12201,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G408" t="n">
-        <v>4.38726997375488</v>
+        <v>4.38727045059204</v>
       </c>
       <c r="H408" t="n">
         <v>85000</v>
@@ -12259,7 +12259,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G410" t="n">
-        <v>4.6337456703186</v>
+        <v>4.63374614715576</v>
       </c>
       <c r="H410" t="n">
         <v>92000</v>
@@ -12288,7 +12288,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G411" t="n">
-        <v>5.0478253364563</v>
+        <v>5.04782581329346</v>
       </c>
       <c r="H411" t="n">
         <v>104000</v>
@@ -12317,7 +12317,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G412" t="n">
-        <v>5.30416011810303</v>
+        <v>5.30416059494019</v>
       </c>
       <c r="H412" t="n">
         <v>82500</v>
@@ -12346,7 +12346,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G413" t="n">
-        <v>5.24500608444214</v>
+        <v>5.2450065612793</v>
       </c>
       <c r="H413" t="n">
         <v>33000</v>
@@ -12375,7 +12375,7 @@
         <v>5</v>
       </c>
       <c r="G414" t="n">
-        <v>4.92951679229736</v>
+        <v>4.92951774597168</v>
       </c>
       <c r="H414" t="n">
         <v>45500</v>
@@ -12404,7 +12404,7 @@
         <v>5</v>
       </c>
       <c r="G415" t="n">
-        <v>4.92951679229736</v>
+        <v>4.92951774597168</v>
       </c>
       <c r="H415" t="n">
         <v>14500</v>
@@ -12433,7 +12433,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G416" t="n">
-        <v>4.96895360946655</v>
+        <v>4.96895313262939</v>
       </c>
       <c r="H416" t="n">
         <v>6000</v>
@@ -12462,7 +12462,7 @@
         <v>5</v>
       </c>
       <c r="G417" t="n">
-        <v>4.92951679229736</v>
+        <v>4.92951774597168</v>
       </c>
       <c r="H417" t="n">
         <v>7500</v>
@@ -12549,7 +12549,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G420" t="n">
-        <v>5.00838994979858</v>
+        <v>5.00838899612427</v>
       </c>
       <c r="H420" t="n">
         <v>4500</v>
@@ -12578,7 +12578,7 @@
         <v>5</v>
       </c>
       <c r="G421" t="n">
-        <v>4.92951679229736</v>
+        <v>4.92951774597168</v>
       </c>
       <c r="H421" t="n">
         <v>8500</v>
@@ -12607,7 +12607,7 @@
         <v>5</v>
       </c>
       <c r="G422" t="n">
-        <v>4.92951679229736</v>
+        <v>4.92951774597168</v>
       </c>
       <c r="H422" t="n">
         <v>9500</v>
@@ -12636,7 +12636,7 @@
         <v>5</v>
       </c>
       <c r="G423" t="n">
-        <v>4.92951679229736</v>
+        <v>4.92951774597168</v>
       </c>
       <c r="H423" t="n">
         <v>38500</v>
@@ -12665,7 +12665,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G424" t="n">
-        <v>4.89008140563965</v>
+        <v>4.89008092880249</v>
       </c>
       <c r="H424" t="n">
         <v>11000</v>
@@ -12781,7 +12781,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G428" t="n">
-        <v>5.00838994979858</v>
+        <v>5.00838899612427</v>
       </c>
       <c r="H428" t="n">
         <v>2500</v>
@@ -12810,7 +12810,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G429" t="n">
-        <v>5.1266975402832</v>
+        <v>5.12669801712036</v>
       </c>
       <c r="H429" t="n">
         <v>7000</v>
@@ -12839,7 +12839,7 @@
         <v>5</v>
       </c>
       <c r="G430" t="n">
-        <v>4.92951679229736</v>
+        <v>4.92951774597168</v>
       </c>
       <c r="H430" t="n">
         <v>8500</v>
@@ -12897,7 +12897,7 @@
         <v>5</v>
       </c>
       <c r="G432" t="n">
-        <v>4.92951679229736</v>
+        <v>4.92951774597168</v>
       </c>
       <c r="H432" t="n">
         <v>1000</v>
@@ -12926,7 +12926,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G433" t="n">
-        <v>4.88022232055664</v>
+        <v>4.88022184371948</v>
       </c>
       <c r="H433" t="n">
         <v>500</v>
@@ -12955,7 +12955,7 @@
         <v>5</v>
       </c>
       <c r="G434" t="n">
-        <v>4.92951679229736</v>
+        <v>4.92951774597168</v>
       </c>
       <c r="H434" t="n">
         <v>7000</v>
@@ -12984,7 +12984,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G435" t="n">
-        <v>4.78163146972656</v>
+        <v>4.78163194656372</v>
       </c>
       <c r="H435" t="n">
         <v>22500</v>
@@ -13071,7 +13071,7 @@
         <v>5</v>
       </c>
       <c r="G438" t="n">
-        <v>4.92951679229736</v>
+        <v>4.92951774597168</v>
       </c>
       <c r="H438" t="n">
         <v>7500</v>
@@ -13100,7 +13100,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G439" t="n">
-        <v>4.89008140563965</v>
+        <v>4.89008092880249</v>
       </c>
       <c r="H439" t="n">
         <v>4500</v>
@@ -13129,7 +13129,7 @@
         <v>5</v>
       </c>
       <c r="G440" t="n">
-        <v>4.92951679229736</v>
+        <v>4.92951774597168</v>
       </c>
       <c r="H440" t="n">
         <v>2000</v>
@@ -13158,7 +13158,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G441" t="n">
-        <v>4.89008140563965</v>
+        <v>4.89008092880249</v>
       </c>
       <c r="H441" t="n">
         <v>2000</v>
@@ -13216,7 +13216,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G443" t="n">
-        <v>5.0478253364563</v>
+        <v>5.04782581329346</v>
       </c>
       <c r="H443" t="n">
         <v>5500</v>
@@ -13274,7 +13274,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G445" t="n">
-        <v>4.96895360946655</v>
+        <v>4.96895313262939</v>
       </c>
       <c r="H445" t="n">
         <v>2500</v>
@@ -13303,7 +13303,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G446" t="n">
-        <v>4.94923543930054</v>
+        <v>4.9492359161377</v>
       </c>
       <c r="H446" t="n">
         <v>6500</v>
@@ -13361,7 +13361,7 @@
         <v>5</v>
       </c>
       <c r="G448" t="n">
-        <v>4.92951679229736</v>
+        <v>4.92951774597168</v>
       </c>
       <c r="H448" t="n">
         <v>19060</v>
@@ -13390,7 +13390,7 @@
         <v>5</v>
       </c>
       <c r="G449" t="n">
-        <v>4.92951679229736</v>
+        <v>4.92951774597168</v>
       </c>
       <c r="H449" t="n">
         <v>10200</v>
@@ -13419,7 +13419,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G450" t="n">
-        <v>4.8309268951416</v>
+        <v>4.83092737197876</v>
       </c>
       <c r="H450" t="n">
         <v>30540</v>
@@ -13448,7 +13448,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G451" t="n">
-        <v>4.8309268951416</v>
+        <v>4.83092737197876</v>
       </c>
       <c r="H451" t="n">
         <v>3150</v>
@@ -13477,7 +13477,7 @@
         <v>5</v>
       </c>
       <c r="G452" t="n">
-        <v>4.92951679229736</v>
+        <v>4.92951774597168</v>
       </c>
       <c r="H452" t="n">
         <v>1500</v>
@@ -13506,7 +13506,7 @@
         <v>5</v>
       </c>
       <c r="G453" t="n">
-        <v>4.92951679229736</v>
+        <v>4.92951774597168</v>
       </c>
       <c r="H453" t="n">
         <v>900</v>
@@ -13593,7 +13593,7 @@
         <v>5</v>
       </c>
       <c r="G456" t="n">
-        <v>4.92951679229736</v>
+        <v>4.92951774597168</v>
       </c>
       <c r="H456" t="n">
         <v>2220</v>
@@ -13622,7 +13622,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G457" t="n">
-        <v>5.0478253364563</v>
+        <v>5.04782581329346</v>
       </c>
       <c r="H457" t="n">
         <v>26170</v>
@@ -13709,7 +13709,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G460" t="n">
-        <v>5.34359693527222</v>
+        <v>5.34359645843506</v>
       </c>
       <c r="H460" t="n">
         <v>6980</v>
@@ -13738,7 +13738,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G461" t="n">
-        <v>5.30416011810303</v>
+        <v>5.30416059494019</v>
       </c>
       <c r="H461" t="n">
         <v>2900</v>
@@ -13825,7 +13825,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G464" t="n">
-        <v>5.0478253364563</v>
+        <v>5.04782581329346</v>
       </c>
       <c r="H464" t="n">
         <v>3580</v>
@@ -13854,7 +13854,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G465" t="n">
-        <v>5.16613388061523</v>
+        <v>5.16613435745239</v>
       </c>
       <c r="H465" t="n">
         <v>650</v>
@@ -13883,7 +13883,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G466" t="n">
-        <v>5.1266975402832</v>
+        <v>5.12669801712036</v>
       </c>
       <c r="H466" t="n">
         <v>7070</v>
@@ -13912,7 +13912,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G467" t="n">
-        <v>5.1266975402832</v>
+        <v>5.12669801712036</v>
       </c>
       <c r="H467" t="n">
         <v>200</v>
@@ -13941,7 +13941,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G468" t="n">
-        <v>5.16613388061523</v>
+        <v>5.16613435745239</v>
       </c>
       <c r="H468" t="n">
         <v>10280</v>
@@ -14086,7 +14086,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G473" t="n">
-        <v>5.20557069778442</v>
+        <v>5.20557022094727</v>
       </c>
       <c r="H473" t="n">
         <v>9950</v>
@@ -14144,7 +14144,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G475" t="n">
-        <v>5.14641618728638</v>
+        <v>5.14641571044922</v>
       </c>
       <c r="H475" t="n">
         <v>14970</v>
@@ -14202,7 +14202,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G477" t="n">
-        <v>5.00838994979858</v>
+        <v>5.00838899612427</v>
       </c>
       <c r="H477" t="n">
         <v>1250</v>
@@ -14231,7 +14231,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G478" t="n">
-        <v>4.96895360946655</v>
+        <v>4.96895313262939</v>
       </c>
       <c r="H478" t="n">
         <v>3060</v>
@@ -14289,7 +14289,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G480" t="n">
-        <v>5.14641618728638</v>
+        <v>5.14641571044922</v>
       </c>
       <c r="H480" t="n">
         <v>11670</v>
@@ -14318,7 +14318,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G481" t="n">
-        <v>5.14641618728638</v>
+        <v>5.14641571044922</v>
       </c>
       <c r="H481" t="n">
         <v>7130</v>
@@ -14376,7 +14376,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G483" t="n">
-        <v>5.1266975402832</v>
+        <v>5.12669801712036</v>
       </c>
       <c r="H483" t="n">
         <v>4620</v>
@@ -14405,7 +14405,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G484" t="n">
-        <v>5.1266975402832</v>
+        <v>5.12669801712036</v>
       </c>
       <c r="H484" t="n">
         <v>6620</v>
@@ -14434,7 +14434,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G485" t="n">
-        <v>5.1266975402832</v>
+        <v>5.12669801712036</v>
       </c>
       <c r="H485" t="n">
         <v>11880</v>
@@ -14463,7 +14463,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G486" t="n">
-        <v>5.0478253364563</v>
+        <v>5.04782581329346</v>
       </c>
       <c r="H486" t="n">
         <v>5290</v>
@@ -14492,7 +14492,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G487" t="n">
-        <v>5.16613388061523</v>
+        <v>5.16613435745239</v>
       </c>
       <c r="H487" t="n">
         <v>18380</v>
@@ -14521,7 +14521,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G488" t="n">
-        <v>5.06754398345947</v>
+        <v>5.06754350662231</v>
       </c>
       <c r="H488" t="n">
         <v>3010</v>
@@ -14579,7 +14579,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G490" t="n">
-        <v>5.1266975402832</v>
+        <v>5.12669801712036</v>
       </c>
       <c r="H490" t="n">
         <v>26550</v>
@@ -14637,7 +14637,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G492" t="n">
-        <v>4.96895360946655</v>
+        <v>4.96895313262939</v>
       </c>
       <c r="H492" t="n">
         <v>10980</v>
@@ -14666,7 +14666,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G493" t="n">
-        <v>5.16613388061523</v>
+        <v>5.16613435745239</v>
       </c>
       <c r="H493" t="n">
         <v>5990</v>
@@ -14753,7 +14753,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G496" t="n">
-        <v>4.94923543930054</v>
+        <v>4.9492359161377</v>
       </c>
       <c r="H496" t="n">
         <v>6100</v>
@@ -14869,7 +14869,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G500" t="n">
-        <v>5.0478253364563</v>
+        <v>5.04782581329346</v>
       </c>
       <c r="H500" t="n">
         <v>4690</v>
@@ -14898,7 +14898,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G501" t="n">
-        <v>5.06754398345947</v>
+        <v>5.06754350662231</v>
       </c>
       <c r="H501" t="n">
         <v>11540</v>
@@ -14985,7 +14985,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G504" t="n">
-        <v>4.8309268951416</v>
+        <v>4.83092737197876</v>
       </c>
       <c r="H504" t="n">
         <v>16000</v>
@@ -15043,7 +15043,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G506" t="n">
-        <v>5.1266975402832</v>
+        <v>5.12669801712036</v>
       </c>
       <c r="H506" t="n">
         <v>5270</v>
@@ -15101,7 +15101,7 @@
         <v>5</v>
       </c>
       <c r="G508" t="n">
-        <v>4.92951679229736</v>
+        <v>4.92951774597168</v>
       </c>
       <c r="H508" t="n">
         <v>5700</v>
@@ -15130,7 +15130,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G509" t="n">
-        <v>5.06754398345947</v>
+        <v>5.06754350662231</v>
       </c>
       <c r="H509" t="n">
         <v>940</v>
@@ -15246,7 +15246,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G513" t="n">
-        <v>5.00838994979858</v>
+        <v>5.00838899612427</v>
       </c>
       <c r="H513" t="n">
         <v>10130</v>
@@ -15275,7 +15275,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G514" t="n">
-        <v>4.96895360946655</v>
+        <v>4.96895313262939</v>
       </c>
       <c r="H514" t="n">
         <v>2590</v>
@@ -15304,7 +15304,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G515" t="n">
-        <v>4.94923543930054</v>
+        <v>4.9492359161377</v>
       </c>
       <c r="H515" t="n">
         <v>3820</v>
@@ -15333,7 +15333,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G516" t="n">
-        <v>5.00838994979858</v>
+        <v>5.00838899612427</v>
       </c>
       <c r="H516" t="n">
         <v>640</v>
@@ -15391,7 +15391,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G518" t="n">
-        <v>5.00838994979858</v>
+        <v>5.00838899612427</v>
       </c>
       <c r="H518" t="n">
         <v>3020</v>
@@ -15420,7 +15420,7 @@
         <v>5</v>
       </c>
       <c r="G519" t="n">
-        <v>4.92951679229736</v>
+        <v>4.92951774597168</v>
       </c>
       <c r="H519" t="n">
         <v>12340</v>
@@ -15478,7 +15478,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G521" t="n">
-        <v>5.20557069778442</v>
+        <v>5.20557022094727</v>
       </c>
       <c r="H521" t="n">
         <v>4650</v>
@@ -15507,7 +15507,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G522" t="n">
-        <v>5.0478253364563</v>
+        <v>5.04782581329346</v>
       </c>
       <c r="H522" t="n">
         <v>27900</v>
@@ -15565,7 +15565,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G524" t="n">
-        <v>4.94923543930054</v>
+        <v>4.9492359161377</v>
       </c>
       <c r="H524" t="n">
         <v>6910</v>
@@ -15594,7 +15594,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G525" t="n">
-        <v>4.88022232055664</v>
+        <v>4.88022184371948</v>
       </c>
       <c r="H525" t="n">
         <v>11030</v>
@@ -15623,7 +15623,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G526" t="n">
-        <v>5.00838994979858</v>
+        <v>5.00838899612427</v>
       </c>
       <c r="H526" t="n">
         <v>2400</v>
@@ -15681,7 +15681,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G528" t="n">
-        <v>4.80135011672974</v>
+        <v>4.80134963989258</v>
       </c>
       <c r="H528" t="n">
         <v>15650</v>
@@ -15739,7 +15739,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G530" t="n">
-        <v>4.73233652114868</v>
+        <v>4.73233699798584</v>
       </c>
       <c r="H530" t="n">
         <v>6730</v>
@@ -15768,7 +15768,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G531" t="n">
-        <v>4.80135011672974</v>
+        <v>4.80134963989258</v>
       </c>
       <c r="H531" t="n">
         <v>6500</v>
@@ -15855,7 +15855,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G534" t="n">
-        <v>4.73233652114868</v>
+        <v>4.73233699798584</v>
       </c>
       <c r="H534" t="n">
         <v>13910</v>
@@ -15884,7 +15884,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G535" t="n">
-        <v>4.73233652114868</v>
+        <v>4.73233699798584</v>
       </c>
       <c r="H535" t="n">
         <v>3100</v>
@@ -15942,7 +15942,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G537" t="n">
-        <v>4.73233652114868</v>
+        <v>4.73233699798584</v>
       </c>
       <c r="H537" t="n">
         <v>2420</v>
@@ -15971,7 +15971,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G538" t="n">
-        <v>4.8999400138855</v>
+        <v>4.89993953704834</v>
       </c>
       <c r="H538" t="n">
         <v>2830</v>
@@ -16029,7 +16029,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G540" t="n">
-        <v>4.8309268951416</v>
+        <v>4.83092737197876</v>
       </c>
       <c r="H540" t="n">
         <v>1600</v>
@@ -16058,7 +16058,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G541" t="n">
-        <v>4.94923543930054</v>
+        <v>4.9492359161377</v>
       </c>
       <c r="H541" t="n">
         <v>2830</v>
@@ -16087,7 +16087,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G542" t="n">
-        <v>4.86050319671631</v>
+        <v>4.86050415039062</v>
       </c>
       <c r="H542" t="n">
         <v>200</v>
@@ -16174,7 +16174,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G545" t="n">
-        <v>4.8309268951416</v>
+        <v>4.83092737197876</v>
       </c>
       <c r="H545" t="n">
         <v>1200</v>
@@ -16232,7 +16232,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G547" t="n">
-        <v>4.62362051010132</v>
+        <v>4.62362098693848</v>
       </c>
       <c r="H547" t="n">
         <v>10330</v>
@@ -16261,7 +16261,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G548" t="n">
-        <v>4.57422351837158</v>
+        <v>4.57422304153442</v>
       </c>
       <c r="H548" t="n">
         <v>17160</v>
@@ -16377,7 +16377,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G552" t="n">
-        <v>4.78169345855713</v>
+        <v>4.78169393539429</v>
       </c>
       <c r="H552" t="n">
         <v>1640</v>
@@ -16406,7 +16406,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G553" t="n">
-        <v>4.78169345855713</v>
+        <v>4.78169393539429</v>
       </c>
       <c r="H553" t="n">
         <v>0</v>
@@ -16435,7 +16435,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G554" t="n">
-        <v>4.78169345855713</v>
+        <v>4.78169393539429</v>
       </c>
       <c r="H554" t="n">
         <v>0</v>
@@ -16464,7 +16464,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G555" t="n">
-        <v>4.86073017120361</v>
+        <v>4.86072969436646</v>
       </c>
       <c r="H555" t="n">
         <v>50</v>
@@ -16609,7 +16609,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G560" t="n">
-        <v>4.80145263671875</v>
+        <v>4.80145215988159</v>
       </c>
       <c r="H560" t="n">
         <v>760</v>
@@ -16696,7 +16696,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G563" t="n">
-        <v>4.84097051620483</v>
+        <v>4.84097099304199</v>
       </c>
       <c r="H563" t="n">
         <v>4490</v>
@@ -16725,7 +16725,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G564" t="n">
-        <v>4.84097051620483</v>
+        <v>4.84097099304199</v>
       </c>
       <c r="H564" t="n">
         <v>0</v>
@@ -16754,7 +16754,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G565" t="n">
-        <v>4.84097051620483</v>
+        <v>4.84097099304199</v>
       </c>
       <c r="H565" t="n">
         <v>0</v>
@@ -16783,7 +16783,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G566" t="n">
-        <v>4.84097051620483</v>
+        <v>4.84097099304199</v>
       </c>
       <c r="H566" t="n">
         <v>0</v>
@@ -16812,7 +16812,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G567" t="n">
-        <v>4.82121181488037</v>
+        <v>4.82121133804321</v>
       </c>
       <c r="H567" t="n">
         <v>2600</v>
@@ -16841,7 +16841,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G568" t="n">
-        <v>4.82121181488037</v>
+        <v>4.82121133804321</v>
       </c>
       <c r="H568" t="n">
         <v>0</v>
@@ -16870,7 +16870,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G569" t="n">
-        <v>4.82121181488037</v>
+        <v>4.82121133804321</v>
       </c>
       <c r="H569" t="n">
         <v>50</v>
@@ -16899,7 +16899,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G570" t="n">
-        <v>4.82121181488037</v>
+        <v>4.82121133804321</v>
       </c>
       <c r="H570" t="n">
         <v>0</v>
@@ -16928,7 +16928,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G571" t="n">
-        <v>4.84097051620483</v>
+        <v>4.84097099304199</v>
       </c>
       <c r="H571" t="n">
         <v>2630</v>
@@ -16957,7 +16957,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G572" t="n">
-        <v>4.55446434020996</v>
+        <v>4.55446481704712</v>
       </c>
       <c r="H572" t="n">
         <v>2940</v>
@@ -17015,7 +17015,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G574" t="n">
-        <v>4.42603063583374</v>
+        <v>4.42603015899658</v>
       </c>
       <c r="H574" t="n">
         <v>2090</v>
@@ -17160,7 +17160,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G579" t="n">
-        <v>4.2778377532959</v>
+        <v>4.27783727645874</v>
       </c>
       <c r="H579" t="n">
         <v>2300</v>
@@ -17218,7 +17218,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G581" t="n">
-        <v>4.40627145767212</v>
+        <v>4.40627098083496</v>
       </c>
       <c r="H581" t="n">
         <v>1200</v>
@@ -17305,7 +17305,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G584" t="n">
-        <v>4.78169345855713</v>
+        <v>4.78169393539429</v>
       </c>
       <c r="H584" t="n">
         <v>3210</v>
@@ -17421,7 +17421,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G588" t="n">
-        <v>4.49518775939941</v>
+        <v>4.49518728256226</v>
       </c>
       <c r="H588" t="n">
         <v>1140</v>
@@ -17508,7 +17508,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G591" t="n">
-        <v>4.34699440002441</v>
+        <v>4.34699392318726</v>
       </c>
       <c r="H591" t="n">
         <v>420</v>
@@ -17537,7 +17537,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G592" t="n">
-        <v>4.34699440002441</v>
+        <v>4.34699392318726</v>
       </c>
       <c r="H592" t="n">
         <v>35740</v>
@@ -17566,7 +17566,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G593" t="n">
-        <v>4.34699440002441</v>
+        <v>4.34699392318726</v>
       </c>
       <c r="H593" t="n">
         <v>10500</v>
@@ -17682,7 +17682,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G597" t="n">
-        <v>4.40627145767212</v>
+        <v>4.40627098083496</v>
       </c>
       <c r="H597" t="n">
         <v>1930</v>
@@ -17711,7 +17711,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G598" t="n">
-        <v>4.49518775939941</v>
+        <v>4.49518728256226</v>
       </c>
       <c r="H598" t="n">
         <v>1400</v>
@@ -17885,7 +17885,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G604" t="n">
-        <v>4.84097051620483</v>
+        <v>4.84097099304199</v>
       </c>
       <c r="H604" t="n">
         <v>7020</v>
@@ -17972,7 +17972,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G607" t="n">
-        <v>4.70265769958496</v>
+        <v>4.7026572227478</v>
       </c>
       <c r="H607" t="n">
         <v>2440</v>
@@ -18001,7 +18001,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G608" t="n">
-        <v>4.70265769958496</v>
+        <v>4.7026572227478</v>
       </c>
       <c r="H608" t="n">
         <v>8050</v>
@@ -18030,7 +18030,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G609" t="n">
-        <v>4.81133222579956</v>
+        <v>4.8113317489624</v>
       </c>
       <c r="H609" t="n">
         <v>1910</v>
@@ -18059,7 +18059,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G610" t="n">
-        <v>4.84097051620483</v>
+        <v>4.84097099304199</v>
       </c>
       <c r="H610" t="n">
         <v>3200</v>
@@ -18088,7 +18088,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G611" t="n">
-        <v>4.72241687774658</v>
+        <v>4.72241640090942</v>
       </c>
       <c r="H611" t="n">
         <v>4980</v>
@@ -18146,7 +18146,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G613" t="n">
-        <v>4.78169345855713</v>
+        <v>4.78169393539429</v>
       </c>
       <c r="H613" t="n">
         <v>1500</v>
@@ -18175,7 +18175,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G614" t="n">
-        <v>4.84097051620483</v>
+        <v>4.84097099304199</v>
       </c>
       <c r="H614" t="n">
         <v>3250</v>
@@ -18233,7 +18233,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G616" t="n">
-        <v>4.97928428649902</v>
+        <v>4.97928380966187</v>
       </c>
       <c r="H616" t="n">
         <v>13050</v>
@@ -18262,7 +18262,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G617" t="n">
-        <v>4.97928428649902</v>
+        <v>4.97928380966187</v>
       </c>
       <c r="H617" t="n">
         <v>2400</v>
@@ -18320,7 +18320,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G619" t="n">
-        <v>4.97928428649902</v>
+        <v>4.97928380966187</v>
       </c>
       <c r="H619" t="n">
         <v>1000</v>
@@ -18378,7 +18378,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G621" t="n">
-        <v>5.01880264282227</v>
+        <v>5.01880168914795</v>
       </c>
       <c r="H621" t="n">
         <v>5130</v>
@@ -18407,7 +18407,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G622" t="n">
-        <v>5.01880264282227</v>
+        <v>5.01880168914795</v>
       </c>
       <c r="H622" t="n">
         <v>2300</v>
@@ -18436,7 +18436,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G623" t="n">
-        <v>5.01880264282227</v>
+        <v>5.01880168914795</v>
       </c>
       <c r="H623" t="n">
         <v>0</v>
@@ -18552,7 +18552,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G627" t="n">
-        <v>4.86073017120361</v>
+        <v>4.86072969436646</v>
       </c>
       <c r="H627" t="n">
         <v>14440</v>
@@ -18610,7 +18610,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G629" t="n">
-        <v>4.86073017120361</v>
+        <v>4.86072969436646</v>
       </c>
       <c r="H629" t="n">
         <v>6500</v>
@@ -18639,7 +18639,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G630" t="n">
-        <v>4.86073017120361</v>
+        <v>4.86072969436646</v>
       </c>
       <c r="H630" t="n">
         <v>2660</v>
@@ -18668,7 +18668,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G631" t="n">
-        <v>4.86073017120361</v>
+        <v>4.86072969436646</v>
       </c>
       <c r="H631" t="n">
         <v>820</v>
@@ -18726,7 +18726,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G633" t="n">
-        <v>4.81133222579956</v>
+        <v>4.8113317489624</v>
       </c>
       <c r="H633" t="n">
         <v>200</v>
@@ -19074,7 +19074,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G645" t="n">
-        <v>4.49518775939941</v>
+        <v>4.49518728256226</v>
       </c>
       <c r="H645" t="n">
         <v>3250</v>
@@ -19132,7 +19132,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G647" t="n">
-        <v>4.34699440002441</v>
+        <v>4.34699392318726</v>
       </c>
       <c r="H647" t="n">
         <v>89070</v>
@@ -19161,7 +19161,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G648" t="n">
-        <v>4.34699440002441</v>
+        <v>4.34699392318726</v>
       </c>
       <c r="H648" t="n">
         <v>66390</v>
@@ -19190,7 +19190,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G649" t="n">
-        <v>4.39639139175415</v>
+        <v>4.39639186859131</v>
       </c>
       <c r="H649" t="n">
         <v>7440</v>
@@ -19219,7 +19219,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G650" t="n">
-        <v>4.52482557296753</v>
+        <v>4.52482509613037</v>
       </c>
       <c r="H650" t="n">
         <v>11950</v>
@@ -19277,7 +19277,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G652" t="n">
-        <v>4.68289804458618</v>
+        <v>4.68289756774902</v>
       </c>
       <c r="H652" t="n">
         <v>470</v>
@@ -19335,7 +19335,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G654" t="n">
-        <v>4.86073017120361</v>
+        <v>4.86072969436646</v>
       </c>
       <c r="H654" t="n">
         <v>410</v>
@@ -19364,7 +19364,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G655" t="n">
-        <v>4.84097051620483</v>
+        <v>4.84097099304199</v>
       </c>
       <c r="H655" t="n">
         <v>2980</v>
@@ -19393,7 +19393,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G656" t="n">
-        <v>4.72241687774658</v>
+        <v>4.72241640090942</v>
       </c>
       <c r="H656" t="n">
         <v>2060</v>
@@ -19422,7 +19422,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G657" t="n">
-        <v>4.72241687774658</v>
+        <v>4.72241640090942</v>
       </c>
       <c r="H657" t="n">
         <v>0</v>
@@ -19451,7 +19451,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G658" t="n">
-        <v>4.80145263671875</v>
+        <v>4.80145215988159</v>
       </c>
       <c r="H658" t="n">
         <v>1750</v>
@@ -19596,7 +19596,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G663" t="n">
-        <v>4.9595251083374</v>
+        <v>4.95952558517456</v>
       </c>
       <c r="H663" t="n">
         <v>3000</v>
@@ -19654,7 +19654,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G665" t="n">
-        <v>4.86073017120361</v>
+        <v>4.86072969436646</v>
       </c>
       <c r="H665" t="n">
         <v>3680</v>
@@ -19683,7 +19683,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G666" t="n">
-        <v>4.81133222579956</v>
+        <v>4.8113317489624</v>
       </c>
       <c r="H666" t="n">
         <v>13530</v>
@@ -19712,7 +19712,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G667" t="n">
-        <v>4.82121181488037</v>
+        <v>4.82121133804321</v>
       </c>
       <c r="H667" t="n">
         <v>8350</v>
@@ -19944,7 +19944,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G675" t="n">
-        <v>4.97928428649902</v>
+        <v>4.97928380966187</v>
       </c>
       <c r="H675" t="n">
         <v>177850</v>
@@ -20205,7 +20205,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G684" t="n">
-        <v>4.52482557296753</v>
+        <v>4.52482509613037</v>
       </c>
       <c r="H684" t="n">
         <v>1210</v>
@@ -20234,7 +20234,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G685" t="n">
-        <v>4.34699440002441</v>
+        <v>4.34699392318726</v>
       </c>
       <c r="H685" t="n">
         <v>19270</v>
@@ -20263,7 +20263,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G686" t="n">
-        <v>4.39639139175415</v>
+        <v>4.39639186859131</v>
       </c>
       <c r="H686" t="n">
         <v>17560</v>
@@ -20379,7 +20379,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G690" t="n">
-        <v>4.71253681182861</v>
+        <v>4.71253633499146</v>
       </c>
       <c r="H690" t="n">
         <v>19330</v>
@@ -20408,7 +20408,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G691" t="n">
-        <v>5.01880264282227</v>
+        <v>5.01880168914795</v>
       </c>
       <c r="H691" t="n">
         <v>40840</v>
@@ -20814,7 +20814,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G705" t="n">
-        <v>4.84097051620483</v>
+        <v>4.84097099304199</v>
       </c>
       <c r="H705" t="n">
         <v>1870</v>
@@ -20843,7 +20843,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G706" t="n">
-        <v>4.84097051620483</v>
+        <v>4.84097099304199</v>
       </c>
       <c r="H706" t="n">
         <v>0</v>
@@ -21017,7 +21017,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G712" t="n">
-        <v>4.72241687774658</v>
+        <v>4.72241640090942</v>
       </c>
       <c r="H712" t="n">
         <v>10280</v>
@@ -21046,7 +21046,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G713" t="n">
-        <v>4.71253681182861</v>
+        <v>4.71253633499146</v>
       </c>
       <c r="H713" t="n">
         <v>4900</v>
@@ -21075,7 +21075,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G714" t="n">
-        <v>4.60386180877686</v>
+        <v>4.6038613319397</v>
       </c>
       <c r="H714" t="n">
         <v>5550</v>
@@ -21104,7 +21104,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G715" t="n">
-        <v>4.71253681182861</v>
+        <v>4.71253633499146</v>
       </c>
       <c r="H715" t="n">
         <v>4150</v>
@@ -21133,7 +21133,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G716" t="n">
-        <v>4.72241687774658</v>
+        <v>4.72241640090942</v>
       </c>
       <c r="H716" t="n">
         <v>10940</v>
@@ -21162,7 +21162,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G717" t="n">
-        <v>4.78169345855713</v>
+        <v>4.78169393539429</v>
       </c>
       <c r="H717" t="n">
         <v>2530</v>
@@ -21191,7 +21191,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G718" t="n">
-        <v>4.82121181488037</v>
+        <v>4.82121133804321</v>
       </c>
       <c r="H718" t="n">
         <v>3100</v>
@@ -21220,7 +21220,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G719" t="n">
-        <v>4.9595251083374</v>
+        <v>4.95952558517456</v>
       </c>
       <c r="H719" t="n">
         <v>5320</v>
@@ -21249,7 +21249,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G720" t="n">
-        <v>5.01880264282227</v>
+        <v>5.01880168914795</v>
       </c>
       <c r="H720" t="n">
         <v>5570</v>
@@ -21452,7 +21452,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G727" t="n">
-        <v>4.97928428649902</v>
+        <v>4.97928380966187</v>
       </c>
       <c r="H727" t="n">
         <v>1500</v>
@@ -21510,7 +21510,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G729" t="n">
-        <v>4.84097051620483</v>
+        <v>4.84097099304199</v>
       </c>
       <c r="H729" t="n">
         <v>2100</v>
@@ -21539,7 +21539,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G730" t="n">
-        <v>4.82121181488037</v>
+        <v>4.82121133804321</v>
       </c>
       <c r="H730" t="n">
         <v>29580</v>
@@ -21597,7 +21597,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G732" t="n">
-        <v>4.86073017120361</v>
+        <v>4.86072969436646</v>
       </c>
       <c r="H732" t="n">
         <v>4460</v>
@@ -21655,7 +21655,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G734" t="n">
-        <v>4.78169345855713</v>
+        <v>4.78169393539429</v>
       </c>
       <c r="H734" t="n">
         <v>2150</v>
@@ -21771,7 +21771,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G738" t="n">
-        <v>4.82121181488037</v>
+        <v>4.82121133804321</v>
       </c>
       <c r="H738" t="n">
         <v>6100</v>
@@ -21800,7 +21800,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G739" t="n">
-        <v>4.82121181488037</v>
+        <v>4.82121133804321</v>
       </c>
       <c r="H739" t="n">
         <v>8640</v>
@@ -21829,7 +21829,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G740" t="n">
-        <v>4.81133222579956</v>
+        <v>4.8113317489624</v>
       </c>
       <c r="H740" t="n">
         <v>13020</v>
@@ -21858,7 +21858,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G741" t="n">
-        <v>4.82121181488037</v>
+        <v>4.82121133804321</v>
       </c>
       <c r="H741" t="n">
         <v>3340</v>
@@ -21887,7 +21887,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G742" t="n">
-        <v>4.84097051620483</v>
+        <v>4.84097099304199</v>
       </c>
       <c r="H742" t="n">
         <v>8310</v>
@@ -21945,7 +21945,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G744" t="n">
-        <v>4.86073017120361</v>
+        <v>4.86072969436646</v>
       </c>
       <c r="H744" t="n">
         <v>3440</v>
@@ -22090,7 +22090,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G749" t="n">
-        <v>4.78169345855713</v>
+        <v>4.78169393539429</v>
       </c>
       <c r="H749" t="n">
         <v>10810</v>
@@ -22148,7 +22148,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G751" t="n">
-        <v>4.17904233932495</v>
+        <v>4.17904186248779</v>
       </c>
       <c r="H751" t="n">
         <v>518850</v>
@@ -22206,7 +22206,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G753" t="n">
-        <v>4.17904233932495</v>
+        <v>4.17904186248779</v>
       </c>
       <c r="H753" t="n">
         <v>125670</v>
@@ -22235,7 +22235,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G754" t="n">
-        <v>4.17904233932495</v>
+        <v>4.17904186248779</v>
       </c>
       <c r="H754" t="n">
         <v>21070</v>
@@ -22264,7 +22264,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G755" t="n">
-        <v>4.1889214515686</v>
+        <v>4.18892097473145</v>
       </c>
       <c r="H755" t="n">
         <v>62780</v>
@@ -22293,7 +22293,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G756" t="n">
-        <v>4.1889214515686</v>
+        <v>4.18892097473145</v>
       </c>
       <c r="H756" t="n">
         <v>28570</v>
@@ -22322,7 +22322,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G757" t="n">
-        <v>4.17904233932495</v>
+        <v>4.17904186248779</v>
       </c>
       <c r="H757" t="n">
         <v>17930</v>
@@ -22351,7 +22351,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G758" t="n">
-        <v>4.14940357208252</v>
+        <v>4.14940309524536</v>
       </c>
       <c r="H758" t="n">
         <v>13040</v>
@@ -22409,7 +22409,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G760" t="n">
-        <v>4.16916227340698</v>
+        <v>4.16916275024414</v>
       </c>
       <c r="H760" t="n">
         <v>13670</v>
@@ -22438,7 +22438,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G761" t="n">
-        <v>4.16916227340698</v>
+        <v>4.16916275024414</v>
       </c>
       <c r="H761" t="n">
         <v>5710</v>
@@ -22525,7 +22525,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G764" t="n">
-        <v>4.02097034454346</v>
+        <v>4.02096939086914</v>
       </c>
       <c r="H764" t="n">
         <v>16670</v>
@@ -22670,7 +22670,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G769" t="n">
-        <v>3.83325862884521</v>
+        <v>3.83325839042664</v>
       </c>
       <c r="H769" t="n">
         <v>12950</v>
@@ -22699,7 +22699,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G770" t="n">
-        <v>3.77398133277893</v>
+        <v>3.77398085594177</v>
       </c>
       <c r="H770" t="n">
         <v>16120</v>
@@ -22815,7 +22815,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G774" t="n">
-        <v>3.75422215461731</v>
+        <v>3.75422191619873</v>
       </c>
       <c r="H774" t="n">
         <v>58020</v>
@@ -22902,7 +22902,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G777" t="n">
-        <v>3.75422215461731</v>
+        <v>3.75422191619873</v>
       </c>
       <c r="H777" t="n">
         <v>185950</v>
@@ -23047,7 +23047,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G782" t="n">
-        <v>4.04072904586792</v>
+        <v>4.04072856903076</v>
       </c>
       <c r="H782" t="n">
         <v>14490</v>
@@ -23192,7 +23192,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G787" t="n">
-        <v>4.03084897994995</v>
+        <v>4.03084850311279</v>
       </c>
       <c r="H787" t="n">
         <v>5350</v>
@@ -23250,7 +23250,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G789" t="n">
-        <v>3.92217445373535</v>
+        <v>3.92217421531677</v>
       </c>
       <c r="H789" t="n">
         <v>12190</v>
@@ -23366,7 +23366,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G793" t="n">
-        <v>3.932053565979</v>
+        <v>3.93205380439758</v>
       </c>
       <c r="H793" t="n">
         <v>9740</v>
@@ -23511,7 +23511,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G798" t="n">
-        <v>3.83325862884521</v>
+        <v>3.83325839042664</v>
       </c>
       <c r="H798" t="n">
         <v>3250</v>
@@ -23540,7 +23540,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G799" t="n">
-        <v>3.91229462623596</v>
+        <v>3.91229438781738</v>
       </c>
       <c r="H799" t="n">
         <v>3000</v>
@@ -23598,7 +23598,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G801" t="n">
-        <v>3.85301733016968</v>
+        <v>3.85301756858826</v>
       </c>
       <c r="H801" t="n">
         <v>47190</v>
@@ -23627,7 +23627,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G802" t="n">
-        <v>3.9223518371582</v>
+        <v>3.92235159873962</v>
       </c>
       <c r="H802" t="n">
         <v>6080</v>
@@ -23656,7 +23656,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G803" t="n">
-        <v>3.9223518371582</v>
+        <v>3.92235159873962</v>
       </c>
       <c r="H803" t="n">
         <v>2580</v>
@@ -23830,7 +23830,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G809" t="n">
-        <v>3.95206642150879</v>
+        <v>3.95206665992737</v>
       </c>
       <c r="H809" t="n">
         <v>8670</v>
@@ -23859,7 +23859,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G810" t="n">
-        <v>3.95206642150879</v>
+        <v>3.95206665992737</v>
       </c>
       <c r="H810" t="n">
         <v>0</v>
@@ -23888,7 +23888,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G811" t="n">
-        <v>3.95206642150879</v>
+        <v>3.95206665992737</v>
       </c>
       <c r="H811" t="n">
         <v>2110</v>
@@ -23946,7 +23946,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G813" t="n">
-        <v>3.99168634414673</v>
+        <v>3.99168682098389</v>
       </c>
       <c r="H813" t="n">
         <v>8200</v>
@@ -24004,7 +24004,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G815" t="n">
-        <v>3.9223518371582</v>
+        <v>3.92235159873962</v>
       </c>
       <c r="H815" t="n">
         <v>8350</v>
@@ -24062,7 +24062,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G817" t="n">
-        <v>3.95206642150879</v>
+        <v>3.95206665992737</v>
       </c>
       <c r="H817" t="n">
         <v>50</v>
@@ -24178,7 +24178,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G821" t="n">
-        <v>4.14026021957397</v>
+        <v>4.14025974273682</v>
       </c>
       <c r="H821" t="n">
         <v>24790</v>
@@ -24207,7 +24207,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G822" t="n">
-        <v>4.09073543548584</v>
+        <v>4.090735912323</v>
       </c>
       <c r="H822" t="n">
         <v>17180</v>
@@ -24265,7 +24265,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G824" t="n">
-        <v>4.00159168243408</v>
+        <v>4.00159120559692</v>
       </c>
       <c r="H824" t="n">
         <v>4360</v>
@@ -24294,7 +24294,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G825" t="n">
-        <v>3.87282729148865</v>
+        <v>3.87282705307007</v>
       </c>
       <c r="H825" t="n">
         <v>85340</v>
@@ -24352,7 +24352,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G827" t="n">
-        <v>4.03130626678467</v>
+        <v>4.03130578994751</v>
       </c>
       <c r="H827" t="n">
         <v>14010</v>
@@ -24468,7 +24468,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G831" t="n">
-        <v>3.97187685966492</v>
+        <v>3.97187662124634</v>
       </c>
       <c r="H831" t="n">
         <v>7140</v>
@@ -24700,7 +24700,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G839" t="n">
-        <v>4.04121112823486</v>
+        <v>4.04121065139771</v>
       </c>
       <c r="H839" t="n">
         <v>14500</v>
@@ -24729,7 +24729,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G840" t="n">
-        <v>4.04121112823486</v>
+        <v>4.04121065139771</v>
       </c>
       <c r="H840" t="n">
         <v>0</v>
@@ -24758,7 +24758,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G841" t="n">
-        <v>4.00159168243408</v>
+        <v>4.00159120559692</v>
       </c>
       <c r="H841" t="n">
         <v>4090</v>
@@ -24874,7 +24874,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G845" t="n">
-        <v>3.95206642150879</v>
+        <v>3.95206665992737</v>
       </c>
       <c r="H845" t="n">
         <v>11870</v>
@@ -24903,7 +24903,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G846" t="n">
-        <v>4.00159168243408</v>
+        <v>4.00159120559692</v>
       </c>
       <c r="H846" t="n">
         <v>1050</v>
@@ -24990,7 +24990,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G849" t="n">
-        <v>4.13035583496094</v>
+        <v>4.13035535812378</v>
       </c>
       <c r="H849" t="n">
         <v>6470</v>
@@ -25019,7 +25019,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G850" t="n">
-        <v>4.14026021957397</v>
+        <v>4.14025974273682</v>
       </c>
       <c r="H850" t="n">
         <v>11320</v>
@@ -25077,7 +25077,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G852" t="n">
-        <v>4.1996898651123</v>
+        <v>4.19968938827515</v>
       </c>
       <c r="H852" t="n">
         <v>8340</v>
@@ -25193,7 +25193,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G856" t="n">
-        <v>4.09073543548584</v>
+        <v>4.090735912323</v>
       </c>
       <c r="H856" t="n">
         <v>19870</v>
@@ -25541,7 +25541,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G868" t="n">
-        <v>4.13035583496094</v>
+        <v>4.13035535812378</v>
       </c>
       <c r="H868" t="n">
         <v>4840</v>
@@ -25860,7 +25860,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G879" t="n">
-        <v>4.29873991012573</v>
+        <v>4.29873943328857</v>
       </c>
       <c r="H879" t="n">
         <v>31140</v>
@@ -25976,7 +25976,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G883" t="n">
-        <v>4.33835935592651</v>
+        <v>4.33835887908936</v>
       </c>
       <c r="H883" t="n">
         <v>5580</v>
@@ -26034,7 +26034,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G885" t="n">
-        <v>4.33835935592651</v>
+        <v>4.33835887908936</v>
       </c>
       <c r="H885" t="n">
         <v>3590</v>
@@ -26266,7 +26266,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G893" t="n">
-        <v>4.2393102645874</v>
+        <v>4.23930978775024</v>
       </c>
       <c r="H893" t="n">
         <v>42450</v>
@@ -26382,7 +26382,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G897" t="n">
-        <v>4.22940492630005</v>
+        <v>4.22940444946289</v>
       </c>
       <c r="H897" t="n">
         <v>3150</v>
@@ -26527,7 +26527,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G902" t="n">
-        <v>4.1996898651123</v>
+        <v>4.19968938827515</v>
       </c>
       <c r="H902" t="n">
         <v>2510</v>
@@ -26701,7 +26701,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G908" t="n">
-        <v>4.00159168243408</v>
+        <v>4.00159120559692</v>
       </c>
       <c r="H908" t="n">
         <v>14460</v>
@@ -26788,7 +26788,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G911" t="n">
-        <v>4.04121112823486</v>
+        <v>4.04121065139771</v>
       </c>
       <c r="H911" t="n">
         <v>1150</v>
@@ -26817,7 +26817,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G912" t="n">
-        <v>4.04121112823486</v>
+        <v>4.04121065139771</v>
       </c>
       <c r="H912" t="n">
         <v>0</v>
@@ -27020,7 +27020,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G919" t="n">
-        <v>3.85301733016968</v>
+        <v>3.85301756858826</v>
       </c>
       <c r="H919" t="n">
         <v>5620</v>
@@ -27774,7 +27774,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G945" t="n">
-        <v>3.90254187583923</v>
+        <v>3.90254211425781</v>
       </c>
       <c r="H945" t="n">
         <v>8060</v>
@@ -27803,7 +27803,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G946" t="n">
-        <v>4.04121112823486</v>
+        <v>4.04121065139771</v>
       </c>
       <c r="H946" t="n">
         <v>34120</v>
@@ -27861,7 +27861,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G948" t="n">
-        <v>4.10064077377319</v>
+        <v>4.10064029693604</v>
       </c>
       <c r="H948" t="n">
         <v>66300</v>
@@ -27919,7 +27919,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G950" t="n">
-        <v>4.10064077377319</v>
+        <v>4.10064029693604</v>
       </c>
       <c r="H950" t="n">
         <v>21380</v>
@@ -28006,7 +28006,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G953" t="n">
-        <v>4.03130626678467</v>
+        <v>4.03130578994751</v>
       </c>
       <c r="H953" t="n">
         <v>13820</v>
@@ -28064,7 +28064,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G955" t="n">
-        <v>4.03130626678467</v>
+        <v>4.03130578994751</v>
       </c>
       <c r="H955" t="n">
         <v>5030</v>
@@ -28093,7 +28093,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G956" t="n">
-        <v>3.99168634414673</v>
+        <v>3.99168682098389</v>
       </c>
       <c r="H956" t="n">
         <v>5970</v>
@@ -28151,7 +28151,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G958" t="n">
-        <v>3.97187685966492</v>
+        <v>3.97187662124634</v>
       </c>
       <c r="H958" t="n">
         <v>46140</v>
@@ -28354,7 +28354,7 @@
         <v>3.97849988937378</v>
       </c>
       <c r="G965" t="n">
-        <v>3.94067573547363</v>
+        <v>3.94067597389221</v>
       </c>
       <c r="H965" t="n">
         <v>9527</v>
@@ -28412,7 +28412,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G967" t="n">
-        <v>3.95206642150879</v>
+        <v>3.95206665992737</v>
       </c>
       <c r="H967" t="n">
         <v>6708</v>
@@ -28441,7 +28441,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G968" t="n">
-        <v>3.90254187583923</v>
+        <v>3.90254211425781</v>
       </c>
       <c r="H968" t="n">
         <v>4990</v>
@@ -28499,7 +28499,7 @@
         <v>3.95050001144409</v>
       </c>
       <c r="G970" t="n">
-        <v>3.91294240951538</v>
+        <v>3.9129421710968</v>
       </c>
       <c r="H970" t="n">
         <v>6820</v>
@@ -28760,7 +28760,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G979" t="n">
-        <v>3.99168634414673</v>
+        <v>3.99168682098389</v>
       </c>
       <c r="H979" t="n">
         <v>7285</v>
@@ -28876,7 +28876,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G983" t="n">
-        <v>3.95206642150879</v>
+        <v>3.95206665992737</v>
       </c>
       <c r="H983" t="n">
         <v>1600</v>
@@ -28992,7 +28992,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G987" t="n">
-        <v>3.85301733016968</v>
+        <v>3.85301756858826</v>
       </c>
       <c r="H987" t="n">
         <v>3417</v>
@@ -29021,7 +29021,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G988" t="n">
-        <v>3.85301733016968</v>
+        <v>3.85301756858826</v>
       </c>
       <c r="H988" t="n">
         <v>9092</v>
@@ -29195,7 +29195,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G994" t="n">
-        <v>3.85301733016968</v>
+        <v>3.85301756858826</v>
       </c>
       <c r="H994" t="n">
         <v>2361</v>
@@ -29427,7 +29427,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G1002" t="n">
-        <v>3.90254187583923</v>
+        <v>3.90254211425781</v>
       </c>
       <c r="H1002" t="n">
         <v>11713</v>
@@ -30094,7 +30094,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G1025" t="n">
-        <v>3.58558416366577</v>
+        <v>3.58558392524719</v>
       </c>
       <c r="H1025" t="n">
         <v>2637</v>
@@ -30471,7 +30471,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1038" t="n">
-        <v>3.48653507232666</v>
+        <v>3.48653483390808</v>
       </c>
       <c r="H1038" t="n">
         <v>11040</v>
@@ -30790,7 +30790,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1049" t="n">
-        <v>3.4370105266571</v>
+        <v>3.43701028823853</v>
       </c>
       <c r="H1049" t="n">
         <v>4178</v>
@@ -30819,7 +30819,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1050" t="n">
-        <v>3.4370105266571</v>
+        <v>3.43701028823853</v>
       </c>
       <c r="H1050" t="n">
         <v>15067</v>
@@ -31022,7 +31022,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1057" t="n">
-        <v>3.48653507232666</v>
+        <v>3.48653483390808</v>
       </c>
       <c r="H1057" t="n">
         <v>18503</v>
@@ -31138,7 +31138,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G1061" t="n">
-        <v>3.90254187583923</v>
+        <v>3.90254211425781</v>
       </c>
       <c r="H1061" t="n">
         <v>105352</v>
@@ -31283,7 +31283,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G1066" t="n">
-        <v>4.00159168243408</v>
+        <v>4.00159120559692</v>
       </c>
       <c r="H1066" t="n">
         <v>8852</v>
@@ -49153,6 +49153,35 @@
         <v>18768</v>
       </c>
       <c r="I1682" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1683">
+      <c r="A1683" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1683" s="1" t="n">
+        <v>46322.3333333333</v>
+      </c>
+      <c r="C1683" t="n">
+        <v>3.1949999332428</v>
+      </c>
+      <c r="D1683" t="n">
+        <v>3.24499988555908</v>
+      </c>
+      <c r="E1683" t="n">
+        <v>3.16000008583069</v>
+      </c>
+      <c r="F1683" t="n">
+        <v>3.1800000667572</v>
+      </c>
+      <c r="G1683" t="n">
+        <v>3.1800000667572</v>
+      </c>
+      <c r="H1683" t="n">
+        <v>101062</v>
+      </c>
+      <c r="I1683" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/UD.MI.xlsx
+++ b/data/UD.MI.xlsx
@@ -427,7 +427,7 @@
         <v>1.5</v>
       </c>
       <c r="G2" t="n">
-        <v>1.47885525226593</v>
+        <v>1.47885513305664</v>
       </c>
       <c r="H2" t="n">
         <v>159000</v>
@@ -456,7 +456,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G3" t="n">
-        <v>1.43941915035248</v>
+        <v>1.43941903114319</v>
       </c>
       <c r="H3" t="n">
         <v>78000</v>
@@ -485,7 +485,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G4" t="n">
-        <v>1.4591372013092</v>
+        <v>1.45913708209991</v>
       </c>
       <c r="H4" t="n">
         <v>240000</v>
@@ -543,7 +543,7 @@
         <v>1.56500005722046</v>
       </c>
       <c r="G6" t="n">
-        <v>1.5429390668869</v>
+        <v>1.54293894767761</v>
       </c>
       <c r="H6" t="n">
         <v>55000</v>
@@ -630,7 +630,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G9" t="n">
-        <v>1.55772757530212</v>
+        <v>1.55772745609283</v>
       </c>
       <c r="H9" t="n">
         <v>13000</v>
@@ -746,7 +746,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G13" t="n">
-        <v>1.55772757530212</v>
+        <v>1.55772745609283</v>
       </c>
       <c r="H13" t="n">
         <v>2000</v>
@@ -804,7 +804,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G15" t="n">
-        <v>1.64645874500275</v>
+        <v>1.64645862579346</v>
       </c>
       <c r="H15" t="n">
         <v>31000</v>
@@ -833,7 +833,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G16" t="n">
-        <v>1.65631783008575</v>
+        <v>1.65631771087646</v>
       </c>
       <c r="H16" t="n">
         <v>28000</v>
@@ -862,7 +862,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G17" t="n">
-        <v>1.66617691516876</v>
+        <v>1.66617679595947</v>
       </c>
       <c r="H17" t="n">
         <v>14000</v>
@@ -891,7 +891,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G18" t="n">
-        <v>1.67603576183319</v>
+        <v>1.67603588104248</v>
       </c>
       <c r="H18" t="n">
         <v>36000</v>
@@ -920,7 +920,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G19" t="n">
-        <v>1.67603576183319</v>
+        <v>1.67603588104248</v>
       </c>
       <c r="H19" t="n">
         <v>18000</v>
@@ -978,7 +978,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G21" t="n">
-        <v>1.65631783008575</v>
+        <v>1.65631771087646</v>
       </c>
       <c r="H21" t="n">
         <v>29000</v>
@@ -1036,7 +1036,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G23" t="n">
-        <v>1.59716367721558</v>
+        <v>1.59716379642487</v>
       </c>
       <c r="H23" t="n">
         <v>43000</v>
@@ -1181,7 +1181,7 @@
         <v>1.59500002861023</v>
       </c>
       <c r="G28" t="n">
-        <v>1.57251620292664</v>
+        <v>1.57251608371735</v>
       </c>
       <c r="H28" t="n">
         <v>22000</v>
@@ -1239,7 +1239,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G30" t="n">
-        <v>1.62674069404602</v>
+        <v>1.62674057483673</v>
       </c>
       <c r="H30" t="n">
         <v>12000</v>
@@ -1268,7 +1268,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G31" t="n">
-        <v>1.63659965991974</v>
+        <v>1.63659977912903</v>
       </c>
       <c r="H31" t="n">
         <v>32000</v>
@@ -1297,7 +1297,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G32" t="n">
-        <v>1.59716367721558</v>
+        <v>1.59716379642487</v>
       </c>
       <c r="H32" t="n">
         <v>4000</v>
@@ -1326,7 +1326,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G33" t="n">
-        <v>1.61688160896301</v>
+        <v>1.6168817281723</v>
       </c>
       <c r="H33" t="n">
         <v>1000</v>
@@ -1355,7 +1355,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G34" t="n">
-        <v>1.62674069404602</v>
+        <v>1.62674057483673</v>
       </c>
       <c r="H34" t="n">
         <v>84000</v>
@@ -1384,7 +1384,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G35" t="n">
-        <v>1.62674069404602</v>
+        <v>1.62674057483673</v>
       </c>
       <c r="H35" t="n">
         <v>0</v>
@@ -1413,7 +1413,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G36" t="n">
-        <v>1.65631783008575</v>
+        <v>1.65631771087646</v>
       </c>
       <c r="H36" t="n">
         <v>8000</v>
@@ -1500,7 +1500,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G39" t="n">
-        <v>1.67110657691956</v>
+        <v>1.67110645771027</v>
       </c>
       <c r="H39" t="n">
         <v>3000</v>
@@ -1529,7 +1529,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G40" t="n">
-        <v>1.6957540512085</v>
+        <v>1.69575393199921</v>
       </c>
       <c r="H40" t="n">
         <v>7000</v>
@@ -1558,7 +1558,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G41" t="n">
-        <v>1.6858948469162</v>
+        <v>1.68589496612549</v>
       </c>
       <c r="H41" t="n">
         <v>14000</v>
@@ -1616,7 +1616,7 @@
         <v>1.72500002384186</v>
       </c>
       <c r="G43" t="n">
-        <v>1.70068347454071</v>
+        <v>1.70068359375</v>
       </c>
       <c r="H43" t="n">
         <v>21000</v>
@@ -1645,7 +1645,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G44" t="n">
-        <v>1.65631783008575</v>
+        <v>1.65631771087646</v>
       </c>
       <c r="H44" t="n">
         <v>21000</v>
@@ -1674,7 +1674,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G45" t="n">
-        <v>1.66617691516876</v>
+        <v>1.66617679595947</v>
       </c>
       <c r="H45" t="n">
         <v>1000</v>
@@ -1703,7 +1703,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G46" t="n">
-        <v>1.67603576183319</v>
+        <v>1.67603588104248</v>
       </c>
       <c r="H46" t="n">
         <v>12000</v>
@@ -1732,7 +1732,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G47" t="n">
-        <v>1.65631783008575</v>
+        <v>1.65631771087646</v>
       </c>
       <c r="H47" t="n">
         <v>5000</v>
@@ -1761,7 +1761,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G48" t="n">
-        <v>1.65631783008575</v>
+        <v>1.65631771087646</v>
       </c>
       <c r="H48" t="n">
         <v>0</v>
@@ -1790,7 +1790,7 @@
         <v>1.72500002384186</v>
       </c>
       <c r="G49" t="n">
-        <v>1.70068347454071</v>
+        <v>1.70068359375</v>
       </c>
       <c r="H49" t="n">
         <v>18000</v>
@@ -1877,7 +1877,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G52" t="n">
-        <v>1.74011969566345</v>
+        <v>1.74011945724487</v>
       </c>
       <c r="H52" t="n">
         <v>6000</v>
@@ -1935,7 +1935,7 @@
         <v>1.72500002384186</v>
       </c>
       <c r="G54" t="n">
-        <v>1.70068347454071</v>
+        <v>1.70068359375</v>
       </c>
       <c r="H54" t="n">
         <v>10000</v>
@@ -1964,7 +1964,7 @@
         <v>1.72500002384186</v>
       </c>
       <c r="G55" t="n">
-        <v>1.70068347454071</v>
+        <v>1.70068359375</v>
       </c>
       <c r="H55" t="n">
         <v>15000</v>
@@ -1993,7 +1993,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G56" t="n">
-        <v>1.6957540512085</v>
+        <v>1.69575393199921</v>
       </c>
       <c r="H56" t="n">
         <v>8000</v>
@@ -2022,7 +2022,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G57" t="n">
-        <v>1.67603576183319</v>
+        <v>1.67603588104248</v>
       </c>
       <c r="H57" t="n">
         <v>30000</v>
@@ -2051,7 +2051,7 @@
         <v>1.7150000333786</v>
       </c>
       <c r="G58" t="n">
-        <v>1.69082450866699</v>
+        <v>1.6908243894577</v>
       </c>
       <c r="H58" t="n">
         <v>7000</v>
@@ -2080,7 +2080,7 @@
         <v>1.7150000333786</v>
       </c>
       <c r="G59" t="n">
-        <v>1.69082450866699</v>
+        <v>1.6908243894577</v>
       </c>
       <c r="H59" t="n">
         <v>0</v>
@@ -2196,7 +2196,7 @@
         <v>1.68499994277954</v>
       </c>
       <c r="G63" t="n">
-        <v>1.66124713420868</v>
+        <v>1.66124725341797</v>
       </c>
       <c r="H63" t="n">
         <v>5000</v>
@@ -2283,7 +2283,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G66" t="n">
-        <v>1.67603576183319</v>
+        <v>1.67603588104248</v>
       </c>
       <c r="H66" t="n">
         <v>3000</v>
@@ -2312,7 +2312,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G67" t="n">
-        <v>1.66617691516876</v>
+        <v>1.66617679595947</v>
       </c>
       <c r="H67" t="n">
         <v>10000</v>
@@ -2341,7 +2341,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G68" t="n">
-        <v>1.6858948469162</v>
+        <v>1.68589496612549</v>
       </c>
       <c r="H68" t="n">
         <v>7000</v>
@@ -2370,7 +2370,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G69" t="n">
-        <v>1.65631783008575</v>
+        <v>1.65631771087646</v>
       </c>
       <c r="H69" t="n">
         <v>19000</v>
@@ -2399,7 +2399,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G70" t="n">
-        <v>1.62674069404602</v>
+        <v>1.62674057483673</v>
       </c>
       <c r="H70" t="n">
         <v>41000</v>
@@ -2428,7 +2428,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G71" t="n">
-        <v>1.62674069404602</v>
+        <v>1.62674057483673</v>
       </c>
       <c r="H71" t="n">
         <v>0</v>
@@ -2457,7 +2457,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G72" t="n">
-        <v>1.64645874500275</v>
+        <v>1.64645862579346</v>
       </c>
       <c r="H72" t="n">
         <v>1000</v>
@@ -2486,7 +2486,7 @@
         <v>1.65499997138977</v>
       </c>
       <c r="G73" t="n">
-        <v>1.63167011737823</v>
+        <v>1.63167023658752</v>
       </c>
       <c r="H73" t="n">
         <v>176000</v>
@@ -2515,7 +2515,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G74" t="n">
-        <v>1.64645874500275</v>
+        <v>1.64645862579346</v>
       </c>
       <c r="H74" t="n">
         <v>1000</v>
@@ -2573,7 +2573,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G76" t="n">
-        <v>1.67110657691956</v>
+        <v>1.67110645771027</v>
       </c>
       <c r="H76" t="n">
         <v>2000</v>
@@ -2602,7 +2602,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G77" t="n">
-        <v>1.6858948469162</v>
+        <v>1.68589496612549</v>
       </c>
       <c r="H77" t="n">
         <v>3000</v>
@@ -2631,7 +2631,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G78" t="n">
-        <v>1.64645874500275</v>
+        <v>1.64645862579346</v>
       </c>
       <c r="H78" t="n">
         <v>4000</v>
@@ -2660,7 +2660,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G79" t="n">
-        <v>1.67603576183319</v>
+        <v>1.67603588104248</v>
       </c>
       <c r="H79" t="n">
         <v>16000</v>
@@ -2689,7 +2689,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G80" t="n">
-        <v>1.67603576183319</v>
+        <v>1.67603588104248</v>
       </c>
       <c r="H80" t="n">
         <v>0</v>
@@ -2718,7 +2718,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G81" t="n">
-        <v>1.67603576183319</v>
+        <v>1.67603588104248</v>
       </c>
       <c r="H81" t="n">
         <v>0</v>
@@ -2747,7 +2747,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G82" t="n">
-        <v>1.65631783008575</v>
+        <v>1.65631771087646</v>
       </c>
       <c r="H82" t="n">
         <v>1000</v>
@@ -2776,7 +2776,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G83" t="n">
-        <v>1.65631783008575</v>
+        <v>1.65631771087646</v>
       </c>
       <c r="H83" t="n">
         <v>8000</v>
@@ -2805,7 +2805,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G84" t="n">
-        <v>1.63659965991974</v>
+        <v>1.63659977912903</v>
       </c>
       <c r="H84" t="n">
         <v>8000</v>
@@ -2834,7 +2834,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G85" t="n">
-        <v>1.62674069404602</v>
+        <v>1.62674057483673</v>
       </c>
       <c r="H85" t="n">
         <v>7000</v>
@@ -2863,7 +2863,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G86" t="n">
-        <v>1.62674069404602</v>
+        <v>1.62674057483673</v>
       </c>
       <c r="H86" t="n">
         <v>0</v>
@@ -2979,7 +2979,7 @@
         <v>1.59500002861023</v>
       </c>
       <c r="G90" t="n">
-        <v>1.57251620292664</v>
+        <v>1.57251608371735</v>
       </c>
       <c r="H90" t="n">
         <v>4000</v>
@@ -3008,7 +3008,7 @@
         <v>1.59500002861023</v>
       </c>
       <c r="G91" t="n">
-        <v>1.57251620292664</v>
+        <v>1.57251608371735</v>
       </c>
       <c r="H91" t="n">
         <v>2000</v>
@@ -3066,7 +3066,7 @@
         <v>1.59500002861023</v>
       </c>
       <c r="G93" t="n">
-        <v>1.57251620292664</v>
+        <v>1.57251608371735</v>
       </c>
       <c r="H93" t="n">
         <v>9000</v>
@@ -3095,7 +3095,7 @@
         <v>1.59500002861023</v>
       </c>
       <c r="G94" t="n">
-        <v>1.57251620292664</v>
+        <v>1.57251608371735</v>
       </c>
       <c r="H94" t="n">
         <v>11000</v>
@@ -3240,7 +3240,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G99" t="n">
-        <v>1.62674069404602</v>
+        <v>1.62674057483673</v>
       </c>
       <c r="H99" t="n">
         <v>7000</v>
@@ -3269,7 +3269,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G100" t="n">
-        <v>1.62674069404602</v>
+        <v>1.62674057483673</v>
       </c>
       <c r="H100" t="n">
         <v>0</v>
@@ -3298,7 +3298,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G101" t="n">
-        <v>1.65631783008575</v>
+        <v>1.65631771087646</v>
       </c>
       <c r="H101" t="n">
         <v>50000</v>
@@ -3327,7 +3327,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G102" t="n">
-        <v>1.62674069404602</v>
+        <v>1.62674057483673</v>
       </c>
       <c r="H102" t="n">
         <v>9000</v>
@@ -3356,7 +3356,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G103" t="n">
-        <v>1.63659965991974</v>
+        <v>1.63659977912903</v>
       </c>
       <c r="H103" t="n">
         <v>35000</v>
@@ -3385,7 +3385,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G104" t="n">
-        <v>1.63659965991974</v>
+        <v>1.63659977912903</v>
       </c>
       <c r="H104" t="n">
         <v>14000</v>
@@ -3443,7 +3443,7 @@
         <v>1.66499996185303</v>
       </c>
       <c r="G106" t="n">
-        <v>1.64152932167053</v>
+        <v>1.64152920246124</v>
       </c>
       <c r="H106" t="n">
         <v>2000</v>
@@ -3472,7 +3472,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G107" t="n">
-        <v>1.62674069404602</v>
+        <v>1.62674057483673</v>
       </c>
       <c r="H107" t="n">
         <v>3000</v>
@@ -3501,7 +3501,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G108" t="n">
-        <v>1.62674069404602</v>
+        <v>1.62674057483673</v>
       </c>
       <c r="H108" t="n">
         <v>1000</v>
@@ -3530,7 +3530,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G109" t="n">
-        <v>1.66617691516876</v>
+        <v>1.66617679595947</v>
       </c>
       <c r="H109" t="n">
         <v>15000</v>
@@ -3559,7 +3559,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G110" t="n">
-        <v>1.67603576183319</v>
+        <v>1.67603588104248</v>
       </c>
       <c r="H110" t="n">
         <v>26000</v>
@@ -3588,7 +3588,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G111" t="n">
-        <v>1.67603576183319</v>
+        <v>1.67603588104248</v>
       </c>
       <c r="H111" t="n">
         <v>53000</v>
@@ -3617,7 +3617,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G112" t="n">
-        <v>1.67603576183319</v>
+        <v>1.67603588104248</v>
       </c>
       <c r="H112" t="n">
         <v>10000</v>
@@ -3646,7 +3646,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G113" t="n">
-        <v>1.67603576183319</v>
+        <v>1.67603588104248</v>
       </c>
       <c r="H113" t="n">
         <v>6000</v>
@@ -3675,7 +3675,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G114" t="n">
-        <v>1.67603576183319</v>
+        <v>1.67603588104248</v>
       </c>
       <c r="H114" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G115" t="n">
-        <v>1.67603576183319</v>
+        <v>1.67603588104248</v>
       </c>
       <c r="H115" t="n">
         <v>22000</v>
@@ -3762,7 +3762,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G117" t="n">
-        <v>1.6858948469162</v>
+        <v>1.68589496612549</v>
       </c>
       <c r="H117" t="n">
         <v>22000</v>
@@ -3791,7 +3791,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G118" t="n">
-        <v>1.6858948469162</v>
+        <v>1.68589496612549</v>
       </c>
       <c r="H118" t="n">
         <v>0</v>
@@ -3849,7 +3849,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G120" t="n">
-        <v>1.89786410331726</v>
+        <v>1.89786422252655</v>
       </c>
       <c r="H120" t="n">
         <v>60000</v>
@@ -3965,7 +3965,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G124" t="n">
-        <v>1.85349857807159</v>
+        <v>1.8534984588623</v>
       </c>
       <c r="H124" t="n">
         <v>32000</v>
@@ -4197,7 +4197,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G132" t="n">
-        <v>1.78448510169983</v>
+        <v>1.78448522090912</v>
       </c>
       <c r="H132" t="n">
         <v>9000</v>
@@ -4226,7 +4226,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G133" t="n">
-        <v>1.85349857807159</v>
+        <v>1.8534984588623</v>
       </c>
       <c r="H133" t="n">
         <v>6000</v>
@@ -4255,7 +4255,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G134" t="n">
-        <v>1.85349857807159</v>
+        <v>1.8534984588623</v>
       </c>
       <c r="H134" t="n">
         <v>0</v>
@@ -4284,7 +4284,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G135" t="n">
-        <v>1.85349857807159</v>
+        <v>1.8534984588623</v>
       </c>
       <c r="H135" t="n">
         <v>3000</v>
@@ -4342,7 +4342,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G137" t="n">
-        <v>1.88307547569275</v>
+        <v>1.88307559490204</v>
       </c>
       <c r="H137" t="n">
         <v>1000</v>
@@ -4371,7 +4371,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G138" t="n">
-        <v>1.88307547569275</v>
+        <v>1.88307559490204</v>
       </c>
       <c r="H138" t="n">
         <v>0</v>
@@ -4748,7 +4748,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G151" t="n">
-        <v>1.74011969566345</v>
+        <v>1.74011945724487</v>
       </c>
       <c r="H151" t="n">
         <v>30000</v>
@@ -5357,7 +5357,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G172" t="n">
-        <v>1.81406235694885</v>
+        <v>1.81406259536743</v>
       </c>
       <c r="H172" t="n">
         <v>3000</v>
@@ -5531,7 +5531,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G178" t="n">
-        <v>1.87814617156982</v>
+        <v>1.87814605236053</v>
       </c>
       <c r="H178" t="n">
         <v>75000</v>
@@ -5560,7 +5560,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G179" t="n">
-        <v>1.88307547569275</v>
+        <v>1.88307559490204</v>
       </c>
       <c r="H179" t="n">
         <v>30000</v>
@@ -5618,7 +5618,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G181" t="n">
-        <v>1.90279376506805</v>
+        <v>1.90279364585876</v>
       </c>
       <c r="H181" t="n">
         <v>23000</v>
@@ -5647,7 +5647,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G182" t="n">
-        <v>1.91265273094177</v>
+        <v>1.91265285015106</v>
       </c>
       <c r="H182" t="n">
         <v>6000</v>
@@ -5705,7 +5705,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G184" t="n">
-        <v>2.01124286651611</v>
+        <v>2.01124310493469</v>
       </c>
       <c r="H184" t="n">
         <v>3000</v>
@@ -5821,7 +5821,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G188" t="n">
-        <v>2.01124286651611</v>
+        <v>2.01124310493469</v>
       </c>
       <c r="H188" t="n">
         <v>4000</v>
@@ -5850,7 +5850,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G189" t="n">
-        <v>2.01124286651611</v>
+        <v>2.01124310493469</v>
       </c>
       <c r="H189" t="n">
         <v>0</v>
@@ -6053,7 +6053,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G196" t="n">
-        <v>1.89293467998505</v>
+        <v>1.89293456077576</v>
       </c>
       <c r="H196" t="n">
         <v>23000</v>
@@ -6082,7 +6082,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G197" t="n">
-        <v>1.91265273094177</v>
+        <v>1.91265285015106</v>
       </c>
       <c r="H197" t="n">
         <v>24000</v>
@@ -6111,7 +6111,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G198" t="n">
-        <v>1.91265273094177</v>
+        <v>1.91265285015106</v>
       </c>
       <c r="H198" t="n">
         <v>17000</v>
@@ -6227,7 +6227,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G202" t="n">
-        <v>1.91265273094177</v>
+        <v>1.91265285015106</v>
       </c>
       <c r="H202" t="n">
         <v>18000</v>
@@ -6430,7 +6430,7 @@
         <v>1.9650000333786</v>
       </c>
       <c r="G209" t="n">
-        <v>1.93730020523071</v>
+        <v>1.93730032444</v>
       </c>
       <c r="H209" t="n">
         <v>11000</v>
@@ -6459,7 +6459,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G210" t="n">
-        <v>1.95701837539673</v>
+        <v>1.95701825618744</v>
       </c>
       <c r="H210" t="n">
         <v>16000</v>
@@ -6604,7 +6604,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G215" t="n">
-        <v>1.95701837539673</v>
+        <v>1.95701825618744</v>
       </c>
       <c r="H215" t="n">
         <v>1000</v>
@@ -6633,7 +6633,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G216" t="n">
-        <v>1.91265273094177</v>
+        <v>1.91265285015106</v>
       </c>
       <c r="H216" t="n">
         <v>9000</v>
@@ -6662,7 +6662,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G217" t="n">
-        <v>1.89786410331726</v>
+        <v>1.89786422252655</v>
       </c>
       <c r="H217" t="n">
         <v>3000</v>
@@ -6691,7 +6691,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G218" t="n">
-        <v>1.89293467998505</v>
+        <v>1.89293456077576</v>
       </c>
       <c r="H218" t="n">
         <v>8000</v>
@@ -6720,7 +6720,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G219" t="n">
-        <v>1.89293467998505</v>
+        <v>1.89293456077576</v>
       </c>
       <c r="H219" t="n">
         <v>1000</v>
@@ -6749,7 +6749,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G220" t="n">
-        <v>1.89786410331726</v>
+        <v>1.89786422252655</v>
       </c>
       <c r="H220" t="n">
         <v>3000</v>
@@ -7039,7 +7039,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G230" t="n">
-        <v>2.02110195159912</v>
+        <v>2.0211021900177</v>
       </c>
       <c r="H230" t="n">
         <v>46000</v>
@@ -7184,7 +7184,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G235" t="n">
-        <v>2.14926958084106</v>
+        <v>2.14926981925964</v>
       </c>
       <c r="H235" t="n">
         <v>11000</v>
@@ -7242,7 +7242,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G237" t="n">
-        <v>2.18870568275452</v>
+        <v>2.1887059211731</v>
       </c>
       <c r="H237" t="n">
         <v>5000</v>
@@ -7648,7 +7648,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G251" t="n">
-        <v>2.33659100532532</v>
+        <v>2.3365912437439</v>
       </c>
       <c r="H251" t="n">
         <v>8000</v>
@@ -7677,7 +7677,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G252" t="n">
-        <v>2.33659100532532</v>
+        <v>2.3365912437439</v>
       </c>
       <c r="H252" t="n">
         <v>0</v>
@@ -7706,7 +7706,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G253" t="n">
-        <v>2.40560436248779</v>
+        <v>2.40560460090637</v>
       </c>
       <c r="H253" t="n">
         <v>26000</v>
@@ -7735,7 +7735,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G254" t="n">
-        <v>2.4844765663147</v>
+        <v>2.48447680473328</v>
       </c>
       <c r="H254" t="n">
         <v>14000</v>
@@ -7764,7 +7764,7 @@
         <v>2.5</v>
       </c>
       <c r="G255" t="n">
-        <v>2.46475887298584</v>
+        <v>2.46475839614868</v>
       </c>
       <c r="H255" t="n">
         <v>11000</v>
@@ -7793,7 +7793,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G256" t="n">
-        <v>2.55348992347717</v>
+        <v>2.55348968505859</v>
       </c>
       <c r="H256" t="n">
         <v>21000</v>
@@ -7822,7 +7822,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G257" t="n">
-        <v>2.55348992347717</v>
+        <v>2.55348968505859</v>
       </c>
       <c r="H257" t="n">
         <v>6000</v>
@@ -7909,7 +7909,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G260" t="n">
-        <v>2.74081134796143</v>
+        <v>2.74081158638</v>
       </c>
       <c r="H260" t="n">
         <v>51000</v>
@@ -7938,7 +7938,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G261" t="n">
-        <v>2.66193962097168</v>
+        <v>2.6619393825531</v>
       </c>
       <c r="H261" t="n">
         <v>22000</v>
@@ -7967,7 +7967,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G262" t="n">
-        <v>2.78024792671204</v>
+        <v>2.78024768829346</v>
       </c>
       <c r="H262" t="n">
         <v>23000</v>
@@ -7996,7 +7996,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G263" t="n">
-        <v>2.97742867469788</v>
+        <v>2.9774284362793</v>
       </c>
       <c r="H263" t="n">
         <v>41000</v>
@@ -8054,7 +8054,7 @@
         <v>3</v>
       </c>
       <c r="G265" t="n">
-        <v>2.95771050453186</v>
+        <v>2.95771026611328</v>
       </c>
       <c r="H265" t="n">
         <v>85000</v>
@@ -8083,7 +8083,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G266" t="n">
-        <v>2.87883830070496</v>
+        <v>2.87883806228638</v>
       </c>
       <c r="H266" t="n">
         <v>27000</v>
@@ -8112,7 +8112,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G267" t="n">
-        <v>2.83940196037292</v>
+        <v>2.8394021987915</v>
       </c>
       <c r="H267" t="n">
         <v>62000</v>
@@ -8228,7 +8228,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G271" t="n">
-        <v>2.84926104545593</v>
+        <v>2.84926128387451</v>
       </c>
       <c r="H271" t="n">
         <v>21000</v>
@@ -8257,7 +8257,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G272" t="n">
-        <v>2.99714636802673</v>
+        <v>2.99714660644531</v>
       </c>
       <c r="H272" t="n">
         <v>21000</v>
@@ -8286,7 +8286,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G273" t="n">
-        <v>2.96756935119629</v>
+        <v>2.96756958961487</v>
       </c>
       <c r="H273" t="n">
         <v>22000</v>
@@ -8315,7 +8315,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G274" t="n">
-        <v>3.26334023475647</v>
+        <v>3.26334047317505</v>
       </c>
       <c r="H274" t="n">
         <v>121000</v>
@@ -8344,7 +8344,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G275" t="n">
-        <v>3.26334023475647</v>
+        <v>3.26334047317505</v>
       </c>
       <c r="H275" t="n">
         <v>74000</v>
@@ -8373,7 +8373,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G276" t="n">
-        <v>3.29291749000549</v>
+        <v>3.29291725158691</v>
       </c>
       <c r="H276" t="n">
         <v>39000</v>
@@ -8431,7 +8431,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G278" t="n">
-        <v>3.18446826934814</v>
+        <v>3.18446803092957</v>
       </c>
       <c r="H278" t="n">
         <v>19000</v>
@@ -8489,7 +8489,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G280" t="n">
-        <v>3.25348138809204</v>
+        <v>3.25348114967346</v>
       </c>
       <c r="H280" t="n">
         <v>4000</v>
@@ -8518,7 +8518,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G281" t="n">
-        <v>3.18446826934814</v>
+        <v>3.18446803092957</v>
       </c>
       <c r="H281" t="n">
         <v>10000</v>
@@ -8605,7 +8605,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G284" t="n">
-        <v>3.19432735443115</v>
+        <v>3.19432759284973</v>
       </c>
       <c r="H284" t="n">
         <v>4000</v>
@@ -8634,7 +8634,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G285" t="n">
-        <v>3.35207152366638</v>
+        <v>3.35207176208496</v>
       </c>
       <c r="H285" t="n">
         <v>25000</v>
@@ -9069,7 +9069,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G300" t="n">
-        <v>3.4802393913269</v>
+        <v>3.48023891448975</v>
       </c>
       <c r="H300" t="n">
         <v>15000</v>
@@ -9272,7 +9272,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G307" t="n">
-        <v>3.9731912612915</v>
+        <v>3.97319102287292</v>
       </c>
       <c r="H307" t="n">
         <v>45000</v>
@@ -9301,7 +9301,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G308" t="n">
-        <v>4.26896190643311</v>
+        <v>4.26896142959595</v>
       </c>
       <c r="H308" t="n">
         <v>57000</v>
@@ -9330,7 +9330,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G309" t="n">
-        <v>4.35769319534302</v>
+        <v>4.35769367218018</v>
       </c>
       <c r="H309" t="n">
         <v>26000</v>
@@ -9417,7 +9417,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G312" t="n">
-        <v>3.99290943145752</v>
+        <v>3.99290919303894</v>
       </c>
       <c r="H312" t="n">
         <v>51000</v>
@@ -9475,7 +9475,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G314" t="n">
-        <v>4.05206346511841</v>
+        <v>4.05206298828125</v>
       </c>
       <c r="H314" t="n">
         <v>6000</v>
@@ -9504,7 +9504,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G315" t="n">
-        <v>4.09149932861328</v>
+        <v>4.09149980545044</v>
       </c>
       <c r="H315" t="n">
         <v>8000</v>
@@ -9591,7 +9591,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G318" t="n">
-        <v>4.17037153244019</v>
+        <v>4.17037200927734</v>
       </c>
       <c r="H318" t="n">
         <v>10000</v>
@@ -9620,7 +9620,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G319" t="n">
-        <v>4.24924373626709</v>
+        <v>4.24924421310425</v>
       </c>
       <c r="H319" t="n">
         <v>6000</v>
@@ -9678,7 +9678,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G321" t="n">
-        <v>4.13093566894531</v>
+        <v>4.13093519210815</v>
       </c>
       <c r="H321" t="n">
         <v>4000</v>
@@ -9707,7 +9707,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G322" t="n">
-        <v>4.10135841369629</v>
+        <v>4.10135793685913</v>
       </c>
       <c r="H322" t="n">
         <v>4000</v>
@@ -9910,7 +9910,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G329" t="n">
-        <v>4.02248573303223</v>
+        <v>4.02248620986938</v>
       </c>
       <c r="H329" t="n">
         <v>5000</v>
@@ -10084,7 +10084,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G335" t="n">
-        <v>4.17037153244019</v>
+        <v>4.17037200927734</v>
       </c>
       <c r="H335" t="n">
         <v>3000</v>
@@ -10403,7 +10403,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G346" t="n">
-        <v>4.04220390319824</v>
+        <v>4.0422043800354</v>
       </c>
       <c r="H346" t="n">
         <v>2500</v>
@@ -10432,7 +10432,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G347" t="n">
-        <v>4.02248573303223</v>
+        <v>4.02248620986938</v>
       </c>
       <c r="H347" t="n">
         <v>3000</v>
@@ -10461,7 +10461,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G348" t="n">
-        <v>4.02248573303223</v>
+        <v>4.02248620986938</v>
       </c>
       <c r="H348" t="n">
         <v>16500</v>
@@ -10490,7 +10490,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G349" t="n">
-        <v>4.21966695785522</v>
+        <v>4.21966743469238</v>
       </c>
       <c r="H349" t="n">
         <v>21000</v>
@@ -10577,7 +10577,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G352" t="n">
-        <v>4.19994926452637</v>
+        <v>4.19994878768921</v>
       </c>
       <c r="H352" t="n">
         <v>8000</v>
@@ -10606,7 +10606,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G353" t="n">
-        <v>4.13093566894531</v>
+        <v>4.13093519210815</v>
       </c>
       <c r="H353" t="n">
         <v>9000</v>
@@ -10722,7 +10722,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G357" t="n">
-        <v>4.05206346511841</v>
+        <v>4.05206298828125</v>
       </c>
       <c r="H357" t="n">
         <v>10000</v>
@@ -10780,7 +10780,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G359" t="n">
-        <v>4.21966695785522</v>
+        <v>4.21966743469238</v>
       </c>
       <c r="H359" t="n">
         <v>14500</v>
@@ -10867,7 +10867,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G362" t="n">
-        <v>4.09149932861328</v>
+        <v>4.09149980545044</v>
       </c>
       <c r="H362" t="n">
         <v>4500</v>
@@ -11099,7 +11099,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G370" t="n">
-        <v>4.10135841369629</v>
+        <v>4.10135793685913</v>
       </c>
       <c r="H370" t="n">
         <v>4500</v>
@@ -11128,7 +11128,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G371" t="n">
-        <v>4.01262712478638</v>
+        <v>4.01262760162354</v>
       </c>
       <c r="H371" t="n">
         <v>6000</v>
@@ -11273,7 +11273,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G376" t="n">
-        <v>4.19994926452637</v>
+        <v>4.19994878768921</v>
       </c>
       <c r="H376" t="n">
         <v>7500</v>
@@ -11360,7 +11360,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G379" t="n">
-        <v>4.21966695785522</v>
+        <v>4.21966743469238</v>
       </c>
       <c r="H379" t="n">
         <v>67000</v>
@@ -11389,7 +11389,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G380" t="n">
-        <v>4.21966695785522</v>
+        <v>4.21966743469238</v>
       </c>
       <c r="H380" t="n">
         <v>3000</v>
@@ -11418,7 +11418,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G381" t="n">
-        <v>4.25910329818726</v>
+        <v>4.2591028213501</v>
       </c>
       <c r="H381" t="n">
         <v>2500</v>
@@ -11447,7 +11447,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G382" t="n">
-        <v>4.29853916168213</v>
+        <v>4.29853963851929</v>
       </c>
       <c r="H382" t="n">
         <v>35000</v>
@@ -11476,7 +11476,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G383" t="n">
-        <v>4.30839776992798</v>
+        <v>4.30839824676514</v>
       </c>
       <c r="H383" t="n">
         <v>2500</v>
@@ -11534,7 +11534,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G385" t="n">
-        <v>4.36755180358887</v>
+        <v>4.36755228042603</v>
       </c>
       <c r="H385" t="n">
         <v>4000</v>
@@ -11563,7 +11563,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G386" t="n">
-        <v>4.30839776992798</v>
+        <v>4.30839824676514</v>
       </c>
       <c r="H386" t="n">
         <v>255000</v>
@@ -11592,7 +11592,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G387" t="n">
-        <v>4.36755180358887</v>
+        <v>4.36755228042603</v>
       </c>
       <c r="H387" t="n">
         <v>6000</v>
@@ -11621,7 +11621,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G388" t="n">
-        <v>4.36755180358887</v>
+        <v>4.36755228042603</v>
       </c>
       <c r="H388" t="n">
         <v>13500</v>
@@ -11650,7 +11650,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G389" t="n">
-        <v>4.26896190643311</v>
+        <v>4.26896142959595</v>
       </c>
       <c r="H389" t="n">
         <v>15000</v>
@@ -11708,7 +11708,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G391" t="n">
-        <v>4.30839776992798</v>
+        <v>4.30839824676514</v>
       </c>
       <c r="H391" t="n">
         <v>34000</v>
@@ -11824,7 +11824,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G395" t="n">
-        <v>4.24924373626709</v>
+        <v>4.24924421310425</v>
       </c>
       <c r="H395" t="n">
         <v>31500</v>
@@ -11911,7 +11911,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G398" t="n">
-        <v>4.04220390319824</v>
+        <v>4.0422043800354</v>
       </c>
       <c r="H398" t="n">
         <v>6000</v>
@@ -11940,7 +11940,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G399" t="n">
-        <v>4.04220390319824</v>
+        <v>4.0422043800354</v>
       </c>
       <c r="H399" t="n">
         <v>7500</v>
@@ -11969,7 +11969,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G400" t="n">
-        <v>4.04220390319824</v>
+        <v>4.0422043800354</v>
       </c>
       <c r="H400" t="n">
         <v>0</v>
@@ -12027,7 +12027,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G402" t="n">
-        <v>4.19994926452637</v>
+        <v>4.19994878768921</v>
       </c>
       <c r="H402" t="n">
         <v>23500</v>
@@ -12056,7 +12056,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G403" t="n">
-        <v>4.29853916168213</v>
+        <v>4.29853963851929</v>
       </c>
       <c r="H403" t="n">
         <v>26500</v>
@@ -12230,7 +12230,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G409" t="n">
-        <v>4.49571990966797</v>
+        <v>4.49571943283081</v>
       </c>
       <c r="H409" t="n">
         <v>23000</v>
@@ -12317,7 +12317,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G412" t="n">
-        <v>5.30416059494019</v>
+        <v>5.30416011810303</v>
       </c>
       <c r="H412" t="n">
         <v>82500</v>
@@ -12375,7 +12375,7 @@
         <v>5</v>
       </c>
       <c r="G414" t="n">
-        <v>4.92951774597168</v>
+        <v>4.92951679229736</v>
       </c>
       <c r="H414" t="n">
         <v>45500</v>
@@ -12404,7 +12404,7 @@
         <v>5</v>
       </c>
       <c r="G415" t="n">
-        <v>4.92951774597168</v>
+        <v>4.92951679229736</v>
       </c>
       <c r="H415" t="n">
         <v>14500</v>
@@ -12433,7 +12433,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G416" t="n">
-        <v>4.96895313262939</v>
+        <v>4.96895360946655</v>
       </c>
       <c r="H416" t="n">
         <v>6000</v>
@@ -12462,7 +12462,7 @@
         <v>5</v>
       </c>
       <c r="G417" t="n">
-        <v>4.92951774597168</v>
+        <v>4.92951679229736</v>
       </c>
       <c r="H417" t="n">
         <v>7500</v>
@@ -12578,7 +12578,7 @@
         <v>5</v>
       </c>
       <c r="G421" t="n">
-        <v>4.92951774597168</v>
+        <v>4.92951679229736</v>
       </c>
       <c r="H421" t="n">
         <v>8500</v>
@@ -12607,7 +12607,7 @@
         <v>5</v>
       </c>
       <c r="G422" t="n">
-        <v>4.92951774597168</v>
+        <v>4.92951679229736</v>
       </c>
       <c r="H422" t="n">
         <v>9500</v>
@@ -12636,7 +12636,7 @@
         <v>5</v>
       </c>
       <c r="G423" t="n">
-        <v>4.92951774597168</v>
+        <v>4.92951679229736</v>
       </c>
       <c r="H423" t="n">
         <v>38500</v>
@@ -12665,7 +12665,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G424" t="n">
-        <v>4.89008092880249</v>
+        <v>4.89008140563965</v>
       </c>
       <c r="H424" t="n">
         <v>11000</v>
@@ -12723,7 +12723,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G426" t="n">
-        <v>5.08726119995117</v>
+        <v>5.08726167678833</v>
       </c>
       <c r="H426" t="n">
         <v>1500</v>
@@ -12810,7 +12810,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G429" t="n">
-        <v>5.12669801712036</v>
+        <v>5.1266975402832</v>
       </c>
       <c r="H429" t="n">
         <v>7000</v>
@@ -12839,7 +12839,7 @@
         <v>5</v>
       </c>
       <c r="G430" t="n">
-        <v>4.92951774597168</v>
+        <v>4.92951679229736</v>
       </c>
       <c r="H430" t="n">
         <v>8500</v>
@@ -12897,7 +12897,7 @@
         <v>5</v>
       </c>
       <c r="G432" t="n">
-        <v>4.92951774597168</v>
+        <v>4.92951679229736</v>
       </c>
       <c r="H432" t="n">
         <v>1000</v>
@@ -12955,7 +12955,7 @@
         <v>5</v>
       </c>
       <c r="G434" t="n">
-        <v>4.92951774597168</v>
+        <v>4.92951679229736</v>
       </c>
       <c r="H434" t="n">
         <v>7000</v>
@@ -12984,7 +12984,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G435" t="n">
-        <v>4.78163194656372</v>
+        <v>4.78163146972656</v>
       </c>
       <c r="H435" t="n">
         <v>22500</v>
@@ -13013,7 +13013,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G436" t="n">
-        <v>4.91965818405151</v>
+        <v>4.91965866088867</v>
       </c>
       <c r="H436" t="n">
         <v>17500</v>
@@ -13071,7 +13071,7 @@
         <v>5</v>
       </c>
       <c r="G438" t="n">
-        <v>4.92951774597168</v>
+        <v>4.92951679229736</v>
       </c>
       <c r="H438" t="n">
         <v>7500</v>
@@ -13100,7 +13100,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G439" t="n">
-        <v>4.89008092880249</v>
+        <v>4.89008140563965</v>
       </c>
       <c r="H439" t="n">
         <v>4500</v>
@@ -13129,7 +13129,7 @@
         <v>5</v>
       </c>
       <c r="G440" t="n">
-        <v>4.92951774597168</v>
+        <v>4.92951679229736</v>
       </c>
       <c r="H440" t="n">
         <v>2000</v>
@@ -13158,7 +13158,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G441" t="n">
-        <v>4.89008092880249</v>
+        <v>4.89008140563965</v>
       </c>
       <c r="H441" t="n">
         <v>2000</v>
@@ -13274,7 +13274,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G445" t="n">
-        <v>4.96895313262939</v>
+        <v>4.96895360946655</v>
       </c>
       <c r="H445" t="n">
         <v>2500</v>
@@ -13303,7 +13303,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G446" t="n">
-        <v>4.9492359161377</v>
+        <v>4.94923543930054</v>
       </c>
       <c r="H446" t="n">
         <v>6500</v>
@@ -13332,7 +13332,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G447" t="n">
-        <v>4.85064554214478</v>
+        <v>4.85064506530762</v>
       </c>
       <c r="H447" t="n">
         <v>3500</v>
@@ -13361,7 +13361,7 @@
         <v>5</v>
       </c>
       <c r="G448" t="n">
-        <v>4.92951774597168</v>
+        <v>4.92951679229736</v>
       </c>
       <c r="H448" t="n">
         <v>19060</v>
@@ -13390,7 +13390,7 @@
         <v>5</v>
       </c>
       <c r="G449" t="n">
-        <v>4.92951774597168</v>
+        <v>4.92951679229736</v>
       </c>
       <c r="H449" t="n">
         <v>10200</v>
@@ -13477,7 +13477,7 @@
         <v>5</v>
       </c>
       <c r="G452" t="n">
-        <v>4.92951774597168</v>
+        <v>4.92951679229736</v>
       </c>
       <c r="H452" t="n">
         <v>1500</v>
@@ -13506,7 +13506,7 @@
         <v>5</v>
       </c>
       <c r="G453" t="n">
-        <v>4.92951774597168</v>
+        <v>4.92951679229736</v>
       </c>
       <c r="H453" t="n">
         <v>900</v>
@@ -13564,7 +13564,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G455" t="n">
-        <v>4.85064554214478</v>
+        <v>4.85064506530762</v>
       </c>
       <c r="H455" t="n">
         <v>1650</v>
@@ -13593,7 +13593,7 @@
         <v>5</v>
       </c>
       <c r="G456" t="n">
-        <v>4.92951774597168</v>
+        <v>4.92951679229736</v>
       </c>
       <c r="H456" t="n">
         <v>2220</v>
@@ -13651,7 +13651,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G458" t="n">
-        <v>5.50134134292603</v>
+        <v>5.50134086608887</v>
       </c>
       <c r="H458" t="n">
         <v>75450</v>
@@ -13680,7 +13680,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G459" t="n">
-        <v>5.26472473144531</v>
+        <v>5.26472520828247</v>
       </c>
       <c r="H459" t="n">
         <v>23670</v>
@@ -13709,7 +13709,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G460" t="n">
-        <v>5.34359645843506</v>
+        <v>5.34359741210938</v>
       </c>
       <c r="H460" t="n">
         <v>6980</v>
@@ -13738,7 +13738,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G461" t="n">
-        <v>5.30416059494019</v>
+        <v>5.30416011810303</v>
       </c>
       <c r="H461" t="n">
         <v>2900</v>
@@ -13854,7 +13854,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G465" t="n">
-        <v>5.16613435745239</v>
+        <v>5.16613388061523</v>
       </c>
       <c r="H465" t="n">
         <v>650</v>
@@ -13883,7 +13883,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G466" t="n">
-        <v>5.12669801712036</v>
+        <v>5.1266975402832</v>
       </c>
       <c r="H466" t="n">
         <v>7070</v>
@@ -13912,7 +13912,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G467" t="n">
-        <v>5.12669801712036</v>
+        <v>5.1266975402832</v>
       </c>
       <c r="H467" t="n">
         <v>200</v>
@@ -13941,7 +13941,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G468" t="n">
-        <v>5.16613435745239</v>
+        <v>5.16613388061523</v>
       </c>
       <c r="H468" t="n">
         <v>10280</v>
@@ -13999,7 +13999,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G470" t="n">
-        <v>5.08726119995117</v>
+        <v>5.08726167678833</v>
       </c>
       <c r="H470" t="n">
         <v>2920</v>
@@ -14144,7 +14144,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G475" t="n">
-        <v>5.14641571044922</v>
+        <v>5.14641618728638</v>
       </c>
       <c r="H475" t="n">
         <v>14970</v>
@@ -14231,7 +14231,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G478" t="n">
-        <v>4.96895313262939</v>
+        <v>4.96895360946655</v>
       </c>
       <c r="H478" t="n">
         <v>3060</v>
@@ -14289,7 +14289,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G480" t="n">
-        <v>5.14641571044922</v>
+        <v>5.14641618728638</v>
       </c>
       <c r="H480" t="n">
         <v>11670</v>
@@ -14318,7 +14318,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G481" t="n">
-        <v>5.14641571044922</v>
+        <v>5.14641618728638</v>
       </c>
       <c r="H481" t="n">
         <v>7130</v>
@@ -14347,7 +14347,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G482" t="n">
-        <v>5.10697984695435</v>
+        <v>5.10697937011719</v>
       </c>
       <c r="H482" t="n">
         <v>7170</v>
@@ -14376,7 +14376,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G483" t="n">
-        <v>5.12669801712036</v>
+        <v>5.1266975402832</v>
       </c>
       <c r="H483" t="n">
         <v>4620</v>
@@ -14405,7 +14405,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G484" t="n">
-        <v>5.12669801712036</v>
+        <v>5.1266975402832</v>
       </c>
       <c r="H484" t="n">
         <v>6620</v>
@@ -14434,7 +14434,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G485" t="n">
-        <v>5.12669801712036</v>
+        <v>5.1266975402832</v>
       </c>
       <c r="H485" t="n">
         <v>11880</v>
@@ -14492,7 +14492,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G487" t="n">
-        <v>5.16613435745239</v>
+        <v>5.16613388061523</v>
       </c>
       <c r="H487" t="n">
         <v>18380</v>
@@ -14521,7 +14521,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G488" t="n">
-        <v>5.06754350662231</v>
+        <v>5.06754398345947</v>
       </c>
       <c r="H488" t="n">
         <v>3010</v>
@@ -14579,7 +14579,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G490" t="n">
-        <v>5.12669801712036</v>
+        <v>5.1266975402832</v>
       </c>
       <c r="H490" t="n">
         <v>26550</v>
@@ -14637,7 +14637,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G492" t="n">
-        <v>4.96895313262939</v>
+        <v>4.96895360946655</v>
       </c>
       <c r="H492" t="n">
         <v>10980</v>
@@ -14666,7 +14666,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G493" t="n">
-        <v>5.16613435745239</v>
+        <v>5.16613388061523</v>
       </c>
       <c r="H493" t="n">
         <v>5990</v>
@@ -14695,7 +14695,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G494" t="n">
-        <v>5.10697984695435</v>
+        <v>5.10697937011719</v>
       </c>
       <c r="H494" t="n">
         <v>11420</v>
@@ -14724,7 +14724,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G495" t="n">
-        <v>5.08726119995117</v>
+        <v>5.08726167678833</v>
       </c>
       <c r="H495" t="n">
         <v>6900</v>
@@ -14753,7 +14753,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G496" t="n">
-        <v>4.9492359161377</v>
+        <v>4.94923543930054</v>
       </c>
       <c r="H496" t="n">
         <v>6100</v>
@@ -14898,7 +14898,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G501" t="n">
-        <v>5.06754350662231</v>
+        <v>5.06754398345947</v>
       </c>
       <c r="H501" t="n">
         <v>11540</v>
@@ -14927,7 +14927,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G502" t="n">
-        <v>5.08726119995117</v>
+        <v>5.08726167678833</v>
       </c>
       <c r="H502" t="n">
         <v>5550</v>
@@ -15043,7 +15043,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G506" t="n">
-        <v>5.12669801712036</v>
+        <v>5.1266975402832</v>
       </c>
       <c r="H506" t="n">
         <v>5270</v>
@@ -15072,7 +15072,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G507" t="n">
-        <v>5.10697984695435</v>
+        <v>5.10697937011719</v>
       </c>
       <c r="H507" t="n">
         <v>3690</v>
@@ -15101,7 +15101,7 @@
         <v>5</v>
       </c>
       <c r="G508" t="n">
-        <v>4.92951774597168</v>
+        <v>4.92951679229736</v>
       </c>
       <c r="H508" t="n">
         <v>5700</v>
@@ -15130,7 +15130,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G509" t="n">
-        <v>5.06754350662231</v>
+        <v>5.06754398345947</v>
       </c>
       <c r="H509" t="n">
         <v>940</v>
@@ -15217,7 +15217,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G512" t="n">
-        <v>5.08726119995117</v>
+        <v>5.08726167678833</v>
       </c>
       <c r="H512" t="n">
         <v>14440</v>
@@ -15275,7 +15275,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G514" t="n">
-        <v>4.96895313262939</v>
+        <v>4.96895360946655</v>
       </c>
       <c r="H514" t="n">
         <v>2590</v>
@@ -15304,7 +15304,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G515" t="n">
-        <v>4.9492359161377</v>
+        <v>4.94923543930054</v>
       </c>
       <c r="H515" t="n">
         <v>3820</v>
@@ -15420,7 +15420,7 @@
         <v>5</v>
       </c>
       <c r="G519" t="n">
-        <v>4.92951774597168</v>
+        <v>4.92951679229736</v>
       </c>
       <c r="H519" t="n">
         <v>12340</v>
@@ -15565,7 +15565,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G524" t="n">
-        <v>4.9492359161377</v>
+        <v>4.94923543930054</v>
       </c>
       <c r="H524" t="n">
         <v>6910</v>
@@ -15652,7 +15652,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G527" t="n">
-        <v>4.85064554214478</v>
+        <v>4.85064506530762</v>
       </c>
       <c r="H527" t="n">
         <v>12990</v>
@@ -15913,7 +15913,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G536" t="n">
-        <v>4.71261882781982</v>
+        <v>4.71261835098267</v>
       </c>
       <c r="H536" t="n">
         <v>153850</v>
@@ -15971,7 +15971,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G538" t="n">
-        <v>4.89993953704834</v>
+        <v>4.8999400138855</v>
       </c>
       <c r="H538" t="n">
         <v>2830</v>
@@ -16000,7 +16000,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G539" t="n">
-        <v>4.85064554214478</v>
+        <v>4.85064506530762</v>
       </c>
       <c r="H539" t="n">
         <v>610</v>
@@ -16058,7 +16058,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G541" t="n">
-        <v>4.9492359161377</v>
+        <v>4.94923543930054</v>
       </c>
       <c r="H541" t="n">
         <v>2830</v>
@@ -16087,7 +16087,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G542" t="n">
-        <v>4.86050415039062</v>
+        <v>4.86050367355347</v>
       </c>
       <c r="H542" t="n">
         <v>200</v>
@@ -16232,7 +16232,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G547" t="n">
-        <v>4.62362098693848</v>
+        <v>4.62362051010132</v>
       </c>
       <c r="H547" t="n">
         <v>10330</v>
@@ -16261,7 +16261,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G548" t="n">
-        <v>4.57422304153442</v>
+        <v>4.57422399520874</v>
       </c>
       <c r="H548" t="n">
         <v>17160</v>
@@ -16290,7 +16290,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G549" t="n">
-        <v>4.5939826965332</v>
+        <v>4.59398221969604</v>
       </c>
       <c r="H549" t="n">
         <v>3190</v>
@@ -16319,7 +16319,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G550" t="n">
-        <v>4.64337968826294</v>
+        <v>4.6433801651001</v>
       </c>
       <c r="H550" t="n">
         <v>1990</v>
@@ -16348,7 +16348,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G551" t="n">
-        <v>4.74217557907104</v>
+        <v>4.7421760559082</v>
       </c>
       <c r="H551" t="n">
         <v>730</v>
@@ -16377,7 +16377,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G552" t="n">
-        <v>4.78169393539429</v>
+        <v>4.78169345855713</v>
       </c>
       <c r="H552" t="n">
         <v>1640</v>
@@ -16406,7 +16406,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G553" t="n">
-        <v>4.78169393539429</v>
+        <v>4.78169345855713</v>
       </c>
       <c r="H553" t="n">
         <v>0</v>
@@ -16435,7 +16435,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G554" t="n">
-        <v>4.78169393539429</v>
+        <v>4.78169345855713</v>
       </c>
       <c r="H554" t="n">
         <v>0</v>
@@ -16493,7 +16493,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G556" t="n">
-        <v>4.74217557907104</v>
+        <v>4.7421760559082</v>
       </c>
       <c r="H556" t="n">
         <v>13120</v>
@@ -16522,7 +16522,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G557" t="n">
-        <v>4.74217557907104</v>
+        <v>4.7421760559082</v>
       </c>
       <c r="H557" t="n">
         <v>260</v>
@@ -16609,7 +16609,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G560" t="n">
-        <v>4.80145215988159</v>
+        <v>4.80145263671875</v>
       </c>
       <c r="H560" t="n">
         <v>760</v>
@@ -16667,7 +16667,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G562" t="n">
-        <v>4.92988634109497</v>
+        <v>4.92988681793213</v>
       </c>
       <c r="H562" t="n">
         <v>2500</v>
@@ -16812,7 +16812,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G567" t="n">
-        <v>4.82121133804321</v>
+        <v>4.82121181488037</v>
       </c>
       <c r="H567" t="n">
         <v>2600</v>
@@ -16841,7 +16841,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G568" t="n">
-        <v>4.82121133804321</v>
+        <v>4.82121181488037</v>
       </c>
       <c r="H568" t="n">
         <v>0</v>
@@ -16870,7 +16870,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G569" t="n">
-        <v>4.82121133804321</v>
+        <v>4.82121181488037</v>
       </c>
       <c r="H569" t="n">
         <v>50</v>
@@ -16899,7 +16899,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G570" t="n">
-        <v>4.82121133804321</v>
+        <v>4.82121181488037</v>
       </c>
       <c r="H570" t="n">
         <v>0</v>
@@ -16986,7 +16986,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G573" t="n">
-        <v>4.43590974807739</v>
+        <v>4.43590927124023</v>
       </c>
       <c r="H573" t="n">
         <v>4370</v>
@@ -17044,7 +17044,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G575" t="n">
-        <v>4.32723522186279</v>
+        <v>4.32723474502563</v>
       </c>
       <c r="H575" t="n">
         <v>1010</v>
@@ -17073,7 +17073,7 @@
         <v>4.5</v>
       </c>
       <c r="G576" t="n">
-        <v>4.4457893371582</v>
+        <v>4.44578981399536</v>
       </c>
       <c r="H576" t="n">
         <v>2400</v>
@@ -17102,7 +17102,7 @@
         <v>4.5</v>
       </c>
       <c r="G577" t="n">
-        <v>4.4457893371582</v>
+        <v>4.44578981399536</v>
       </c>
       <c r="H577" t="n">
         <v>1890</v>
@@ -17131,7 +17131,7 @@
         <v>4.5</v>
       </c>
       <c r="G578" t="n">
-        <v>4.4457893371582</v>
+        <v>4.44578981399536</v>
       </c>
       <c r="H578" t="n">
         <v>550</v>
@@ -17218,7 +17218,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G581" t="n">
-        <v>4.40627098083496</v>
+        <v>4.40627145767212</v>
       </c>
       <c r="H581" t="n">
         <v>1200</v>
@@ -17276,7 +17276,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G583" t="n">
-        <v>4.64337968826294</v>
+        <v>4.6433801651001</v>
       </c>
       <c r="H583" t="n">
         <v>1100</v>
@@ -17305,7 +17305,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G584" t="n">
-        <v>4.78169393539429</v>
+        <v>4.78169345855713</v>
       </c>
       <c r="H584" t="n">
         <v>3210</v>
@@ -17334,7 +17334,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G585" t="n">
-        <v>4.5939826965332</v>
+        <v>4.59398221969604</v>
       </c>
       <c r="H585" t="n">
         <v>4270</v>
@@ -17363,7 +17363,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G586" t="n">
-        <v>4.74217557907104</v>
+        <v>4.7421760559082</v>
       </c>
       <c r="H586" t="n">
         <v>200</v>
@@ -17392,7 +17392,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G587" t="n">
-        <v>4.43590974807739</v>
+        <v>4.43590927124023</v>
       </c>
       <c r="H587" t="n">
         <v>18770</v>
@@ -17450,7 +17450,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G589" t="n">
-        <v>4.43590974807739</v>
+        <v>4.43590927124023</v>
       </c>
       <c r="H589" t="n">
         <v>3330</v>
@@ -17479,7 +17479,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G590" t="n">
-        <v>4.3865122795105</v>
+        <v>4.38651275634766</v>
       </c>
       <c r="H590" t="n">
         <v>37290</v>
@@ -17508,7 +17508,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G591" t="n">
-        <v>4.34699392318726</v>
+        <v>4.34699440002441</v>
       </c>
       <c r="H591" t="n">
         <v>420</v>
@@ -17537,7 +17537,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G592" t="n">
-        <v>4.34699392318726</v>
+        <v>4.34699440002441</v>
       </c>
       <c r="H592" t="n">
         <v>35740</v>
@@ -17566,7 +17566,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G593" t="n">
-        <v>4.34699392318726</v>
+        <v>4.34699440002441</v>
       </c>
       <c r="H593" t="n">
         <v>10500</v>
@@ -17595,7 +17595,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G594" t="n">
-        <v>4.48530721664429</v>
+        <v>4.48530769348145</v>
       </c>
       <c r="H594" t="n">
         <v>1520</v>
@@ -17653,7 +17653,7 @@
         <v>4.5</v>
       </c>
       <c r="G596" t="n">
-        <v>4.4457893371582</v>
+        <v>4.44578981399536</v>
       </c>
       <c r="H596" t="n">
         <v>3880</v>
@@ -17682,7 +17682,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G597" t="n">
-        <v>4.40627098083496</v>
+        <v>4.40627145767212</v>
       </c>
       <c r="H597" t="n">
         <v>1930</v>
@@ -17740,7 +17740,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G599" t="n">
-        <v>4.43590974807739</v>
+        <v>4.43590927124023</v>
       </c>
       <c r="H599" t="n">
         <v>690</v>
@@ -17769,7 +17769,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G600" t="n">
-        <v>4.48530721664429</v>
+        <v>4.48530769348145</v>
       </c>
       <c r="H600" t="n">
         <v>1360</v>
@@ -17827,7 +17827,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G602" t="n">
-        <v>4.5939826965332</v>
+        <v>4.59398221969604</v>
       </c>
       <c r="H602" t="n">
         <v>1680</v>
@@ -17856,7 +17856,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G603" t="n">
-        <v>4.64337968826294</v>
+        <v>4.6433801651001</v>
       </c>
       <c r="H603" t="n">
         <v>1550</v>
@@ -17914,7 +17914,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G605" t="n">
-        <v>4.83109092712402</v>
+        <v>4.83109140396118</v>
       </c>
       <c r="H605" t="n">
         <v>9220</v>
@@ -17943,7 +17943,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G606" t="n">
-        <v>4.89036846160889</v>
+        <v>4.89036798477173</v>
       </c>
       <c r="H606" t="n">
         <v>2760</v>
@@ -18146,7 +18146,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G613" t="n">
-        <v>4.78169393539429</v>
+        <v>4.78169345855713</v>
       </c>
       <c r="H613" t="n">
         <v>1500</v>
@@ -18233,7 +18233,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G616" t="n">
-        <v>4.97928380966187</v>
+        <v>4.97928428649902</v>
       </c>
       <c r="H616" t="n">
         <v>13050</v>
@@ -18262,7 +18262,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G617" t="n">
-        <v>4.97928380966187</v>
+        <v>4.97928428649902</v>
       </c>
       <c r="H617" t="n">
         <v>2400</v>
@@ -18320,7 +18320,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G619" t="n">
-        <v>4.97928380966187</v>
+        <v>4.97928428649902</v>
       </c>
       <c r="H619" t="n">
         <v>1000</v>
@@ -18523,7 +18523,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G626" t="n">
-        <v>4.92988634109497</v>
+        <v>4.92988681793213</v>
       </c>
       <c r="H626" t="n">
         <v>49150</v>
@@ -18581,7 +18581,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G628" t="n">
-        <v>4.87060880661011</v>
+        <v>4.87060928344727</v>
       </c>
       <c r="H628" t="n">
         <v>1000</v>
@@ -18697,7 +18697,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G632" t="n">
-        <v>4.7520546913147</v>
+        <v>4.75205516815186</v>
       </c>
       <c r="H632" t="n">
         <v>3780</v>
@@ -18755,7 +18755,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G634" t="n">
-        <v>4.92988634109497</v>
+        <v>4.92988681793213</v>
       </c>
       <c r="H634" t="n">
         <v>4840</v>
@@ -18813,7 +18813,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G636" t="n">
-        <v>4.89036846160889</v>
+        <v>4.89036798477173</v>
       </c>
       <c r="H636" t="n">
         <v>1500</v>
@@ -18900,7 +18900,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G639" t="n">
-        <v>4.87060880661011</v>
+        <v>4.87060928344727</v>
       </c>
       <c r="H639" t="n">
         <v>6120</v>
@@ -19016,7 +19016,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G643" t="n">
-        <v>4.73229598999023</v>
+        <v>4.73229551315308</v>
       </c>
       <c r="H643" t="n">
         <v>4150</v>
@@ -19103,7 +19103,7 @@
         <v>4.5</v>
       </c>
       <c r="G646" t="n">
-        <v>4.4457893371582</v>
+        <v>4.44578981399536</v>
       </c>
       <c r="H646" t="n">
         <v>8070</v>
@@ -19132,7 +19132,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G647" t="n">
-        <v>4.34699392318726</v>
+        <v>4.34699440002441</v>
       </c>
       <c r="H647" t="n">
         <v>89070</v>
@@ -19161,7 +19161,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G648" t="n">
-        <v>4.34699392318726</v>
+        <v>4.34699440002441</v>
       </c>
       <c r="H648" t="n">
         <v>66390</v>
@@ -19219,7 +19219,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G650" t="n">
-        <v>4.52482509613037</v>
+        <v>4.52482557296753</v>
       </c>
       <c r="H650" t="n">
         <v>11950</v>
@@ -19277,7 +19277,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G652" t="n">
-        <v>4.68289756774902</v>
+        <v>4.68289804458618</v>
       </c>
       <c r="H652" t="n">
         <v>470</v>
@@ -19451,7 +19451,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G658" t="n">
-        <v>4.80145215988159</v>
+        <v>4.80145263671875</v>
       </c>
       <c r="H658" t="n">
         <v>1750</v>
@@ -19480,7 +19480,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G659" t="n">
-        <v>4.74217557907104</v>
+        <v>4.7421760559082</v>
       </c>
       <c r="H659" t="n">
         <v>60</v>
@@ -19509,7 +19509,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G660" t="n">
-        <v>4.74217557907104</v>
+        <v>4.7421760559082</v>
       </c>
       <c r="H660" t="n">
         <v>12790</v>
@@ -19567,7 +19567,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G662" t="n">
-        <v>4.74217557907104</v>
+        <v>4.7421760559082</v>
       </c>
       <c r="H662" t="n">
         <v>10540</v>
@@ -19596,7 +19596,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G663" t="n">
-        <v>4.95952558517456</v>
+        <v>4.9595251083374</v>
       </c>
       <c r="H663" t="n">
         <v>3000</v>
@@ -19712,7 +19712,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G667" t="n">
-        <v>4.82121133804321</v>
+        <v>4.82121181488037</v>
       </c>
       <c r="H667" t="n">
         <v>8350</v>
@@ -19770,7 +19770,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G669" t="n">
-        <v>5.11759757995605</v>
+        <v>5.1175971031189</v>
       </c>
       <c r="H669" t="n">
         <v>13730</v>
@@ -19799,7 +19799,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G670" t="n">
-        <v>5.11759757995605</v>
+        <v>5.1175971031189</v>
       </c>
       <c r="H670" t="n">
         <v>340</v>
@@ -19857,7 +19857,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G672" t="n">
-        <v>5.11759757995605</v>
+        <v>5.1175971031189</v>
       </c>
       <c r="H672" t="n">
         <v>3970</v>
@@ -19944,7 +19944,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G675" t="n">
-        <v>4.97928380966187</v>
+        <v>4.97928428649902</v>
       </c>
       <c r="H675" t="n">
         <v>177850</v>
@@ -20002,7 +20002,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G677" t="n">
-        <v>4.89036846160889</v>
+        <v>4.89036798477173</v>
       </c>
       <c r="H677" t="n">
         <v>54910</v>
@@ -20031,7 +20031,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G678" t="n">
-        <v>4.74217557907104</v>
+        <v>4.7421760559082</v>
       </c>
       <c r="H678" t="n">
         <v>42730</v>
@@ -20089,7 +20089,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G680" t="n">
-        <v>4.73229598999023</v>
+        <v>4.73229551315308</v>
       </c>
       <c r="H680" t="n">
         <v>23420</v>
@@ -20205,7 +20205,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G684" t="n">
-        <v>4.52482509613037</v>
+        <v>4.52482557296753</v>
       </c>
       <c r="H684" t="n">
         <v>1210</v>
@@ -20234,7 +20234,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G685" t="n">
-        <v>4.34699392318726</v>
+        <v>4.34699440002441</v>
       </c>
       <c r="H685" t="n">
         <v>19270</v>
@@ -20292,7 +20292,7 @@
         <v>4.5</v>
       </c>
       <c r="G687" t="n">
-        <v>4.4457893371582</v>
+        <v>4.44578981399536</v>
       </c>
       <c r="H687" t="n">
         <v>5450</v>
@@ -20321,7 +20321,7 @@
         <v>4.5</v>
       </c>
       <c r="G688" t="n">
-        <v>4.4457893371582</v>
+        <v>4.44578981399536</v>
       </c>
       <c r="H688" t="n">
         <v>6510</v>
@@ -20379,7 +20379,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G690" t="n">
-        <v>4.71253633499146</v>
+        <v>4.71253681182861</v>
       </c>
       <c r="H690" t="n">
         <v>19330</v>
@@ -20553,7 +20553,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G696" t="n">
-        <v>5.216392993927</v>
+        <v>5.21639251708984</v>
       </c>
       <c r="H696" t="n">
         <v>1320</v>
@@ -20611,7 +20611,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G698" t="n">
-        <v>5.11759757995605</v>
+        <v>5.1175971031189</v>
       </c>
       <c r="H698" t="n">
         <v>3510</v>
@@ -20640,7 +20640,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G699" t="n">
-        <v>5.11759757995605</v>
+        <v>5.1175971031189</v>
       </c>
       <c r="H699" t="n">
         <v>0</v>
@@ -20756,7 +20756,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G703" t="n">
-        <v>4.87060880661011</v>
+        <v>4.87060928344727</v>
       </c>
       <c r="H703" t="n">
         <v>5400</v>
@@ -20785,7 +20785,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G704" t="n">
-        <v>4.74217557907104</v>
+        <v>4.7421760559082</v>
       </c>
       <c r="H704" t="n">
         <v>5760</v>
@@ -20901,7 +20901,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G708" t="n">
-        <v>5.11759757995605</v>
+        <v>5.1175971031189</v>
       </c>
       <c r="H708" t="n">
         <v>8710</v>
@@ -20930,7 +20930,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G709" t="n">
-        <v>4.92988634109497</v>
+        <v>4.92988681793213</v>
       </c>
       <c r="H709" t="n">
         <v>2230</v>
@@ -20959,7 +20959,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G710" t="n">
-        <v>4.92988634109497</v>
+        <v>4.92988681793213</v>
       </c>
       <c r="H710" t="n">
         <v>2210</v>
@@ -21046,7 +21046,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G713" t="n">
-        <v>4.71253633499146</v>
+        <v>4.71253681182861</v>
       </c>
       <c r="H713" t="n">
         <v>4900</v>
@@ -21075,7 +21075,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G714" t="n">
-        <v>4.6038613319397</v>
+        <v>4.60386180877686</v>
       </c>
       <c r="H714" t="n">
         <v>5550</v>
@@ -21104,7 +21104,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G715" t="n">
-        <v>4.71253633499146</v>
+        <v>4.71253681182861</v>
       </c>
       <c r="H715" t="n">
         <v>4150</v>
@@ -21162,7 +21162,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G717" t="n">
-        <v>4.78169393539429</v>
+        <v>4.78169345855713</v>
       </c>
       <c r="H717" t="n">
         <v>2530</v>
@@ -21191,7 +21191,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G718" t="n">
-        <v>4.82121133804321</v>
+        <v>4.82121181488037</v>
       </c>
       <c r="H718" t="n">
         <v>3100</v>
@@ -21220,7 +21220,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G719" t="n">
-        <v>4.95952558517456</v>
+        <v>4.9595251083374</v>
       </c>
       <c r="H719" t="n">
         <v>5320</v>
@@ -21278,7 +21278,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G721" t="n">
-        <v>5.09783792495728</v>
+        <v>5.09783840179443</v>
       </c>
       <c r="H721" t="n">
         <v>3950</v>
@@ -21336,7 +21336,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G723" t="n">
-        <v>5.11759757995605</v>
+        <v>5.1175971031189</v>
       </c>
       <c r="H723" t="n">
         <v>6040</v>
@@ -21365,7 +21365,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G724" t="n">
-        <v>5.11759757995605</v>
+        <v>5.1175971031189</v>
       </c>
       <c r="H724" t="n">
         <v>3650</v>
@@ -21452,7 +21452,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G727" t="n">
-        <v>4.97928380966187</v>
+        <v>4.97928428649902</v>
       </c>
       <c r="H727" t="n">
         <v>1500</v>
@@ -21539,7 +21539,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G730" t="n">
-        <v>4.82121133804321</v>
+        <v>4.82121181488037</v>
       </c>
       <c r="H730" t="n">
         <v>29580</v>
@@ -21568,7 +21568,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G731" t="n">
-        <v>4.74217557907104</v>
+        <v>4.7421760559082</v>
       </c>
       <c r="H731" t="n">
         <v>2850</v>
@@ -21655,7 +21655,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G734" t="n">
-        <v>4.78169393539429</v>
+        <v>4.78169345855713</v>
       </c>
       <c r="H734" t="n">
         <v>2150</v>
@@ -21742,7 +21742,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G737" t="n">
-        <v>4.89036846160889</v>
+        <v>4.89036798477173</v>
       </c>
       <c r="H737" t="n">
         <v>3100</v>
@@ -21771,7 +21771,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G738" t="n">
-        <v>4.82121133804321</v>
+        <v>4.82121181488037</v>
       </c>
       <c r="H738" t="n">
         <v>6100</v>
@@ -21800,7 +21800,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G739" t="n">
-        <v>4.82121133804321</v>
+        <v>4.82121181488037</v>
       </c>
       <c r="H739" t="n">
         <v>8640</v>
@@ -21858,7 +21858,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G741" t="n">
-        <v>4.82121133804321</v>
+        <v>4.82121181488037</v>
       </c>
       <c r="H741" t="n">
         <v>3340</v>
@@ -22032,7 +22032,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G747" t="n">
-        <v>4.74217557907104</v>
+        <v>4.7421760559082</v>
       </c>
       <c r="H747" t="n">
         <v>63650</v>
@@ -22061,7 +22061,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G748" t="n">
-        <v>4.7520546913147</v>
+        <v>4.75205516815186</v>
       </c>
       <c r="H748" t="n">
         <v>39170</v>
@@ -22090,7 +22090,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G749" t="n">
-        <v>4.78169393539429</v>
+        <v>4.78169345855713</v>
       </c>
       <c r="H749" t="n">
         <v>10810</v>
@@ -22148,7 +22148,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G751" t="n">
-        <v>4.17904186248779</v>
+        <v>4.17904233932495</v>
       </c>
       <c r="H751" t="n">
         <v>518850</v>
@@ -22177,7 +22177,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G752" t="n">
-        <v>4.22843980789185</v>
+        <v>4.228440284729</v>
       </c>
       <c r="H752" t="n">
         <v>104770</v>
@@ -22206,7 +22206,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G753" t="n">
-        <v>4.17904186248779</v>
+        <v>4.17904233932495</v>
       </c>
       <c r="H753" t="n">
         <v>125670</v>
@@ -22235,7 +22235,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G754" t="n">
-        <v>4.17904186248779</v>
+        <v>4.17904233932495</v>
       </c>
       <c r="H754" t="n">
         <v>21070</v>
@@ -22264,7 +22264,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G755" t="n">
-        <v>4.18892097473145</v>
+        <v>4.1889214515686</v>
       </c>
       <c r="H755" t="n">
         <v>62780</v>
@@ -22293,7 +22293,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G756" t="n">
-        <v>4.18892097473145</v>
+        <v>4.1889214515686</v>
       </c>
       <c r="H756" t="n">
         <v>28570</v>
@@ -22322,7 +22322,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G757" t="n">
-        <v>4.17904186248779</v>
+        <v>4.17904233932495</v>
       </c>
       <c r="H757" t="n">
         <v>17930</v>
@@ -22351,7 +22351,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G758" t="n">
-        <v>4.14940309524536</v>
+        <v>4.14940357208252</v>
       </c>
       <c r="H758" t="n">
         <v>13040</v>
@@ -22409,7 +22409,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G760" t="n">
-        <v>4.16916275024414</v>
+        <v>4.16916227340698</v>
       </c>
       <c r="H760" t="n">
         <v>13670</v>
@@ -22438,7 +22438,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G761" t="n">
-        <v>4.16916275024414</v>
+        <v>4.16916227340698</v>
       </c>
       <c r="H761" t="n">
         <v>5710</v>
@@ -22496,7 +22496,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G763" t="n">
-        <v>4.05060815811157</v>
+        <v>4.05060863494873</v>
       </c>
       <c r="H763" t="n">
         <v>55200</v>
@@ -22525,7 +22525,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G764" t="n">
-        <v>4.02096939086914</v>
+        <v>4.0209698677063</v>
       </c>
       <c r="H764" t="n">
         <v>16670</v>
@@ -22670,7 +22670,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G769" t="n">
-        <v>3.83325839042664</v>
+        <v>3.83325862884521</v>
       </c>
       <c r="H769" t="n">
         <v>12950</v>
@@ -22699,7 +22699,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G770" t="n">
-        <v>3.77398085594177</v>
+        <v>3.77398109436035</v>
       </c>
       <c r="H770" t="n">
         <v>16120</v>
@@ -22786,7 +22786,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G773" t="n">
-        <v>3.8036196231842</v>
+        <v>3.80361986160278</v>
       </c>
       <c r="H773" t="n">
         <v>4390</v>
@@ -22815,7 +22815,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G774" t="n">
-        <v>3.75422191619873</v>
+        <v>3.75422215461731</v>
       </c>
       <c r="H774" t="n">
         <v>58020</v>
@@ -22873,7 +22873,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G776" t="n">
-        <v>3.6949450969696</v>
+        <v>3.69494485855103</v>
       </c>
       <c r="H776" t="n">
         <v>5950</v>
@@ -22902,7 +22902,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G777" t="n">
-        <v>3.75422191619873</v>
+        <v>3.75422215461731</v>
       </c>
       <c r="H777" t="n">
         <v>185950</v>
@@ -23047,7 +23047,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G782" t="n">
-        <v>4.04072856903076</v>
+        <v>4.04072904586792</v>
       </c>
       <c r="H782" t="n">
         <v>14490</v>
@@ -23076,7 +23076,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G783" t="n">
-        <v>3.98145174980164</v>
+        <v>3.98145151138306</v>
       </c>
       <c r="H783" t="n">
         <v>8720</v>
@@ -23192,7 +23192,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G787" t="n">
-        <v>4.03084850311279</v>
+        <v>4.03084897994995</v>
       </c>
       <c r="H787" t="n">
         <v>5350</v>
@@ -23250,7 +23250,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G789" t="n">
-        <v>3.92217421531677</v>
+        <v>3.92217397689819</v>
       </c>
       <c r="H789" t="n">
         <v>12190</v>
@@ -23511,7 +23511,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G798" t="n">
-        <v>3.83325839042664</v>
+        <v>3.83325862884521</v>
       </c>
       <c r="H798" t="n">
         <v>3250</v>
@@ -23540,7 +23540,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G799" t="n">
-        <v>3.91229438781738</v>
+        <v>3.91229462623596</v>
       </c>
       <c r="H799" t="n">
         <v>3000</v>
@@ -49182,6 +49182,35 @@
         <v>101062</v>
       </c>
       <c r="I1683" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1684">
+      <c r="A1684" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1684" s="1" t="n">
+        <v>46323.3333333333</v>
+      </c>
+      <c r="C1684" t="n">
+        <v>3.18499994277954</v>
+      </c>
+      <c r="D1684" t="n">
+        <v>3.21000003814697</v>
+      </c>
+      <c r="E1684" t="n">
+        <v>3.17000007629395</v>
+      </c>
+      <c r="F1684" t="n">
+        <v>3.1800000667572</v>
+      </c>
+      <c r="G1684" t="n">
+        <v>3.1800000667572</v>
+      </c>
+      <c r="H1684" t="n">
+        <v>15687</v>
+      </c>
+      <c r="I1684" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/UD.MI.xlsx
+++ b/data/UD.MI.xlsx
@@ -485,7 +485,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G4" t="n">
-        <v>1.45913708209991</v>
+        <v>1.4591372013092</v>
       </c>
       <c r="H4" t="n">
         <v>240000</v>
@@ -514,7 +514,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G5" t="n">
-        <v>1.50843226909637</v>
+        <v>1.50843238830566</v>
       </c>
       <c r="H5" t="n">
         <v>88000</v>
@@ -572,7 +572,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G7" t="n">
-        <v>1.51829123497009</v>
+        <v>1.51829147338867</v>
       </c>
       <c r="H7" t="n">
         <v>61000</v>
@@ -601,7 +601,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G8" t="n">
-        <v>1.53800928592682</v>
+        <v>1.53800940513611</v>
       </c>
       <c r="H8" t="n">
         <v>19000</v>
@@ -630,7 +630,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G9" t="n">
-        <v>1.55772745609283</v>
+        <v>1.55772757530212</v>
       </c>
       <c r="H9" t="n">
         <v>13000</v>
@@ -659,7 +659,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G10" t="n">
-        <v>1.53800928592682</v>
+        <v>1.53800940513611</v>
       </c>
       <c r="H10" t="n">
         <v>17000</v>
@@ -688,7 +688,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G11" t="n">
-        <v>1.56265687942505</v>
+        <v>1.56265699863434</v>
       </c>
       <c r="H11" t="n">
         <v>16000</v>
@@ -746,7 +746,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G13" t="n">
-        <v>1.55772745609283</v>
+        <v>1.55772757530212</v>
       </c>
       <c r="H13" t="n">
         <v>2000</v>
@@ -804,7 +804,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G15" t="n">
-        <v>1.64645862579346</v>
+        <v>1.64645886421204</v>
       </c>
       <c r="H15" t="n">
         <v>31000</v>
@@ -833,7 +833,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G16" t="n">
-        <v>1.65631771087646</v>
+        <v>1.65631783008575</v>
       </c>
       <c r="H16" t="n">
         <v>28000</v>
@@ -862,7 +862,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G17" t="n">
-        <v>1.66617679595947</v>
+        <v>1.66617703437805</v>
       </c>
       <c r="H17" t="n">
         <v>14000</v>
@@ -891,7 +891,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G18" t="n">
-        <v>1.67603588104248</v>
+        <v>1.67603600025177</v>
       </c>
       <c r="H18" t="n">
         <v>36000</v>
@@ -920,7 +920,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G19" t="n">
-        <v>1.67603588104248</v>
+        <v>1.67603600025177</v>
       </c>
       <c r="H19" t="n">
         <v>18000</v>
@@ -949,7 +949,7 @@
         <v>1.67499995231628</v>
       </c>
       <c r="G20" t="n">
-        <v>1.65138828754425</v>
+        <v>1.65138816833496</v>
       </c>
       <c r="H20" t="n">
         <v>17000</v>
@@ -978,7 +978,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G21" t="n">
-        <v>1.65631771087646</v>
+        <v>1.65631783008575</v>
       </c>
       <c r="H21" t="n">
         <v>29000</v>
@@ -1007,7 +1007,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G22" t="n">
-        <v>1.62181127071381</v>
+        <v>1.62181103229523</v>
       </c>
       <c r="H22" t="n">
         <v>30000</v>
@@ -1036,7 +1036,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G23" t="n">
-        <v>1.59716379642487</v>
+        <v>1.59716367721558</v>
       </c>
       <c r="H23" t="n">
         <v>43000</v>
@@ -1094,7 +1094,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G25" t="n">
-        <v>1.58730459213257</v>
+        <v>1.58730471134186</v>
       </c>
       <c r="H25" t="n">
         <v>22000</v>
@@ -1239,7 +1239,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G30" t="n">
-        <v>1.62674057483673</v>
+        <v>1.62674069404602</v>
       </c>
       <c r="H30" t="n">
         <v>12000</v>
@@ -1297,7 +1297,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G32" t="n">
-        <v>1.59716379642487</v>
+        <v>1.59716367721558</v>
       </c>
       <c r="H32" t="n">
         <v>4000</v>
@@ -1355,7 +1355,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G34" t="n">
-        <v>1.62674057483673</v>
+        <v>1.62674069404602</v>
       </c>
       <c r="H34" t="n">
         <v>84000</v>
@@ -1384,7 +1384,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G35" t="n">
-        <v>1.62674057483673</v>
+        <v>1.62674069404602</v>
       </c>
       <c r="H35" t="n">
         <v>0</v>
@@ -1413,7 +1413,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G36" t="n">
-        <v>1.65631771087646</v>
+        <v>1.65631783008575</v>
       </c>
       <c r="H36" t="n">
         <v>8000</v>
@@ -1558,7 +1558,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G41" t="n">
-        <v>1.68589496612549</v>
+        <v>1.6858948469162</v>
       </c>
       <c r="H41" t="n">
         <v>14000</v>
@@ -1616,7 +1616,7 @@
         <v>1.72500002384186</v>
       </c>
       <c r="G43" t="n">
-        <v>1.70068359375</v>
+        <v>1.70068347454071</v>
       </c>
       <c r="H43" t="n">
         <v>21000</v>
@@ -1645,7 +1645,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G44" t="n">
-        <v>1.65631771087646</v>
+        <v>1.65631783008575</v>
       </c>
       <c r="H44" t="n">
         <v>21000</v>
@@ -1674,7 +1674,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G45" t="n">
-        <v>1.66617679595947</v>
+        <v>1.66617703437805</v>
       </c>
       <c r="H45" t="n">
         <v>1000</v>
@@ -1703,7 +1703,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G46" t="n">
-        <v>1.67603588104248</v>
+        <v>1.67603600025177</v>
       </c>
       <c r="H46" t="n">
         <v>12000</v>
@@ -1732,7 +1732,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G47" t="n">
-        <v>1.65631771087646</v>
+        <v>1.65631783008575</v>
       </c>
       <c r="H47" t="n">
         <v>5000</v>
@@ -1761,7 +1761,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G48" t="n">
-        <v>1.65631771087646</v>
+        <v>1.65631783008575</v>
       </c>
       <c r="H48" t="n">
         <v>0</v>
@@ -1790,7 +1790,7 @@
         <v>1.72500002384186</v>
       </c>
       <c r="G49" t="n">
-        <v>1.70068359375</v>
+        <v>1.70068347454071</v>
       </c>
       <c r="H49" t="n">
         <v>18000</v>
@@ -1877,7 +1877,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G52" t="n">
-        <v>1.74011945724487</v>
+        <v>1.74011969566345</v>
       </c>
       <c r="H52" t="n">
         <v>6000</v>
@@ -1906,7 +1906,7 @@
         <v>1.74500000476837</v>
       </c>
       <c r="G53" t="n">
-        <v>1.72040164470673</v>
+        <v>1.72040152549744</v>
       </c>
       <c r="H53" t="n">
         <v>7000</v>
@@ -1935,7 +1935,7 @@
         <v>1.72500002384186</v>
       </c>
       <c r="G54" t="n">
-        <v>1.70068359375</v>
+        <v>1.70068347454071</v>
       </c>
       <c r="H54" t="n">
         <v>10000</v>
@@ -1964,7 +1964,7 @@
         <v>1.72500002384186</v>
       </c>
       <c r="G55" t="n">
-        <v>1.70068359375</v>
+        <v>1.70068347454071</v>
       </c>
       <c r="H55" t="n">
         <v>15000</v>
@@ -2022,7 +2022,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G57" t="n">
-        <v>1.67603588104248</v>
+        <v>1.67603600025177</v>
       </c>
       <c r="H57" t="n">
         <v>30000</v>
@@ -2167,7 +2167,7 @@
         <v>1.67499995231628</v>
       </c>
       <c r="G62" t="n">
-        <v>1.65138828754425</v>
+        <v>1.65138816833496</v>
       </c>
       <c r="H62" t="n">
         <v>8000</v>
@@ -2225,7 +2225,7 @@
         <v>1.67499995231628</v>
       </c>
       <c r="G64" t="n">
-        <v>1.65138828754425</v>
+        <v>1.65138816833496</v>
       </c>
       <c r="H64" t="n">
         <v>9000</v>
@@ -2254,7 +2254,7 @@
         <v>1.67499995231628</v>
       </c>
       <c r="G65" t="n">
-        <v>1.65138828754425</v>
+        <v>1.65138816833496</v>
       </c>
       <c r="H65" t="n">
         <v>0</v>
@@ -2283,7 +2283,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G66" t="n">
-        <v>1.67603588104248</v>
+        <v>1.67603600025177</v>
       </c>
       <c r="H66" t="n">
         <v>3000</v>
@@ -2312,7 +2312,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G67" t="n">
-        <v>1.66617679595947</v>
+        <v>1.66617703437805</v>
       </c>
       <c r="H67" t="n">
         <v>10000</v>
@@ -2341,7 +2341,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G68" t="n">
-        <v>1.68589496612549</v>
+        <v>1.6858948469162</v>
       </c>
       <c r="H68" t="n">
         <v>7000</v>
@@ -2370,7 +2370,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G69" t="n">
-        <v>1.65631771087646</v>
+        <v>1.65631783008575</v>
       </c>
       <c r="H69" t="n">
         <v>19000</v>
@@ -2399,7 +2399,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G70" t="n">
-        <v>1.62674057483673</v>
+        <v>1.62674069404602</v>
       </c>
       <c r="H70" t="n">
         <v>41000</v>
@@ -2428,7 +2428,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G71" t="n">
-        <v>1.62674057483673</v>
+        <v>1.62674069404602</v>
       </c>
       <c r="H71" t="n">
         <v>0</v>
@@ -2457,7 +2457,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G72" t="n">
-        <v>1.64645862579346</v>
+        <v>1.64645886421204</v>
       </c>
       <c r="H72" t="n">
         <v>1000</v>
@@ -2486,7 +2486,7 @@
         <v>1.65499997138977</v>
       </c>
       <c r="G73" t="n">
-        <v>1.63167023658752</v>
+        <v>1.63167011737823</v>
       </c>
       <c r="H73" t="n">
         <v>176000</v>
@@ -2515,7 +2515,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G74" t="n">
-        <v>1.64645862579346</v>
+        <v>1.64645886421204</v>
       </c>
       <c r="H74" t="n">
         <v>1000</v>
@@ -2544,7 +2544,7 @@
         <v>1.67499995231628</v>
       </c>
       <c r="G75" t="n">
-        <v>1.65138828754425</v>
+        <v>1.65138816833496</v>
       </c>
       <c r="H75" t="n">
         <v>4000</v>
@@ -2602,7 +2602,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G77" t="n">
-        <v>1.68589496612549</v>
+        <v>1.6858948469162</v>
       </c>
       <c r="H77" t="n">
         <v>3000</v>
@@ -2631,7 +2631,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G78" t="n">
-        <v>1.64645862579346</v>
+        <v>1.64645886421204</v>
       </c>
       <c r="H78" t="n">
         <v>4000</v>
@@ -2660,7 +2660,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G79" t="n">
-        <v>1.67603588104248</v>
+        <v>1.67603600025177</v>
       </c>
       <c r="H79" t="n">
         <v>16000</v>
@@ -2689,7 +2689,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G80" t="n">
-        <v>1.67603588104248</v>
+        <v>1.67603600025177</v>
       </c>
       <c r="H80" t="n">
         <v>0</v>
@@ -2718,7 +2718,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G81" t="n">
-        <v>1.67603588104248</v>
+        <v>1.67603600025177</v>
       </c>
       <c r="H81" t="n">
         <v>0</v>
@@ -2747,7 +2747,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G82" t="n">
-        <v>1.65631771087646</v>
+        <v>1.65631783008575</v>
       </c>
       <c r="H82" t="n">
         <v>1000</v>
@@ -2776,7 +2776,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G83" t="n">
-        <v>1.65631771087646</v>
+        <v>1.65631783008575</v>
       </c>
       <c r="H83" t="n">
         <v>8000</v>
@@ -2834,7 +2834,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G85" t="n">
-        <v>1.62674057483673</v>
+        <v>1.62674069404602</v>
       </c>
       <c r="H85" t="n">
         <v>7000</v>
@@ -2863,7 +2863,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G86" t="n">
-        <v>1.62674057483673</v>
+        <v>1.62674069404602</v>
       </c>
       <c r="H86" t="n">
         <v>0</v>
@@ -3037,7 +3037,7 @@
         <v>1.62999999523163</v>
       </c>
       <c r="G92" t="n">
-        <v>1.60702264308929</v>
+        <v>1.60702276229858</v>
       </c>
       <c r="H92" t="n">
         <v>32000</v>
@@ -3124,7 +3124,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G95" t="n">
-        <v>1.58730459213257</v>
+        <v>1.58730471134186</v>
       </c>
       <c r="H95" t="n">
         <v>11000</v>
@@ -3153,7 +3153,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G96" t="n">
-        <v>1.62181127071381</v>
+        <v>1.62181103229523</v>
       </c>
       <c r="H96" t="n">
         <v>16000</v>
@@ -3182,7 +3182,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G97" t="n">
-        <v>1.58730459213257</v>
+        <v>1.58730471134186</v>
       </c>
       <c r="H97" t="n">
         <v>31000</v>
@@ -3211,7 +3211,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G98" t="n">
-        <v>1.58730459213257</v>
+        <v>1.58730471134186</v>
       </c>
       <c r="H98" t="n">
         <v>11000</v>
@@ -3240,7 +3240,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G99" t="n">
-        <v>1.62674057483673</v>
+        <v>1.62674069404602</v>
       </c>
       <c r="H99" t="n">
         <v>7000</v>
@@ -3269,7 +3269,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G100" t="n">
-        <v>1.62674057483673</v>
+        <v>1.62674069404602</v>
       </c>
       <c r="H100" t="n">
         <v>0</v>
@@ -3298,7 +3298,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G101" t="n">
-        <v>1.65631771087646</v>
+        <v>1.65631783008575</v>
       </c>
       <c r="H101" t="n">
         <v>50000</v>
@@ -3327,7 +3327,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G102" t="n">
-        <v>1.62674057483673</v>
+        <v>1.62674069404602</v>
       </c>
       <c r="H102" t="n">
         <v>9000</v>
@@ -3414,7 +3414,7 @@
         <v>1.63499999046326</v>
       </c>
       <c r="G105" t="n">
-        <v>1.61195206642151</v>
+        <v>1.6119521856308</v>
       </c>
       <c r="H105" t="n">
         <v>26000</v>
@@ -3472,7 +3472,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G107" t="n">
-        <v>1.62674057483673</v>
+        <v>1.62674069404602</v>
       </c>
       <c r="H107" t="n">
         <v>3000</v>
@@ -3501,7 +3501,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G108" t="n">
-        <v>1.62674057483673</v>
+        <v>1.62674069404602</v>
       </c>
       <c r="H108" t="n">
         <v>1000</v>
@@ -3530,7 +3530,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G109" t="n">
-        <v>1.66617679595947</v>
+        <v>1.66617703437805</v>
       </c>
       <c r="H109" t="n">
         <v>15000</v>
@@ -3559,7 +3559,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G110" t="n">
-        <v>1.67603588104248</v>
+        <v>1.67603600025177</v>
       </c>
       <c r="H110" t="n">
         <v>26000</v>
@@ -3588,7 +3588,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G111" t="n">
-        <v>1.67603588104248</v>
+        <v>1.67603600025177</v>
       </c>
       <c r="H111" t="n">
         <v>53000</v>
@@ -3617,7 +3617,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G112" t="n">
-        <v>1.67603588104248</v>
+        <v>1.67603600025177</v>
       </c>
       <c r="H112" t="n">
         <v>10000</v>
@@ -3646,7 +3646,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G113" t="n">
-        <v>1.67603588104248</v>
+        <v>1.67603600025177</v>
       </c>
       <c r="H113" t="n">
         <v>6000</v>
@@ -3675,7 +3675,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G114" t="n">
-        <v>1.67603588104248</v>
+        <v>1.67603600025177</v>
       </c>
       <c r="H114" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G115" t="n">
-        <v>1.67603588104248</v>
+        <v>1.67603600025177</v>
       </c>
       <c r="H115" t="n">
         <v>22000</v>
@@ -3762,7 +3762,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G117" t="n">
-        <v>1.68589496612549</v>
+        <v>1.6858948469162</v>
       </c>
       <c r="H117" t="n">
         <v>22000</v>
@@ -3791,7 +3791,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G118" t="n">
-        <v>1.68589496612549</v>
+        <v>1.6858948469162</v>
       </c>
       <c r="H118" t="n">
         <v>0</v>
@@ -3849,7 +3849,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G120" t="n">
-        <v>1.89786422252655</v>
+        <v>1.89786410331726</v>
       </c>
       <c r="H120" t="n">
         <v>60000</v>
@@ -4023,7 +4023,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G126" t="n">
-        <v>1.83378040790558</v>
+        <v>1.83378028869629</v>
       </c>
       <c r="H126" t="n">
         <v>15000</v>
@@ -4139,7 +4139,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G130" t="n">
-        <v>1.83871006965637</v>
+        <v>1.83870995044708</v>
       </c>
       <c r="H130" t="n">
         <v>8000</v>
@@ -4168,7 +4168,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G131" t="n">
-        <v>1.83378040790558</v>
+        <v>1.83378028869629</v>
       </c>
       <c r="H131" t="n">
         <v>1000</v>
@@ -4516,7 +4516,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G143" t="n">
-        <v>1.79927384853363</v>
+        <v>1.79927396774292</v>
       </c>
       <c r="H143" t="n">
         <v>10000</v>
@@ -4661,7 +4661,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G148" t="n">
-        <v>1.7598375082016</v>
+        <v>1.75983762741089</v>
       </c>
       <c r="H148" t="n">
         <v>12000</v>
@@ -4748,7 +4748,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G151" t="n">
-        <v>1.74011945724487</v>
+        <v>1.74011969566345</v>
       </c>
       <c r="H151" t="n">
         <v>30000</v>
@@ -4777,7 +4777,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G152" t="n">
-        <v>1.7696967124939</v>
+        <v>1.76969659328461</v>
       </c>
       <c r="H152" t="n">
         <v>4000</v>
@@ -4922,7 +4922,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G157" t="n">
-        <v>1.83871006965637</v>
+        <v>1.83870995044708</v>
       </c>
       <c r="H157" t="n">
         <v>2000</v>
@@ -4951,7 +4951,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G158" t="n">
-        <v>1.83378040790558</v>
+        <v>1.83378028869629</v>
       </c>
       <c r="H158" t="n">
         <v>7000</v>
@@ -5299,7 +5299,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G170" t="n">
-        <v>1.83871006965637</v>
+        <v>1.83870995044708</v>
       </c>
       <c r="H170" t="n">
         <v>39000</v>
@@ -5328,7 +5328,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G171" t="n">
-        <v>1.83871006965637</v>
+        <v>1.83870995044708</v>
       </c>
       <c r="H171" t="n">
         <v>0</v>
@@ -5357,7 +5357,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G172" t="n">
-        <v>1.81406259536743</v>
+        <v>1.81406247615814</v>
       </c>
       <c r="H172" t="n">
         <v>3000</v>
@@ -5473,7 +5473,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G176" t="n">
-        <v>1.83871006965637</v>
+        <v>1.83870995044708</v>
       </c>
       <c r="H176" t="n">
         <v>47000</v>
@@ -5531,7 +5531,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G178" t="n">
-        <v>1.87814605236053</v>
+        <v>1.87814617156982</v>
       </c>
       <c r="H178" t="n">
         <v>75000</v>
@@ -5589,7 +5589,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G180" t="n">
-        <v>1.88800513744354</v>
+        <v>1.88800525665283</v>
       </c>
       <c r="H180" t="n">
         <v>73000</v>
@@ -5618,7 +5618,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G181" t="n">
-        <v>1.90279364585876</v>
+        <v>1.90279352664948</v>
       </c>
       <c r="H181" t="n">
         <v>23000</v>
@@ -5647,7 +5647,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G182" t="n">
-        <v>1.91265285015106</v>
+        <v>1.91265273094177</v>
       </c>
       <c r="H182" t="n">
         <v>6000</v>
@@ -5792,7 +5792,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G187" t="n">
-        <v>1.95208883285522</v>
+        <v>1.95208895206451</v>
       </c>
       <c r="H187" t="n">
         <v>7000</v>
@@ -5879,7 +5879,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G190" t="n">
-        <v>1.91758239269257</v>
+        <v>1.91758227348328</v>
       </c>
       <c r="H190" t="n">
         <v>76000</v>
@@ -5995,7 +5995,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G194" t="n">
-        <v>1.92251181602478</v>
+        <v>1.92251169681549</v>
       </c>
       <c r="H194" t="n">
         <v>6000</v>
@@ -6024,7 +6024,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G195" t="n">
-        <v>1.86335754394531</v>
+        <v>1.86335742473602</v>
       </c>
       <c r="H195" t="n">
         <v>42000</v>
@@ -6082,7 +6082,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G197" t="n">
-        <v>1.91265285015106</v>
+        <v>1.91265273094177</v>
       </c>
       <c r="H197" t="n">
         <v>24000</v>
@@ -6111,7 +6111,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G198" t="n">
-        <v>1.91265285015106</v>
+        <v>1.91265273094177</v>
       </c>
       <c r="H198" t="n">
         <v>17000</v>
@@ -6140,7 +6140,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G199" t="n">
-        <v>1.91758239269257</v>
+        <v>1.91758227348328</v>
       </c>
       <c r="H199" t="n">
         <v>3000</v>
@@ -6169,7 +6169,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G200" t="n">
-        <v>1.92251181602478</v>
+        <v>1.92251169681549</v>
       </c>
       <c r="H200" t="n">
         <v>18000</v>
@@ -6227,7 +6227,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G202" t="n">
-        <v>1.91265285015106</v>
+        <v>1.91265273094177</v>
       </c>
       <c r="H202" t="n">
         <v>18000</v>
@@ -6285,7 +6285,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G204" t="n">
-        <v>1.92251181602478</v>
+        <v>1.92251169681549</v>
       </c>
       <c r="H204" t="n">
         <v>8000</v>
@@ -6401,7 +6401,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G208" t="n">
-        <v>1.95208883285522</v>
+        <v>1.95208895206451</v>
       </c>
       <c r="H208" t="n">
         <v>18000</v>
@@ -6459,7 +6459,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G210" t="n">
-        <v>1.95701825618744</v>
+        <v>1.95701837539673</v>
       </c>
       <c r="H210" t="n">
         <v>16000</v>
@@ -6517,7 +6517,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G212" t="n">
-        <v>1.94222986698151</v>
+        <v>1.9422299861908</v>
       </c>
       <c r="H212" t="n">
         <v>31000</v>
@@ -6546,7 +6546,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G213" t="n">
-        <v>1.92251181602478</v>
+        <v>1.92251169681549</v>
       </c>
       <c r="H213" t="n">
         <v>20000</v>
@@ -6575,7 +6575,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G214" t="n">
-        <v>1.92251181602478</v>
+        <v>1.92251169681549</v>
       </c>
       <c r="H214" t="n">
         <v>1000</v>
@@ -6604,7 +6604,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G215" t="n">
-        <v>1.95701825618744</v>
+        <v>1.95701837539673</v>
       </c>
       <c r="H215" t="n">
         <v>1000</v>
@@ -6633,7 +6633,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G216" t="n">
-        <v>1.91265285015106</v>
+        <v>1.91265273094177</v>
       </c>
       <c r="H216" t="n">
         <v>9000</v>
@@ -6662,7 +6662,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G217" t="n">
-        <v>1.89786422252655</v>
+        <v>1.89786410331726</v>
       </c>
       <c r="H217" t="n">
         <v>3000</v>
@@ -6749,7 +6749,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G220" t="n">
-        <v>1.89786422252655</v>
+        <v>1.89786410331726</v>
       </c>
       <c r="H220" t="n">
         <v>3000</v>
@@ -6778,7 +6778,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G221" t="n">
-        <v>1.92251181602478</v>
+        <v>1.92251169681549</v>
       </c>
       <c r="H221" t="n">
         <v>2000</v>
@@ -6807,7 +6807,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G222" t="n">
-        <v>1.92251181602478</v>
+        <v>1.92251169681549</v>
       </c>
       <c r="H222" t="n">
         <v>0</v>
@@ -6836,7 +6836,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G223" t="n">
-        <v>1.92251181602478</v>
+        <v>1.92251169681549</v>
       </c>
       <c r="H223" t="n">
         <v>0</v>
@@ -6865,7 +6865,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G224" t="n">
-        <v>1.92251181602478</v>
+        <v>1.92251169681549</v>
       </c>
       <c r="H224" t="n">
         <v>3000</v>
@@ -6894,7 +6894,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G225" t="n">
-        <v>1.94222986698151</v>
+        <v>1.9422299861908</v>
       </c>
       <c r="H225" t="n">
         <v>5000</v>
@@ -6952,7 +6952,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G227" t="n">
-        <v>1.98166608810425</v>
+        <v>1.98166596889496</v>
       </c>
       <c r="H227" t="n">
         <v>10000</v>
@@ -6981,7 +6981,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G228" t="n">
-        <v>2.00138401985168</v>
+        <v>2.00138425827026</v>
       </c>
       <c r="H228" t="n">
         <v>18000</v>
@@ -7039,7 +7039,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G230" t="n">
-        <v>2.0211021900177</v>
+        <v>2.02110242843628</v>
       </c>
       <c r="H230" t="n">
         <v>46000</v>
@@ -7155,7 +7155,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G234" t="n">
-        <v>2.16898775100708</v>
+        <v>2.16898798942566</v>
       </c>
       <c r="H234" t="n">
         <v>85000</v>
@@ -7184,7 +7184,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G235" t="n">
-        <v>2.14926981925964</v>
+        <v>2.14926958084106</v>
       </c>
       <c r="H235" t="n">
         <v>11000</v>
@@ -7213,7 +7213,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G236" t="n">
-        <v>2.19856476783752</v>
+        <v>2.1985650062561</v>
       </c>
       <c r="H236" t="n">
         <v>9000</v>
@@ -7329,7 +7329,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G240" t="n">
-        <v>2.20842361450195</v>
+        <v>2.20842385292053</v>
       </c>
       <c r="H240" t="n">
         <v>35000</v>
@@ -7387,7 +7387,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G242" t="n">
-        <v>2.25771880149841</v>
+        <v>2.25771903991699</v>
       </c>
       <c r="H242" t="n">
         <v>19000</v>
@@ -7445,7 +7445,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G244" t="n">
-        <v>2.29715490341187</v>
+        <v>2.29715514183044</v>
       </c>
       <c r="H244" t="n">
         <v>6000</v>
@@ -7474,7 +7474,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G245" t="n">
-        <v>2.29715490341187</v>
+        <v>2.29715514183044</v>
       </c>
       <c r="H245" t="n">
         <v>0</v>
@@ -7503,7 +7503,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G246" t="n">
-        <v>2.28729581832886</v>
+        <v>2.28729605674744</v>
       </c>
       <c r="H246" t="n">
         <v>12000</v>
@@ -7532,7 +7532,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G247" t="n">
-        <v>2.28729581832886</v>
+        <v>2.28729605674744</v>
       </c>
       <c r="H247" t="n">
         <v>2000</v>
@@ -7648,7 +7648,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G251" t="n">
-        <v>2.3365912437439</v>
+        <v>2.33659100532532</v>
       </c>
       <c r="H251" t="n">
         <v>8000</v>
@@ -7677,7 +7677,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G252" t="n">
-        <v>2.3365912437439</v>
+        <v>2.33659100532532</v>
       </c>
       <c r="H252" t="n">
         <v>0</v>
@@ -7764,7 +7764,7 @@
         <v>2.5</v>
       </c>
       <c r="G255" t="n">
-        <v>2.46475839614868</v>
+        <v>2.46475887298584</v>
       </c>
       <c r="H255" t="n">
         <v>11000</v>
@@ -7793,7 +7793,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G256" t="n">
-        <v>2.55348968505859</v>
+        <v>2.55348992347717</v>
       </c>
       <c r="H256" t="n">
         <v>21000</v>
@@ -7822,7 +7822,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G257" t="n">
-        <v>2.55348968505859</v>
+        <v>2.55348992347717</v>
       </c>
       <c r="H257" t="n">
         <v>6000</v>
@@ -7851,7 +7851,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G258" t="n">
-        <v>2.61264443397522</v>
+        <v>2.6126446723938</v>
       </c>
       <c r="H258" t="n">
         <v>6000</v>
@@ -7880,7 +7880,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G259" t="n">
-        <v>2.59292602539062</v>
+        <v>2.59292650222778</v>
       </c>
       <c r="H259" t="n">
         <v>5000</v>
@@ -7909,7 +7909,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G260" t="n">
-        <v>2.74081158638</v>
+        <v>2.74081182479858</v>
       </c>
       <c r="H260" t="n">
         <v>51000</v>
@@ -8112,7 +8112,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G267" t="n">
-        <v>2.8394021987915</v>
+        <v>2.83940196037292</v>
       </c>
       <c r="H267" t="n">
         <v>62000</v>
@@ -8199,7 +8199,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G270" t="n">
-        <v>2.77038860321045</v>
+        <v>2.77038884162903</v>
       </c>
       <c r="H270" t="n">
         <v>11000</v>
@@ -8257,7 +8257,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G272" t="n">
-        <v>2.99714660644531</v>
+        <v>2.99714636802673</v>
       </c>
       <c r="H272" t="n">
         <v>21000</v>
@@ -8286,7 +8286,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G273" t="n">
-        <v>2.96756958961487</v>
+        <v>2.96756935119629</v>
       </c>
       <c r="H273" t="n">
         <v>22000</v>
@@ -8315,7 +8315,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G274" t="n">
-        <v>3.26334047317505</v>
+        <v>3.26334023475647</v>
       </c>
       <c r="H274" t="n">
         <v>121000</v>
@@ -8344,7 +8344,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G275" t="n">
-        <v>3.26334047317505</v>
+        <v>3.26334023475647</v>
       </c>
       <c r="H275" t="n">
         <v>74000</v>
@@ -8373,7 +8373,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G276" t="n">
-        <v>3.29291725158691</v>
+        <v>3.29291772842407</v>
       </c>
       <c r="H276" t="n">
         <v>39000</v>
@@ -8402,7 +8402,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G277" t="n">
-        <v>3.17460918426514</v>
+        <v>3.17460942268372</v>
       </c>
       <c r="H277" t="n">
         <v>36000</v>
@@ -8431,7 +8431,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G278" t="n">
-        <v>3.18446803092957</v>
+        <v>3.18446826934814</v>
       </c>
       <c r="H278" t="n">
         <v>19000</v>
@@ -8460,7 +8460,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G279" t="n">
-        <v>3.3027765750885</v>
+        <v>3.30277633666992</v>
       </c>
       <c r="H279" t="n">
         <v>14000</v>
@@ -8489,7 +8489,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G280" t="n">
-        <v>3.25348114967346</v>
+        <v>3.25348138809204</v>
       </c>
       <c r="H280" t="n">
         <v>4000</v>
@@ -8518,7 +8518,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G281" t="n">
-        <v>3.18446803092957</v>
+        <v>3.18446826934814</v>
       </c>
       <c r="H281" t="n">
         <v>10000</v>
@@ -8547,7 +8547,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G282" t="n">
-        <v>3.21404528617859</v>
+        <v>3.21404552459717</v>
       </c>
       <c r="H282" t="n">
         <v>6000</v>
@@ -8576,7 +8576,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G283" t="n">
-        <v>3.24362254142761</v>
+        <v>3.24362206459045</v>
       </c>
       <c r="H283" t="n">
         <v>13000</v>
@@ -8605,7 +8605,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G284" t="n">
-        <v>3.19432759284973</v>
+        <v>3.19432735443115</v>
       </c>
       <c r="H284" t="n">
         <v>4000</v>
@@ -8634,7 +8634,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G285" t="n">
-        <v>3.35207176208496</v>
+        <v>3.35207200050354</v>
       </c>
       <c r="H285" t="n">
         <v>25000</v>
@@ -8779,7 +8779,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G290" t="n">
-        <v>3.72671508789062</v>
+        <v>3.72671484947205</v>
       </c>
       <c r="H290" t="n">
         <v>11000</v>
@@ -8895,7 +8895,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G294" t="n">
-        <v>3.53939342498779</v>
+        <v>3.53939318656921</v>
       </c>
       <c r="H294" t="n">
         <v>30000</v>
@@ -8924,7 +8924,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G295" t="n">
-        <v>3.5196750164032</v>
+        <v>3.51967525482178</v>
       </c>
       <c r="H295" t="n">
         <v>95000</v>
@@ -9069,7 +9069,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G300" t="n">
-        <v>3.48023891448975</v>
+        <v>3.4802393913269</v>
       </c>
       <c r="H300" t="n">
         <v>15000</v>
@@ -9272,7 +9272,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G307" t="n">
-        <v>3.97319102287292</v>
+        <v>3.9731912612915</v>
       </c>
       <c r="H307" t="n">
         <v>45000</v>
@@ -9359,7 +9359,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G310" t="n">
-        <v>4.33797550201416</v>
+        <v>4.33797597885132</v>
       </c>
       <c r="H310" t="n">
         <v>1000</v>
@@ -9417,7 +9417,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G312" t="n">
-        <v>3.99290919303894</v>
+        <v>3.99290895462036</v>
       </c>
       <c r="H312" t="n">
         <v>51000</v>
@@ -9475,7 +9475,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G314" t="n">
-        <v>4.05206298828125</v>
+        <v>4.05206346511841</v>
       </c>
       <c r="H314" t="n">
         <v>6000</v>
@@ -9591,7 +9591,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G318" t="n">
-        <v>4.17037200927734</v>
+        <v>4.17037153244019</v>
       </c>
       <c r="H318" t="n">
         <v>10000</v>
@@ -9620,7 +9620,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G319" t="n">
-        <v>4.24924421310425</v>
+        <v>4.24924373626709</v>
       </c>
       <c r="H319" t="n">
         <v>6000</v>
@@ -9678,7 +9678,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G321" t="n">
-        <v>4.13093519210815</v>
+        <v>4.13093566894531</v>
       </c>
       <c r="H321" t="n">
         <v>4000</v>
@@ -9707,7 +9707,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G322" t="n">
-        <v>4.10135793685913</v>
+        <v>4.10135841369629</v>
       </c>
       <c r="H322" t="n">
         <v>4000</v>
@@ -9823,7 +9823,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G326" t="n">
-        <v>4.00276803970337</v>
+        <v>4.00276851654053</v>
       </c>
       <c r="H326" t="n">
         <v>5000</v>
@@ -10084,7 +10084,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G335" t="n">
-        <v>4.17037200927734</v>
+        <v>4.17037153244019</v>
       </c>
       <c r="H335" t="n">
         <v>3000</v>
@@ -10113,7 +10113,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G336" t="n">
-        <v>4.00276803970337</v>
+        <v>4.00276851654053</v>
       </c>
       <c r="H336" t="n">
         <v>3000</v>
@@ -10142,7 +10142,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G337" t="n">
-        <v>4.00276803970337</v>
+        <v>4.00276851654053</v>
       </c>
       <c r="H337" t="n">
         <v>0</v>
@@ -10345,7 +10345,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G344" t="n">
-        <v>4.1112174987793</v>
+        <v>4.11121797561646</v>
       </c>
       <c r="H344" t="n">
         <v>1000</v>
@@ -10403,7 +10403,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G346" t="n">
-        <v>4.0422043800354</v>
+        <v>4.04220485687256</v>
       </c>
       <c r="H346" t="n">
         <v>2500</v>
@@ -10490,7 +10490,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G349" t="n">
-        <v>4.21966743469238</v>
+        <v>4.21966695785522</v>
       </c>
       <c r="H349" t="n">
         <v>21000</v>
@@ -10606,7 +10606,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G353" t="n">
-        <v>4.13093519210815</v>
+        <v>4.13093566894531</v>
       </c>
       <c r="H353" t="n">
         <v>9000</v>
@@ -10722,7 +10722,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G357" t="n">
-        <v>4.05206298828125</v>
+        <v>4.05206346511841</v>
       </c>
       <c r="H357" t="n">
         <v>10000</v>
@@ -10780,7 +10780,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G359" t="n">
-        <v>4.21966743469238</v>
+        <v>4.21966695785522</v>
       </c>
       <c r="H359" t="n">
         <v>14500</v>
@@ -10896,7 +10896,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G363" t="n">
-        <v>4.12107610702515</v>
+        <v>4.1210765838623</v>
       </c>
       <c r="H363" t="n">
         <v>500</v>
@@ -10925,7 +10925,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G364" t="n">
-        <v>4.12107610702515</v>
+        <v>4.1210765838623</v>
       </c>
       <c r="H364" t="n">
         <v>0</v>
@@ -10954,7 +10954,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G365" t="n">
-        <v>4.12107610702515</v>
+        <v>4.1210765838623</v>
       </c>
       <c r="H365" t="n">
         <v>0</v>
@@ -11099,7 +11099,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G370" t="n">
-        <v>4.10135793685913</v>
+        <v>4.10135841369629</v>
       </c>
       <c r="H370" t="n">
         <v>4500</v>
@@ -11128,7 +11128,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G371" t="n">
-        <v>4.01262760162354</v>
+        <v>4.01262712478638</v>
       </c>
       <c r="H371" t="n">
         <v>6000</v>
@@ -11360,7 +11360,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G379" t="n">
-        <v>4.21966743469238</v>
+        <v>4.21966695785522</v>
       </c>
       <c r="H379" t="n">
         <v>67000</v>
@@ -11389,7 +11389,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G380" t="n">
-        <v>4.21966743469238</v>
+        <v>4.21966695785522</v>
       </c>
       <c r="H380" t="n">
         <v>3000</v>
@@ -11418,7 +11418,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G381" t="n">
-        <v>4.2591028213501</v>
+        <v>4.25910329818726</v>
       </c>
       <c r="H381" t="n">
         <v>2500</v>
@@ -11447,7 +11447,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G382" t="n">
-        <v>4.29853963851929</v>
+        <v>4.29853916168213</v>
       </c>
       <c r="H382" t="n">
         <v>35000</v>
@@ -11476,7 +11476,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G383" t="n">
-        <v>4.30839824676514</v>
+        <v>4.30839776992798</v>
       </c>
       <c r="H383" t="n">
         <v>2500</v>
@@ -11505,7 +11505,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G384" t="n">
-        <v>4.33797550201416</v>
+        <v>4.33797597885132</v>
       </c>
       <c r="H384" t="n">
         <v>17000</v>
@@ -11563,7 +11563,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G386" t="n">
-        <v>4.30839824676514</v>
+        <v>4.30839776992798</v>
       </c>
       <c r="H386" t="n">
         <v>255000</v>
@@ -11679,7 +11679,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G390" t="n">
-        <v>4.33797550201416</v>
+        <v>4.33797597885132</v>
       </c>
       <c r="H390" t="n">
         <v>15000</v>
@@ -11708,7 +11708,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G391" t="n">
-        <v>4.30839824676514</v>
+        <v>4.30839776992798</v>
       </c>
       <c r="H391" t="n">
         <v>34000</v>
@@ -11766,7 +11766,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G393" t="n">
-        <v>4.33797550201416</v>
+        <v>4.33797597885132</v>
       </c>
       <c r="H393" t="n">
         <v>6000</v>
@@ -11795,7 +11795,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G394" t="n">
-        <v>4.4069881439209</v>
+        <v>4.40698862075806</v>
       </c>
       <c r="H394" t="n">
         <v>2000</v>
@@ -11824,7 +11824,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G395" t="n">
-        <v>4.24924421310425</v>
+        <v>4.24924373626709</v>
       </c>
       <c r="H395" t="n">
         <v>31500</v>
@@ -11911,7 +11911,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G398" t="n">
-        <v>4.0422043800354</v>
+        <v>4.04220485687256</v>
       </c>
       <c r="H398" t="n">
         <v>6000</v>
@@ -11940,7 +11940,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G399" t="n">
-        <v>4.0422043800354</v>
+        <v>4.04220485687256</v>
       </c>
       <c r="H399" t="n">
         <v>7500</v>
@@ -11969,7 +11969,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G400" t="n">
-        <v>4.0422043800354</v>
+        <v>4.04220485687256</v>
       </c>
       <c r="H400" t="n">
         <v>0</v>
@@ -12056,7 +12056,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G403" t="n">
-        <v>4.29853963851929</v>
+        <v>4.29853916168213</v>
       </c>
       <c r="H403" t="n">
         <v>26500</v>
@@ -12085,7 +12085,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G404" t="n">
-        <v>4.33797550201416</v>
+        <v>4.33797597885132</v>
       </c>
       <c r="H404" t="n">
         <v>37500</v>
@@ -12114,7 +12114,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G405" t="n">
-        <v>4.38727045059204</v>
+        <v>4.38726997375488</v>
       </c>
       <c r="H405" t="n">
         <v>13000</v>
@@ -12143,7 +12143,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G406" t="n">
-        <v>4.39712953567505</v>
+        <v>4.39713001251221</v>
       </c>
       <c r="H406" t="n">
         <v>19500</v>
@@ -12172,7 +12172,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G407" t="n">
-        <v>4.38727045059204</v>
+        <v>4.38726997375488</v>
       </c>
       <c r="H407" t="n">
         <v>6000</v>
@@ -12201,7 +12201,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G408" t="n">
-        <v>4.38727045059204</v>
+        <v>4.38726997375488</v>
       </c>
       <c r="H408" t="n">
         <v>85000</v>
@@ -12230,7 +12230,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G409" t="n">
-        <v>4.49571943283081</v>
+        <v>4.49571990966797</v>
       </c>
       <c r="H409" t="n">
         <v>23000</v>
@@ -12259,7 +12259,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G410" t="n">
-        <v>4.63374614715576</v>
+        <v>4.63374662399292</v>
       </c>
       <c r="H410" t="n">
         <v>92000</v>
@@ -12288,7 +12288,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G411" t="n">
-        <v>5.04782581329346</v>
+        <v>5.0478253364563</v>
       </c>
       <c r="H411" t="n">
         <v>104000</v>
@@ -12317,7 +12317,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G412" t="n">
-        <v>5.30416011810303</v>
+        <v>5.30416059494019</v>
       </c>
       <c r="H412" t="n">
         <v>82500</v>
@@ -12346,7 +12346,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G413" t="n">
-        <v>5.2450065612793</v>
+        <v>5.24500703811646</v>
       </c>
       <c r="H413" t="n">
         <v>33000</v>
@@ -12375,7 +12375,7 @@
         <v>5</v>
       </c>
       <c r="G414" t="n">
-        <v>4.92951679229736</v>
+        <v>4.92951774597168</v>
       </c>
       <c r="H414" t="n">
         <v>45500</v>
@@ -12404,7 +12404,7 @@
         <v>5</v>
       </c>
       <c r="G415" t="n">
-        <v>4.92951679229736</v>
+        <v>4.92951774597168</v>
       </c>
       <c r="H415" t="n">
         <v>14500</v>
@@ -12462,7 +12462,7 @@
         <v>5</v>
       </c>
       <c r="G417" t="n">
-        <v>4.92951679229736</v>
+        <v>4.92951774597168</v>
       </c>
       <c r="H417" t="n">
         <v>7500</v>
@@ -12491,7 +12491,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G418" t="n">
-        <v>4.98867130279541</v>
+        <v>4.98867177963257</v>
       </c>
       <c r="H418" t="n">
         <v>23500</v>
@@ -12520,7 +12520,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G419" t="n">
-        <v>5.02810764312744</v>
+        <v>5.02810716629028</v>
       </c>
       <c r="H419" t="n">
         <v>5500</v>
@@ -12549,7 +12549,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G420" t="n">
-        <v>5.00838899612427</v>
+        <v>5.00838994979858</v>
       </c>
       <c r="H420" t="n">
         <v>4500</v>
@@ -12578,7 +12578,7 @@
         <v>5</v>
       </c>
       <c r="G421" t="n">
-        <v>4.92951679229736</v>
+        <v>4.92951774597168</v>
       </c>
       <c r="H421" t="n">
         <v>8500</v>
@@ -12607,7 +12607,7 @@
         <v>5</v>
       </c>
       <c r="G422" t="n">
-        <v>4.92951679229736</v>
+        <v>4.92951774597168</v>
       </c>
       <c r="H422" t="n">
         <v>9500</v>
@@ -12636,7 +12636,7 @@
         <v>5</v>
       </c>
       <c r="G423" t="n">
-        <v>4.92951679229736</v>
+        <v>4.92951774597168</v>
       </c>
       <c r="H423" t="n">
         <v>38500</v>
@@ -12665,7 +12665,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G424" t="n">
-        <v>4.89008140563965</v>
+        <v>4.89008188247681</v>
       </c>
       <c r="H424" t="n">
         <v>11000</v>
@@ -12694,7 +12694,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G425" t="n">
-        <v>5.02810764312744</v>
+        <v>5.02810716629028</v>
       </c>
       <c r="H425" t="n">
         <v>4500</v>
@@ -12752,7 +12752,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G427" t="n">
-        <v>5.02810764312744</v>
+        <v>5.02810716629028</v>
       </c>
       <c r="H427" t="n">
         <v>1500</v>
@@ -12781,7 +12781,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G428" t="n">
-        <v>5.00838899612427</v>
+        <v>5.00838994979858</v>
       </c>
       <c r="H428" t="n">
         <v>2500</v>
@@ -12810,7 +12810,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G429" t="n">
-        <v>5.1266975402832</v>
+        <v>5.12669801712036</v>
       </c>
       <c r="H429" t="n">
         <v>7000</v>
@@ -12839,7 +12839,7 @@
         <v>5</v>
       </c>
       <c r="G430" t="n">
-        <v>4.92951679229736</v>
+        <v>4.92951774597168</v>
       </c>
       <c r="H430" t="n">
         <v>8500</v>
@@ -12868,7 +12868,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G431" t="n">
-        <v>4.98867130279541</v>
+        <v>4.98867177963257</v>
       </c>
       <c r="H431" t="n">
         <v>8000</v>
@@ -12897,7 +12897,7 @@
         <v>5</v>
       </c>
       <c r="G432" t="n">
-        <v>4.92951679229736</v>
+        <v>4.92951774597168</v>
       </c>
       <c r="H432" t="n">
         <v>1000</v>
@@ -12955,7 +12955,7 @@
         <v>5</v>
       </c>
       <c r="G434" t="n">
-        <v>4.92951679229736</v>
+        <v>4.92951774597168</v>
       </c>
       <c r="H434" t="n">
         <v>7000</v>
@@ -12984,7 +12984,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G435" t="n">
-        <v>4.78163146972656</v>
+        <v>4.78163194656372</v>
       </c>
       <c r="H435" t="n">
         <v>22500</v>
@@ -13013,7 +13013,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G436" t="n">
-        <v>4.91965866088867</v>
+        <v>4.91965818405151</v>
       </c>
       <c r="H436" t="n">
         <v>17500</v>
@@ -13071,7 +13071,7 @@
         <v>5</v>
       </c>
       <c r="G438" t="n">
-        <v>4.92951679229736</v>
+        <v>4.92951774597168</v>
       </c>
       <c r="H438" t="n">
         <v>7500</v>
@@ -13100,7 +13100,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G439" t="n">
-        <v>4.89008140563965</v>
+        <v>4.89008188247681</v>
       </c>
       <c r="H439" t="n">
         <v>4500</v>
@@ -13129,7 +13129,7 @@
         <v>5</v>
       </c>
       <c r="G440" t="n">
-        <v>4.92951679229736</v>
+        <v>4.92951774597168</v>
       </c>
       <c r="H440" t="n">
         <v>2000</v>
@@ -13158,7 +13158,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G441" t="n">
-        <v>4.89008140563965</v>
+        <v>4.89008188247681</v>
       </c>
       <c r="H441" t="n">
         <v>2000</v>
@@ -13216,7 +13216,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G443" t="n">
-        <v>5.04782581329346</v>
+        <v>5.0478253364563</v>
       </c>
       <c r="H443" t="n">
         <v>5500</v>
@@ -13245,7 +13245,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G444" t="n">
-        <v>5.02810764312744</v>
+        <v>5.02810716629028</v>
       </c>
       <c r="H444" t="n">
         <v>6500</v>
@@ -13332,7 +13332,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G447" t="n">
-        <v>4.85064506530762</v>
+        <v>4.85064554214478</v>
       </c>
       <c r="H447" t="n">
         <v>3500</v>
@@ -13361,7 +13361,7 @@
         <v>5</v>
       </c>
       <c r="G448" t="n">
-        <v>4.92951679229736</v>
+        <v>4.92951774597168</v>
       </c>
       <c r="H448" t="n">
         <v>19060</v>
@@ -13390,7 +13390,7 @@
         <v>5</v>
       </c>
       <c r="G449" t="n">
-        <v>4.92951679229736</v>
+        <v>4.92951774597168</v>
       </c>
       <c r="H449" t="n">
         <v>10200</v>
@@ -13419,7 +13419,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G450" t="n">
-        <v>4.83092737197876</v>
+        <v>4.8309268951416</v>
       </c>
       <c r="H450" t="n">
         <v>30540</v>
@@ -13448,7 +13448,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G451" t="n">
-        <v>4.83092737197876</v>
+        <v>4.8309268951416</v>
       </c>
       <c r="H451" t="n">
         <v>3150</v>
@@ -13477,7 +13477,7 @@
         <v>5</v>
       </c>
       <c r="G452" t="n">
-        <v>4.92951679229736</v>
+        <v>4.92951774597168</v>
       </c>
       <c r="H452" t="n">
         <v>1500</v>
@@ -13506,7 +13506,7 @@
         <v>5</v>
       </c>
       <c r="G453" t="n">
-        <v>4.92951679229736</v>
+        <v>4.92951774597168</v>
       </c>
       <c r="H453" t="n">
         <v>900</v>
@@ -13535,7 +13535,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G454" t="n">
-        <v>4.84078598022461</v>
+        <v>4.84078550338745</v>
       </c>
       <c r="H454" t="n">
         <v>1250</v>
@@ -13564,7 +13564,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G455" t="n">
-        <v>4.85064506530762</v>
+        <v>4.85064554214478</v>
       </c>
       <c r="H455" t="n">
         <v>1650</v>
@@ -13593,7 +13593,7 @@
         <v>5</v>
       </c>
       <c r="G456" t="n">
-        <v>4.92951679229736</v>
+        <v>4.92951774597168</v>
       </c>
       <c r="H456" t="n">
         <v>2220</v>
@@ -13622,7 +13622,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G457" t="n">
-        <v>5.04782581329346</v>
+        <v>5.0478253364563</v>
       </c>
       <c r="H457" t="n">
         <v>26170</v>
@@ -13651,7 +13651,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G458" t="n">
-        <v>5.50134086608887</v>
+        <v>5.50134181976318</v>
       </c>
       <c r="H458" t="n">
         <v>75450</v>
@@ -13680,7 +13680,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G459" t="n">
-        <v>5.26472520828247</v>
+        <v>5.26472473144531</v>
       </c>
       <c r="H459" t="n">
         <v>23670</v>
@@ -13709,7 +13709,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G460" t="n">
-        <v>5.34359741210938</v>
+        <v>5.34359693527222</v>
       </c>
       <c r="H460" t="n">
         <v>6980</v>
@@ -13738,7 +13738,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G461" t="n">
-        <v>5.30416011810303</v>
+        <v>5.30416059494019</v>
       </c>
       <c r="H461" t="n">
         <v>2900</v>
@@ -13767,7 +13767,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G462" t="n">
-        <v>5.22528886795044</v>
+        <v>5.2252893447876</v>
       </c>
       <c r="H462" t="n">
         <v>3000</v>
@@ -13796,7 +13796,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G463" t="n">
-        <v>5.22528886795044</v>
+        <v>5.2252893447876</v>
       </c>
       <c r="H463" t="n">
         <v>2000</v>
@@ -13825,7 +13825,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G464" t="n">
-        <v>5.04782581329346</v>
+        <v>5.0478253364563</v>
       </c>
       <c r="H464" t="n">
         <v>3580</v>
@@ -13883,7 +13883,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G466" t="n">
-        <v>5.1266975402832</v>
+        <v>5.12669801712036</v>
       </c>
       <c r="H466" t="n">
         <v>7070</v>
@@ -13912,7 +13912,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G467" t="n">
-        <v>5.1266975402832</v>
+        <v>5.12669801712036</v>
       </c>
       <c r="H467" t="n">
         <v>200</v>
@@ -13970,7 +13970,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G469" t="n">
-        <v>5.22528886795044</v>
+        <v>5.2252893447876</v>
       </c>
       <c r="H469" t="n">
         <v>3400</v>
@@ -14028,7 +14028,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G471" t="n">
-        <v>5.22528886795044</v>
+        <v>5.2252893447876</v>
       </c>
       <c r="H471" t="n">
         <v>450</v>
@@ -14057,7 +14057,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G472" t="n">
-        <v>5.22528886795044</v>
+        <v>5.2252893447876</v>
       </c>
       <c r="H472" t="n">
         <v>0</v>
@@ -14086,7 +14086,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G473" t="n">
-        <v>5.20557022094727</v>
+        <v>5.20557069778442</v>
       </c>
       <c r="H473" t="n">
         <v>9950</v>
@@ -14115,7 +14115,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G474" t="n">
-        <v>4.98867130279541</v>
+        <v>4.98867177963257</v>
       </c>
       <c r="H474" t="n">
         <v>17780</v>
@@ -14144,7 +14144,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G475" t="n">
-        <v>5.14641618728638</v>
+        <v>5.14641571044922</v>
       </c>
       <c r="H475" t="n">
         <v>14970</v>
@@ -14173,7 +14173,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G476" t="n">
-        <v>5.02810764312744</v>
+        <v>5.02810716629028</v>
       </c>
       <c r="H476" t="n">
         <v>2700</v>
@@ -14202,7 +14202,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G477" t="n">
-        <v>5.00838899612427</v>
+        <v>5.00838994979858</v>
       </c>
       <c r="H477" t="n">
         <v>1250</v>
@@ -14260,7 +14260,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G479" t="n">
-        <v>5.02810764312744</v>
+        <v>5.02810716629028</v>
       </c>
       <c r="H479" t="n">
         <v>12190</v>
@@ -14289,7 +14289,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G480" t="n">
-        <v>5.14641618728638</v>
+        <v>5.14641571044922</v>
       </c>
       <c r="H480" t="n">
         <v>11670</v>
@@ -14318,7 +14318,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G481" t="n">
-        <v>5.14641618728638</v>
+        <v>5.14641571044922</v>
       </c>
       <c r="H481" t="n">
         <v>7130</v>
@@ -14347,7 +14347,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G482" t="n">
-        <v>5.10697937011719</v>
+        <v>5.10697984695435</v>
       </c>
       <c r="H482" t="n">
         <v>7170</v>
@@ -14376,7 +14376,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G483" t="n">
-        <v>5.1266975402832</v>
+        <v>5.12669801712036</v>
       </c>
       <c r="H483" t="n">
         <v>4620</v>
@@ -14405,7 +14405,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G484" t="n">
-        <v>5.1266975402832</v>
+        <v>5.12669801712036</v>
       </c>
       <c r="H484" t="n">
         <v>6620</v>
@@ -14434,7 +14434,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G485" t="n">
-        <v>5.1266975402832</v>
+        <v>5.12669801712036</v>
       </c>
       <c r="H485" t="n">
         <v>11880</v>
@@ -14463,7 +14463,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G486" t="n">
-        <v>5.04782581329346</v>
+        <v>5.0478253364563</v>
       </c>
       <c r="H486" t="n">
         <v>5290</v>
@@ -14521,7 +14521,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G488" t="n">
-        <v>5.06754398345947</v>
+        <v>5.06754350662231</v>
       </c>
       <c r="H488" t="n">
         <v>3010</v>
@@ -14550,7 +14550,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G489" t="n">
-        <v>4.98867130279541</v>
+        <v>4.98867177963257</v>
       </c>
       <c r="H489" t="n">
         <v>21530</v>
@@ -14579,7 +14579,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G490" t="n">
-        <v>5.1266975402832</v>
+        <v>5.12669801712036</v>
       </c>
       <c r="H490" t="n">
         <v>26550</v>
@@ -14608,7 +14608,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G491" t="n">
-        <v>4.98867130279541</v>
+        <v>4.98867177963257</v>
       </c>
       <c r="H491" t="n">
         <v>28100</v>
@@ -14695,7 +14695,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G494" t="n">
-        <v>5.10697937011719</v>
+        <v>5.10697984695435</v>
       </c>
       <c r="H494" t="n">
         <v>11420</v>
@@ -14811,7 +14811,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G498" t="n">
-        <v>5.02810764312744</v>
+        <v>5.02810716629028</v>
       </c>
       <c r="H498" t="n">
         <v>7720</v>
@@ -14840,7 +14840,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G499" t="n">
-        <v>5.02810764312744</v>
+        <v>5.02810716629028</v>
       </c>
       <c r="H499" t="n">
         <v>4040</v>
@@ -14869,7 +14869,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G500" t="n">
-        <v>5.04782581329346</v>
+        <v>5.0478253364563</v>
       </c>
       <c r="H500" t="n">
         <v>4690</v>
@@ -14898,7 +14898,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G501" t="n">
-        <v>5.06754398345947</v>
+        <v>5.06754350662231</v>
       </c>
       <c r="H501" t="n">
         <v>11540</v>
@@ -14956,7 +14956,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G503" t="n">
-        <v>5.02810764312744</v>
+        <v>5.02810716629028</v>
       </c>
       <c r="H503" t="n">
         <v>14170</v>
@@ -14985,7 +14985,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G504" t="n">
-        <v>4.83092737197876</v>
+        <v>4.8309268951416</v>
       </c>
       <c r="H504" t="n">
         <v>16000</v>
@@ -15014,7 +15014,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G505" t="n">
-        <v>4.98867130279541</v>
+        <v>4.98867177963257</v>
       </c>
       <c r="H505" t="n">
         <v>4800</v>
@@ -15043,7 +15043,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G506" t="n">
-        <v>5.1266975402832</v>
+        <v>5.12669801712036</v>
       </c>
       <c r="H506" t="n">
         <v>5270</v>
@@ -15072,7 +15072,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G507" t="n">
-        <v>5.10697937011719</v>
+        <v>5.10697984695435</v>
       </c>
       <c r="H507" t="n">
         <v>3690</v>
@@ -15101,7 +15101,7 @@
         <v>5</v>
       </c>
       <c r="G508" t="n">
-        <v>4.92951679229736</v>
+        <v>4.92951774597168</v>
       </c>
       <c r="H508" t="n">
         <v>5700</v>
@@ -15130,7 +15130,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G509" t="n">
-        <v>5.06754398345947</v>
+        <v>5.06754350662231</v>
       </c>
       <c r="H509" t="n">
         <v>940</v>
@@ -15159,7 +15159,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G510" t="n">
-        <v>4.98867130279541</v>
+        <v>4.98867177963257</v>
       </c>
       <c r="H510" t="n">
         <v>1110</v>
@@ -15188,7 +15188,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G511" t="n">
-        <v>5.02810764312744</v>
+        <v>5.02810716629028</v>
       </c>
       <c r="H511" t="n">
         <v>2710</v>
@@ -15246,7 +15246,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G513" t="n">
-        <v>5.00838899612427</v>
+        <v>5.00838994979858</v>
       </c>
       <c r="H513" t="n">
         <v>10130</v>
@@ -15333,7 +15333,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G516" t="n">
-        <v>5.00838899612427</v>
+        <v>5.00838994979858</v>
       </c>
       <c r="H516" t="n">
         <v>640</v>
@@ -15362,7 +15362,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G517" t="n">
-        <v>5.02810764312744</v>
+        <v>5.02810716629028</v>
       </c>
       <c r="H517" t="n">
         <v>80</v>
@@ -15391,7 +15391,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G518" t="n">
-        <v>5.00838899612427</v>
+        <v>5.00838994979858</v>
       </c>
       <c r="H518" t="n">
         <v>3020</v>
@@ -15420,7 +15420,7 @@
         <v>5</v>
       </c>
       <c r="G519" t="n">
-        <v>4.92951679229736</v>
+        <v>4.92951774597168</v>
       </c>
       <c r="H519" t="n">
         <v>12340</v>
@@ -15449,7 +15449,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G520" t="n">
-        <v>5.02810764312744</v>
+        <v>5.02810716629028</v>
       </c>
       <c r="H520" t="n">
         <v>18090</v>
@@ -15478,7 +15478,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G521" t="n">
-        <v>5.20557022094727</v>
+        <v>5.20557069778442</v>
       </c>
       <c r="H521" t="n">
         <v>4650</v>
@@ -15507,7 +15507,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G522" t="n">
-        <v>5.04782581329346</v>
+        <v>5.0478253364563</v>
       </c>
       <c r="H522" t="n">
         <v>27900</v>
@@ -15536,7 +15536,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G523" t="n">
-        <v>5.02810764312744</v>
+        <v>5.02810716629028</v>
       </c>
       <c r="H523" t="n">
         <v>1940</v>
@@ -15623,7 +15623,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G526" t="n">
-        <v>5.00838899612427</v>
+        <v>5.00838994979858</v>
       </c>
       <c r="H526" t="n">
         <v>2400</v>
@@ -15652,7 +15652,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G527" t="n">
-        <v>4.85064506530762</v>
+        <v>4.85064554214478</v>
       </c>
       <c r="H527" t="n">
         <v>12990</v>
@@ -15710,7 +15710,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G529" t="n">
-        <v>4.77177286148071</v>
+        <v>4.77177333831787</v>
       </c>
       <c r="H529" t="n">
         <v>14510</v>
@@ -15797,7 +15797,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G532" t="n">
-        <v>4.77177286148071</v>
+        <v>4.77177333831787</v>
       </c>
       <c r="H532" t="n">
         <v>4310</v>
@@ -15913,7 +15913,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G536" t="n">
-        <v>4.71261835098267</v>
+        <v>4.71261882781982</v>
       </c>
       <c r="H536" t="n">
         <v>153850</v>
@@ -16000,7 +16000,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G539" t="n">
-        <v>4.85064506530762</v>
+        <v>4.85064554214478</v>
       </c>
       <c r="H539" t="n">
         <v>610</v>
@@ -16029,7 +16029,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G540" t="n">
-        <v>4.83092737197876</v>
+        <v>4.8309268951416</v>
       </c>
       <c r="H540" t="n">
         <v>1600</v>
@@ -16116,7 +16116,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G543" t="n">
-        <v>4.84078598022461</v>
+        <v>4.84078550338745</v>
       </c>
       <c r="H543" t="n">
         <v>3320</v>
@@ -16145,7 +16145,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G544" t="n">
-        <v>4.84078598022461</v>
+        <v>4.84078550338745</v>
       </c>
       <c r="H544" t="n">
         <v>0</v>
@@ -16174,7 +16174,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G545" t="n">
-        <v>4.83092737197876</v>
+        <v>4.8309268951416</v>
       </c>
       <c r="H545" t="n">
         <v>1200</v>
@@ -16203,7 +16203,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G546" t="n">
-        <v>4.75205516815186</v>
+        <v>4.7520546913147</v>
       </c>
       <c r="H546" t="n">
         <v>6100</v>
@@ -16232,7 +16232,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G547" t="n">
-        <v>4.62362051010132</v>
+        <v>4.62362098693848</v>
       </c>
       <c r="H547" t="n">
         <v>10330</v>
@@ -16261,7 +16261,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G548" t="n">
-        <v>4.57422399520874</v>
+        <v>4.57422351837158</v>
       </c>
       <c r="H548" t="n">
         <v>17160</v>
@@ -16377,7 +16377,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G552" t="n">
-        <v>4.78169345855713</v>
+        <v>4.78169393539429</v>
       </c>
       <c r="H552" t="n">
         <v>1640</v>
@@ -16406,7 +16406,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G553" t="n">
-        <v>4.78169345855713</v>
+        <v>4.78169393539429</v>
       </c>
       <c r="H553" t="n">
         <v>0</v>
@@ -16435,7 +16435,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G554" t="n">
-        <v>4.78169345855713</v>
+        <v>4.78169393539429</v>
       </c>
       <c r="H554" t="n">
         <v>0</v>
@@ -16667,7 +16667,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G562" t="n">
-        <v>4.92988681793213</v>
+        <v>4.92988634109497</v>
       </c>
       <c r="H562" t="n">
         <v>2500</v>
@@ -16957,7 +16957,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G572" t="n">
-        <v>4.55446481704712</v>
+        <v>4.55446434020996</v>
       </c>
       <c r="H572" t="n">
         <v>2940</v>
@@ -17044,7 +17044,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G575" t="n">
-        <v>4.32723474502563</v>
+        <v>4.32723522186279</v>
       </c>
       <c r="H575" t="n">
         <v>1010</v>
@@ -17073,7 +17073,7 @@
         <v>4.5</v>
       </c>
       <c r="G576" t="n">
-        <v>4.44578981399536</v>
+        <v>4.4457893371582</v>
       </c>
       <c r="H576" t="n">
         <v>2400</v>
@@ -17102,7 +17102,7 @@
         <v>4.5</v>
       </c>
       <c r="G577" t="n">
-        <v>4.44578981399536</v>
+        <v>4.4457893371582</v>
       </c>
       <c r="H577" t="n">
         <v>1890</v>
@@ -17131,7 +17131,7 @@
         <v>4.5</v>
       </c>
       <c r="G578" t="n">
-        <v>4.44578981399536</v>
+        <v>4.4457893371582</v>
       </c>
       <c r="H578" t="n">
         <v>550</v>
@@ -17218,7 +17218,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G581" t="n">
-        <v>4.40627145767212</v>
+        <v>4.40627193450928</v>
       </c>
       <c r="H581" t="n">
         <v>1200</v>
@@ -17305,7 +17305,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G584" t="n">
-        <v>4.78169345855713</v>
+        <v>4.78169393539429</v>
       </c>
       <c r="H584" t="n">
         <v>3210</v>
@@ -17421,7 +17421,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G588" t="n">
-        <v>4.49518728256226</v>
+        <v>4.4951868057251</v>
       </c>
       <c r="H588" t="n">
         <v>1140</v>
@@ -17479,7 +17479,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G590" t="n">
-        <v>4.38651275634766</v>
+        <v>4.3865122795105</v>
       </c>
       <c r="H590" t="n">
         <v>37290</v>
@@ -17624,7 +17624,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G595" t="n">
-        <v>4.35687351226807</v>
+        <v>4.35687398910522</v>
       </c>
       <c r="H595" t="n">
         <v>30</v>
@@ -17653,7 +17653,7 @@
         <v>4.5</v>
       </c>
       <c r="G596" t="n">
-        <v>4.44578981399536</v>
+        <v>4.4457893371582</v>
       </c>
       <c r="H596" t="n">
         <v>3880</v>
@@ -17682,7 +17682,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G597" t="n">
-        <v>4.40627145767212</v>
+        <v>4.40627193450928</v>
       </c>
       <c r="H597" t="n">
         <v>1930</v>
@@ -17711,7 +17711,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G598" t="n">
-        <v>4.49518728256226</v>
+        <v>4.4951868057251</v>
       </c>
       <c r="H598" t="n">
         <v>1400</v>
@@ -17914,7 +17914,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G605" t="n">
-        <v>4.83109140396118</v>
+        <v>4.83109092712402</v>
       </c>
       <c r="H605" t="n">
         <v>9220</v>
@@ -18146,7 +18146,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G613" t="n">
-        <v>4.78169345855713</v>
+        <v>4.78169393539429</v>
       </c>
       <c r="H613" t="n">
         <v>1500</v>
@@ -18349,7 +18349,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G620" t="n">
-        <v>4.99904298782349</v>
+        <v>4.99904346466064</v>
       </c>
       <c r="H620" t="n">
         <v>3460</v>
@@ -18378,7 +18378,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G621" t="n">
-        <v>5.01880168914795</v>
+        <v>5.01880264282227</v>
       </c>
       <c r="H621" t="n">
         <v>5130</v>
@@ -18407,7 +18407,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G622" t="n">
-        <v>5.01880168914795</v>
+        <v>5.01880264282227</v>
       </c>
       <c r="H622" t="n">
         <v>2300</v>
@@ -18436,7 +18436,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G623" t="n">
-        <v>5.01880168914795</v>
+        <v>5.01880264282227</v>
       </c>
       <c r="H623" t="n">
         <v>0</v>
@@ -18465,7 +18465,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G624" t="n">
-        <v>5.03856134414673</v>
+        <v>5.03856086730957</v>
       </c>
       <c r="H624" t="n">
         <v>200</v>
@@ -18494,7 +18494,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G625" t="n">
-        <v>5.03856134414673</v>
+        <v>5.03856086730957</v>
       </c>
       <c r="H625" t="n">
         <v>2500</v>
@@ -18523,7 +18523,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G626" t="n">
-        <v>4.92988681793213</v>
+        <v>4.92988634109497</v>
       </c>
       <c r="H626" t="n">
         <v>49150</v>
@@ -18581,7 +18581,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G628" t="n">
-        <v>4.87060928344727</v>
+        <v>4.87060880661011</v>
       </c>
       <c r="H628" t="n">
         <v>1000</v>
@@ -18697,7 +18697,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G632" t="n">
-        <v>4.75205516815186</v>
+        <v>4.75205421447754</v>
       </c>
       <c r="H632" t="n">
         <v>3780</v>
@@ -18755,7 +18755,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G634" t="n">
-        <v>4.92988681793213</v>
+        <v>4.92988634109497</v>
       </c>
       <c r="H634" t="n">
         <v>4840</v>
@@ -18900,7 +18900,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G639" t="n">
-        <v>4.87060928344727</v>
+        <v>4.87060880661011</v>
       </c>
       <c r="H639" t="n">
         <v>6120</v>
@@ -19074,7 +19074,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G645" t="n">
-        <v>4.49518728256226</v>
+        <v>4.4951868057251</v>
       </c>
       <c r="H645" t="n">
         <v>3250</v>
@@ -19103,7 +19103,7 @@
         <v>4.5</v>
       </c>
       <c r="G646" t="n">
-        <v>4.44578981399536</v>
+        <v>4.4457893371582</v>
       </c>
       <c r="H646" t="n">
         <v>8070</v>
@@ -19190,7 +19190,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G649" t="n">
-        <v>4.39639186859131</v>
+        <v>4.39639139175415</v>
       </c>
       <c r="H649" t="n">
         <v>7440</v>
@@ -19219,7 +19219,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G650" t="n">
-        <v>4.52482557296753</v>
+        <v>4.52482604980469</v>
       </c>
       <c r="H650" t="n">
         <v>11950</v>
@@ -19741,7 +19741,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G668" t="n">
-        <v>5.03856134414673</v>
+        <v>5.03856086730957</v>
       </c>
       <c r="H668" t="n">
         <v>8110</v>
@@ -19770,7 +19770,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G669" t="n">
-        <v>5.1175971031189</v>
+        <v>5.11759757995605</v>
       </c>
       <c r="H669" t="n">
         <v>13730</v>
@@ -19799,7 +19799,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G670" t="n">
-        <v>5.1175971031189</v>
+        <v>5.11759757995605</v>
       </c>
       <c r="H670" t="n">
         <v>340</v>
@@ -19828,7 +19828,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G671" t="n">
-        <v>5.03856134414673</v>
+        <v>5.03856086730957</v>
       </c>
       <c r="H671" t="n">
         <v>4620</v>
@@ -19857,7 +19857,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G672" t="n">
-        <v>5.1175971031189</v>
+        <v>5.11759757995605</v>
       </c>
       <c r="H672" t="n">
         <v>3970</v>
@@ -19915,7 +19915,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G674" t="n">
-        <v>5.03856134414673</v>
+        <v>5.03856086730957</v>
       </c>
       <c r="H674" t="n">
         <v>1320</v>
@@ -20118,7 +20118,7 @@
         <v>4.71000003814697</v>
       </c>
       <c r="G681" t="n">
-        <v>4.65325975418091</v>
+        <v>4.65325927734375</v>
       </c>
       <c r="H681" t="n">
         <v>37500</v>
@@ -20205,7 +20205,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G684" t="n">
-        <v>4.52482557296753</v>
+        <v>4.52482604980469</v>
       </c>
       <c r="H684" t="n">
         <v>1210</v>
@@ -20263,7 +20263,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G686" t="n">
-        <v>4.39639186859131</v>
+        <v>4.39639139175415</v>
       </c>
       <c r="H686" t="n">
         <v>17560</v>
@@ -20292,7 +20292,7 @@
         <v>4.5</v>
       </c>
       <c r="G687" t="n">
-        <v>4.44578981399536</v>
+        <v>4.4457893371582</v>
       </c>
       <c r="H687" t="n">
         <v>5450</v>
@@ -20321,7 +20321,7 @@
         <v>4.5</v>
       </c>
       <c r="G688" t="n">
-        <v>4.44578981399536</v>
+        <v>4.4457893371582</v>
       </c>
       <c r="H688" t="n">
         <v>6510</v>
@@ -20408,7 +20408,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G691" t="n">
-        <v>5.01880168914795</v>
+        <v>5.01880264282227</v>
       </c>
       <c r="H691" t="n">
         <v>40840</v>
@@ -20437,7 +20437,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G692" t="n">
-        <v>5.03856134414673</v>
+        <v>5.03856086730957</v>
       </c>
       <c r="H692" t="n">
         <v>52130</v>
@@ -20495,7 +20495,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G694" t="n">
-        <v>5.03856134414673</v>
+        <v>5.03856086730957</v>
       </c>
       <c r="H694" t="n">
         <v>39050</v>
@@ -20524,7 +20524,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G695" t="n">
-        <v>4.99904298782349</v>
+        <v>4.99904346466064</v>
       </c>
       <c r="H695" t="n">
         <v>25780</v>
@@ -20553,7 +20553,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G696" t="n">
-        <v>5.21639251708984</v>
+        <v>5.216392993927</v>
       </c>
       <c r="H696" t="n">
         <v>1320</v>
@@ -20582,7 +20582,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G697" t="n">
-        <v>5.03856134414673</v>
+        <v>5.03856086730957</v>
       </c>
       <c r="H697" t="n">
         <v>10770</v>
@@ -20611,7 +20611,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G698" t="n">
-        <v>5.1175971031189</v>
+        <v>5.11759757995605</v>
       </c>
       <c r="H698" t="n">
         <v>3510</v>
@@ -20640,7 +20640,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G699" t="n">
-        <v>5.1175971031189</v>
+        <v>5.11759757995605</v>
       </c>
       <c r="H699" t="n">
         <v>0</v>
@@ -20669,7 +20669,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G700" t="n">
-        <v>5.03856134414673</v>
+        <v>5.03856086730957</v>
       </c>
       <c r="H700" t="n">
         <v>300</v>
@@ -20698,7 +20698,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G701" t="n">
-        <v>5.03856134414673</v>
+        <v>5.03856086730957</v>
       </c>
       <c r="H701" t="n">
         <v>1190</v>
@@ -20727,7 +20727,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G702" t="n">
-        <v>5.03856134414673</v>
+        <v>5.03856086730957</v>
       </c>
       <c r="H702" t="n">
         <v>110</v>
@@ -20756,7 +20756,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G703" t="n">
-        <v>4.87060928344727</v>
+        <v>4.87060880661011</v>
       </c>
       <c r="H703" t="n">
         <v>5400</v>
@@ -20901,7 +20901,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G708" t="n">
-        <v>5.1175971031189</v>
+        <v>5.11759757995605</v>
       </c>
       <c r="H708" t="n">
         <v>8710</v>
@@ -20930,7 +20930,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G709" t="n">
-        <v>4.92988681793213</v>
+        <v>4.92988634109497</v>
       </c>
       <c r="H709" t="n">
         <v>2230</v>
@@ -20959,7 +20959,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G710" t="n">
-        <v>4.92988681793213</v>
+        <v>4.92988634109497</v>
       </c>
       <c r="H710" t="n">
         <v>2210</v>
@@ -21162,7 +21162,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G717" t="n">
-        <v>4.78169345855713</v>
+        <v>4.78169393539429</v>
       </c>
       <c r="H717" t="n">
         <v>2530</v>
@@ -21249,7 +21249,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G720" t="n">
-        <v>5.01880168914795</v>
+        <v>5.01880264282227</v>
       </c>
       <c r="H720" t="n">
         <v>5570</v>
@@ -21336,7 +21336,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G723" t="n">
-        <v>5.1175971031189</v>
+        <v>5.11759757995605</v>
       </c>
       <c r="H723" t="n">
         <v>6040</v>
@@ -21365,7 +21365,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G724" t="n">
-        <v>5.1175971031189</v>
+        <v>5.11759757995605</v>
       </c>
       <c r="H724" t="n">
         <v>3650</v>
@@ -21394,7 +21394,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G725" t="n">
-        <v>5.13735628128052</v>
+        <v>5.13735675811768</v>
       </c>
       <c r="H725" t="n">
         <v>3650</v>
@@ -21423,7 +21423,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G726" t="n">
-        <v>5.03856134414673</v>
+        <v>5.03856086730957</v>
       </c>
       <c r="H726" t="n">
         <v>3700</v>
@@ -21655,7 +21655,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G734" t="n">
-        <v>4.78169345855713</v>
+        <v>4.78169393539429</v>
       </c>
       <c r="H734" t="n">
         <v>2150</v>
@@ -22061,7 +22061,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G748" t="n">
-        <v>4.75205516815186</v>
+        <v>4.75205421447754</v>
       </c>
       <c r="H748" t="n">
         <v>39170</v>
@@ -22090,7 +22090,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G749" t="n">
-        <v>4.78169345855713</v>
+        <v>4.78169393539429</v>
       </c>
       <c r="H749" t="n">
         <v>10810</v>
@@ -22148,7 +22148,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G751" t="n">
-        <v>4.17904233932495</v>
+        <v>4.17904186248779</v>
       </c>
       <c r="H751" t="n">
         <v>518850</v>
@@ -22177,7 +22177,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G752" t="n">
-        <v>4.228440284729</v>
+        <v>4.22843980789185</v>
       </c>
       <c r="H752" t="n">
         <v>104770</v>
@@ -22206,7 +22206,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G753" t="n">
-        <v>4.17904233932495</v>
+        <v>4.17904186248779</v>
       </c>
       <c r="H753" t="n">
         <v>125670</v>
@@ -22235,7 +22235,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G754" t="n">
-        <v>4.17904233932495</v>
+        <v>4.17904186248779</v>
       </c>
       <c r="H754" t="n">
         <v>21070</v>
@@ -22322,7 +22322,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G757" t="n">
-        <v>4.17904233932495</v>
+        <v>4.17904186248779</v>
       </c>
       <c r="H757" t="n">
         <v>17930</v>
@@ -22380,7 +22380,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G759" t="n">
-        <v>4.15928316116333</v>
+        <v>4.15928268432617</v>
       </c>
       <c r="H759" t="n">
         <v>8420</v>
@@ -22409,7 +22409,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G760" t="n">
-        <v>4.16916227340698</v>
+        <v>4.16916275024414</v>
       </c>
       <c r="H760" t="n">
         <v>13670</v>
@@ -22438,7 +22438,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G761" t="n">
-        <v>4.16916227340698</v>
+        <v>4.16916275024414</v>
       </c>
       <c r="H761" t="n">
         <v>5710</v>
@@ -22467,7 +22467,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G762" t="n">
-        <v>4.15928316116333</v>
+        <v>4.15928268432617</v>
       </c>
       <c r="H762" t="n">
         <v>1760</v>
@@ -22496,7 +22496,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G763" t="n">
-        <v>4.05060863494873</v>
+        <v>4.05060815811157</v>
       </c>
       <c r="H763" t="n">
         <v>55200</v>
@@ -22525,7 +22525,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G764" t="n">
-        <v>4.0209698677063</v>
+        <v>4.02096939086914</v>
       </c>
       <c r="H764" t="n">
         <v>16670</v>
@@ -22670,7 +22670,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G769" t="n">
-        <v>3.83325862884521</v>
+        <v>3.83325839042664</v>
       </c>
       <c r="H769" t="n">
         <v>12950</v>
@@ -22786,7 +22786,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G773" t="n">
-        <v>3.80361986160278</v>
+        <v>3.8036196231842</v>
       </c>
       <c r="H773" t="n">
         <v>4390</v>
@@ -22815,7 +22815,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G774" t="n">
-        <v>3.75422215461731</v>
+        <v>3.75422191619873</v>
       </c>
       <c r="H774" t="n">
         <v>58020</v>
@@ -22902,7 +22902,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G777" t="n">
-        <v>3.75422215461731</v>
+        <v>3.75422191619873</v>
       </c>
       <c r="H777" t="n">
         <v>185950</v>
@@ -22931,7 +22931,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G778" t="n">
-        <v>3.88265609741211</v>
+        <v>3.88265633583069</v>
       </c>
       <c r="H778" t="n">
         <v>6390</v>
@@ -23047,7 +23047,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G782" t="n">
-        <v>4.04072904586792</v>
+        <v>4.04072856903076</v>
       </c>
       <c r="H782" t="n">
         <v>14490</v>
@@ -23076,7 +23076,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G783" t="n">
-        <v>3.98145151138306</v>
+        <v>3.98145174980164</v>
       </c>
       <c r="H783" t="n">
         <v>8720</v>
@@ -23163,7 +23163,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G786" t="n">
-        <v>3.96169233322144</v>
+        <v>3.96169257164001</v>
       </c>
       <c r="H786" t="n">
         <v>3050</v>
@@ -23192,7 +23192,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G787" t="n">
-        <v>4.03084897994995</v>
+        <v>4.03084945678711</v>
       </c>
       <c r="H787" t="n">
         <v>5350</v>
@@ -23279,7 +23279,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G790" t="n">
-        <v>3.88265609741211</v>
+        <v>3.88265633583069</v>
       </c>
       <c r="H790" t="n">
         <v>7320</v>
@@ -23511,7 +23511,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G798" t="n">
-        <v>3.83325862884521</v>
+        <v>3.83325839042664</v>
       </c>
       <c r="H798" t="n">
         <v>3250</v>
@@ -23540,7 +23540,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G799" t="n">
-        <v>3.91229462623596</v>
+        <v>3.91229438781738</v>
       </c>
       <c r="H799" t="n">
         <v>3000</v>
@@ -23627,7 +23627,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G802" t="n">
-        <v>3.92235159873962</v>
+        <v>3.92235207557678</v>
       </c>
       <c r="H802" t="n">
         <v>6080</v>
@@ -23656,7 +23656,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G803" t="n">
-        <v>3.92235159873962</v>
+        <v>3.92235207557678</v>
       </c>
       <c r="H803" t="n">
         <v>2580</v>
@@ -23714,7 +23714,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G805" t="n">
-        <v>3.80349278450012</v>
+        <v>3.80349254608154</v>
       </c>
       <c r="H805" t="n">
         <v>3750</v>
@@ -23830,7 +23830,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G809" t="n">
-        <v>3.95206665992737</v>
+        <v>3.95206642150879</v>
       </c>
       <c r="H809" t="n">
         <v>8670</v>
@@ -23859,7 +23859,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G810" t="n">
-        <v>3.95206665992737</v>
+        <v>3.95206642150879</v>
       </c>
       <c r="H810" t="n">
         <v>0</v>
@@ -23888,7 +23888,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G811" t="n">
-        <v>3.95206665992737</v>
+        <v>3.95206642150879</v>
       </c>
       <c r="H811" t="n">
         <v>2110</v>
@@ -23917,7 +23917,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G812" t="n">
-        <v>3.94216179847717</v>
+        <v>3.94216156005859</v>
       </c>
       <c r="H812" t="n">
         <v>4340</v>
@@ -23946,7 +23946,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G813" t="n">
-        <v>3.99168682098389</v>
+        <v>3.99168658256531</v>
       </c>
       <c r="H813" t="n">
         <v>8200</v>
@@ -23975,7 +23975,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G814" t="n">
-        <v>3.94216179847717</v>
+        <v>3.94216156005859</v>
       </c>
       <c r="H814" t="n">
         <v>6790</v>
@@ -24004,7 +24004,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G815" t="n">
-        <v>3.92235159873962</v>
+        <v>3.92235207557678</v>
       </c>
       <c r="H815" t="n">
         <v>8350</v>
@@ -24062,7 +24062,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G817" t="n">
-        <v>3.95206665992737</v>
+        <v>3.95206642150879</v>
       </c>
       <c r="H817" t="n">
         <v>50</v>
@@ -24091,7 +24091,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G818" t="n">
-        <v>3.94216179847717</v>
+        <v>3.94216156005859</v>
       </c>
       <c r="H818" t="n">
         <v>6250</v>
@@ -24178,7 +24178,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G821" t="n">
-        <v>4.14025974273682</v>
+        <v>4.14026021957397</v>
       </c>
       <c r="H821" t="n">
         <v>24790</v>
@@ -24207,7 +24207,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G822" t="n">
-        <v>4.090735912323</v>
+        <v>4.09073543548584</v>
       </c>
       <c r="H822" t="n">
         <v>17180</v>
@@ -24294,7 +24294,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G825" t="n">
-        <v>3.87282705307007</v>
+        <v>3.87282729148865</v>
       </c>
       <c r="H825" t="n">
         <v>85340</v>
@@ -24352,7 +24352,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G827" t="n">
-        <v>4.03130578994751</v>
+        <v>4.03130626678467</v>
       </c>
       <c r="H827" t="n">
         <v>14010</v>
@@ -24410,7 +24410,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G829" t="n">
-        <v>4.05111598968506</v>
+        <v>4.05111646652222</v>
       </c>
       <c r="H829" t="n">
         <v>27250</v>
@@ -24497,7 +24497,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G832" t="n">
-        <v>4.05111598968506</v>
+        <v>4.05111646652222</v>
       </c>
       <c r="H832" t="n">
         <v>300</v>
@@ -24526,7 +24526,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G833" t="n">
-        <v>4.05111598968506</v>
+        <v>4.05111646652222</v>
       </c>
       <c r="H833" t="n">
         <v>12070</v>
@@ -24584,7 +24584,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G835" t="n">
-        <v>4.02140092849731</v>
+        <v>4.02140140533447</v>
       </c>
       <c r="H835" t="n">
         <v>3690</v>
@@ -24613,7 +24613,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G836" t="n">
-        <v>4.02140092849731</v>
+        <v>4.02140140533447</v>
       </c>
       <c r="H836" t="n">
         <v>0</v>
@@ -24671,7 +24671,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G838" t="n">
-        <v>4.05111598968506</v>
+        <v>4.05111646652222</v>
       </c>
       <c r="H838" t="n">
         <v>8480</v>
@@ -24700,7 +24700,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G839" t="n">
-        <v>4.04121065139771</v>
+        <v>4.04121112823486</v>
       </c>
       <c r="H839" t="n">
         <v>14500</v>
@@ -24729,7 +24729,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G840" t="n">
-        <v>4.04121065139771</v>
+        <v>4.04121112823486</v>
       </c>
       <c r="H840" t="n">
         <v>0</v>
@@ -24787,7 +24787,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G842" t="n">
-        <v>4.07092618942261</v>
+        <v>4.07092571258545</v>
       </c>
       <c r="H842" t="n">
         <v>13210</v>
@@ -24816,7 +24816,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G843" t="n">
-        <v>4.02140092849731</v>
+        <v>4.02140140533447</v>
       </c>
       <c r="H843" t="n">
         <v>7610</v>
@@ -24874,7 +24874,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G845" t="n">
-        <v>3.95206665992737</v>
+        <v>3.95206642150879</v>
       </c>
       <c r="H845" t="n">
         <v>11870</v>
@@ -24961,7 +24961,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G848" t="n">
-        <v>4.08083057403564</v>
+        <v>4.0808310508728</v>
       </c>
       <c r="H848" t="n">
         <v>10590</v>
@@ -25019,7 +25019,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G850" t="n">
-        <v>4.14025974273682</v>
+        <v>4.14026021957397</v>
       </c>
       <c r="H850" t="n">
         <v>11320</v>
@@ -25048,7 +25048,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G851" t="n">
-        <v>4.16997528076172</v>
+        <v>4.16997480392456</v>
       </c>
       <c r="H851" t="n">
         <v>9220</v>
@@ -25077,7 +25077,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G852" t="n">
-        <v>4.19968938827515</v>
+        <v>4.1996898651123</v>
       </c>
       <c r="H852" t="n">
         <v>8340</v>
@@ -25135,7 +25135,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G854" t="n">
-        <v>4.16006994247437</v>
+        <v>4.16007041931152</v>
       </c>
       <c r="H854" t="n">
         <v>31610</v>
@@ -25164,7 +25164,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G855" t="n">
-        <v>4.16006994247437</v>
+        <v>4.16007041931152</v>
       </c>
       <c r="H855" t="n">
         <v>8120</v>
@@ -25193,7 +25193,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G856" t="n">
-        <v>4.090735912323</v>
+        <v>4.09073543548584</v>
       </c>
       <c r="H856" t="n">
         <v>19870</v>
@@ -25222,7 +25222,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G857" t="n">
-        <v>4.07092618942261</v>
+        <v>4.07092571258545</v>
       </c>
       <c r="H857" t="n">
         <v>22390</v>
@@ -25251,7 +25251,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G858" t="n">
-        <v>4.11054563522339</v>
+        <v>4.11054515838623</v>
       </c>
       <c r="H858" t="n">
         <v>10230</v>
@@ -25309,7 +25309,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G860" t="n">
-        <v>4.07092618942261</v>
+        <v>4.07092571258545</v>
       </c>
       <c r="H860" t="n">
         <v>20440</v>
@@ -25367,7 +25367,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G862" t="n">
-        <v>4.08083057403564</v>
+        <v>4.0808310508728</v>
       </c>
       <c r="H862" t="n">
         <v>12200</v>
@@ -25396,7 +25396,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G863" t="n">
-        <v>4.11054563522339</v>
+        <v>4.11054515838623</v>
       </c>
       <c r="H863" t="n">
         <v>7840</v>
@@ -25425,7 +25425,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G864" t="n">
-        <v>4.08083057403564</v>
+        <v>4.0808310508728</v>
       </c>
       <c r="H864" t="n">
         <v>1130</v>
@@ -25454,7 +25454,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G865" t="n">
-        <v>4.08083057403564</v>
+        <v>4.0808310508728</v>
       </c>
       <c r="H865" t="n">
         <v>21410</v>
@@ -25512,7 +25512,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G867" t="n">
-        <v>4.05111598968506</v>
+        <v>4.05111646652222</v>
       </c>
       <c r="H867" t="n">
         <v>24460</v>
@@ -25599,7 +25599,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G870" t="n">
-        <v>4.02140092849731</v>
+        <v>4.02140140533447</v>
       </c>
       <c r="H870" t="n">
         <v>100090</v>
@@ -25657,7 +25657,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G872" t="n">
-        <v>4.02140092849731</v>
+        <v>4.02140140533447</v>
       </c>
       <c r="H872" t="n">
         <v>5620</v>
@@ -25773,7 +25773,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G876" t="n">
-        <v>4.08083057403564</v>
+        <v>4.0808310508728</v>
       </c>
       <c r="H876" t="n">
         <v>6660</v>
@@ -25802,7 +25802,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G877" t="n">
-        <v>4.16997528076172</v>
+        <v>4.16997480392456</v>
       </c>
       <c r="H877" t="n">
         <v>14160</v>
@@ -25860,7 +25860,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G879" t="n">
-        <v>4.29873943328857</v>
+        <v>4.29873991012573</v>
       </c>
       <c r="H879" t="n">
         <v>31140</v>
@@ -26266,7 +26266,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G893" t="n">
-        <v>4.23930978775024</v>
+        <v>4.2393102645874</v>
       </c>
       <c r="H893" t="n">
         <v>42450</v>
@@ -26469,7 +26469,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G900" t="n">
-        <v>4.25911951065063</v>
+        <v>4.25911998748779</v>
       </c>
       <c r="H900" t="n">
         <v>2300</v>
@@ -26498,7 +26498,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G901" t="n">
-        <v>4.25911951065063</v>
+        <v>4.25911998748779</v>
       </c>
       <c r="H901" t="n">
         <v>7230</v>
@@ -26527,7 +26527,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G902" t="n">
-        <v>4.19968938827515</v>
+        <v>4.1996898651123</v>
       </c>
       <c r="H902" t="n">
         <v>2510</v>
@@ -26585,7 +26585,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G904" t="n">
-        <v>4.07092618942261</v>
+        <v>4.07092571258545</v>
       </c>
       <c r="H904" t="n">
         <v>7020</v>
@@ -26730,7 +26730,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G909" t="n">
-        <v>4.11054563522339</v>
+        <v>4.11054515838623</v>
       </c>
       <c r="H909" t="n">
         <v>271200</v>
@@ -26788,7 +26788,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G911" t="n">
-        <v>4.04121065139771</v>
+        <v>4.04121112823486</v>
       </c>
       <c r="H911" t="n">
         <v>1150</v>
@@ -26817,7 +26817,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G912" t="n">
-        <v>4.04121065139771</v>
+        <v>4.04121112823486</v>
       </c>
       <c r="H912" t="n">
         <v>0</v>
@@ -26875,7 +26875,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G914" t="n">
-        <v>3.94216179847717</v>
+        <v>3.94216156005859</v>
       </c>
       <c r="H914" t="n">
         <v>14640</v>
@@ -26904,7 +26904,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G915" t="n">
-        <v>3.78368258476257</v>
+        <v>3.78368282318115</v>
       </c>
       <c r="H915" t="n">
         <v>17270</v>
@@ -27078,7 +27078,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G921" t="n">
-        <v>3.70444345474243</v>
+        <v>3.70444321632385</v>
       </c>
       <c r="H921" t="n">
         <v>2880</v>
@@ -27107,7 +27107,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G922" t="n">
-        <v>3.69453859329224</v>
+        <v>3.69453835487366</v>
       </c>
       <c r="H922" t="n">
         <v>8160</v>
@@ -27194,7 +27194,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G925" t="n">
-        <v>3.6450138092041</v>
+        <v>3.64501404762268</v>
       </c>
       <c r="H925" t="n">
         <v>3530</v>
@@ -27252,7 +27252,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G927" t="n">
-        <v>3.5657742023468</v>
+        <v>3.56577444076538</v>
       </c>
       <c r="H927" t="n">
         <v>13970</v>
@@ -27281,7 +27281,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G928" t="n">
-        <v>3.5657742023468</v>
+        <v>3.56577444076538</v>
       </c>
       <c r="H928" t="n">
         <v>7010</v>
@@ -27368,7 +27368,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G931" t="n">
-        <v>3.5657742023468</v>
+        <v>3.56577444076538</v>
       </c>
       <c r="H931" t="n">
         <v>7780</v>
@@ -27426,7 +27426,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G933" t="n">
-        <v>3.5657742023468</v>
+        <v>3.56577444076538</v>
       </c>
       <c r="H933" t="n">
         <v>5210</v>
@@ -27455,7 +27455,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G934" t="n">
-        <v>3.5657742023468</v>
+        <v>3.56577444076538</v>
       </c>
       <c r="H934" t="n">
         <v>17050</v>
@@ -27542,7 +27542,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G937" t="n">
-        <v>3.70444345474243</v>
+        <v>3.70444321632385</v>
       </c>
       <c r="H937" t="n">
         <v>4340</v>
@@ -27571,7 +27571,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G938" t="n">
-        <v>3.70444345474243</v>
+        <v>3.70444321632385</v>
       </c>
       <c r="H938" t="n">
         <v>29290</v>
@@ -27629,7 +27629,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G940" t="n">
-        <v>3.77377796173096</v>
+        <v>3.77377772331238</v>
       </c>
       <c r="H940" t="n">
         <v>14330</v>
@@ -27803,7 +27803,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G946" t="n">
-        <v>4.04121065139771</v>
+        <v>4.04121112823486</v>
       </c>
       <c r="H946" t="n">
         <v>34120</v>
@@ -27861,7 +27861,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G948" t="n">
-        <v>4.10064029693604</v>
+        <v>4.10064077377319</v>
       </c>
       <c r="H948" t="n">
         <v>66300</v>
@@ -27919,7 +27919,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G950" t="n">
-        <v>4.10064029693604</v>
+        <v>4.10064077377319</v>
       </c>
       <c r="H950" t="n">
         <v>21380</v>
@@ -27977,7 +27977,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G952" t="n">
-        <v>3.89263701438904</v>
+        <v>3.89263725280762</v>
       </c>
       <c r="H952" t="n">
         <v>18360</v>
@@ -28006,7 +28006,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G953" t="n">
-        <v>4.03130578994751</v>
+        <v>4.03130626678467</v>
       </c>
       <c r="H953" t="n">
         <v>13820</v>
@@ -28064,7 +28064,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G955" t="n">
-        <v>4.03130578994751</v>
+        <v>4.03130626678467</v>
       </c>
       <c r="H955" t="n">
         <v>5030</v>
@@ -28093,7 +28093,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G956" t="n">
-        <v>3.99168682098389</v>
+        <v>3.99168658256531</v>
       </c>
       <c r="H956" t="n">
         <v>5970</v>
@@ -28122,7 +28122,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G957" t="n">
-        <v>3.94216179847717</v>
+        <v>3.94216156005859</v>
       </c>
       <c r="H957" t="n">
         <v>9780</v>
@@ -28180,7 +28180,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G959" t="n">
-        <v>3.94216179847717</v>
+        <v>3.94216156005859</v>
       </c>
       <c r="H959" t="n">
         <v>68590</v>
@@ -28209,7 +28209,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G960" t="n">
-        <v>4.02140092849731</v>
+        <v>4.02140140533447</v>
       </c>
       <c r="H960" t="n">
         <v>97910</v>
@@ -28238,7 +28238,7 @@
         <v>40.5999984741211</v>
       </c>
       <c r="G961" t="n">
-        <v>40.2140121459961</v>
+        <v>40.2140083312988</v>
       </c>
       <c r="H961" t="n">
         <v>13565</v>
@@ -28354,7 +28354,7 @@
         <v>3.97849988937378</v>
       </c>
       <c r="G965" t="n">
-        <v>3.94067597389221</v>
+        <v>3.94067573547363</v>
       </c>
       <c r="H965" t="n">
         <v>9527</v>
@@ -28412,7 +28412,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G967" t="n">
-        <v>3.95206665992737</v>
+        <v>3.95206642150879</v>
       </c>
       <c r="H967" t="n">
         <v>6708</v>
@@ -28731,7 +28731,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G978" t="n">
-        <v>4.02140092849731</v>
+        <v>4.02140140533447</v>
       </c>
       <c r="H978" t="n">
         <v>1125</v>
@@ -28760,7 +28760,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G979" t="n">
-        <v>3.99168682098389</v>
+        <v>3.99168658256531</v>
       </c>
       <c r="H979" t="n">
         <v>7285</v>
@@ -28876,7 +28876,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G983" t="n">
-        <v>3.95206665992737</v>
+        <v>3.95206642150879</v>
       </c>
       <c r="H983" t="n">
         <v>1600</v>
@@ -28905,7 +28905,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G984" t="n">
-        <v>3.94216179847717</v>
+        <v>3.94216156005859</v>
       </c>
       <c r="H984" t="n">
         <v>11270</v>
@@ -29050,7 +29050,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G989" t="n">
-        <v>3.80349278450012</v>
+        <v>3.80349254608154</v>
       </c>
       <c r="H989" t="n">
         <v>4556</v>
@@ -29079,7 +29079,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G990" t="n">
-        <v>3.80349278450012</v>
+        <v>3.80349254608154</v>
       </c>
       <c r="H990" t="n">
         <v>4594</v>
@@ -29253,7 +29253,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G996" t="n">
-        <v>3.80349278450012</v>
+        <v>3.80349254608154</v>
       </c>
       <c r="H996" t="n">
         <v>5243</v>
@@ -29282,7 +29282,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G997" t="n">
-        <v>3.80349278450012</v>
+        <v>3.80349254608154</v>
       </c>
       <c r="H997" t="n">
         <v>4400</v>
@@ -29369,7 +29369,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G1000" t="n">
-        <v>3.94216179847717</v>
+        <v>3.94216156005859</v>
       </c>
       <c r="H1000" t="n">
         <v>36970</v>
@@ -29485,7 +29485,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1004" t="n">
-        <v>3.78368258476257</v>
+        <v>3.78368282318115</v>
       </c>
       <c r="H1004" t="n">
         <v>13201</v>
@@ -29920,7 +29920,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1019" t="n">
-        <v>3.6450138092041</v>
+        <v>3.64501404762268</v>
       </c>
       <c r="H1019" t="n">
         <v>452</v>
@@ -29978,7 +29978,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1021" t="n">
-        <v>3.6450138092041</v>
+        <v>3.64501404762268</v>
       </c>
       <c r="H1021" t="n">
         <v>19653</v>
@@ -30065,7 +30065,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1024" t="n">
-        <v>3.61529898643494</v>
+        <v>3.61529922485352</v>
       </c>
       <c r="H1024" t="n">
         <v>8732</v>
@@ -30094,7 +30094,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G1025" t="n">
-        <v>3.58558392524719</v>
+        <v>3.58558416366577</v>
       </c>
       <c r="H1025" t="n">
         <v>2637</v>
@@ -30152,7 +30152,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1027" t="n">
-        <v>3.61529898643494</v>
+        <v>3.61529922485352</v>
       </c>
       <c r="H1027" t="n">
         <v>4783</v>
@@ -30181,7 +30181,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1028" t="n">
-        <v>3.61529898643494</v>
+        <v>3.61529922485352</v>
       </c>
       <c r="H1028" t="n">
         <v>4537</v>
@@ -30210,7 +30210,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1029" t="n">
-        <v>3.61529898643494</v>
+        <v>3.61529922485352</v>
       </c>
       <c r="H1029" t="n">
         <v>2959</v>
@@ -30384,7 +30384,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1035" t="n">
-        <v>3.5657742023468</v>
+        <v>3.56577444076538</v>
       </c>
       <c r="H1035" t="n">
         <v>11486</v>
@@ -30442,7 +30442,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G1037" t="n">
-        <v>3.52615475654602</v>
+        <v>3.52615451812744</v>
       </c>
       <c r="H1037" t="n">
         <v>5035</v>
@@ -30703,7 +30703,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G1046" t="n">
-        <v>3.52615475654602</v>
+        <v>3.52615451812744</v>
       </c>
       <c r="H1046" t="n">
         <v>4465</v>
@@ -30761,7 +30761,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1048" t="n">
-        <v>3.41720032691956</v>
+        <v>3.41720056533813</v>
       </c>
       <c r="H1048" t="n">
         <v>10706</v>
@@ -30848,7 +30848,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G1051" t="n">
-        <v>3.4568202495575</v>
+        <v>3.45682001113892</v>
       </c>
       <c r="H1051" t="n">
         <v>7061</v>
@@ -30935,7 +30935,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1054" t="n">
-        <v>3.5657742023468</v>
+        <v>3.56577444076538</v>
       </c>
       <c r="H1054" t="n">
         <v>4383</v>
@@ -30964,7 +30964,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1055" t="n">
-        <v>3.5657742023468</v>
+        <v>3.56577444076538</v>
       </c>
       <c r="H1055" t="n">
         <v>2348</v>
@@ -31109,7 +31109,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1060" t="n">
-        <v>3.5657742023468</v>
+        <v>3.56577444076538</v>
       </c>
       <c r="H1060" t="n">
         <v>2239</v>
@@ -31196,7 +31196,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1063" t="n">
-        <v>3.80349278450012</v>
+        <v>3.80349254608154</v>
       </c>
       <c r="H1063" t="n">
         <v>27840</v>
@@ -31225,7 +31225,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G1064" t="n">
-        <v>3.89263701438904</v>
+        <v>3.89263725280762</v>
       </c>
       <c r="H1064" t="n">
         <v>23123</v>
@@ -31341,7 +31341,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1068" t="n">
-        <v>3.80349278450012</v>
+        <v>3.80349254608154</v>
       </c>
       <c r="H1068" t="n">
         <v>32889</v>
@@ -31399,7 +31399,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1070" t="n">
-        <v>3.80349278450012</v>
+        <v>3.80349254608154</v>
       </c>
       <c r="H1070" t="n">
         <v>5736</v>
@@ -31428,7 +31428,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1071" t="n">
-        <v>3.80349278450012</v>
+        <v>3.80349254608154</v>
       </c>
       <c r="H1071" t="n">
         <v>5360</v>
@@ -31660,7 +31660,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1079" t="n">
-        <v>3.78368258476257</v>
+        <v>3.78368282318115</v>
       </c>
       <c r="H1079" t="n">
         <v>36488</v>
@@ -49208,9 +49208,38 @@
         <v>3.1800000667572</v>
       </c>
       <c r="H1684" t="n">
-        <v>15687</v>
+        <v>16370</v>
       </c>
       <c r="I1684" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1685">
+      <c r="A1685" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1685" s="1" t="n">
+        <v>46324.3333333333</v>
+      </c>
+      <c r="C1685" t="n">
+        <v>3.20000004768372</v>
+      </c>
+      <c r="D1685" t="n">
+        <v>3.24000000953674</v>
+      </c>
+      <c r="E1685" t="n">
+        <v>3.16000008583069</v>
+      </c>
+      <c r="F1685" t="n">
+        <v>3.22499990463257</v>
+      </c>
+      <c r="G1685" t="n">
+        <v>3.22499990463257</v>
+      </c>
+      <c r="H1685" t="n">
+        <v>16984</v>
+      </c>
+      <c r="I1685" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/UD.MI.xlsx
+++ b/data/UD.MI.xlsx
@@ -514,7 +514,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G5" t="n">
-        <v>1.50843238830566</v>
+        <v>1.50843226909637</v>
       </c>
       <c r="H5" t="n">
         <v>88000</v>
@@ -572,7 +572,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G7" t="n">
-        <v>1.51829147338867</v>
+        <v>1.51829135417938</v>
       </c>
       <c r="H7" t="n">
         <v>61000</v>
@@ -601,7 +601,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G8" t="n">
-        <v>1.53800940513611</v>
+        <v>1.53800928592682</v>
       </c>
       <c r="H8" t="n">
         <v>19000</v>
@@ -630,7 +630,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G9" t="n">
-        <v>1.55772757530212</v>
+        <v>1.55772745609283</v>
       </c>
       <c r="H9" t="n">
         <v>13000</v>
@@ -659,7 +659,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G10" t="n">
-        <v>1.53800940513611</v>
+        <v>1.53800928592682</v>
       </c>
       <c r="H10" t="n">
         <v>17000</v>
@@ -746,7 +746,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G13" t="n">
-        <v>1.55772757530212</v>
+        <v>1.55772745609283</v>
       </c>
       <c r="H13" t="n">
         <v>2000</v>
@@ -804,7 +804,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G15" t="n">
-        <v>1.64645886421204</v>
+        <v>1.64645874500275</v>
       </c>
       <c r="H15" t="n">
         <v>31000</v>
@@ -1007,7 +1007,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G22" t="n">
-        <v>1.62181103229523</v>
+        <v>1.62181115150452</v>
       </c>
       <c r="H22" t="n">
         <v>30000</v>
@@ -1036,7 +1036,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G23" t="n">
-        <v>1.59716367721558</v>
+        <v>1.59716355800629</v>
       </c>
       <c r="H23" t="n">
         <v>43000</v>
@@ -1094,7 +1094,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G25" t="n">
-        <v>1.58730471134186</v>
+        <v>1.58730459213257</v>
       </c>
       <c r="H25" t="n">
         <v>22000</v>
@@ -1268,7 +1268,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G31" t="n">
-        <v>1.63659977912903</v>
+        <v>1.63659965991974</v>
       </c>
       <c r="H31" t="n">
         <v>32000</v>
@@ -1297,7 +1297,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G32" t="n">
-        <v>1.59716367721558</v>
+        <v>1.59716355800629</v>
       </c>
       <c r="H32" t="n">
         <v>4000</v>
@@ -1326,7 +1326,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G33" t="n">
-        <v>1.6168817281723</v>
+        <v>1.61688160896301</v>
       </c>
       <c r="H33" t="n">
         <v>1000</v>
@@ -1442,7 +1442,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G37" t="n">
-        <v>1.70561301708221</v>
+        <v>1.70561289787292</v>
       </c>
       <c r="H37" t="n">
         <v>16000</v>
@@ -1471,7 +1471,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G38" t="n">
-        <v>1.70561301708221</v>
+        <v>1.70561289787292</v>
       </c>
       <c r="H38" t="n">
         <v>2000</v>
@@ -1877,7 +1877,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G52" t="n">
-        <v>1.74011969566345</v>
+        <v>1.74011981487274</v>
       </c>
       <c r="H52" t="n">
         <v>6000</v>
@@ -1906,7 +1906,7 @@
         <v>1.74500000476837</v>
       </c>
       <c r="G53" t="n">
-        <v>1.72040152549744</v>
+        <v>1.72040164470673</v>
       </c>
       <c r="H53" t="n">
         <v>7000</v>
@@ -2051,7 +2051,7 @@
         <v>1.7150000333786</v>
       </c>
       <c r="G58" t="n">
-        <v>1.6908243894577</v>
+        <v>1.69082450866699</v>
       </c>
       <c r="H58" t="n">
         <v>7000</v>
@@ -2080,7 +2080,7 @@
         <v>1.7150000333786</v>
       </c>
       <c r="G59" t="n">
-        <v>1.6908243894577</v>
+        <v>1.69082450866699</v>
       </c>
       <c r="H59" t="n">
         <v>0</v>
@@ -2457,7 +2457,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G72" t="n">
-        <v>1.64645886421204</v>
+        <v>1.64645874500275</v>
       </c>
       <c r="H72" t="n">
         <v>1000</v>
@@ -2515,7 +2515,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G74" t="n">
-        <v>1.64645886421204</v>
+        <v>1.64645874500275</v>
       </c>
       <c r="H74" t="n">
         <v>1000</v>
@@ -2631,7 +2631,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G78" t="n">
-        <v>1.64645886421204</v>
+        <v>1.64645874500275</v>
       </c>
       <c r="H78" t="n">
         <v>4000</v>
@@ -2805,7 +2805,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G84" t="n">
-        <v>1.63659977912903</v>
+        <v>1.63659965991974</v>
       </c>
       <c r="H84" t="n">
         <v>8000</v>
@@ -3037,7 +3037,7 @@
         <v>1.62999999523163</v>
       </c>
       <c r="G92" t="n">
-        <v>1.60702276229858</v>
+        <v>1.60702264308929</v>
       </c>
       <c r="H92" t="n">
         <v>32000</v>
@@ -3124,7 +3124,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G95" t="n">
-        <v>1.58730471134186</v>
+        <v>1.58730459213257</v>
       </c>
       <c r="H95" t="n">
         <v>11000</v>
@@ -3153,7 +3153,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G96" t="n">
-        <v>1.62181103229523</v>
+        <v>1.62181115150452</v>
       </c>
       <c r="H96" t="n">
         <v>16000</v>
@@ -3182,7 +3182,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G97" t="n">
-        <v>1.58730471134186</v>
+        <v>1.58730459213257</v>
       </c>
       <c r="H97" t="n">
         <v>31000</v>
@@ -3211,7 +3211,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G98" t="n">
-        <v>1.58730471134186</v>
+        <v>1.58730459213257</v>
       </c>
       <c r="H98" t="n">
         <v>11000</v>
@@ -3356,7 +3356,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G103" t="n">
-        <v>1.63659977912903</v>
+        <v>1.63659965991974</v>
       </c>
       <c r="H103" t="n">
         <v>35000</v>
@@ -3385,7 +3385,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G104" t="n">
-        <v>1.63659977912903</v>
+        <v>1.63659965991974</v>
       </c>
       <c r="H104" t="n">
         <v>14000</v>
@@ -3443,7 +3443,7 @@
         <v>1.66499996185303</v>
       </c>
       <c r="G106" t="n">
-        <v>1.64152920246124</v>
+        <v>1.64152932167053</v>
       </c>
       <c r="H106" t="n">
         <v>2000</v>
@@ -4023,7 +4023,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G126" t="n">
-        <v>1.83378028869629</v>
+        <v>1.83378040790558</v>
       </c>
       <c r="H126" t="n">
         <v>15000</v>
@@ -4052,7 +4052,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G127" t="n">
-        <v>1.82392144203186</v>
+        <v>1.82392132282257</v>
       </c>
       <c r="H127" t="n">
         <v>7000</v>
@@ -4081,7 +4081,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G128" t="n">
-        <v>1.82392144203186</v>
+        <v>1.82392132282257</v>
       </c>
       <c r="H128" t="n">
         <v>0</v>
@@ -4110,7 +4110,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G129" t="n">
-        <v>1.82392144203186</v>
+        <v>1.82392132282257</v>
       </c>
       <c r="H129" t="n">
         <v>0</v>
@@ -4168,7 +4168,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G131" t="n">
-        <v>1.83378028869629</v>
+        <v>1.83378040790558</v>
       </c>
       <c r="H131" t="n">
         <v>1000</v>
@@ -4197,7 +4197,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G132" t="n">
-        <v>1.78448522090912</v>
+        <v>1.78448534011841</v>
       </c>
       <c r="H132" t="n">
         <v>9000</v>
@@ -4342,7 +4342,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G137" t="n">
-        <v>1.88307559490204</v>
+        <v>1.88307571411133</v>
       </c>
       <c r="H137" t="n">
         <v>1000</v>
@@ -4371,7 +4371,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G138" t="n">
-        <v>1.88307559490204</v>
+        <v>1.88307571411133</v>
       </c>
       <c r="H138" t="n">
         <v>0</v>
@@ -4458,7 +4458,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G141" t="n">
-        <v>1.82392144203186</v>
+        <v>1.82392132282257</v>
       </c>
       <c r="H141" t="n">
         <v>12000</v>
@@ -4487,7 +4487,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G142" t="n">
-        <v>1.82392144203186</v>
+        <v>1.82392132282257</v>
       </c>
       <c r="H142" t="n">
         <v>13000</v>
@@ -4516,7 +4516,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G143" t="n">
-        <v>1.79927396774292</v>
+        <v>1.79927384853363</v>
       </c>
       <c r="H143" t="n">
         <v>10000</v>
@@ -4661,7 +4661,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G148" t="n">
-        <v>1.75983762741089</v>
+        <v>1.7598375082016</v>
       </c>
       <c r="H148" t="n">
         <v>12000</v>
@@ -4748,7 +4748,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G151" t="n">
-        <v>1.74011969566345</v>
+        <v>1.74011981487274</v>
       </c>
       <c r="H151" t="n">
         <v>30000</v>
@@ -4864,7 +4864,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G155" t="n">
-        <v>1.82392144203186</v>
+        <v>1.82392132282257</v>
       </c>
       <c r="H155" t="n">
         <v>13000</v>
@@ -4893,7 +4893,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G156" t="n">
-        <v>1.82392144203186</v>
+        <v>1.82392132282257</v>
       </c>
       <c r="H156" t="n">
         <v>0</v>
@@ -4951,7 +4951,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G158" t="n">
-        <v>1.83378028869629</v>
+        <v>1.83378040790558</v>
       </c>
       <c r="H158" t="n">
         <v>7000</v>
@@ -5386,7 +5386,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G173" t="n">
-        <v>1.82885098457336</v>
+        <v>1.82885086536407</v>
       </c>
       <c r="H173" t="n">
         <v>18000</v>
@@ -5415,7 +5415,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G174" t="n">
-        <v>1.82885098457336</v>
+        <v>1.82885086536407</v>
       </c>
       <c r="H174" t="n">
         <v>28000</v>
@@ -5531,7 +5531,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G178" t="n">
-        <v>1.87814617156982</v>
+        <v>1.87814605236053</v>
       </c>
       <c r="H178" t="n">
         <v>75000</v>
@@ -5560,7 +5560,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G179" t="n">
-        <v>1.88307559490204</v>
+        <v>1.88307571411133</v>
       </c>
       <c r="H179" t="n">
         <v>30000</v>
@@ -5589,7 +5589,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G180" t="n">
-        <v>1.88800525665283</v>
+        <v>1.88800513744354</v>
       </c>
       <c r="H180" t="n">
         <v>73000</v>
@@ -5647,7 +5647,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G182" t="n">
-        <v>1.91265273094177</v>
+        <v>1.91265285015106</v>
       </c>
       <c r="H182" t="n">
         <v>6000</v>
@@ -5676,7 +5676,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G183" t="n">
-        <v>2.03096103668213</v>
+        <v>2.03096127510071</v>
       </c>
       <c r="H183" t="n">
         <v>24000</v>
@@ -5705,7 +5705,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G184" t="n">
-        <v>2.01124310493469</v>
+        <v>2.01124286651611</v>
       </c>
       <c r="H184" t="n">
         <v>3000</v>
@@ -5734,7 +5734,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G185" t="n">
-        <v>2.03096103668213</v>
+        <v>2.03096127510071</v>
       </c>
       <c r="H185" t="n">
         <v>54000</v>
@@ -5792,7 +5792,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G187" t="n">
-        <v>1.95208895206451</v>
+        <v>1.95208883285522</v>
       </c>
       <c r="H187" t="n">
         <v>7000</v>
@@ -5821,7 +5821,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G188" t="n">
-        <v>2.01124310493469</v>
+        <v>2.01124286651611</v>
       </c>
       <c r="H188" t="n">
         <v>4000</v>
@@ -5850,7 +5850,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G189" t="n">
-        <v>2.01124310493469</v>
+        <v>2.01124286651611</v>
       </c>
       <c r="H189" t="n">
         <v>0</v>
@@ -5908,7 +5908,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G191" t="n">
-        <v>1.9323707818985</v>
+        <v>1.93237090110779</v>
       </c>
       <c r="H191" t="n">
         <v>8000</v>
@@ -5937,7 +5937,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G192" t="n">
-        <v>1.9323707818985</v>
+        <v>1.93237090110779</v>
       </c>
       <c r="H192" t="n">
         <v>2000</v>
@@ -5966,7 +5966,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G193" t="n">
-        <v>1.9323707818985</v>
+        <v>1.93237090110779</v>
       </c>
       <c r="H193" t="n">
         <v>0</v>
@@ -6024,7 +6024,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G195" t="n">
-        <v>1.86335742473602</v>
+        <v>1.86335754394531</v>
       </c>
       <c r="H195" t="n">
         <v>42000</v>
@@ -6053,7 +6053,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G196" t="n">
-        <v>1.89293456077576</v>
+        <v>1.89293467998505</v>
       </c>
       <c r="H196" t="n">
         <v>23000</v>
@@ -6082,7 +6082,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G197" t="n">
-        <v>1.91265273094177</v>
+        <v>1.91265285015106</v>
       </c>
       <c r="H197" t="n">
         <v>24000</v>
@@ -6111,7 +6111,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G198" t="n">
-        <v>1.91265273094177</v>
+        <v>1.91265285015106</v>
       </c>
       <c r="H198" t="n">
         <v>17000</v>
@@ -6227,7 +6227,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G202" t="n">
-        <v>1.91265273094177</v>
+        <v>1.91265285015106</v>
       </c>
       <c r="H202" t="n">
         <v>18000</v>
@@ -6314,7 +6314,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G205" t="n">
-        <v>1.9323707818985</v>
+        <v>1.93237090110779</v>
       </c>
       <c r="H205" t="n">
         <v>12000</v>
@@ -6401,7 +6401,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G208" t="n">
-        <v>1.95208895206451</v>
+        <v>1.95208883285522</v>
       </c>
       <c r="H208" t="n">
         <v>18000</v>
@@ -6459,7 +6459,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G210" t="n">
-        <v>1.95701837539673</v>
+        <v>1.95701849460602</v>
       </c>
       <c r="H210" t="n">
         <v>16000</v>
@@ -6517,7 +6517,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G212" t="n">
-        <v>1.9422299861908</v>
+        <v>1.94222986698151</v>
       </c>
       <c r="H212" t="n">
         <v>31000</v>
@@ -6604,7 +6604,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G215" t="n">
-        <v>1.95701837539673</v>
+        <v>1.95701849460602</v>
       </c>
       <c r="H215" t="n">
         <v>1000</v>
@@ -6633,7 +6633,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G216" t="n">
-        <v>1.91265273094177</v>
+        <v>1.91265285015106</v>
       </c>
       <c r="H216" t="n">
         <v>9000</v>
@@ -6691,7 +6691,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G218" t="n">
-        <v>1.89293456077576</v>
+        <v>1.89293467998505</v>
       </c>
       <c r="H218" t="n">
         <v>8000</v>
@@ -6720,7 +6720,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G219" t="n">
-        <v>1.89293456077576</v>
+        <v>1.89293467998505</v>
       </c>
       <c r="H219" t="n">
         <v>1000</v>
@@ -6894,7 +6894,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G225" t="n">
-        <v>1.9422299861908</v>
+        <v>1.94222986698151</v>
       </c>
       <c r="H225" t="n">
         <v>5000</v>
@@ -6952,7 +6952,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G227" t="n">
-        <v>1.98166596889496</v>
+        <v>1.98166584968567</v>
       </c>
       <c r="H227" t="n">
         <v>10000</v>
@@ -6981,7 +6981,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G228" t="n">
-        <v>2.00138425827026</v>
+        <v>2.00138401985168</v>
       </c>
       <c r="H228" t="n">
         <v>18000</v>
@@ -7010,7 +7010,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G229" t="n">
-        <v>2.08025622367859</v>
+        <v>2.08025598526001</v>
       </c>
       <c r="H229" t="n">
         <v>20000</v>
@@ -7039,7 +7039,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G230" t="n">
-        <v>2.02110242843628</v>
+        <v>2.0211021900177</v>
       </c>
       <c r="H230" t="n">
         <v>46000</v>
@@ -7097,7 +7097,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G232" t="n">
-        <v>2.267578125</v>
+        <v>2.26757788658142</v>
       </c>
       <c r="H232" t="n">
         <v>41000</v>
@@ -7155,7 +7155,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G234" t="n">
-        <v>2.16898798942566</v>
+        <v>2.16898775100708</v>
       </c>
       <c r="H234" t="n">
         <v>85000</v>
@@ -7213,7 +7213,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G236" t="n">
-        <v>2.1985650062561</v>
+        <v>2.19856476783752</v>
       </c>
       <c r="H236" t="n">
         <v>9000</v>
@@ -7242,7 +7242,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G237" t="n">
-        <v>2.1887059211731</v>
+        <v>2.18870568275452</v>
       </c>
       <c r="H237" t="n">
         <v>5000</v>
@@ -7271,7 +7271,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G238" t="n">
-        <v>2.23800086975098</v>
+        <v>2.2380006313324</v>
       </c>
       <c r="H238" t="n">
         <v>13000</v>
@@ -7329,7 +7329,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G240" t="n">
-        <v>2.20842385292053</v>
+        <v>2.20842361450195</v>
       </c>
       <c r="H240" t="n">
         <v>35000</v>
@@ -7416,7 +7416,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G243" t="n">
-        <v>2.267578125</v>
+        <v>2.26757788658142</v>
       </c>
       <c r="H243" t="n">
         <v>5000</v>
@@ -7445,7 +7445,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G244" t="n">
-        <v>2.29715514183044</v>
+        <v>2.29715490341187</v>
       </c>
       <c r="H244" t="n">
         <v>6000</v>
@@ -7474,7 +7474,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G245" t="n">
-        <v>2.29715514183044</v>
+        <v>2.29715490341187</v>
       </c>
       <c r="H245" t="n">
         <v>0</v>
@@ -7880,7 +7880,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G259" t="n">
-        <v>2.59292650222778</v>
+        <v>2.5929262638092</v>
       </c>
       <c r="H259" t="n">
         <v>5000</v>
@@ -7909,7 +7909,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G260" t="n">
-        <v>2.74081182479858</v>
+        <v>2.74081158638</v>
       </c>
       <c r="H260" t="n">
         <v>51000</v>
@@ -7967,7 +7967,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G262" t="n">
-        <v>2.78024768829346</v>
+        <v>2.78024744987488</v>
       </c>
       <c r="H262" t="n">
         <v>23000</v>
@@ -7996,7 +7996,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G263" t="n">
-        <v>2.9774284362793</v>
+        <v>2.97742819786072</v>
       </c>
       <c r="H263" t="n">
         <v>41000</v>
@@ -8228,7 +8228,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G271" t="n">
-        <v>2.84926128387451</v>
+        <v>2.84926104545593</v>
       </c>
       <c r="H271" t="n">
         <v>21000</v>
@@ -8257,7 +8257,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G272" t="n">
-        <v>2.99714636802673</v>
+        <v>2.99714660644531</v>
       </c>
       <c r="H272" t="n">
         <v>21000</v>
@@ -8373,7 +8373,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G276" t="n">
-        <v>3.29291772842407</v>
+        <v>3.29291749000549</v>
       </c>
       <c r="H276" t="n">
         <v>39000</v>
@@ -8402,7 +8402,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G277" t="n">
-        <v>3.17460942268372</v>
+        <v>3.17460918426514</v>
       </c>
       <c r="H277" t="n">
         <v>36000</v>
@@ -8431,7 +8431,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G278" t="n">
-        <v>3.18446826934814</v>
+        <v>3.18446850776672</v>
       </c>
       <c r="H278" t="n">
         <v>19000</v>
@@ -8518,7 +8518,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G281" t="n">
-        <v>3.18446826934814</v>
+        <v>3.18446850776672</v>
       </c>
       <c r="H281" t="n">
         <v>10000</v>
@@ -8547,7 +8547,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G282" t="n">
-        <v>3.21404552459717</v>
+        <v>3.21404528617859</v>
       </c>
       <c r="H282" t="n">
         <v>6000</v>
@@ -8576,7 +8576,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G283" t="n">
-        <v>3.24362206459045</v>
+        <v>3.24362230300903</v>
       </c>
       <c r="H283" t="n">
         <v>13000</v>
@@ -8605,7 +8605,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G284" t="n">
-        <v>3.19432735443115</v>
+        <v>3.19432711601257</v>
       </c>
       <c r="H284" t="n">
         <v>4000</v>
@@ -8692,7 +8692,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G287" t="n">
-        <v>3.60840678215027</v>
+        <v>3.60840702056885</v>
       </c>
       <c r="H287" t="n">
         <v>86000</v>
@@ -8779,7 +8779,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G290" t="n">
-        <v>3.72671484947205</v>
+        <v>3.72671508789062</v>
       </c>
       <c r="H290" t="n">
         <v>11000</v>
@@ -8837,7 +8837,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G292" t="n">
-        <v>3.64784288406372</v>
+        <v>3.64784264564514</v>
       </c>
       <c r="H292" t="n">
         <v>5000</v>
@@ -8866,7 +8866,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G293" t="n">
-        <v>3.64784288406372</v>
+        <v>3.64784264564514</v>
       </c>
       <c r="H293" t="n">
         <v>16000</v>
@@ -8924,7 +8924,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G295" t="n">
-        <v>3.51967525482178</v>
+        <v>3.5196750164032</v>
       </c>
       <c r="H295" t="n">
         <v>95000</v>
@@ -8982,7 +8982,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G297" t="n">
-        <v>3.55911135673523</v>
+        <v>3.55911111831665</v>
       </c>
       <c r="H297" t="n">
         <v>30000</v>
@@ -9069,7 +9069,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G300" t="n">
-        <v>3.4802393913269</v>
+        <v>3.48023962974548</v>
       </c>
       <c r="H300" t="n">
         <v>15000</v>
@@ -9272,7 +9272,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G307" t="n">
-        <v>3.9731912612915</v>
+        <v>3.97319102287292</v>
       </c>
       <c r="H307" t="n">
         <v>45000</v>
@@ -9301,7 +9301,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G308" t="n">
-        <v>4.26896142959595</v>
+        <v>4.26896190643311</v>
       </c>
       <c r="H308" t="n">
         <v>57000</v>
@@ -9359,7 +9359,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G310" t="n">
-        <v>4.33797597885132</v>
+        <v>4.33797550201416</v>
       </c>
       <c r="H310" t="n">
         <v>1000</v>
@@ -9388,7 +9388,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G311" t="n">
-        <v>4.14079475402832</v>
+        <v>4.14079523086548</v>
       </c>
       <c r="H311" t="n">
         <v>40000</v>
@@ -9417,7 +9417,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G312" t="n">
-        <v>3.99290895462036</v>
+        <v>3.99290943145752</v>
       </c>
       <c r="H312" t="n">
         <v>51000</v>
@@ -9446,7 +9446,7 @@
         <v>4</v>
       </c>
       <c r="G313" t="n">
-        <v>3.9436137676239</v>
+        <v>3.94361352920532</v>
       </c>
       <c r="H313" t="n">
         <v>19000</v>
@@ -9504,7 +9504,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G315" t="n">
-        <v>4.09149980545044</v>
+        <v>4.09149932861328</v>
       </c>
       <c r="H315" t="n">
         <v>8000</v>
@@ -9533,7 +9533,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G316" t="n">
-        <v>4.08164024353027</v>
+        <v>4.08163976669312</v>
       </c>
       <c r="H316" t="n">
         <v>8000</v>
@@ -9562,7 +9562,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G317" t="n">
-        <v>4.14079475402832</v>
+        <v>4.14079523086548</v>
       </c>
       <c r="H317" t="n">
         <v>21000</v>
@@ -9591,7 +9591,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G318" t="n">
-        <v>4.17037153244019</v>
+        <v>4.17037105560303</v>
       </c>
       <c r="H318" t="n">
         <v>10000</v>
@@ -9794,7 +9794,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G325" t="n">
-        <v>4.06192207336426</v>
+        <v>4.06192255020142</v>
       </c>
       <c r="H325" t="n">
         <v>7000</v>
@@ -9823,7 +9823,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G326" t="n">
-        <v>4.00276851654053</v>
+        <v>4.00276803970337</v>
       </c>
       <c r="H326" t="n">
         <v>5000</v>
@@ -9852,7 +9852,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G327" t="n">
-        <v>4.16051244735718</v>
+        <v>4.16051197052002</v>
       </c>
       <c r="H327" t="n">
         <v>7000</v>
@@ -9881,7 +9881,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G328" t="n">
-        <v>4.16051244735718</v>
+        <v>4.16051197052002</v>
       </c>
       <c r="H328" t="n">
         <v>2000</v>
@@ -9910,7 +9910,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G329" t="n">
-        <v>4.02248620986938</v>
+        <v>4.02248573303223</v>
       </c>
       <c r="H329" t="n">
         <v>5000</v>
@@ -10026,7 +10026,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G333" t="n">
-        <v>4.16051244735718</v>
+        <v>4.16051197052002</v>
       </c>
       <c r="H333" t="n">
         <v>5000</v>
@@ -10055,7 +10055,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G334" t="n">
-        <v>4.16051244735718</v>
+        <v>4.16051197052002</v>
       </c>
       <c r="H334" t="n">
         <v>14000</v>
@@ -10084,7 +10084,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G335" t="n">
-        <v>4.17037153244019</v>
+        <v>4.17037105560303</v>
       </c>
       <c r="H335" t="n">
         <v>3000</v>
@@ -10113,7 +10113,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G336" t="n">
-        <v>4.00276851654053</v>
+        <v>4.00276803970337</v>
       </c>
       <c r="H336" t="n">
         <v>3000</v>
@@ -10142,7 +10142,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G337" t="n">
-        <v>4.00276851654053</v>
+        <v>4.00276803970337</v>
       </c>
       <c r="H337" t="n">
         <v>0</v>
@@ -10171,7 +10171,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G338" t="n">
-        <v>4.16051244735718</v>
+        <v>4.16051197052002</v>
       </c>
       <c r="H338" t="n">
         <v>5000</v>
@@ -10200,7 +10200,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G339" t="n">
-        <v>4.16051244735718</v>
+        <v>4.16051197052002</v>
       </c>
       <c r="H339" t="n">
         <v>0</v>
@@ -10229,7 +10229,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G340" t="n">
-        <v>4.14079475402832</v>
+        <v>4.14079523086548</v>
       </c>
       <c r="H340" t="n">
         <v>16000</v>
@@ -10258,7 +10258,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G341" t="n">
-        <v>4.14079475402832</v>
+        <v>4.14079523086548</v>
       </c>
       <c r="H341" t="n">
         <v>15500</v>
@@ -10287,7 +10287,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G342" t="n">
-        <v>4.06192207336426</v>
+        <v>4.06192255020142</v>
       </c>
       <c r="H342" t="n">
         <v>5000</v>
@@ -10316,7 +10316,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G343" t="n">
-        <v>4.14079475402832</v>
+        <v>4.14079523086548</v>
       </c>
       <c r="H343" t="n">
         <v>3500</v>
@@ -10374,7 +10374,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G345" t="n">
-        <v>4.08164024353027</v>
+        <v>4.08163976669312</v>
       </c>
       <c r="H345" t="n">
         <v>1000</v>
@@ -10403,7 +10403,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G346" t="n">
-        <v>4.04220485687256</v>
+        <v>4.0422043800354</v>
       </c>
       <c r="H346" t="n">
         <v>2500</v>
@@ -10432,7 +10432,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G347" t="n">
-        <v>4.02248620986938</v>
+        <v>4.02248573303223</v>
       </c>
       <c r="H347" t="n">
         <v>3000</v>
@@ -10461,7 +10461,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G348" t="n">
-        <v>4.02248620986938</v>
+        <v>4.02248573303223</v>
       </c>
       <c r="H348" t="n">
         <v>16500</v>
@@ -10490,7 +10490,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G349" t="n">
-        <v>4.21966695785522</v>
+        <v>4.21966648101807</v>
       </c>
       <c r="H349" t="n">
         <v>21000</v>
@@ -10635,7 +10635,7 @@
         <v>4.25</v>
       </c>
       <c r="G354" t="n">
-        <v>4.1900897026062</v>
+        <v>4.19009017944336</v>
       </c>
       <c r="H354" t="n">
         <v>20500</v>
@@ -10664,7 +10664,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G355" t="n">
-        <v>4.08164024353027</v>
+        <v>4.08163976669312</v>
       </c>
       <c r="H355" t="n">
         <v>21000</v>
@@ -10693,7 +10693,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G356" t="n">
-        <v>4.14079475402832</v>
+        <v>4.14079523086548</v>
       </c>
       <c r="H356" t="n">
         <v>8500</v>
@@ -10780,7 +10780,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G359" t="n">
-        <v>4.21966695785522</v>
+        <v>4.21966648101807</v>
       </c>
       <c r="H359" t="n">
         <v>14500</v>
@@ -10838,7 +10838,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G361" t="n">
-        <v>4.08164024353027</v>
+        <v>4.08163976669312</v>
       </c>
       <c r="H361" t="n">
         <v>10500</v>
@@ -10867,7 +10867,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G362" t="n">
-        <v>4.09149980545044</v>
+        <v>4.09149932861328</v>
       </c>
       <c r="H362" t="n">
         <v>4500</v>
@@ -10896,7 +10896,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G363" t="n">
-        <v>4.1210765838623</v>
+        <v>4.12107610702515</v>
       </c>
       <c r="H363" t="n">
         <v>500</v>
@@ -10925,7 +10925,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G364" t="n">
-        <v>4.1210765838623</v>
+        <v>4.12107610702515</v>
       </c>
       <c r="H364" t="n">
         <v>0</v>
@@ -10954,7 +10954,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G365" t="n">
-        <v>4.1210765838623</v>
+        <v>4.12107610702515</v>
       </c>
       <c r="H365" t="n">
         <v>0</v>
@@ -10983,7 +10983,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G366" t="n">
-        <v>4.14079475402832</v>
+        <v>4.14079523086548</v>
       </c>
       <c r="H366" t="n">
         <v>1500</v>
@@ -11012,7 +11012,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G367" t="n">
-        <v>4.14079475402832</v>
+        <v>4.14079523086548</v>
       </c>
       <c r="H367" t="n">
         <v>1000</v>
@@ -11041,7 +11041,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G368" t="n">
-        <v>4.14079475402832</v>
+        <v>4.14079523086548</v>
       </c>
       <c r="H368" t="n">
         <v>0</v>
@@ -11070,7 +11070,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G369" t="n">
-        <v>4.08164024353027</v>
+        <v>4.08163976669312</v>
       </c>
       <c r="H369" t="n">
         <v>1500</v>
@@ -11157,7 +11157,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G372" t="n">
-        <v>4.08164024353027</v>
+        <v>4.08163976669312</v>
       </c>
       <c r="H372" t="n">
         <v>8500</v>
@@ -11186,7 +11186,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G373" t="n">
-        <v>4.14079475402832</v>
+        <v>4.14079523086548</v>
       </c>
       <c r="H373" t="n">
         <v>500</v>
@@ -11215,7 +11215,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G374" t="n">
-        <v>4.14079475402832</v>
+        <v>4.14079523086548</v>
       </c>
       <c r="H374" t="n">
         <v>0</v>
@@ -11244,7 +11244,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G375" t="n">
-        <v>4.14079475402832</v>
+        <v>4.14079523086548</v>
       </c>
       <c r="H375" t="n">
         <v>0</v>
@@ -11331,7 +11331,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G378" t="n">
-        <v>4.27882146835327</v>
+        <v>4.27882099151611</v>
       </c>
       <c r="H378" t="n">
         <v>7000</v>
@@ -11360,7 +11360,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G379" t="n">
-        <v>4.21966695785522</v>
+        <v>4.21966648101807</v>
       </c>
       <c r="H379" t="n">
         <v>67000</v>
@@ -11389,7 +11389,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G380" t="n">
-        <v>4.21966695785522</v>
+        <v>4.21966648101807</v>
       </c>
       <c r="H380" t="n">
         <v>3000</v>
@@ -11505,7 +11505,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G384" t="n">
-        <v>4.33797597885132</v>
+        <v>4.33797550201416</v>
       </c>
       <c r="H384" t="n">
         <v>17000</v>
@@ -11650,7 +11650,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G389" t="n">
-        <v>4.26896142959595</v>
+        <v>4.26896190643311</v>
       </c>
       <c r="H389" t="n">
         <v>15000</v>
@@ -11679,7 +11679,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G390" t="n">
-        <v>4.33797597885132</v>
+        <v>4.33797550201416</v>
       </c>
       <c r="H390" t="n">
         <v>15000</v>
@@ -11737,7 +11737,7 @@
         <v>4.25</v>
       </c>
       <c r="G392" t="n">
-        <v>4.1900897026062</v>
+        <v>4.19009017944336</v>
       </c>
       <c r="H392" t="n">
         <v>8000</v>
@@ -11766,7 +11766,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G393" t="n">
-        <v>4.33797597885132</v>
+        <v>4.33797550201416</v>
       </c>
       <c r="H393" t="n">
         <v>6000</v>
@@ -11882,7 +11882,7 @@
         <v>4.25</v>
       </c>
       <c r="G397" t="n">
-        <v>4.1900897026062</v>
+        <v>4.19009017944336</v>
       </c>
       <c r="H397" t="n">
         <v>7500</v>
@@ -11911,7 +11911,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G398" t="n">
-        <v>4.04220485687256</v>
+        <v>4.0422043800354</v>
       </c>
       <c r="H398" t="n">
         <v>6000</v>
@@ -11940,7 +11940,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G399" t="n">
-        <v>4.04220485687256</v>
+        <v>4.0422043800354</v>
       </c>
       <c r="H399" t="n">
         <v>7500</v>
@@ -11969,7 +11969,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G400" t="n">
-        <v>4.04220485687256</v>
+        <v>4.0422043800354</v>
       </c>
       <c r="H400" t="n">
         <v>0</v>
@@ -12085,7 +12085,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G404" t="n">
-        <v>4.33797597885132</v>
+        <v>4.33797550201416</v>
       </c>
       <c r="H404" t="n">
         <v>37500</v>
@@ -12114,7 +12114,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G405" t="n">
-        <v>4.38726997375488</v>
+        <v>4.38727045059204</v>
       </c>
       <c r="H405" t="n">
         <v>13000</v>
@@ -12143,7 +12143,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G406" t="n">
-        <v>4.39713001251221</v>
+        <v>4.39712953567505</v>
       </c>
       <c r="H406" t="n">
         <v>19500</v>
@@ -12172,7 +12172,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G407" t="n">
-        <v>4.38726997375488</v>
+        <v>4.38727045059204</v>
       </c>
       <c r="H407" t="n">
         <v>6000</v>
@@ -12201,7 +12201,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G408" t="n">
-        <v>4.38726997375488</v>
+        <v>4.38727045059204</v>
       </c>
       <c r="H408" t="n">
         <v>85000</v>
@@ -12230,7 +12230,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G409" t="n">
-        <v>4.49571990966797</v>
+        <v>4.49571943283081</v>
       </c>
       <c r="H409" t="n">
         <v>23000</v>
@@ -12288,7 +12288,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G411" t="n">
-        <v>5.0478253364563</v>
+        <v>5.04782485961914</v>
       </c>
       <c r="H411" t="n">
         <v>104000</v>
@@ -12317,7 +12317,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G412" t="n">
-        <v>5.30416059494019</v>
+        <v>5.30416011810303</v>
       </c>
       <c r="H412" t="n">
         <v>82500</v>
@@ -12346,7 +12346,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G413" t="n">
-        <v>5.24500703811646</v>
+        <v>5.2450065612793</v>
       </c>
       <c r="H413" t="n">
         <v>33000</v>
@@ -12491,7 +12491,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G418" t="n">
-        <v>4.98867177963257</v>
+        <v>4.98867130279541</v>
       </c>
       <c r="H418" t="n">
         <v>23500</v>
@@ -12520,7 +12520,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G419" t="n">
-        <v>5.02810716629028</v>
+        <v>5.02810764312744</v>
       </c>
       <c r="H419" t="n">
         <v>5500</v>
@@ -12665,7 +12665,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G424" t="n">
-        <v>4.89008188247681</v>
+        <v>4.89008140563965</v>
       </c>
       <c r="H424" t="n">
         <v>11000</v>
@@ -12694,7 +12694,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G425" t="n">
-        <v>5.02810716629028</v>
+        <v>5.02810764312744</v>
       </c>
       <c r="H425" t="n">
         <v>4500</v>
@@ -12723,7 +12723,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G426" t="n">
-        <v>5.08726167678833</v>
+        <v>5.08726119995117</v>
       </c>
       <c r="H426" t="n">
         <v>1500</v>
@@ -12752,7 +12752,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G427" t="n">
-        <v>5.02810716629028</v>
+        <v>5.02810764312744</v>
       </c>
       <c r="H427" t="n">
         <v>1500</v>
@@ -12810,7 +12810,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G429" t="n">
-        <v>5.12669801712036</v>
+        <v>5.1266975402832</v>
       </c>
       <c r="H429" t="n">
         <v>7000</v>
@@ -12868,7 +12868,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G431" t="n">
-        <v>4.98867177963257</v>
+        <v>4.98867130279541</v>
       </c>
       <c r="H431" t="n">
         <v>8000</v>
@@ -12926,7 +12926,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G433" t="n">
-        <v>4.88022184371948</v>
+        <v>4.88022232055664</v>
       </c>
       <c r="H433" t="n">
         <v>500</v>
@@ -13042,7 +13042,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G437" t="n">
-        <v>4.90979909896851</v>
+        <v>4.90979957580566</v>
       </c>
       <c r="H437" t="n">
         <v>16000</v>
@@ -13100,7 +13100,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G439" t="n">
-        <v>4.89008188247681</v>
+        <v>4.89008140563965</v>
       </c>
       <c r="H439" t="n">
         <v>4500</v>
@@ -13158,7 +13158,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G441" t="n">
-        <v>4.89008188247681</v>
+        <v>4.89008140563965</v>
       </c>
       <c r="H441" t="n">
         <v>2000</v>
@@ -13187,7 +13187,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G442" t="n">
-        <v>4.90979909896851</v>
+        <v>4.90979957580566</v>
       </c>
       <c r="H442" t="n">
         <v>11000</v>
@@ -13216,7 +13216,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G443" t="n">
-        <v>5.0478253364563</v>
+        <v>5.04782485961914</v>
       </c>
       <c r="H443" t="n">
         <v>5500</v>
@@ -13245,7 +13245,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G444" t="n">
-        <v>5.02810716629028</v>
+        <v>5.02810764312744</v>
       </c>
       <c r="H444" t="n">
         <v>6500</v>
@@ -13332,7 +13332,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G447" t="n">
-        <v>4.85064554214478</v>
+        <v>4.85064506530762</v>
       </c>
       <c r="H447" t="n">
         <v>3500</v>
@@ -13535,7 +13535,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G454" t="n">
-        <v>4.84078550338745</v>
+        <v>4.84078598022461</v>
       </c>
       <c r="H454" t="n">
         <v>1250</v>
@@ -13564,7 +13564,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G455" t="n">
-        <v>4.85064554214478</v>
+        <v>4.85064506530762</v>
       </c>
       <c r="H455" t="n">
         <v>1650</v>
@@ -13622,7 +13622,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G457" t="n">
-        <v>5.0478253364563</v>
+        <v>5.04782485961914</v>
       </c>
       <c r="H457" t="n">
         <v>26170</v>
@@ -13651,7 +13651,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G458" t="n">
-        <v>5.50134181976318</v>
+        <v>5.50134134292603</v>
       </c>
       <c r="H458" t="n">
         <v>75450</v>
@@ -13680,7 +13680,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G459" t="n">
-        <v>5.26472473144531</v>
+        <v>5.26472425460815</v>
       </c>
       <c r="H459" t="n">
         <v>23670</v>
@@ -13709,7 +13709,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G460" t="n">
-        <v>5.34359693527222</v>
+        <v>5.34359645843506</v>
       </c>
       <c r="H460" t="n">
         <v>6980</v>
@@ -13738,7 +13738,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G461" t="n">
-        <v>5.30416059494019</v>
+        <v>5.30416011810303</v>
       </c>
       <c r="H461" t="n">
         <v>2900</v>
@@ -13825,7 +13825,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G464" t="n">
-        <v>5.0478253364563</v>
+        <v>5.04782485961914</v>
       </c>
       <c r="H464" t="n">
         <v>3580</v>
@@ -13883,7 +13883,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G466" t="n">
-        <v>5.12669801712036</v>
+        <v>5.1266975402832</v>
       </c>
       <c r="H466" t="n">
         <v>7070</v>
@@ -13912,7 +13912,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G467" t="n">
-        <v>5.12669801712036</v>
+        <v>5.1266975402832</v>
       </c>
       <c r="H467" t="n">
         <v>200</v>
@@ -13999,7 +13999,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G470" t="n">
-        <v>5.08726167678833</v>
+        <v>5.08726119995117</v>
       </c>
       <c r="H470" t="n">
         <v>2920</v>
@@ -14115,7 +14115,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G474" t="n">
-        <v>4.98867177963257</v>
+        <v>4.98867130279541</v>
       </c>
       <c r="H474" t="n">
         <v>17780</v>
@@ -14144,7 +14144,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G475" t="n">
-        <v>5.14641571044922</v>
+        <v>5.14641618728638</v>
       </c>
       <c r="H475" t="n">
         <v>14970</v>
@@ -14173,7 +14173,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G476" t="n">
-        <v>5.02810716629028</v>
+        <v>5.02810764312744</v>
       </c>
       <c r="H476" t="n">
         <v>2700</v>
@@ -14260,7 +14260,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G479" t="n">
-        <v>5.02810716629028</v>
+        <v>5.02810764312744</v>
       </c>
       <c r="H479" t="n">
         <v>12190</v>
@@ -14289,7 +14289,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G480" t="n">
-        <v>5.14641571044922</v>
+        <v>5.14641618728638</v>
       </c>
       <c r="H480" t="n">
         <v>11670</v>
@@ -14318,7 +14318,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G481" t="n">
-        <v>5.14641571044922</v>
+        <v>5.14641618728638</v>
       </c>
       <c r="H481" t="n">
         <v>7130</v>
@@ -14376,7 +14376,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G483" t="n">
-        <v>5.12669801712036</v>
+        <v>5.1266975402832</v>
       </c>
       <c r="H483" t="n">
         <v>4620</v>
@@ -14405,7 +14405,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G484" t="n">
-        <v>5.12669801712036</v>
+        <v>5.1266975402832</v>
       </c>
       <c r="H484" t="n">
         <v>6620</v>
@@ -14434,7 +14434,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G485" t="n">
-        <v>5.12669801712036</v>
+        <v>5.1266975402832</v>
       </c>
       <c r="H485" t="n">
         <v>11880</v>
@@ -14463,7 +14463,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G486" t="n">
-        <v>5.0478253364563</v>
+        <v>5.04782485961914</v>
       </c>
       <c r="H486" t="n">
         <v>5290</v>
@@ -14550,7 +14550,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G489" t="n">
-        <v>4.98867177963257</v>
+        <v>4.98867130279541</v>
       </c>
       <c r="H489" t="n">
         <v>21530</v>
@@ -14579,7 +14579,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G490" t="n">
-        <v>5.12669801712036</v>
+        <v>5.1266975402832</v>
       </c>
       <c r="H490" t="n">
         <v>26550</v>
@@ -14608,7 +14608,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G491" t="n">
-        <v>4.98867177963257</v>
+        <v>4.98867130279541</v>
       </c>
       <c r="H491" t="n">
         <v>28100</v>
@@ -14724,7 +14724,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G495" t="n">
-        <v>5.08726167678833</v>
+        <v>5.08726119995117</v>
       </c>
       <c r="H495" t="n">
         <v>6900</v>
@@ -14782,7 +14782,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G497" t="n">
-        <v>4.87036323547363</v>
+        <v>4.87036275863647</v>
       </c>
       <c r="H497" t="n">
         <v>20640</v>
@@ -14811,7 +14811,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G498" t="n">
-        <v>5.02810716629028</v>
+        <v>5.02810764312744</v>
       </c>
       <c r="H498" t="n">
         <v>7720</v>
@@ -14840,7 +14840,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G499" t="n">
-        <v>5.02810716629028</v>
+        <v>5.02810764312744</v>
       </c>
       <c r="H499" t="n">
         <v>4040</v>
@@ -14869,7 +14869,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G500" t="n">
-        <v>5.0478253364563</v>
+        <v>5.04782485961914</v>
       </c>
       <c r="H500" t="n">
         <v>4690</v>
@@ -14927,7 +14927,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G502" t="n">
-        <v>5.08726167678833</v>
+        <v>5.08726119995117</v>
       </c>
       <c r="H502" t="n">
         <v>5550</v>
@@ -14956,7 +14956,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G503" t="n">
-        <v>5.02810716629028</v>
+        <v>5.02810764312744</v>
       </c>
       <c r="H503" t="n">
         <v>14170</v>
@@ -15014,7 +15014,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G505" t="n">
-        <v>4.98867177963257</v>
+        <v>4.98867130279541</v>
       </c>
       <c r="H505" t="n">
         <v>4800</v>
@@ -15043,7 +15043,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G506" t="n">
-        <v>5.12669801712036</v>
+        <v>5.1266975402832</v>
       </c>
       <c r="H506" t="n">
         <v>5270</v>
@@ -15159,7 +15159,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G510" t="n">
-        <v>4.98867177963257</v>
+        <v>4.98867130279541</v>
       </c>
       <c r="H510" t="n">
         <v>1110</v>
@@ -15188,7 +15188,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G511" t="n">
-        <v>5.02810716629028</v>
+        <v>5.02810764312744</v>
       </c>
       <c r="H511" t="n">
         <v>2710</v>
@@ -15217,7 +15217,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G512" t="n">
-        <v>5.08726167678833</v>
+        <v>5.08726119995117</v>
       </c>
       <c r="H512" t="n">
         <v>14440</v>
@@ -15362,7 +15362,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G517" t="n">
-        <v>5.02810716629028</v>
+        <v>5.02810764312744</v>
       </c>
       <c r="H517" t="n">
         <v>80</v>
@@ -15449,7 +15449,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G520" t="n">
-        <v>5.02810716629028</v>
+        <v>5.02810764312744</v>
       </c>
       <c r="H520" t="n">
         <v>18090</v>
@@ -15507,7 +15507,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G522" t="n">
-        <v>5.0478253364563</v>
+        <v>5.04782485961914</v>
       </c>
       <c r="H522" t="n">
         <v>27900</v>
@@ -15536,7 +15536,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G523" t="n">
-        <v>5.02810716629028</v>
+        <v>5.02810764312744</v>
       </c>
       <c r="H523" t="n">
         <v>1940</v>
@@ -15594,7 +15594,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G525" t="n">
-        <v>4.88022184371948</v>
+        <v>4.88022232055664</v>
       </c>
       <c r="H525" t="n">
         <v>11030</v>
@@ -15652,7 +15652,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G527" t="n">
-        <v>4.85064554214478</v>
+        <v>4.85064506530762</v>
       </c>
       <c r="H527" t="n">
         <v>12990</v>
@@ -15710,7 +15710,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G529" t="n">
-        <v>4.77177333831787</v>
+        <v>4.77177286148071</v>
       </c>
       <c r="H529" t="n">
         <v>14510</v>
@@ -15739,7 +15739,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G530" t="n">
-        <v>4.73233699798584</v>
+        <v>4.73233652114868</v>
       </c>
       <c r="H530" t="n">
         <v>6730</v>
@@ -15797,7 +15797,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G532" t="n">
-        <v>4.77177333831787</v>
+        <v>4.77177286148071</v>
       </c>
       <c r="H532" t="n">
         <v>4310</v>
@@ -15855,7 +15855,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G534" t="n">
-        <v>4.73233699798584</v>
+        <v>4.73233652114868</v>
       </c>
       <c r="H534" t="n">
         <v>13910</v>
@@ -15884,7 +15884,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G535" t="n">
-        <v>4.73233699798584</v>
+        <v>4.73233652114868</v>
       </c>
       <c r="H535" t="n">
         <v>3100</v>
@@ -15913,7 +15913,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G536" t="n">
-        <v>4.71261882781982</v>
+        <v>4.71261930465698</v>
       </c>
       <c r="H536" t="n">
         <v>153850</v>
@@ -15942,7 +15942,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G537" t="n">
-        <v>4.73233699798584</v>
+        <v>4.73233652114868</v>
       </c>
       <c r="H537" t="n">
         <v>2420</v>
@@ -16000,7 +16000,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G539" t="n">
-        <v>4.85064554214478</v>
+        <v>4.85064506530762</v>
       </c>
       <c r="H539" t="n">
         <v>610</v>
@@ -16116,7 +16116,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G543" t="n">
-        <v>4.84078550338745</v>
+        <v>4.84078598022461</v>
       </c>
       <c r="H543" t="n">
         <v>3320</v>
@@ -16145,7 +16145,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G544" t="n">
-        <v>4.84078550338745</v>
+        <v>4.84078598022461</v>
       </c>
       <c r="H544" t="n">
         <v>0</v>
@@ -16232,7 +16232,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G547" t="n">
-        <v>4.62362098693848</v>
+        <v>4.62362051010132</v>
       </c>
       <c r="H547" t="n">
         <v>10330</v>
@@ -16319,7 +16319,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G550" t="n">
-        <v>4.6433801651001</v>
+        <v>4.64337968826294</v>
       </c>
       <c r="H550" t="n">
         <v>1990</v>
@@ -16348,7 +16348,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G551" t="n">
-        <v>4.7421760559082</v>
+        <v>4.74217557907104</v>
       </c>
       <c r="H551" t="n">
         <v>730</v>
@@ -16377,7 +16377,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G552" t="n">
-        <v>4.78169393539429</v>
+        <v>4.78169345855713</v>
       </c>
       <c r="H552" t="n">
         <v>1640</v>
@@ -16406,7 +16406,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G553" t="n">
-        <v>4.78169393539429</v>
+        <v>4.78169345855713</v>
       </c>
       <c r="H553" t="n">
         <v>0</v>
@@ -16435,7 +16435,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G554" t="n">
-        <v>4.78169393539429</v>
+        <v>4.78169345855713</v>
       </c>
       <c r="H554" t="n">
         <v>0</v>
@@ -16493,7 +16493,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G556" t="n">
-        <v>4.7421760559082</v>
+        <v>4.74217557907104</v>
       </c>
       <c r="H556" t="n">
         <v>13120</v>
@@ -16522,7 +16522,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G557" t="n">
-        <v>4.7421760559082</v>
+        <v>4.74217557907104</v>
       </c>
       <c r="H557" t="n">
         <v>260</v>
@@ -16696,7 +16696,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G563" t="n">
-        <v>4.84097099304199</v>
+        <v>4.84097051620483</v>
       </c>
       <c r="H563" t="n">
         <v>4490</v>
@@ -16725,7 +16725,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G564" t="n">
-        <v>4.84097099304199</v>
+        <v>4.84097051620483</v>
       </c>
       <c r="H564" t="n">
         <v>0</v>
@@ -16754,7 +16754,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G565" t="n">
-        <v>4.84097099304199</v>
+        <v>4.84097051620483</v>
       </c>
       <c r="H565" t="n">
         <v>0</v>
@@ -16783,7 +16783,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G566" t="n">
-        <v>4.84097099304199</v>
+        <v>4.84097051620483</v>
       </c>
       <c r="H566" t="n">
         <v>0</v>
@@ -16928,7 +16928,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G571" t="n">
-        <v>4.84097099304199</v>
+        <v>4.84097051620483</v>
       </c>
       <c r="H571" t="n">
         <v>2630</v>
@@ -17160,7 +17160,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G579" t="n">
-        <v>4.27783727645874</v>
+        <v>4.2778377532959</v>
       </c>
       <c r="H579" t="n">
         <v>2300</v>
@@ -17218,7 +17218,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G581" t="n">
-        <v>4.40627193450928</v>
+        <v>4.40627145767212</v>
       </c>
       <c r="H581" t="n">
         <v>1200</v>
@@ -17276,7 +17276,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G583" t="n">
-        <v>4.6433801651001</v>
+        <v>4.64337968826294</v>
       </c>
       <c r="H583" t="n">
         <v>1100</v>
@@ -17305,7 +17305,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G584" t="n">
-        <v>4.78169393539429</v>
+        <v>4.78169345855713</v>
       </c>
       <c r="H584" t="n">
         <v>3210</v>
@@ -17363,7 +17363,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G586" t="n">
-        <v>4.7421760559082</v>
+        <v>4.74217557907104</v>
       </c>
       <c r="H586" t="n">
         <v>200</v>
@@ -17421,7 +17421,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G588" t="n">
-        <v>4.4951868057251</v>
+        <v>4.49518728256226</v>
       </c>
       <c r="H588" t="n">
         <v>1140</v>
@@ -17479,7 +17479,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G590" t="n">
-        <v>4.3865122795105</v>
+        <v>4.38651180267334</v>
       </c>
       <c r="H590" t="n">
         <v>37290</v>
@@ -17595,7 +17595,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G594" t="n">
-        <v>4.48530769348145</v>
+        <v>4.48530721664429</v>
       </c>
       <c r="H594" t="n">
         <v>1520</v>
@@ -17624,7 +17624,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G595" t="n">
-        <v>4.35687398910522</v>
+        <v>4.35687351226807</v>
       </c>
       <c r="H595" t="n">
         <v>30</v>
@@ -17682,7 +17682,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G597" t="n">
-        <v>4.40627193450928</v>
+        <v>4.40627145767212</v>
       </c>
       <c r="H597" t="n">
         <v>1930</v>
@@ -17711,7 +17711,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G598" t="n">
-        <v>4.4951868057251</v>
+        <v>4.49518728256226</v>
       </c>
       <c r="H598" t="n">
         <v>1400</v>
@@ -17769,7 +17769,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G600" t="n">
-        <v>4.48530769348145</v>
+        <v>4.48530721664429</v>
       </c>
       <c r="H600" t="n">
         <v>1360</v>
@@ -17798,7 +17798,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G601" t="n">
-        <v>4.54458475112915</v>
+        <v>4.54458427429199</v>
       </c>
       <c r="H601" t="n">
         <v>3410</v>
@@ -17856,7 +17856,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G603" t="n">
-        <v>4.6433801651001</v>
+        <v>4.64337968826294</v>
       </c>
       <c r="H603" t="n">
         <v>1550</v>
@@ -17885,7 +17885,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G604" t="n">
-        <v>4.84097099304199</v>
+        <v>4.84097051620483</v>
       </c>
       <c r="H604" t="n">
         <v>7020</v>
@@ -17943,7 +17943,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G606" t="n">
-        <v>4.89036798477173</v>
+        <v>4.89036846160889</v>
       </c>
       <c r="H606" t="n">
         <v>2760</v>
@@ -18059,7 +18059,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G610" t="n">
-        <v>4.84097099304199</v>
+        <v>4.84097051620483</v>
       </c>
       <c r="H610" t="n">
         <v>3200</v>
@@ -18146,7 +18146,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G613" t="n">
-        <v>4.78169393539429</v>
+        <v>4.78169345855713</v>
       </c>
       <c r="H613" t="n">
         <v>1500</v>
@@ -18175,7 +18175,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G614" t="n">
-        <v>4.84097099304199</v>
+        <v>4.84097051620483</v>
       </c>
       <c r="H614" t="n">
         <v>3250</v>
@@ -18204,7 +18204,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G615" t="n">
-        <v>4.88048887252808</v>
+        <v>4.88048839569092</v>
       </c>
       <c r="H615" t="n">
         <v>1500</v>
@@ -18349,7 +18349,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G620" t="n">
-        <v>4.99904346466064</v>
+        <v>4.99904298782349</v>
       </c>
       <c r="H620" t="n">
         <v>3460</v>
@@ -18813,7 +18813,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G636" t="n">
-        <v>4.89036798477173</v>
+        <v>4.89036846160889</v>
       </c>
       <c r="H636" t="n">
         <v>1500</v>
@@ -18842,7 +18842,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G637" t="n">
-        <v>4.88048887252808</v>
+        <v>4.88048839569092</v>
       </c>
       <c r="H637" t="n">
         <v>1800</v>
@@ -18871,7 +18871,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G638" t="n">
-        <v>4.88048887252808</v>
+        <v>4.88048839569092</v>
       </c>
       <c r="H638" t="n">
         <v>0</v>
@@ -19016,7 +19016,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G643" t="n">
-        <v>4.73229551315308</v>
+        <v>4.73229598999023</v>
       </c>
       <c r="H643" t="n">
         <v>4150</v>
@@ -19045,7 +19045,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G644" t="n">
-        <v>4.54458475112915</v>
+        <v>4.54458427429199</v>
       </c>
       <c r="H644" t="n">
         <v>7280</v>
@@ -19074,7 +19074,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G645" t="n">
-        <v>4.4951868057251</v>
+        <v>4.49518728256226</v>
       </c>
       <c r="H645" t="n">
         <v>3250</v>
@@ -19219,7 +19219,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G650" t="n">
-        <v>4.52482604980469</v>
+        <v>4.52482557296753</v>
       </c>
       <c r="H650" t="n">
         <v>11950</v>
@@ -19364,7 +19364,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G655" t="n">
-        <v>4.84097099304199</v>
+        <v>4.84097051620483</v>
       </c>
       <c r="H655" t="n">
         <v>2980</v>
@@ -19480,7 +19480,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G659" t="n">
-        <v>4.7421760559082</v>
+        <v>4.74217557907104</v>
       </c>
       <c r="H659" t="n">
         <v>60</v>
@@ -19509,7 +19509,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G660" t="n">
-        <v>4.7421760559082</v>
+        <v>4.74217557907104</v>
       </c>
       <c r="H660" t="n">
         <v>12790</v>
@@ -19538,7 +19538,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G661" t="n">
-        <v>4.88048887252808</v>
+        <v>4.88048839569092</v>
       </c>
       <c r="H661" t="n">
         <v>1600</v>
@@ -19567,7 +19567,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G662" t="n">
-        <v>4.7421760559082</v>
+        <v>4.74217557907104</v>
       </c>
       <c r="H662" t="n">
         <v>10540</v>
@@ -20002,7 +20002,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G677" t="n">
-        <v>4.89036798477173</v>
+        <v>4.89036846160889</v>
       </c>
       <c r="H677" t="n">
         <v>54910</v>
@@ -20031,7 +20031,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G678" t="n">
-        <v>4.7421760559082</v>
+        <v>4.74217557907104</v>
       </c>
       <c r="H678" t="n">
         <v>42730</v>
@@ -20089,7 +20089,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G680" t="n">
-        <v>4.73229551315308</v>
+        <v>4.73229598999023</v>
       </c>
       <c r="H680" t="n">
         <v>23420</v>
@@ -20205,7 +20205,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G684" t="n">
-        <v>4.52482604980469</v>
+        <v>4.52482557296753</v>
       </c>
       <c r="H684" t="n">
         <v>1210</v>
@@ -20524,7 +20524,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G695" t="n">
-        <v>4.99904346466064</v>
+        <v>4.99904298782349</v>
       </c>
       <c r="H695" t="n">
         <v>25780</v>
@@ -20785,7 +20785,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G704" t="n">
-        <v>4.7421760559082</v>
+        <v>4.74217557907104</v>
       </c>
       <c r="H704" t="n">
         <v>5760</v>
@@ -20814,7 +20814,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G705" t="n">
-        <v>4.84097099304199</v>
+        <v>4.84097051620483</v>
       </c>
       <c r="H705" t="n">
         <v>1870</v>
@@ -20843,7 +20843,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G706" t="n">
-        <v>4.84097099304199</v>
+        <v>4.84097051620483</v>
       </c>
       <c r="H706" t="n">
         <v>0</v>
@@ -20872,7 +20872,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G707" t="n">
-        <v>4.85085010528564</v>
+        <v>4.8508505821228</v>
       </c>
       <c r="H707" t="n">
         <v>250</v>
@@ -20988,7 +20988,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G711" t="n">
-        <v>4.88048887252808</v>
+        <v>4.88048839569092</v>
       </c>
       <c r="H711" t="n">
         <v>1130</v>
@@ -21162,7 +21162,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G717" t="n">
-        <v>4.78169393539429</v>
+        <v>4.78169345855713</v>
       </c>
       <c r="H717" t="n">
         <v>2530</v>
@@ -21278,7 +21278,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G721" t="n">
-        <v>5.09783840179443</v>
+        <v>5.09783792495728</v>
       </c>
       <c r="H721" t="n">
         <v>3950</v>
@@ -21394,7 +21394,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G725" t="n">
-        <v>5.13735675811768</v>
+        <v>5.13735628128052</v>
       </c>
       <c r="H725" t="n">
         <v>3650</v>
@@ -21510,7 +21510,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G729" t="n">
-        <v>4.84097099304199</v>
+        <v>4.84097051620483</v>
       </c>
       <c r="H729" t="n">
         <v>2100</v>
@@ -21568,7 +21568,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G731" t="n">
-        <v>4.7421760559082</v>
+        <v>4.74217557907104</v>
       </c>
       <c r="H731" t="n">
         <v>2850</v>
@@ -21626,7 +21626,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G733" t="n">
-        <v>4.88048887252808</v>
+        <v>4.88048839569092</v>
       </c>
       <c r="H733" t="n">
         <v>7390</v>
@@ -21655,7 +21655,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G734" t="n">
-        <v>4.78169393539429</v>
+        <v>4.78169345855713</v>
       </c>
       <c r="H734" t="n">
         <v>2150</v>
@@ -21713,7 +21713,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G736" t="n">
-        <v>4.88048887252808</v>
+        <v>4.88048839569092</v>
       </c>
       <c r="H736" t="n">
         <v>3780</v>
@@ -21742,7 +21742,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G737" t="n">
-        <v>4.89036798477173</v>
+        <v>4.89036846160889</v>
       </c>
       <c r="H737" t="n">
         <v>3100</v>
@@ -21887,7 +21887,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G742" t="n">
-        <v>4.84097099304199</v>
+        <v>4.84097051620483</v>
       </c>
       <c r="H742" t="n">
         <v>8310</v>
@@ -21916,7 +21916,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G743" t="n">
-        <v>4.85085010528564</v>
+        <v>4.8508505821228</v>
       </c>
       <c r="H743" t="n">
         <v>3070</v>
@@ -22032,7 +22032,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G747" t="n">
-        <v>4.7421760559082</v>
+        <v>4.74217557907104</v>
       </c>
       <c r="H747" t="n">
         <v>63650</v>
@@ -22090,7 +22090,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G749" t="n">
-        <v>4.78169393539429</v>
+        <v>4.78169345855713</v>
       </c>
       <c r="H749" t="n">
         <v>10810</v>
@@ -22177,7 +22177,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G752" t="n">
-        <v>4.22843980789185</v>
+        <v>4.22843933105469</v>
       </c>
       <c r="H752" t="n">
         <v>104770</v>
@@ -22409,7 +22409,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G760" t="n">
-        <v>4.16916275024414</v>
+        <v>4.16916227340698</v>
       </c>
       <c r="H760" t="n">
         <v>13670</v>
@@ -22438,7 +22438,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G761" t="n">
-        <v>4.16916275024414</v>
+        <v>4.16916227340698</v>
       </c>
       <c r="H761" t="n">
         <v>5710</v>
@@ -22496,7 +22496,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G763" t="n">
-        <v>4.05060815811157</v>
+        <v>4.05060768127441</v>
       </c>
       <c r="H763" t="n">
         <v>55200</v>
@@ -22525,7 +22525,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G764" t="n">
-        <v>4.02096939086914</v>
+        <v>4.0209698677063</v>
       </c>
       <c r="H764" t="n">
         <v>16670</v>
@@ -23163,7 +23163,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G786" t="n">
-        <v>3.96169257164001</v>
+        <v>3.96169233322144</v>
       </c>
       <c r="H786" t="n">
         <v>3050</v>
@@ -23192,7 +23192,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G787" t="n">
-        <v>4.03084945678711</v>
+        <v>4.03084897994995</v>
       </c>
       <c r="H787" t="n">
         <v>5350</v>
@@ -23250,7 +23250,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G789" t="n">
-        <v>3.92217397689819</v>
+        <v>3.92217421531677</v>
       </c>
       <c r="H789" t="n">
         <v>12190</v>
@@ -49240,6 +49240,35 @@
         <v>16984</v>
       </c>
       <c r="I1685" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1686">
+      <c r="A1686" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1686" s="1" t="n">
+        <v>46325.3333333333</v>
+      </c>
+      <c r="C1686" t="n">
+        <v>3.17499995231628</v>
+      </c>
+      <c r="D1686" t="n">
+        <v>3.26500010490417</v>
+      </c>
+      <c r="E1686" t="n">
+        <v>3.10999989509583</v>
+      </c>
+      <c r="F1686" t="n">
+        <v>3.24000000953674</v>
+      </c>
+      <c r="G1686" t="n">
+        <v>3.24000000953674</v>
+      </c>
+      <c r="H1686" t="n">
+        <v>40411</v>
+      </c>
+      <c r="I1686" t="s">
         <v>9</v>
       </c>
     </row>
